--- a/data/50001541 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001541 - XEMORTIZ MINERA FRISCO.xlsx
@@ -2275,13 +2275,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46132.42191706019</v>
+        <v>46132.58858372685</v>
       </c>
       <c r="C4" s="5">
-        <v>46133.721585057865</v>
+        <v>46133.88825172454</v>
       </c>
       <c r="D4" s="5">
-        <v>46134.37518803241</v>
+        <v>46134.54185469907</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -2324,13 +2324,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46132.421995972225</v>
+        <v>46132.58866263889</v>
       </c>
       <c r="C5" s="8">
-        <v>46140.46108958333</v>
+        <v>46140.62775625</v>
       </c>
       <c r="D5" s="8">
-        <v>46140.46121216435</v>
+        <v>46140.627878831016</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -2389,13 +2389,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46132.421999074075</v>
+        <v>46132.58866574074</v>
       </c>
       <c r="C6" s="5">
-        <v>46133.72485732639</v>
+        <v>46133.89152399305</v>
       </c>
       <c r="D6" s="5">
-        <v>46133.7248587037</v>
+        <v>46133.891525370374</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -2454,13 +2454,13 @@
         <v>36</v>
       </c>
       <c r="B7" s="8">
-        <v>46132.422001747684</v>
+        <v>46132.58866841435</v>
       </c>
       <c r="C7" s="8">
-        <v>46133.72662366898</v>
+        <v>46133.89329033565</v>
       </c>
       <c r="D7" s="8">
-        <v>46133.72662489583</v>
+        <v>46133.893291562505</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>37</v>
@@ -2519,13 +2519,13 @@
         <v>38</v>
       </c>
       <c r="B8" s="5">
-        <v>46132.42200439815</v>
+        <v>46132.58867106482</v>
       </c>
       <c r="C8" s="5">
-        <v>46133.72662822917</v>
+        <v>46133.89329489583</v>
       </c>
       <c r="D8" s="5">
-        <v>46133.726629675926</v>
+        <v>46133.89329634259</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>39</v>
@@ -2584,13 +2584,13 @@
         <v>41</v>
       </c>
       <c r="B9" s="8">
-        <v>46132.422007824076</v>
+        <v>46132.58867449074</v>
       </c>
       <c r="C9" s="8">
-        <v>46133.72663559028</v>
+        <v>46133.89330225694</v>
       </c>
       <c r="D9" s="8">
-        <v>46133.726636956024</v>
+        <v>46133.89330362268</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>42</v>
@@ -2649,11 +2649,11 @@
         <v>43</v>
       </c>
       <c r="B10" s="5">
-        <v>46132.42192311343</v>
+        <v>46132.58858978009</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46183.70357681713</v>
+        <v>46183.8702434838</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>44</v>
@@ -2696,13 +2696,13 @@
         <v>46</v>
       </c>
       <c r="B11" s="8">
-        <v>46132.422011620365</v>
+        <v>46132.58867828704</v>
       </c>
       <c r="C11" s="8">
-        <v>46183.70356657407</v>
+        <v>46183.87023324074</v>
       </c>
       <c r="D11" s="8">
-        <v>46183.703586331016</v>
+        <v>46183.87025299769</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>47</v>
@@ -2761,13 +2761,13 @@
         <v>49</v>
       </c>
       <c r="B12" s="5">
-        <v>46132.42201688657</v>
+        <v>46132.588683553244</v>
       </c>
       <c r="C12" s="5">
-        <v>46157.374976990744</v>
+        <v>46157.54164365741</v>
       </c>
       <c r="D12" s="5">
-        <v>46157.37499372685</v>
+        <v>46157.541660393515</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>50</v>
@@ -2826,13 +2826,13 @@
         <v>52</v>
       </c>
       <c r="B13" s="8">
-        <v>46132.422022071754</v>
+        <v>46132.588688738426</v>
       </c>
       <c r="C13" s="8">
-        <v>46175.561882766204</v>
+        <v>46175.72854943287</v>
       </c>
       <c r="D13" s="8">
-        <v>46175.561901319445</v>
+        <v>46175.72856798611</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>53</v>
@@ -2891,11 +2891,11 @@
         <v>55</v>
       </c>
       <c r="B14" s="5">
-        <v>46132.42202712963</v>
+        <v>46132.58869379629</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46142.01959041666</v>
+        <v>46142.18625708333</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>56</v>
@@ -2954,11 +2954,11 @@
         <v>59</v>
       </c>
       <c r="B15" s="8">
-        <v>46132.42192842593</v>
+        <v>46132.58859509259</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="8">
-        <v>46183.70366184028</v>
+        <v>46183.87032850695</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>60</v>
@@ -3003,13 +3003,13 @@
         <v>62</v>
       </c>
       <c r="B16" s="5">
-        <v>46132.422032291666</v>
+        <v>46132.58869895834</v>
       </c>
       <c r="C16" s="5">
-        <v>46157.37661576389</v>
+        <v>46157.54328243056</v>
       </c>
       <c r="D16" s="5">
-        <v>46157.37663075232</v>
+        <v>46157.54329741898</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>63</v>
@@ -3068,13 +3068,13 @@
         <v>65</v>
       </c>
       <c r="B17" s="8">
-        <v>46132.42203732639</v>
+        <v>46132.58870399305</v>
       </c>
       <c r="C17" s="8">
-        <v>46157.37509891204</v>
+        <v>46157.5417655787</v>
       </c>
       <c r="D17" s="8">
-        <v>46157.37511559028</v>
+        <v>46157.54178225694</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>66</v>
@@ -3133,13 +3133,13 @@
         <v>69</v>
       </c>
       <c r="B18" s="5">
-        <v>46132.42204243055</v>
+        <v>46132.588709097225</v>
       </c>
       <c r="C18" s="5">
-        <v>46183.70363614583</v>
+        <v>46183.8703028125</v>
       </c>
       <c r="D18" s="5">
-        <v>46183.703653275465</v>
+        <v>46183.87031994213</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>70</v>
@@ -3198,13 +3198,13 @@
         <v>72</v>
       </c>
       <c r="B19" s="8">
-        <v>46132.42204715278</v>
+        <v>46132.588713819445</v>
       </c>
       <c r="C19" s="8">
-        <v>46140.459930682875</v>
+        <v>46140.62659734953</v>
       </c>
       <c r="D19" s="8">
-        <v>46169.01362467592</v>
+        <v>46169.18029134259</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>73</v>
@@ -3263,13 +3263,13 @@
         <v>79</v>
       </c>
       <c r="B20" s="5">
-        <v>46132.461424375</v>
+        <v>46132.62809104167</v>
       </c>
       <c r="C20" s="5">
-        <v>46140.459872314816</v>
+        <v>46140.62653898148</v>
       </c>
       <c r="D20" s="5">
-        <v>46169.01362454861</v>
+        <v>46169.18029121528</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>80</v>
@@ -3328,11 +3328,11 @@
         <v>82</v>
       </c>
       <c r="B21" s="8">
-        <v>46132.46132069445</v>
+        <v>46132.62798736111</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="8">
-        <v>46169.69144738426</v>
+        <v>46169.85811405093</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>83</v>
@@ -3391,13 +3391,13 @@
         <v>85</v>
       </c>
       <c r="B22" s="5">
-        <v>46132.461378645836</v>
+        <v>46132.6280453125</v>
       </c>
       <c r="C22" s="5">
-        <v>46140.459785416664</v>
+        <v>46140.626452083336</v>
       </c>
       <c r="D22" s="5">
-        <v>46169.013624618055</v>
+        <v>46169.18029128472</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>86</v>
@@ -3456,11 +3456,11 @@
         <v>88</v>
       </c>
       <c r="B23" s="8">
-        <v>46132.42193364583</v>
+        <v>46132.588600312505</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="8">
-        <v>46157.376429780095</v>
+        <v>46157.54309644676</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>89</v>
@@ -3503,13 +3503,13 @@
         <v>91</v>
       </c>
       <c r="B24" s="5">
-        <v>46132.42205288194</v>
+        <v>46132.588719548614</v>
       </c>
       <c r="C24" s="5">
-        <v>46157.376424131944</v>
+        <v>46157.543090798616</v>
       </c>
       <c r="D24" s="5">
-        <v>46157.376913182874</v>
+        <v>46157.54357984954</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>92</v>
@@ -3568,13 +3568,13 @@
         <v>96</v>
       </c>
       <c r="B25" s="8">
-        <v>46132.42205756945</v>
+        <v>46132.588724236106</v>
       </c>
       <c r="C25" s="8">
-        <v>46157.37668335648</v>
+        <v>46157.543350023145</v>
       </c>
       <c r="D25" s="8">
-        <v>46157.37668490741</v>
+        <v>46157.54335157407</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>97</v>
@@ -3629,13 +3629,13 @@
         <v>102</v>
       </c>
       <c r="B26" s="5">
-        <v>46132.42206225694</v>
+        <v>46132.58872892361</v>
       </c>
       <c r="C26" s="5">
-        <v>46157.37672043982</v>
+        <v>46157.54338710648</v>
       </c>
       <c r="D26" s="5">
-        <v>46157.376721759254</v>
+        <v>46157.543388425926</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>103</v>
@@ -3690,13 +3690,13 @@
         <v>105</v>
       </c>
       <c r="B27" s="8">
-        <v>46132.422067314816</v>
+        <v>46132.58873398148</v>
       </c>
       <c r="C27" s="8">
-        <v>46157.37520400463</v>
+        <v>46157.541870671295</v>
       </c>
       <c r="D27" s="8">
-        <v>46162.00908238426</v>
+        <v>46162.175749050926</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>106</v>
@@ -3755,13 +3755,13 @@
         <v>108</v>
       </c>
       <c r="B28" s="5">
-        <v>46132.4220722801</v>
+        <v>46132.58873894676</v>
       </c>
       <c r="C28" s="5">
-        <v>46157.37514805555</v>
+        <v>46157.54181472222</v>
       </c>
       <c r="D28" s="5">
-        <v>46157.375149988424</v>
+        <v>46157.541816655095</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>109</v>
@@ -3816,13 +3816,13 @@
         <v>111</v>
       </c>
       <c r="B29" s="8">
-        <v>46132.422077256946</v>
+        <v>46132.58874392361</v>
       </c>
       <c r="C29" s="8">
-        <v>46157.3751890162</v>
+        <v>46157.541855682866</v>
       </c>
       <c r="D29" s="8">
-        <v>46157.37519023148</v>
+        <v>46157.54185689815</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>112</v>
@@ -3877,11 +3877,11 @@
         <v>114</v>
       </c>
       <c r="B30" s="5">
-        <v>46132.42208211806</v>
+        <v>46132.58874878472</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46185.35326605324</v>
+        <v>46185.51993271991</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>115</v>
@@ -3940,11 +3940,11 @@
         <v>117</v>
       </c>
       <c r="B31" s="8">
-        <v>46132.42208668981</v>
+        <v>46132.58875335648</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="8">
-        <v>46183.703653460645</v>
+        <v>46183.87032012732</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>118</v>
@@ -3999,11 +3999,11 @@
         <v>120</v>
       </c>
       <c r="B32" s="5">
-        <v>46132.42209600694</v>
+        <v>46132.58876267361</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46169.691606203705</v>
+        <v>46169.85827287037</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>121</v>
@@ -4058,11 +4058,11 @@
         <v>124</v>
       </c>
       <c r="B33" s="8">
-        <v>46132.42209122685</v>
+        <v>46132.58875789352</v>
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="8">
-        <v>46175.001791574075</v>
+        <v>46175.16845824074</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>122</v>
@@ -4117,13 +4117,13 @@
         <v>126</v>
       </c>
       <c r="B34" s="5">
-        <v>46132.42210037037</v>
+        <v>46132.588767037036</v>
       </c>
       <c r="C34" s="5">
-        <v>46140.460326030094</v>
+        <v>46140.62699269676</v>
       </c>
       <c r="D34" s="5">
-        <v>46178.00184576389</v>
+        <v>46178.16851243055</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>127</v>
@@ -4182,13 +4182,13 @@
         <v>131</v>
       </c>
       <c r="B35" s="8">
-        <v>46132.42210472222</v>
+        <v>46132.58877138889</v>
       </c>
       <c r="C35" s="8">
-        <v>46140.460234004626</v>
+        <v>46140.6269006713</v>
       </c>
       <c r="D35" s="8">
-        <v>46140.46023538194</v>
+        <v>46140.62690204861</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>132</v>
@@ -4243,13 +4243,13 @@
         <v>134</v>
       </c>
       <c r="B36" s="5">
-        <v>46132.42210923611</v>
+        <v>46132.58877590278</v>
       </c>
       <c r="C36" s="5">
-        <v>46140.460271655094</v>
+        <v>46140.62693832176</v>
       </c>
       <c r="D36" s="5">
-        <v>46140.460273703706</v>
+        <v>46140.62694037037</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>135</v>
@@ -4304,13 +4304,13 @@
         <v>137</v>
       </c>
       <c r="B37" s="8">
-        <v>46132.46017288194</v>
+        <v>46132.62683954861</v>
       </c>
       <c r="C37" s="8">
-        <v>46140.46030037037</v>
+        <v>46140.62696703704</v>
       </c>
       <c r="D37" s="8">
-        <v>46178.001846875</v>
+        <v>46178.16851354166</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>138</v>
@@ -4369,13 +4369,13 @@
         <v>140</v>
       </c>
       <c r="B38" s="5">
-        <v>46132.46046269676</v>
+        <v>46132.62712936343</v>
       </c>
       <c r="C38" s="5">
-        <v>46140.46011893518</v>
+        <v>46140.62678560185</v>
       </c>
       <c r="D38" s="5">
-        <v>46140.46012013889</v>
+        <v>46140.62678680556</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>81</v>
@@ -4424,13 +4424,13 @@
         <v>142</v>
       </c>
       <c r="B39" s="8">
-        <v>46132.46060174768</v>
+        <v>46132.62726841435</v>
       </c>
       <c r="C39" s="8">
-        <v>46140.46015943287</v>
+        <v>46140.62682609954</v>
       </c>
       <c r="D39" s="8">
-        <v>46140.4601606713</v>
+        <v>46140.62682733797</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>143</v>
@@ -4479,13 +4479,13 @@
         <v>145</v>
       </c>
       <c r="B40" s="5">
-        <v>46132.46030399305</v>
+        <v>46132.62697065972</v>
       </c>
       <c r="C40" s="5">
-        <v>46147.73109282408</v>
+        <v>46147.89775949074</v>
       </c>
       <c r="D40" s="5">
-        <v>46178.0018456713</v>
+        <v>46178.16851233796</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>146</v>
@@ -4544,13 +4544,13 @@
         <v>148</v>
       </c>
       <c r="B41" s="8">
-        <v>46132.46086706019</v>
+        <v>46132.62753372685</v>
       </c>
       <c r="C41" s="8">
-        <v>46140.46041891204</v>
+        <v>46140.6270855787</v>
       </c>
       <c r="D41" s="8">
-        <v>46140.46042069445</v>
+        <v>46140.62708736111</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>87</v>
@@ -4599,13 +4599,13 @@
         <v>150</v>
       </c>
       <c r="B42" s="5">
-        <v>46132.46094913194</v>
+        <v>46132.627615798614</v>
       </c>
       <c r="C42" s="5">
-        <v>46147.731079641206</v>
+        <v>46147.89774630787</v>
       </c>
       <c r="D42" s="5">
-        <v>46147.731081307866</v>
+        <v>46147.89774797454</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>151</v>
@@ -4654,11 +4654,11 @@
         <v>153</v>
       </c>
       <c r="B43" s="8">
-        <v>46132.421939837965</v>
+        <v>46132.58860650463</v>
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="8">
-        <v>46175.56199270833</v>
+        <v>46175.728659375</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>154</v>
@@ -4701,13 +4701,13 @@
         <v>156</v>
       </c>
       <c r="B44" s="5">
-        <v>46132.42217290509</v>
+        <v>46132.58883957176</v>
       </c>
       <c r="C44" s="5">
-        <v>46175.56198648148</v>
+        <v>46175.72865314815</v>
       </c>
       <c r="D44" s="5">
-        <v>46175.56200251158</v>
+        <v>46175.728669178236</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>157</v>
@@ -4766,11 +4766,11 @@
         <v>161</v>
       </c>
       <c r="B45" s="8">
-        <v>46132.42218010417</v>
+        <v>46132.58884677083</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="8">
-        <v>46177.4615522338</v>
+        <v>46177.62821890046</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>162</v>
@@ -4829,11 +4829,11 @@
         <v>165</v>
       </c>
       <c r="B46" s="5">
-        <v>46132.42218681713</v>
+        <v>46132.5888534838</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46177.465265798615</v>
+        <v>46177.63193246528</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>76</v>
@@ -4890,11 +4890,11 @@
         <v>167</v>
       </c>
       <c r="B47" s="8">
-        <v>46132.42219435185</v>
+        <v>46132.58886101852</v>
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="8">
-        <v>46134.413910613424</v>
+        <v>46134.580577280096</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>168</v>
@@ -4951,11 +4951,11 @@
         <v>172</v>
       </c>
       <c r="B48" s="5">
-        <v>46132.46788423611</v>
+        <v>46132.634550902774</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46134.41324927083</v>
+        <v>46134.5799159375</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>173</v>
@@ -5002,11 +5002,11 @@
         <v>176</v>
       </c>
       <c r="B49" s="8">
-        <v>46132.46789189815</v>
+        <v>46132.634558564816</v>
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="8">
-        <v>46181.442566365746</v>
+        <v>46181.6092330324</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>177</v>
@@ -5053,11 +5053,11 @@
         <v>179</v>
       </c>
       <c r="B50" s="5">
-        <v>46132.46790087963</v>
+        <v>46132.634567546294</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46155.41676506944</v>
+        <v>46155.583431736115</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>180</v>
@@ -5104,11 +5104,11 @@
         <v>181</v>
       </c>
       <c r="B51" s="8">
-        <v>46132.46790520834</v>
+        <v>46132.634571875</v>
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="8">
-        <v>46134.41334626157</v>
+        <v>46134.58001292824</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>182</v>
@@ -5155,11 +5155,11 @@
         <v>183</v>
       </c>
       <c r="B52" s="5">
-        <v>46132.467911053245</v>
+        <v>46132.6345777199</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46168.64152829861</v>
+        <v>46168.80819496528</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>184</v>
@@ -5206,11 +5206,11 @@
         <v>185</v>
       </c>
       <c r="B53" s="8">
-        <v>46132.4679154051</v>
+        <v>46132.634582071754</v>
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="8">
-        <v>46134.413405949075</v>
+        <v>46134.58007261574</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>186</v>
@@ -5257,11 +5257,11 @@
         <v>187</v>
       </c>
       <c r="B54" s="5">
-        <v>46132.46791936342</v>
+        <v>46132.63458603009</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46162.6287241088</v>
+        <v>46162.79539077546</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>188</v>
@@ -5308,11 +5308,11 @@
         <v>190</v>
       </c>
       <c r="B55" s="8">
-        <v>46132.46792502315</v>
+        <v>46132.63459168981</v>
       </c>
       <c r="C55" s="9"/>
       <c r="D55" s="8">
-        <v>46134.413466412036</v>
+        <v>46134.58013307871</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>191</v>
@@ -5359,11 +5359,11 @@
         <v>192</v>
       </c>
       <c r="B56" s="5">
-        <v>46132.46793042824</v>
+        <v>46132.634597094904</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46134.41350059028</v>
+        <v>46134.58016725694</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>193</v>
@@ -5410,11 +5410,11 @@
         <v>194</v>
       </c>
       <c r="B57" s="8">
-        <v>46132.46793587963</v>
+        <v>46132.6346025463</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46134.413528414356</v>
+        <v>46134.58019508102</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>195</v>
@@ -5461,11 +5461,11 @@
         <v>196</v>
       </c>
       <c r="B58" s="5">
-        <v>46132.46800738426</v>
+        <v>46132.634674050925</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46134.413658425925</v>
+        <v>46134.5803250926</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>197</v>
@@ -5512,11 +5512,11 @@
         <v>198</v>
       </c>
       <c r="B59" s="8">
-        <v>46132.468022326386</v>
+        <v>46132.63468899306</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46134.41369050926</v>
+        <v>46134.580357175924</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>199</v>
@@ -5563,11 +5563,11 @@
         <v>200</v>
       </c>
       <c r="B60" s="5">
-        <v>46132.46804099537</v>
+        <v>46132.63470766204</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46134.41372877314</v>
+        <v>46134.580395439814</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>201</v>
@@ -5614,11 +5614,11 @@
         <v>202</v>
       </c>
       <c r="B61" s="8">
-        <v>46132.46805321759</v>
+        <v>46132.634719884256</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46134.41376473379</v>
+        <v>46134.58043140046</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>203</v>
@@ -5665,11 +5665,11 @@
         <v>204</v>
       </c>
       <c r="B62" s="5">
-        <v>46132.46806118055</v>
+        <v>46132.634727847224</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46134.41379980324</v>
+        <v>46134.58046646991</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>205</v>
@@ -5716,11 +5716,11 @@
         <v>206</v>
       </c>
       <c r="B63" s="8">
-        <v>46132.46794055555</v>
+        <v>46132.63460722222</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46134.413910787036</v>
+        <v>46134.5805774537</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>207</v>
@@ -5767,13 +5767,13 @@
         <v>209</v>
       </c>
       <c r="B64" s="5">
-        <v>46132.48055251157</v>
+        <v>46132.64721917824</v>
       </c>
       <c r="C64" s="5">
-        <v>46157.32731126157</v>
+        <v>46157.49397792824</v>
       </c>
       <c r="D64" s="5">
-        <v>46157.3273225</v>
+        <v>46157.493989166665</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>210</v>
@@ -5820,13 +5820,13 @@
         <v>212</v>
       </c>
       <c r="B65" s="8">
-        <v>46132.45817625</v>
+        <v>46132.624842916666</v>
       </c>
       <c r="C65" s="8">
-        <v>46157.32715798611</v>
+        <v>46157.493824652774</v>
       </c>
       <c r="D65" s="8">
-        <v>46182.01687796296</v>
+        <v>46182.18354462963</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>213</v>
@@ -5885,13 +5885,13 @@
         <v>215</v>
       </c>
       <c r="B66" s="5">
-        <v>46132.45824061343</v>
+        <v>46132.62490728009</v>
       </c>
       <c r="C66" s="5">
-        <v>46157.327186828705</v>
+        <v>46157.49385349537</v>
       </c>
       <c r="D66" s="5">
-        <v>46182.01687792824</v>
+        <v>46182.18354459491</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>216</v>
@@ -5950,13 +5950,13 @@
         <v>218</v>
       </c>
       <c r="B67" s="8">
-        <v>46132.45828695602</v>
+        <v>46132.62495362268</v>
       </c>
       <c r="C67" s="8">
-        <v>46157.32720113426</v>
+        <v>46157.49386780093</v>
       </c>
       <c r="D67" s="8">
-        <v>46182.01687810185</v>
+        <v>46182.183544768515</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>219</v>
@@ -6015,13 +6015,13 @@
         <v>221</v>
       </c>
       <c r="B68" s="5">
-        <v>46132.54075635417</v>
+        <v>46132.70742302084</v>
       </c>
       <c r="C68" s="5">
-        <v>46157.32728145833</v>
+        <v>46157.493948125004</v>
       </c>
       <c r="D68" s="5">
-        <v>46184.03642771991</v>
+        <v>46184.203094386576</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>222</v>
@@ -6080,13 +6080,13 @@
         <v>226</v>
       </c>
       <c r="B69" s="8">
-        <v>46132.5408630787</v>
+        <v>46132.70752974537</v>
       </c>
       <c r="C69" s="8">
-        <v>46157.32728627315</v>
+        <v>46157.49395293981</v>
       </c>
       <c r="D69" s="8">
-        <v>46184.036431354165</v>
+        <v>46184.20309802084</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>227</v>
@@ -6145,13 +6145,13 @@
         <v>229</v>
       </c>
       <c r="B70" s="5">
-        <v>46132.540933842596</v>
+        <v>46132.70760050926</v>
       </c>
       <c r="C70" s="5">
-        <v>46157.32729354167</v>
+        <v>46157.49396020833</v>
       </c>
       <c r="D70" s="5">
-        <v>46184.03642754629</v>
+        <v>46184.203094212964</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>230</v>
@@ -6210,11 +6210,11 @@
         <v>231</v>
       </c>
       <c r="B71" s="8">
-        <v>46132.42221524306</v>
+        <v>46132.58888190972</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46132.62330640046</v>
+        <v>46132.789973067134</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>232</v>
@@ -6257,11 +6257,11 @@
         <v>234</v>
       </c>
       <c r="B72" s="5">
-        <v>46132.42221851852</v>
+        <v>46132.588885185185</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46178.002987245374</v>
+        <v>46178.16965391204</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>84</v>
@@ -6320,11 +6320,11 @@
         <v>238</v>
       </c>
       <c r="B73" s="8">
-        <v>46132.422223761576</v>
+        <v>46132.58889042824</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46134.40117913194</v>
+        <v>46134.56784579861</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>239</v>
@@ -6383,11 +6383,11 @@
         <v>241</v>
       </c>
       <c r="B74" s="5">
-        <v>46132.46461180555</v>
+        <v>46132.631278472225</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46157.32730230324</v>
+        <v>46157.49396896991</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>174</v>
@@ -6436,11 +6436,11 @@
         <v>244</v>
       </c>
       <c r="B75" s="8">
-        <v>46132.46462783565</v>
+        <v>46132.63129450232</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46157.327304756946</v>
+        <v>46157.49397142361</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>174</v>
@@ -6489,11 +6489,11 @@
         <v>245</v>
       </c>
       <c r="B76" s="5">
-        <v>46132.46463585648</v>
+        <v>46132.63130252315</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46157.32730266204</v>
+        <v>46157.4939693287</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>174</v>
@@ -6542,11 +6542,11 @@
         <v>248</v>
       </c>
       <c r="B77" s="8">
-        <v>46132.46464202546</v>
+        <v>46132.63130869213</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46157.32730608796</v>
+        <v>46157.49397275463</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>174</v>
@@ -6595,11 +6595,11 @@
         <v>249</v>
       </c>
       <c r="B78" s="5">
-        <v>46132.46464780092</v>
+        <v>46132.631314467595</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46157.327305439816</v>
+        <v>46157.49397210648</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>174</v>
@@ -6648,11 +6648,11 @@
         <v>251</v>
       </c>
       <c r="B79" s="8">
-        <v>46132.46465391204</v>
+        <v>46132.6313205787</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46157.32730369213</v>
+        <v>46157.493970358795</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>174</v>
@@ -6701,11 +6701,11 @@
         <v>253</v>
       </c>
       <c r="B80" s="5">
-        <v>46132.46465927083</v>
+        <v>46132.6313259375</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46157.32730576389</v>
+        <v>46157.49397243056</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>174</v>
@@ -6754,11 +6754,11 @@
         <v>255</v>
       </c>
       <c r="B81" s="8">
-        <v>46132.46466375</v>
+        <v>46132.63133041667</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46157.32730392361</v>
+        <v>46157.49397059028</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>174</v>
@@ -6807,11 +6807,11 @@
         <v>257</v>
       </c>
       <c r="B82" s="5">
-        <v>46132.46466979166</v>
+        <v>46132.63133645833</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46157.3273044213</v>
+        <v>46157.49397108796</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>174</v>
@@ -6860,11 +6860,11 @@
         <v>258</v>
       </c>
       <c r="B83" s="8">
-        <v>46132.46467407407</v>
+        <v>46132.63134074074</v>
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46157.32730585648</v>
+        <v>46157.49397252315</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>174</v>
@@ -6913,11 +6913,11 @@
         <v>260</v>
       </c>
       <c r="B84" s="5">
-        <v>46132.46467980324</v>
+        <v>46132.631346469905</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46157.327305081024</v>
+        <v>46157.49397174768</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>174</v>
@@ -6966,11 +6966,11 @@
         <v>261</v>
       </c>
       <c r="B85" s="8">
-        <v>46132.464685416664</v>
+        <v>46132.631352083336</v>
       </c>
       <c r="C85" s="9"/>
       <c r="D85" s="8">
-        <v>46157.32730644676</v>
+        <v>46157.49397311342</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>174</v>
@@ -7019,11 +7019,11 @@
         <v>262</v>
       </c>
       <c r="B86" s="5">
-        <v>46132.464691099536</v>
+        <v>46132.63135776621</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46157.32730335648</v>
+        <v>46157.49397002315</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>174</v>
@@ -7072,11 +7072,11 @@
         <v>263</v>
       </c>
       <c r="B87" s="8">
-        <v>46132.4646962963</v>
+        <v>46132.63136296296</v>
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="8">
-        <v>46157.32730302084</v>
+        <v>46157.4939696875</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>174</v>
@@ -7125,11 +7125,11 @@
         <v>265</v>
       </c>
       <c r="B88" s="5">
-        <v>46132.464700219905</v>
+        <v>46132.63136688658</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46157.327306747684</v>
+        <v>46157.493973414355</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>174</v>
@@ -7178,11 +7178,11 @@
         <v>267</v>
       </c>
       <c r="B89" s="8">
-        <v>46132.464705729166</v>
+        <v>46132.63137239583</v>
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="8">
-        <v>46157.327304085644</v>
+        <v>46157.493970752315</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>174</v>
@@ -7231,11 +7231,11 @@
         <v>268</v>
       </c>
       <c r="B90" s="5">
-        <v>46132.42223142361</v>
+        <v>46132.58889809028</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46134.40120248843</v>
+        <v>46134.56786915509</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>269</v>
@@ -7294,11 +7294,11 @@
         <v>271</v>
       </c>
       <c r="B91" s="8">
-        <v>46132.46481228009</v>
+        <v>46132.63147894676</v>
       </c>
       <c r="C91" s="9"/>
       <c r="D91" s="8">
-        <v>46133.73443402778</v>
+        <v>46133.90110069445</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>272</v>
@@ -7347,11 +7347,11 @@
         <v>275</v>
       </c>
       <c r="B92" s="5">
-        <v>46132.46482415509</v>
+        <v>46132.63149082176</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46133.73445847222</v>
+        <v>46133.90112513889</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>272</v>
@@ -7400,11 +7400,11 @@
         <v>277</v>
       </c>
       <c r="B93" s="8">
-        <v>46132.464830474535</v>
+        <v>46132.63149714121</v>
       </c>
       <c r="C93" s="9"/>
       <c r="D93" s="8">
-        <v>46133.734481273146</v>
+        <v>46133.90114793982</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>272</v>
@@ -7453,11 +7453,11 @@
         <v>278</v>
       </c>
       <c r="B94" s="5">
-        <v>46132.464836134255</v>
+        <v>46132.63150280093</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46133.7345087037</v>
+        <v>46133.90117537037</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>272</v>
@@ -7506,11 +7506,11 @@
         <v>279</v>
       </c>
       <c r="B95" s="8">
-        <v>46132.464842291665</v>
+        <v>46132.63150895834</v>
       </c>
       <c r="C95" s="9"/>
       <c r="D95" s="8">
-        <v>46133.73453538194</v>
+        <v>46133.90120204861</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>272</v>
@@ -7559,11 +7559,11 @@
         <v>280</v>
       </c>
       <c r="B96" s="5">
-        <v>46132.464847662035</v>
+        <v>46132.63151432871</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46133.734566747684</v>
+        <v>46133.90123341435</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>272</v>
@@ -7612,11 +7612,11 @@
         <v>281</v>
       </c>
       <c r="B97" s="8">
-        <v>46132.4648528588</v>
+        <v>46132.631519525465</v>
       </c>
       <c r="C97" s="9"/>
       <c r="D97" s="8">
-        <v>46133.73459518519</v>
+        <v>46133.90126185185</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>272</v>
@@ -7665,11 +7665,11 @@
         <v>282</v>
       </c>
       <c r="B98" s="5">
-        <v>46132.46485758101</v>
+        <v>46132.631524247685</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46133.734618622686</v>
+        <v>46133.90128528935</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>272</v>
@@ -7718,11 +7718,11 @@
         <v>283</v>
       </c>
       <c r="B99" s="8">
-        <v>46132.464864837966</v>
+        <v>46132.63153150463</v>
       </c>
       <c r="C99" s="9"/>
       <c r="D99" s="8">
-        <v>46133.73464377315</v>
+        <v>46133.90131043982</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>272</v>
@@ -7771,11 +7771,11 @@
         <v>284</v>
       </c>
       <c r="B100" s="5">
-        <v>46132.46487260416</v>
+        <v>46132.631539270835</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46133.73467363426</v>
+        <v>46133.90134030093</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>272</v>
@@ -7824,11 +7824,11 @@
         <v>285</v>
       </c>
       <c r="B101" s="8">
-        <v>46132.46487950231</v>
+        <v>46132.63154616898</v>
       </c>
       <c r="C101" s="9"/>
       <c r="D101" s="8">
-        <v>46133.73469883102</v>
+        <v>46133.90136549769</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>272</v>
@@ -7877,11 +7877,11 @@
         <v>286</v>
       </c>
       <c r="B102" s="5">
-        <v>46132.46488840278</v>
+        <v>46132.63155506944</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46133.73473527777</v>
+        <v>46133.901401944444</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>272</v>
@@ -7930,11 +7930,11 @@
         <v>287</v>
       </c>
       <c r="B103" s="8">
-        <v>46132.464897557875</v>
+        <v>46132.63156422453</v>
       </c>
       <c r="C103" s="9"/>
       <c r="D103" s="8">
-        <v>46133.73475856481</v>
+        <v>46133.90142523148</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>272</v>
@@ -7983,11 +7983,11 @@
         <v>288</v>
       </c>
       <c r="B104" s="5">
-        <v>46132.46490584491</v>
+        <v>46132.63157251157</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46133.734785347224</v>
+        <v>46133.90145201389</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>272</v>
@@ -8036,11 +8036,11 @@
         <v>289</v>
       </c>
       <c r="B105" s="8">
-        <v>46132.46490997685</v>
+        <v>46132.631576643515</v>
       </c>
       <c r="C105" s="9"/>
       <c r="D105" s="8">
-        <v>46133.734818125</v>
+        <v>46133.90148479167</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>174</v>
@@ -8089,11 +8089,11 @@
         <v>290</v>
       </c>
       <c r="B106" s="5">
-        <v>46132.46524119213</v>
+        <v>46132.6319078588</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46133.73485579861</v>
+        <v>46133.90152246528</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>272</v>
@@ -8142,11 +8142,11 @@
         <v>291</v>
       </c>
       <c r="B107" s="8">
-        <v>46132.42223726852</v>
+        <v>46132.58890393519</v>
       </c>
       <c r="C107" s="9"/>
       <c r="D107" s="8">
-        <v>46157.37538366899</v>
+        <v>46157.54205033564</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>292</v>
@@ -8189,11 +8189,11 @@
         <v>294</v>
       </c>
       <c r="B108" s="5">
-        <v>46132.42224050926</v>
+        <v>46132.58890717593</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46157.37673563657</v>
+        <v>46157.54340230324</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>295</v>
@@ -8250,13 +8250,13 @@
         <v>297</v>
       </c>
       <c r="B109" s="8">
-        <v>46132.42224613426</v>
+        <v>46132.58891280093</v>
       </c>
       <c r="C109" s="8">
-        <v>46157.37537709491</v>
+        <v>46157.542043761576</v>
       </c>
       <c r="D109" s="8">
-        <v>46163.022396562505</v>
+        <v>46163.18906322916</v>
       </c>
       <c r="E109" s="9" t="s">
         <v>298</v>
@@ -8313,11 +8313,11 @@
         <v>299</v>
       </c>
       <c r="B110" s="5">
-        <v>46132.42225142361</v>
+        <v>46132.588918090274</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46177.007650983796</v>
+        <v>46177.17431765047</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>300</v>
@@ -8374,11 +8374,11 @@
         <v>302</v>
       </c>
       <c r="B111" s="8">
-        <v>46132.422256446764</v>
+        <v>46132.58892311342</v>
       </c>
       <c r="C111" s="9"/>
       <c r="D111" s="8">
-        <v>46133.416960925926</v>
+        <v>46133.5836275926</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>303</v>
@@ -8421,11 +8421,11 @@
         <v>305</v>
       </c>
       <c r="B112" s="5">
-        <v>46132.42225991898</v>
+        <v>46132.58892658565</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46134.4124047338</v>
+        <v>46134.57907140046</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>306</v>
@@ -8484,11 +8484,11 @@
         <v>308</v>
       </c>
       <c r="B113" s="8">
-        <v>46132.465366516204</v>
+        <v>46132.632033182876</v>
       </c>
       <c r="C113" s="9"/>
       <c r="D113" s="8">
-        <v>46134.39993447917</v>
+        <v>46134.56660114584</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>174</v>
@@ -8537,11 +8537,11 @@
         <v>310</v>
       </c>
       <c r="B114" s="5">
-        <v>46132.465438645835</v>
+        <v>46132.6321053125</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46134.399953935186</v>
+        <v>46134.56662060185</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>272</v>
@@ -8590,11 +8590,11 @@
         <v>311</v>
       </c>
       <c r="B115" s="8">
-        <v>46132.46544728009</v>
+        <v>46132.63211394676</v>
       </c>
       <c r="C115" s="9"/>
       <c r="D115" s="8">
-        <v>46134.39999815972</v>
+        <v>46134.56666482639</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>272</v>
@@ -8643,11 +8643,11 @@
         <v>313</v>
       </c>
       <c r="B116" s="5">
-        <v>46132.46545552083</v>
+        <v>46132.6321221875</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46134.400052349534</v>
+        <v>46134.566719016206</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>174</v>
@@ -8696,11 +8696,11 @@
         <v>314</v>
       </c>
       <c r="B117" s="8">
-        <v>46132.465461631946</v>
+        <v>46132.63212829861</v>
       </c>
       <c r="C117" s="9"/>
       <c r="D117" s="8">
-        <v>46134.400101990745</v>
+        <v>46134.56676865741</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>174</v>
@@ -8749,11 +8749,11 @@
         <v>315</v>
       </c>
       <c r="B118" s="5">
-        <v>46132.465468587965</v>
+        <v>46132.63213525463</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46134.400161655096</v>
+        <v>46134.56682832176</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>174</v>
@@ -8802,11 +8802,11 @@
         <v>317</v>
       </c>
       <c r="B119" s="8">
-        <v>46132.46547675926</v>
+        <v>46132.63214342593</v>
       </c>
       <c r="C119" s="9"/>
       <c r="D119" s="8">
-        <v>46134.40018653935</v>
+        <v>46134.56685320602</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>272</v>
@@ -8855,11 +8855,11 @@
         <v>318</v>
       </c>
       <c r="B120" s="5">
-        <v>46132.465484479166</v>
+        <v>46132.63215114584</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46134.400209988424</v>
+        <v>46134.566876655095</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>174</v>
@@ -8908,11 +8908,11 @@
         <v>319</v>
       </c>
       <c r="B121" s="8">
-        <v>46132.46549349537</v>
+        <v>46132.63216016204</v>
       </c>
       <c r="C121" s="9"/>
       <c r="D121" s="8">
-        <v>46134.400229583334</v>
+        <v>46134.56689625</v>
       </c>
       <c r="E121" s="9" t="s">
         <v>174</v>
@@ -8961,11 +8961,11 @@
         <v>320</v>
       </c>
       <c r="B122" s="5">
-        <v>46132.465507974535</v>
+        <v>46132.6321746412</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46134.40025510416</v>
+        <v>46134.566921770835</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>272</v>
@@ -9014,11 +9014,11 @@
         <v>321</v>
       </c>
       <c r="B123" s="8">
-        <v>46132.4655005324</v>
+        <v>46132.63216719907</v>
       </c>
       <c r="C123" s="9"/>
       <c r="D123" s="8">
-        <v>46134.4002772338</v>
+        <v>46134.56694390046</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>174</v>
@@ -9067,11 +9067,11 @@
         <v>322</v>
       </c>
       <c r="B124" s="5">
-        <v>46132.46551407407</v>
+        <v>46132.63218074074</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46134.40030488426</v>
+        <v>46134.56697155093</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>174</v>
@@ -9120,11 +9120,11 @@
         <v>323</v>
       </c>
       <c r="B125" s="8">
-        <v>46132.465520196754</v>
+        <v>46132.632186863426</v>
       </c>
       <c r="C125" s="9"/>
       <c r="D125" s="8">
-        <v>46134.40034331019</v>
+        <v>46134.56700997685</v>
       </c>
       <c r="E125" s="9" t="s">
         <v>174</v>
@@ -9173,11 +9173,11 @@
         <v>324</v>
       </c>
       <c r="B126" s="5">
-        <v>46132.465527430555</v>
+        <v>46132.63219409723</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46134.400369166666</v>
+        <v>46134.56703583333</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>174</v>
@@ -9226,11 +9226,11 @@
         <v>325</v>
       </c>
       <c r="B127" s="8">
-        <v>46132.46553420139</v>
+        <v>46132.63220086806</v>
       </c>
       <c r="C127" s="9"/>
       <c r="D127" s="8">
-        <v>46134.40039130787</v>
+        <v>46134.567057974535</v>
       </c>
       <c r="E127" s="9" t="s">
         <v>174</v>
@@ -9279,11 +9279,11 @@
         <v>326</v>
       </c>
       <c r="B128" s="5">
-        <v>46132.46554068287</v>
+        <v>46132.63220734954</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46134.40041349537</v>
+        <v>46134.567080162036</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>174</v>
@@ -9332,11 +9332,11 @@
         <v>327</v>
       </c>
       <c r="B129" s="8">
-        <v>46132.422271979165</v>
+        <v>46132.58893864583</v>
       </c>
       <c r="C129" s="9"/>
       <c r="D129" s="8">
-        <v>46134.412491469906</v>
+        <v>46134.57915813658</v>
       </c>
       <c r="E129" s="9" t="s">
         <v>328</v>
@@ -9393,11 +9393,11 @@
         <v>329</v>
       </c>
       <c r="B130" s="5">
-        <v>46132.46630138889</v>
+        <v>46132.63296805556</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46134.403638449076</v>
+        <v>46134.57030511574</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>174</v>
@@ -9444,11 +9444,11 @@
         <v>332</v>
       </c>
       <c r="B131" s="8">
-        <v>46132.466312881945</v>
+        <v>46132.63297954861</v>
       </c>
       <c r="C131" s="9"/>
       <c r="D131" s="8">
-        <v>46134.40367459491</v>
+        <v>46134.57034126157</v>
       </c>
       <c r="E131" s="9" t="s">
         <v>174</v>
@@ -9495,11 +9495,11 @@
         <v>334</v>
       </c>
       <c r="B132" s="5">
-        <v>46132.46632092593</v>
+        <v>46132.63298759259</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46134.40369875</v>
+        <v>46134.57036541667</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>174</v>
@@ -9546,11 +9546,11 @@
         <v>335</v>
       </c>
       <c r="B133" s="8">
-        <v>46132.466326608795</v>
+        <v>46132.63299327546</v>
       </c>
       <c r="C133" s="9"/>
       <c r="D133" s="8">
-        <v>46134.40370732639</v>
+        <v>46134.570373993054</v>
       </c>
       <c r="E133" s="9" t="s">
         <v>174</v>
@@ -9597,11 +9597,11 @@
         <v>337</v>
       </c>
       <c r="B134" s="5">
-        <v>46132.466333275464</v>
+        <v>46132.63299994213</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46134.403738402776</v>
+        <v>46134.57040506945</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>174</v>
@@ -9648,11 +9648,11 @@
         <v>338</v>
       </c>
       <c r="B135" s="8">
-        <v>46132.46634035879</v>
+        <v>46132.63300702546</v>
       </c>
       <c r="C135" s="9"/>
       <c r="D135" s="8">
-        <v>46134.40374789352</v>
+        <v>46134.570414560185</v>
       </c>
       <c r="E135" s="9" t="s">
         <v>174</v>
@@ -9699,11 +9699,11 @@
         <v>340</v>
       </c>
       <c r="B136" s="5">
-        <v>46132.46634604166</v>
+        <v>46132.633012708335</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46134.40379078704</v>
+        <v>46134.57045745371</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>174</v>
@@ -9750,11 +9750,11 @@
         <v>342</v>
       </c>
       <c r="B137" s="8">
-        <v>46132.46635333334</v>
+        <v>46132.63302</v>
       </c>
       <c r="C137" s="9"/>
       <c r="D137" s="8">
-        <v>46134.40379997685</v>
+        <v>46134.57046664352</v>
       </c>
       <c r="E137" s="9" t="s">
         <v>174</v>
@@ -9801,11 +9801,11 @@
         <v>343</v>
       </c>
       <c r="B138" s="5">
-        <v>46132.46635981482</v>
+        <v>46132.63302648148</v>
       </c>
       <c r="C138" s="6"/>
       <c r="D138" s="5">
-        <v>46134.40382603009</v>
+        <v>46134.57049269676</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>174</v>
@@ -9852,11 +9852,11 @@
         <v>344</v>
       </c>
       <c r="B139" s="8">
-        <v>46132.46636619213</v>
+        <v>46132.633032858794</v>
       </c>
       <c r="C139" s="9"/>
       <c r="D139" s="8">
-        <v>46134.403847407404</v>
+        <v>46134.570514074076</v>
       </c>
       <c r="E139" s="9" t="s">
         <v>174</v>
@@ -9903,11 +9903,11 @@
         <v>346</v>
       </c>
       <c r="B140" s="5">
-        <v>46132.46637274306</v>
+        <v>46132.633039409724</v>
       </c>
       <c r="C140" s="6"/>
       <c r="D140" s="5">
-        <v>46134.40387707176</v>
+        <v>46134.57054373843</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>174</v>
@@ -9954,11 +9954,11 @@
         <v>347</v>
       </c>
       <c r="B141" s="8">
-        <v>46132.46637915509</v>
+        <v>46132.633045821756</v>
       </c>
       <c r="C141" s="9"/>
       <c r="D141" s="8">
-        <v>46134.403904328705</v>
+        <v>46134.57057099537</v>
       </c>
       <c r="E141" s="9" t="s">
         <v>174</v>
@@ -10005,11 +10005,11 @@
         <v>348</v>
       </c>
       <c r="B142" s="5">
-        <v>46132.46639339121</v>
+        <v>46132.633060057866</v>
       </c>
       <c r="C142" s="6"/>
       <c r="D142" s="5">
-        <v>46134.40393626157</v>
+        <v>46134.570602928245</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>174</v>
@@ -10056,11 +10056,11 @@
         <v>349</v>
       </c>
       <c r="B143" s="8">
-        <v>46132.466386319444</v>
+        <v>46132.633052986115</v>
       </c>
       <c r="C143" s="9"/>
       <c r="D143" s="8">
-        <v>46134.40402259259</v>
+        <v>46134.57068925926</v>
       </c>
       <c r="E143" s="9" t="s">
         <v>174</v>
@@ -10107,11 +10107,11 @@
         <v>350</v>
       </c>
       <c r="B144" s="5">
-        <v>46132.46639913194</v>
+        <v>46132.63306579861</v>
       </c>
       <c r="C144" s="6"/>
       <c r="D144" s="5">
-        <v>46134.40405877314</v>
+        <v>46134.570725439815</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>174</v>
@@ -10158,11 +10158,11 @@
         <v>351</v>
       </c>
       <c r="B145" s="8">
-        <v>46132.46640567129</v>
+        <v>46132.633072337965</v>
       </c>
       <c r="C145" s="9"/>
       <c r="D145" s="8">
-        <v>46134.404092349534</v>
+        <v>46134.570759016206</v>
       </c>
       <c r="E145" s="9" t="s">
         <v>174</v>
@@ -10209,11 +10209,11 @@
         <v>352</v>
       </c>
       <c r="B146" s="5">
-        <v>46132.42227886574</v>
+        <v>46132.58894553241</v>
       </c>
       <c r="C146" s="6"/>
       <c r="D146" s="5">
-        <v>46134.41249231482</v>
+        <v>46134.579158981476</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>353</v>
@@ -10270,11 +10270,11 @@
         <v>354</v>
       </c>
       <c r="B147" s="8">
-        <v>46132.466473622684</v>
+        <v>46132.633140289356</v>
       </c>
       <c r="C147" s="9"/>
       <c r="D147" s="8">
-        <v>46157.375384328705</v>
+        <v>46157.54205099537</v>
       </c>
       <c r="E147" s="9" t="s">
         <v>174</v>
@@ -10321,11 +10321,11 @@
         <v>357</v>
       </c>
       <c r="B148" s="5">
-        <v>46132.46648241898</v>
+        <v>46132.63314908565</v>
       </c>
       <c r="C148" s="6"/>
       <c r="D148" s="5">
-        <v>46157.3753849537</v>
+        <v>46157.542051620374</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>174</v>
@@ -10372,11 +10372,11 @@
         <v>359</v>
       </c>
       <c r="B149" s="8">
-        <v>46132.466488668986</v>
+        <v>46132.63315533564</v>
       </c>
       <c r="C149" s="9"/>
       <c r="D149" s="8">
-        <v>46157.37538557871</v>
+        <v>46157.54205224537</v>
       </c>
       <c r="E149" s="9" t="s">
         <v>174</v>
@@ -10423,11 +10423,11 @@
         <v>360</v>
       </c>
       <c r="B150" s="5">
-        <v>46132.466495995366</v>
+        <v>46132.63316266204</v>
       </c>
       <c r="C150" s="6"/>
       <c r="D150" s="5">
-        <v>46157.375386307875</v>
+        <v>46157.54205297454</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>174</v>
@@ -10474,11 +10474,11 @@
         <v>361</v>
       </c>
       <c r="B151" s="8">
-        <v>46132.46650239584</v>
+        <v>46132.6331690625</v>
       </c>
       <c r="C151" s="9"/>
       <c r="D151" s="8">
-        <v>46157.37538694445</v>
+        <v>46157.54205361111</v>
       </c>
       <c r="E151" s="9" t="s">
         <v>174</v>
@@ -10525,11 +10525,11 @@
         <v>362</v>
       </c>
       <c r="B152" s="5">
-        <v>46132.46650928241</v>
+        <v>46132.63317594907</v>
       </c>
       <c r="C152" s="6"/>
       <c r="D152" s="5">
-        <v>46157.37538758102</v>
+        <v>46157.542054247686</v>
       </c>
       <c r="E152" s="6" t="s">
         <v>174</v>
@@ -10576,11 +10576,11 @@
         <v>363</v>
       </c>
       <c r="B153" s="8">
-        <v>46132.46652184028</v>
+        <v>46132.633188506945</v>
       </c>
       <c r="C153" s="9"/>
       <c r="D153" s="8">
-        <v>46157.37538815972</v>
+        <v>46157.542054826394</v>
       </c>
       <c r="E153" s="9" t="s">
         <v>174</v>
@@ -10627,11 +10627,11 @@
         <v>364</v>
       </c>
       <c r="B154" s="5">
-        <v>46132.46651493055</v>
+        <v>46132.63318159722</v>
       </c>
       <c r="C154" s="6"/>
       <c r="D154" s="5">
-        <v>46157.375388773144</v>
+        <v>46157.542055439815</v>
       </c>
       <c r="E154" s="6" t="s">
         <v>174</v>
@@ -10678,11 +10678,11 @@
         <v>365</v>
       </c>
       <c r="B155" s="8">
-        <v>46132.4665277662</v>
+        <v>46132.63319443287</v>
       </c>
       <c r="C155" s="9"/>
       <c r="D155" s="8">
-        <v>46157.37538939815</v>
+        <v>46157.54205606482</v>
       </c>
       <c r="E155" s="9" t="s">
         <v>174</v>
@@ -10729,11 +10729,11 @@
         <v>366</v>
       </c>
       <c r="B156" s="5">
-        <v>46132.46654149306</v>
+        <v>46132.63320815972</v>
       </c>
       <c r="C156" s="6"/>
       <c r="D156" s="5">
-        <v>46157.375389953704</v>
+        <v>46157.54205662037</v>
       </c>
       <c r="E156" s="6" t="s">
         <v>174</v>
@@ -10780,11 +10780,11 @@
         <v>367</v>
       </c>
       <c r="B157" s="8">
-        <v>46132.46653415509</v>
+        <v>46132.63320082176</v>
       </c>
       <c r="C157" s="9"/>
       <c r="D157" s="8">
-        <v>46157.37539074074</v>
+        <v>46157.54205740741</v>
       </c>
       <c r="E157" s="9" t="s">
         <v>174</v>
@@ -10831,11 +10831,11 @@
         <v>368</v>
       </c>
       <c r="B158" s="5">
-        <v>46132.46655430556</v>
+        <v>46132.63322097222</v>
       </c>
       <c r="C158" s="6"/>
       <c r="D158" s="5">
-        <v>46157.37539130787</v>
+        <v>46157.54205797454</v>
       </c>
       <c r="E158" s="6" t="s">
         <v>174</v>
@@ -10882,11 +10882,11 @@
         <v>369</v>
       </c>
       <c r="B159" s="8">
-        <v>46132.46654837963</v>
+        <v>46132.6332150463</v>
       </c>
       <c r="C159" s="9"/>
       <c r="D159" s="8">
-        <v>46157.37539188657</v>
+        <v>46157.54205855324</v>
       </c>
       <c r="E159" s="9" t="s">
         <v>174</v>
@@ -10933,11 +10933,11 @@
         <v>370</v>
       </c>
       <c r="B160" s="5">
-        <v>46132.466561354166</v>
+        <v>46132.63322802083</v>
       </c>
       <c r="C160" s="6"/>
       <c r="D160" s="5">
-        <v>46157.37539248842</v>
+        <v>46157.542059155094</v>
       </c>
       <c r="E160" s="6" t="s">
         <v>174</v>
@@ -10984,11 +10984,11 @@
         <v>371</v>
       </c>
       <c r="B161" s="8">
-        <v>46132.46656908565</v>
+        <v>46132.63323575231</v>
       </c>
       <c r="C161" s="9"/>
       <c r="D161" s="8">
-        <v>46157.375393090275</v>
+        <v>46157.54205975695</v>
       </c>
       <c r="E161" s="9" t="s">
         <v>174</v>
@@ -11035,11 +11035,11 @@
         <v>372</v>
       </c>
       <c r="B162" s="5">
-        <v>46132.46657733797</v>
+        <v>46132.633244004624</v>
       </c>
       <c r="C162" s="6"/>
       <c r="D162" s="5">
-        <v>46157.37539375</v>
+        <v>46157.54206041667</v>
       </c>
       <c r="E162" s="6" t="s">
         <v>174</v>
@@ -11086,11 +11086,11 @@
         <v>373</v>
       </c>
       <c r="B163" s="8">
-        <v>46132.4222650463</v>
+        <v>46132.58893171296</v>
       </c>
       <c r="C163" s="9"/>
       <c r="D163" s="8">
-        <v>46134.412493090276</v>
+        <v>46134.57915975695</v>
       </c>
       <c r="E163" s="9" t="s">
         <v>374</v>
@@ -11147,11 +11147,11 @@
         <v>375</v>
       </c>
       <c r="B164" s="5">
-        <v>46132.46613763889</v>
+        <v>46132.632804305555</v>
       </c>
       <c r="C164" s="6"/>
       <c r="D164" s="5">
-        <v>46134.406735833334</v>
+        <v>46134.5734025</v>
       </c>
       <c r="E164" s="6" t="s">
         <v>174</v>
@@ -11198,11 +11198,11 @@
         <v>378</v>
       </c>
       <c r="B165" s="8">
-        <v>46132.46614895834</v>
+        <v>46132.632815624995</v>
       </c>
       <c r="C165" s="9"/>
       <c r="D165" s="8">
-        <v>46134.40676083333</v>
+        <v>46134.5734275</v>
       </c>
       <c r="E165" s="9" t="s">
         <v>174</v>
@@ -11249,11 +11249,11 @@
         <v>379</v>
       </c>
       <c r="B166" s="5">
-        <v>46132.466156180555</v>
+        <v>46132.63282284723</v>
       </c>
       <c r="C166" s="6"/>
       <c r="D166" s="5">
-        <v>46134.40678253472</v>
+        <v>46134.57344920139</v>
       </c>
       <c r="E166" s="6" t="s">
         <v>174</v>
@@ -11300,11 +11300,11 @@
         <v>381</v>
       </c>
       <c r="B167" s="8">
-        <v>46132.466165694444</v>
+        <v>46132.63283236111</v>
       </c>
       <c r="C167" s="9"/>
       <c r="D167" s="8">
-        <v>46134.40681689815</v>
+        <v>46134.57348356482</v>
       </c>
       <c r="E167" s="9" t="s">
         <v>174</v>
@@ -11351,11 +11351,11 @@
         <v>382</v>
       </c>
       <c r="B168" s="5">
-        <v>46132.46617071759</v>
+        <v>46132.632837384255</v>
       </c>
       <c r="C168" s="6"/>
       <c r="D168" s="5">
-        <v>46134.40690241898</v>
+        <v>46134.57356908565</v>
       </c>
       <c r="E168" s="6" t="s">
         <v>174</v>
@@ -11402,11 +11402,11 @@
         <v>384</v>
       </c>
       <c r="B169" s="8">
-        <v>46132.46617695602</v>
+        <v>46132.63284362269</v>
       </c>
       <c r="C169" s="9"/>
       <c r="D169" s="8">
-        <v>46134.40693696759</v>
+        <v>46134.57360363426</v>
       </c>
       <c r="E169" s="9" t="s">
         <v>174</v>
@@ -11453,11 +11453,11 @@
         <v>385</v>
       </c>
       <c r="B170" s="5">
-        <v>46132.46618309028</v>
+        <v>46132.63284975695</v>
       </c>
       <c r="C170" s="6"/>
       <c r="D170" s="5">
-        <v>46134.4069824537</v>
+        <v>46134.57364912037</v>
       </c>
       <c r="E170" s="6" t="s">
         <v>174</v>
@@ -11504,11 +11504,11 @@
         <v>386</v>
       </c>
       <c r="B171" s="8">
-        <v>46132.46619560185</v>
+        <v>46132.63286226852</v>
       </c>
       <c r="C171" s="9"/>
       <c r="D171" s="8">
-        <v>46134.40699137731</v>
+        <v>46134.573658043984</v>
       </c>
       <c r="E171" s="9" t="s">
         <v>174</v>
@@ -11555,11 +11555,11 @@
         <v>387</v>
       </c>
       <c r="B172" s="5">
-        <v>46132.46619009259</v>
+        <v>46132.63285675926</v>
       </c>
       <c r="C172" s="6"/>
       <c r="D172" s="5">
-        <v>46134.407016006946</v>
+        <v>46134.57368267361</v>
       </c>
       <c r="E172" s="6" t="s">
         <v>174</v>
@@ -11606,11 +11606,11 @@
         <v>388</v>
       </c>
       <c r="B173" s="8">
-        <v>46132.466201620366</v>
+        <v>46132.63286828704</v>
       </c>
       <c r="C173" s="9"/>
       <c r="D173" s="8">
-        <v>46134.407049814814</v>
+        <v>46134.57371648148</v>
       </c>
       <c r="E173" s="9" t="s">
         <v>174</v>
@@ -11657,11 +11657,11 @@
         <v>389</v>
       </c>
       <c r="B174" s="5">
-        <v>46132.466207453705</v>
+        <v>46132.63287412037</v>
       </c>
       <c r="C174" s="6"/>
       <c r="D174" s="5">
-        <v>46134.4070724537</v>
+        <v>46134.57373912037</v>
       </c>
       <c r="E174" s="6" t="s">
         <v>174</v>
@@ -11708,11 +11708,11 @@
         <v>390</v>
       </c>
       <c r="B175" s="8">
-        <v>46132.46621466435</v>
+        <v>46132.63288133102</v>
       </c>
       <c r="C175" s="9"/>
       <c r="D175" s="8">
-        <v>46134.4070952662</v>
+        <v>46134.57376193287</v>
       </c>
       <c r="E175" s="9" t="s">
         <v>174</v>
@@ -11759,11 +11759,11 @@
         <v>391</v>
       </c>
       <c r="B176" s="5">
-        <v>46132.46622134259</v>
+        <v>46132.63288800926</v>
       </c>
       <c r="C176" s="6"/>
       <c r="D176" s="5">
-        <v>46134.40711494213</v>
+        <v>46134.57378160879</v>
       </c>
       <c r="E176" s="6" t="s">
         <v>174</v>
@@ -11810,11 +11810,11 @@
         <v>392</v>
       </c>
       <c r="B177" s="8">
-        <v>46132.4662275463</v>
+        <v>46132.63289421296</v>
       </c>
       <c r="C177" s="9"/>
       <c r="D177" s="8">
-        <v>46134.407128900464</v>
+        <v>46134.57379556713</v>
       </c>
       <c r="E177" s="9" t="s">
         <v>174</v>
@@ -11861,11 +11861,11 @@
         <v>393</v>
       </c>
       <c r="B178" s="5">
-        <v>46132.46623362269</v>
+        <v>46132.63290028935</v>
       </c>
       <c r="C178" s="6"/>
       <c r="D178" s="5">
-        <v>46134.40717228009</v>
+        <v>46134.57383894676</v>
       </c>
       <c r="E178" s="6" t="s">
         <v>174</v>
@@ -11912,11 +11912,11 @@
         <v>394</v>
       </c>
       <c r="B179" s="8">
-        <v>46132.46624105324</v>
+        <v>46132.632907719904</v>
       </c>
       <c r="C179" s="9"/>
       <c r="D179" s="8">
-        <v>46134.40721119213</v>
+        <v>46134.5738778588</v>
       </c>
       <c r="E179" s="9" t="s">
         <v>174</v>
@@ -11963,11 +11963,11 @@
         <v>395</v>
       </c>
       <c r="B180" s="5">
-        <v>46132.42228591435</v>
+        <v>46132.58895258102</v>
       </c>
       <c r="C180" s="6"/>
       <c r="D180" s="5">
-        <v>46134.41249390046</v>
+        <v>46134.579160567126</v>
       </c>
       <c r="E180" s="6" t="s">
         <v>396</v>
@@ -12024,11 +12024,11 @@
         <v>397</v>
       </c>
       <c r="B181" s="8">
-        <v>46132.46663340278</v>
+        <v>46132.63330006944</v>
       </c>
       <c r="C181" s="9"/>
       <c r="D181" s="8">
-        <v>46134.40963775463</v>
+        <v>46134.576304421294</v>
       </c>
       <c r="E181" s="9" t="s">
         <v>174</v>
@@ -12075,11 +12075,11 @@
         <v>400</v>
       </c>
       <c r="B182" s="5">
-        <v>46132.46664318287</v>
+        <v>46132.63330984954</v>
       </c>
       <c r="C182" s="6"/>
       <c r="D182" s="5">
-        <v>46134.40966780092</v>
+        <v>46134.576334467594</v>
       </c>
       <c r="E182" s="6" t="s">
         <v>174</v>
@@ -12126,11 +12126,11 @@
         <v>402</v>
       </c>
       <c r="B183" s="8">
-        <v>46132.46664971065</v>
+        <v>46132.633316377316</v>
       </c>
       <c r="C183" s="9"/>
       <c r="D183" s="8">
-        <v>46134.40968888889</v>
+        <v>46134.57635555556</v>
       </c>
       <c r="E183" s="9" t="s">
         <v>174</v>
@@ -12177,11 +12177,11 @@
         <v>404</v>
       </c>
       <c r="B184" s="5">
-        <v>46132.46665666667</v>
+        <v>46132.63332333333</v>
       </c>
       <c r="C184" s="6"/>
       <c r="D184" s="5">
-        <v>46134.409710231484</v>
+        <v>46134.57637689815</v>
       </c>
       <c r="E184" s="6" t="s">
         <v>174</v>
@@ -12228,11 +12228,11 @@
         <v>406</v>
       </c>
       <c r="B185" s="8">
-        <v>46132.466669016205</v>
+        <v>46132.63333568287</v>
       </c>
       <c r="C185" s="9"/>
       <c r="D185" s="8">
-        <v>46134.409749502316</v>
+        <v>46134.57641616898</v>
       </c>
       <c r="E185" s="9" t="s">
         <v>174</v>
@@ -12279,11 +12279,11 @@
         <v>408</v>
       </c>
       <c r="B186" s="5">
-        <v>46132.46666261574</v>
+        <v>46132.633329282406</v>
       </c>
       <c r="C186" s="6"/>
       <c r="D186" s="5">
-        <v>46134.40977741899</v>
+        <v>46134.576444085644</v>
       </c>
       <c r="E186" s="6" t="s">
         <v>174</v>
@@ -12330,11 +12330,11 @@
         <v>410</v>
       </c>
       <c r="B187" s="8">
-        <v>46132.466682592596</v>
+        <v>46132.63334925926</v>
       </c>
       <c r="C187" s="9"/>
       <c r="D187" s="8">
-        <v>46134.40981337963</v>
+        <v>46134.57648004629</v>
       </c>
       <c r="E187" s="9" t="s">
         <v>174</v>
@@ -12381,11 +12381,11 @@
         <v>412</v>
       </c>
       <c r="B188" s="5">
-        <v>46132.4666866551</v>
+        <v>46132.633353321755</v>
       </c>
       <c r="C188" s="6"/>
       <c r="D188" s="5">
-        <v>46134.4098374537</v>
+        <v>46134.57650412037</v>
       </c>
       <c r="E188" s="6" t="s">
         <v>174</v>
@@ -12432,11 +12432,11 @@
         <v>414</v>
       </c>
       <c r="B189" s="8">
-        <v>46132.46669449074</v>
+        <v>46132.63336115741</v>
       </c>
       <c r="C189" s="9"/>
       <c r="D189" s="8">
-        <v>46134.409860115746</v>
+        <v>46134.5765267824</v>
       </c>
       <c r="E189" s="9" t="s">
         <v>174</v>
@@ -12483,11 +12483,11 @@
         <v>416</v>
       </c>
       <c r="B190" s="5">
-        <v>46132.466699490746</v>
+        <v>46132.6333661574</v>
       </c>
       <c r="C190" s="6"/>
       <c r="D190" s="5">
-        <v>46134.4098853125</v>
+        <v>46134.57655197917</v>
       </c>
       <c r="E190" s="6" t="s">
         <v>174</v>
@@ -12534,11 +12534,11 @@
         <v>418</v>
       </c>
       <c r="B191" s="8">
-        <v>46132.46670837963</v>
+        <v>46132.633375046295</v>
       </c>
       <c r="C191" s="9"/>
       <c r="D191" s="8">
-        <v>46134.40993851852</v>
+        <v>46134.57660518518</v>
       </c>
       <c r="E191" s="9" t="s">
         <v>174</v>
@@ -12585,11 +12585,11 @@
         <v>420</v>
       </c>
       <c r="B192" s="5">
-        <v>46132.46671283565</v>
+        <v>46132.63337950232</v>
       </c>
       <c r="C192" s="6"/>
       <c r="D192" s="5">
-        <v>46134.40996846065</v>
+        <v>46134.57663512732</v>
       </c>
       <c r="E192" s="6" t="s">
         <v>174</v>
@@ -12636,11 +12636,11 @@
         <v>422</v>
       </c>
       <c r="B193" s="8">
-        <v>46132.46672</v>
+        <v>46132.63338666667</v>
       </c>
       <c r="C193" s="9"/>
       <c r="D193" s="8">
-        <v>46134.40999233796</v>
+        <v>46134.576659004626</v>
       </c>
       <c r="E193" s="9" t="s">
         <v>174</v>
@@ -12687,11 +12687,11 @@
         <v>424</v>
       </c>
       <c r="B194" s="5">
-        <v>46132.46672708333</v>
+        <v>46132.63339375</v>
       </c>
       <c r="C194" s="6"/>
       <c r="D194" s="5">
-        <v>46134.41001733796</v>
+        <v>46134.57668400463</v>
       </c>
       <c r="E194" s="6" t="s">
         <v>174</v>
@@ -12738,11 +12738,11 @@
         <v>426</v>
       </c>
       <c r="B195" s="8">
-        <v>46132.46673206019</v>
+        <v>46132.63339872685</v>
       </c>
       <c r="C195" s="9"/>
       <c r="D195" s="8">
-        <v>46134.410042777774</v>
+        <v>46134.576709444445</v>
       </c>
       <c r="E195" s="9" t="s">
         <v>174</v>
@@ -12789,11 +12789,11 @@
         <v>428</v>
       </c>
       <c r="B196" s="5">
-        <v>46132.46673741898</v>
+        <v>46132.633404085645</v>
       </c>
       <c r="C196" s="6"/>
       <c r="D196" s="5">
-        <v>46134.41010097222</v>
+        <v>46134.57676763889</v>
       </c>
       <c r="E196" s="6" t="s">
         <v>174</v>
@@ -12840,11 +12840,11 @@
         <v>430</v>
       </c>
       <c r="B197" s="8">
-        <v>46132.422338993056</v>
+        <v>46132.58900565973</v>
       </c>
       <c r="C197" s="9"/>
       <c r="D197" s="8">
-        <v>46134.41249466436</v>
+        <v>46134.579161331014</v>
       </c>
       <c r="E197" s="9" t="s">
         <v>431</v>
@@ -12901,11 +12901,11 @@
         <v>434</v>
       </c>
       <c r="B198" s="5">
-        <v>46132.466786770834</v>
+        <v>46132.6334534375</v>
       </c>
       <c r="C198" s="6"/>
       <c r="D198" s="5">
-        <v>46134.41359752315</v>
+        <v>46134.58026418982</v>
       </c>
       <c r="E198" s="6" t="s">
         <v>174</v>
@@ -12952,11 +12952,11 @@
         <v>436</v>
       </c>
       <c r="B199" s="8">
-        <v>46132.46679535879</v>
+        <v>46132.633462025464</v>
       </c>
       <c r="C199" s="9"/>
       <c r="D199" s="8">
-        <v>46134.41156540509</v>
+        <v>46134.578232071755</v>
       </c>
       <c r="E199" s="9" t="s">
         <v>174</v>
@@ -13003,11 +13003,11 @@
         <v>437</v>
       </c>
       <c r="B200" s="5">
-        <v>46132.46680195602</v>
+        <v>46132.633468622684</v>
       </c>
       <c r="C200" s="6"/>
       <c r="D200" s="5">
-        <v>46134.4116025</v>
+        <v>46134.57826916667</v>
       </c>
       <c r="E200" s="6" t="s">
         <v>174</v>
@@ -13054,11 +13054,11 @@
         <v>438</v>
       </c>
       <c r="B201" s="8">
-        <v>46132.46680835648</v>
+        <v>46132.63347502315</v>
       </c>
       <c r="C201" s="9"/>
       <c r="D201" s="8">
-        <v>46134.41162270833</v>
+        <v>46134.578289375</v>
       </c>
       <c r="E201" s="9" t="s">
         <v>174</v>
@@ -13105,11 +13105,11 @@
         <v>439</v>
       </c>
       <c r="B202" s="5">
-        <v>46132.46681403935</v>
+        <v>46132.63348070602</v>
       </c>
       <c r="C202" s="6"/>
       <c r="D202" s="5">
-        <v>46134.411630891205</v>
+        <v>46134.57829755787</v>
       </c>
       <c r="E202" s="6" t="s">
         <v>174</v>
@@ -13156,11 +13156,11 @@
         <v>440</v>
       </c>
       <c r="B203" s="8">
-        <v>46132.466819953705</v>
+        <v>46132.63348662037</v>
       </c>
       <c r="C203" s="9"/>
       <c r="D203" s="8">
-        <v>46134.41166219907</v>
+        <v>46134.57832886574</v>
       </c>
       <c r="E203" s="9" t="s">
         <v>174</v>
@@ -13207,11 +13207,11 @@
         <v>441</v>
       </c>
       <c r="B204" s="5">
-        <v>46132.466826284726</v>
+        <v>46132.63349295139</v>
       </c>
       <c r="C204" s="6"/>
       <c r="D204" s="5">
-        <v>46134.41169792824</v>
+        <v>46134.57836459491</v>
       </c>
       <c r="E204" s="6" t="s">
         <v>174</v>
@@ -13258,11 +13258,11 @@
         <v>442</v>
       </c>
       <c r="B205" s="8">
-        <v>46132.46683347222</v>
+        <v>46132.633500138894</v>
       </c>
       <c r="C205" s="9"/>
       <c r="D205" s="8">
-        <v>46134.41173365741</v>
+        <v>46134.57840032407</v>
       </c>
       <c r="E205" s="9" t="s">
         <v>174</v>
@@ -13309,11 +13309,11 @@
         <v>443</v>
       </c>
       <c r="B206" s="5">
-        <v>46132.46683931713</v>
+        <v>46132.633505983795</v>
       </c>
       <c r="C206" s="6"/>
       <c r="D206" s="5">
-        <v>46134.411741724536</v>
+        <v>46134.5784083912</v>
       </c>
       <c r="E206" s="6" t="s">
         <v>174</v>
@@ -13360,11 +13360,11 @@
         <v>444</v>
       </c>
       <c r="B207" s="8">
-        <v>46132.466845787036</v>
+        <v>46132.6335124537</v>
       </c>
       <c r="C207" s="9"/>
       <c r="D207" s="8">
-        <v>46134.41177078703</v>
+        <v>46134.5784374537</v>
       </c>
       <c r="E207" s="9" t="s">
         <v>174</v>
@@ -13411,11 +13411,11 @@
         <v>445</v>
       </c>
       <c r="B208" s="5">
-        <v>46132.4668530787</v>
+        <v>46132.63351974537</v>
       </c>
       <c r="C208" s="6"/>
       <c r="D208" s="5">
-        <v>46134.411791770835</v>
+        <v>46134.5784584375</v>
       </c>
       <c r="E208" s="6" t="s">
         <v>174</v>
@@ -13462,11 +13462,11 @@
         <v>446</v>
       </c>
       <c r="B209" s="8">
-        <v>46132.466861099536</v>
+        <v>46132.6335277662</v>
       </c>
       <c r="C209" s="9"/>
       <c r="D209" s="8">
-        <v>46134.41183957176</v>
+        <v>46134.578506238424</v>
       </c>
       <c r="E209" s="9" t="s">
         <v>174</v>
@@ -13513,11 +13513,11 @@
         <v>447</v>
       </c>
       <c r="B210" s="5">
-        <v>46132.46686832176</v>
+        <v>46132.633534988425</v>
       </c>
       <c r="C210" s="6"/>
       <c r="D210" s="5">
-        <v>46134.41186925926</v>
+        <v>46134.578535925924</v>
       </c>
       <c r="E210" s="6" t="s">
         <v>174</v>
@@ -13564,11 +13564,11 @@
         <v>448</v>
       </c>
       <c r="B211" s="8">
-        <v>46132.46687415509</v>
+        <v>46132.63354082176</v>
       </c>
       <c r="C211" s="9"/>
       <c r="D211" s="8">
-        <v>46134.41188699074</v>
+        <v>46134.57855365741</v>
       </c>
       <c r="E211" s="9" t="s">
         <v>174</v>
@@ -13615,11 +13615,11 @@
         <v>449</v>
       </c>
       <c r="B212" s="5">
-        <v>46132.4668809375</v>
+        <v>46132.63354760417</v>
       </c>
       <c r="C212" s="6"/>
       <c r="D212" s="5">
-        <v>46134.41191811343</v>
+        <v>46134.578584780094</v>
       </c>
       <c r="E212" s="6" t="s">
         <v>174</v>
@@ -13666,11 +13666,11 @@
         <v>450</v>
       </c>
       <c r="B213" s="8">
-        <v>46133.41633472222</v>
+        <v>46133.58300138889</v>
       </c>
       <c r="C213" s="9"/>
       <c r="D213" s="8">
-        <v>46134.41194211805</v>
+        <v>46134.57860878472</v>
       </c>
       <c r="E213" s="9" t="s">
         <v>272</v>
@@ -13717,11 +13717,11 @@
         <v>451</v>
       </c>
       <c r="B214" s="5">
-        <v>46132.42234625</v>
+        <v>46132.589012916666</v>
       </c>
       <c r="C214" s="6"/>
       <c r="D214" s="5">
-        <v>46133.42102390046</v>
+        <v>46133.58769056713</v>
       </c>
       <c r="E214" s="6" t="s">
         <v>452</v>
@@ -13764,11 +13764,11 @@
         <v>454</v>
       </c>
       <c r="B215" s="8">
-        <v>46132.42235</v>
+        <v>46132.589016666665</v>
       </c>
       <c r="C215" s="9"/>
       <c r="D215" s="8">
-        <v>46133.41815366899</v>
+        <v>46133.58482033564</v>
       </c>
       <c r="E215" s="9" t="s">
         <v>455</v>
@@ -13825,11 +13825,11 @@
         <v>459</v>
       </c>
       <c r="B216" s="5">
-        <v>46132.46694003472</v>
+        <v>46132.63360670139</v>
       </c>
       <c r="C216" s="6"/>
       <c r="D216" s="5">
-        <v>46133.48245181713</v>
+        <v>46133.649118483794</v>
       </c>
       <c r="E216" s="6" t="s">
         <v>174</v>
@@ -13876,11 +13876,11 @@
         <v>460</v>
       </c>
       <c r="B217" s="8">
-        <v>46132.46694637732</v>
+        <v>46132.63361304398</v>
       </c>
       <c r="C217" s="9"/>
       <c r="D217" s="8">
-        <v>46133.4825030787</v>
+        <v>46133.649169745375</v>
       </c>
       <c r="E217" s="9" t="s">
         <v>174</v>
@@ -13927,11 +13927,11 @@
         <v>461</v>
       </c>
       <c r="B218" s="5">
-        <v>46132.46695307871</v>
+        <v>46132.63361974537</v>
       </c>
       <c r="C218" s="6"/>
       <c r="D218" s="5">
-        <v>46133.482554965274</v>
+        <v>46133.649221631946</v>
       </c>
       <c r="E218" s="6" t="s">
         <v>174</v>
@@ -13978,11 +13978,11 @@
         <v>462</v>
       </c>
       <c r="B219" s="8">
-        <v>46132.46696471065</v>
+        <v>46132.63363137731</v>
       </c>
       <c r="C219" s="9"/>
       <c r="D219" s="8">
-        <v>46133.48260270833</v>
+        <v>46133.649269375004</v>
       </c>
       <c r="E219" s="9" t="s">
         <v>174</v>
@@ -14029,11 +14029,11 @@
         <v>463</v>
       </c>
       <c r="B220" s="5">
-        <v>46132.466958888894</v>
+        <v>46132.63362555555</v>
       </c>
       <c r="C220" s="6"/>
       <c r="D220" s="5">
-        <v>46133.48263878472</v>
+        <v>46133.649305451385</v>
       </c>
       <c r="E220" s="6" t="s">
         <v>174</v>
@@ -14080,11 +14080,11 @@
         <v>464</v>
       </c>
       <c r="B221" s="8">
-        <v>46132.46697193287</v>
+        <v>46132.63363859954</v>
       </c>
       <c r="C221" s="9"/>
       <c r="D221" s="8">
-        <v>46133.48268208333</v>
+        <v>46133.64934875</v>
       </c>
       <c r="E221" s="9" t="s">
         <v>174</v>
@@ -14131,11 +14131,11 @@
         <v>465</v>
       </c>
       <c r="B222" s="5">
-        <v>46132.46698001157</v>
+        <v>46132.63364667824</v>
       </c>
       <c r="C222" s="6"/>
       <c r="D222" s="5">
-        <v>46133.48270832176</v>
+        <v>46133.649374988425</v>
       </c>
       <c r="E222" s="6" t="s">
         <v>174</v>
@@ -14182,11 +14182,11 @@
         <v>466</v>
       </c>
       <c r="B223" s="8">
-        <v>46132.466986388885</v>
+        <v>46132.633653055556</v>
       </c>
       <c r="C223" s="9"/>
       <c r="D223" s="8">
-        <v>46133.48273841436</v>
+        <v>46133.649405081014</v>
       </c>
       <c r="E223" s="9" t="s">
         <v>174</v>
@@ -14233,11 +14233,11 @@
         <v>467</v>
       </c>
       <c r="B224" s="5">
-        <v>46132.466992546295</v>
+        <v>46132.63365921297</v>
       </c>
       <c r="C224" s="6"/>
       <c r="D224" s="5">
-        <v>46133.48276636574</v>
+        <v>46133.649433032406</v>
       </c>
       <c r="E224" s="6" t="s">
         <v>174</v>
@@ -14284,11 +14284,11 @@
         <v>468</v>
       </c>
       <c r="B225" s="8">
-        <v>46132.46699868055</v>
+        <v>46132.633665347224</v>
       </c>
       <c r="C225" s="9"/>
       <c r="D225" s="8">
-        <v>46133.48282024305</v>
+        <v>46133.64948690972</v>
       </c>
       <c r="E225" s="9" t="s">
         <v>174</v>
@@ -14335,11 +14335,11 @@
         <v>469</v>
       </c>
       <c r="B226" s="5">
-        <v>46132.46700740741</v>
+        <v>46132.63367407407</v>
       </c>
       <c r="C226" s="6"/>
       <c r="D226" s="5">
-        <v>46133.48285042824</v>
+        <v>46133.649517094906</v>
       </c>
       <c r="E226" s="6" t="s">
         <v>174</v>
@@ -14386,11 +14386,11 @@
         <v>470</v>
       </c>
       <c r="B227" s="8">
-        <v>46132.46701559028</v>
+        <v>46132.63368225694</v>
       </c>
       <c r="C227" s="9"/>
       <c r="D227" s="8">
-        <v>46133.48289063657</v>
+        <v>46133.649557303244</v>
       </c>
       <c r="E227" s="9" t="s">
         <v>174</v>
@@ -14437,11 +14437,11 @@
         <v>471</v>
       </c>
       <c r="B228" s="5">
-        <v>46132.4670221875</v>
+        <v>46132.63368885417</v>
       </c>
       <c r="C228" s="6"/>
       <c r="D228" s="5">
-        <v>46133.48292591435</v>
+        <v>46133.649592581016</v>
       </c>
       <c r="E228" s="6" t="s">
         <v>174</v>
@@ -14488,11 +14488,11 @@
         <v>472</v>
       </c>
       <c r="B229" s="8">
-        <v>46132.46702829861</v>
+        <v>46132.633694965276</v>
       </c>
       <c r="C229" s="9"/>
       <c r="D229" s="8">
-        <v>46133.48295619213</v>
+        <v>46133.64962285879</v>
       </c>
       <c r="E229" s="9" t="s">
         <v>174</v>
@@ -14539,11 +14539,11 @@
         <v>473</v>
       </c>
       <c r="B230" s="5">
-        <v>46132.467034444446</v>
+        <v>46132.63370111111</v>
       </c>
       <c r="C230" s="6"/>
       <c r="D230" s="5">
-        <v>46133.48298398148</v>
+        <v>46133.64965064815</v>
       </c>
       <c r="E230" s="6" t="s">
         <v>174</v>
@@ -14590,11 +14590,11 @@
         <v>474</v>
       </c>
       <c r="B231" s="8">
-        <v>46132.46712287037</v>
+        <v>46132.63378953704</v>
       </c>
       <c r="C231" s="9"/>
       <c r="D231" s="8">
-        <v>46133.48303570602</v>
+        <v>46133.649702372684</v>
       </c>
       <c r="E231" s="9" t="s">
         <v>174</v>
@@ -14641,11 +14641,11 @@
         <v>475</v>
       </c>
       <c r="B232" s="5">
-        <v>46132.422355069444</v>
+        <v>46132.589021736116</v>
       </c>
       <c r="C232" s="6"/>
       <c r="D232" s="5">
-        <v>46133.41984377315</v>
+        <v>46133.58651043981</v>
       </c>
       <c r="E232" s="6" t="s">
         <v>476</v>
@@ -14702,11 +14702,11 @@
         <v>478</v>
       </c>
       <c r="B233" s="8">
-        <v>46132.46719494213</v>
+        <v>46132.633861608796</v>
       </c>
       <c r="C233" s="9"/>
       <c r="D233" s="8">
-        <v>46133.48389579861</v>
+        <v>46133.65056246528</v>
       </c>
       <c r="E233" s="9" t="s">
         <v>174</v>
@@ -14753,11 +14753,11 @@
         <v>479</v>
       </c>
       <c r="B234" s="5">
-        <v>46132.4672033449</v>
+        <v>46132.633870011574</v>
       </c>
       <c r="C234" s="6"/>
       <c r="D234" s="5">
-        <v>46133.48393898148</v>
+        <v>46133.650605648145</v>
       </c>
       <c r="E234" s="6" t="s">
         <v>174</v>
@@ -14804,11 +14804,11 @@
         <v>480</v>
       </c>
       <c r="B235" s="8">
-        <v>46132.46720991898</v>
+        <v>46132.63387658565</v>
       </c>
       <c r="C235" s="9"/>
       <c r="D235" s="8">
-        <v>46133.48397962963</v>
+        <v>46133.6506462963</v>
       </c>
       <c r="E235" s="9" t="s">
         <v>174</v>
@@ -14855,11 +14855,11 @@
         <v>481</v>
       </c>
       <c r="B236" s="5">
-        <v>46132.46721592592</v>
+        <v>46132.63388259259</v>
       </c>
       <c r="C236" s="6"/>
       <c r="D236" s="5">
-        <v>46133.48401165509</v>
+        <v>46133.65067832176</v>
       </c>
       <c r="E236" s="6" t="s">
         <v>174</v>
@@ -14906,11 +14906,11 @@
         <v>482</v>
       </c>
       <c r="B237" s="8">
-        <v>46132.46721966435</v>
+        <v>46132.63388633102</v>
       </c>
       <c r="C237" s="9"/>
       <c r="D237" s="8">
-        <v>46133.4840615162</v>
+        <v>46133.65072818287</v>
       </c>
       <c r="E237" s="9" t="s">
         <v>174</v>
@@ -14957,11 +14957,11 @@
         <v>483</v>
       </c>
       <c r="B238" s="5">
-        <v>46132.46722439815</v>
+        <v>46132.63389106482</v>
       </c>
       <c r="C238" s="6"/>
       <c r="D238" s="5">
-        <v>46133.484099837966</v>
+        <v>46133.65076650463</v>
       </c>
       <c r="E238" s="6" t="s">
         <v>174</v>
@@ -15008,11 +15008,11 @@
         <v>484</v>
       </c>
       <c r="B239" s="8">
-        <v>46132.46723072916</v>
+        <v>46132.63389739583</v>
       </c>
       <c r="C239" s="9"/>
       <c r="D239" s="8">
-        <v>46133.48414105324</v>
+        <v>46133.65080771991</v>
       </c>
       <c r="E239" s="9" t="s">
         <v>174</v>
@@ -15059,11 +15059,11 @@
         <v>485</v>
       </c>
       <c r="B240" s="5">
-        <v>46132.46723621528</v>
+        <v>46132.63390288195</v>
       </c>
       <c r="C240" s="6"/>
       <c r="D240" s="5">
-        <v>46133.484173206016</v>
+        <v>46133.65083987269</v>
       </c>
       <c r="E240" s="6" t="s">
         <v>174</v>
@@ -15110,11 +15110,11 @@
         <v>486</v>
       </c>
       <c r="B241" s="8">
-        <v>46132.46724194444</v>
+        <v>46132.63390861111</v>
       </c>
       <c r="C241" s="9"/>
       <c r="D241" s="8">
-        <v>46133.48420111111</v>
+        <v>46133.650867777775</v>
       </c>
       <c r="E241" s="9" t="s">
         <v>174</v>
@@ -15161,11 +15161,11 @@
         <v>487</v>
       </c>
       <c r="B242" s="5">
-        <v>46132.467246099535</v>
+        <v>46132.63391276621</v>
       </c>
       <c r="C242" s="6"/>
       <c r="D242" s="5">
-        <v>46133.484241620376</v>
+        <v>46133.65090828703</v>
       </c>
       <c r="E242" s="6" t="s">
         <v>174</v>
@@ -15212,11 +15212,11 @@
         <v>488</v>
       </c>
       <c r="B243" s="8">
-        <v>46132.4672521412</v>
+        <v>46132.63391880787</v>
       </c>
       <c r="C243" s="9"/>
       <c r="D243" s="8">
-        <v>46133.48427043982</v>
+        <v>46133.65093710648</v>
       </c>
       <c r="E243" s="9" t="s">
         <v>174</v>
@@ -15263,11 +15263,11 @@
         <v>489</v>
       </c>
       <c r="B244" s="5">
-        <v>46132.46725635417</v>
+        <v>46132.63392302083</v>
       </c>
       <c r="C244" s="6"/>
       <c r="D244" s="5">
-        <v>46133.48430795139</v>
+        <v>46133.65097461805</v>
       </c>
       <c r="E244" s="6" t="s">
         <v>174</v>
@@ -15314,11 +15314,11 @@
         <v>490</v>
       </c>
       <c r="B245" s="8">
-        <v>46132.467263750004</v>
+        <v>46132.63393041666</v>
       </c>
       <c r="C245" s="9"/>
       <c r="D245" s="8">
-        <v>46133.48436133102</v>
+        <v>46133.65102799769</v>
       </c>
       <c r="E245" s="9" t="s">
         <v>174</v>
@@ -15365,11 +15365,11 @@
         <v>491</v>
       </c>
       <c r="B246" s="5">
-        <v>46132.467270231486</v>
+        <v>46132.63393689815</v>
       </c>
       <c r="C246" s="6"/>
       <c r="D246" s="5">
-        <v>46133.484409282406</v>
+        <v>46133.65107594908</v>
       </c>
       <c r="E246" s="6" t="s">
         <v>174</v>
@@ -15416,11 +15416,11 @@
         <v>492</v>
       </c>
       <c r="B247" s="8">
-        <v>46132.46727641203</v>
+        <v>46132.633943078705</v>
       </c>
       <c r="C247" s="9"/>
       <c r="D247" s="8">
-        <v>46133.48444152778</v>
+        <v>46133.65110819445</v>
       </c>
       <c r="E247" s="9" t="s">
         <v>174</v>
@@ -15467,11 +15467,11 @@
         <v>493</v>
       </c>
       <c r="B248" s="5">
-        <v>46132.46728891204</v>
+        <v>46132.633955578705</v>
       </c>
       <c r="C248" s="6"/>
       <c r="D248" s="5">
-        <v>46133.48447834491</v>
+        <v>46133.65114501158</v>
       </c>
       <c r="E248" s="6" t="s">
         <v>174</v>
@@ -15518,11 +15518,11 @@
         <v>494</v>
       </c>
       <c r="B249" s="8">
-        <v>46132.422360150464</v>
+        <v>46132.58902681713</v>
       </c>
       <c r="C249" s="9"/>
       <c r="D249" s="8">
-        <v>46133.42054438658</v>
+        <v>46133.58721105324</v>
       </c>
       <c r="E249" s="9" t="s">
         <v>495</v>
@@ -15581,11 +15581,11 @@
         <v>499</v>
       </c>
       <c r="B250" s="5">
-        <v>46132.4673577662</v>
+        <v>46132.634024432875</v>
       </c>
       <c r="C250" s="6"/>
       <c r="D250" s="5">
-        <v>46133.48464278935</v>
+        <v>46133.65130945602</v>
       </c>
       <c r="E250" s="6" t="s">
         <v>174</v>
@@ -15632,11 +15632,11 @@
         <v>500</v>
       </c>
       <c r="B251" s="8">
-        <v>46132.46736601852</v>
+        <v>46132.634032685186</v>
       </c>
       <c r="C251" s="9"/>
       <c r="D251" s="8">
-        <v>46133.4846850926</v>
+        <v>46133.651351759254</v>
       </c>
       <c r="E251" s="9" t="s">
         <v>174</v>
@@ -15683,11 +15683,11 @@
         <v>501</v>
       </c>
       <c r="B252" s="5">
-        <v>46132.46737334491</v>
+        <v>46132.63404001157</v>
       </c>
       <c r="C252" s="6"/>
       <c r="D252" s="5">
-        <v>46133.48472665509</v>
+        <v>46133.65139332176</v>
       </c>
       <c r="E252" s="6" t="s">
         <v>174</v>
@@ -15734,11 +15734,11 @@
         <v>502</v>
       </c>
       <c r="B253" s="8">
-        <v>46132.46737993056</v>
+        <v>46132.63404659722</v>
       </c>
       <c r="C253" s="9"/>
       <c r="D253" s="8">
-        <v>46133.48476856481</v>
+        <v>46133.651435231484</v>
       </c>
       <c r="E253" s="9" t="s">
         <v>174</v>
@@ -15785,11 +15785,11 @@
         <v>503</v>
       </c>
       <c r="B254" s="5">
-        <v>46132.46738703703</v>
+        <v>46132.6340537037</v>
       </c>
       <c r="C254" s="6"/>
       <c r="D254" s="5">
-        <v>46133.48479761574</v>
+        <v>46133.651464282404</v>
       </c>
       <c r="E254" s="6" t="s">
         <v>174</v>
@@ -15836,11 +15836,11 @@
         <v>504</v>
       </c>
       <c r="B255" s="8">
-        <v>46132.46739449074</v>
+        <v>46132.63406115741</v>
       </c>
       <c r="C255" s="9"/>
       <c r="D255" s="8">
-        <v>46133.48484372685</v>
+        <v>46133.65151039352</v>
       </c>
       <c r="E255" s="9" t="s">
         <v>174</v>
@@ -15887,11 +15887,11 @@
         <v>505</v>
       </c>
       <c r="B256" s="5">
-        <v>46132.467399953704</v>
+        <v>46132.63406662037</v>
       </c>
       <c r="C256" s="6"/>
       <c r="D256" s="5">
-        <v>46133.48487853009</v>
+        <v>46133.65154519676</v>
       </c>
       <c r="E256" s="6" t="s">
         <v>174</v>
@@ -15938,11 +15938,11 @@
         <v>506</v>
       </c>
       <c r="B257" s="8">
-        <v>46132.46740572917</v>
+        <v>46132.634072395835</v>
       </c>
       <c r="C257" s="9"/>
       <c r="D257" s="8">
-        <v>46133.48491005787</v>
+        <v>46133.65157672454</v>
       </c>
       <c r="E257" s="9" t="s">
         <v>174</v>
@@ -15989,11 +15989,11 @@
         <v>507</v>
       </c>
       <c r="B258" s="5">
-        <v>46132.467410428246</v>
+        <v>46132.6340770949</v>
       </c>
       <c r="C258" s="6"/>
       <c r="D258" s="5">
-        <v>46133.48495219907</v>
+        <v>46133.65161886574</v>
       </c>
       <c r="E258" s="6" t="s">
         <v>174</v>
@@ -16040,11 +16040,11 @@
         <v>508</v>
       </c>
       <c r="B259" s="8">
-        <v>46132.46741611111</v>
+        <v>46132.634082777775</v>
       </c>
       <c r="C259" s="9"/>
       <c r="D259" s="8">
-        <v>46133.48498954861</v>
+        <v>46133.65165621528</v>
       </c>
       <c r="E259" s="9" t="s">
         <v>174</v>
@@ -16091,11 +16091,11 @@
         <v>509</v>
       </c>
       <c r="B260" s="5">
-        <v>46132.46742232639</v>
+        <v>46132.63408899306</v>
       </c>
       <c r="C260" s="6"/>
       <c r="D260" s="5">
-        <v>46133.485030509255</v>
+        <v>46133.65169717593</v>
       </c>
       <c r="E260" s="6" t="s">
         <v>174</v>
@@ -16142,11 +16142,11 @@
         <v>510</v>
       </c>
       <c r="B261" s="8">
-        <v>46132.46742878472</v>
+        <v>46132.63409545139</v>
       </c>
       <c r="C261" s="9"/>
       <c r="D261" s="8">
-        <v>46133.485077743055</v>
+        <v>46133.651744409726</v>
       </c>
       <c r="E261" s="9" t="s">
         <v>174</v>
@@ -16193,11 +16193,11 @@
         <v>511</v>
       </c>
       <c r="B262" s="5">
-        <v>46132.46743421296</v>
+        <v>46132.63410087963</v>
       </c>
       <c r="C262" s="6"/>
       <c r="D262" s="5">
-        <v>46133.48512136574</v>
+        <v>46133.65178803241</v>
       </c>
       <c r="E262" s="6" t="s">
         <v>174</v>
@@ -16244,11 +16244,11 @@
         <v>512</v>
       </c>
       <c r="B263" s="8">
-        <v>46132.46744021991</v>
+        <v>46132.63410688657</v>
       </c>
       <c r="C263" s="9"/>
       <c r="D263" s="8">
-        <v>46133.485174918984</v>
+        <v>46133.65184158565</v>
       </c>
       <c r="E263" s="9" t="s">
         <v>174</v>
@@ -16295,11 +16295,11 @@
         <v>513</v>
       </c>
       <c r="B264" s="5">
-        <v>46132.467446678245</v>
+        <v>46132.6341133449</v>
       </c>
       <c r="C264" s="6"/>
       <c r="D264" s="5">
-        <v>46133.485210405095</v>
+        <v>46133.65187707176</v>
       </c>
       <c r="E264" s="6" t="s">
         <v>174</v>
@@ -16346,11 +16346,11 @@
         <v>514</v>
       </c>
       <c r="B265" s="8">
-        <v>46132.467452997684</v>
+        <v>46132.63411966435</v>
       </c>
       <c r="C265" s="9"/>
       <c r="D265" s="8">
-        <v>46133.48529186343</v>
+        <v>46133.65195853009</v>
       </c>
       <c r="E265" s="9" t="s">
         <v>174</v>
@@ -16397,11 +16397,11 @@
         <v>515</v>
       </c>
       <c r="B266" s="5">
-        <v>46132.42236523148</v>
+        <v>46132.58903189815</v>
       </c>
       <c r="C266" s="6"/>
       <c r="D266" s="5">
-        <v>46133.48745912037</v>
+        <v>46133.65412578704</v>
       </c>
       <c r="E266" s="6" t="s">
         <v>516</v>
@@ -16458,11 +16458,11 @@
         <v>518</v>
       </c>
       <c r="B267" s="8">
-        <v>46132.467562025464</v>
+        <v>46132.63422869213</v>
       </c>
       <c r="C267" s="9"/>
       <c r="D267" s="8">
-        <v>46133.48746956019</v>
+        <v>46133.65413622685</v>
       </c>
       <c r="E267" s="9" t="s">
         <v>174</v>
@@ -16509,11 +16509,11 @@
         <v>520</v>
       </c>
       <c r="B268" s="5">
-        <v>46132.467568252316</v>
+        <v>46132.63423491898</v>
       </c>
       <c r="C268" s="6"/>
       <c r="D268" s="5">
-        <v>46133.48747148148</v>
+        <v>46133.65413814815</v>
       </c>
       <c r="E268" s="6" t="s">
         <v>174</v>
@@ -16560,11 +16560,11 @@
         <v>521</v>
       </c>
       <c r="B269" s="8">
-        <v>46132.46757429398</v>
+        <v>46132.634240960644</v>
       </c>
       <c r="C269" s="9"/>
       <c r="D269" s="8">
-        <v>46133.487473298606</v>
+        <v>46133.65413996528</v>
       </c>
       <c r="E269" s="9" t="s">
         <v>174</v>
@@ -16611,11 +16611,11 @@
         <v>522</v>
       </c>
       <c r="B270" s="5">
-        <v>46132.467581226854</v>
+        <v>46132.63424789352</v>
       </c>
       <c r="C270" s="6"/>
       <c r="D270" s="5">
-        <v>46133.487475104164</v>
+        <v>46133.654141770836</v>
       </c>
       <c r="E270" s="6" t="s">
         <v>174</v>
@@ -16662,11 +16662,11 @@
         <v>523</v>
       </c>
       <c r="B271" s="8">
-        <v>46132.467587719904</v>
+        <v>46132.634254386576</v>
       </c>
       <c r="C271" s="9"/>
       <c r="D271" s="8">
-        <v>46133.487476689814</v>
+        <v>46133.654143356485</v>
       </c>
       <c r="E271" s="9" t="s">
         <v>174</v>
@@ -16713,11 +16713,11 @@
         <v>524</v>
       </c>
       <c r="B272" s="5">
-        <v>46132.46759414352</v>
+        <v>46132.634260810184</v>
       </c>
       <c r="C272" s="6"/>
       <c r="D272" s="5">
-        <v>46133.487478379626</v>
+        <v>46133.6541450463</v>
       </c>
       <c r="E272" s="6" t="s">
         <v>174</v>
@@ -16764,11 +16764,11 @@
         <v>525</v>
       </c>
       <c r="B273" s="8">
-        <v>46132.46760059027</v>
+        <v>46132.634267256944</v>
       </c>
       <c r="C273" s="9"/>
       <c r="D273" s="8">
-        <v>46133.48747998843</v>
+        <v>46133.65414665509</v>
       </c>
       <c r="E273" s="9" t="s">
         <v>174</v>
@@ -16815,11 +16815,11 @@
         <v>526</v>
       </c>
       <c r="B274" s="5">
-        <v>46132.46760456018</v>
+        <v>46132.63427122685</v>
       </c>
       <c r="C274" s="6"/>
       <c r="D274" s="5">
-        <v>46133.487481689815</v>
+        <v>46133.65414835648</v>
       </c>
       <c r="E274" s="6" t="s">
         <v>174</v>
@@ -16866,11 +16866,11 @@
         <v>528</v>
       </c>
       <c r="B275" s="8">
-        <v>46132.46760969907</v>
+        <v>46132.634276365745</v>
       </c>
       <c r="C275" s="9"/>
       <c r="D275" s="8">
-        <v>46133.4874834375</v>
+        <v>46133.654150104165</v>
       </c>
       <c r="E275" s="9" t="s">
         <v>174</v>
@@ -16917,11 +16917,11 @@
         <v>529</v>
       </c>
       <c r="B276" s="5">
-        <v>46132.46761432871</v>
+        <v>46132.63428099537</v>
       </c>
       <c r="C276" s="6"/>
       <c r="D276" s="5">
-        <v>46133.48748513889</v>
+        <v>46133.65415180556</v>
       </c>
       <c r="E276" s="6" t="s">
         <v>174</v>
@@ -16968,11 +16968,11 @@
         <v>530</v>
       </c>
       <c r="B277" s="8">
-        <v>46132.46761857639</v>
+        <v>46132.63428524305</v>
       </c>
       <c r="C277" s="9"/>
       <c r="D277" s="8">
-        <v>46133.48748673611</v>
+        <v>46133.65415340278</v>
       </c>
       <c r="E277" s="9" t="s">
         <v>174</v>
@@ -17019,11 +17019,11 @@
         <v>531</v>
       </c>
       <c r="B278" s="5">
-        <v>46132.46762436343</v>
+        <v>46132.63429103009</v>
       </c>
       <c r="C278" s="6"/>
       <c r="D278" s="5">
-        <v>46133.48748846065</v>
+        <v>46133.65415512731</v>
       </c>
       <c r="E278" s="6" t="s">
         <v>174</v>
@@ -17070,11 +17070,11 @@
         <v>532</v>
       </c>
       <c r="B279" s="8">
-        <v>46132.46762856482</v>
+        <v>46132.63429523148</v>
       </c>
       <c r="C279" s="9"/>
       <c r="D279" s="8">
-        <v>46133.487490127314</v>
+        <v>46133.654156793986</v>
       </c>
       <c r="E279" s="9" t="s">
         <v>174</v>
@@ -17121,11 +17121,11 @@
         <v>533</v>
       </c>
       <c r="B280" s="5">
-        <v>46132.4676369213</v>
+        <v>46132.63430358796</v>
       </c>
       <c r="C280" s="6"/>
       <c r="D280" s="5">
-        <v>46133.487492037035</v>
+        <v>46133.654158703706</v>
       </c>
       <c r="E280" s="6" t="s">
         <v>174</v>
@@ -17172,11 +17172,11 @@
         <v>534</v>
       </c>
       <c r="B281" s="8">
-        <v>46132.46764481482</v>
+        <v>46132.63431148148</v>
       </c>
       <c r="C281" s="9"/>
       <c r="D281" s="8">
-        <v>46133.48749375</v>
+        <v>46133.65416041667</v>
       </c>
       <c r="E281" s="9" t="s">
         <v>174</v>
@@ -17223,11 +17223,11 @@
         <v>535</v>
       </c>
       <c r="B282" s="5">
-        <v>46132.467709965276</v>
+        <v>46132.63437663195</v>
       </c>
       <c r="C282" s="6"/>
       <c r="D282" s="5">
-        <v>46133.4874959375</v>
+        <v>46133.654162604165</v>
       </c>
       <c r="E282" s="6" t="s">
         <v>174</v>
@@ -17274,11 +17274,11 @@
         <v>536</v>
       </c>
       <c r="B283" s="8">
-        <v>46132.4223709375</v>
+        <v>46132.589037604164</v>
       </c>
       <c r="C283" s="9"/>
       <c r="D283" s="8">
-        <v>46133.425690034725</v>
+        <v>46133.59235670139</v>
       </c>
       <c r="E283" s="9" t="s">
         <v>537</v>
@@ -17321,11 +17321,11 @@
         <v>538</v>
       </c>
       <c r="B284" s="5">
-        <v>46132.42237400463</v>
+        <v>46132.5890406713</v>
       </c>
       <c r="C284" s="6"/>
       <c r="D284" s="5">
-        <v>46134.41258914352</v>
+        <v>46134.57925581018</v>
       </c>
       <c r="E284" s="6" t="s">
         <v>539</v>
@@ -17384,11 +17384,11 @@
         <v>543</v>
       </c>
       <c r="B285" s="8">
-        <v>46132.42237892361</v>
+        <v>46132.58904559028</v>
       </c>
       <c r="C285" s="9"/>
       <c r="D285" s="8">
-        <v>46134.412592361114</v>
+        <v>46134.57925902778</v>
       </c>
       <c r="E285" s="9" t="s">
         <v>544</v>

--- a/data/50001541 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001541 - XEMORTIZ MINERA FRISCO.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3235" uniqueCount="546">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3235" uniqueCount="548">
   <si>
     <t>50001541 -  XEMORTIZ MINERA FRISCO</t>
   </si>
@@ -88,7 +88,7 @@
     <t>Kick Off meeting:</t>
   </si>
   <si>
-    <t>Fabricación 50001541-OT 4232 ZVN 1-9-86/2 XEMORTIZ MINERA FRISCO</t>
+    <t>Fabricación 50001541-OT 4307 ZVN 1-9-86/2 XEMORTIZ MINERA FRISCO</t>
   </si>
   <si>
     <t/>
@@ -511,7 +511,7 @@
     <t>1214138711508170</t>
   </si>
   <si>
-    <t>Propuesta Fabricación externa  OT 4307 ,Propuesta Mecanizado,Propuesta Corte plasma ,propuesta Corte laser,Ingenieria y diseñoo:,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2</t>
+    <t>Propuesta Fabricación externa  OT 4307 ,Propuesta Mecanizado,Propuesta Corte plasma ,propuesta Corte laser,Ingenieria y diseñoo:,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2</t>
   </si>
   <si>
     <t>1214138720958805</t>
@@ -688,7 +688,7 @@
     <t>nicolas.lopez@zitron.com</t>
   </si>
   <si>
-    <t xml:space="preserve">Bodega ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 </t>
+    <t xml:space="preserve">Bodega ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 </t>
   </si>
   <si>
     <t>1214137717389805</t>
@@ -697,7 +697,7 @@
     <t xml:space="preserve">Control de calidad Corte plasma </t>
   </si>
   <si>
-    <t xml:space="preserve">Bodega ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 </t>
+    <t xml:space="preserve">Bodega ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 </t>
   </si>
   <si>
     <t>1214137717389806</t>
@@ -724,7 +724,7 @@
     <t>rosemary.singh@zitron.com</t>
   </si>
   <si>
-    <t xml:space="preserve">Fabricación externa:,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 </t>
+    <t xml:space="preserve">Fabricación externa:,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 </t>
   </si>
   <si>
     <t>1214138711519166</t>
@@ -733,271 +733,277 @@
     <t>Armado</t>
   </si>
   <si>
+    <t xml:space="preserve">OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 </t>
+  </si>
+  <si>
+    <t>1214137717389464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4307 ZVN 1-9-86/2 </t>
+  </si>
+  <si>
+    <t>Generación OC Fabricación externa ,Control de calidad Mecanizado,Control de calidad corte Laser,Control de calidad Corte plasma ,Check Planos</t>
+  </si>
+  <si>
+    <t>OT 4232 ZVN 1-9-86/2,Armado</t>
+  </si>
+  <si>
+    <t>1214137717389465</t>
+  </si>
+  <si>
+    <t>1214137717389466</t>
+  </si>
+  <si>
+    <t>Generación OC Fabricación externa ,Control de calidad corte Laser,Control de calidad Corte plasma ,Control de calidad Mecanizado,Check Planos</t>
+  </si>
+  <si>
+    <t>Armado,OT 4232 ZVN 1-9-86/2</t>
+  </si>
+  <si>
+    <t>1214137717389467</t>
+  </si>
+  <si>
+    <t>1214137717389468</t>
+  </si>
+  <si>
+    <t>Generación OC Fabricación externa ,Control de calidad corte Laser,Control de calidad Mecanizado,Check Planos</t>
+  </si>
+  <si>
+    <t>1214137717389469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Mecanizado,Generación OC Fabricación externa ,Check Planos,Control de calidad corte Laser,Control de calidad Corte plasma </t>
+  </si>
+  <si>
+    <t>1214137717389470</t>
+  </si>
+  <si>
+    <t>Control de calidad corte Laser,Control de calidad Corte plasma ,Control de calidad Mecanizado,Generación OC Fabricación externa ,Check Planos</t>
+  </si>
+  <si>
+    <t>1214137717389471</t>
+  </si>
+  <si>
+    <t>Control de calidad Corte plasma ,Generación OC Fabricación externa ,Check Planos,Control de calidad corte Laser</t>
+  </si>
+  <si>
+    <t>1214137717389472</t>
+  </si>
+  <si>
+    <t>1214137717389473</t>
+  </si>
+  <si>
+    <t>Control de calidad corte Laser,Control de calidad Corte plasma ,Generación OC Fabricación externa ,Check Planos</t>
+  </si>
+  <si>
+    <t>1214137717389474</t>
+  </si>
+  <si>
+    <t>1214137717389475</t>
+  </si>
+  <si>
+    <t>1214137717389476</t>
+  </si>
+  <si>
+    <t>1214137717389477</t>
+  </si>
+  <si>
+    <t>Control de calidad corte Laser,Control de calidad Mecanizado,Generación OC Fabricación externa ,Check Planos</t>
+  </si>
+  <si>
+    <t>1214137717389478</t>
+  </si>
+  <si>
+    <t>OT 4232 ZVN 1-9-86/2 ,Armado</t>
+  </si>
+  <si>
+    <t>1214137717389479</t>
+  </si>
+  <si>
+    <t>1214138711519194</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2</t>
+  </si>
+  <si>
+    <t>1214137717389481</t>
+  </si>
+  <si>
+    <t>OT 4232 ZVN 1-9-86/2</t>
+  </si>
+  <si>
+    <t>OT 4307 ZVN 1-9-86/2 ,Check Planos</t>
+  </si>
+  <si>
+    <t>OT 4232 ZVN 1-9-86/2 ,Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>1214137717389482</t>
+  </si>
+  <si>
+    <t>OT 4232 ZVN 1-9-86/2,Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>1214137717389483</t>
+  </si>
+  <si>
+    <t>1214137717389484</t>
+  </si>
+  <si>
+    <t>1214137717389485</t>
+  </si>
+  <si>
+    <t>1214137717389486</t>
+  </si>
+  <si>
+    <t>1214137717389487</t>
+  </si>
+  <si>
+    <t>1214137717389488</t>
+  </si>
+  <si>
+    <t>1214137717389489</t>
+  </si>
+  <si>
+    <t>1214137717389490</t>
+  </si>
+  <si>
+    <t>1214137717389491</t>
+  </si>
+  <si>
+    <t>1214137717389492</t>
+  </si>
+  <si>
+    <t>1214137717389493</t>
+  </si>
+  <si>
+    <t>1214137717389494</t>
+  </si>
+  <si>
+    <t>1214137717389495</t>
+  </si>
+  <si>
+    <t>1214137717389497</t>
+  </si>
+  <si>
+    <t>1214138720971081</t>
+  </si>
+  <si>
+    <t>Bodega:</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete,Recepcion motor,Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>1214138844805204</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodega:,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 </t>
+  </si>
+  <si>
+    <t>1214138844805224</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete</t>
+  </si>
+  <si>
+    <t>1214138720975469</t>
+  </si>
+  <si>
+    <t>Recepcion motor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodega:,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 </t>
+  </si>
+  <si>
+    <t>1214138720975489</t>
+  </si>
+  <si>
+    <t>Montaje:</t>
+  </si>
+  <si>
+    <t>Revestimiento,Montaje motor,Montaje Rodete,RE-PINTADO,Montaje Alabe,Pruebas FAT</t>
+  </si>
+  <si>
+    <t>1214138644320327</t>
+  </si>
+  <si>
+    <t>Revestimiento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 </t>
+  </si>
+  <si>
+    <t>1214137717389498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4232 ZVN 1-9-86/2 ,Revestimiento,OT 4232 ZVN 1-9-86/2 </t>
+  </si>
+  <si>
+    <t>1214137717389499</t>
+  </si>
+  <si>
+    <t>1214137717389500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4232 ZVN 1-9-86/2 ,Revestimiento,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 </t>
+  </si>
+  <si>
+    <t>1214137717389501</t>
+  </si>
+  <si>
+    <t>1214137717389502</t>
+  </si>
+  <si>
+    <t>1214137717389503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revestimiento,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 </t>
+  </si>
+  <si>
+    <t>1214137717389504</t>
+  </si>
+  <si>
+    <t>1214137717389505</t>
+  </si>
+  <si>
+    <t>1214137717389506</t>
+  </si>
+  <si>
+    <t>1214137717389508</t>
+  </si>
+  <si>
+    <t>1214137717389507</t>
+  </si>
+  <si>
+    <t>1214137717389509</t>
+  </si>
+  <si>
+    <t>1214137717389510</t>
+  </si>
+  <si>
+    <t>1214137717389511</t>
+  </si>
+  <si>
+    <t>1214137717389512</t>
+  </si>
+  <si>
+    <t>1214137717389513</t>
+  </si>
+  <si>
+    <t>1214138711530631</t>
+  </si>
+  <si>
+    <t>Montaje Alabe</t>
+  </si>
+  <si>
     <t xml:space="preserve">OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 </t>
-  </si>
-  <si>
-    <t>1214137717389464</t>
-  </si>
-  <si>
-    <t>Generación OC Fabricación externa ,Control de calidad Mecanizado,Control de calidad corte Laser,Control de calidad Corte plasma ,Check Planos</t>
-  </si>
-  <si>
-    <t>OT 4232 ZVN 1-9-86/2,Armado</t>
-  </si>
-  <si>
-    <t>1214137717389465</t>
-  </si>
-  <si>
-    <t>1214137717389466</t>
-  </si>
-  <si>
-    <t>Generación OC Fabricación externa ,Control de calidad corte Laser,Control de calidad Corte plasma ,Control de calidad Mecanizado,Check Planos</t>
-  </si>
-  <si>
-    <t>Armado,OT 4232 ZVN 1-9-86/2</t>
-  </si>
-  <si>
-    <t>1214137717389467</t>
-  </si>
-  <si>
-    <t>1214137717389468</t>
-  </si>
-  <si>
-    <t>Generación OC Fabricación externa ,Control de calidad corte Laser,Control de calidad Mecanizado,Check Planos</t>
-  </si>
-  <si>
-    <t>1214137717389469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Mecanizado,Generación OC Fabricación externa ,Check Planos,Control de calidad corte Laser,Control de calidad Corte plasma </t>
-  </si>
-  <si>
-    <t>1214137717389470</t>
-  </si>
-  <si>
-    <t>Control de calidad corte Laser,Control de calidad Corte plasma ,Control de calidad Mecanizado,Generación OC Fabricación externa ,Check Planos</t>
-  </si>
-  <si>
-    <t>1214137717389471</t>
-  </si>
-  <si>
-    <t>Control de calidad Corte plasma ,Generación OC Fabricación externa ,Check Planos,Control de calidad corte Laser</t>
-  </si>
-  <si>
-    <t>1214137717389472</t>
-  </si>
-  <si>
-    <t>1214137717389473</t>
-  </si>
-  <si>
-    <t>Control de calidad corte Laser,Control de calidad Corte plasma ,Generación OC Fabricación externa ,Check Planos</t>
-  </si>
-  <si>
-    <t>1214137717389474</t>
-  </si>
-  <si>
-    <t>1214137717389475</t>
-  </si>
-  <si>
-    <t>1214137717389476</t>
-  </si>
-  <si>
-    <t>1214137717389477</t>
-  </si>
-  <si>
-    <t>Control de calidad corte Laser,Control de calidad Mecanizado,Generación OC Fabricación externa ,Check Planos</t>
-  </si>
-  <si>
-    <t>1214137717389478</t>
-  </si>
-  <si>
-    <t>OT 4232 ZVN 1-9-86/2 ,Armado</t>
-  </si>
-  <si>
-    <t>1214137717389479</t>
-  </si>
-  <si>
-    <t>1214138711519194</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2</t>
-  </si>
-  <si>
-    <t>1214137717389481</t>
-  </si>
-  <si>
-    <t>OT 4232 ZVN 1-9-86/2</t>
-  </si>
-  <si>
-    <t>OT 4232 ZVN 1-9-86/2 ,Check Planos</t>
-  </si>
-  <si>
-    <t>OT 4232 ZVN 1-9-86/2 ,Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>1214137717389482</t>
-  </si>
-  <si>
-    <t>OT 4232 ZVN 1-9-86/2,Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>1214137717389483</t>
-  </si>
-  <si>
-    <t>1214137717389484</t>
-  </si>
-  <si>
-    <t>1214137717389485</t>
-  </si>
-  <si>
-    <t>1214137717389486</t>
-  </si>
-  <si>
-    <t>1214137717389487</t>
-  </si>
-  <si>
-    <t>1214137717389488</t>
-  </si>
-  <si>
-    <t>1214137717389489</t>
-  </si>
-  <si>
-    <t>1214137717389490</t>
-  </si>
-  <si>
-    <t>1214137717389491</t>
-  </si>
-  <si>
-    <t>1214137717389492</t>
-  </si>
-  <si>
-    <t>1214137717389493</t>
-  </si>
-  <si>
-    <t>1214137717389494</t>
-  </si>
-  <si>
-    <t>1214137717389495</t>
-  </si>
-  <si>
-    <t>1214137717389497</t>
-  </si>
-  <si>
-    <t>1214138720971081</t>
-  </si>
-  <si>
-    <t>Bodega:</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete,Recepcion motor,Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>1214138844805204</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodega:,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 </t>
-  </si>
-  <si>
-    <t>1214138844805224</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete</t>
-  </si>
-  <si>
-    <t>1214138720975469</t>
-  </si>
-  <si>
-    <t>Recepcion motor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodega:,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 </t>
-  </si>
-  <si>
-    <t>1214138720975489</t>
-  </si>
-  <si>
-    <t>Montaje:</t>
-  </si>
-  <si>
-    <t>Revestimiento,Montaje motor,Montaje Rodete,RE-PINTADO,Montaje Alabe,Pruebas FAT</t>
-  </si>
-  <si>
-    <t>1214138644320327</t>
-  </si>
-  <si>
-    <t>Revestimiento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 </t>
-  </si>
-  <si>
-    <t>1214137717389498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4232 ZVN 1-9-86/2 ,Revestimiento,OT 4232 ZVN 1-9-86/2 </t>
-  </si>
-  <si>
-    <t>1214137717389499</t>
-  </si>
-  <si>
-    <t>1214137717389500</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4232 ZVN 1-9-86/2 ,Revestimiento,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 </t>
-  </si>
-  <si>
-    <t>1214137717389501</t>
-  </si>
-  <si>
-    <t>1214137717389502</t>
-  </si>
-  <si>
-    <t>1214137717389503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revestimiento,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 </t>
-  </si>
-  <si>
-    <t>1214137717389504</t>
-  </si>
-  <si>
-    <t>1214137717389505</t>
-  </si>
-  <si>
-    <t>1214137717389506</t>
-  </si>
-  <si>
-    <t>1214137717389508</t>
-  </si>
-  <si>
-    <t>1214137717389507</t>
-  </si>
-  <si>
-    <t>1214137717389509</t>
-  </si>
-  <si>
-    <t>1214137717389510</t>
-  </si>
-  <si>
-    <t>1214137717389511</t>
-  </si>
-  <si>
-    <t>1214137717389512</t>
-  </si>
-  <si>
-    <t>1214137717389513</t>
-  </si>
-  <si>
-    <t>1214138711530631</t>
-  </si>
-  <si>
-    <t>Montaje Alabe</t>
   </si>
   <si>
     <t>1214137717389530</t>
@@ -6234,7 +6240,7 @@
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46132.789973067134</v>
+        <v>46196.691984930556</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>232</v>
@@ -6279,9 +6285,11 @@
       <c r="B72" s="5">
         <v>46132.588885185185</v>
       </c>
-      <c r="C72" s="6"/>
+      <c r="C72" s="5">
+        <v>46196.68414012731</v>
+      </c>
       <c r="D72" s="5">
-        <v>46196.640668113425</v>
+        <v>46196.68415487268</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>83</v>
@@ -6329,10 +6337,10 @@
         <v>32</v>
       </c>
       <c r="T72" s="6">
-        <v>0</v>
-      </c>
-      <c r="U72" s="12" t="s">
-        <v>58</v>
+        <v>1</v>
+      </c>
+      <c r="U72" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
@@ -6342,9 +6350,11 @@
       <c r="B73" s="8">
         <v>46132.58889042824</v>
       </c>
-      <c r="C73" s="9"/>
+      <c r="C73" s="8">
+        <v>46196.69197697917</v>
+      </c>
       <c r="D73" s="8">
-        <v>46134.56784579861</v>
+        <v>46196.692663379625</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>239</v>
@@ -6392,10 +6402,10 @@
         <v>100</v>
       </c>
       <c r="T73" s="9">
-        <v>0</v>
-      </c>
-      <c r="U73" s="10" t="s">
-        <v>101</v>
+        <v>1</v>
+      </c>
+      <c r="U73" s="12" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
@@ -6405,12 +6415,14 @@
       <c r="B74" s="5">
         <v>46132.631278472225</v>
       </c>
-      <c r="C74" s="6"/>
+      <c r="C74" s="5">
+        <v>46196.69130792824</v>
+      </c>
       <c r="D74" s="5">
-        <v>46191.91761795139</v>
+        <v>46196.69266049768</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>174</v>
+        <v>242</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -6440,10 +6452,10 @@
         <v>239</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6453,17 +6465,19 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B75" s="8">
         <v>46132.63129450232</v>
       </c>
-      <c r="C75" s="9"/>
+      <c r="C75" s="8">
+        <v>46196.69160608796</v>
+      </c>
       <c r="D75" s="8">
-        <v>46191.917625381946</v>
+        <v>46196.692844907404</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>174</v>
+        <v>242</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
@@ -6493,10 +6507,10 @@
         <v>239</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q75" s="9"/>
       <c r="R75" s="9"/>
@@ -6506,17 +6520,19 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B76" s="5">
         <v>46132.63130252315</v>
       </c>
-      <c r="C76" s="6"/>
+      <c r="C76" s="5">
+        <v>46196.69194896991</v>
+      </c>
       <c r="D76" s="5">
-        <v>46191.91760784722</v>
+        <v>46196.69317986111</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>174</v>
+        <v>242</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -6546,10 +6562,10 @@
         <v>239</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6559,17 +6575,19 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B77" s="8">
         <v>46132.63130869213</v>
       </c>
-      <c r="C77" s="9"/>
+      <c r="C77" s="8">
+        <v>46196.69194981482</v>
+      </c>
       <c r="D77" s="8">
-        <v>46191.91762702547</v>
+        <v>46196.693142592594</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>174</v>
+        <v>242</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
@@ -6599,10 +6617,10 @@
         <v>239</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q77" s="9"/>
       <c r="R77" s="9"/>
@@ -6612,17 +6630,19 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B78" s="5">
         <v>46132.631314467595</v>
       </c>
-      <c r="C78" s="6"/>
+      <c r="C78" s="5">
+        <v>46196.691950416665</v>
+      </c>
       <c r="D78" s="5">
-        <v>46191.91762633102</v>
+        <v>46196.693131458334</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>174</v>
+        <v>242</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -6652,10 +6672,10 @@
         <v>239</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6665,17 +6685,19 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B79" s="8">
         <v>46132.6313205787</v>
       </c>
-      <c r="C79" s="9"/>
+      <c r="C79" s="8">
+        <v>46196.69195099537</v>
+      </c>
       <c r="D79" s="8">
-        <v>46191.917616875</v>
+        <v>46196.693120717595</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>174</v>
+        <v>242</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
@@ -6705,10 +6727,10 @@
         <v>239</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q79" s="9"/>
       <c r="R79" s="9"/>
@@ -6718,17 +6740,19 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B80" s="5">
         <v>46132.6313259375</v>
       </c>
-      <c r="C80" s="6"/>
+      <c r="C80" s="5">
+        <v>46196.69195158565</v>
+      </c>
       <c r="D80" s="5">
-        <v>46191.91762666666</v>
+        <v>46196.69310042824</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>174</v>
+        <v>242</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6758,10 +6782,10 @@
         <v>239</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6771,17 +6795,19 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B81" s="8">
         <v>46132.63133041667</v>
       </c>
-      <c r="C81" s="9"/>
+      <c r="C81" s="8">
+        <v>46196.69195221065</v>
+      </c>
       <c r="D81" s="8">
-        <v>46191.91762113426</v>
+        <v>46196.693085949075</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>174</v>
+        <v>242</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
@@ -6811,10 +6837,10 @@
         <v>239</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q81" s="9"/>
       <c r="R81" s="9"/>
@@ -6824,17 +6850,19 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B82" s="5">
         <v>46132.63133645833</v>
       </c>
-      <c r="C82" s="6"/>
+      <c r="C82" s="5">
+        <v>46196.69195284722</v>
+      </c>
       <c r="D82" s="5">
-        <v>46191.91762170139</v>
+        <v>46196.69307368055</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>174</v>
+        <v>242</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6864,10 +6892,10 @@
         <v>239</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6877,17 +6905,19 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B83" s="8">
         <v>46132.63134074074</v>
       </c>
-      <c r="C83" s="9"/>
+      <c r="C83" s="8">
+        <v>46196.69174834491</v>
+      </c>
       <c r="D83" s="8">
-        <v>46191.9176284375</v>
+        <v>46196.69306041667</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>174</v>
+        <v>242</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
@@ -6917,10 +6947,10 @@
         <v>239</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q83" s="9"/>
       <c r="R83" s="9"/>
@@ -6930,17 +6960,19 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B84" s="5">
         <v>46132.631346469905</v>
       </c>
-      <c r="C84" s="6"/>
+      <c r="C84" s="5">
+        <v>46196.691953437505</v>
+      </c>
       <c r="D84" s="5">
-        <v>46191.91762577546</v>
+        <v>46196.693049560185</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>174</v>
+        <v>242</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6970,10 +7002,10 @@
         <v>239</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6983,17 +7015,19 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B85" s="8">
         <v>46132.631352083336</v>
       </c>
-      <c r="C85" s="9"/>
+      <c r="C85" s="8">
+        <v>46196.69195403935</v>
+      </c>
       <c r="D85" s="8">
-        <v>46191.91762925926</v>
+        <v>46196.6930421412</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>174</v>
+        <v>242</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
@@ -7023,10 +7057,10 @@
         <v>239</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q85" s="9"/>
       <c r="R85" s="9"/>
@@ -7036,17 +7070,19 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B86" s="5">
         <v>46132.63135776621</v>
       </c>
-      <c r="C86" s="6"/>
+      <c r="C86" s="5">
+        <v>46196.69195462963</v>
+      </c>
       <c r="D86" s="5">
-        <v>46191.91760960648</v>
+        <v>46196.69303037037</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>174</v>
+        <v>242</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -7076,10 +7112,10 @@
         <v>239</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -7089,17 +7125,19 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B87" s="8">
         <v>46132.63136296296</v>
       </c>
-      <c r="C87" s="9"/>
+      <c r="C87" s="8">
+        <v>46196.6919552662</v>
+      </c>
       <c r="D87" s="8">
-        <v>46191.91760861111</v>
+        <v>46196.69302122685</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>174</v>
+        <v>242</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
@@ -7129,10 +7167,10 @@
         <v>239</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P87" s="9" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q87" s="9"/>
       <c r="R87" s="9"/>
@@ -7142,17 +7180,19 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B88" s="5">
         <v>46132.63136688658</v>
       </c>
-      <c r="C88" s="6"/>
+      <c r="C88" s="5">
+        <v>46196.69195586805</v>
+      </c>
       <c r="D88" s="5">
-        <v>46191.91763945602</v>
+        <v>46196.692995543985</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>174</v>
+        <v>242</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -7182,10 +7222,10 @@
         <v>239</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -7195,17 +7235,19 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B89" s="8">
         <v>46132.63137239583</v>
       </c>
-      <c r="C89" s="9"/>
+      <c r="C89" s="8">
+        <v>46196.69195645834</v>
+      </c>
       <c r="D89" s="8">
-        <v>46191.91761834491</v>
+        <v>46196.69300998843</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>174</v>
+        <v>242</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
@@ -7235,10 +7277,10 @@
         <v>239</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q89" s="9"/>
       <c r="R89" s="9"/>
@@ -7248,7 +7290,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B90" s="5">
         <v>46132.58889809028</v>
@@ -7258,7 +7300,7 @@
         <v>46134.56786915509</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -7288,7 +7330,7 @@
         <v>232</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>232</v>
@@ -7311,17 +7353,17 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B91" s="8">
         <v>46132.63147894676</v>
       </c>
       <c r="C91" s="9"/>
       <c r="D91" s="8">
-        <v>46191.91762224537</v>
+        <v>46196.691315324075</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
@@ -7348,13 +7390,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q91" s="9"/>
       <c r="R91" s="9"/>
@@ -7364,17 +7406,17 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B92" s="5">
         <v>46132.63149082176</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46191.91762974537</v>
+        <v>46196.691612083334</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -7401,13 +7443,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -7417,17 +7459,17 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B93" s="8">
         <v>46132.63149714121</v>
       </c>
       <c r="C93" s="9"/>
       <c r="D93" s="8">
-        <v>46191.91764103009</v>
+        <v>46196.69197650463</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
@@ -7454,13 +7496,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q93" s="9"/>
       <c r="R93" s="9"/>
@@ -7470,17 +7512,17 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B94" s="5">
         <v>46132.63150280093</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46191.91761954861</v>
+        <v>46196.691969039355</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -7507,13 +7549,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7523,17 +7565,17 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B95" s="8">
         <v>46132.63150895834</v>
       </c>
       <c r="C95" s="9"/>
       <c r="D95" s="8">
-        <v>46191.91762753473</v>
+        <v>46196.69196927083</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
@@ -7560,13 +7602,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q95" s="9"/>
       <c r="R95" s="9"/>
@@ -7576,17 +7618,17 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B96" s="5">
         <v>46132.63151432871</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46191.91762277778</v>
+        <v>46196.691969363426</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7613,13 +7655,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7629,17 +7671,17 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B97" s="8">
         <v>46132.631519525465</v>
       </c>
       <c r="C97" s="9"/>
       <c r="D97" s="8">
-        <v>46191.91761885417</v>
+        <v>46196.69196891204</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
@@ -7666,13 +7708,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q97" s="9"/>
       <c r="R97" s="9"/>
@@ -7682,17 +7724,17 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B98" s="5">
         <v>46132.631524247685</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46191.91762894676</v>
+        <v>46196.6919696875</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7719,13 +7761,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7735,17 +7777,17 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B99" s="8">
         <v>46132.63153150463</v>
       </c>
       <c r="C99" s="9"/>
       <c r="D99" s="8">
-        <v>46191.917623368056</v>
+        <v>46196.69196924768</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
@@ -7772,13 +7814,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P99" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q99" s="9"/>
       <c r="R99" s="9"/>
@@ -7788,17 +7830,17 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B100" s="5">
         <v>46132.631539270835</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46191.91762390046</v>
+        <v>46196.691753541665</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7825,13 +7867,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7841,17 +7883,17 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B101" s="8">
         <v>46132.63154616898</v>
       </c>
       <c r="C101" s="9"/>
       <c r="D101" s="8">
-        <v>46191.917624699076</v>
+        <v>46196.691969189815</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
@@ -7878,13 +7920,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P101" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q101" s="9"/>
       <c r="R101" s="9"/>
@@ -7894,17 +7936,17 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B102" s="5">
         <v>46132.63155506944</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46191.91762795139</v>
+        <v>46196.691969189815</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7931,13 +7973,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7947,17 +7989,17 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B103" s="8">
         <v>46132.63156422453</v>
       </c>
       <c r="C103" s="9"/>
       <c r="D103" s="8">
-        <v>46191.91763030093</v>
+        <v>46196.691969224536</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>26</v>
@@ -7984,13 +8026,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P103" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q103" s="9"/>
       <c r="R103" s="9"/>
@@ -8000,17 +8042,17 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B104" s="5">
         <v>46132.63157251157</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46191.91761167824</v>
+        <v>46196.69196909722</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -8037,13 +8079,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -8053,14 +8095,14 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B105" s="8">
         <v>46132.631576643515</v>
       </c>
       <c r="C105" s="9"/>
       <c r="D105" s="8">
-        <v>46191.91762054398</v>
+        <v>46196.69196927083</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>174</v>
@@ -8090,13 +8132,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P105" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q105" s="9"/>
       <c r="R105" s="9"/>
@@ -8106,17 +8148,17 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B106" s="5">
         <v>46132.6319078588</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46191.91761039352</v>
+        <v>46196.69196938658</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -8143,13 +8185,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -8159,7 +8201,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B107" s="8">
         <v>46132.58890393519</v>
@@ -8169,7 +8211,7 @@
         <v>46157.54205033564</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>25</v>
@@ -8193,7 +8235,7 @@
         <v>26</v>
       </c>
       <c r="O107" s="9" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="P107" s="9" t="s">
         <v>26</v>
@@ -8206,7 +8248,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B108" s="5">
         <v>46132.58890717593</v>
@@ -8216,7 +8258,7 @@
         <v>46157.54340230324</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -8241,13 +8283,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="O108" s="6" t="s">
         <v>103</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q108" s="5">
         <v>46146</v>
@@ -8267,7 +8309,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B109" s="8">
         <v>46132.58891280093</v>
@@ -8279,7 +8321,7 @@
         <v>46163.18906322916</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>26</v>
@@ -8304,13 +8346,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="9" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="O109" s="9" t="s">
         <v>112</v>
       </c>
       <c r="P109" s="9" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q109" s="8">
         <v>46162</v>
@@ -8330,7 +8372,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B110" s="5">
         <v>46132.588918090274</v>
@@ -8340,7 +8382,7 @@
         <v>46191.909131064815</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -8365,13 +8407,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="O110" s="6" t="s">
         <v>122</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q110" s="5">
         <v>46176</v>
@@ -8391,7 +8433,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B111" s="8">
         <v>46132.58892311342</v>
@@ -8401,7 +8443,7 @@
         <v>46133.5836275926</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>25</v>
@@ -8425,7 +8467,7 @@
         <v>26</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P111" s="9" t="s">
         <v>26</v>
@@ -8438,7 +8480,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B112" s="5">
         <v>46132.58892658565</v>
@@ -8448,7 +8490,7 @@
         <v>46134.57907140046</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8475,13 +8517,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q112" s="5">
         <v>46217</v>
@@ -8501,7 +8543,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B113" s="8">
         <v>46132.632033182876</v>
@@ -8538,13 +8580,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P113" s="9" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q113" s="9"/>
       <c r="R113" s="9"/>
@@ -8554,7 +8596,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B114" s="5">
         <v>46132.6321053125</v>
@@ -8564,7 +8606,7 @@
         <v>46134.56662060185</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
@@ -8591,13 +8633,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -8607,7 +8649,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B115" s="8">
         <v>46132.63211394676</v>
@@ -8617,7 +8659,7 @@
         <v>46134.56666482639</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>26</v>
@@ -8644,13 +8686,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O115" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P115" s="9" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q115" s="9"/>
       <c r="R115" s="9"/>
@@ -8660,7 +8702,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B116" s="5">
         <v>46132.6321221875</v>
@@ -8697,13 +8739,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8713,7 +8755,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B117" s="8">
         <v>46132.63212829861</v>
@@ -8750,13 +8792,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O117" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P117" s="9" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q117" s="9"/>
       <c r="R117" s="9"/>
@@ -8766,7 +8808,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B118" s="5">
         <v>46132.63213525463</v>
@@ -8803,13 +8845,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8819,7 +8861,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B119" s="8">
         <v>46132.63214342593</v>
@@ -8829,7 +8871,7 @@
         <v>46134.56685320602</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>26</v>
@@ -8856,13 +8898,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O119" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P119" s="9" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q119" s="9"/>
       <c r="R119" s="9"/>
@@ -8872,7 +8914,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B120" s="5">
         <v>46132.63215114584</v>
@@ -8909,13 +8951,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8925,7 +8967,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B121" s="8">
         <v>46132.63216016204</v>
@@ -8962,13 +9004,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O121" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P121" s="9" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q121" s="9"/>
       <c r="R121" s="9"/>
@@ -8978,7 +9020,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B122" s="5">
         <v>46132.6321746412</v>
@@ -8988,7 +9030,7 @@
         <v>46134.566921770835</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -9015,13 +9057,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -9031,7 +9073,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B123" s="8">
         <v>46132.63216719907</v>
@@ -9068,13 +9110,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O123" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P123" s="9" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q123" s="9"/>
       <c r="R123" s="9"/>
@@ -9084,7 +9126,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B124" s="5">
         <v>46132.63218074074</v>
@@ -9121,13 +9163,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -9137,7 +9179,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B125" s="8">
         <v>46132.632186863426</v>
@@ -9174,13 +9216,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O125" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P125" s="9" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q125" s="9"/>
       <c r="R125" s="9"/>
@@ -9190,7 +9232,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B126" s="5">
         <v>46132.63219409723</v>
@@ -9227,13 +9269,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -9243,7 +9285,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B127" s="8">
         <v>46132.63220086806</v>
@@ -9280,13 +9322,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O127" s="9" t="s">
         <v>174</v>
       </c>
       <c r="P127" s="9" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q127" s="9"/>
       <c r="R127" s="9"/>
@@ -9296,7 +9338,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B128" s="5">
         <v>46132.63220734954</v>
@@ -9333,13 +9375,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -9349,7 +9391,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B129" s="8">
         <v>46132.58893864583</v>
@@ -9359,7 +9401,7 @@
         <v>46134.57915813658</v>
       </c>
       <c r="E129" s="9" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>26</v>
@@ -9384,13 +9426,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="9" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O129" s="9" t="s">
-        <v>240</v>
+        <v>330</v>
       </c>
       <c r="P129" s="9" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q129" s="8">
         <v>46218</v>
@@ -9410,7 +9452,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B130" s="5">
         <v>46132.63296805556</v>
@@ -9445,13 +9487,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -9461,7 +9503,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B131" s="8">
         <v>46132.63297954861</v>
@@ -9496,13 +9538,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="9" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O131" s="9" t="s">
+        <v>335</v>
+      </c>
+      <c r="P131" s="9" t="s">
         <v>333</v>
-      </c>
-      <c r="P131" s="9" t="s">
-        <v>331</v>
       </c>
       <c r="Q131" s="9"/>
       <c r="R131" s="9"/>
@@ -9512,7 +9554,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B132" s="5">
         <v>46132.63298759259</v>
@@ -9547,13 +9589,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O132" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="P132" s="6" t="s">
         <v>333</v>
-      </c>
-      <c r="P132" s="6" t="s">
-        <v>331</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9563,7 +9605,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B133" s="8">
         <v>46132.63299327546</v>
@@ -9598,13 +9640,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="9" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O133" s="9" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="P133" s="9" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q133" s="9"/>
       <c r="R133" s="9"/>
@@ -9614,7 +9656,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B134" s="5">
         <v>46132.63299994213</v>
@@ -9649,13 +9691,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9665,7 +9707,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B135" s="8">
         <v>46132.63300702546</v>
@@ -9700,13 +9742,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="9" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O135" s="9" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="P135" s="9" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q135" s="9"/>
       <c r="R135" s="9"/>
@@ -9716,7 +9758,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B136" s="5">
         <v>46132.633012708335</v>
@@ -9751,13 +9793,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9767,7 +9809,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B137" s="8">
         <v>46132.63302</v>
@@ -9802,13 +9844,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="9" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O137" s="9" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="P137" s="9" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q137" s="9"/>
       <c r="R137" s="9"/>
@@ -9818,7 +9860,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B138" s="5">
         <v>46132.63302648148</v>
@@ -9853,13 +9895,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9869,7 +9911,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B139" s="8">
         <v>46132.633032858794</v>
@@ -9904,13 +9946,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="9" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O139" s="9" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="P139" s="9" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q139" s="9"/>
       <c r="R139" s="9"/>
@@ -9920,7 +9962,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B140" s="5">
         <v>46132.633039409724</v>
@@ -9955,13 +9997,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -9971,7 +10013,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B141" s="8">
         <v>46132.633045821756</v>
@@ -10006,13 +10048,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="9" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O141" s="9" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="P141" s="9" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q141" s="9"/>
       <c r="R141" s="9"/>
@@ -10022,7 +10064,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B142" s="5">
         <v>46132.633060057866</v>
@@ -10057,13 +10099,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -10073,7 +10115,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="7" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B143" s="8">
         <v>46132.633052986115</v>
@@ -10108,13 +10150,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="9" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O143" s="9" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="P143" s="9" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q143" s="9"/>
       <c r="R143" s="9"/>
@@ -10124,7 +10166,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B144" s="5">
         <v>46132.63306579861</v>
@@ -10159,13 +10201,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -10175,7 +10217,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B145" s="8">
         <v>46132.633072337965</v>
@@ -10210,13 +10252,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="9" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O145" s="9" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="P145" s="9" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q145" s="9"/>
       <c r="R145" s="9"/>
@@ -10226,7 +10268,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B146" s="5">
         <v>46132.58894553241</v>
@@ -10236,7 +10278,7 @@
         <v>46134.579158981476</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
@@ -10261,13 +10303,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>240</v>
+        <v>330</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q146" s="5">
         <v>46219</v>
@@ -10287,7 +10329,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="7" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B147" s="8">
         <v>46132.633140289356</v>
@@ -10322,13 +10364,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="9" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="O147" s="9" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="P147" s="9" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Q147" s="9"/>
       <c r="R147" s="9"/>
@@ -10338,7 +10380,7 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B148" s="5">
         <v>46132.63314908565</v>
@@ -10373,13 +10415,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="O148" s="6" t="s">
+        <v>360</v>
+      </c>
+      <c r="P148" s="6" t="s">
         <v>358</v>
-      </c>
-      <c r="P148" s="6" t="s">
-        <v>356</v>
       </c>
       <c r="Q148" s="6"/>
       <c r="R148" s="6"/>
@@ -10389,7 +10431,7 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="7" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B149" s="8">
         <v>46132.63315533564</v>
@@ -10424,13 +10466,13 @@
         <v>26</v>
       </c>
       <c r="N149" s="9" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="O149" s="9" t="s">
+        <v>360</v>
+      </c>
+      <c r="P149" s="9" t="s">
         <v>358</v>
-      </c>
-      <c r="P149" s="9" t="s">
-        <v>356</v>
       </c>
       <c r="Q149" s="9"/>
       <c r="R149" s="9"/>
@@ -10440,7 +10482,7 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B150" s="5">
         <v>46132.63316266204</v>
@@ -10475,13 +10517,13 @@
         <v>26</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="P150" s="6" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Q150" s="6"/>
       <c r="R150" s="6"/>
@@ -10491,7 +10533,7 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="7" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B151" s="8">
         <v>46132.6331690625</v>
@@ -10526,13 +10568,13 @@
         <v>26</v>
       </c>
       <c r="N151" s="9" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="O151" s="9" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="P151" s="9" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Q151" s="9"/>
       <c r="R151" s="9"/>
@@ -10542,7 +10584,7 @@
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B152" s="5">
         <v>46132.63317594907</v>
@@ -10577,13 +10619,13 @@
         <v>26</v>
       </c>
       <c r="N152" s="6" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="O152" s="6" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="P152" s="6" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Q152" s="6"/>
       <c r="R152" s="6"/>
@@ -10593,7 +10635,7 @@
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" s="7" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B153" s="8">
         <v>46132.633188506945</v>
@@ -10628,13 +10670,13 @@
         <v>26</v>
       </c>
       <c r="N153" s="9" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="O153" s="9" t="s">
+        <v>360</v>
+      </c>
+      <c r="P153" s="9" t="s">
         <v>358</v>
-      </c>
-      <c r="P153" s="9" t="s">
-        <v>356</v>
       </c>
       <c r="Q153" s="9"/>
       <c r="R153" s="9"/>
@@ -10644,7 +10686,7 @@
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B154" s="5">
         <v>46132.63318159722</v>
@@ -10679,13 +10721,13 @@
         <v>26</v>
       </c>
       <c r="N154" s="6" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="P154" s="6" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Q154" s="6"/>
       <c r="R154" s="6"/>
@@ -10695,7 +10737,7 @@
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155" s="7" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B155" s="8">
         <v>46132.63319443287</v>
@@ -10730,13 +10772,13 @@
         <v>26</v>
       </c>
       <c r="N155" s="9" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="O155" s="9" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="P155" s="9" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Q155" s="9"/>
       <c r="R155" s="9"/>
@@ -10746,7 +10788,7 @@
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B156" s="5">
         <v>46132.63320815972</v>
@@ -10781,13 +10823,13 @@
         <v>26</v>
       </c>
       <c r="N156" s="6" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="O156" s="6" t="s">
+        <v>360</v>
+      </c>
+      <c r="P156" s="6" t="s">
         <v>358</v>
-      </c>
-      <c r="P156" s="6" t="s">
-        <v>356</v>
       </c>
       <c r="Q156" s="6"/>
       <c r="R156" s="6"/>
@@ -10797,7 +10839,7 @@
     </row>
     <row r="157" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A157" s="7" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B157" s="8">
         <v>46132.63320082176</v>
@@ -10832,13 +10874,13 @@
         <v>26</v>
       </c>
       <c r="N157" s="9" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="O157" s="9" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="P157" s="9" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Q157" s="9"/>
       <c r="R157" s="9"/>
@@ -10848,7 +10890,7 @@
     </row>
     <row r="158" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B158" s="5">
         <v>46132.63322097222</v>
@@ -10883,13 +10925,13 @@
         <v>26</v>
       </c>
       <c r="N158" s="6" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="O158" s="6" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="P158" s="6" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Q158" s="6"/>
       <c r="R158" s="6"/>
@@ -10899,7 +10941,7 @@
     </row>
     <row r="159" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A159" s="7" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B159" s="8">
         <v>46132.6332150463</v>
@@ -10934,13 +10976,13 @@
         <v>26</v>
       </c>
       <c r="N159" s="9" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="O159" s="9" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="P159" s="9" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Q159" s="9"/>
       <c r="R159" s="9"/>
@@ -10950,7 +10992,7 @@
     </row>
     <row r="160" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B160" s="5">
         <v>46132.63322802083</v>
@@ -10985,13 +11027,13 @@
         <v>26</v>
       </c>
       <c r="N160" s="6" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="O160" s="6" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="P160" s="6" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Q160" s="6"/>
       <c r="R160" s="6"/>
@@ -11001,7 +11043,7 @@
     </row>
     <row r="161" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A161" s="7" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B161" s="8">
         <v>46132.63323575231</v>
@@ -11036,13 +11078,13 @@
         <v>26</v>
       </c>
       <c r="N161" s="9" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="O161" s="9" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="P161" s="9" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Q161" s="9"/>
       <c r="R161" s="9"/>
@@ -11052,7 +11094,7 @@
     </row>
     <row r="162" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B162" s="5">
         <v>46132.633244004624</v>
@@ -11087,13 +11129,13 @@
         <v>26</v>
       </c>
       <c r="N162" s="6" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="O162" s="6" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="P162" s="6" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Q162" s="6"/>
       <c r="R162" s="6"/>
@@ -11103,7 +11145,7 @@
     </row>
     <row r="163" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A163" s="7" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B163" s="8">
         <v>46132.58893171296</v>
@@ -11113,7 +11155,7 @@
         <v>46134.57915975695</v>
       </c>
       <c r="E163" s="9" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="F163" s="9" t="s">
         <v>26</v>
@@ -11138,13 +11180,13 @@
         <v>26</v>
       </c>
       <c r="N163" s="9" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O163" s="9" t="s">
-        <v>240</v>
+        <v>330</v>
       </c>
       <c r="P163" s="9" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q163" s="8">
         <v>46220</v>
@@ -11164,7 +11206,7 @@
     </row>
     <row r="164" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B164" s="5">
         <v>46132.632804305555</v>
@@ -11199,13 +11241,13 @@
         <v>26</v>
       </c>
       <c r="N164" s="6" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="O164" s="6" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="P164" s="6" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="Q164" s="6"/>
       <c r="R164" s="6"/>
@@ -11215,7 +11257,7 @@
     </row>
     <row r="165" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A165" s="7" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B165" s="8">
         <v>46132.632815624995</v>
@@ -11250,13 +11292,13 @@
         <v>26</v>
       </c>
       <c r="N165" s="9" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="O165" s="9" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="P165" s="9" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="Q165" s="9"/>
       <c r="R165" s="9"/>
@@ -11266,7 +11308,7 @@
     </row>
     <row r="166" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B166" s="5">
         <v>46132.63282284723</v>
@@ -11301,13 +11343,13 @@
         <v>26</v>
       </c>
       <c r="N166" s="6" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="O166" s="6" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="P166" s="6" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="Q166" s="6"/>
       <c r="R166" s="6"/>
@@ -11317,7 +11359,7 @@
     </row>
     <row r="167" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A167" s="7" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B167" s="8">
         <v>46132.63283236111</v>
@@ -11352,13 +11394,13 @@
         <v>26</v>
       </c>
       <c r="N167" s="9" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="O167" s="9" t="s">
         <v>174</v>
       </c>
       <c r="P167" s="9" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="Q167" s="9"/>
       <c r="R167" s="9"/>
@@ -11368,7 +11410,7 @@
     </row>
     <row r="168" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B168" s="5">
         <v>46132.632837384255</v>
@@ -11403,13 +11445,13 @@
         <v>26</v>
       </c>
       <c r="N168" s="6" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="O168" s="6" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="P168" s="6" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="Q168" s="6"/>
       <c r="R168" s="6"/>
@@ -11419,7 +11461,7 @@
     </row>
     <row r="169" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A169" s="7" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B169" s="8">
         <v>46132.63284362269</v>
@@ -11454,13 +11496,13 @@
         <v>26</v>
       </c>
       <c r="N169" s="9" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="O169" s="9" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="P169" s="9" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="Q169" s="9"/>
       <c r="R169" s="9"/>
@@ -11470,7 +11512,7 @@
     </row>
     <row r="170" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B170" s="5">
         <v>46132.63284975695</v>
@@ -11505,13 +11547,13 @@
         <v>26</v>
       </c>
       <c r="N170" s="6" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="O170" s="6" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="P170" s="6" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="Q170" s="6"/>
       <c r="R170" s="6"/>
@@ -11521,7 +11563,7 @@
     </row>
     <row r="171" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A171" s="7" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B171" s="8">
         <v>46132.63286226852</v>
@@ -11556,13 +11598,13 @@
         <v>26</v>
       </c>
       <c r="N171" s="9" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="O171" s="9" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="P171" s="9" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="Q171" s="9"/>
       <c r="R171" s="9"/>
@@ -11572,7 +11614,7 @@
     </row>
     <row r="172" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A172" s="4" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B172" s="5">
         <v>46132.63285675926</v>
@@ -11607,13 +11649,13 @@
         <v>26</v>
       </c>
       <c r="N172" s="6" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="O172" s="6" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="P172" s="6" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="Q172" s="6"/>
       <c r="R172" s="6"/>
@@ -11623,7 +11665,7 @@
     </row>
     <row r="173" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A173" s="7" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B173" s="8">
         <v>46132.63286828704</v>
@@ -11658,13 +11700,13 @@
         <v>26</v>
       </c>
       <c r="N173" s="9" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="O173" s="9" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="P173" s="9" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="Q173" s="9"/>
       <c r="R173" s="9"/>
@@ -11674,7 +11716,7 @@
     </row>
     <row r="174" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A174" s="4" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B174" s="5">
         <v>46132.63287412037</v>
@@ -11709,13 +11751,13 @@
         <v>26</v>
       </c>
       <c r="N174" s="6" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="O174" s="6" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="P174" s="6" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="Q174" s="6"/>
       <c r="R174" s="6"/>
@@ -11725,7 +11767,7 @@
     </row>
     <row r="175" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A175" s="7" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B175" s="8">
         <v>46132.63288133102</v>
@@ -11760,13 +11802,13 @@
         <v>26</v>
       </c>
       <c r="N175" s="9" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="O175" s="9" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="P175" s="9" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="Q175" s="9"/>
       <c r="R175" s="9"/>
@@ -11776,7 +11818,7 @@
     </row>
     <row r="176" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A176" s="4" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B176" s="5">
         <v>46132.63288800926</v>
@@ -11811,13 +11853,13 @@
         <v>26</v>
       </c>
       <c r="N176" s="6" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="O176" s="6" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="P176" s="6" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="Q176" s="6"/>
       <c r="R176" s="6"/>
@@ -11827,7 +11869,7 @@
     </row>
     <row r="177" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A177" s="7" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B177" s="8">
         <v>46132.63289421296</v>
@@ -11862,13 +11904,13 @@
         <v>26</v>
       </c>
       <c r="N177" s="9" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="O177" s="9" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="P177" s="9" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="Q177" s="9"/>
       <c r="R177" s="9"/>
@@ -11878,7 +11920,7 @@
     </row>
     <row r="178" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A178" s="4" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B178" s="5">
         <v>46132.63290028935</v>
@@ -11913,13 +11955,13 @@
         <v>26</v>
       </c>
       <c r="N178" s="6" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="O178" s="6" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="P178" s="6" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="Q178" s="6"/>
       <c r="R178" s="6"/>
@@ -11929,7 +11971,7 @@
     </row>
     <row r="179" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A179" s="7" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B179" s="8">
         <v>46132.632907719904</v>
@@ -11964,13 +12006,13 @@
         <v>26</v>
       </c>
       <c r="N179" s="9" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="O179" s="9" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="P179" s="9" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="Q179" s="9"/>
       <c r="R179" s="9"/>
@@ -11980,7 +12022,7 @@
     </row>
     <row r="180" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A180" s="4" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B180" s="5">
         <v>46132.58895258102</v>
@@ -11990,7 +12032,7 @@
         <v>46134.579160567126</v>
       </c>
       <c r="E180" s="6" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F180" s="6" t="s">
         <v>26</v>
@@ -12015,13 +12057,13 @@
         <v>26</v>
       </c>
       <c r="N180" s="6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O180" s="6" t="s">
-        <v>240</v>
+        <v>330</v>
       </c>
       <c r="P180" s="6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q180" s="5">
         <v>46223</v>
@@ -12041,7 +12083,7 @@
     </row>
     <row r="181" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A181" s="7" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B181" s="8">
         <v>46132.63330006944</v>
@@ -12076,13 +12118,13 @@
         <v>26</v>
       </c>
       <c r="N181" s="9" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="O181" s="9" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="P181" s="9" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="Q181" s="9"/>
       <c r="R181" s="9"/>
@@ -12092,7 +12134,7 @@
     </row>
     <row r="182" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A182" s="4" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B182" s="5">
         <v>46132.63330984954</v>
@@ -12127,13 +12169,13 @@
         <v>26</v>
       </c>
       <c r="N182" s="6" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="O182" s="6" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="P182" s="6" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="Q182" s="6"/>
       <c r="R182" s="6"/>
@@ -12143,7 +12185,7 @@
     </row>
     <row r="183" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A183" s="7" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B183" s="8">
         <v>46132.633316377316</v>
@@ -12178,13 +12220,13 @@
         <v>26</v>
       </c>
       <c r="N183" s="9" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="O183" s="9" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="P183" s="9" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="Q183" s="9"/>
       <c r="R183" s="9"/>
@@ -12194,7 +12236,7 @@
     </row>
     <row r="184" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A184" s="4" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B184" s="5">
         <v>46132.63332333333</v>
@@ -12229,13 +12271,13 @@
         <v>26</v>
       </c>
       <c r="N184" s="6" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="O184" s="6" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="P184" s="6" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="Q184" s="6"/>
       <c r="R184" s="6"/>
@@ -12245,7 +12287,7 @@
     </row>
     <row r="185" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A185" s="7" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B185" s="8">
         <v>46132.63333568287</v>
@@ -12280,13 +12322,13 @@
         <v>26</v>
       </c>
       <c r="N185" s="9" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="O185" s="9" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="P185" s="9" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="Q185" s="9"/>
       <c r="R185" s="9"/>
@@ -12296,7 +12338,7 @@
     </row>
     <row r="186" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A186" s="4" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B186" s="5">
         <v>46132.633329282406</v>
@@ -12331,13 +12373,13 @@
         <v>26</v>
       </c>
       <c r="N186" s="6" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="O186" s="6" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="P186" s="6" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="Q186" s="6"/>
       <c r="R186" s="6"/>
@@ -12347,7 +12389,7 @@
     </row>
     <row r="187" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A187" s="7" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B187" s="8">
         <v>46132.63334925926</v>
@@ -12382,13 +12424,13 @@
         <v>26</v>
       </c>
       <c r="N187" s="9" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="O187" s="9" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="P187" s="9" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="Q187" s="9"/>
       <c r="R187" s="9"/>
@@ -12398,7 +12440,7 @@
     </row>
     <row r="188" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A188" s="4" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B188" s="5">
         <v>46132.633353321755</v>
@@ -12433,13 +12475,13 @@
         <v>26</v>
       </c>
       <c r="N188" s="6" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="O188" s="6" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="P188" s="6" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="Q188" s="6"/>
       <c r="R188" s="6"/>
@@ -12449,7 +12491,7 @@
     </row>
     <row r="189" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A189" s="7" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B189" s="8">
         <v>46132.63336115741</v>
@@ -12484,13 +12526,13 @@
         <v>26</v>
       </c>
       <c r="N189" s="9" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="O189" s="9" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="P189" s="9" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="Q189" s="9"/>
       <c r="R189" s="9"/>
@@ -12500,7 +12542,7 @@
     </row>
     <row r="190" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B190" s="5">
         <v>46132.6333661574</v>
@@ -12535,13 +12577,13 @@
         <v>26</v>
       </c>
       <c r="N190" s="6" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="O190" s="6" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="P190" s="6" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="Q190" s="6"/>
       <c r="R190" s="6"/>
@@ -12551,7 +12593,7 @@
     </row>
     <row r="191" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A191" s="7" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B191" s="8">
         <v>46132.633375046295</v>
@@ -12586,13 +12628,13 @@
         <v>26</v>
       </c>
       <c r="N191" s="9" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="O191" s="9" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="P191" s="9" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="Q191" s="9"/>
       <c r="R191" s="9"/>
@@ -12602,7 +12644,7 @@
     </row>
     <row r="192" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B192" s="5">
         <v>46132.63337950232</v>
@@ -12637,13 +12679,13 @@
         <v>26</v>
       </c>
       <c r="N192" s="6" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="O192" s="6" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="P192" s="6" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="Q192" s="6"/>
       <c r="R192" s="6"/>
@@ -12653,7 +12695,7 @@
     </row>
     <row r="193" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A193" s="7" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B193" s="8">
         <v>46132.63338666667</v>
@@ -12688,13 +12730,13 @@
         <v>26</v>
       </c>
       <c r="N193" s="9" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="O193" s="9" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="P193" s="9" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="Q193" s="9"/>
       <c r="R193" s="9"/>
@@ -12704,7 +12746,7 @@
     </row>
     <row r="194" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B194" s="5">
         <v>46132.63339375</v>
@@ -12739,13 +12781,13 @@
         <v>26</v>
       </c>
       <c r="N194" s="6" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="O194" s="6" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="P194" s="6" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="Q194" s="6"/>
       <c r="R194" s="6"/>
@@ -12755,7 +12797,7 @@
     </row>
     <row r="195" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A195" s="7" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B195" s="8">
         <v>46132.63339872685</v>
@@ -12790,13 +12832,13 @@
         <v>26</v>
       </c>
       <c r="N195" s="9" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="O195" s="9" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="P195" s="9" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="Q195" s="9"/>
       <c r="R195" s="9"/>
@@ -12806,7 +12848,7 @@
     </row>
     <row r="196" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B196" s="5">
         <v>46132.633404085645</v>
@@ -12841,13 +12883,13 @@
         <v>26</v>
       </c>
       <c r="N196" s="6" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="O196" s="6" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="P196" s="6" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="Q196" s="6"/>
       <c r="R196" s="6"/>
@@ -12857,7 +12899,7 @@
     </row>
     <row r="197" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A197" s="7" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B197" s="8">
         <v>46132.58900565973</v>
@@ -12867,7 +12909,7 @@
         <v>46134.579161331014</v>
       </c>
       <c r="E197" s="9" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="F197" s="9" t="s">
         <v>26</v>
@@ -12892,13 +12934,13 @@
         <v>26</v>
       </c>
       <c r="N197" s="9" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O197" s="9" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="P197" s="9" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="Q197" s="8">
         <v>46225</v>
@@ -12918,7 +12960,7 @@
     </row>
     <row r="198" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A198" s="4" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B198" s="5">
         <v>46132.6334534375</v>
@@ -12953,13 +12995,13 @@
         <v>26</v>
       </c>
       <c r="N198" s="6" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="O198" s="6" t="s">
         <v>173</v>
       </c>
       <c r="P198" s="6" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="Q198" s="6"/>
       <c r="R198" s="6"/>
@@ -12969,7 +13011,7 @@
     </row>
     <row r="199" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A199" s="7" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B199" s="8">
         <v>46132.633462025464</v>
@@ -13004,13 +13046,13 @@
         <v>26</v>
       </c>
       <c r="N199" s="9" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="O199" s="9" t="s">
         <v>177</v>
       </c>
       <c r="P199" s="9" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="Q199" s="9"/>
       <c r="R199" s="9"/>
@@ -13020,7 +13062,7 @@
     </row>
     <row r="200" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A200" s="4" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B200" s="5">
         <v>46132.633468622684</v>
@@ -13055,13 +13097,13 @@
         <v>26</v>
       </c>
       <c r="N200" s="6" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="O200" s="6" t="s">
         <v>180</v>
       </c>
       <c r="P200" s="6" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="Q200" s="6"/>
       <c r="R200" s="6"/>
@@ -13071,7 +13113,7 @@
     </row>
     <row r="201" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A201" s="7" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B201" s="8">
         <v>46132.63347502315</v>
@@ -13106,13 +13148,13 @@
         <v>26</v>
       </c>
       <c r="N201" s="9" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="O201" s="9" t="s">
         <v>182</v>
       </c>
       <c r="P201" s="9" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="Q201" s="9"/>
       <c r="R201" s="9"/>
@@ -13122,7 +13164,7 @@
     </row>
     <row r="202" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A202" s="4" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B202" s="5">
         <v>46132.63348070602</v>
@@ -13157,13 +13199,13 @@
         <v>26</v>
       </c>
       <c r="N202" s="6" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="O202" s="6" t="s">
         <v>184</v>
       </c>
       <c r="P202" s="6" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="Q202" s="6"/>
       <c r="R202" s="6"/>
@@ -13173,7 +13215,7 @@
     </row>
     <row r="203" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A203" s="7" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B203" s="8">
         <v>46132.63348662037</v>
@@ -13208,13 +13250,13 @@
         <v>26</v>
       </c>
       <c r="N203" s="9" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="O203" s="9" t="s">
         <v>186</v>
       </c>
       <c r="P203" s="9" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="Q203" s="9"/>
       <c r="R203" s="9"/>
@@ -13224,7 +13266,7 @@
     </row>
     <row r="204" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A204" s="4" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B204" s="5">
         <v>46132.63349295139</v>
@@ -13259,13 +13301,13 @@
         <v>26</v>
       </c>
       <c r="N204" s="6" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="O204" s="6" t="s">
         <v>188</v>
       </c>
       <c r="P204" s="6" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="Q204" s="6"/>
       <c r="R204" s="6"/>
@@ -13275,7 +13317,7 @@
     </row>
     <row r="205" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A205" s="7" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B205" s="8">
         <v>46132.633500138894</v>
@@ -13310,13 +13352,13 @@
         <v>26</v>
       </c>
       <c r="N205" s="9" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="O205" s="9" t="s">
         <v>191</v>
       </c>
       <c r="P205" s="9" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="Q205" s="9"/>
       <c r="R205" s="9"/>
@@ -13326,7 +13368,7 @@
     </row>
     <row r="206" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A206" s="4" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B206" s="5">
         <v>46132.633505983795</v>
@@ -13361,13 +13403,13 @@
         <v>26</v>
       </c>
       <c r="N206" s="6" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="O206" s="6" t="s">
         <v>193</v>
       </c>
       <c r="P206" s="6" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="Q206" s="6"/>
       <c r="R206" s="6"/>
@@ -13377,7 +13419,7 @@
     </row>
     <row r="207" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A207" s="7" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B207" s="8">
         <v>46132.6335124537</v>
@@ -13412,13 +13454,13 @@
         <v>26</v>
       </c>
       <c r="N207" s="9" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="O207" s="9" t="s">
         <v>195</v>
       </c>
       <c r="P207" s="9" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="Q207" s="9"/>
       <c r="R207" s="9"/>
@@ -13428,7 +13470,7 @@
     </row>
     <row r="208" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A208" s="4" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B208" s="5">
         <v>46132.63351974537</v>
@@ -13463,13 +13505,13 @@
         <v>26</v>
       </c>
       <c r="N208" s="6" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="O208" s="6" t="s">
         <v>197</v>
       </c>
       <c r="P208" s="6" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="Q208" s="6"/>
       <c r="R208" s="6"/>
@@ -13479,7 +13521,7 @@
     </row>
     <row r="209" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A209" s="7" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B209" s="8">
         <v>46132.6335277662</v>
@@ -13514,13 +13556,13 @@
         <v>26</v>
       </c>
       <c r="N209" s="9" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="O209" s="9" t="s">
         <v>199</v>
       </c>
       <c r="P209" s="9" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="Q209" s="9"/>
       <c r="R209" s="9"/>
@@ -13530,7 +13572,7 @@
     </row>
     <row r="210" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A210" s="4" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B210" s="5">
         <v>46132.633534988425</v>
@@ -13565,13 +13607,13 @@
         <v>26</v>
       </c>
       <c r="N210" s="6" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="O210" s="6" t="s">
         <v>201</v>
       </c>
       <c r="P210" s="6" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="Q210" s="6"/>
       <c r="R210" s="6"/>
@@ -13581,7 +13623,7 @@
     </row>
     <row r="211" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A211" s="7" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B211" s="8">
         <v>46132.63354082176</v>
@@ -13616,13 +13658,13 @@
         <v>26</v>
       </c>
       <c r="N211" s="9" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="O211" s="9" t="s">
         <v>203</v>
       </c>
       <c r="P211" s="9" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="Q211" s="9"/>
       <c r="R211" s="9"/>
@@ -13632,7 +13674,7 @@
     </row>
     <row r="212" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A212" s="4" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B212" s="5">
         <v>46132.63354760417</v>
@@ -13667,13 +13709,13 @@
         <v>26</v>
       </c>
       <c r="N212" s="6" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="O212" s="6" t="s">
         <v>205</v>
       </c>
       <c r="P212" s="6" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="Q212" s="6"/>
       <c r="R212" s="6"/>
@@ -13683,7 +13725,7 @@
     </row>
     <row r="213" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A213" s="7" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B213" s="8">
         <v>46133.58300138889</v>
@@ -13693,7 +13735,7 @@
         <v>46134.57860878472</v>
       </c>
       <c r="E213" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F213" s="9" t="s">
         <v>26</v>
@@ -13718,13 +13760,13 @@
         <v>26</v>
       </c>
       <c r="N213" s="9" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="O213" s="9" t="s">
         <v>207</v>
       </c>
       <c r="P213" s="9" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="Q213" s="9"/>
       <c r="R213" s="9"/>
@@ -13734,7 +13776,7 @@
     </row>
     <row r="214" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A214" s="4" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B214" s="5">
         <v>46132.589012916666</v>
@@ -13744,7 +13786,7 @@
         <v>46133.58769056713</v>
       </c>
       <c r="E214" s="6" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="F214" s="6" t="s">
         <v>25</v>
@@ -13768,7 +13810,7 @@
         <v>26</v>
       </c>
       <c r="O214" s="6" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="P214" s="6" t="s">
         <v>26</v>
@@ -13781,7 +13823,7 @@
     </row>
     <row r="215" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A215" s="7" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B215" s="8">
         <v>46132.589016666665</v>
@@ -13791,16 +13833,16 @@
         <v>46133.58482033564</v>
       </c>
       <c r="E215" s="9" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="F215" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G215" s="9" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="H215" s="9" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="I215" s="9"/>
       <c r="J215" s="8">
@@ -13816,13 +13858,13 @@
         <v>26</v>
       </c>
       <c r="N215" s="9" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="O215" s="9" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="P215" s="9" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="Q215" s="8">
         <v>46226</v>
@@ -13842,7 +13884,7 @@
     </row>
     <row r="216" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A216" s="4" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B216" s="5">
         <v>46132.63360670139</v>
@@ -13858,10 +13900,10 @@
         <v>26</v>
       </c>
       <c r="G216" s="6" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="H216" s="6" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="I216" s="6"/>
       <c r="J216" s="5">
@@ -13877,7 +13919,7 @@
         <v>26</v>
       </c>
       <c r="N216" s="6" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="O216" s="6" t="s">
         <v>174</v>
@@ -13893,7 +13935,7 @@
     </row>
     <row r="217" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A217" s="7" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B217" s="8">
         <v>46132.63361304398</v>
@@ -13909,10 +13951,10 @@
         <v>26</v>
       </c>
       <c r="G217" s="9" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="H217" s="9" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="I217" s="9"/>
       <c r="J217" s="8">
@@ -13928,7 +13970,7 @@
         <v>26</v>
       </c>
       <c r="N217" s="9" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="O217" s="9" t="s">
         <v>174</v>
@@ -13944,7 +13986,7 @@
     </row>
     <row r="218" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A218" s="4" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B218" s="5">
         <v>46132.63361974537</v>
@@ -13960,10 +14002,10 @@
         <v>26</v>
       </c>
       <c r="G218" s="6" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="H218" s="6" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="I218" s="6"/>
       <c r="J218" s="5">
@@ -13979,7 +14021,7 @@
         <v>26</v>
       </c>
       <c r="N218" s="6" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="O218" s="6" t="s">
         <v>174</v>
@@ -13995,7 +14037,7 @@
     </row>
     <row r="219" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A219" s="7" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B219" s="8">
         <v>46132.63363137731</v>
@@ -14011,10 +14053,10 @@
         <v>26</v>
       </c>
       <c r="G219" s="9" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="H219" s="9" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="I219" s="9"/>
       <c r="J219" s="8">
@@ -14030,7 +14072,7 @@
         <v>26</v>
       </c>
       <c r="N219" s="9" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="O219" s="9" t="s">
         <v>174</v>
@@ -14046,7 +14088,7 @@
     </row>
     <row r="220" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A220" s="4" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B220" s="5">
         <v>46132.63362555555</v>
@@ -14062,10 +14104,10 @@
         <v>26</v>
       </c>
       <c r="G220" s="6" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="H220" s="6" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="I220" s="6"/>
       <c r="J220" s="5">
@@ -14081,7 +14123,7 @@
         <v>26</v>
       </c>
       <c r="N220" s="6" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="O220" s="6" t="s">
         <v>174</v>
@@ -14097,7 +14139,7 @@
     </row>
     <row r="221" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A221" s="7" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B221" s="8">
         <v>46132.63363859954</v>
@@ -14113,10 +14155,10 @@
         <v>26</v>
       </c>
       <c r="G221" s="9" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="H221" s="9" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="I221" s="9"/>
       <c r="J221" s="8">
@@ -14132,7 +14174,7 @@
         <v>26</v>
       </c>
       <c r="N221" s="9" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="O221" s="9" t="s">
         <v>174</v>
@@ -14148,7 +14190,7 @@
     </row>
     <row r="222" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A222" s="4" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B222" s="5">
         <v>46132.63364667824</v>
@@ -14164,10 +14206,10 @@
         <v>26</v>
       </c>
       <c r="G222" s="6" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="H222" s="6" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="I222" s="6"/>
       <c r="J222" s="5">
@@ -14183,7 +14225,7 @@
         <v>26</v>
       </c>
       <c r="N222" s="6" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="O222" s="6" t="s">
         <v>174</v>
@@ -14199,7 +14241,7 @@
     </row>
     <row r="223" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A223" s="7" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B223" s="8">
         <v>46132.633653055556</v>
@@ -14215,10 +14257,10 @@
         <v>26</v>
       </c>
       <c r="G223" s="9" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="H223" s="9" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="I223" s="9"/>
       <c r="J223" s="8">
@@ -14234,7 +14276,7 @@
         <v>26</v>
       </c>
       <c r="N223" s="9" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="O223" s="9" t="s">
         <v>174</v>
@@ -14250,7 +14292,7 @@
     </row>
     <row r="224" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A224" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B224" s="5">
         <v>46132.63365921297</v>
@@ -14266,10 +14308,10 @@
         <v>26</v>
       </c>
       <c r="G224" s="6" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="H224" s="6" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="I224" s="6"/>
       <c r="J224" s="5">
@@ -14285,7 +14327,7 @@
         <v>26</v>
       </c>
       <c r="N224" s="6" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="O224" s="6" t="s">
         <v>174</v>
@@ -14301,7 +14343,7 @@
     </row>
     <row r="225" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A225" s="7" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B225" s="8">
         <v>46132.633665347224</v>
@@ -14317,10 +14359,10 @@
         <v>26</v>
       </c>
       <c r="G225" s="9" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="H225" s="9" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="I225" s="9"/>
       <c r="J225" s="8">
@@ -14336,7 +14378,7 @@
         <v>26</v>
       </c>
       <c r="N225" s="9" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="O225" s="9" t="s">
         <v>174</v>
@@ -14352,7 +14394,7 @@
     </row>
     <row r="226" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A226" s="4" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B226" s="5">
         <v>46132.63367407407</v>
@@ -14368,10 +14410,10 @@
         <v>26</v>
       </c>
       <c r="G226" s="6" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="H226" s="6" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="I226" s="6"/>
       <c r="J226" s="5">
@@ -14387,7 +14429,7 @@
         <v>26</v>
       </c>
       <c r="N226" s="6" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="O226" s="6" t="s">
         <v>174</v>
@@ -14403,7 +14445,7 @@
     </row>
     <row r="227" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A227" s="7" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B227" s="8">
         <v>46132.63368225694</v>
@@ -14419,10 +14461,10 @@
         <v>26</v>
       </c>
       <c r="G227" s="9" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="H227" s="9" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="I227" s="9"/>
       <c r="J227" s="8">
@@ -14438,7 +14480,7 @@
         <v>26</v>
       </c>
       <c r="N227" s="9" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="O227" s="9" t="s">
         <v>174</v>
@@ -14454,7 +14496,7 @@
     </row>
     <row r="228" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A228" s="4" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B228" s="5">
         <v>46132.63368885417</v>
@@ -14470,10 +14512,10 @@
         <v>26</v>
       </c>
       <c r="G228" s="6" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="H228" s="6" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="I228" s="6"/>
       <c r="J228" s="5">
@@ -14489,7 +14531,7 @@
         <v>26</v>
       </c>
       <c r="N228" s="6" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="O228" s="6" t="s">
         <v>174</v>
@@ -14505,7 +14547,7 @@
     </row>
     <row r="229" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A229" s="7" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B229" s="8">
         <v>46132.633694965276</v>
@@ -14521,10 +14563,10 @@
         <v>26</v>
       </c>
       <c r="G229" s="9" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="H229" s="9" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="I229" s="9"/>
       <c r="J229" s="8">
@@ -14540,7 +14582,7 @@
         <v>26</v>
       </c>
       <c r="N229" s="9" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="O229" s="9" t="s">
         <v>174</v>
@@ -14556,7 +14598,7 @@
     </row>
     <row r="230" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A230" s="4" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B230" s="5">
         <v>46132.63370111111</v>
@@ -14572,10 +14614,10 @@
         <v>26</v>
       </c>
       <c r="G230" s="6" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="H230" s="6" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="I230" s="6"/>
       <c r="J230" s="5">
@@ -14591,7 +14633,7 @@
         <v>26</v>
       </c>
       <c r="N230" s="6" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="O230" s="6" t="s">
         <v>174</v>
@@ -14607,7 +14649,7 @@
     </row>
     <row r="231" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A231" s="7" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B231" s="8">
         <v>46132.63378953704</v>
@@ -14623,10 +14665,10 @@
         <v>26</v>
       </c>
       <c r="G231" s="9" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="H231" s="9" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="I231" s="9"/>
       <c r="J231" s="8">
@@ -14642,10 +14684,10 @@
         <v>26</v>
       </c>
       <c r="N231" s="9" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="O231" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P231" s="9" t="s">
         <v>174</v>
@@ -14658,7 +14700,7 @@
     </row>
     <row r="232" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A232" s="4" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B232" s="5">
         <v>46132.589021736116</v>
@@ -14668,7 +14710,7 @@
         <v>46133.58651043981</v>
       </c>
       <c r="E232" s="6" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F232" s="6" t="s">
         <v>26</v>
@@ -14693,13 +14735,13 @@
         <v>26</v>
       </c>
       <c r="N232" s="6" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="O232" s="6" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="P232" s="6" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="Q232" s="5">
         <v>46227</v>
@@ -14719,7 +14761,7 @@
     </row>
     <row r="233" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A233" s="7" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B233" s="8">
         <v>46132.633861608796</v>
@@ -14754,7 +14796,7 @@
         <v>26</v>
       </c>
       <c r="N233" s="9" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="O233" s="9" t="s">
         <v>174</v>
@@ -14770,7 +14812,7 @@
     </row>
     <row r="234" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A234" s="4" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B234" s="5">
         <v>46132.633870011574</v>
@@ -14805,7 +14847,7 @@
         <v>26</v>
       </c>
       <c r="N234" s="6" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="O234" s="6" t="s">
         <v>174</v>
@@ -14821,7 +14863,7 @@
     </row>
     <row r="235" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A235" s="7" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B235" s="8">
         <v>46132.63387658565</v>
@@ -14856,7 +14898,7 @@
         <v>26</v>
       </c>
       <c r="N235" s="9" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="O235" s="9" t="s">
         <v>174</v>
@@ -14872,7 +14914,7 @@
     </row>
     <row r="236" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A236" s="4" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B236" s="5">
         <v>46132.63388259259</v>
@@ -14907,7 +14949,7 @@
         <v>26</v>
       </c>
       <c r="N236" s="6" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="O236" s="6" t="s">
         <v>174</v>
@@ -14923,7 +14965,7 @@
     </row>
     <row r="237" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A237" s="7" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B237" s="8">
         <v>46132.63388633102</v>
@@ -14958,7 +15000,7 @@
         <v>26</v>
       </c>
       <c r="N237" s="9" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="O237" s="9" t="s">
         <v>174</v>
@@ -14974,7 +15016,7 @@
     </row>
     <row r="238" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A238" s="4" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B238" s="5">
         <v>46132.63389106482</v>
@@ -15009,7 +15051,7 @@
         <v>26</v>
       </c>
       <c r="N238" s="6" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="O238" s="6" t="s">
         <v>174</v>
@@ -15025,7 +15067,7 @@
     </row>
     <row r="239" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A239" s="7" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B239" s="8">
         <v>46132.63389739583</v>
@@ -15060,7 +15102,7 @@
         <v>26</v>
       </c>
       <c r="N239" s="9" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="O239" s="9" t="s">
         <v>174</v>
@@ -15076,7 +15118,7 @@
     </row>
     <row r="240" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A240" s="4" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B240" s="5">
         <v>46132.63390288195</v>
@@ -15111,7 +15153,7 @@
         <v>26</v>
       </c>
       <c r="N240" s="6" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="O240" s="6" t="s">
         <v>174</v>
@@ -15127,7 +15169,7 @@
     </row>
     <row r="241" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A241" s="7" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B241" s="8">
         <v>46132.63390861111</v>
@@ -15162,7 +15204,7 @@
         <v>26</v>
       </c>
       <c r="N241" s="9" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="O241" s="9" t="s">
         <v>174</v>
@@ -15178,7 +15220,7 @@
     </row>
     <row r="242" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A242" s="4" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B242" s="5">
         <v>46132.63391276621</v>
@@ -15213,7 +15255,7 @@
         <v>26</v>
       </c>
       <c r="N242" s="6" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="O242" s="6" t="s">
         <v>174</v>
@@ -15229,7 +15271,7 @@
     </row>
     <row r="243" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A243" s="7" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="B243" s="8">
         <v>46132.63391880787</v>
@@ -15264,7 +15306,7 @@
         <v>26</v>
       </c>
       <c r="N243" s="9" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="O243" s="9" t="s">
         <v>174</v>
@@ -15280,7 +15322,7 @@
     </row>
     <row r="244" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A244" s="4" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B244" s="5">
         <v>46132.63392302083</v>
@@ -15315,7 +15357,7 @@
         <v>26</v>
       </c>
       <c r="N244" s="6" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="O244" s="6" t="s">
         <v>174</v>
@@ -15331,7 +15373,7 @@
     </row>
     <row r="245" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A245" s="7" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B245" s="8">
         <v>46132.63393041666</v>
@@ -15366,7 +15408,7 @@
         <v>26</v>
       </c>
       <c r="N245" s="9" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="O245" s="9" t="s">
         <v>174</v>
@@ -15382,7 +15424,7 @@
     </row>
     <row r="246" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A246" s="4" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B246" s="5">
         <v>46132.63393689815</v>
@@ -15417,7 +15459,7 @@
         <v>26</v>
       </c>
       <c r="N246" s="6" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="O246" s="6" t="s">
         <v>174</v>
@@ -15433,7 +15475,7 @@
     </row>
     <row r="247" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A247" s="7" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B247" s="8">
         <v>46132.633943078705</v>
@@ -15468,7 +15510,7 @@
         <v>26</v>
       </c>
       <c r="N247" s="9" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="O247" s="9" t="s">
         <v>174</v>
@@ -15484,7 +15526,7 @@
     </row>
     <row r="248" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A248" s="4" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B248" s="5">
         <v>46132.633955578705</v>
@@ -15519,7 +15561,7 @@
         <v>26</v>
       </c>
       <c r="N248" s="6" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="O248" s="6" t="s">
         <v>174</v>
@@ -15535,7 +15577,7 @@
     </row>
     <row r="249" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A249" s="7" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="B249" s="8">
         <v>46132.58902681713</v>
@@ -15545,16 +15587,16 @@
         <v>46133.58721105324</v>
       </c>
       <c r="E249" s="9" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F249" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G249" s="9" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="H249" s="9" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="I249" s="8">
         <v>46230</v>
@@ -15572,13 +15614,13 @@
         <v>26</v>
       </c>
       <c r="N249" s="9" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="O249" s="9" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="P249" s="9" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="Q249" s="8">
         <v>46230</v>
@@ -15598,7 +15640,7 @@
     </row>
     <row r="250" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A250" s="4" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B250" s="5">
         <v>46132.634024432875</v>
@@ -15614,10 +15656,10 @@
         <v>26</v>
       </c>
       <c r="G250" s="6" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="H250" s="6" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="I250" s="6"/>
       <c r="J250" s="5">
@@ -15633,7 +15675,7 @@
         <v>26</v>
       </c>
       <c r="N250" s="6" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="O250" s="6" t="s">
         <v>174</v>
@@ -15649,7 +15691,7 @@
     </row>
     <row r="251" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A251" s="7" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B251" s="8">
         <v>46132.634032685186</v>
@@ -15665,10 +15707,10 @@
         <v>26</v>
       </c>
       <c r="G251" s="9" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="H251" s="9" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="I251" s="9"/>
       <c r="J251" s="8">
@@ -15684,7 +15726,7 @@
         <v>26</v>
       </c>
       <c r="N251" s="9" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="O251" s="9" t="s">
         <v>174</v>
@@ -15700,7 +15742,7 @@
     </row>
     <row r="252" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A252" s="4" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B252" s="5">
         <v>46132.63404001157</v>
@@ -15716,10 +15758,10 @@
         <v>26</v>
       </c>
       <c r="G252" s="6" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="H252" s="6" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="I252" s="6"/>
       <c r="J252" s="5">
@@ -15735,7 +15777,7 @@
         <v>26</v>
       </c>
       <c r="N252" s="6" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="O252" s="6" t="s">
         <v>174</v>
@@ -15751,7 +15793,7 @@
     </row>
     <row r="253" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A253" s="7" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B253" s="8">
         <v>46132.63404659722</v>
@@ -15767,10 +15809,10 @@
         <v>26</v>
       </c>
       <c r="G253" s="9" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="H253" s="9" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="I253" s="9"/>
       <c r="J253" s="8">
@@ -15786,7 +15828,7 @@
         <v>26</v>
       </c>
       <c r="N253" s="9" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="O253" s="9" t="s">
         <v>174</v>
@@ -15802,7 +15844,7 @@
     </row>
     <row r="254" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A254" s="4" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B254" s="5">
         <v>46132.6340537037</v>
@@ -15818,10 +15860,10 @@
         <v>26</v>
       </c>
       <c r="G254" s="6" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="H254" s="6" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="I254" s="6"/>
       <c r="J254" s="5">
@@ -15837,7 +15879,7 @@
         <v>26</v>
       </c>
       <c r="N254" s="6" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="O254" s="6" t="s">
         <v>174</v>
@@ -15853,7 +15895,7 @@
     </row>
     <row r="255" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A255" s="7" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="B255" s="8">
         <v>46132.63406115741</v>
@@ -15869,10 +15911,10 @@
         <v>26</v>
       </c>
       <c r="G255" s="9" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="H255" s="9" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="I255" s="9"/>
       <c r="J255" s="8">
@@ -15888,7 +15930,7 @@
         <v>26</v>
       </c>
       <c r="N255" s="9" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="O255" s="9" t="s">
         <v>174</v>
@@ -15904,7 +15946,7 @@
     </row>
     <row r="256" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A256" s="4" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B256" s="5">
         <v>46132.63406662037</v>
@@ -15920,10 +15962,10 @@
         <v>26</v>
       </c>
       <c r="G256" s="6" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="H256" s="6" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="I256" s="6"/>
       <c r="J256" s="5">
@@ -15939,7 +15981,7 @@
         <v>26</v>
       </c>
       <c r="N256" s="6" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="O256" s="6" t="s">
         <v>174</v>
@@ -15955,7 +15997,7 @@
     </row>
     <row r="257" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A257" s="7" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B257" s="8">
         <v>46132.634072395835</v>
@@ -15971,10 +16013,10 @@
         <v>26</v>
       </c>
       <c r="G257" s="9" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="H257" s="9" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="I257" s="9"/>
       <c r="J257" s="8">
@@ -15990,7 +16032,7 @@
         <v>26</v>
       </c>
       <c r="N257" s="9" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="O257" s="9" t="s">
         <v>174</v>
@@ -16006,7 +16048,7 @@
     </row>
     <row r="258" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A258" s="4" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B258" s="5">
         <v>46132.6340770949</v>
@@ -16022,10 +16064,10 @@
         <v>26</v>
       </c>
       <c r="G258" s="6" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="H258" s="6" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="I258" s="6"/>
       <c r="J258" s="5">
@@ -16041,7 +16083,7 @@
         <v>26</v>
       </c>
       <c r="N258" s="6" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="O258" s="6" t="s">
         <v>174</v>
@@ -16057,7 +16099,7 @@
     </row>
     <row r="259" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A259" s="7" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="B259" s="8">
         <v>46132.634082777775</v>
@@ -16073,10 +16115,10 @@
         <v>26</v>
       </c>
       <c r="G259" s="9" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="H259" s="9" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="I259" s="9"/>
       <c r="J259" s="8">
@@ -16092,7 +16134,7 @@
         <v>26</v>
       </c>
       <c r="N259" s="9" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="O259" s="9" t="s">
         <v>174</v>
@@ -16108,7 +16150,7 @@
     </row>
     <row r="260" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A260" s="4" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B260" s="5">
         <v>46132.63408899306</v>
@@ -16124,10 +16166,10 @@
         <v>26</v>
       </c>
       <c r="G260" s="6" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="H260" s="6" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="I260" s="6"/>
       <c r="J260" s="5">
@@ -16143,7 +16185,7 @@
         <v>26</v>
       </c>
       <c r="N260" s="6" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="O260" s="6" t="s">
         <v>174</v>
@@ -16159,7 +16201,7 @@
     </row>
     <row r="261" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A261" s="7" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="B261" s="8">
         <v>46132.63409545139</v>
@@ -16175,10 +16217,10 @@
         <v>26</v>
       </c>
       <c r="G261" s="9" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="H261" s="9" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="I261" s="9"/>
       <c r="J261" s="8">
@@ -16194,7 +16236,7 @@
         <v>26</v>
       </c>
       <c r="N261" s="9" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="O261" s="9" t="s">
         <v>174</v>
@@ -16210,7 +16252,7 @@
     </row>
     <row r="262" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A262" s="4" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="B262" s="5">
         <v>46132.63410087963</v>
@@ -16226,10 +16268,10 @@
         <v>26</v>
       </c>
       <c r="G262" s="6" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="H262" s="6" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="I262" s="6"/>
       <c r="J262" s="5">
@@ -16245,7 +16287,7 @@
         <v>26</v>
       </c>
       <c r="N262" s="6" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="O262" s="6" t="s">
         <v>174</v>
@@ -16261,7 +16303,7 @@
     </row>
     <row r="263" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A263" s="7" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B263" s="8">
         <v>46132.63410688657</v>
@@ -16277,10 +16319,10 @@
         <v>26</v>
       </c>
       <c r="G263" s="9" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="H263" s="9" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="I263" s="9"/>
       <c r="J263" s="8">
@@ -16296,7 +16338,7 @@
         <v>26</v>
       </c>
       <c r="N263" s="9" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="O263" s="9" t="s">
         <v>174</v>
@@ -16312,7 +16354,7 @@
     </row>
     <row r="264" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A264" s="4" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B264" s="5">
         <v>46132.6341133449</v>
@@ -16328,10 +16370,10 @@
         <v>26</v>
       </c>
       <c r="G264" s="6" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="H264" s="6" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="I264" s="6"/>
       <c r="J264" s="5">
@@ -16347,7 +16389,7 @@
         <v>26</v>
       </c>
       <c r="N264" s="6" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="O264" s="6" t="s">
         <v>174</v>
@@ -16363,7 +16405,7 @@
     </row>
     <row r="265" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A265" s="7" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="B265" s="8">
         <v>46132.63411966435</v>
@@ -16379,10 +16421,10 @@
         <v>26</v>
       </c>
       <c r="G265" s="9" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="H265" s="9" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="I265" s="9"/>
       <c r="J265" s="8">
@@ -16398,7 +16440,7 @@
         <v>26</v>
       </c>
       <c r="N265" s="9" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="O265" s="9" t="s">
         <v>174</v>
@@ -16414,7 +16456,7 @@
     </row>
     <row r="266" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A266" s="4" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B266" s="5">
         <v>46132.58903189815</v>
@@ -16424,16 +16466,16 @@
         <v>46133.65412578704</v>
       </c>
       <c r="E266" s="6" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="F266" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G266" s="6" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="H266" s="6" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="I266" s="6"/>
       <c r="J266" s="5">
@@ -16449,13 +16491,13 @@
         <v>26</v>
       </c>
       <c r="N266" s="6" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="O266" s="6" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="P266" s="6" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="Q266" s="5">
         <v>46231</v>
@@ -16475,7 +16517,7 @@
     </row>
     <row r="267" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A267" s="7" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="B267" s="8">
         <v>46132.63422869213</v>
@@ -16491,10 +16533,10 @@
         <v>26</v>
       </c>
       <c r="G267" s="9" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="H267" s="9" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="I267" s="9"/>
       <c r="J267" s="8">
@@ -16510,13 +16552,13 @@
         <v>26</v>
       </c>
       <c r="N267" s="9" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="O267" s="9" t="s">
         <v>174</v>
       </c>
       <c r="P267" s="9" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="Q267" s="9"/>
       <c r="R267" s="9"/>
@@ -16526,7 +16568,7 @@
     </row>
     <row r="268" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A268" s="4" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B268" s="5">
         <v>46132.63423491898</v>
@@ -16542,10 +16584,10 @@
         <v>26</v>
       </c>
       <c r="G268" s="6" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="H268" s="6" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="I268" s="6"/>
       <c r="J268" s="5">
@@ -16561,13 +16603,13 @@
         <v>26</v>
       </c>
       <c r="N268" s="6" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="O268" s="6" t="s">
         <v>174</v>
       </c>
       <c r="P268" s="6" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="Q268" s="6"/>
       <c r="R268" s="6"/>
@@ -16577,7 +16619,7 @@
     </row>
     <row r="269" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A269" s="7" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B269" s="8">
         <v>46132.634240960644</v>
@@ -16593,10 +16635,10 @@
         <v>26</v>
       </c>
       <c r="G269" s="9" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="H269" s="9" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="I269" s="9"/>
       <c r="J269" s="8">
@@ -16612,13 +16654,13 @@
         <v>26</v>
       </c>
       <c r="N269" s="9" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="O269" s="9" t="s">
         <v>174</v>
       </c>
       <c r="P269" s="9" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="Q269" s="9"/>
       <c r="R269" s="9"/>
@@ -16628,7 +16670,7 @@
     </row>
     <row r="270" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A270" s="4" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B270" s="5">
         <v>46132.63424789352</v>
@@ -16644,10 +16686,10 @@
         <v>26</v>
       </c>
       <c r="G270" s="6" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="H270" s="6" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="I270" s="6"/>
       <c r="J270" s="5">
@@ -16663,13 +16705,13 @@
         <v>26</v>
       </c>
       <c r="N270" s="6" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="O270" s="6" t="s">
         <v>174</v>
       </c>
       <c r="P270" s="6" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="Q270" s="6"/>
       <c r="R270" s="6"/>
@@ -16679,7 +16721,7 @@
     </row>
     <row r="271" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A271" s="7" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B271" s="8">
         <v>46132.634254386576</v>
@@ -16695,10 +16737,10 @@
         <v>26</v>
       </c>
       <c r="G271" s="9" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="H271" s="9" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="I271" s="9"/>
       <c r="J271" s="8">
@@ -16714,13 +16756,13 @@
         <v>26</v>
       </c>
       <c r="N271" s="9" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="O271" s="9" t="s">
         <v>174</v>
       </c>
       <c r="P271" s="9" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="Q271" s="9"/>
       <c r="R271" s="9"/>
@@ -16730,7 +16772,7 @@
     </row>
     <row r="272" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A272" s="4" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B272" s="5">
         <v>46132.634260810184</v>
@@ -16746,10 +16788,10 @@
         <v>26</v>
       </c>
       <c r="G272" s="6" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="H272" s="6" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="I272" s="6"/>
       <c r="J272" s="5">
@@ -16765,13 +16807,13 @@
         <v>26</v>
       </c>
       <c r="N272" s="6" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="O272" s="6" t="s">
         <v>174</v>
       </c>
       <c r="P272" s="6" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="Q272" s="6"/>
       <c r="R272" s="6"/>
@@ -16781,7 +16823,7 @@
     </row>
     <row r="273" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A273" s="7" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B273" s="8">
         <v>46132.634267256944</v>
@@ -16797,10 +16839,10 @@
         <v>26</v>
       </c>
       <c r="G273" s="9" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="H273" s="9" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="I273" s="9"/>
       <c r="J273" s="8">
@@ -16816,13 +16858,13 @@
         <v>26</v>
       </c>
       <c r="N273" s="9" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="O273" s="9" t="s">
         <v>174</v>
       </c>
       <c r="P273" s="9" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="Q273" s="9"/>
       <c r="R273" s="9"/>
@@ -16832,7 +16874,7 @@
     </row>
     <row r="274" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A274" s="4" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="B274" s="5">
         <v>46132.63427122685</v>
@@ -16848,10 +16890,10 @@
         <v>26</v>
       </c>
       <c r="G274" s="6" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="H274" s="6" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="I274" s="6"/>
       <c r="J274" s="5">
@@ -16867,13 +16909,13 @@
         <v>26</v>
       </c>
       <c r="N274" s="6" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="O274" s="6" t="s">
         <v>174</v>
       </c>
       <c r="P274" s="6" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="Q274" s="6"/>
       <c r="R274" s="6"/>
@@ -16883,7 +16925,7 @@
     </row>
     <row r="275" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A275" s="7" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B275" s="8">
         <v>46132.634276365745</v>
@@ -16899,10 +16941,10 @@
         <v>26</v>
       </c>
       <c r="G275" s="9" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="H275" s="9" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="I275" s="9"/>
       <c r="J275" s="8">
@@ -16918,13 +16960,13 @@
         <v>26</v>
       </c>
       <c r="N275" s="9" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="O275" s="9" t="s">
         <v>174</v>
       </c>
       <c r="P275" s="9" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="Q275" s="9"/>
       <c r="R275" s="9"/>
@@ -16934,7 +16976,7 @@
     </row>
     <row r="276" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A276" s="4" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B276" s="5">
         <v>46132.63428099537</v>
@@ -16950,10 +16992,10 @@
         <v>26</v>
       </c>
       <c r="G276" s="6" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="H276" s="6" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="I276" s="6"/>
       <c r="J276" s="5">
@@ -16969,13 +17011,13 @@
         <v>26</v>
       </c>
       <c r="N276" s="6" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="O276" s="6" t="s">
         <v>174</v>
       </c>
       <c r="P276" s="6" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="Q276" s="6"/>
       <c r="R276" s="6"/>
@@ -16985,7 +17027,7 @@
     </row>
     <row r="277" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A277" s="7" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B277" s="8">
         <v>46132.63428524305</v>
@@ -17001,10 +17043,10 @@
         <v>26</v>
       </c>
       <c r="G277" s="9" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="H277" s="9" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="I277" s="9"/>
       <c r="J277" s="8">
@@ -17020,13 +17062,13 @@
         <v>26</v>
       </c>
       <c r="N277" s="9" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="O277" s="9" t="s">
         <v>174</v>
       </c>
       <c r="P277" s="9" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="Q277" s="9"/>
       <c r="R277" s="9"/>
@@ -17036,7 +17078,7 @@
     </row>
     <row r="278" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A278" s="4" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="B278" s="5">
         <v>46132.63429103009</v>
@@ -17052,10 +17094,10 @@
         <v>26</v>
       </c>
       <c r="G278" s="6" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="H278" s="6" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="I278" s="6"/>
       <c r="J278" s="5">
@@ -17071,13 +17113,13 @@
         <v>26</v>
       </c>
       <c r="N278" s="6" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="O278" s="6" t="s">
         <v>174</v>
       </c>
       <c r="P278" s="6" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="Q278" s="6"/>
       <c r="R278" s="6"/>
@@ -17087,7 +17129,7 @@
     </row>
     <row r="279" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A279" s="7" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="B279" s="8">
         <v>46132.63429523148</v>
@@ -17103,10 +17145,10 @@
         <v>26</v>
       </c>
       <c r="G279" s="9" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="H279" s="9" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="I279" s="9"/>
       <c r="J279" s="8">
@@ -17122,13 +17164,13 @@
         <v>26</v>
       </c>
       <c r="N279" s="9" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="O279" s="9" t="s">
         <v>174</v>
       </c>
       <c r="P279" s="9" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="Q279" s="9"/>
       <c r="R279" s="9"/>
@@ -17138,7 +17180,7 @@
     </row>
     <row r="280" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A280" s="4" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B280" s="5">
         <v>46132.63430358796</v>
@@ -17154,10 +17196,10 @@
         <v>26</v>
       </c>
       <c r="G280" s="6" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="H280" s="6" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="I280" s="6"/>
       <c r="J280" s="5">
@@ -17173,13 +17215,13 @@
         <v>26</v>
       </c>
       <c r="N280" s="6" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="O280" s="6" t="s">
         <v>174</v>
       </c>
       <c r="P280" s="6" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="Q280" s="6"/>
       <c r="R280" s="6"/>
@@ -17189,7 +17231,7 @@
     </row>
     <row r="281" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A281" s="7" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="B281" s="8">
         <v>46132.63431148148</v>
@@ -17205,10 +17247,10 @@
         <v>26</v>
       </c>
       <c r="G281" s="9" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="H281" s="9" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="I281" s="9"/>
       <c r="J281" s="8">
@@ -17224,13 +17266,13 @@
         <v>26</v>
       </c>
       <c r="N281" s="9" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="O281" s="9" t="s">
         <v>174</v>
       </c>
       <c r="P281" s="9" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="Q281" s="9"/>
       <c r="R281" s="9"/>
@@ -17240,7 +17282,7 @@
     </row>
     <row r="282" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A282" s="4" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B282" s="5">
         <v>46132.63437663195</v>
@@ -17256,10 +17298,10 @@
         <v>26</v>
       </c>
       <c r="G282" s="6" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="H282" s="6" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="I282" s="6"/>
       <c r="J282" s="5">
@@ -17275,13 +17317,13 @@
         <v>26</v>
       </c>
       <c r="N282" s="6" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="O282" s="6" t="s">
         <v>174</v>
       </c>
       <c r="P282" s="6" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="Q282" s="6"/>
       <c r="R282" s="6"/>
@@ -17291,7 +17333,7 @@
     </row>
     <row r="283" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A283" s="7" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="B283" s="8">
         <v>46132.589037604164</v>
@@ -17301,7 +17343,7 @@
         <v>46133.59235670139</v>
       </c>
       <c r="E283" s="9" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F283" s="9" t="s">
         <v>25</v>
@@ -17325,7 +17367,7 @@
         <v>26</v>
       </c>
       <c r="O283" s="9" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="P283" s="9" t="s">
         <v>26</v>
@@ -17338,7 +17380,7 @@
     </row>
     <row r="284" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A284" s="4" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="B284" s="5">
         <v>46132.5890406713</v>
@@ -17348,16 +17390,16 @@
         <v>46134.57925581018</v>
       </c>
       <c r="E284" s="6" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="F284" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G284" s="6" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H284" s="6" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="I284" s="5">
         <v>46232</v>
@@ -17375,13 +17417,13 @@
         <v>26</v>
       </c>
       <c r="N284" s="6" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="O284" s="6" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="P284" s="6" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="Q284" s="5">
         <v>46240</v>
@@ -17401,7 +17443,7 @@
     </row>
     <row r="285" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A285" s="7" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B285" s="8">
         <v>46132.58904559028</v>
@@ -17411,16 +17453,16 @@
         <v>46134.57925902778</v>
       </c>
       <c r="E285" s="9" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="F285" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G285" s="9" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H285" s="9" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="I285" s="8">
         <v>46232</v>
@@ -17438,13 +17480,13 @@
         <v>26</v>
       </c>
       <c r="N285" s="9" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="O285" s="9" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="P285" s="9" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="Q285" s="8">
         <v>46240</v>

--- a/data/50001541 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001541 - XEMORTIZ MINERA FRISCO.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3235" uniqueCount="548">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3235" uniqueCount="549">
   <si>
     <t>50001541 -  XEMORTIZ MINERA FRISCO</t>
   </si>
@@ -511,7 +511,7 @@
     <t>1214138711508170</t>
   </si>
   <si>
-    <t>Propuesta Fabricación externa  OT 4307 ,Propuesta Mecanizado,Propuesta Corte plasma ,propuesta Corte laser,Ingenieria y diseñoo:,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2</t>
+    <t>Propuesta Fabricación externa  OT 4307 ,Propuesta Mecanizado,Propuesta Corte plasma ,propuesta Corte laser,Ingenieria y diseñoo:,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2</t>
   </si>
   <si>
     <t>1214138720958805</t>
@@ -526,118 +526,121 @@
     <t>francisca.gonzalez@zitron.com</t>
   </si>
   <si>
-    <t xml:space="preserve">OT1 4232 ZVN 1-9-86/2 ,OT2 4232 ZVN 1-9-86/2 ,OT3 4232 ZVN 1-9-86/2 ,OT4 4232 ZVN 1-9-86/2 ,OT5 4232 ZVN 1-9-86/2 ,OT6 4232 ZVN 1-9-86/2 ,OT7 4232 ZVN 1-9-86/2 ,OT8 4232 ZVN 1-9-86/2 ,OT9 4232 ZVN 1-9-86/2 ,OT10 4232 ZVN 1-9-86/2  ,OT11 4232 ZVN 1-9-86/2 ,OT12 4232 ZVN 1-9-86/2 ,OT13 4232 ZVN 1-9-86/2 ,OT14 4232 ZVN 1-9-86/2 ,OT15 4232 ZVN 1-9-86/2 ,OT16 4232 ZVN 1-9-86/2 </t>
+    <t xml:space="preserve">OT1 4307 ZVN 1-9-86/2 ,OT2 4307 ZVN 1-9-86/2 ,OT3 4307 ZVN 1-9-86/2 ,OT4 4307 ZVN 1-9-86/2 ,OT5 4307 ZVN 1-9-86/2 ,OT6 4307 ZVN 1-9-86/2 ,OT7 4307 ZVN 1-9-86/2 ,OT8 4307  ZVN 1-9-86/2 ,OT9 4307 ZVN 1-9-86/2 ,OT10 4307 ZVN 1-9-86/2  ,OT11 4307 ZVN 1-9-86/2 ,OT12 4307 ZVN 1-9-86/2 ,OT13 4307 ZVN 1-9-86/2 ,OT14 4307 ZVN 1-9-86/2 ,OT15 4307 ZVN 1-9-86/2 ,OT16 4307 ZVN 1-9-86/2 </t>
   </si>
   <si>
     <t>1214137717389660</t>
   </si>
   <si>
-    <t xml:space="preserve">OT1 4232 ZVN 1-9-86/2 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4232 ZVN 1-9-86/2 </t>
-  </si>
-  <si>
-    <t>OT 4232 ZVN 1-9-86/2 ,Check pruebas FAT</t>
+    <t xml:space="preserve">OT1 4307 ZVN 1-9-86/2 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4307 ZVN 1-9-86/2 </t>
+  </si>
+  <si>
+    <t>OT 4307 ZVN 1-9-86/2 ,Check pruebas FAT</t>
   </si>
   <si>
     <t>1214137717389661</t>
   </si>
   <si>
-    <t xml:space="preserve">OT2 4232 ZVN 1-9-86/2 </t>
-  </si>
-  <si>
-    <t>OT 4232 ZVN 1-9-86/2 ,Check pruebas FAT,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales</t>
+    <t xml:space="preserve">OT2 4307 ZVN 1-9-86/2 </t>
+  </si>
+  <si>
+    <t>OT 4307 ZVN 1-9-86/2 ,Check pruebas FAT,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales</t>
   </si>
   <si>
     <t>1214137717389662</t>
   </si>
   <si>
-    <t xml:space="preserve">OT3 4232 ZVN 1-9-86/2 </t>
+    <t xml:space="preserve">OT3 4307 ZVN 1-9-86/2 </t>
   </si>
   <si>
     <t>1214137717389663</t>
   </si>
   <si>
-    <t xml:space="preserve">OT4 4232 ZVN 1-9-86/2 </t>
+    <t xml:space="preserve">OT4 4307 ZVN 1-9-86/2 </t>
   </si>
   <si>
     <t>1214137717389664</t>
   </si>
   <si>
-    <t xml:space="preserve">OT5 4232 ZVN 1-9-86/2 </t>
+    <t xml:space="preserve">OT5 4307 ZVN 1-9-86/2 </t>
   </si>
   <si>
     <t>1214137717389665</t>
   </si>
   <si>
-    <t xml:space="preserve">OT6 4232 ZVN 1-9-86/2 </t>
+    <t xml:space="preserve">OT6 4307 ZVN 1-9-86/2 </t>
   </si>
   <si>
     <t>1214137717389666</t>
   </si>
   <si>
-    <t xml:space="preserve">OT7 4232 ZVN 1-9-86/2 </t>
-  </si>
-  <si>
-    <t>OT 4232 ZVN 1-9-86/2 ,Check pruebas FAT,OT 4325- ZVN 1-7-63/2,OT 4327- ZVN 2-9-103/2</t>
+    <t xml:space="preserve">OT7 4307 ZVN 1-9-86/2 </t>
+  </si>
+  <si>
+    <t>OT 4307 ZVN 1-9-86/2 ,Check pruebas FAT,OT 4325- ZVN 1-7-63/2,OT 4327- ZVN 2-9-103/2</t>
   </si>
   <si>
     <t>1214137717389667</t>
   </si>
   <si>
-    <t xml:space="preserve">OT8 4232 ZVN 1-9-86/2 </t>
+    <t xml:space="preserve">OT8 4307  ZVN 1-9-86/2 </t>
   </si>
   <si>
     <t>1214137717389668</t>
   </si>
   <si>
-    <t xml:space="preserve">OT9 4232 ZVN 1-9-86/2 </t>
+    <t xml:space="preserve">OT9 4307 ZVN 1-9-86/2 </t>
   </si>
   <si>
     <t>1214137717389669</t>
   </si>
   <si>
-    <t xml:space="preserve">OT10 4232 ZVN 1-9-86/2  </t>
+    <t xml:space="preserve">OT10 4307 ZVN 1-9-86/2  </t>
   </si>
   <si>
     <t>1214137717389671</t>
   </si>
   <si>
-    <t xml:space="preserve">OT11 4232 ZVN 1-9-86/2 </t>
+    <t xml:space="preserve">OT11 4307 ZVN 1-9-86/2 </t>
   </si>
   <si>
     <t>1214137717389672</t>
   </si>
   <si>
-    <t xml:space="preserve">OT12 4232 ZVN 1-9-86/2 </t>
+    <t xml:space="preserve">OT12 4307 ZVN 1-9-86/2 </t>
   </si>
   <si>
     <t>1214137717389673</t>
   </si>
   <si>
-    <t xml:space="preserve">OT13 4232 ZVN 1-9-86/2 </t>
+    <t xml:space="preserve">OT13 4307 ZVN 1-9-86/2 </t>
   </si>
   <si>
     <t>1214137717389674</t>
   </si>
   <si>
-    <t xml:space="preserve">OT14 4232 ZVN 1-9-86/2 </t>
+    <t xml:space="preserve">OT14 4307 ZVN 1-9-86/2 </t>
   </si>
   <si>
     <t>1214137717389675</t>
   </si>
   <si>
-    <t xml:space="preserve">OT15 4232 ZVN 1-9-86/2 </t>
+    <t xml:space="preserve">OT15 4307 ZVN 1-9-86/2 </t>
+  </si>
+  <si>
+    <t>OT 4307  ZVN 1-9-86/2 ,Check pruebas FAT</t>
   </si>
   <si>
     <t>1214137717389670</t>
   </si>
   <si>
-    <t xml:space="preserve">OT16 4232 ZVN 1-9-86/2 </t>
-  </si>
-  <si>
-    <t>OT 4232 ZVN 1-9-86/2,Check pruebas FAT</t>
+    <t xml:space="preserve">OT16 4307 ZVN 1-9-86/2 </t>
+  </si>
+  <si>
+    <t>OT 4307 ZVN 1-9-86/2,Check pruebas FAT</t>
   </si>
   <si>
     <t>1214137717389712</t>
@@ -739,13 +742,10 @@
     <t>1214137717389464</t>
   </si>
   <si>
-    <t xml:space="preserve">OT 4307 ZVN 1-9-86/2 </t>
-  </si>
-  <si>
     <t>Generación OC Fabricación externa ,Control de calidad Mecanizado,Control de calidad corte Laser,Control de calidad Corte plasma ,Check Planos</t>
   </si>
   <si>
-    <t>OT 4232 ZVN 1-9-86/2,Armado</t>
+    <t>OT 4307 ZVN 1-9-86/2,Armado</t>
   </si>
   <si>
     <t>1214137717389465</t>
@@ -757,7 +757,7 @@
     <t>Generación OC Fabricación externa ,Control de calidad corte Laser,Control de calidad Corte plasma ,Control de calidad Mecanizado,Check Planos</t>
   </si>
   <si>
-    <t>Armado,OT 4232 ZVN 1-9-86/2</t>
+    <t>Armado,OT 4307 ZVN 1-9-86/2</t>
   </si>
   <si>
     <t>1214137717389467</t>
@@ -814,7 +814,7 @@
     <t>1214137717389478</t>
   </si>
   <si>
-    <t>OT 4232 ZVN 1-9-86/2 ,Armado</t>
+    <t>OT 4307 ZVN 1-9-86/2 ,Armado</t>
   </si>
   <si>
     <t>1214137717389479</t>
@@ -826,25 +826,25 @@
     <t>Control de calidad Armado</t>
   </si>
   <si>
-    <t>OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2</t>
+    <t>OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2</t>
   </si>
   <si>
     <t>1214137717389481</t>
   </si>
   <si>
-    <t>OT 4232 ZVN 1-9-86/2</t>
+    <t>OT 4307 ZVN 1-9-86/2</t>
   </si>
   <si>
     <t>OT 4307 ZVN 1-9-86/2 ,Check Planos</t>
   </si>
   <si>
-    <t>OT 4232 ZVN 1-9-86/2 ,Control de calidad Armado</t>
+    <t>OT 4307 ZVN 1-9-86/2 ,Control de calidad Armado</t>
   </si>
   <si>
     <t>1214137717389482</t>
   </si>
   <si>
-    <t>OT 4232 ZVN 1-9-86/2,Control de calidad Armado</t>
+    <t>OT 4307 ZVN 1-9-86/2,Control de calidad Armado</t>
   </si>
   <si>
     <t>1214137717389483</t>
@@ -904,7 +904,7 @@
     <t>Recepcion Alabe</t>
   </si>
   <si>
-    <t xml:space="preserve">Bodega:,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 </t>
+    <t xml:space="preserve">Bodega:,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 </t>
   </si>
   <si>
     <t>1214138844805224</t>
@@ -919,7 +919,7 @@
     <t>Recepcion motor</t>
   </si>
   <si>
-    <t xml:space="preserve">Bodega:,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 </t>
+    <t xml:space="preserve">Bodega:,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 </t>
   </si>
   <si>
     <t>1214138720975489</t>
@@ -937,13 +937,13 @@
     <t>Revestimiento</t>
   </si>
   <si>
-    <t xml:space="preserve">OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 </t>
+    <t xml:space="preserve">OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 </t>
   </si>
   <si>
     <t>1214137717389498</t>
   </si>
   <si>
-    <t xml:space="preserve">OT 4232 ZVN 1-9-86/2 ,Revestimiento,OT 4232 ZVN 1-9-86/2 </t>
+    <t xml:space="preserve">OT 4307 ZVN 1-9-86/2 ,Revestimiento,OT 4307 ZVN 1-9-86/2 </t>
   </si>
   <si>
     <t>1214137717389499</t>
@@ -952,7 +952,7 @@
     <t>1214137717389500</t>
   </si>
   <si>
-    <t xml:space="preserve">OT 4232 ZVN 1-9-86/2 ,Revestimiento,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 </t>
+    <t xml:space="preserve">OT 4307 ZVN 1-9-86/2 ,Revestimiento,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 </t>
   </si>
   <si>
     <t>1214137717389501</t>
@@ -964,7 +964,7 @@
     <t>1214137717389503</t>
   </si>
   <si>
-    <t xml:space="preserve">Revestimiento,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 </t>
+    <t xml:space="preserve">Revestimiento,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 </t>
   </si>
   <si>
     <t>1214137717389504</t>
@@ -1003,22 +1003,19 @@
     <t>Montaje Alabe</t>
   </si>
   <si>
-    <t xml:space="preserve">OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 </t>
-  </si>
-  <si>
     <t>1214137717389530</t>
   </si>
   <si>
-    <t>OT 4232 ZVN 1-9-86/2 ,Recepcion Alabe,Check Planos</t>
-  </si>
-  <si>
-    <t>OT 4232 ZVN 1-9-86/2 ,Montaje Alabe</t>
+    <t>OT 4307 ZVN 1-9-86/2 ,Recepcion Alabe,Check Planos</t>
+  </si>
+  <si>
+    <t>OT 4307 ZVN 1-9-86/2 ,Montaje Alabe</t>
   </si>
   <si>
     <t>1214137717389531</t>
   </si>
   <si>
-    <t>OT 4232 ZVN 1-9-86/2,Recepcion Alabe,Check Planos</t>
+    <t>OT 4307 ZVN 1-9-86/2,Recepcion Alabe,Check Planos</t>
   </si>
   <si>
     <t>1214137717389532</t>
@@ -1027,7 +1024,7 @@
     <t>1214137717389533</t>
   </si>
   <si>
-    <t xml:space="preserve">Recepcion Alabe,Check Planos,OT 4232 ZVN 1-9-86/2 </t>
+    <t xml:space="preserve">Recepcion Alabe,Check Planos,OT 4307 ZVN 1-9-86/2 </t>
   </si>
   <si>
     <t>1214137717389534</t>
@@ -1036,13 +1033,13 @@
     <t>1214137717389535</t>
   </si>
   <si>
-    <t>OT 4232 ZVN 1-9-86/2 ,Recepcion Alabe</t>
+    <t>OT 4307 ZVN 1-9-86/2 ,Recepcion Alabe</t>
   </si>
   <si>
     <t>1214137717389536</t>
   </si>
   <si>
-    <t>Recepcion Alabe,OT 4232 ZVN 1-9-86/2</t>
+    <t>Recepcion Alabe,OT 4307 ZVN 1-9-86/2</t>
   </si>
   <si>
     <t>1214137717389537</t>
@@ -1054,7 +1051,7 @@
     <t>1214137717389539</t>
   </si>
   <si>
-    <t>OT 4232 ZVN 1-9-86/2,Recepcion Alabe</t>
+    <t>OT 4307 ZVN 1-9-86/2,Recepcion Alabe</t>
   </si>
   <si>
     <t>1214137717389540</t>
@@ -1084,16 +1081,16 @@
     <t>1214137717389546</t>
   </si>
   <si>
-    <t xml:space="preserve">Recepcion Rodete,OT 4232 ZVN 1-9-86/2 </t>
-  </si>
-  <si>
-    <t>OT 4232 ZVN 1-9-86/2 ,Montaje Rodete</t>
+    <t xml:space="preserve">Recepcion Rodete,OT 4307 ZVN 1-9-86/2 </t>
+  </si>
+  <si>
+    <t>OT 4307 ZVN 1-9-86/2 ,Montaje Rodete</t>
   </si>
   <si>
     <t>1214137717389547</t>
   </si>
   <si>
-    <t>Recepcion Rodete,OT 4232 ZVN 1-9-86/2</t>
+    <t>Recepcion Rodete,OT 4307 ZVN 1-9-86/2</t>
   </si>
   <si>
     <t>1214137717389548</t>
@@ -1150,7 +1147,7 @@
     <t>Recepcion motor,Check Planos</t>
   </si>
   <si>
-    <t>OT 4232 ZVN 1-9-86/2 ,Montaje motor</t>
+    <t>OT 4307 ZVN 1-9-86/2 ,Montaje motor</t>
   </si>
   <si>
     <t>1214137717389515</t>
@@ -1159,7 +1156,7 @@
     <t>1214137717389516</t>
   </si>
   <si>
-    <t>OT 4232 ZVN 1-9-86/2,Recepcion motor</t>
+    <t>OT 4307 ZVN 1-9-86/2,Recepcion motor</t>
   </si>
   <si>
     <t>1214137717389517</t>
@@ -1168,7 +1165,7 @@
     <t>1214137717389518</t>
   </si>
   <si>
-    <t>OT 4232 ZVN 1-9-86/2 ,Recepcion motor</t>
+    <t>OT 4307 ZVN 1-9-86/2 ,Recepcion motor</t>
   </si>
   <si>
     <t>1214137717389519</t>
@@ -1213,100 +1210,100 @@
     <t>1214137717389562</t>
   </si>
   <si>
-    <t xml:space="preserve">OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 </t>
-  </si>
-  <si>
-    <t>OT1 4232 ZVN 1-9-86/2 ,Pruebas FAT</t>
+    <t xml:space="preserve">OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 </t>
+  </si>
+  <si>
+    <t>OT1 4307 ZVN 1-9-86/2 ,Pruebas FAT</t>
   </si>
   <si>
     <t>1214137717389563</t>
   </si>
   <si>
-    <t>OT2 4232 ZVN 1-9-86/2 ,Pruebas FAT</t>
+    <t>OT2 4307 ZVN 1-9-86/2 ,Pruebas FAT</t>
   </si>
   <si>
     <t>1214137717389564</t>
   </si>
   <si>
-    <t>OT3 4232 ZVN 1-9-86/2 ,Pruebas FAT</t>
+    <t>OT3 4307 ZVN 1-9-86/2 ,Pruebas FAT</t>
   </si>
   <si>
     <t>1214137717389565</t>
   </si>
   <si>
-    <t>OT4 4232 ZVN 1-9-86/2 ,Pruebas FAT</t>
+    <t>OT4 4307 ZVN 1-9-86/2 ,Pruebas FAT</t>
   </si>
   <si>
     <t>1214137717389567</t>
   </si>
   <si>
-    <t>OT5 4232 ZVN 1-9-86/2 ,Pruebas FAT</t>
+    <t>OT5 4307 ZVN 1-9-86/2 ,Pruebas FAT</t>
   </si>
   <si>
     <t>1214137717389566</t>
   </si>
   <si>
-    <t>OT6 4232 ZVN 1-9-86/2 ,Pruebas FAT</t>
+    <t>OT6 4307 ZVN 1-9-86/2 ,Pruebas FAT</t>
   </si>
   <si>
     <t>1214137717389568</t>
   </si>
   <si>
-    <t>OT7 4232 ZVN 1-9-86/2 ,Pruebas FAT</t>
+    <t>OT7 4307 ZVN 1-9-86/2 ,Pruebas FAT</t>
   </si>
   <si>
     <t>1214137717389569</t>
   </si>
   <si>
-    <t>OT8 4232 ZVN 1-9-86/2 ,Pruebas FAT</t>
+    <t>OT8 4307  ZVN 1-9-86/2 ,Pruebas FAT</t>
   </si>
   <si>
     <t>1214137717389570</t>
   </si>
   <si>
-    <t>OT9 4232 ZVN 1-9-86/2 ,Pruebas FAT</t>
+    <t>OT9 4307 ZVN 1-9-86/2 ,Pruebas FAT</t>
   </si>
   <si>
     <t>1214137717389571</t>
   </si>
   <si>
-    <t>OT10 4232 ZVN 1-9-86/2  ,Pruebas FAT</t>
+    <t>OT10 4307 ZVN 1-9-86/2  ,Pruebas FAT</t>
   </si>
   <si>
     <t>1214137717389572</t>
   </si>
   <si>
-    <t>OT11 4232 ZVN 1-9-86/2 ,Pruebas FAT</t>
+    <t>OT11 4307 ZVN 1-9-86/2 ,Pruebas FAT</t>
   </si>
   <si>
     <t>1214137717389573</t>
   </si>
   <si>
-    <t>OT12 4232 ZVN 1-9-86/2 ,Pruebas FAT</t>
+    <t>OT12 4307 ZVN 1-9-86/2 ,Pruebas FAT</t>
   </si>
   <si>
     <t>1214137717389574</t>
   </si>
   <si>
-    <t>OT13 4232 ZVN 1-9-86/2 ,Pruebas FAT</t>
+    <t>OT13 4307 ZVN 1-9-86/2 ,Pruebas FAT</t>
   </si>
   <si>
     <t>1214137717389575</t>
   </si>
   <si>
-    <t>OT14 4232 ZVN 1-9-86/2 ,Pruebas FAT</t>
+    <t>OT14 4307 ZVN 1-9-86/2 ,Pruebas FAT</t>
   </si>
   <si>
     <t>1214137717389576</t>
   </si>
   <si>
-    <t>OT15 4232 ZVN 1-9-86/2 ,Pruebas FAT</t>
+    <t>OT15 4307 ZVN 1-9-86/2 ,Pruebas FAT</t>
   </si>
   <si>
     <t>1214137717389577</t>
   </si>
   <si>
-    <t>OT16 4232 ZVN 1-9-86/2 ,Pruebas FAT</t>
+    <t>OT16 4307 ZVN 1-9-86/2 ,Pruebas FAT</t>
   </si>
   <si>
     <t>1214138801633922</t>
@@ -1315,7 +1312,7 @@
     <t>RE-PINTADO</t>
   </si>
   <si>
-    <t>OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2</t>
+    <t>OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307  ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2</t>
   </si>
   <si>
     <t>Coordinacion Entrega con Cliente,Montaje:</t>
@@ -1324,7 +1321,7 @@
     <t>1214137717389578</t>
   </si>
   <si>
-    <t>OT 4232 ZVN 1-9-86/2 ,RE-PINTADO</t>
+    <t>OT 4307 ZVN 1-9-86/2 ,RE-PINTADO</t>
   </si>
   <si>
     <t>1214137717389579</t>
@@ -1345,6 +1342,9 @@
     <t>1214137717389584</t>
   </si>
   <si>
+    <t>OT 4307  ZVN 1-9-86/2 ,RE-PINTADO</t>
+  </si>
+  <si>
     <t>1214137717389585</t>
   </si>
   <si>
@@ -1369,6 +1369,9 @@
     <t>1214137717389592</t>
   </si>
   <si>
+    <t xml:space="preserve">OT 4307  ZVN 1-9-86/2 </t>
+  </si>
+  <si>
     <t>1214150417415297</t>
   </si>
   <si>
@@ -1645,7 +1648,7 @@
     <t>nicolas.tello@zitron.com</t>
   </si>
   <si>
-    <t xml:space="preserve">Despacho,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 </t>
+    <t xml:space="preserve">Despacho,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 </t>
   </si>
   <si>
     <t>1214138801687063</t>
@@ -1654,7 +1657,7 @@
     <t>Costos</t>
   </si>
   <si>
-    <t>Despacho,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,OT 4232 ZVN 1-9-86/2 ,Analisis de costeo</t>
+    <t>Despacho,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,Analisis de costeo</t>
   </si>
 </sst>
 </file>
@@ -4981,7 +4984,7 @@
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46134.5799159375</v>
+        <v>46196.91191069444</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>173</v>
@@ -5032,7 +5035,7 @@
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="8">
-        <v>46181.6092330324</v>
+        <v>46196.91191847222</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>177</v>
@@ -5083,7 +5086,7 @@
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46155.583431736115</v>
+        <v>46196.911927002315</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>180</v>
@@ -5134,7 +5137,7 @@
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="8">
-        <v>46134.58001292824</v>
+        <v>46196.91193416667</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>182</v>
@@ -5185,7 +5188,7 @@
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46168.80819496528</v>
+        <v>46196.91194335648</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>184</v>
@@ -5236,7 +5239,7 @@
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="8">
-        <v>46134.58007261574</v>
+        <v>46196.911952731476</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>186</v>
@@ -5287,7 +5290,7 @@
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46162.79539077546</v>
+        <v>46196.91195940972</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>188</v>
@@ -5338,7 +5341,7 @@
       </c>
       <c r="C55" s="9"/>
       <c r="D55" s="8">
-        <v>46134.58013307871</v>
+        <v>46196.91196953703</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>191</v>
@@ -5389,7 +5392,7 @@
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46134.58016725694</v>
+        <v>46196.91198518519</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>193</v>
@@ -5440,7 +5443,7 @@
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46134.58019508102</v>
+        <v>46196.912005659724</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>195</v>
@@ -5491,7 +5494,7 @@
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46134.5803250926</v>
+        <v>46196.912017662034</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>197</v>
@@ -5542,7 +5545,7 @@
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46134.580357175924</v>
+        <v>46196.91202767361</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>199</v>
@@ -5593,7 +5596,7 @@
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46134.580395439814</v>
+        <v>46196.912036967595</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>201</v>
@@ -5644,7 +5647,7 @@
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46134.58043140046</v>
+        <v>46196.91204791667</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>203</v>
@@ -5695,7 +5698,7 @@
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46134.58046646991</v>
+        <v>46196.9120665625</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>205</v>
@@ -5729,7 +5732,7 @@
         <v>174</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>175</v>
+        <v>206</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5739,17 +5742,17 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B63" s="8">
         <v>46132.63460722222</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46134.5805774537</v>
+        <v>46196.91208912037</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
@@ -5780,7 +5783,7 @@
         <v>174</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q63" s="9"/>
       <c r="R63" s="9"/>
@@ -5790,7 +5793,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B64" s="5">
         <v>46132.64721917824</v>
@@ -5802,7 +5805,7 @@
         <v>46157.493989166665</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>25</v>
@@ -5826,7 +5829,7 @@
         <v>26</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P64" s="6" t="s">
         <v>26</v>
@@ -5843,7 +5846,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B65" s="8">
         <v>46132.624842916666</v>
@@ -5855,7 +5858,7 @@
         <v>46182.18354462963</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
@@ -5882,13 +5885,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="O65" s="9" t="s">
         <v>135</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q65" s="8">
         <v>46181</v>
@@ -5908,7 +5911,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B66" s="5">
         <v>46132.62490728009</v>
@@ -5920,7 +5923,7 @@
         <v>46182.18354459491</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
@@ -5947,13 +5950,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="O66" s="6" t="s">
         <v>143</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q66" s="5">
         <v>46181</v>
@@ -5973,7 +5976,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B67" s="8">
         <v>46132.62495362268</v>
@@ -5985,7 +5988,7 @@
         <v>46182.183544768515</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
@@ -6012,13 +6015,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="O67" s="9" t="s">
         <v>151</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q67" s="8">
         <v>46181</v>
@@ -6038,7 +6041,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B68" s="5">
         <v>46132.70742302084</v>
@@ -6050,16 +6053,16 @@
         <v>46184.203094386576</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I68" s="5">
         <v>46182</v>
@@ -6077,13 +6080,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q68" s="5">
         <v>46183</v>
@@ -6103,7 +6106,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B69" s="8">
         <v>46132.70752974537</v>
@@ -6115,16 +6118,16 @@
         <v>46184.20309802084</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I69" s="8">
         <v>46182</v>
@@ -6142,13 +6145,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q69" s="8">
         <v>46183</v>
@@ -6168,7 +6171,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B70" s="5">
         <v>46132.70760050926</v>
@@ -6180,16 +6183,16 @@
         <v>46184.203094212964</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I70" s="5">
         <v>46182</v>
@@ -6207,13 +6210,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q70" s="5">
         <v>46183</v>
@@ -6233,7 +6236,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B71" s="8">
         <v>46132.58888190972</v>
@@ -6243,7 +6246,7 @@
         <v>46196.691984930556</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>25</v>
@@ -6267,7 +6270,7 @@
         <v>26</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P71" s="9" t="s">
         <v>26</v>
@@ -6280,7 +6283,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B72" s="5">
         <v>46132.588885185185</v>
@@ -6298,10 +6301,10 @@
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I72" s="5">
         <v>46169</v>
@@ -6319,13 +6322,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O72" s="6" t="s">
         <v>82</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q72" s="5">
         <v>46147</v>
@@ -6345,7 +6348,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B73" s="8">
         <v>46132.58889042824</v>
@@ -6357,16 +6360,16 @@
         <v>46196.692663379625</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I73" s="8">
         <v>46184</v>
@@ -6384,13 +6387,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q73" s="8">
         <v>46206</v>
@@ -6410,7 +6413,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B74" s="5">
         <v>46132.631278472225</v>
@@ -6422,16 +6425,16 @@
         <v>46196.69266049768</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>242</v>
+        <v>174</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I74" s="5">
         <v>46184</v>
@@ -6449,7 +6452,7 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O74" s="6" t="s">
         <v>243</v>
@@ -6477,16 +6480,16 @@
         <v>46196.692844907404</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>242</v>
+        <v>174</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I75" s="8">
         <v>46184</v>
@@ -6504,7 +6507,7 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O75" s="9" t="s">
         <v>243</v>
@@ -6532,16 +6535,16 @@
         <v>46196.69317986111</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>242</v>
+        <v>174</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I76" s="5">
         <v>46184</v>
@@ -6559,7 +6562,7 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O76" s="6" t="s">
         <v>247</v>
@@ -6587,16 +6590,16 @@
         <v>46196.693142592594</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>242</v>
+        <v>174</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I77" s="8">
         <v>46184</v>
@@ -6614,7 +6617,7 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O77" s="9" t="s">
         <v>243</v>
@@ -6642,16 +6645,16 @@
         <v>46196.693131458334</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>242</v>
+        <v>174</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I78" s="5">
         <v>46184</v>
@@ -6669,7 +6672,7 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O78" s="6" t="s">
         <v>251</v>
@@ -6697,16 +6700,16 @@
         <v>46196.693120717595</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>242</v>
+        <v>174</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I79" s="8">
         <v>46184</v>
@@ -6724,7 +6727,7 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O79" s="9" t="s">
         <v>253</v>
@@ -6752,16 +6755,16 @@
         <v>46196.69310042824</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>242</v>
+        <v>174</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I80" s="5">
         <v>46184</v>
@@ -6779,7 +6782,7 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O80" s="6" t="s">
         <v>255</v>
@@ -6807,16 +6810,16 @@
         <v>46196.693085949075</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>242</v>
+        <v>174</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I81" s="8">
         <v>46184</v>
@@ -6834,7 +6837,7 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O81" s="9" t="s">
         <v>257</v>
@@ -6862,16 +6865,16 @@
         <v>46196.69307368055</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>242</v>
+        <v>174</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I82" s="5">
         <v>46184</v>
@@ -6889,7 +6892,7 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O82" s="6" t="s">
         <v>255</v>
@@ -6917,16 +6920,16 @@
         <v>46196.69306041667</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>242</v>
+        <v>174</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I83" s="8">
         <v>46184</v>
@@ -6944,7 +6947,7 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O83" s="9" t="s">
         <v>260</v>
@@ -6972,16 +6975,16 @@
         <v>46196.693049560185</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>242</v>
+        <v>174</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I84" s="5">
         <v>46184</v>
@@ -6999,7 +7002,7 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O84" s="6" t="s">
         <v>255</v>
@@ -7027,16 +7030,16 @@
         <v>46196.6930421412</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>242</v>
+        <v>174</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H85" s="9" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I85" s="8">
         <v>46184</v>
@@ -7054,7 +7057,7 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O85" s="9" t="s">
         <v>255</v>
@@ -7082,16 +7085,16 @@
         <v>46196.69303037037</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>242</v>
+        <v>174</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I86" s="5">
         <v>46184</v>
@@ -7109,7 +7112,7 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O86" s="6" t="s">
         <v>255</v>
@@ -7137,16 +7140,16 @@
         <v>46196.69302122685</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>242</v>
+        <v>174</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H87" s="9" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I87" s="8">
         <v>46184</v>
@@ -7164,7 +7167,7 @@
         <v>26</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O87" s="9" t="s">
         <v>265</v>
@@ -7192,16 +7195,16 @@
         <v>46196.692995543985</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>242</v>
+        <v>174</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I88" s="5">
         <v>46184</v>
@@ -7219,7 +7222,7 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O88" s="6" t="s">
         <v>255</v>
@@ -7247,16 +7250,16 @@
         <v>46196.69300998843</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>242</v>
+        <v>174</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I89" s="8">
         <v>46184</v>
@@ -7274,7 +7277,7 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O89" s="9" t="s">
         <v>255</v>
@@ -7297,7 +7300,7 @@
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46134.56786915509</v>
+        <v>46196.91358532407</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>270</v>
@@ -7306,10 +7309,10 @@
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I90" s="5">
         <v>46209</v>
@@ -7327,13 +7330,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O90" s="6" t="s">
         <v>271</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q90" s="5">
         <v>46210</v>
@@ -7358,9 +7361,11 @@
       <c r="B91" s="8">
         <v>46132.63147894676</v>
       </c>
-      <c r="C91" s="9"/>
+      <c r="C91" s="8">
+        <v>46196.91330332176</v>
+      </c>
       <c r="D91" s="8">
-        <v>46196.691315324075</v>
+        <v>46196.913305381946</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>273</v>
@@ -7369,10 +7374,10 @@
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H91" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I91" s="8">
         <v>46209</v>
@@ -7411,9 +7416,11 @@
       <c r="B92" s="5">
         <v>46132.63149082176</v>
       </c>
-      <c r="C92" s="6"/>
+      <c r="C92" s="5">
+        <v>46196.91330880787</v>
+      </c>
       <c r="D92" s="5">
-        <v>46196.691612083334</v>
+        <v>46196.9133102662</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>273</v>
@@ -7422,10 +7429,10 @@
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I92" s="5">
         <v>46209</v>
@@ -7464,9 +7471,11 @@
       <c r="B93" s="8">
         <v>46132.63149714121</v>
       </c>
-      <c r="C93" s="9"/>
+      <c r="C93" s="8">
+        <v>46196.91331665509</v>
+      </c>
       <c r="D93" s="8">
-        <v>46196.69197650463</v>
+        <v>46196.91331809028</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>273</v>
@@ -7475,10 +7484,10 @@
         <v>26</v>
       </c>
       <c r="G93" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H93" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I93" s="8">
         <v>46209</v>
@@ -7517,9 +7526,11 @@
       <c r="B94" s="5">
         <v>46132.63150280093</v>
       </c>
-      <c r="C94" s="6"/>
+      <c r="C94" s="5">
+        <v>46196.9133241088</v>
+      </c>
       <c r="D94" s="5">
-        <v>46196.691969039355</v>
+        <v>46196.91332601852</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>273</v>
@@ -7528,10 +7539,10 @@
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I94" s="5">
         <v>46209</v>
@@ -7570,9 +7581,11 @@
       <c r="B95" s="8">
         <v>46132.63150895834</v>
       </c>
-      <c r="C95" s="9"/>
+      <c r="C95" s="8">
+        <v>46196.91332903935</v>
+      </c>
       <c r="D95" s="8">
-        <v>46196.69196927083</v>
+        <v>46196.91333064815</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>273</v>
@@ -7581,10 +7594,10 @@
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H95" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I95" s="8">
         <v>46209</v>
@@ -7623,9 +7636,11 @@
       <c r="B96" s="5">
         <v>46132.63151432871</v>
       </c>
-      <c r="C96" s="6"/>
+      <c r="C96" s="5">
+        <v>46196.91333642361</v>
+      </c>
       <c r="D96" s="5">
-        <v>46196.691969363426</v>
+        <v>46196.91333818287</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>273</v>
@@ -7634,10 +7649,10 @@
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I96" s="5">
         <v>46209</v>
@@ -7676,9 +7691,11 @@
       <c r="B97" s="8">
         <v>46132.631519525465</v>
       </c>
-      <c r="C97" s="9"/>
+      <c r="C97" s="8">
+        <v>46196.91334673611</v>
+      </c>
       <c r="D97" s="8">
-        <v>46196.69196891204</v>
+        <v>46196.91334849537</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>273</v>
@@ -7687,10 +7704,10 @@
         <v>26</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H97" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I97" s="8">
         <v>46209</v>
@@ -7729,9 +7746,11 @@
       <c r="B98" s="5">
         <v>46132.631524247685</v>
       </c>
-      <c r="C98" s="6"/>
+      <c r="C98" s="5">
+        <v>46196.913354247685</v>
+      </c>
       <c r="D98" s="5">
-        <v>46196.6919696875</v>
+        <v>46196.91335584491</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>273</v>
@@ -7740,10 +7759,10 @@
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I98" s="5">
         <v>46209</v>
@@ -7782,9 +7801,11 @@
       <c r="B99" s="8">
         <v>46132.63153150463</v>
       </c>
-      <c r="C99" s="9"/>
+      <c r="C99" s="8">
+        <v>46196.913358935184</v>
+      </c>
       <c r="D99" s="8">
-        <v>46196.69196924768</v>
+        <v>46196.913360879626</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>273</v>
@@ -7793,10 +7814,10 @@
         <v>26</v>
       </c>
       <c r="G99" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H99" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I99" s="8">
         <v>46209</v>
@@ -7835,9 +7856,11 @@
       <c r="B100" s="5">
         <v>46132.631539270835</v>
       </c>
-      <c r="C100" s="6"/>
+      <c r="C100" s="5">
+        <v>46196.91336784722</v>
+      </c>
       <c r="D100" s="5">
-        <v>46196.691753541665</v>
+        <v>46196.913369456015</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>273</v>
@@ -7846,10 +7869,10 @@
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I100" s="5">
         <v>46209</v>
@@ -7888,9 +7911,11 @@
       <c r="B101" s="8">
         <v>46132.63154616898</v>
       </c>
-      <c r="C101" s="9"/>
+      <c r="C101" s="8">
+        <v>46196.913381562495</v>
+      </c>
       <c r="D101" s="8">
-        <v>46196.691969189815</v>
+        <v>46196.91338305555</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>273</v>
@@ -7899,10 +7924,10 @@
         <v>26</v>
       </c>
       <c r="G101" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H101" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I101" s="8">
         <v>46209</v>
@@ -7941,9 +7966,11 @@
       <c r="B102" s="5">
         <v>46132.63155506944</v>
       </c>
-      <c r="C102" s="6"/>
+      <c r="C102" s="5">
+        <v>46196.913390381946</v>
+      </c>
       <c r="D102" s="5">
-        <v>46196.691969189815</v>
+        <v>46196.91339189815</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>273</v>
@@ -7952,10 +7979,10 @@
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I102" s="5">
         <v>46209</v>
@@ -7994,9 +8021,11 @@
       <c r="B103" s="8">
         <v>46132.63156422453</v>
       </c>
-      <c r="C103" s="9"/>
+      <c r="C103" s="8">
+        <v>46196.91339768519</v>
+      </c>
       <c r="D103" s="8">
-        <v>46196.691969224536</v>
+        <v>46196.91339939815</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>273</v>
@@ -8005,10 +8034,10 @@
         <v>26</v>
       </c>
       <c r="G103" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H103" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I103" s="8">
         <v>46209</v>
@@ -8049,7 +8078,7 @@
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46196.69196909722</v>
+        <v>46196.912235208336</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>273</v>
@@ -8058,10 +8087,10 @@
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I104" s="5">
         <v>46209</v>
@@ -8102,7 +8131,7 @@
       </c>
       <c r="C105" s="9"/>
       <c r="D105" s="8">
-        <v>46196.69196927083</v>
+        <v>46196.91224765046</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>174</v>
@@ -8111,10 +8140,10 @@
         <v>26</v>
       </c>
       <c r="G105" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H105" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I105" s="8">
         <v>46209</v>
@@ -8155,7 +8184,7 @@
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46196.69196938658</v>
+        <v>46196.91227103009</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>273</v>
@@ -8164,10 +8193,10 @@
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I106" s="5">
         <v>46209</v>
@@ -8550,7 +8579,7 @@
       </c>
       <c r="C113" s="9"/>
       <c r="D113" s="8">
-        <v>46134.56660114584</v>
+        <v>46196.913310648146</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>174</v>
@@ -8603,7 +8632,7 @@
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46134.56662060185</v>
+        <v>46196.91331428241</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>273</v>
@@ -8656,7 +8685,7 @@
       </c>
       <c r="C115" s="9"/>
       <c r="D115" s="8">
-        <v>46134.56666482639</v>
+        <v>46196.91332363426</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>273</v>
@@ -8709,7 +8738,7 @@
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46134.566719016206</v>
+        <v>46196.913330208336</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>174</v>
@@ -8762,7 +8791,7 @@
       </c>
       <c r="C117" s="9"/>
       <c r="D117" s="8">
-        <v>46134.56676865741</v>
+        <v>46196.91333635416</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>174</v>
@@ -8815,7 +8844,7 @@
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46134.56682832176</v>
+        <v>46196.91334300926</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>174</v>
@@ -8868,7 +8897,7 @@
       </c>
       <c r="C119" s="9"/>
       <c r="D119" s="8">
-        <v>46134.56685320602</v>
+        <v>46196.913353067124</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>273</v>
@@ -8921,7 +8950,7 @@
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46134.566876655095</v>
+        <v>46196.91335983796</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>174</v>
@@ -8974,7 +9003,7 @@
       </c>
       <c r="C121" s="9"/>
       <c r="D121" s="8">
-        <v>46134.56689625</v>
+        <v>46196.91336582176</v>
       </c>
       <c r="E121" s="9" t="s">
         <v>174</v>
@@ -9027,7 +9056,7 @@
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46134.566921770835</v>
+        <v>46196.913376006945</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>273</v>
@@ -9080,7 +9109,7 @@
       </c>
       <c r="C123" s="9"/>
       <c r="D123" s="8">
-        <v>46134.56694390046</v>
+        <v>46196.91338866898</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>174</v>
@@ -9133,7 +9162,7 @@
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46134.56697155093</v>
+        <v>46196.913398680554</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>174</v>
@@ -9186,7 +9215,7 @@
       </c>
       <c r="C125" s="9"/>
       <c r="D125" s="8">
-        <v>46134.56700997685</v>
+        <v>46196.91340450232</v>
       </c>
       <c r="E125" s="9" t="s">
         <v>174</v>
@@ -9239,7 +9268,7 @@
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46134.56703583333</v>
+        <v>46196.91288795139</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>174</v>
@@ -9292,7 +9321,7 @@
       </c>
       <c r="C127" s="9"/>
       <c r="D127" s="8">
-        <v>46134.567057974535</v>
+        <v>46196.91289704861</v>
       </c>
       <c r="E127" s="9" t="s">
         <v>174</v>
@@ -9345,7 +9374,7 @@
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46134.567080162036</v>
+        <v>46196.912913125</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>174</v>
@@ -9429,7 +9458,7 @@
         <v>304</v>
       </c>
       <c r="O129" s="9" t="s">
-        <v>330</v>
+        <v>241</v>
       </c>
       <c r="P129" s="9" t="s">
         <v>304</v>
@@ -9452,14 +9481,14 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B130" s="5">
         <v>46132.63296805556</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46191.91763167824</v>
+        <v>46196.91295196759</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>174</v>
@@ -9490,10 +9519,10 @@
         <v>329</v>
       </c>
       <c r="O130" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="P130" s="6" t="s">
         <v>332</v>
-      </c>
-      <c r="P130" s="6" t="s">
-        <v>333</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -9503,14 +9532,14 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B131" s="8">
         <v>46132.63297954861</v>
       </c>
       <c r="C131" s="9"/>
       <c r="D131" s="8">
-        <v>46191.917635034726</v>
+        <v>46196.91296126157</v>
       </c>
       <c r="E131" s="9" t="s">
         <v>174</v>
@@ -9541,10 +9570,10 @@
         <v>329</v>
       </c>
       <c r="O131" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="P131" s="9" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="Q131" s="9"/>
       <c r="R131" s="9"/>
@@ -9554,14 +9583,14 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B132" s="5">
         <v>46132.63298759259</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46191.917636886574</v>
+        <v>46196.91296799769</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>174</v>
@@ -9592,10 +9621,10 @@
         <v>329</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9605,14 +9634,14 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B133" s="8">
         <v>46132.63299327546</v>
       </c>
       <c r="C133" s="9"/>
       <c r="D133" s="8">
-        <v>46191.91761567129</v>
+        <v>46196.912974652776</v>
       </c>
       <c r="E133" s="9" t="s">
         <v>174</v>
@@ -9643,10 +9672,10 @@
         <v>329</v>
       </c>
       <c r="O133" s="9" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="P133" s="9" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="Q133" s="9"/>
       <c r="R133" s="9"/>
@@ -9656,14 +9685,14 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B134" s="5">
         <v>46132.63299994213</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46191.91763310185</v>
+        <v>46196.91298125</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>174</v>
@@ -9694,10 +9723,10 @@
         <v>329</v>
       </c>
       <c r="O134" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="P134" s="6" t="s">
         <v>332</v>
-      </c>
-      <c r="P134" s="6" t="s">
-        <v>333</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9707,14 +9736,14 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B135" s="8">
         <v>46132.63300702546</v>
       </c>
       <c r="C135" s="9"/>
       <c r="D135" s="8">
-        <v>46134.570414560185</v>
+        <v>46196.9129903125</v>
       </c>
       <c r="E135" s="9" t="s">
         <v>174</v>
@@ -9745,10 +9774,10 @@
         <v>329</v>
       </c>
       <c r="O135" s="9" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="P135" s="9" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="Q135" s="9"/>
       <c r="R135" s="9"/>
@@ -9758,14 +9787,14 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B136" s="5">
         <v>46132.633012708335</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46134.57045745371</v>
+        <v>46196.91300965278</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>174</v>
@@ -9796,10 +9825,10 @@
         <v>329</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9809,14 +9838,14 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B137" s="8">
         <v>46132.63302</v>
       </c>
       <c r="C137" s="9"/>
       <c r="D137" s="8">
-        <v>46134.57046664352</v>
+        <v>46196.91302356482</v>
       </c>
       <c r="E137" s="9" t="s">
         <v>174</v>
@@ -9847,10 +9876,10 @@
         <v>329</v>
       </c>
       <c r="O137" s="9" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="P137" s="9" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="Q137" s="9"/>
       <c r="R137" s="9"/>
@@ -9860,14 +9889,14 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B138" s="5">
         <v>46132.63302648148</v>
       </c>
       <c r="C138" s="6"/>
       <c r="D138" s="5">
-        <v>46134.57049269676</v>
+        <v>46196.91303289351</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>174</v>
@@ -9898,10 +9927,10 @@
         <v>329</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9911,14 +9940,14 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B139" s="8">
         <v>46132.633032858794</v>
       </c>
       <c r="C139" s="9"/>
       <c r="D139" s="8">
-        <v>46134.570514074076</v>
+        <v>46196.913042245375</v>
       </c>
       <c r="E139" s="9" t="s">
         <v>174</v>
@@ -9949,10 +9978,10 @@
         <v>329</v>
       </c>
       <c r="O139" s="9" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="P139" s="9" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="Q139" s="9"/>
       <c r="R139" s="9"/>
@@ -9962,14 +9991,14 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B140" s="5">
         <v>46132.633039409724</v>
       </c>
       <c r="C140" s="6"/>
       <c r="D140" s="5">
-        <v>46134.57054373843</v>
+        <v>46196.91306868056</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>174</v>
@@ -10000,10 +10029,10 @@
         <v>329</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -10013,14 +10042,14 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B141" s="8">
         <v>46132.633045821756</v>
       </c>
       <c r="C141" s="9"/>
       <c r="D141" s="8">
-        <v>46134.57057099537</v>
+        <v>46196.91308063657</v>
       </c>
       <c r="E141" s="9" t="s">
         <v>174</v>
@@ -10051,10 +10080,10 @@
         <v>329</v>
       </c>
       <c r="O141" s="9" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="P141" s="9" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="Q141" s="9"/>
       <c r="R141" s="9"/>
@@ -10064,14 +10093,14 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B142" s="5">
         <v>46132.633060057866</v>
       </c>
       <c r="C142" s="6"/>
       <c r="D142" s="5">
-        <v>46134.570602928245</v>
+        <v>46196.91309128472</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>174</v>
@@ -10102,10 +10131,10 @@
         <v>329</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -10115,14 +10144,14 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="7" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B143" s="8">
         <v>46132.633052986115</v>
       </c>
       <c r="C143" s="9"/>
       <c r="D143" s="8">
-        <v>46134.57068925926</v>
+        <v>46196.91310061343</v>
       </c>
       <c r="E143" s="9" t="s">
         <v>174</v>
@@ -10153,10 +10182,10 @@
         <v>329</v>
       </c>
       <c r="O143" s="9" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="P143" s="9" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="Q143" s="9"/>
       <c r="R143" s="9"/>
@@ -10166,14 +10195,14 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B144" s="5">
         <v>46132.63306579861</v>
       </c>
       <c r="C144" s="6"/>
       <c r="D144" s="5">
-        <v>46134.570725439815</v>
+        <v>46196.913109270834</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>174</v>
@@ -10204,10 +10233,10 @@
         <v>329</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -10217,14 +10246,14 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B145" s="8">
         <v>46132.633072337965</v>
       </c>
       <c r="C145" s="9"/>
       <c r="D145" s="8">
-        <v>46134.570759016206</v>
+        <v>46196.91313299768</v>
       </c>
       <c r="E145" s="9" t="s">
         <v>174</v>
@@ -10255,10 +10284,10 @@
         <v>329</v>
       </c>
       <c r="O145" s="9" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="P145" s="9" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="Q145" s="9"/>
       <c r="R145" s="9"/>
@@ -10268,7 +10297,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B146" s="5">
         <v>46132.58894553241</v>
@@ -10278,7 +10307,7 @@
         <v>46134.579158981476</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
@@ -10306,7 +10335,7 @@
         <v>304</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>330</v>
+        <v>241</v>
       </c>
       <c r="P146" s="6" t="s">
         <v>304</v>
@@ -10329,14 +10358,14 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="7" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B147" s="8">
         <v>46132.633140289356</v>
       </c>
       <c r="C147" s="9"/>
       <c r="D147" s="8">
-        <v>46157.54205099537</v>
+        <v>46196.91316769676</v>
       </c>
       <c r="E147" s="9" t="s">
         <v>174</v>
@@ -10364,13 +10393,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="9" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="O147" s="9" t="s">
+        <v>356</v>
+      </c>
+      <c r="P147" s="9" t="s">
         <v>357</v>
-      </c>
-      <c r="P147" s="9" t="s">
-        <v>358</v>
       </c>
       <c r="Q147" s="9"/>
       <c r="R147" s="9"/>
@@ -10380,14 +10409,14 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B148" s="5">
         <v>46132.63314908565</v>
       </c>
       <c r="C148" s="6"/>
       <c r="D148" s="5">
-        <v>46157.542051620374</v>
+        <v>46196.913174201385</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>174</v>
@@ -10415,13 +10444,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="Q148" s="6"/>
       <c r="R148" s="6"/>
@@ -10431,14 +10460,14 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="7" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B149" s="8">
         <v>46132.63315533564</v>
       </c>
       <c r="C149" s="9"/>
       <c r="D149" s="8">
-        <v>46157.54205224537</v>
+        <v>46196.91318321759</v>
       </c>
       <c r="E149" s="9" t="s">
         <v>174</v>
@@ -10466,13 +10495,13 @@
         <v>26</v>
       </c>
       <c r="N149" s="9" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="O149" s="9" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="P149" s="9" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="Q149" s="9"/>
       <c r="R149" s="9"/>
@@ -10482,14 +10511,14 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B150" s="5">
         <v>46132.63316266204</v>
       </c>
       <c r="C150" s="6"/>
       <c r="D150" s="5">
-        <v>46157.54205297454</v>
+        <v>46196.91318989583</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>174</v>
@@ -10517,13 +10546,13 @@
         <v>26</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="O150" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="P150" s="6" t="s">
         <v>357</v>
-      </c>
-      <c r="P150" s="6" t="s">
-        <v>358</v>
       </c>
       <c r="Q150" s="6"/>
       <c r="R150" s="6"/>
@@ -10533,14 +10562,14 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="7" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B151" s="8">
         <v>46132.6331690625</v>
       </c>
       <c r="C151" s="9"/>
       <c r="D151" s="8">
-        <v>46157.54205361111</v>
+        <v>46196.913196319445</v>
       </c>
       <c r="E151" s="9" t="s">
         <v>174</v>
@@ -10568,13 +10597,13 @@
         <v>26</v>
       </c>
       <c r="N151" s="9" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="O151" s="9" t="s">
+        <v>356</v>
+      </c>
+      <c r="P151" s="9" t="s">
         <v>357</v>
-      </c>
-      <c r="P151" s="9" t="s">
-        <v>358</v>
       </c>
       <c r="Q151" s="9"/>
       <c r="R151" s="9"/>
@@ -10584,14 +10613,14 @@
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B152" s="5">
         <v>46132.63317594907</v>
       </c>
       <c r="C152" s="6"/>
       <c r="D152" s="5">
-        <v>46157.542054247686</v>
+        <v>46196.913203275464</v>
       </c>
       <c r="E152" s="6" t="s">
         <v>174</v>
@@ -10619,13 +10648,13 @@
         <v>26</v>
       </c>
       <c r="N152" s="6" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="O152" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="P152" s="6" t="s">
         <v>357</v>
-      </c>
-      <c r="P152" s="6" t="s">
-        <v>358</v>
       </c>
       <c r="Q152" s="6"/>
       <c r="R152" s="6"/>
@@ -10635,14 +10664,14 @@
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" s="7" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B153" s="8">
         <v>46132.633188506945</v>
       </c>
       <c r="C153" s="9"/>
       <c r="D153" s="8">
-        <v>46157.542054826394</v>
+        <v>46196.91320924769</v>
       </c>
       <c r="E153" s="9" t="s">
         <v>174</v>
@@ -10670,13 +10699,13 @@
         <v>26</v>
       </c>
       <c r="N153" s="9" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="O153" s="9" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="P153" s="9" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="Q153" s="9"/>
       <c r="R153" s="9"/>
@@ -10686,14 +10715,14 @@
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B154" s="5">
         <v>46132.63318159722</v>
       </c>
       <c r="C154" s="6"/>
       <c r="D154" s="5">
-        <v>46157.542055439815</v>
+        <v>46196.9132163426</v>
       </c>
       <c r="E154" s="6" t="s">
         <v>174</v>
@@ -10721,13 +10750,13 @@
         <v>26</v>
       </c>
       <c r="N154" s="6" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="O154" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="P154" s="6" t="s">
         <v>357</v>
-      </c>
-      <c r="P154" s="6" t="s">
-        <v>358</v>
       </c>
       <c r="Q154" s="6"/>
       <c r="R154" s="6"/>
@@ -10737,14 +10766,14 @@
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155" s="7" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B155" s="8">
         <v>46132.63319443287</v>
       </c>
       <c r="C155" s="9"/>
       <c r="D155" s="8">
-        <v>46157.54205606482</v>
+        <v>46196.913238333334</v>
       </c>
       <c r="E155" s="9" t="s">
         <v>174</v>
@@ -10772,13 +10801,13 @@
         <v>26</v>
       </c>
       <c r="N155" s="9" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="O155" s="9" t="s">
+        <v>356</v>
+      </c>
+      <c r="P155" s="9" t="s">
         <v>357</v>
-      </c>
-      <c r="P155" s="9" t="s">
-        <v>358</v>
       </c>
       <c r="Q155" s="9"/>
       <c r="R155" s="9"/>
@@ -10788,14 +10817,14 @@
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B156" s="5">
         <v>46132.63320815972</v>
       </c>
       <c r="C156" s="6"/>
       <c r="D156" s="5">
-        <v>46157.54205662037</v>
+        <v>46196.91324483797</v>
       </c>
       <c r="E156" s="6" t="s">
         <v>174</v>
@@ -10823,13 +10852,13 @@
         <v>26</v>
       </c>
       <c r="N156" s="6" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="O156" s="6" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="P156" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="Q156" s="6"/>
       <c r="R156" s="6"/>
@@ -10839,14 +10868,14 @@
     </row>
     <row r="157" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A157" s="7" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B157" s="8">
         <v>46132.63320082176</v>
       </c>
       <c r="C157" s="9"/>
       <c r="D157" s="8">
-        <v>46157.54205740741</v>
+        <v>46196.91325182871</v>
       </c>
       <c r="E157" s="9" t="s">
         <v>174</v>
@@ -10874,13 +10903,13 @@
         <v>26</v>
       </c>
       <c r="N157" s="9" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="O157" s="9" t="s">
+        <v>356</v>
+      </c>
+      <c r="P157" s="9" t="s">
         <v>357</v>
-      </c>
-      <c r="P157" s="9" t="s">
-        <v>358</v>
       </c>
       <c r="Q157" s="9"/>
       <c r="R157" s="9"/>
@@ -10890,14 +10919,14 @@
     </row>
     <row r="158" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B158" s="5">
         <v>46132.63322097222</v>
       </c>
       <c r="C158" s="6"/>
       <c r="D158" s="5">
-        <v>46157.54205797454</v>
+        <v>46196.91325798611</v>
       </c>
       <c r="E158" s="6" t="s">
         <v>174</v>
@@ -10925,13 +10954,13 @@
         <v>26</v>
       </c>
       <c r="N158" s="6" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="O158" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="P158" s="6" t="s">
         <v>357</v>
-      </c>
-      <c r="P158" s="6" t="s">
-        <v>358</v>
       </c>
       <c r="Q158" s="6"/>
       <c r="R158" s="6"/>
@@ -10941,14 +10970,14 @@
     </row>
     <row r="159" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A159" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B159" s="8">
         <v>46132.6332150463</v>
       </c>
       <c r="C159" s="9"/>
       <c r="D159" s="8">
-        <v>46157.54205855324</v>
+        <v>46196.91326434028</v>
       </c>
       <c r="E159" s="9" t="s">
         <v>174</v>
@@ -10976,13 +11005,13 @@
         <v>26</v>
       </c>
       <c r="N159" s="9" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="O159" s="9" t="s">
+        <v>356</v>
+      </c>
+      <c r="P159" s="9" t="s">
         <v>357</v>
-      </c>
-      <c r="P159" s="9" t="s">
-        <v>358</v>
       </c>
       <c r="Q159" s="9"/>
       <c r="R159" s="9"/>
@@ -10992,14 +11021,14 @@
     </row>
     <row r="160" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B160" s="5">
         <v>46132.63322802083</v>
       </c>
       <c r="C160" s="6"/>
       <c r="D160" s="5">
-        <v>46157.542059155094</v>
+        <v>46196.91327159722</v>
       </c>
       <c r="E160" s="6" t="s">
         <v>174</v>
@@ -11027,13 +11056,13 @@
         <v>26</v>
       </c>
       <c r="N160" s="6" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="O160" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="P160" s="6" t="s">
         <v>357</v>
-      </c>
-      <c r="P160" s="6" t="s">
-        <v>358</v>
       </c>
       <c r="Q160" s="6"/>
       <c r="R160" s="6"/>
@@ -11043,14 +11072,14 @@
     </row>
     <row r="161" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A161" s="7" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B161" s="8">
         <v>46132.63323575231</v>
       </c>
       <c r="C161" s="9"/>
       <c r="D161" s="8">
-        <v>46157.54205975695</v>
+        <v>46196.913280625</v>
       </c>
       <c r="E161" s="9" t="s">
         <v>174</v>
@@ -11078,13 +11107,13 @@
         <v>26</v>
       </c>
       <c r="N161" s="9" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="O161" s="9" t="s">
+        <v>356</v>
+      </c>
+      <c r="P161" s="9" t="s">
         <v>357</v>
-      </c>
-      <c r="P161" s="9" t="s">
-        <v>358</v>
       </c>
       <c r="Q161" s="9"/>
       <c r="R161" s="9"/>
@@ -11094,14 +11123,14 @@
     </row>
     <row r="162" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B162" s="5">
         <v>46132.633244004624</v>
       </c>
       <c r="C162" s="6"/>
       <c r="D162" s="5">
-        <v>46157.54206041667</v>
+        <v>46196.91329380787</v>
       </c>
       <c r="E162" s="6" t="s">
         <v>174</v>
@@ -11129,13 +11158,13 @@
         <v>26</v>
       </c>
       <c r="N162" s="6" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="O162" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="P162" s="6" t="s">
         <v>357</v>
-      </c>
-      <c r="P162" s="6" t="s">
-        <v>358</v>
       </c>
       <c r="Q162" s="6"/>
       <c r="R162" s="6"/>
@@ -11145,7 +11174,7 @@
     </row>
     <row r="163" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A163" s="7" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B163" s="8">
         <v>46132.58893171296</v>
@@ -11155,7 +11184,7 @@
         <v>46134.57915975695</v>
       </c>
       <c r="E163" s="9" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="F163" s="9" t="s">
         <v>26</v>
@@ -11183,7 +11212,7 @@
         <v>304</v>
       </c>
       <c r="O163" s="9" t="s">
-        <v>330</v>
+        <v>241</v>
       </c>
       <c r="P163" s="9" t="s">
         <v>304</v>
@@ -11206,14 +11235,14 @@
     </row>
     <row r="164" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B164" s="5">
         <v>46132.632804305555</v>
       </c>
       <c r="C164" s="6"/>
       <c r="D164" s="5">
-        <v>46191.91763888889</v>
+        <v>46196.91332662037</v>
       </c>
       <c r="E164" s="6" t="s">
         <v>174</v>
@@ -11241,13 +11270,13 @@
         <v>26</v>
       </c>
       <c r="N164" s="6" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="O164" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="P164" s="6" t="s">
         <v>378</v>
-      </c>
-      <c r="P164" s="6" t="s">
-        <v>379</v>
       </c>
       <c r="Q164" s="6"/>
       <c r="R164" s="6"/>
@@ -11257,14 +11286,14 @@
     </row>
     <row r="165" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A165" s="7" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B165" s="8">
         <v>46132.632815624995</v>
       </c>
       <c r="C165" s="9"/>
       <c r="D165" s="8">
-        <v>46191.91763082176</v>
+        <v>46196.91333607639</v>
       </c>
       <c r="E165" s="9" t="s">
         <v>174</v>
@@ -11292,13 +11321,13 @@
         <v>26</v>
       </c>
       <c r="N165" s="9" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="O165" s="9" t="s">
+        <v>377</v>
+      </c>
+      <c r="P165" s="9" t="s">
         <v>378</v>
-      </c>
-      <c r="P165" s="9" t="s">
-        <v>379</v>
       </c>
       <c r="Q165" s="9"/>
       <c r="R165" s="9"/>
@@ -11308,14 +11337,14 @@
     </row>
     <row r="166" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B166" s="5">
         <v>46132.63282284723</v>
       </c>
       <c r="C166" s="6"/>
       <c r="D166" s="5">
-        <v>46134.57344920139</v>
+        <v>46196.913343078704</v>
       </c>
       <c r="E166" s="6" t="s">
         <v>174</v>
@@ -11343,13 +11372,13 @@
         <v>26</v>
       </c>
       <c r="N166" s="6" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="O166" s="6" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="P166" s="6" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="Q166" s="6"/>
       <c r="R166" s="6"/>
@@ -11359,14 +11388,14 @@
     </row>
     <row r="167" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A167" s="7" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B167" s="8">
         <v>46132.63283236111</v>
       </c>
       <c r="C167" s="9"/>
       <c r="D167" s="8">
-        <v>46134.57348356482</v>
+        <v>46196.913348946764</v>
       </c>
       <c r="E167" s="9" t="s">
         <v>174</v>
@@ -11394,13 +11423,13 @@
         <v>26</v>
       </c>
       <c r="N167" s="9" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="O167" s="9" t="s">
         <v>174</v>
       </c>
       <c r="P167" s="9" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="Q167" s="9"/>
       <c r="R167" s="9"/>
@@ -11410,14 +11439,14 @@
     </row>
     <row r="168" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B168" s="5">
         <v>46132.632837384255</v>
       </c>
       <c r="C168" s="6"/>
       <c r="D168" s="5">
-        <v>46134.57356908565</v>
+        <v>46196.9133558912</v>
       </c>
       <c r="E168" s="6" t="s">
         <v>174</v>
@@ -11445,13 +11474,13 @@
         <v>26</v>
       </c>
       <c r="N168" s="6" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="O168" s="6" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="P168" s="6" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="Q168" s="6"/>
       <c r="R168" s="6"/>
@@ -11461,14 +11490,14 @@
     </row>
     <row r="169" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A169" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B169" s="8">
         <v>46132.63284362269</v>
       </c>
       <c r="C169" s="9"/>
       <c r="D169" s="8">
-        <v>46134.57360363426</v>
+        <v>46196.91336501157</v>
       </c>
       <c r="E169" s="9" t="s">
         <v>174</v>
@@ -11496,13 +11525,13 @@
         <v>26</v>
       </c>
       <c r="N169" s="9" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="O169" s="9" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="P169" s="9" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="Q169" s="9"/>
       <c r="R169" s="9"/>
@@ -11512,14 +11541,14 @@
     </row>
     <row r="170" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B170" s="5">
         <v>46132.63284975695</v>
       </c>
       <c r="C170" s="6"/>
       <c r="D170" s="5">
-        <v>46134.57364912037</v>
+        <v>46196.91338157408</v>
       </c>
       <c r="E170" s="6" t="s">
         <v>174</v>
@@ -11547,13 +11576,13 @@
         <v>26</v>
       </c>
       <c r="N170" s="6" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="O170" s="6" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="P170" s="6" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="Q170" s="6"/>
       <c r="R170" s="6"/>
@@ -11563,14 +11592,14 @@
     </row>
     <row r="171" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A171" s="7" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B171" s="8">
         <v>46132.63286226852</v>
       </c>
       <c r="C171" s="9"/>
       <c r="D171" s="8">
-        <v>46134.573658043984</v>
+        <v>46196.913389050926</v>
       </c>
       <c r="E171" s="9" t="s">
         <v>174</v>
@@ -11598,13 +11627,13 @@
         <v>26</v>
       </c>
       <c r="N171" s="9" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="O171" s="9" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="P171" s="9" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="Q171" s="9"/>
       <c r="R171" s="9"/>
@@ -11614,14 +11643,14 @@
     </row>
     <row r="172" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A172" s="4" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B172" s="5">
         <v>46132.63285675926</v>
       </c>
       <c r="C172" s="6"/>
       <c r="D172" s="5">
-        <v>46134.57368267361</v>
+        <v>46196.91340076389</v>
       </c>
       <c r="E172" s="6" t="s">
         <v>174</v>
@@ -11649,13 +11678,13 @@
         <v>26</v>
       </c>
       <c r="N172" s="6" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="O172" s="6" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="P172" s="6" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="Q172" s="6"/>
       <c r="R172" s="6"/>
@@ -11665,14 +11694,14 @@
     </row>
     <row r="173" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A173" s="7" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B173" s="8">
         <v>46132.63286828704</v>
       </c>
       <c r="C173" s="9"/>
       <c r="D173" s="8">
-        <v>46134.57371648148</v>
+        <v>46196.91340517361</v>
       </c>
       <c r="E173" s="9" t="s">
         <v>174</v>
@@ -11700,13 +11729,13 @@
         <v>26</v>
       </c>
       <c r="N173" s="9" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="O173" s="9" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="P173" s="9" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="Q173" s="9"/>
       <c r="R173" s="9"/>
@@ -11716,14 +11745,14 @@
     </row>
     <row r="174" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A174" s="4" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B174" s="5">
         <v>46132.63287412037</v>
       </c>
       <c r="C174" s="6"/>
       <c r="D174" s="5">
-        <v>46134.57373912037</v>
+        <v>46196.91341680556</v>
       </c>
       <c r="E174" s="6" t="s">
         <v>174</v>
@@ -11751,13 +11780,13 @@
         <v>26</v>
       </c>
       <c r="N174" s="6" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="O174" s="6" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="P174" s="6" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="Q174" s="6"/>
       <c r="R174" s="6"/>
@@ -11767,14 +11796,14 @@
     </row>
     <row r="175" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A175" s="7" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B175" s="8">
         <v>46132.63288133102</v>
       </c>
       <c r="C175" s="9"/>
       <c r="D175" s="8">
-        <v>46134.57376193287</v>
+        <v>46196.91342331019</v>
       </c>
       <c r="E175" s="9" t="s">
         <v>174</v>
@@ -11802,13 +11831,13 @@
         <v>26</v>
       </c>
       <c r="N175" s="9" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="O175" s="9" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="P175" s="9" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="Q175" s="9"/>
       <c r="R175" s="9"/>
@@ -11818,14 +11847,14 @@
     </row>
     <row r="176" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A176" s="4" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B176" s="5">
         <v>46132.63288800926</v>
       </c>
       <c r="C176" s="6"/>
       <c r="D176" s="5">
-        <v>46134.57378160879</v>
+        <v>46196.913429849534</v>
       </c>
       <c r="E176" s="6" t="s">
         <v>174</v>
@@ -11853,13 +11882,13 @@
         <v>26</v>
       </c>
       <c r="N176" s="6" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="O176" s="6" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="P176" s="6" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="Q176" s="6"/>
       <c r="R176" s="6"/>
@@ -11869,14 +11898,14 @@
     </row>
     <row r="177" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A177" s="7" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B177" s="8">
         <v>46132.63289421296</v>
       </c>
       <c r="C177" s="9"/>
       <c r="D177" s="8">
-        <v>46134.57379556713</v>
+        <v>46196.91343652778</v>
       </c>
       <c r="E177" s="9" t="s">
         <v>174</v>
@@ -11904,13 +11933,13 @@
         <v>26</v>
       </c>
       <c r="N177" s="9" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="O177" s="9" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="P177" s="9" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="Q177" s="9"/>
       <c r="R177" s="9"/>
@@ -11920,14 +11949,14 @@
     </row>
     <row r="178" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A178" s="4" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B178" s="5">
         <v>46132.63290028935</v>
       </c>
       <c r="C178" s="6"/>
       <c r="D178" s="5">
-        <v>46134.57383894676</v>
+        <v>46196.91344907407</v>
       </c>
       <c r="E178" s="6" t="s">
         <v>174</v>
@@ -11955,13 +11984,13 @@
         <v>26</v>
       </c>
       <c r="N178" s="6" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="O178" s="6" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="P178" s="6" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="Q178" s="6"/>
       <c r="R178" s="6"/>
@@ -11971,14 +12000,14 @@
     </row>
     <row r="179" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A179" s="7" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B179" s="8">
         <v>46132.632907719904</v>
       </c>
       <c r="C179" s="9"/>
       <c r="D179" s="8">
-        <v>46134.5738778588</v>
+        <v>46196.91346278935</v>
       </c>
       <c r="E179" s="9" t="s">
         <v>174</v>
@@ -12006,13 +12035,13 @@
         <v>26</v>
       </c>
       <c r="N179" s="9" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="O179" s="9" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="P179" s="9" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="Q179" s="9"/>
       <c r="R179" s="9"/>
@@ -12022,7 +12051,7 @@
     </row>
     <row r="180" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A180" s="4" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B180" s="5">
         <v>46132.58895258102</v>
@@ -12032,7 +12061,7 @@
         <v>46134.579160567126</v>
       </c>
       <c r="E180" s="6" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="F180" s="6" t="s">
         <v>26</v>
@@ -12060,7 +12089,7 @@
         <v>304</v>
       </c>
       <c r="O180" s="6" t="s">
-        <v>330</v>
+        <v>241</v>
       </c>
       <c r="P180" s="6" t="s">
         <v>304</v>
@@ -12083,14 +12112,14 @@
     </row>
     <row r="181" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A181" s="7" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B181" s="8">
         <v>46132.63330006944</v>
       </c>
       <c r="C181" s="9"/>
       <c r="D181" s="8">
-        <v>46134.576304421294</v>
+        <v>46196.91349186342</v>
       </c>
       <c r="E181" s="9" t="s">
         <v>174</v>
@@ -12118,13 +12147,13 @@
         <v>26</v>
       </c>
       <c r="N181" s="9" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="O181" s="9" t="s">
+        <v>399</v>
+      </c>
+      <c r="P181" s="9" t="s">
         <v>400</v>
-      </c>
-      <c r="P181" s="9" t="s">
-        <v>401</v>
       </c>
       <c r="Q181" s="9"/>
       <c r="R181" s="9"/>
@@ -12134,14 +12163,14 @@
     </row>
     <row r="182" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A182" s="4" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B182" s="5">
         <v>46132.63330984954</v>
       </c>
       <c r="C182" s="6"/>
       <c r="D182" s="5">
-        <v>46134.576334467594</v>
+        <v>46196.913516817134</v>
       </c>
       <c r="E182" s="6" t="s">
         <v>174</v>
@@ -12169,13 +12198,13 @@
         <v>26</v>
       </c>
       <c r="N182" s="6" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="O182" s="6" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="P182" s="6" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="Q182" s="6"/>
       <c r="R182" s="6"/>
@@ -12185,14 +12214,14 @@
     </row>
     <row r="183" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A183" s="7" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B183" s="8">
         <v>46132.633316377316</v>
       </c>
       <c r="C183" s="9"/>
       <c r="D183" s="8">
-        <v>46134.57635555556</v>
+        <v>46196.913533425926</v>
       </c>
       <c r="E183" s="9" t="s">
         <v>174</v>
@@ -12220,13 +12249,13 @@
         <v>26</v>
       </c>
       <c r="N183" s="9" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="O183" s="9" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="P183" s="9" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="Q183" s="9"/>
       <c r="R183" s="9"/>
@@ -12236,14 +12265,14 @@
     </row>
     <row r="184" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A184" s="4" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B184" s="5">
         <v>46132.63332333333</v>
       </c>
       <c r="C184" s="6"/>
       <c r="D184" s="5">
-        <v>46134.57637689815</v>
+        <v>46196.91352673611</v>
       </c>
       <c r="E184" s="6" t="s">
         <v>174</v>
@@ -12271,13 +12300,13 @@
         <v>26</v>
       </c>
       <c r="N184" s="6" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="O184" s="6" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="P184" s="6" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="Q184" s="6"/>
       <c r="R184" s="6"/>
@@ -12287,14 +12316,14 @@
     </row>
     <row r="185" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A185" s="7" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B185" s="8">
         <v>46132.63333568287</v>
       </c>
       <c r="C185" s="9"/>
       <c r="D185" s="8">
-        <v>46134.57641616898</v>
+        <v>46196.91354314815</v>
       </c>
       <c r="E185" s="9" t="s">
         <v>174</v>
@@ -12322,13 +12351,13 @@
         <v>26</v>
       </c>
       <c r="N185" s="9" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="O185" s="9" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="P185" s="9" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="Q185" s="9"/>
       <c r="R185" s="9"/>
@@ -12338,14 +12367,14 @@
     </row>
     <row r="186" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A186" s="4" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B186" s="5">
         <v>46132.633329282406</v>
       </c>
       <c r="C186" s="6"/>
       <c r="D186" s="5">
-        <v>46134.576444085644</v>
+        <v>46196.913549942125</v>
       </c>
       <c r="E186" s="6" t="s">
         <v>174</v>
@@ -12373,13 +12402,13 @@
         <v>26</v>
       </c>
       <c r="N186" s="6" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="O186" s="6" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="P186" s="6" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="Q186" s="6"/>
       <c r="R186" s="6"/>
@@ -12389,14 +12418,14 @@
     </row>
     <row r="187" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A187" s="7" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B187" s="8">
         <v>46132.63334925926</v>
       </c>
       <c r="C187" s="9"/>
       <c r="D187" s="8">
-        <v>46134.57648004629</v>
+        <v>46196.91355706019</v>
       </c>
       <c r="E187" s="9" t="s">
         <v>174</v>
@@ -12424,13 +12453,13 @@
         <v>26</v>
       </c>
       <c r="N187" s="9" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="O187" s="9" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="P187" s="9" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="Q187" s="9"/>
       <c r="R187" s="9"/>
@@ -12440,14 +12469,14 @@
     </row>
     <row r="188" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A188" s="4" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B188" s="5">
         <v>46132.633353321755</v>
       </c>
       <c r="C188" s="6"/>
       <c r="D188" s="5">
-        <v>46134.57650412037</v>
+        <v>46196.91356591435</v>
       </c>
       <c r="E188" s="6" t="s">
         <v>174</v>
@@ -12475,13 +12504,13 @@
         <v>26</v>
       </c>
       <c r="N188" s="6" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="O188" s="6" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="P188" s="6" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="Q188" s="6"/>
       <c r="R188" s="6"/>
@@ -12491,14 +12520,14 @@
     </row>
     <row r="189" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A189" s="7" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B189" s="8">
         <v>46132.63336115741</v>
       </c>
       <c r="C189" s="9"/>
       <c r="D189" s="8">
-        <v>46134.5765267824</v>
+        <v>46196.91357502315</v>
       </c>
       <c r="E189" s="9" t="s">
         <v>174</v>
@@ -12526,13 +12555,13 @@
         <v>26</v>
       </c>
       <c r="N189" s="9" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="O189" s="9" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="P189" s="9" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="Q189" s="9"/>
       <c r="R189" s="9"/>
@@ -12542,14 +12571,14 @@
     </row>
     <row r="190" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B190" s="5">
         <v>46132.6333661574</v>
       </c>
       <c r="C190" s="6"/>
       <c r="D190" s="5">
-        <v>46134.57655197917</v>
+        <v>46196.91357896991</v>
       </c>
       <c r="E190" s="6" t="s">
         <v>174</v>
@@ -12577,13 +12606,13 @@
         <v>26</v>
       </c>
       <c r="N190" s="6" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="O190" s="6" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="P190" s="6" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="Q190" s="6"/>
       <c r="R190" s="6"/>
@@ -12593,14 +12622,14 @@
     </row>
     <row r="191" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A191" s="7" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B191" s="8">
         <v>46132.633375046295</v>
       </c>
       <c r="C191" s="9"/>
       <c r="D191" s="8">
-        <v>46134.57660518518</v>
+        <v>46196.91359459491</v>
       </c>
       <c r="E191" s="9" t="s">
         <v>174</v>
@@ -12628,13 +12657,13 @@
         <v>26</v>
       </c>
       <c r="N191" s="9" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="O191" s="9" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="P191" s="9" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="Q191" s="9"/>
       <c r="R191" s="9"/>
@@ -12644,14 +12673,14 @@
     </row>
     <row r="192" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B192" s="5">
         <v>46132.63337950232</v>
       </c>
       <c r="C192" s="6"/>
       <c r="D192" s="5">
-        <v>46134.57663512732</v>
+        <v>46196.913601423614</v>
       </c>
       <c r="E192" s="6" t="s">
         <v>174</v>
@@ -12679,13 +12708,13 @@
         <v>26</v>
       </c>
       <c r="N192" s="6" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="O192" s="6" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="P192" s="6" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="Q192" s="6"/>
       <c r="R192" s="6"/>
@@ -12695,14 +12724,14 @@
     </row>
     <row r="193" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A193" s="7" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B193" s="8">
         <v>46132.63338666667</v>
       </c>
       <c r="C193" s="9"/>
       <c r="D193" s="8">
-        <v>46134.576659004626</v>
+        <v>46196.91361079861</v>
       </c>
       <c r="E193" s="9" t="s">
         <v>174</v>
@@ -12730,13 +12759,13 @@
         <v>26</v>
       </c>
       <c r="N193" s="9" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="O193" s="9" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="P193" s="9" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="Q193" s="9"/>
       <c r="R193" s="9"/>
@@ -12746,14 +12775,14 @@
     </row>
     <row r="194" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B194" s="5">
         <v>46132.63339375</v>
       </c>
       <c r="C194" s="6"/>
       <c r="D194" s="5">
-        <v>46134.57668400463</v>
+        <v>46196.91361791667</v>
       </c>
       <c r="E194" s="6" t="s">
         <v>174</v>
@@ -12781,13 +12810,13 @@
         <v>26</v>
       </c>
       <c r="N194" s="6" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="O194" s="6" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="P194" s="6" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="Q194" s="6"/>
       <c r="R194" s="6"/>
@@ -12797,14 +12826,14 @@
     </row>
     <row r="195" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A195" s="7" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B195" s="8">
         <v>46132.63339872685</v>
       </c>
       <c r="C195" s="9"/>
       <c r="D195" s="8">
-        <v>46134.576709444445</v>
+        <v>46196.91362990741</v>
       </c>
       <c r="E195" s="9" t="s">
         <v>174</v>
@@ -12832,13 +12861,13 @@
         <v>26</v>
       </c>
       <c r="N195" s="9" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="O195" s="9" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="P195" s="9" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="Q195" s="9"/>
       <c r="R195" s="9"/>
@@ -12848,14 +12877,14 @@
     </row>
     <row r="196" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B196" s="5">
         <v>46132.633404085645</v>
       </c>
       <c r="C196" s="6"/>
       <c r="D196" s="5">
-        <v>46134.57676763889</v>
+        <v>46196.91364925926</v>
       </c>
       <c r="E196" s="6" t="s">
         <v>174</v>
@@ -12883,13 +12912,13 @@
         <v>26</v>
       </c>
       <c r="N196" s="6" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="O196" s="6" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="P196" s="6" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="Q196" s="6"/>
       <c r="R196" s="6"/>
@@ -12899,7 +12928,7 @@
     </row>
     <row r="197" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A197" s="7" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B197" s="8">
         <v>46132.58900565973</v>
@@ -12909,7 +12938,7 @@
         <v>46134.579161331014</v>
       </c>
       <c r="E197" s="9" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="F197" s="9" t="s">
         <v>26</v>
@@ -12937,10 +12966,10 @@
         <v>304</v>
       </c>
       <c r="O197" s="9" t="s">
+        <v>433</v>
+      </c>
+      <c r="P197" s="9" t="s">
         <v>434</v>
-      </c>
-      <c r="P197" s="9" t="s">
-        <v>435</v>
       </c>
       <c r="Q197" s="8">
         <v>46225</v>
@@ -12960,14 +12989,14 @@
     </row>
     <row r="198" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A198" s="4" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B198" s="5">
         <v>46132.6334534375</v>
       </c>
       <c r="C198" s="6"/>
       <c r="D198" s="5">
-        <v>46134.58026418982</v>
+        <v>46196.91368532408</v>
       </c>
       <c r="E198" s="6" t="s">
         <v>174</v>
@@ -12995,13 +13024,13 @@
         <v>26</v>
       </c>
       <c r="N198" s="6" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="O198" s="6" t="s">
         <v>173</v>
       </c>
       <c r="P198" s="6" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="Q198" s="6"/>
       <c r="R198" s="6"/>
@@ -13011,14 +13040,14 @@
     </row>
     <row r="199" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A199" s="7" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B199" s="8">
         <v>46132.633462025464</v>
       </c>
       <c r="C199" s="9"/>
       <c r="D199" s="8">
-        <v>46134.578232071755</v>
+        <v>46196.91369168981</v>
       </c>
       <c r="E199" s="9" t="s">
         <v>174</v>
@@ -13046,13 +13075,13 @@
         <v>26</v>
       </c>
       <c r="N199" s="9" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="O199" s="9" t="s">
         <v>177</v>
       </c>
       <c r="P199" s="9" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="Q199" s="9"/>
       <c r="R199" s="9"/>
@@ -13062,14 +13091,14 @@
     </row>
     <row r="200" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A200" s="4" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B200" s="5">
         <v>46132.633468622684</v>
       </c>
       <c r="C200" s="6"/>
       <c r="D200" s="5">
-        <v>46134.57826916667</v>
+        <v>46196.91369818287</v>
       </c>
       <c r="E200" s="6" t="s">
         <v>174</v>
@@ -13097,13 +13126,13 @@
         <v>26</v>
       </c>
       <c r="N200" s="6" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="O200" s="6" t="s">
         <v>180</v>
       </c>
       <c r="P200" s="6" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="Q200" s="6"/>
       <c r="R200" s="6"/>
@@ -13113,14 +13142,14 @@
     </row>
     <row r="201" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A201" s="7" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B201" s="8">
         <v>46132.63347502315</v>
       </c>
       <c r="C201" s="9"/>
       <c r="D201" s="8">
-        <v>46134.578289375</v>
+        <v>46196.91371429398</v>
       </c>
       <c r="E201" s="9" t="s">
         <v>174</v>
@@ -13148,13 +13177,13 @@
         <v>26</v>
       </c>
       <c r="N201" s="9" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="O201" s="9" t="s">
         <v>182</v>
       </c>
       <c r="P201" s="9" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="Q201" s="9"/>
       <c r="R201" s="9"/>
@@ -13164,14 +13193,14 @@
     </row>
     <row r="202" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A202" s="4" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B202" s="5">
         <v>46132.63348070602</v>
       </c>
       <c r="C202" s="6"/>
       <c r="D202" s="5">
-        <v>46134.57829755787</v>
+        <v>46196.91372087963</v>
       </c>
       <c r="E202" s="6" t="s">
         <v>174</v>
@@ -13199,13 +13228,13 @@
         <v>26</v>
       </c>
       <c r="N202" s="6" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="O202" s="6" t="s">
         <v>184</v>
       </c>
       <c r="P202" s="6" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="Q202" s="6"/>
       <c r="R202" s="6"/>
@@ -13215,14 +13244,14 @@
     </row>
     <row r="203" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A203" s="7" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B203" s="8">
         <v>46132.63348662037</v>
       </c>
       <c r="C203" s="9"/>
       <c r="D203" s="8">
-        <v>46134.57832886574</v>
+        <v>46196.91372986111</v>
       </c>
       <c r="E203" s="9" t="s">
         <v>174</v>
@@ -13250,13 +13279,13 @@
         <v>26</v>
       </c>
       <c r="N203" s="9" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="O203" s="9" t="s">
         <v>186</v>
       </c>
       <c r="P203" s="9" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="Q203" s="9"/>
       <c r="R203" s="9"/>
@@ -13266,14 +13295,14 @@
     </row>
     <row r="204" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A204" s="4" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B204" s="5">
         <v>46132.63349295139</v>
       </c>
       <c r="C204" s="6"/>
       <c r="D204" s="5">
-        <v>46134.57836459491</v>
+        <v>46196.91373467592</v>
       </c>
       <c r="E204" s="6" t="s">
         <v>174</v>
@@ -13301,13 +13330,13 @@
         <v>26</v>
       </c>
       <c r="N204" s="6" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="O204" s="6" t="s">
         <v>188</v>
       </c>
       <c r="P204" s="6" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="Q204" s="6"/>
       <c r="R204" s="6"/>
@@ -13324,7 +13353,7 @@
       </c>
       <c r="C205" s="9"/>
       <c r="D205" s="8">
-        <v>46134.57840032407</v>
+        <v>46196.91374106481</v>
       </c>
       <c r="E205" s="9" t="s">
         <v>174</v>
@@ -13352,13 +13381,13 @@
         <v>26</v>
       </c>
       <c r="N205" s="9" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="O205" s="9" t="s">
         <v>191</v>
       </c>
       <c r="P205" s="9" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="Q205" s="9"/>
       <c r="R205" s="9"/>
@@ -13375,7 +13404,7 @@
       </c>
       <c r="C206" s="6"/>
       <c r="D206" s="5">
-        <v>46134.5784083912</v>
+        <v>46196.91374993055</v>
       </c>
       <c r="E206" s="6" t="s">
         <v>174</v>
@@ -13403,13 +13432,13 @@
         <v>26</v>
       </c>
       <c r="N206" s="6" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="O206" s="6" t="s">
         <v>193</v>
       </c>
       <c r="P206" s="6" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="Q206" s="6"/>
       <c r="R206" s="6"/>
@@ -13426,7 +13455,7 @@
       </c>
       <c r="C207" s="9"/>
       <c r="D207" s="8">
-        <v>46134.5784374537</v>
+        <v>46196.91377486111</v>
       </c>
       <c r="E207" s="9" t="s">
         <v>174</v>
@@ -13454,13 +13483,13 @@
         <v>26</v>
       </c>
       <c r="N207" s="9" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="O207" s="9" t="s">
         <v>195</v>
       </c>
       <c r="P207" s="9" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="Q207" s="9"/>
       <c r="R207" s="9"/>
@@ -13477,7 +13506,7 @@
       </c>
       <c r="C208" s="6"/>
       <c r="D208" s="5">
-        <v>46134.5784584375</v>
+        <v>46196.91379184028</v>
       </c>
       <c r="E208" s="6" t="s">
         <v>174</v>
@@ -13505,13 +13534,13 @@
         <v>26</v>
       </c>
       <c r="N208" s="6" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="O208" s="6" t="s">
         <v>197</v>
       </c>
       <c r="P208" s="6" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="Q208" s="6"/>
       <c r="R208" s="6"/>
@@ -13528,7 +13557,7 @@
       </c>
       <c r="C209" s="9"/>
       <c r="D209" s="8">
-        <v>46134.578506238424</v>
+        <v>46196.913807916666</v>
       </c>
       <c r="E209" s="9" t="s">
         <v>174</v>
@@ -13556,13 +13585,13 @@
         <v>26</v>
       </c>
       <c r="N209" s="9" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="O209" s="9" t="s">
         <v>199</v>
       </c>
       <c r="P209" s="9" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="Q209" s="9"/>
       <c r="R209" s="9"/>
@@ -13579,7 +13608,7 @@
       </c>
       <c r="C210" s="6"/>
       <c r="D210" s="5">
-        <v>46134.578535925924</v>
+        <v>46196.91381409722</v>
       </c>
       <c r="E210" s="6" t="s">
         <v>174</v>
@@ -13607,13 +13636,13 @@
         <v>26</v>
       </c>
       <c r="N210" s="6" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="O210" s="6" t="s">
         <v>201</v>
       </c>
       <c r="P210" s="6" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="Q210" s="6"/>
       <c r="R210" s="6"/>
@@ -13630,7 +13659,7 @@
       </c>
       <c r="C211" s="9"/>
       <c r="D211" s="8">
-        <v>46134.57855365741</v>
+        <v>46196.91383046296</v>
       </c>
       <c r="E211" s="9" t="s">
         <v>174</v>
@@ -13658,13 +13687,13 @@
         <v>26</v>
       </c>
       <c r="N211" s="9" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="O211" s="9" t="s">
         <v>203</v>
       </c>
       <c r="P211" s="9" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="Q211" s="9"/>
       <c r="R211" s="9"/>
@@ -13681,10 +13710,10 @@
       </c>
       <c r="C212" s="6"/>
       <c r="D212" s="5">
-        <v>46134.578584780094</v>
+        <v>46196.913837025466</v>
       </c>
       <c r="E212" s="6" t="s">
-        <v>174</v>
+        <v>452</v>
       </c>
       <c r="F212" s="6" t="s">
         <v>26</v>
@@ -13709,13 +13738,13 @@
         <v>26</v>
       </c>
       <c r="N212" s="6" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="O212" s="6" t="s">
         <v>205</v>
       </c>
       <c r="P212" s="6" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="Q212" s="6"/>
       <c r="R212" s="6"/>
@@ -13725,14 +13754,14 @@
     </row>
     <row r="213" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A213" s="7" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B213" s="8">
         <v>46133.58300138889</v>
       </c>
       <c r="C213" s="9"/>
       <c r="D213" s="8">
-        <v>46134.57860878472</v>
+        <v>46196.91385334491</v>
       </c>
       <c r="E213" s="9" t="s">
         <v>273</v>
@@ -13760,13 +13789,13 @@
         <v>26</v>
       </c>
       <c r="N213" s="9" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="O213" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P213" s="9" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="Q213" s="9"/>
       <c r="R213" s="9"/>
@@ -13776,7 +13805,7 @@
     </row>
     <row r="214" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A214" s="4" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B214" s="5">
         <v>46132.589012916666</v>
@@ -13786,7 +13815,7 @@
         <v>46133.58769056713</v>
       </c>
       <c r="E214" s="6" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F214" s="6" t="s">
         <v>25</v>
@@ -13810,7 +13839,7 @@
         <v>26</v>
       </c>
       <c r="O214" s="6" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="P214" s="6" t="s">
         <v>26</v>
@@ -13823,7 +13852,7 @@
     </row>
     <row r="215" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A215" s="7" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B215" s="8">
         <v>46132.589016666665</v>
@@ -13833,16 +13862,16 @@
         <v>46133.58482033564</v>
       </c>
       <c r="E215" s="9" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="F215" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G215" s="9" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H215" s="9" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="I215" s="9"/>
       <c r="J215" s="8">
@@ -13858,13 +13887,13 @@
         <v>26</v>
       </c>
       <c r="N215" s="9" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="O215" s="9" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="P215" s="9" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="Q215" s="8">
         <v>46226</v>
@@ -13884,14 +13913,14 @@
     </row>
     <row r="216" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A216" s="4" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B216" s="5">
         <v>46132.63360670139</v>
       </c>
       <c r="C216" s="6"/>
       <c r="D216" s="5">
-        <v>46133.649118483794</v>
+        <v>46196.91388565973</v>
       </c>
       <c r="E216" s="6" t="s">
         <v>174</v>
@@ -13900,10 +13929,10 @@
         <v>26</v>
       </c>
       <c r="G216" s="6" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H216" s="6" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="I216" s="6"/>
       <c r="J216" s="5">
@@ -13919,7 +13948,7 @@
         <v>26</v>
       </c>
       <c r="N216" s="6" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O216" s="6" t="s">
         <v>174</v>
@@ -13935,14 +13964,14 @@
     </row>
     <row r="217" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A217" s="7" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B217" s="8">
         <v>46132.63361304398</v>
       </c>
       <c r="C217" s="9"/>
       <c r="D217" s="8">
-        <v>46133.649169745375</v>
+        <v>46196.91389173611</v>
       </c>
       <c r="E217" s="9" t="s">
         <v>174</v>
@@ -13951,10 +13980,10 @@
         <v>26</v>
       </c>
       <c r="G217" s="9" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H217" s="9" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="I217" s="9"/>
       <c r="J217" s="8">
@@ -13970,7 +13999,7 @@
         <v>26</v>
       </c>
       <c r="N217" s="9" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O217" s="9" t="s">
         <v>174</v>
@@ -13986,14 +14015,14 @@
     </row>
     <row r="218" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A218" s="4" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B218" s="5">
         <v>46132.63361974537</v>
       </c>
       <c r="C218" s="6"/>
       <c r="D218" s="5">
-        <v>46133.649221631946</v>
+        <v>46196.91390143518</v>
       </c>
       <c r="E218" s="6" t="s">
         <v>174</v>
@@ -14002,10 +14031,10 @@
         <v>26</v>
       </c>
       <c r="G218" s="6" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H218" s="6" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="I218" s="6"/>
       <c r="J218" s="5">
@@ -14021,7 +14050,7 @@
         <v>26</v>
       </c>
       <c r="N218" s="6" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O218" s="6" t="s">
         <v>174</v>
@@ -14037,14 +14066,14 @@
     </row>
     <row r="219" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A219" s="7" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B219" s="8">
         <v>46132.63363137731</v>
       </c>
       <c r="C219" s="9"/>
       <c r="D219" s="8">
-        <v>46133.649269375004</v>
+        <v>46196.913907152775</v>
       </c>
       <c r="E219" s="9" t="s">
         <v>174</v>
@@ -14053,10 +14082,10 @@
         <v>26</v>
       </c>
       <c r="G219" s="9" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H219" s="9" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="I219" s="9"/>
       <c r="J219" s="8">
@@ -14072,7 +14101,7 @@
         <v>26</v>
       </c>
       <c r="N219" s="9" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O219" s="9" t="s">
         <v>174</v>
@@ -14088,14 +14117,14 @@
     </row>
     <row r="220" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A220" s="4" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B220" s="5">
         <v>46132.63362555555</v>
       </c>
       <c r="C220" s="6"/>
       <c r="D220" s="5">
-        <v>46133.649305451385</v>
+        <v>46196.91391674768</v>
       </c>
       <c r="E220" s="6" t="s">
         <v>174</v>
@@ -14104,10 +14133,10 @@
         <v>26</v>
       </c>
       <c r="G220" s="6" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H220" s="6" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="I220" s="6"/>
       <c r="J220" s="5">
@@ -14123,7 +14152,7 @@
         <v>26</v>
       </c>
       <c r="N220" s="6" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O220" s="6" t="s">
         <v>174</v>
@@ -14139,14 +14168,14 @@
     </row>
     <row r="221" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A221" s="7" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B221" s="8">
         <v>46132.63363859954</v>
       </c>
       <c r="C221" s="9"/>
       <c r="D221" s="8">
-        <v>46133.64934875</v>
+        <v>46196.913933171294</v>
       </c>
       <c r="E221" s="9" t="s">
         <v>174</v>
@@ -14155,10 +14184,10 @@
         <v>26</v>
       </c>
       <c r="G221" s="9" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H221" s="9" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="I221" s="9"/>
       <c r="J221" s="8">
@@ -14174,7 +14203,7 @@
         <v>26</v>
       </c>
       <c r="N221" s="9" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O221" s="9" t="s">
         <v>174</v>
@@ -14190,26 +14219,26 @@
     </row>
     <row r="222" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A222" s="4" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B222" s="5">
         <v>46132.63364667824</v>
       </c>
       <c r="C222" s="6"/>
       <c r="D222" s="5">
-        <v>46133.649374988425</v>
+        <v>46196.913939861115</v>
       </c>
       <c r="E222" s="6" t="s">
-        <v>174</v>
+        <v>452</v>
       </c>
       <c r="F222" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G222" s="6" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H222" s="6" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="I222" s="6"/>
       <c r="J222" s="5">
@@ -14225,7 +14254,7 @@
         <v>26</v>
       </c>
       <c r="N222" s="6" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O222" s="6" t="s">
         <v>174</v>
@@ -14241,14 +14270,14 @@
     </row>
     <row r="223" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A223" s="7" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B223" s="8">
         <v>46132.633653055556</v>
       </c>
       <c r="C223" s="9"/>
       <c r="D223" s="8">
-        <v>46133.649405081014</v>
+        <v>46196.91395613426</v>
       </c>
       <c r="E223" s="9" t="s">
         <v>174</v>
@@ -14257,10 +14286,10 @@
         <v>26</v>
       </c>
       <c r="G223" s="9" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H223" s="9" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="I223" s="9"/>
       <c r="J223" s="8">
@@ -14276,7 +14305,7 @@
         <v>26</v>
       </c>
       <c r="N223" s="9" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O223" s="9" t="s">
         <v>174</v>
@@ -14292,14 +14321,14 @@
     </row>
     <row r="224" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A224" s="4" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B224" s="5">
         <v>46132.63365921297</v>
       </c>
       <c r="C224" s="6"/>
       <c r="D224" s="5">
-        <v>46133.649433032406</v>
+        <v>46196.9139649537</v>
       </c>
       <c r="E224" s="6" t="s">
         <v>174</v>
@@ -14308,10 +14337,10 @@
         <v>26</v>
       </c>
       <c r="G224" s="6" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H224" s="6" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="I224" s="6"/>
       <c r="J224" s="5">
@@ -14327,7 +14356,7 @@
         <v>26</v>
       </c>
       <c r="N224" s="6" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O224" s="6" t="s">
         <v>174</v>
@@ -14343,14 +14372,14 @@
     </row>
     <row r="225" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A225" s="7" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B225" s="8">
         <v>46132.633665347224</v>
       </c>
       <c r="C225" s="9"/>
       <c r="D225" s="8">
-        <v>46133.64948690972</v>
+        <v>46196.91397201389</v>
       </c>
       <c r="E225" s="9" t="s">
         <v>174</v>
@@ -14359,10 +14388,10 @@
         <v>26</v>
       </c>
       <c r="G225" s="9" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H225" s="9" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="I225" s="9"/>
       <c r="J225" s="8">
@@ -14378,7 +14407,7 @@
         <v>26</v>
       </c>
       <c r="N225" s="9" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O225" s="9" t="s">
         <v>174</v>
@@ -14394,14 +14423,14 @@
     </row>
     <row r="226" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A226" s="4" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B226" s="5">
         <v>46132.63367407407</v>
       </c>
       <c r="C226" s="6"/>
       <c r="D226" s="5">
-        <v>46133.649517094906</v>
+        <v>46196.91398435185</v>
       </c>
       <c r="E226" s="6" t="s">
         <v>174</v>
@@ -14410,10 +14439,10 @@
         <v>26</v>
       </c>
       <c r="G226" s="6" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H226" s="6" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="I226" s="6"/>
       <c r="J226" s="5">
@@ -14429,7 +14458,7 @@
         <v>26</v>
       </c>
       <c r="N226" s="6" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O226" s="6" t="s">
         <v>174</v>
@@ -14445,14 +14474,14 @@
     </row>
     <row r="227" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A227" s="7" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B227" s="8">
         <v>46132.63368225694</v>
       </c>
       <c r="C227" s="9"/>
       <c r="D227" s="8">
-        <v>46133.649557303244</v>
+        <v>46196.91399296296</v>
       </c>
       <c r="E227" s="9" t="s">
         <v>174</v>
@@ -14461,10 +14490,10 @@
         <v>26</v>
       </c>
       <c r="G227" s="9" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H227" s="9" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="I227" s="9"/>
       <c r="J227" s="8">
@@ -14480,7 +14509,7 @@
         <v>26</v>
       </c>
       <c r="N227" s="9" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O227" s="9" t="s">
         <v>174</v>
@@ -14496,14 +14525,14 @@
     </row>
     <row r="228" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A228" s="4" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B228" s="5">
         <v>46132.63368885417</v>
       </c>
       <c r="C228" s="6"/>
       <c r="D228" s="5">
-        <v>46133.649592581016</v>
+        <v>46196.913999675926</v>
       </c>
       <c r="E228" s="6" t="s">
         <v>174</v>
@@ -14512,10 +14541,10 @@
         <v>26</v>
       </c>
       <c r="G228" s="6" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H228" s="6" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="I228" s="6"/>
       <c r="J228" s="5">
@@ -14531,7 +14560,7 @@
         <v>26</v>
       </c>
       <c r="N228" s="6" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O228" s="6" t="s">
         <v>174</v>
@@ -14547,14 +14576,14 @@
     </row>
     <row r="229" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A229" s="7" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B229" s="8">
         <v>46132.633694965276</v>
       </c>
       <c r="C229" s="9"/>
       <c r="D229" s="8">
-        <v>46133.64962285879</v>
+        <v>46196.914015358794</v>
       </c>
       <c r="E229" s="9" t="s">
         <v>174</v>
@@ -14563,10 +14592,10 @@
         <v>26</v>
       </c>
       <c r="G229" s="9" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H229" s="9" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="I229" s="9"/>
       <c r="J229" s="8">
@@ -14582,7 +14611,7 @@
         <v>26</v>
       </c>
       <c r="N229" s="9" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O229" s="9" t="s">
         <v>174</v>
@@ -14598,26 +14627,26 @@
     </row>
     <row r="230" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A230" s="4" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B230" s="5">
         <v>46132.63370111111</v>
       </c>
       <c r="C230" s="6"/>
       <c r="D230" s="5">
-        <v>46133.64965064815</v>
+        <v>46196.9140217824</v>
       </c>
       <c r="E230" s="6" t="s">
-        <v>174</v>
+        <v>452</v>
       </c>
       <c r="F230" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G230" s="6" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H230" s="6" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="I230" s="6"/>
       <c r="J230" s="5">
@@ -14633,13 +14662,13 @@
         <v>26</v>
       </c>
       <c r="N230" s="6" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O230" s="6" t="s">
-        <v>174</v>
+        <v>452</v>
       </c>
       <c r="P230" s="6" t="s">
-        <v>174</v>
+        <v>452</v>
       </c>
       <c r="Q230" s="6"/>
       <c r="R230" s="6"/>
@@ -14649,14 +14678,14 @@
     </row>
     <row r="231" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A231" s="7" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B231" s="8">
         <v>46132.63378953704</v>
       </c>
       <c r="C231" s="9"/>
       <c r="D231" s="8">
-        <v>46133.649702372684</v>
+        <v>46196.91403721065</v>
       </c>
       <c r="E231" s="9" t="s">
         <v>174</v>
@@ -14665,10 +14694,10 @@
         <v>26</v>
       </c>
       <c r="G231" s="9" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H231" s="9" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="I231" s="9"/>
       <c r="J231" s="8">
@@ -14684,7 +14713,7 @@
         <v>26</v>
       </c>
       <c r="N231" s="9" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O231" s="9" t="s">
         <v>273</v>
@@ -14700,7 +14729,7 @@
     </row>
     <row r="232" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A232" s="4" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B232" s="5">
         <v>46132.589021736116</v>
@@ -14710,7 +14739,7 @@
         <v>46133.58651043981</v>
       </c>
       <c r="E232" s="6" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F232" s="6" t="s">
         <v>26</v>
@@ -14735,13 +14764,13 @@
         <v>26</v>
       </c>
       <c r="N232" s="6" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="O232" s="6" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="P232" s="6" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="Q232" s="5">
         <v>46227</v>
@@ -14761,14 +14790,14 @@
     </row>
     <row r="233" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A233" s="7" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B233" s="8">
         <v>46132.633861608796</v>
       </c>
       <c r="C233" s="9"/>
       <c r="D233" s="8">
-        <v>46133.65056246528</v>
+        <v>46196.91407126158</v>
       </c>
       <c r="E233" s="9" t="s">
         <v>174</v>
@@ -14796,7 +14825,7 @@
         <v>26</v>
       </c>
       <c r="N233" s="9" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O233" s="9" t="s">
         <v>174</v>
@@ -14812,14 +14841,14 @@
     </row>
     <row r="234" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A234" s="4" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B234" s="5">
         <v>46132.633870011574</v>
       </c>
       <c r="C234" s="6"/>
       <c r="D234" s="5">
-        <v>46133.650605648145</v>
+        <v>46196.914077905094</v>
       </c>
       <c r="E234" s="6" t="s">
         <v>174</v>
@@ -14847,7 +14876,7 @@
         <v>26</v>
       </c>
       <c r="N234" s="6" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O234" s="6" t="s">
         <v>174</v>
@@ -14863,14 +14892,14 @@
     </row>
     <row r="235" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A235" s="7" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B235" s="8">
         <v>46132.63387658565</v>
       </c>
       <c r="C235" s="9"/>
       <c r="D235" s="8">
-        <v>46133.6506462963</v>
+        <v>46196.914084212964</v>
       </c>
       <c r="E235" s="9" t="s">
         <v>174</v>
@@ -14898,7 +14927,7 @@
         <v>26</v>
       </c>
       <c r="N235" s="9" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O235" s="9" t="s">
         <v>174</v>
@@ -14914,14 +14943,14 @@
     </row>
     <row r="236" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A236" s="4" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B236" s="5">
         <v>46132.63388259259</v>
       </c>
       <c r="C236" s="6"/>
       <c r="D236" s="5">
-        <v>46133.65067832176</v>
+        <v>46196.91409322916</v>
       </c>
       <c r="E236" s="6" t="s">
         <v>174</v>
@@ -14949,7 +14978,7 @@
         <v>26</v>
       </c>
       <c r="N236" s="6" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O236" s="6" t="s">
         <v>174</v>
@@ -14965,14 +14994,14 @@
     </row>
     <row r="237" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A237" s="7" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B237" s="8">
         <v>46132.63388633102</v>
       </c>
       <c r="C237" s="9"/>
       <c r="D237" s="8">
-        <v>46133.65072818287</v>
+        <v>46196.914099340276</v>
       </c>
       <c r="E237" s="9" t="s">
         <v>174</v>
@@ -15000,7 +15029,7 @@
         <v>26</v>
       </c>
       <c r="N237" s="9" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O237" s="9" t="s">
         <v>174</v>
@@ -15016,14 +15045,14 @@
     </row>
     <row r="238" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A238" s="4" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B238" s="5">
         <v>46132.63389106482</v>
       </c>
       <c r="C238" s="6"/>
       <c r="D238" s="5">
-        <v>46133.65076650463</v>
+        <v>46196.9141059838</v>
       </c>
       <c r="E238" s="6" t="s">
         <v>174</v>
@@ -15051,7 +15080,7 @@
         <v>26</v>
       </c>
       <c r="N238" s="6" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O238" s="6" t="s">
         <v>174</v>
@@ -15067,14 +15096,14 @@
     </row>
     <row r="239" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A239" s="7" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B239" s="8">
         <v>46132.63389739583</v>
       </c>
       <c r="C239" s="9"/>
       <c r="D239" s="8">
-        <v>46133.65080771991</v>
+        <v>46196.91411261574</v>
       </c>
       <c r="E239" s="9" t="s">
         <v>174</v>
@@ -15102,10 +15131,10 @@
         <v>26</v>
       </c>
       <c r="N239" s="9" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O239" s="9" t="s">
-        <v>174</v>
+        <v>452</v>
       </c>
       <c r="P239" s="9" t="s">
         <v>174</v>
@@ -15118,14 +15147,14 @@
     </row>
     <row r="240" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A240" s="4" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B240" s="5">
         <v>46132.63390288195</v>
       </c>
       <c r="C240" s="6"/>
       <c r="D240" s="5">
-        <v>46133.65083987269</v>
+        <v>46196.91411917824</v>
       </c>
       <c r="E240" s="6" t="s">
         <v>174</v>
@@ -15153,7 +15182,7 @@
         <v>26</v>
       </c>
       <c r="N240" s="6" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O240" s="6" t="s">
         <v>174</v>
@@ -15169,14 +15198,14 @@
     </row>
     <row r="241" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A241" s="7" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B241" s="8">
         <v>46132.63390861111</v>
       </c>
       <c r="C241" s="9"/>
       <c r="D241" s="8">
-        <v>46133.650867777775</v>
+        <v>46196.91413769676</v>
       </c>
       <c r="E241" s="9" t="s">
         <v>174</v>
@@ -15204,7 +15233,7 @@
         <v>26</v>
       </c>
       <c r="N241" s="9" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O241" s="9" t="s">
         <v>174</v>
@@ -15220,14 +15249,14 @@
     </row>
     <row r="242" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A242" s="4" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B242" s="5">
         <v>46132.63391276621</v>
       </c>
       <c r="C242" s="6"/>
       <c r="D242" s="5">
-        <v>46133.65090828703</v>
+        <v>46196.91415084491</v>
       </c>
       <c r="E242" s="6" t="s">
         <v>174</v>
@@ -15255,7 +15284,7 @@
         <v>26</v>
       </c>
       <c r="N242" s="6" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O242" s="6" t="s">
         <v>174</v>
@@ -15271,14 +15300,14 @@
     </row>
     <row r="243" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A243" s="7" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B243" s="8">
         <v>46132.63391880787</v>
       </c>
       <c r="C243" s="9"/>
       <c r="D243" s="8">
-        <v>46133.65093710648</v>
+        <v>46196.914157175925</v>
       </c>
       <c r="E243" s="9" t="s">
         <v>174</v>
@@ -15306,7 +15335,7 @@
         <v>26</v>
       </c>
       <c r="N243" s="9" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O243" s="9" t="s">
         <v>174</v>
@@ -15322,14 +15351,14 @@
     </row>
     <row r="244" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A244" s="4" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B244" s="5">
         <v>46132.63392302083</v>
       </c>
       <c r="C244" s="6"/>
       <c r="D244" s="5">
-        <v>46133.65097461805</v>
+        <v>46196.91416721065</v>
       </c>
       <c r="E244" s="6" t="s">
         <v>174</v>
@@ -15357,7 +15386,7 @@
         <v>26</v>
       </c>
       <c r="N244" s="6" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O244" s="6" t="s">
         <v>174</v>
@@ -15373,14 +15402,14 @@
     </row>
     <row r="245" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A245" s="7" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B245" s="8">
         <v>46132.63393041666</v>
       </c>
       <c r="C245" s="9"/>
       <c r="D245" s="8">
-        <v>46133.65102799769</v>
+        <v>46196.91417351852</v>
       </c>
       <c r="E245" s="9" t="s">
         <v>174</v>
@@ -15408,7 +15437,7 @@
         <v>26</v>
       </c>
       <c r="N245" s="9" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O245" s="9" t="s">
         <v>174</v>
@@ -15424,14 +15453,14 @@
     </row>
     <row r="246" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A246" s="4" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B246" s="5">
         <v>46132.63393689815</v>
       </c>
       <c r="C246" s="6"/>
       <c r="D246" s="5">
-        <v>46133.65107594908</v>
+        <v>46196.91418997685</v>
       </c>
       <c r="E246" s="6" t="s">
         <v>174</v>
@@ -15459,7 +15488,7 @@
         <v>26</v>
       </c>
       <c r="N246" s="6" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O246" s="6" t="s">
         <v>174</v>
@@ -15475,17 +15504,17 @@
     </row>
     <row r="247" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A247" s="7" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B247" s="8">
         <v>46132.633943078705</v>
       </c>
       <c r="C247" s="9"/>
       <c r="D247" s="8">
-        <v>46133.65110819445</v>
+        <v>46196.91419930555</v>
       </c>
       <c r="E247" s="9" t="s">
-        <v>174</v>
+        <v>452</v>
       </c>
       <c r="F247" s="9" t="s">
         <v>26</v>
@@ -15510,10 +15539,10 @@
         <v>26</v>
       </c>
       <c r="N247" s="9" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O247" s="9" t="s">
-        <v>174</v>
+        <v>452</v>
       </c>
       <c r="P247" s="9" t="s">
         <v>174</v>
@@ -15526,14 +15555,14 @@
     </row>
     <row r="248" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A248" s="4" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B248" s="5">
         <v>46132.633955578705</v>
       </c>
       <c r="C248" s="6"/>
       <c r="D248" s="5">
-        <v>46133.65114501158</v>
+        <v>46196.91421935185</v>
       </c>
       <c r="E248" s="6" t="s">
         <v>174</v>
@@ -15561,7 +15590,7 @@
         <v>26</v>
       </c>
       <c r="N248" s="6" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O248" s="6" t="s">
         <v>174</v>
@@ -15577,7 +15606,7 @@
     </row>
     <row r="249" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A249" s="7" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B249" s="8">
         <v>46132.58902681713</v>
@@ -15587,16 +15616,16 @@
         <v>46133.58721105324</v>
       </c>
       <c r="E249" s="9" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="F249" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G249" s="9" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H249" s="9" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I249" s="8">
         <v>46230</v>
@@ -15614,13 +15643,13 @@
         <v>26</v>
       </c>
       <c r="N249" s="9" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="O249" s="9" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="P249" s="9" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="Q249" s="8">
         <v>46230</v>
@@ -15640,14 +15669,14 @@
     </row>
     <row r="250" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A250" s="4" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B250" s="5">
         <v>46132.634024432875</v>
       </c>
       <c r="C250" s="6"/>
       <c r="D250" s="5">
-        <v>46133.65130945602</v>
+        <v>46196.914276875</v>
       </c>
       <c r="E250" s="6" t="s">
         <v>174</v>
@@ -15656,10 +15685,10 @@
         <v>26</v>
       </c>
       <c r="G250" s="6" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H250" s="6" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I250" s="6"/>
       <c r="J250" s="5">
@@ -15675,7 +15704,7 @@
         <v>26</v>
       </c>
       <c r="N250" s="6" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="O250" s="6" t="s">
         <v>174</v>
@@ -15691,14 +15720,14 @@
     </row>
     <row r="251" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A251" s="7" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B251" s="8">
         <v>46132.634032685186</v>
       </c>
       <c r="C251" s="9"/>
       <c r="D251" s="8">
-        <v>46133.651351759254</v>
+        <v>46196.914286666666</v>
       </c>
       <c r="E251" s="9" t="s">
         <v>174</v>
@@ -15707,10 +15736,10 @@
         <v>26</v>
       </c>
       <c r="G251" s="9" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H251" s="9" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I251" s="9"/>
       <c r="J251" s="8">
@@ -15726,7 +15755,7 @@
         <v>26</v>
       </c>
       <c r="N251" s="9" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="O251" s="9" t="s">
         <v>174</v>
@@ -15742,14 +15771,14 @@
     </row>
     <row r="252" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A252" s="4" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B252" s="5">
         <v>46132.63404001157</v>
       </c>
       <c r="C252" s="6"/>
       <c r="D252" s="5">
-        <v>46133.65139332176</v>
+        <v>46196.91429060185</v>
       </c>
       <c r="E252" s="6" t="s">
         <v>174</v>
@@ -15758,10 +15787,10 @@
         <v>26</v>
       </c>
       <c r="G252" s="6" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H252" s="6" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I252" s="6"/>
       <c r="J252" s="5">
@@ -15777,7 +15806,7 @@
         <v>26</v>
       </c>
       <c r="N252" s="6" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="O252" s="6" t="s">
         <v>174</v>
@@ -15793,14 +15822,14 @@
     </row>
     <row r="253" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A253" s="7" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B253" s="8">
         <v>46132.63404659722</v>
       </c>
       <c r="C253" s="9"/>
       <c r="D253" s="8">
-        <v>46133.651435231484</v>
+        <v>46196.914299571756</v>
       </c>
       <c r="E253" s="9" t="s">
         <v>174</v>
@@ -15809,10 +15838,10 @@
         <v>26</v>
       </c>
       <c r="G253" s="9" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H253" s="9" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I253" s="9"/>
       <c r="J253" s="8">
@@ -15828,7 +15857,7 @@
         <v>26</v>
       </c>
       <c r="N253" s="9" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="O253" s="9" t="s">
         <v>174</v>
@@ -15844,14 +15873,14 @@
     </row>
     <row r="254" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A254" s="4" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B254" s="5">
         <v>46132.6340537037</v>
       </c>
       <c r="C254" s="6"/>
       <c r="D254" s="5">
-        <v>46133.651464282404</v>
+        <v>46196.91430931713</v>
       </c>
       <c r="E254" s="6" t="s">
         <v>174</v>
@@ -15860,10 +15889,10 @@
         <v>26</v>
       </c>
       <c r="G254" s="6" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H254" s="6" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I254" s="6"/>
       <c r="J254" s="5">
@@ -15879,7 +15908,7 @@
         <v>26</v>
       </c>
       <c r="N254" s="6" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="O254" s="6" t="s">
         <v>174</v>
@@ -15895,14 +15924,14 @@
     </row>
     <row r="255" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A255" s="7" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B255" s="8">
         <v>46132.63406115741</v>
       </c>
       <c r="C255" s="9"/>
       <c r="D255" s="8">
-        <v>46133.65151039352</v>
+        <v>46196.914319143514</v>
       </c>
       <c r="E255" s="9" t="s">
         <v>174</v>
@@ -15911,10 +15940,10 @@
         <v>26</v>
       </c>
       <c r="G255" s="9" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H255" s="9" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I255" s="9"/>
       <c r="J255" s="8">
@@ -15930,7 +15959,7 @@
         <v>26</v>
       </c>
       <c r="N255" s="9" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="O255" s="9" t="s">
         <v>174</v>
@@ -15946,14 +15975,14 @@
     </row>
     <row r="256" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A256" s="4" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B256" s="5">
         <v>46132.63406662037</v>
       </c>
       <c r="C256" s="6"/>
       <c r="D256" s="5">
-        <v>46133.65154519676</v>
+        <v>46196.91432607639</v>
       </c>
       <c r="E256" s="6" t="s">
         <v>174</v>
@@ -15962,10 +15991,10 @@
         <v>26</v>
       </c>
       <c r="G256" s="6" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H256" s="6" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I256" s="6"/>
       <c r="J256" s="5">
@@ -15981,7 +16010,7 @@
         <v>26</v>
       </c>
       <c r="N256" s="6" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="O256" s="6" t="s">
         <v>174</v>
@@ -15997,14 +16026,14 @@
     </row>
     <row r="257" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A257" s="7" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B257" s="8">
         <v>46132.634072395835</v>
       </c>
       <c r="C257" s="9"/>
       <c r="D257" s="8">
-        <v>46133.65157672454</v>
+        <v>46196.914335231486</v>
       </c>
       <c r="E257" s="9" t="s">
         <v>174</v>
@@ -16013,10 +16042,10 @@
         <v>26</v>
       </c>
       <c r="G257" s="9" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H257" s="9" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I257" s="9"/>
       <c r="J257" s="8">
@@ -16032,7 +16061,7 @@
         <v>26</v>
       </c>
       <c r="N257" s="9" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="O257" s="9" t="s">
         <v>174</v>
@@ -16048,14 +16077,14 @@
     </row>
     <row r="258" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A258" s="4" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B258" s="5">
         <v>46132.6340770949</v>
       </c>
       <c r="C258" s="6"/>
       <c r="D258" s="5">
-        <v>46133.65161886574</v>
+        <v>46196.914344687495</v>
       </c>
       <c r="E258" s="6" t="s">
         <v>174</v>
@@ -16064,10 +16093,10 @@
         <v>26</v>
       </c>
       <c r="G258" s="6" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H258" s="6" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I258" s="6"/>
       <c r="J258" s="5">
@@ -16083,7 +16112,7 @@
         <v>26</v>
       </c>
       <c r="N258" s="6" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="O258" s="6" t="s">
         <v>174</v>
@@ -16099,14 +16128,14 @@
     </row>
     <row r="259" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A259" s="7" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B259" s="8">
         <v>46132.634082777775</v>
       </c>
       <c r="C259" s="9"/>
       <c r="D259" s="8">
-        <v>46133.65165621528</v>
+        <v>46196.91435427083</v>
       </c>
       <c r="E259" s="9" t="s">
         <v>174</v>
@@ -16115,10 +16144,10 @@
         <v>26</v>
       </c>
       <c r="G259" s="9" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H259" s="9" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I259" s="9"/>
       <c r="J259" s="8">
@@ -16134,7 +16163,7 @@
         <v>26</v>
       </c>
       <c r="N259" s="9" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="O259" s="9" t="s">
         <v>174</v>
@@ -16150,14 +16179,14 @@
     </row>
     <row r="260" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A260" s="4" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B260" s="5">
         <v>46132.63408899306</v>
       </c>
       <c r="C260" s="6"/>
       <c r="D260" s="5">
-        <v>46133.65169717593</v>
+        <v>46196.91437050926</v>
       </c>
       <c r="E260" s="6" t="s">
         <v>174</v>
@@ -16166,10 +16195,10 @@
         <v>26</v>
       </c>
       <c r="G260" s="6" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H260" s="6" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I260" s="6"/>
       <c r="J260" s="5">
@@ -16185,7 +16214,7 @@
         <v>26</v>
       </c>
       <c r="N260" s="6" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="O260" s="6" t="s">
         <v>174</v>
@@ -16201,14 +16230,14 @@
     </row>
     <row r="261" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A261" s="7" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B261" s="8">
         <v>46132.63409545139</v>
       </c>
       <c r="C261" s="9"/>
       <c r="D261" s="8">
-        <v>46133.651744409726</v>
+        <v>46196.914380057875</v>
       </c>
       <c r="E261" s="9" t="s">
         <v>174</v>
@@ -16217,10 +16246,10 @@
         <v>26</v>
       </c>
       <c r="G261" s="9" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H261" s="9" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I261" s="9"/>
       <c r="J261" s="8">
@@ -16236,7 +16265,7 @@
         <v>26</v>
       </c>
       <c r="N261" s="9" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="O261" s="9" t="s">
         <v>174</v>
@@ -16252,14 +16281,14 @@
     </row>
     <row r="262" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A262" s="4" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B262" s="5">
         <v>46132.63410087963</v>
       </c>
       <c r="C262" s="6"/>
       <c r="D262" s="5">
-        <v>46133.65178803241</v>
+        <v>46196.914383738425</v>
       </c>
       <c r="E262" s="6" t="s">
         <v>174</v>
@@ -16268,10 +16297,10 @@
         <v>26</v>
       </c>
       <c r="G262" s="6" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H262" s="6" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I262" s="6"/>
       <c r="J262" s="5">
@@ -16287,7 +16316,7 @@
         <v>26</v>
       </c>
       <c r="N262" s="6" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="O262" s="6" t="s">
         <v>174</v>
@@ -16303,14 +16332,14 @@
     </row>
     <row r="263" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A263" s="7" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B263" s="8">
         <v>46132.63410688657</v>
       </c>
       <c r="C263" s="9"/>
       <c r="D263" s="8">
-        <v>46133.65184158565</v>
+        <v>46196.914396527776</v>
       </c>
       <c r="E263" s="9" t="s">
         <v>174</v>
@@ -16319,10 +16348,10 @@
         <v>26</v>
       </c>
       <c r="G263" s="9" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H263" s="9" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I263" s="9"/>
       <c r="J263" s="8">
@@ -16338,7 +16367,7 @@
         <v>26</v>
       </c>
       <c r="N263" s="9" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="O263" s="9" t="s">
         <v>174</v>
@@ -16354,14 +16383,14 @@
     </row>
     <row r="264" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A264" s="4" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B264" s="5">
         <v>46132.6341133449</v>
       </c>
       <c r="C264" s="6"/>
       <c r="D264" s="5">
-        <v>46133.65187707176</v>
+        <v>46196.914406261574</v>
       </c>
       <c r="E264" s="6" t="s">
         <v>174</v>
@@ -16370,10 +16399,10 @@
         <v>26</v>
       </c>
       <c r="G264" s="6" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H264" s="6" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I264" s="6"/>
       <c r="J264" s="5">
@@ -16389,10 +16418,10 @@
         <v>26</v>
       </c>
       <c r="N264" s="6" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="O264" s="6" t="s">
-        <v>174</v>
+        <v>452</v>
       </c>
       <c r="P264" s="6" t="s">
         <v>174</v>
@@ -16405,14 +16434,14 @@
     </row>
     <row r="265" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A265" s="7" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B265" s="8">
         <v>46132.63411966435</v>
       </c>
       <c r="C265" s="9"/>
       <c r="D265" s="8">
-        <v>46133.65195853009</v>
+        <v>46196.91441971065</v>
       </c>
       <c r="E265" s="9" t="s">
         <v>174</v>
@@ -16421,10 +16450,10 @@
         <v>26</v>
       </c>
       <c r="G265" s="9" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H265" s="9" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I265" s="9"/>
       <c r="J265" s="8">
@@ -16440,7 +16469,7 @@
         <v>26</v>
       </c>
       <c r="N265" s="9" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="O265" s="9" t="s">
         <v>174</v>
@@ -16456,7 +16485,7 @@
     </row>
     <row r="266" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A266" s="4" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B266" s="5">
         <v>46132.58903189815</v>
@@ -16466,16 +16495,16 @@
         <v>46133.65412578704</v>
       </c>
       <c r="E266" s="6" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="F266" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G266" s="6" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H266" s="6" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I266" s="6"/>
       <c r="J266" s="5">
@@ -16491,13 +16520,13 @@
         <v>26</v>
       </c>
       <c r="N266" s="6" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="O266" s="6" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="P266" s="6" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="Q266" s="5">
         <v>46231</v>
@@ -16517,14 +16546,14 @@
     </row>
     <row r="267" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A267" s="7" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B267" s="8">
         <v>46132.63422869213</v>
       </c>
       <c r="C267" s="9"/>
       <c r="D267" s="8">
-        <v>46133.65413622685</v>
+        <v>46196.91446424769</v>
       </c>
       <c r="E267" s="9" t="s">
         <v>174</v>
@@ -16533,10 +16562,10 @@
         <v>26</v>
       </c>
       <c r="G267" s="9" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H267" s="9" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I267" s="9"/>
       <c r="J267" s="8">
@@ -16552,13 +16581,13 @@
         <v>26</v>
       </c>
       <c r="N267" s="9" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="O267" s="9" t="s">
         <v>174</v>
       </c>
       <c r="P267" s="9" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="Q267" s="9"/>
       <c r="R267" s="9"/>
@@ -16568,14 +16597,14 @@
     </row>
     <row r="268" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A268" s="4" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B268" s="5">
         <v>46132.63423491898</v>
       </c>
       <c r="C268" s="6"/>
       <c r="D268" s="5">
-        <v>46133.65413814815</v>
+        <v>46196.91447116898</v>
       </c>
       <c r="E268" s="6" t="s">
         <v>174</v>
@@ -16584,10 +16613,10 @@
         <v>26</v>
       </c>
       <c r="G268" s="6" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H268" s="6" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I268" s="6"/>
       <c r="J268" s="5">
@@ -16603,13 +16632,13 @@
         <v>26</v>
       </c>
       <c r="N268" s="6" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="O268" s="6" t="s">
         <v>174</v>
       </c>
       <c r="P268" s="6" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="Q268" s="6"/>
       <c r="R268" s="6"/>
@@ -16619,14 +16648,14 @@
     </row>
     <row r="269" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A269" s="7" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B269" s="8">
         <v>46132.634240960644</v>
       </c>
       <c r="C269" s="9"/>
       <c r="D269" s="8">
-        <v>46133.65413996528</v>
+        <v>46196.914480694446</v>
       </c>
       <c r="E269" s="9" t="s">
         <v>174</v>
@@ -16635,10 +16664,10 @@
         <v>26</v>
       </c>
       <c r="G269" s="9" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H269" s="9" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I269" s="9"/>
       <c r="J269" s="8">
@@ -16654,13 +16683,13 @@
         <v>26</v>
       </c>
       <c r="N269" s="9" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="O269" s="9" t="s">
         <v>174</v>
       </c>
       <c r="P269" s="9" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="Q269" s="9"/>
       <c r="R269" s="9"/>
@@ -16670,14 +16699,14 @@
     </row>
     <row r="270" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A270" s="4" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B270" s="5">
         <v>46132.63424789352</v>
       </c>
       <c r="C270" s="6"/>
       <c r="D270" s="5">
-        <v>46133.654141770836</v>
+        <v>46196.91449018518</v>
       </c>
       <c r="E270" s="6" t="s">
         <v>174</v>
@@ -16686,10 +16715,10 @@
         <v>26</v>
       </c>
       <c r="G270" s="6" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H270" s="6" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I270" s="6"/>
       <c r="J270" s="5">
@@ -16705,13 +16734,13 @@
         <v>26</v>
       </c>
       <c r="N270" s="6" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="O270" s="6" t="s">
         <v>174</v>
       </c>
       <c r="P270" s="6" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="Q270" s="6"/>
       <c r="R270" s="6"/>
@@ -16721,14 +16750,14 @@
     </row>
     <row r="271" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A271" s="7" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B271" s="8">
         <v>46132.634254386576</v>
       </c>
       <c r="C271" s="9"/>
       <c r="D271" s="8">
-        <v>46133.654143356485</v>
+        <v>46196.91449658565</v>
       </c>
       <c r="E271" s="9" t="s">
         <v>174</v>
@@ -16737,10 +16766,10 @@
         <v>26</v>
       </c>
       <c r="G271" s="9" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H271" s="9" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I271" s="9"/>
       <c r="J271" s="8">
@@ -16756,13 +16785,13 @@
         <v>26</v>
       </c>
       <c r="N271" s="9" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="O271" s="9" t="s">
         <v>174</v>
       </c>
       <c r="P271" s="9" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="Q271" s="9"/>
       <c r="R271" s="9"/>
@@ -16772,14 +16801,14 @@
     </row>
     <row r="272" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A272" s="4" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B272" s="5">
         <v>46132.634260810184</v>
       </c>
       <c r="C272" s="6"/>
       <c r="D272" s="5">
-        <v>46133.6541450463</v>
+        <v>46196.914503645836</v>
       </c>
       <c r="E272" s="6" t="s">
         <v>174</v>
@@ -16788,10 +16817,10 @@
         <v>26</v>
       </c>
       <c r="G272" s="6" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H272" s="6" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I272" s="6"/>
       <c r="J272" s="5">
@@ -16807,13 +16836,13 @@
         <v>26</v>
       </c>
       <c r="N272" s="6" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="O272" s="6" t="s">
         <v>174</v>
       </c>
       <c r="P272" s="6" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="Q272" s="6"/>
       <c r="R272" s="6"/>
@@ -16823,14 +16852,14 @@
     </row>
     <row r="273" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A273" s="7" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B273" s="8">
         <v>46132.634267256944</v>
       </c>
       <c r="C273" s="9"/>
       <c r="D273" s="8">
-        <v>46133.65414665509</v>
+        <v>46196.91450951389</v>
       </c>
       <c r="E273" s="9" t="s">
         <v>174</v>
@@ -16839,10 +16868,10 @@
         <v>26</v>
       </c>
       <c r="G273" s="9" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H273" s="9" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I273" s="9"/>
       <c r="J273" s="8">
@@ -16858,13 +16887,13 @@
         <v>26</v>
       </c>
       <c r="N273" s="9" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="O273" s="9" t="s">
         <v>174</v>
       </c>
       <c r="P273" s="9" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="Q273" s="9"/>
       <c r="R273" s="9"/>
@@ -16874,14 +16903,14 @@
     </row>
     <row r="274" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A274" s="4" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B274" s="5">
         <v>46132.63427122685</v>
       </c>
       <c r="C274" s="6"/>
       <c r="D274" s="5">
-        <v>46133.65414835648</v>
+        <v>46196.91451931713</v>
       </c>
       <c r="E274" s="6" t="s">
         <v>174</v>
@@ -16890,10 +16919,10 @@
         <v>26</v>
       </c>
       <c r="G274" s="6" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H274" s="6" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I274" s="6"/>
       <c r="J274" s="5">
@@ -16909,13 +16938,13 @@
         <v>26</v>
       </c>
       <c r="N274" s="6" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="O274" s="6" t="s">
         <v>174</v>
       </c>
       <c r="P274" s="6" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="Q274" s="6"/>
       <c r="R274" s="6"/>
@@ -16925,14 +16954,14 @@
     </row>
     <row r="275" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A275" s="7" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B275" s="8">
         <v>46132.634276365745</v>
       </c>
       <c r="C275" s="9"/>
       <c r="D275" s="8">
-        <v>46133.654150104165</v>
+        <v>46196.914524629625</v>
       </c>
       <c r="E275" s="9" t="s">
         <v>174</v>
@@ -16941,10 +16970,10 @@
         <v>26</v>
       </c>
       <c r="G275" s="9" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H275" s="9" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I275" s="9"/>
       <c r="J275" s="8">
@@ -16960,13 +16989,13 @@
         <v>26</v>
       </c>
       <c r="N275" s="9" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="O275" s="9" t="s">
         <v>174</v>
       </c>
       <c r="P275" s="9" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="Q275" s="9"/>
       <c r="R275" s="9"/>
@@ -16976,14 +17005,14 @@
     </row>
     <row r="276" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A276" s="4" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B276" s="5">
         <v>46132.63428099537</v>
       </c>
       <c r="C276" s="6"/>
       <c r="D276" s="5">
-        <v>46133.65415180556</v>
+        <v>46196.91452907407</v>
       </c>
       <c r="E276" s="6" t="s">
         <v>174</v>
@@ -16992,10 +17021,10 @@
         <v>26</v>
       </c>
       <c r="G276" s="6" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H276" s="6" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I276" s="6"/>
       <c r="J276" s="5">
@@ -17011,13 +17040,13 @@
         <v>26</v>
       </c>
       <c r="N276" s="6" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="O276" s="6" t="s">
         <v>174</v>
       </c>
       <c r="P276" s="6" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="Q276" s="6"/>
       <c r="R276" s="6"/>
@@ -17027,14 +17056,14 @@
     </row>
     <row r="277" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A277" s="7" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B277" s="8">
         <v>46132.63428524305</v>
       </c>
       <c r="C277" s="9"/>
       <c r="D277" s="8">
-        <v>46133.65415340278</v>
+        <v>46196.91453917824</v>
       </c>
       <c r="E277" s="9" t="s">
         <v>174</v>
@@ -17043,10 +17072,10 @@
         <v>26</v>
       </c>
       <c r="G277" s="9" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H277" s="9" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I277" s="9"/>
       <c r="J277" s="8">
@@ -17062,13 +17091,13 @@
         <v>26</v>
       </c>
       <c r="N277" s="9" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="O277" s="9" t="s">
         <v>174</v>
       </c>
       <c r="P277" s="9" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="Q277" s="9"/>
       <c r="R277" s="9"/>
@@ -17078,14 +17107,14 @@
     </row>
     <row r="278" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A278" s="4" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B278" s="5">
         <v>46132.63429103009</v>
       </c>
       <c r="C278" s="6"/>
       <c r="D278" s="5">
-        <v>46133.65415512731</v>
+        <v>46196.91454204862</v>
       </c>
       <c r="E278" s="6" t="s">
         <v>174</v>
@@ -17094,10 +17123,10 @@
         <v>26</v>
       </c>
       <c r="G278" s="6" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H278" s="6" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I278" s="6"/>
       <c r="J278" s="5">
@@ -17113,13 +17142,13 @@
         <v>26</v>
       </c>
       <c r="N278" s="6" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="O278" s="6" t="s">
         <v>174</v>
       </c>
       <c r="P278" s="6" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="Q278" s="6"/>
       <c r="R278" s="6"/>
@@ -17129,14 +17158,14 @@
     </row>
     <row r="279" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A279" s="7" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B279" s="8">
         <v>46132.63429523148</v>
       </c>
       <c r="C279" s="9"/>
       <c r="D279" s="8">
-        <v>46133.654156793986</v>
+        <v>46196.914551724534</v>
       </c>
       <c r="E279" s="9" t="s">
         <v>174</v>
@@ -17145,10 +17174,10 @@
         <v>26</v>
       </c>
       <c r="G279" s="9" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H279" s="9" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I279" s="9"/>
       <c r="J279" s="8">
@@ -17164,13 +17193,13 @@
         <v>26</v>
       </c>
       <c r="N279" s="9" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="O279" s="9" t="s">
         <v>174</v>
       </c>
       <c r="P279" s="9" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="Q279" s="9"/>
       <c r="R279" s="9"/>
@@ -17180,14 +17209,14 @@
     </row>
     <row r="280" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A280" s="4" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B280" s="5">
         <v>46132.63430358796</v>
       </c>
       <c r="C280" s="6"/>
       <c r="D280" s="5">
-        <v>46133.654158703706</v>
+        <v>46196.91457195602</v>
       </c>
       <c r="E280" s="6" t="s">
         <v>174</v>
@@ -17196,10 +17225,10 @@
         <v>26</v>
       </c>
       <c r="G280" s="6" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H280" s="6" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I280" s="6"/>
       <c r="J280" s="5">
@@ -17215,13 +17244,13 @@
         <v>26</v>
       </c>
       <c r="N280" s="6" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="O280" s="6" t="s">
         <v>174</v>
       </c>
       <c r="P280" s="6" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="Q280" s="6"/>
       <c r="R280" s="6"/>
@@ -17231,14 +17260,14 @@
     </row>
     <row r="281" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A281" s="7" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B281" s="8">
         <v>46132.63431148148</v>
       </c>
       <c r="C281" s="9"/>
       <c r="D281" s="8">
-        <v>46133.65416041667</v>
+        <v>46196.91458070602</v>
       </c>
       <c r="E281" s="9" t="s">
         <v>174</v>
@@ -17247,10 +17276,10 @@
         <v>26</v>
       </c>
       <c r="G281" s="9" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H281" s="9" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I281" s="9"/>
       <c r="J281" s="8">
@@ -17266,13 +17295,13 @@
         <v>26</v>
       </c>
       <c r="N281" s="9" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="O281" s="9" t="s">
         <v>174</v>
       </c>
       <c r="P281" s="9" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="Q281" s="9"/>
       <c r="R281" s="9"/>
@@ -17282,14 +17311,14 @@
     </row>
     <row r="282" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A282" s="4" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B282" s="5">
         <v>46132.63437663195</v>
       </c>
       <c r="C282" s="6"/>
       <c r="D282" s="5">
-        <v>46133.654162604165</v>
+        <v>46196.91461018518</v>
       </c>
       <c r="E282" s="6" t="s">
         <v>174</v>
@@ -17298,10 +17327,10 @@
         <v>26</v>
       </c>
       <c r="G282" s="6" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H282" s="6" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I282" s="6"/>
       <c r="J282" s="5">
@@ -17317,13 +17346,13 @@
         <v>26</v>
       </c>
       <c r="N282" s="6" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="O282" s="6" t="s">
         <v>174</v>
       </c>
       <c r="P282" s="6" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="Q282" s="6"/>
       <c r="R282" s="6"/>
@@ -17333,7 +17362,7 @@
     </row>
     <row r="283" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A283" s="7" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B283" s="8">
         <v>46132.589037604164</v>
@@ -17343,7 +17372,7 @@
         <v>46133.59235670139</v>
       </c>
       <c r="E283" s="9" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="F283" s="9" t="s">
         <v>25</v>
@@ -17367,7 +17396,7 @@
         <v>26</v>
       </c>
       <c r="O283" s="9" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="P283" s="9" t="s">
         <v>26</v>
@@ -17380,7 +17409,7 @@
     </row>
     <row r="284" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A284" s="4" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B284" s="5">
         <v>46132.5890406713</v>
@@ -17390,16 +17419,16 @@
         <v>46134.57925581018</v>
       </c>
       <c r="E284" s="6" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="F284" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G284" s="6" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H284" s="6" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="I284" s="5">
         <v>46232</v>
@@ -17417,13 +17446,13 @@
         <v>26</v>
       </c>
       <c r="N284" s="6" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="O284" s="6" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="P284" s="6" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="Q284" s="5">
         <v>46240</v>
@@ -17443,7 +17472,7 @@
     </row>
     <row r="285" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A285" s="7" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B285" s="8">
         <v>46132.58904559028</v>
@@ -17453,16 +17482,16 @@
         <v>46134.57925902778</v>
       </c>
       <c r="E285" s="9" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="F285" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G285" s="9" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H285" s="9" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="I285" s="8">
         <v>46232</v>
@@ -17480,13 +17509,13 @@
         <v>26</v>
       </c>
       <c r="N285" s="9" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="O285" s="9" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="P285" s="9" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="Q285" s="8">
         <v>46240</v>

--- a/data/50001541 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001541 - XEMORTIZ MINERA FRISCO.xlsx
@@ -2284,13 +2284,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46132.58858372685</v>
+        <v>46132.42191706019</v>
       </c>
       <c r="C4" s="5">
-        <v>46133.88825172454</v>
+        <v>46133.721585057865</v>
       </c>
       <c r="D4" s="5">
-        <v>46134.54185469907</v>
+        <v>46134.37518803241</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -2333,13 +2333,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46132.58866263889</v>
+        <v>46132.421995972225</v>
       </c>
       <c r="C5" s="8">
-        <v>46140.62775625</v>
+        <v>46140.46108958333</v>
       </c>
       <c r="D5" s="8">
-        <v>46140.627878831016</v>
+        <v>46140.46121216435</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -2398,13 +2398,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46132.58866574074</v>
+        <v>46132.421999074075</v>
       </c>
       <c r="C6" s="5">
-        <v>46133.89152399305</v>
+        <v>46133.72485732639</v>
       </c>
       <c r="D6" s="5">
-        <v>46133.891525370374</v>
+        <v>46133.7248587037</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -2463,13 +2463,13 @@
         <v>36</v>
       </c>
       <c r="B7" s="8">
-        <v>46132.58866841435</v>
+        <v>46132.422001747684</v>
       </c>
       <c r="C7" s="8">
-        <v>46133.89329033565</v>
+        <v>46133.72662366898</v>
       </c>
       <c r="D7" s="8">
-        <v>46133.893291562505</v>
+        <v>46133.72662489583</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>37</v>
@@ -2528,13 +2528,13 @@
         <v>38</v>
       </c>
       <c r="B8" s="5">
-        <v>46132.58867106482</v>
+        <v>46132.42200439815</v>
       </c>
       <c r="C8" s="5">
-        <v>46133.89329489583</v>
+        <v>46133.72662822917</v>
       </c>
       <c r="D8" s="5">
-        <v>46133.89329634259</v>
+        <v>46133.726629675926</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>39</v>
@@ -2593,13 +2593,13 @@
         <v>41</v>
       </c>
       <c r="B9" s="8">
-        <v>46132.58867449074</v>
+        <v>46132.422007824076</v>
       </c>
       <c r="C9" s="8">
-        <v>46133.89330225694</v>
+        <v>46133.72663559028</v>
       </c>
       <c r="D9" s="8">
-        <v>46133.89330362268</v>
+        <v>46133.726636956024</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>42</v>
@@ -2658,11 +2658,11 @@
         <v>43</v>
       </c>
       <c r="B10" s="5">
-        <v>46132.58858978009</v>
+        <v>46132.42192311343</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46183.8702434838</v>
+        <v>46183.70357681713</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>44</v>
@@ -2705,13 +2705,13 @@
         <v>46</v>
       </c>
       <c r="B11" s="8">
-        <v>46132.58867828704</v>
+        <v>46132.422011620365</v>
       </c>
       <c r="C11" s="8">
-        <v>46183.87023324074</v>
+        <v>46183.70356657407</v>
       </c>
       <c r="D11" s="8">
-        <v>46183.87025299769</v>
+        <v>46183.703586331016</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>47</v>
@@ -2770,13 +2770,13 @@
         <v>49</v>
       </c>
       <c r="B12" s="5">
-        <v>46132.588683553244</v>
+        <v>46132.42201688657</v>
       </c>
       <c r="C12" s="5">
-        <v>46157.54164365741</v>
+        <v>46157.374976990744</v>
       </c>
       <c r="D12" s="5">
-        <v>46157.541660393515</v>
+        <v>46157.37499372685</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>50</v>
@@ -2835,13 +2835,13 @@
         <v>52</v>
       </c>
       <c r="B13" s="8">
-        <v>46132.588688738426</v>
+        <v>46132.422022071754</v>
       </c>
       <c r="C13" s="8">
-        <v>46175.72854943287</v>
+        <v>46175.561882766204</v>
       </c>
       <c r="D13" s="8">
-        <v>46175.72856798611</v>
+        <v>46175.561901319445</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>53</v>
@@ -2900,11 +2900,11 @@
         <v>55</v>
       </c>
       <c r="B14" s="5">
-        <v>46132.58869379629</v>
+        <v>46132.42202712963</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46142.18625708333</v>
+        <v>46142.01959041666</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>56</v>
@@ -2963,13 +2963,13 @@
         <v>59</v>
       </c>
       <c r="B15" s="8">
-        <v>46132.58859509259</v>
+        <v>46132.42192842593</v>
       </c>
       <c r="C15" s="8">
-        <v>46196.640665405095</v>
+        <v>46196.473998738424</v>
       </c>
       <c r="D15" s="8">
-        <v>46196.64067877315</v>
+        <v>46196.47401210648</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>60</v>
@@ -3016,13 +3016,13 @@
         <v>62</v>
       </c>
       <c r="B16" s="5">
-        <v>46132.58869895834</v>
+        <v>46132.422032291666</v>
       </c>
       <c r="C16" s="5">
-        <v>46157.54328243056</v>
+        <v>46157.37661576389</v>
       </c>
       <c r="D16" s="5">
-        <v>46157.54329741898</v>
+        <v>46157.37663075232</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>63</v>
@@ -3081,13 +3081,13 @@
         <v>65</v>
       </c>
       <c r="B17" s="8">
-        <v>46132.58870399305</v>
+        <v>46132.42203732639</v>
       </c>
       <c r="C17" s="8">
-        <v>46157.5417655787</v>
+        <v>46157.37509891204</v>
       </c>
       <c r="D17" s="8">
-        <v>46157.54178225694</v>
+        <v>46157.37511559028</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>66</v>
@@ -3146,13 +3146,13 @@
         <v>69</v>
       </c>
       <c r="B18" s="5">
-        <v>46132.588709097225</v>
+        <v>46132.42204243055</v>
       </c>
       <c r="C18" s="5">
-        <v>46183.8703028125</v>
+        <v>46183.70363614583</v>
       </c>
       <c r="D18" s="5">
-        <v>46183.87031994213</v>
+        <v>46183.703653275465</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>70</v>
@@ -3211,13 +3211,13 @@
         <v>72</v>
       </c>
       <c r="B19" s="8">
-        <v>46132.588713819445</v>
+        <v>46132.42204715278</v>
       </c>
       <c r="C19" s="8">
-        <v>46140.62659734953</v>
+        <v>46140.459930682875</v>
       </c>
       <c r="D19" s="8">
-        <v>46191.91766813658</v>
+        <v>46191.75100146991</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>73</v>
@@ -3276,13 +3276,13 @@
         <v>78</v>
       </c>
       <c r="B20" s="5">
-        <v>46132.62809104167</v>
+        <v>46132.461424375</v>
       </c>
       <c r="C20" s="5">
-        <v>46140.62653898148</v>
+        <v>46140.459872314816</v>
       </c>
       <c r="D20" s="5">
-        <v>46191.91766824074</v>
+        <v>46191.75100157407</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>79</v>
@@ -3341,13 +3341,13 @@
         <v>81</v>
       </c>
       <c r="B21" s="8">
-        <v>46132.62798736111</v>
+        <v>46132.46132069445</v>
       </c>
       <c r="C21" s="8">
-        <v>46196.64064614583</v>
+        <v>46196.47397947917</v>
       </c>
       <c r="D21" s="8">
-        <v>46196.6430977662</v>
+        <v>46196.47643109954</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>82</v>
@@ -3406,13 +3406,13 @@
         <v>84</v>
       </c>
       <c r="B22" s="5">
-        <v>46132.6280453125</v>
+        <v>46132.461378645836</v>
       </c>
       <c r="C22" s="5">
-        <v>46140.626452083336</v>
+        <v>46140.459785416664</v>
       </c>
       <c r="D22" s="5">
-        <v>46191.91766803241</v>
+        <v>46191.751001365745</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>85</v>
@@ -3471,11 +3471,11 @@
         <v>87</v>
       </c>
       <c r="B23" s="8">
-        <v>46132.588600312505</v>
+        <v>46132.42193364583</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="8">
-        <v>46191.90919450231</v>
+        <v>46191.74252783565</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>88</v>
@@ -3520,13 +3520,13 @@
         <v>90</v>
       </c>
       <c r="B24" s="5">
-        <v>46132.588719548614</v>
+        <v>46132.42205288194</v>
       </c>
       <c r="C24" s="5">
-        <v>46157.543090798616</v>
+        <v>46157.376424131944</v>
       </c>
       <c r="D24" s="5">
-        <v>46157.54357984954</v>
+        <v>46157.376913182874</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>91</v>
@@ -3585,13 +3585,13 @@
         <v>95</v>
       </c>
       <c r="B25" s="8">
-        <v>46132.588724236106</v>
+        <v>46132.42205756945</v>
       </c>
       <c r="C25" s="8">
-        <v>46157.543350023145</v>
+        <v>46157.37668335648</v>
       </c>
       <c r="D25" s="8">
-        <v>46157.54335157407</v>
+        <v>46157.37668490741</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>96</v>
@@ -3646,13 +3646,13 @@
         <v>102</v>
       </c>
       <c r="B26" s="5">
-        <v>46132.58872892361</v>
+        <v>46132.42206225694</v>
       </c>
       <c r="C26" s="5">
-        <v>46157.54338710648</v>
+        <v>46157.37672043982</v>
       </c>
       <c r="D26" s="5">
-        <v>46157.543388425926</v>
+        <v>46157.376721759254</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>103</v>
@@ -3707,13 +3707,13 @@
         <v>105</v>
       </c>
       <c r="B27" s="8">
-        <v>46132.58873398148</v>
+        <v>46132.422067314816</v>
       </c>
       <c r="C27" s="8">
-        <v>46157.541870671295</v>
+        <v>46157.37520400463</v>
       </c>
       <c r="D27" s="8">
-        <v>46162.175749050926</v>
+        <v>46162.00908238426</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>106</v>
@@ -3772,13 +3772,13 @@
         <v>108</v>
       </c>
       <c r="B28" s="5">
-        <v>46132.58873894676</v>
+        <v>46132.4220722801</v>
       </c>
       <c r="C28" s="5">
-        <v>46157.54181472222</v>
+        <v>46157.37514805555</v>
       </c>
       <c r="D28" s="5">
-        <v>46157.541816655095</v>
+        <v>46157.375149988424</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>109</v>
@@ -3833,13 +3833,13 @@
         <v>111</v>
       </c>
       <c r="B29" s="8">
-        <v>46132.58874392361</v>
+        <v>46132.422077256946</v>
       </c>
       <c r="C29" s="8">
-        <v>46157.541855682866</v>
+        <v>46157.3751890162</v>
       </c>
       <c r="D29" s="8">
-        <v>46157.54185689815</v>
+        <v>46157.37519023148</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>112</v>
@@ -3894,13 +3894,13 @@
         <v>114</v>
       </c>
       <c r="B30" s="5">
-        <v>46132.58874878472</v>
+        <v>46132.42208211806</v>
       </c>
       <c r="C30" s="5">
-        <v>46191.90915011574</v>
+        <v>46191.742483449074</v>
       </c>
       <c r="D30" s="5">
-        <v>46191.90918642361</v>
+        <v>46191.74251975694</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>115</v>
@@ -3959,13 +3959,13 @@
         <v>117</v>
       </c>
       <c r="B31" s="8">
-        <v>46132.58875335648</v>
+        <v>46132.42208668981</v>
       </c>
       <c r="C31" s="8">
-        <v>46191.9085853125</v>
+        <v>46191.74191864583</v>
       </c>
       <c r="D31" s="8">
-        <v>46191.908590590276</v>
+        <v>46191.74192392361</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>118</v>
@@ -4020,13 +4020,13 @@
         <v>120</v>
       </c>
       <c r="B32" s="5">
-        <v>46132.58876267361</v>
+        <v>46132.42209600694</v>
       </c>
       <c r="C32" s="5">
-        <v>46191.909130879634</v>
+        <v>46191.74246421296</v>
       </c>
       <c r="D32" s="5">
-        <v>46191.90913269676</v>
+        <v>46191.74246603009</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>121</v>
@@ -4081,13 +4081,13 @@
         <v>124</v>
       </c>
       <c r="B33" s="8">
-        <v>46132.58875789352</v>
+        <v>46132.42209122685</v>
       </c>
       <c r="C33" s="8">
-        <v>46191.90908200231</v>
+        <v>46191.74241533565</v>
       </c>
       <c r="D33" s="8">
-        <v>46191.90908534722</v>
+        <v>46191.74241868056</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>122</v>
@@ -4142,13 +4142,13 @@
         <v>126</v>
       </c>
       <c r="B34" s="5">
-        <v>46132.588767037036</v>
+        <v>46132.42210037037</v>
       </c>
       <c r="C34" s="5">
-        <v>46140.62699269676</v>
+        <v>46140.460326030094</v>
       </c>
       <c r="D34" s="5">
-        <v>46178.16851243055</v>
+        <v>46178.00184576389</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>127</v>
@@ -4207,13 +4207,13 @@
         <v>131</v>
       </c>
       <c r="B35" s="8">
-        <v>46132.58877138889</v>
+        <v>46132.42210472222</v>
       </c>
       <c r="C35" s="8">
-        <v>46140.6269006713</v>
+        <v>46140.460234004626</v>
       </c>
       <c r="D35" s="8">
-        <v>46140.62690204861</v>
+        <v>46140.46023538194</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>132</v>
@@ -4268,13 +4268,13 @@
         <v>134</v>
       </c>
       <c r="B36" s="5">
-        <v>46132.58877590278</v>
+        <v>46132.42210923611</v>
       </c>
       <c r="C36" s="5">
-        <v>46140.62693832176</v>
+        <v>46140.460271655094</v>
       </c>
       <c r="D36" s="5">
-        <v>46140.62694037037</v>
+        <v>46140.460273703706</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>135</v>
@@ -4329,13 +4329,13 @@
         <v>137</v>
       </c>
       <c r="B37" s="8">
-        <v>46132.62683954861</v>
+        <v>46132.46017288194</v>
       </c>
       <c r="C37" s="8">
-        <v>46140.62696703704</v>
+        <v>46140.46030037037</v>
       </c>
       <c r="D37" s="8">
-        <v>46178.16851354166</v>
+        <v>46178.001846875</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>138</v>
@@ -4394,13 +4394,13 @@
         <v>140</v>
       </c>
       <c r="B38" s="5">
-        <v>46132.62712936343</v>
+        <v>46132.46046269676</v>
       </c>
       <c r="C38" s="5">
-        <v>46140.62678560185</v>
+        <v>46140.46011893518</v>
       </c>
       <c r="D38" s="5">
-        <v>46140.62678680556</v>
+        <v>46140.46012013889</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>80</v>
@@ -4449,13 +4449,13 @@
         <v>142</v>
       </c>
       <c r="B39" s="8">
-        <v>46132.62726841435</v>
+        <v>46132.46060174768</v>
       </c>
       <c r="C39" s="8">
-        <v>46140.62682609954</v>
+        <v>46140.46015943287</v>
       </c>
       <c r="D39" s="8">
-        <v>46140.62682733797</v>
+        <v>46140.4601606713</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>143</v>
@@ -4504,13 +4504,13 @@
         <v>145</v>
       </c>
       <c r="B40" s="5">
-        <v>46132.62697065972</v>
+        <v>46132.46030399305</v>
       </c>
       <c r="C40" s="5">
-        <v>46147.89775949074</v>
+        <v>46147.73109282408</v>
       </c>
       <c r="D40" s="5">
-        <v>46178.16851233796</v>
+        <v>46178.0018456713</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>146</v>
@@ -4569,13 +4569,13 @@
         <v>148</v>
       </c>
       <c r="B41" s="8">
-        <v>46132.62753372685</v>
+        <v>46132.46086706019</v>
       </c>
       <c r="C41" s="8">
-        <v>46140.6270855787</v>
+        <v>46140.46041891204</v>
       </c>
       <c r="D41" s="8">
-        <v>46140.62708736111</v>
+        <v>46140.46042069445</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>86</v>
@@ -4624,13 +4624,13 @@
         <v>150</v>
       </c>
       <c r="B42" s="5">
-        <v>46132.627615798614</v>
+        <v>46132.46094913194</v>
       </c>
       <c r="C42" s="5">
-        <v>46147.89774630787</v>
+        <v>46147.731079641206</v>
       </c>
       <c r="D42" s="5">
-        <v>46147.89774797454</v>
+        <v>46147.731081307866</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>151</v>
@@ -4679,11 +4679,11 @@
         <v>153</v>
       </c>
       <c r="B43" s="8">
-        <v>46132.58860650463</v>
+        <v>46132.421939837965</v>
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="8">
-        <v>46191.91760722222</v>
+        <v>46191.750940555554</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>154</v>
@@ -4726,13 +4726,13 @@
         <v>156</v>
       </c>
       <c r="B44" s="5">
-        <v>46132.58883957176</v>
+        <v>46132.42217290509</v>
       </c>
       <c r="C44" s="5">
-        <v>46175.72865314815</v>
+        <v>46175.56198648148</v>
       </c>
       <c r="D44" s="5">
-        <v>46175.728669178236</v>
+        <v>46175.56200251158</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>157</v>
@@ -4791,13 +4791,13 @@
         <v>161</v>
       </c>
       <c r="B45" s="8">
-        <v>46132.58884677083</v>
+        <v>46132.42218010417</v>
       </c>
       <c r="C45" s="8">
-        <v>46191.91739681713</v>
+        <v>46191.75073015047</v>
       </c>
       <c r="D45" s="8">
-        <v>46191.917420451384</v>
+        <v>46191.75075378473</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>162</v>
@@ -4856,13 +4856,13 @@
         <v>165</v>
       </c>
       <c r="B46" s="5">
-        <v>46132.5888534838</v>
+        <v>46132.42218681713</v>
       </c>
       <c r="C46" s="5">
-        <v>46191.917582326394</v>
+        <v>46191.75091565972</v>
       </c>
       <c r="D46" s="5">
-        <v>46191.91760793982</v>
+        <v>46191.750941273145</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>76</v>
@@ -4919,11 +4919,11 @@
         <v>167</v>
       </c>
       <c r="B47" s="8">
-        <v>46132.58886101852</v>
+        <v>46132.42219435185</v>
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="8">
-        <v>46134.580577280096</v>
+        <v>46134.413910613424</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>168</v>
@@ -4980,11 +4980,11 @@
         <v>172</v>
       </c>
       <c r="B48" s="5">
-        <v>46132.634550902774</v>
+        <v>46132.46788423611</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46196.91191069444</v>
+        <v>46196.74524402778</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>173</v>
@@ -5031,11 +5031,11 @@
         <v>176</v>
       </c>
       <c r="B49" s="8">
-        <v>46132.634558564816</v>
+        <v>46132.46789189815</v>
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="8">
-        <v>46196.91191847222</v>
+        <v>46196.74525180555</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>177</v>
@@ -5082,11 +5082,11 @@
         <v>179</v>
       </c>
       <c r="B50" s="5">
-        <v>46132.634567546294</v>
+        <v>46132.46790087963</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46196.911927002315</v>
+        <v>46196.74526033565</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>180</v>
@@ -5133,11 +5133,11 @@
         <v>181</v>
       </c>
       <c r="B51" s="8">
-        <v>46132.634571875</v>
+        <v>46132.46790520834</v>
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="8">
-        <v>46196.91193416667</v>
+        <v>46196.745267499995</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>182</v>
@@ -5184,11 +5184,11 @@
         <v>183</v>
       </c>
       <c r="B52" s="5">
-        <v>46132.6345777199</v>
+        <v>46132.467911053245</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46196.91194335648</v>
+        <v>46196.74527668981</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>184</v>
@@ -5235,11 +5235,11 @@
         <v>185</v>
       </c>
       <c r="B53" s="8">
-        <v>46132.634582071754</v>
+        <v>46132.4679154051</v>
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="8">
-        <v>46196.911952731476</v>
+        <v>46196.74528606482</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>186</v>
@@ -5286,11 +5286,11 @@
         <v>187</v>
       </c>
       <c r="B54" s="5">
-        <v>46132.63458603009</v>
+        <v>46132.46791936342</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46196.91195940972</v>
+        <v>46196.74529274306</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>188</v>
@@ -5337,11 +5337,11 @@
         <v>190</v>
       </c>
       <c r="B55" s="8">
-        <v>46132.63459168981</v>
+        <v>46132.46792502315</v>
       </c>
       <c r="C55" s="9"/>
       <c r="D55" s="8">
-        <v>46196.91196953703</v>
+        <v>46196.745302870375</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>191</v>
@@ -5388,11 +5388,11 @@
         <v>192</v>
       </c>
       <c r="B56" s="5">
-        <v>46132.634597094904</v>
+        <v>46132.46793042824</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46196.91198518519</v>
+        <v>46196.745318518515</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>193</v>
@@ -5439,11 +5439,11 @@
         <v>194</v>
       </c>
       <c r="B57" s="8">
-        <v>46132.6346025463</v>
+        <v>46132.46793587963</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46196.912005659724</v>
+        <v>46196.74533899306</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>195</v>
@@ -5490,11 +5490,11 @@
         <v>196</v>
       </c>
       <c r="B58" s="5">
-        <v>46132.634674050925</v>
+        <v>46132.46800738426</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46196.912017662034</v>
+        <v>46196.74535099537</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>197</v>
@@ -5541,11 +5541,11 @@
         <v>198</v>
       </c>
       <c r="B59" s="8">
-        <v>46132.63468899306</v>
+        <v>46132.468022326386</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46196.91202767361</v>
+        <v>46196.74536100695</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>199</v>
@@ -5592,11 +5592,11 @@
         <v>200</v>
       </c>
       <c r="B60" s="5">
-        <v>46132.63470766204</v>
+        <v>46132.46804099537</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46196.912036967595</v>
+        <v>46196.74537030092</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>201</v>
@@ -5643,11 +5643,11 @@
         <v>202</v>
       </c>
       <c r="B61" s="8">
-        <v>46132.634719884256</v>
+        <v>46132.46805321759</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46196.91204791667</v>
+        <v>46196.74538125</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>203</v>
@@ -5694,11 +5694,11 @@
         <v>204</v>
       </c>
       <c r="B62" s="5">
-        <v>46132.634727847224</v>
+        <v>46132.46806118055</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46196.9120665625</v>
+        <v>46196.74539989584</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>205</v>
@@ -5745,11 +5745,11 @@
         <v>207</v>
       </c>
       <c r="B63" s="8">
-        <v>46132.63460722222</v>
+        <v>46132.46794055555</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46196.91208912037</v>
+        <v>46196.74542245371</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>208</v>
@@ -5796,13 +5796,13 @@
         <v>210</v>
       </c>
       <c r="B64" s="5">
-        <v>46132.64721917824</v>
+        <v>46132.48055251157</v>
       </c>
       <c r="C64" s="5">
-        <v>46157.49397792824</v>
+        <v>46157.32731126157</v>
       </c>
       <c r="D64" s="5">
-        <v>46157.493989166665</v>
+        <v>46157.3273225</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>211</v>
@@ -5849,13 +5849,13 @@
         <v>213</v>
       </c>
       <c r="B65" s="8">
-        <v>46132.624842916666</v>
+        <v>46132.45817625</v>
       </c>
       <c r="C65" s="8">
-        <v>46157.493824652774</v>
+        <v>46157.32715798611</v>
       </c>
       <c r="D65" s="8">
-        <v>46182.18354462963</v>
+        <v>46182.01687796296</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>214</v>
@@ -5914,13 +5914,13 @@
         <v>216</v>
       </c>
       <c r="B66" s="5">
-        <v>46132.62490728009</v>
+        <v>46132.45824061343</v>
       </c>
       <c r="C66" s="5">
-        <v>46157.49385349537</v>
+        <v>46157.327186828705</v>
       </c>
       <c r="D66" s="5">
-        <v>46182.18354459491</v>
+        <v>46182.01687792824</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>217</v>
@@ -5979,13 +5979,13 @@
         <v>219</v>
       </c>
       <c r="B67" s="8">
-        <v>46132.62495362268</v>
+        <v>46132.45828695602</v>
       </c>
       <c r="C67" s="8">
-        <v>46157.49386780093</v>
+        <v>46157.32720113426</v>
       </c>
       <c r="D67" s="8">
-        <v>46182.183544768515</v>
+        <v>46182.01687810185</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>220</v>
@@ -6044,13 +6044,13 @@
         <v>222</v>
       </c>
       <c r="B68" s="5">
-        <v>46132.70742302084</v>
+        <v>46132.54075635417</v>
       </c>
       <c r="C68" s="5">
-        <v>46157.493948125004</v>
+        <v>46157.32728145833</v>
       </c>
       <c r="D68" s="5">
-        <v>46184.203094386576</v>
+        <v>46184.03642771991</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>223</v>
@@ -6109,13 +6109,13 @@
         <v>227</v>
       </c>
       <c r="B69" s="8">
-        <v>46132.70752974537</v>
+        <v>46132.5408630787</v>
       </c>
       <c r="C69" s="8">
-        <v>46157.49395293981</v>
+        <v>46157.32728627315</v>
       </c>
       <c r="D69" s="8">
-        <v>46184.20309802084</v>
+        <v>46184.036431354165</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>228</v>
@@ -6174,13 +6174,13 @@
         <v>230</v>
       </c>
       <c r="B70" s="5">
-        <v>46132.70760050926</v>
+        <v>46132.540933842596</v>
       </c>
       <c r="C70" s="5">
-        <v>46157.49396020833</v>
+        <v>46157.32729354167</v>
       </c>
       <c r="D70" s="5">
-        <v>46184.203094212964</v>
+        <v>46184.03642754629</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>231</v>
@@ -6239,11 +6239,11 @@
         <v>232</v>
       </c>
       <c r="B71" s="8">
-        <v>46132.58888190972</v>
+        <v>46132.42221524306</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46196.691984930556</v>
+        <v>46196.525318263884</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>233</v>
@@ -6286,13 +6286,13 @@
         <v>235</v>
       </c>
       <c r="B72" s="5">
-        <v>46132.588885185185</v>
+        <v>46132.42221851852</v>
       </c>
       <c r="C72" s="5">
-        <v>46196.68414012731</v>
+        <v>46196.51747346065</v>
       </c>
       <c r="D72" s="5">
-        <v>46196.68415487268</v>
+        <v>46196.517488206024</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>83</v>
@@ -6351,13 +6351,13 @@
         <v>239</v>
       </c>
       <c r="B73" s="8">
-        <v>46132.58889042824</v>
+        <v>46132.422223761576</v>
       </c>
       <c r="C73" s="8">
-        <v>46196.69197697917</v>
+        <v>46196.5253103125</v>
       </c>
       <c r="D73" s="8">
-        <v>46196.692663379625</v>
+        <v>46196.52599671297</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>240</v>
@@ -6416,13 +6416,13 @@
         <v>242</v>
       </c>
       <c r="B74" s="5">
-        <v>46132.631278472225</v>
+        <v>46132.46461180555</v>
       </c>
       <c r="C74" s="5">
-        <v>46196.69130792824</v>
+        <v>46196.524641261574</v>
       </c>
       <c r="D74" s="5">
-        <v>46196.69266049768</v>
+        <v>46196.52599383102</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>174</v>
@@ -6471,13 +6471,13 @@
         <v>245</v>
       </c>
       <c r="B75" s="8">
-        <v>46132.63129450232</v>
+        <v>46132.46462783565</v>
       </c>
       <c r="C75" s="8">
-        <v>46196.69160608796</v>
+        <v>46196.524939421295</v>
       </c>
       <c r="D75" s="8">
-        <v>46196.692844907404</v>
+        <v>46196.52617824074</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>174</v>
@@ -6526,13 +6526,13 @@
         <v>246</v>
       </c>
       <c r="B76" s="5">
-        <v>46132.63130252315</v>
+        <v>46132.46463585648</v>
       </c>
       <c r="C76" s="5">
-        <v>46196.69194896991</v>
+        <v>46196.52528230324</v>
       </c>
       <c r="D76" s="5">
-        <v>46196.69317986111</v>
+        <v>46196.52651319445</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>174</v>
@@ -6581,13 +6581,13 @@
         <v>249</v>
       </c>
       <c r="B77" s="8">
-        <v>46132.63130869213</v>
+        <v>46132.46464202546</v>
       </c>
       <c r="C77" s="8">
-        <v>46196.69194981482</v>
+        <v>46196.52528314815</v>
       </c>
       <c r="D77" s="8">
-        <v>46196.693142592594</v>
+        <v>46196.52647592593</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>174</v>
@@ -6636,13 +6636,13 @@
         <v>250</v>
       </c>
       <c r="B78" s="5">
-        <v>46132.631314467595</v>
+        <v>46132.46464780092</v>
       </c>
       <c r="C78" s="5">
-        <v>46196.691950416665</v>
+        <v>46196.52528375</v>
       </c>
       <c r="D78" s="5">
-        <v>46196.693131458334</v>
+        <v>46196.52646479166</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>174</v>
@@ -6691,13 +6691,13 @@
         <v>252</v>
       </c>
       <c r="B79" s="8">
-        <v>46132.6313205787</v>
+        <v>46132.46465391204</v>
       </c>
       <c r="C79" s="8">
-        <v>46196.69195099537</v>
+        <v>46196.5252843287</v>
       </c>
       <c r="D79" s="8">
-        <v>46196.693120717595</v>
+        <v>46196.52645405092</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>174</v>
@@ -6746,13 +6746,13 @@
         <v>254</v>
       </c>
       <c r="B80" s="5">
-        <v>46132.6313259375</v>
+        <v>46132.46465927083</v>
       </c>
       <c r="C80" s="5">
-        <v>46196.69195158565</v>
+        <v>46196.525284918986</v>
       </c>
       <c r="D80" s="5">
-        <v>46196.69310042824</v>
+        <v>46196.52643376157</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>174</v>
@@ -6801,13 +6801,13 @@
         <v>256</v>
       </c>
       <c r="B81" s="8">
-        <v>46132.63133041667</v>
+        <v>46132.46466375</v>
       </c>
       <c r="C81" s="8">
-        <v>46196.69195221065</v>
+        <v>46196.52528554398</v>
       </c>
       <c r="D81" s="8">
-        <v>46196.693085949075</v>
+        <v>46196.52641928241</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>174</v>
@@ -6856,13 +6856,13 @@
         <v>258</v>
       </c>
       <c r="B82" s="5">
-        <v>46132.63133645833</v>
+        <v>46132.46466979166</v>
       </c>
       <c r="C82" s="5">
-        <v>46196.69195284722</v>
+        <v>46196.52528618056</v>
       </c>
       <c r="D82" s="5">
-        <v>46196.69307368055</v>
+        <v>46196.52640701389</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>174</v>
@@ -6911,13 +6911,13 @@
         <v>259</v>
       </c>
       <c r="B83" s="8">
-        <v>46132.63134074074</v>
+        <v>46132.46467407407</v>
       </c>
       <c r="C83" s="8">
-        <v>46196.69174834491</v>
+        <v>46196.525081678235</v>
       </c>
       <c r="D83" s="8">
-        <v>46196.69306041667</v>
+        <v>46196.52639375</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>174</v>
@@ -6966,13 +6966,13 @@
         <v>261</v>
       </c>
       <c r="B84" s="5">
-        <v>46132.631346469905</v>
+        <v>46132.46467980324</v>
       </c>
       <c r="C84" s="5">
-        <v>46196.691953437505</v>
+        <v>46196.52528677083</v>
       </c>
       <c r="D84" s="5">
-        <v>46196.693049560185</v>
+        <v>46196.52638289351</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>174</v>
@@ -7021,13 +7021,13 @@
         <v>262</v>
       </c>
       <c r="B85" s="8">
-        <v>46132.631352083336</v>
+        <v>46132.464685416664</v>
       </c>
       <c r="C85" s="8">
-        <v>46196.69195403935</v>
+        <v>46196.525287372686</v>
       </c>
       <c r="D85" s="8">
-        <v>46196.6930421412</v>
+        <v>46196.52637547454</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>174</v>
@@ -7076,13 +7076,13 @@
         <v>263</v>
       </c>
       <c r="B86" s="5">
-        <v>46132.63135776621</v>
+        <v>46132.464691099536</v>
       </c>
       <c r="C86" s="5">
-        <v>46196.69195462963</v>
+        <v>46196.52528796296</v>
       </c>
       <c r="D86" s="5">
-        <v>46196.69303037037</v>
+        <v>46196.5263637037</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>174</v>
@@ -7131,13 +7131,13 @@
         <v>264</v>
       </c>
       <c r="B87" s="8">
-        <v>46132.63136296296</v>
+        <v>46132.4646962963</v>
       </c>
       <c r="C87" s="8">
-        <v>46196.6919552662</v>
+        <v>46196.525288599536</v>
       </c>
       <c r="D87" s="8">
-        <v>46196.69302122685</v>
+        <v>46196.526354560185</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>174</v>
@@ -7186,13 +7186,13 @@
         <v>266</v>
       </c>
       <c r="B88" s="5">
-        <v>46132.63136688658</v>
+        <v>46132.464700219905</v>
       </c>
       <c r="C88" s="5">
-        <v>46196.69195586805</v>
+        <v>46196.52528920139</v>
       </c>
       <c r="D88" s="5">
-        <v>46196.692995543985</v>
+        <v>46196.52632887731</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>174</v>
@@ -7241,13 +7241,13 @@
         <v>268</v>
       </c>
       <c r="B89" s="8">
-        <v>46132.63137239583</v>
+        <v>46132.464705729166</v>
       </c>
       <c r="C89" s="8">
-        <v>46196.69195645834</v>
+        <v>46196.525289791665</v>
       </c>
       <c r="D89" s="8">
-        <v>46196.69300998843</v>
+        <v>46196.52634332176</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>174</v>
@@ -7296,11 +7296,11 @@
         <v>269</v>
       </c>
       <c r="B90" s="5">
-        <v>46132.58889809028</v>
+        <v>46132.42223142361</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46196.91358532407</v>
+        <v>46196.74691865741</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>270</v>
@@ -7359,13 +7359,13 @@
         <v>272</v>
       </c>
       <c r="B91" s="8">
-        <v>46132.63147894676</v>
+        <v>46132.46481228009</v>
       </c>
       <c r="C91" s="8">
-        <v>46196.91330332176</v>
+        <v>46196.746636655094</v>
       </c>
       <c r="D91" s="8">
-        <v>46196.913305381946</v>
+        <v>46196.74663871528</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>273</v>
@@ -7414,13 +7414,13 @@
         <v>276</v>
       </c>
       <c r="B92" s="5">
-        <v>46132.63149082176</v>
+        <v>46132.46482415509</v>
       </c>
       <c r="C92" s="5">
-        <v>46196.91330880787</v>
+        <v>46196.7466421412</v>
       </c>
       <c r="D92" s="5">
-        <v>46196.9133102662</v>
+        <v>46196.74664359954</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>273</v>
@@ -7469,13 +7469,13 @@
         <v>278</v>
       </c>
       <c r="B93" s="8">
-        <v>46132.63149714121</v>
+        <v>46132.464830474535</v>
       </c>
       <c r="C93" s="8">
-        <v>46196.91331665509</v>
+        <v>46196.746649988425</v>
       </c>
       <c r="D93" s="8">
-        <v>46196.91331809028</v>
+        <v>46196.746651423615</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>273</v>
@@ -7524,13 +7524,13 @@
         <v>279</v>
       </c>
       <c r="B94" s="5">
-        <v>46132.63150280093</v>
+        <v>46132.464836134255</v>
       </c>
       <c r="C94" s="5">
-        <v>46196.9133241088</v>
+        <v>46196.74665744213</v>
       </c>
       <c r="D94" s="5">
-        <v>46196.91332601852</v>
+        <v>46196.74665935185</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>273</v>
@@ -7579,13 +7579,13 @@
         <v>280</v>
       </c>
       <c r="B95" s="8">
-        <v>46132.63150895834</v>
+        <v>46132.464842291665</v>
       </c>
       <c r="C95" s="8">
-        <v>46196.91332903935</v>
+        <v>46196.74666237269</v>
       </c>
       <c r="D95" s="8">
-        <v>46196.91333064815</v>
+        <v>46196.74666398148</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>273</v>
@@ -7634,13 +7634,13 @@
         <v>281</v>
       </c>
       <c r="B96" s="5">
-        <v>46132.63151432871</v>
+        <v>46132.464847662035</v>
       </c>
       <c r="C96" s="5">
-        <v>46196.91333642361</v>
+        <v>46196.74666975695</v>
       </c>
       <c r="D96" s="5">
-        <v>46196.91333818287</v>
+        <v>46196.7466715162</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>273</v>
@@ -7689,13 +7689,13 @@
         <v>282</v>
       </c>
       <c r="B97" s="8">
-        <v>46132.631519525465</v>
+        <v>46132.4648528588</v>
       </c>
       <c r="C97" s="8">
-        <v>46196.91334673611</v>
+        <v>46196.746680069446</v>
       </c>
       <c r="D97" s="8">
-        <v>46196.91334849537</v>
+        <v>46196.74668182871</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>273</v>
@@ -7744,13 +7744,13 @@
         <v>283</v>
       </c>
       <c r="B98" s="5">
-        <v>46132.631524247685</v>
+        <v>46132.46485758101</v>
       </c>
       <c r="C98" s="5">
-        <v>46196.913354247685</v>
+        <v>46196.74668758102</v>
       </c>
       <c r="D98" s="5">
-        <v>46196.91335584491</v>
+        <v>46196.74668917824</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>273</v>
@@ -7799,13 +7799,13 @@
         <v>284</v>
       </c>
       <c r="B99" s="8">
-        <v>46132.63153150463</v>
+        <v>46132.464864837966</v>
       </c>
       <c r="C99" s="8">
-        <v>46196.913358935184</v>
+        <v>46196.74669226852</v>
       </c>
       <c r="D99" s="8">
-        <v>46196.913360879626</v>
+        <v>46196.74669421296</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>273</v>
@@ -7854,13 +7854,13 @@
         <v>285</v>
       </c>
       <c r="B100" s="5">
-        <v>46132.631539270835</v>
+        <v>46132.46487260416</v>
       </c>
       <c r="C100" s="5">
-        <v>46196.91336784722</v>
+        <v>46196.74670118056</v>
       </c>
       <c r="D100" s="5">
-        <v>46196.913369456015</v>
+        <v>46196.74670278935</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>273</v>
@@ -7909,13 +7909,13 @@
         <v>286</v>
       </c>
       <c r="B101" s="8">
-        <v>46132.63154616898</v>
+        <v>46132.46487950231</v>
       </c>
       <c r="C101" s="8">
-        <v>46196.913381562495</v>
+        <v>46196.74671489584</v>
       </c>
       <c r="D101" s="8">
-        <v>46196.91338305555</v>
+        <v>46196.746716388894</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>273</v>
@@ -7964,13 +7964,13 @@
         <v>287</v>
       </c>
       <c r="B102" s="5">
-        <v>46132.63155506944</v>
+        <v>46132.46488840278</v>
       </c>
       <c r="C102" s="5">
-        <v>46196.913390381946</v>
+        <v>46196.746723715274</v>
       </c>
       <c r="D102" s="5">
-        <v>46196.91339189815</v>
+        <v>46196.74672523148</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>273</v>
@@ -8019,13 +8019,13 @@
         <v>288</v>
       </c>
       <c r="B103" s="8">
-        <v>46132.63156422453</v>
+        <v>46132.464897557875</v>
       </c>
       <c r="C103" s="8">
-        <v>46196.91339768519</v>
+        <v>46196.74673101852</v>
       </c>
       <c r="D103" s="8">
-        <v>46196.91339939815</v>
+        <v>46196.74673273148</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>273</v>
@@ -8074,11 +8074,11 @@
         <v>289</v>
       </c>
       <c r="B104" s="5">
-        <v>46132.63157251157</v>
+        <v>46132.46490584491</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46196.912235208336</v>
+        <v>46196.745568541664</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>273</v>
@@ -8127,11 +8127,11 @@
         <v>290</v>
       </c>
       <c r="B105" s="8">
-        <v>46132.631576643515</v>
+        <v>46132.46490997685</v>
       </c>
       <c r="C105" s="9"/>
       <c r="D105" s="8">
-        <v>46196.91224765046</v>
+        <v>46196.7455809838</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>174</v>
@@ -8180,11 +8180,11 @@
         <v>291</v>
       </c>
       <c r="B106" s="5">
-        <v>46132.6319078588</v>
+        <v>46132.46524119213</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46196.91227103009</v>
+        <v>46196.74560436343</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>273</v>
@@ -8233,11 +8233,11 @@
         <v>292</v>
       </c>
       <c r="B107" s="8">
-        <v>46132.58890393519</v>
+        <v>46132.42223726852</v>
       </c>
       <c r="C107" s="9"/>
       <c r="D107" s="8">
-        <v>46157.54205033564</v>
+        <v>46157.37538366899</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>293</v>
@@ -8280,11 +8280,11 @@
         <v>295</v>
       </c>
       <c r="B108" s="5">
-        <v>46132.58890717593</v>
+        <v>46132.42224050926</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46157.54340230324</v>
+        <v>46157.37673563657</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>296</v>
@@ -8341,13 +8341,13 @@
         <v>298</v>
       </c>
       <c r="B109" s="8">
-        <v>46132.58891280093</v>
+        <v>46132.42224613426</v>
       </c>
       <c r="C109" s="8">
-        <v>46157.542043761576</v>
+        <v>46157.37537709491</v>
       </c>
       <c r="D109" s="8">
-        <v>46163.18906322916</v>
+        <v>46163.022396562505</v>
       </c>
       <c r="E109" s="9" t="s">
         <v>299</v>
@@ -8404,11 +8404,11 @@
         <v>300</v>
       </c>
       <c r="B110" s="5">
-        <v>46132.588918090274</v>
+        <v>46132.42225142361</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46191.909131064815</v>
+        <v>46191.74246439815</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>301</v>
@@ -8465,11 +8465,11 @@
         <v>303</v>
       </c>
       <c r="B111" s="8">
-        <v>46132.58892311342</v>
+        <v>46132.422256446764</v>
       </c>
       <c r="C111" s="9"/>
       <c r="D111" s="8">
-        <v>46133.5836275926</v>
+        <v>46133.416960925926</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>304</v>
@@ -8512,11 +8512,11 @@
         <v>306</v>
       </c>
       <c r="B112" s="5">
-        <v>46132.58892658565</v>
+        <v>46132.42225991898</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46134.57907140046</v>
+        <v>46134.4124047338</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>307</v>
@@ -8575,11 +8575,11 @@
         <v>309</v>
       </c>
       <c r="B113" s="8">
-        <v>46132.632033182876</v>
+        <v>46132.465366516204</v>
       </c>
       <c r="C113" s="9"/>
       <c r="D113" s="8">
-        <v>46196.913310648146</v>
+        <v>46196.74664398148</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>174</v>
@@ -8628,11 +8628,11 @@
         <v>311</v>
       </c>
       <c r="B114" s="5">
-        <v>46132.6321053125</v>
+        <v>46132.465438645835</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46196.91331428241</v>
+        <v>46196.74664761574</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>273</v>
@@ -8681,11 +8681,11 @@
         <v>312</v>
       </c>
       <c r="B115" s="8">
-        <v>46132.63211394676</v>
+        <v>46132.46544728009</v>
       </c>
       <c r="C115" s="9"/>
       <c r="D115" s="8">
-        <v>46196.91332363426</v>
+        <v>46196.74665696759</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>273</v>
@@ -8734,11 +8734,11 @@
         <v>314</v>
       </c>
       <c r="B116" s="5">
-        <v>46132.6321221875</v>
+        <v>46132.46545552083</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46196.913330208336</v>
+        <v>46196.746663541664</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>174</v>
@@ -8787,11 +8787,11 @@
         <v>315</v>
       </c>
       <c r="B117" s="8">
-        <v>46132.63212829861</v>
+        <v>46132.465461631946</v>
       </c>
       <c r="C117" s="9"/>
       <c r="D117" s="8">
-        <v>46196.91333635416</v>
+        <v>46196.746669687505</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>174</v>
@@ -8840,11 +8840,11 @@
         <v>316</v>
       </c>
       <c r="B118" s="5">
-        <v>46132.63213525463</v>
+        <v>46132.465468587965</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46196.91334300926</v>
+        <v>46196.74667634259</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>174</v>
@@ -8893,11 +8893,11 @@
         <v>318</v>
       </c>
       <c r="B119" s="8">
-        <v>46132.63214342593</v>
+        <v>46132.46547675926</v>
       </c>
       <c r="C119" s="9"/>
       <c r="D119" s="8">
-        <v>46196.913353067124</v>
+        <v>46196.74668640047</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>273</v>
@@ -8946,11 +8946,11 @@
         <v>319</v>
       </c>
       <c r="B120" s="5">
-        <v>46132.63215114584</v>
+        <v>46132.465484479166</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46196.91335983796</v>
+        <v>46196.7466931713</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>174</v>
@@ -8999,11 +8999,11 @@
         <v>320</v>
       </c>
       <c r="B121" s="8">
-        <v>46132.63216016204</v>
+        <v>46132.46549349537</v>
       </c>
       <c r="C121" s="9"/>
       <c r="D121" s="8">
-        <v>46196.91336582176</v>
+        <v>46196.74669915509</v>
       </c>
       <c r="E121" s="9" t="s">
         <v>174</v>
@@ -9052,11 +9052,11 @@
         <v>321</v>
       </c>
       <c r="B122" s="5">
-        <v>46132.6321746412</v>
+        <v>46132.465507974535</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46196.913376006945</v>
+        <v>46196.74670934028</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>273</v>
@@ -9105,11 +9105,11 @@
         <v>322</v>
       </c>
       <c r="B123" s="8">
-        <v>46132.63216719907</v>
+        <v>46132.4655005324</v>
       </c>
       <c r="C123" s="9"/>
       <c r="D123" s="8">
-        <v>46196.91338866898</v>
+        <v>46196.74672200231</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>174</v>
@@ -9158,11 +9158,11 @@
         <v>323</v>
       </c>
       <c r="B124" s="5">
-        <v>46132.63218074074</v>
+        <v>46132.46551407407</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46196.913398680554</v>
+        <v>46196.74673201389</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>174</v>
@@ -9211,11 +9211,11 @@
         <v>324</v>
       </c>
       <c r="B125" s="8">
-        <v>46132.632186863426</v>
+        <v>46132.465520196754</v>
       </c>
       <c r="C125" s="9"/>
       <c r="D125" s="8">
-        <v>46196.91340450232</v>
+        <v>46196.74673783565</v>
       </c>
       <c r="E125" s="9" t="s">
         <v>174</v>
@@ -9264,11 +9264,11 @@
         <v>325</v>
       </c>
       <c r="B126" s="5">
-        <v>46132.63219409723</v>
+        <v>46132.465527430555</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46196.91288795139</v>
+        <v>46196.746221284724</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>174</v>
@@ -9317,11 +9317,11 @@
         <v>326</v>
       </c>
       <c r="B127" s="8">
-        <v>46132.63220086806</v>
+        <v>46132.46553420139</v>
       </c>
       <c r="C127" s="9"/>
       <c r="D127" s="8">
-        <v>46196.91289704861</v>
+        <v>46196.74623038195</v>
       </c>
       <c r="E127" s="9" t="s">
         <v>174</v>
@@ -9370,11 +9370,11 @@
         <v>327</v>
       </c>
       <c r="B128" s="5">
-        <v>46132.63220734954</v>
+        <v>46132.46554068287</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46196.912913125</v>
+        <v>46196.74624645834</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>174</v>
@@ -9423,11 +9423,11 @@
         <v>328</v>
       </c>
       <c r="B129" s="8">
-        <v>46132.58893864583</v>
+        <v>46132.422271979165</v>
       </c>
       <c r="C129" s="9"/>
       <c r="D129" s="8">
-        <v>46134.57915813658</v>
+        <v>46134.412491469906</v>
       </c>
       <c r="E129" s="9" t="s">
         <v>329</v>
@@ -9484,11 +9484,11 @@
         <v>330</v>
       </c>
       <c r="B130" s="5">
-        <v>46132.63296805556</v>
+        <v>46132.46630138889</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46196.91295196759</v>
+        <v>46196.74628530093</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>174</v>
@@ -9535,11 +9535,11 @@
         <v>333</v>
       </c>
       <c r="B131" s="8">
-        <v>46132.63297954861</v>
+        <v>46132.466312881945</v>
       </c>
       <c r="C131" s="9"/>
       <c r="D131" s="8">
-        <v>46196.91296126157</v>
+        <v>46196.74629459491</v>
       </c>
       <c r="E131" s="9" t="s">
         <v>174</v>
@@ -9586,11 +9586,11 @@
         <v>335</v>
       </c>
       <c r="B132" s="5">
-        <v>46132.63298759259</v>
+        <v>46132.46632092593</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46196.91296799769</v>
+        <v>46196.74630133102</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>174</v>
@@ -9637,11 +9637,11 @@
         <v>336</v>
       </c>
       <c r="B133" s="8">
-        <v>46132.63299327546</v>
+        <v>46132.466326608795</v>
       </c>
       <c r="C133" s="9"/>
       <c r="D133" s="8">
-        <v>46196.912974652776</v>
+        <v>46196.74630798611</v>
       </c>
       <c r="E133" s="9" t="s">
         <v>174</v>
@@ -9688,11 +9688,11 @@
         <v>338</v>
       </c>
       <c r="B134" s="5">
-        <v>46132.63299994213</v>
+        <v>46132.466333275464</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46196.91298125</v>
+        <v>46196.74631458333</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>174</v>
@@ -9739,11 +9739,11 @@
         <v>339</v>
       </c>
       <c r="B135" s="8">
-        <v>46132.63300702546</v>
+        <v>46132.46634035879</v>
       </c>
       <c r="C135" s="9"/>
       <c r="D135" s="8">
-        <v>46196.9129903125</v>
+        <v>46196.74632364583</v>
       </c>
       <c r="E135" s="9" t="s">
         <v>174</v>
@@ -9790,11 +9790,11 @@
         <v>341</v>
       </c>
       <c r="B136" s="5">
-        <v>46132.633012708335</v>
+        <v>46132.46634604166</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46196.91300965278</v>
+        <v>46196.74634298611</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>174</v>
@@ -9841,11 +9841,11 @@
         <v>343</v>
       </c>
       <c r="B137" s="8">
-        <v>46132.63302</v>
+        <v>46132.46635333334</v>
       </c>
       <c r="C137" s="9"/>
       <c r="D137" s="8">
-        <v>46196.91302356482</v>
+        <v>46196.74635689815</v>
       </c>
       <c r="E137" s="9" t="s">
         <v>174</v>
@@ -9892,11 +9892,11 @@
         <v>344</v>
       </c>
       <c r="B138" s="5">
-        <v>46132.63302648148</v>
+        <v>46132.46635981482</v>
       </c>
       <c r="C138" s="6"/>
       <c r="D138" s="5">
-        <v>46196.91303289351</v>
+        <v>46196.74636622686</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>174</v>
@@ -9943,11 +9943,11 @@
         <v>345</v>
       </c>
       <c r="B139" s="8">
-        <v>46132.633032858794</v>
+        <v>46132.46636619213</v>
       </c>
       <c r="C139" s="9"/>
       <c r="D139" s="8">
-        <v>46196.913042245375</v>
+        <v>46196.7463755787</v>
       </c>
       <c r="E139" s="9" t="s">
         <v>174</v>
@@ -9994,11 +9994,11 @@
         <v>347</v>
       </c>
       <c r="B140" s="5">
-        <v>46132.633039409724</v>
+        <v>46132.46637274306</v>
       </c>
       <c r="C140" s="6"/>
       <c r="D140" s="5">
-        <v>46196.91306868056</v>
+        <v>46196.74640201389</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>174</v>
@@ -10045,11 +10045,11 @@
         <v>348</v>
       </c>
       <c r="B141" s="8">
-        <v>46132.633045821756</v>
+        <v>46132.46637915509</v>
       </c>
       <c r="C141" s="9"/>
       <c r="D141" s="8">
-        <v>46196.91308063657</v>
+        <v>46196.74641396991</v>
       </c>
       <c r="E141" s="9" t="s">
         <v>174</v>
@@ -10096,11 +10096,11 @@
         <v>349</v>
       </c>
       <c r="B142" s="5">
-        <v>46132.633060057866</v>
+        <v>46132.46639339121</v>
       </c>
       <c r="C142" s="6"/>
       <c r="D142" s="5">
-        <v>46196.91309128472</v>
+        <v>46196.74642461806</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>174</v>
@@ -10147,11 +10147,11 @@
         <v>350</v>
       </c>
       <c r="B143" s="8">
-        <v>46132.633052986115</v>
+        <v>46132.466386319444</v>
       </c>
       <c r="C143" s="9"/>
       <c r="D143" s="8">
-        <v>46196.91310061343</v>
+        <v>46196.746433946755</v>
       </c>
       <c r="E143" s="9" t="s">
         <v>174</v>
@@ -10198,11 +10198,11 @@
         <v>351</v>
       </c>
       <c r="B144" s="5">
-        <v>46132.63306579861</v>
+        <v>46132.46639913194</v>
       </c>
       <c r="C144" s="6"/>
       <c r="D144" s="5">
-        <v>46196.913109270834</v>
+        <v>46196.74644260417</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>174</v>
@@ -10249,11 +10249,11 @@
         <v>352</v>
       </c>
       <c r="B145" s="8">
-        <v>46132.633072337965</v>
+        <v>46132.46640567129</v>
       </c>
       <c r="C145" s="9"/>
       <c r="D145" s="8">
-        <v>46196.91313299768</v>
+        <v>46196.746466331024</v>
       </c>
       <c r="E145" s="9" t="s">
         <v>174</v>
@@ -10300,11 +10300,11 @@
         <v>353</v>
       </c>
       <c r="B146" s="5">
-        <v>46132.58894553241</v>
+        <v>46132.42227886574</v>
       </c>
       <c r="C146" s="6"/>
       <c r="D146" s="5">
-        <v>46134.579158981476</v>
+        <v>46134.41249231482</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>354</v>
@@ -10361,11 +10361,11 @@
         <v>355</v>
       </c>
       <c r="B147" s="8">
-        <v>46132.633140289356</v>
+        <v>46132.466473622684</v>
       </c>
       <c r="C147" s="9"/>
       <c r="D147" s="8">
-        <v>46196.91316769676</v>
+        <v>46196.746501030095</v>
       </c>
       <c r="E147" s="9" t="s">
         <v>174</v>
@@ -10412,11 +10412,11 @@
         <v>358</v>
       </c>
       <c r="B148" s="5">
-        <v>46132.63314908565</v>
+        <v>46132.46648241898</v>
       </c>
       <c r="C148" s="6"/>
       <c r="D148" s="5">
-        <v>46196.913174201385</v>
+        <v>46196.74650753472</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>174</v>
@@ -10463,11 +10463,11 @@
         <v>360</v>
       </c>
       <c r="B149" s="8">
-        <v>46132.63315533564</v>
+        <v>46132.466488668986</v>
       </c>
       <c r="C149" s="9"/>
       <c r="D149" s="8">
-        <v>46196.91318321759</v>
+        <v>46196.74651655093</v>
       </c>
       <c r="E149" s="9" t="s">
         <v>174</v>
@@ -10514,11 +10514,11 @@
         <v>361</v>
       </c>
       <c r="B150" s="5">
-        <v>46132.63316266204</v>
+        <v>46132.466495995366</v>
       </c>
       <c r="C150" s="6"/>
       <c r="D150" s="5">
-        <v>46196.91318989583</v>
+        <v>46196.746523229165</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>174</v>
@@ -10565,11 +10565,11 @@
         <v>362</v>
       </c>
       <c r="B151" s="8">
-        <v>46132.6331690625</v>
+        <v>46132.46650239584</v>
       </c>
       <c r="C151" s="9"/>
       <c r="D151" s="8">
-        <v>46196.913196319445</v>
+        <v>46196.74652965278</v>
       </c>
       <c r="E151" s="9" t="s">
         <v>174</v>
@@ -10616,11 +10616,11 @@
         <v>363</v>
       </c>
       <c r="B152" s="5">
-        <v>46132.63317594907</v>
+        <v>46132.46650928241</v>
       </c>
       <c r="C152" s="6"/>
       <c r="D152" s="5">
-        <v>46196.913203275464</v>
+        <v>46196.7465366088</v>
       </c>
       <c r="E152" s="6" t="s">
         <v>174</v>
@@ -10667,11 +10667,11 @@
         <v>364</v>
       </c>
       <c r="B153" s="8">
-        <v>46132.633188506945</v>
+        <v>46132.46652184028</v>
       </c>
       <c r="C153" s="9"/>
       <c r="D153" s="8">
-        <v>46196.91320924769</v>
+        <v>46196.74654258102</v>
       </c>
       <c r="E153" s="9" t="s">
         <v>174</v>
@@ -10718,11 +10718,11 @@
         <v>365</v>
       </c>
       <c r="B154" s="5">
-        <v>46132.63318159722</v>
+        <v>46132.46651493055</v>
       </c>
       <c r="C154" s="6"/>
       <c r="D154" s="5">
-        <v>46196.9132163426</v>
+        <v>46196.746549675925</v>
       </c>
       <c r="E154" s="6" t="s">
         <v>174</v>
@@ -10769,11 +10769,11 @@
         <v>366</v>
       </c>
       <c r="B155" s="8">
-        <v>46132.63319443287</v>
+        <v>46132.4665277662</v>
       </c>
       <c r="C155" s="9"/>
       <c r="D155" s="8">
-        <v>46196.913238333334</v>
+        <v>46196.74657166666</v>
       </c>
       <c r="E155" s="9" t="s">
         <v>174</v>
@@ -10820,11 +10820,11 @@
         <v>367</v>
       </c>
       <c r="B156" s="5">
-        <v>46132.63320815972</v>
+        <v>46132.46654149306</v>
       </c>
       <c r="C156" s="6"/>
       <c r="D156" s="5">
-        <v>46196.91324483797</v>
+        <v>46196.746578171296</v>
       </c>
       <c r="E156" s="6" t="s">
         <v>174</v>
@@ -10871,11 +10871,11 @@
         <v>368</v>
       </c>
       <c r="B157" s="8">
-        <v>46132.63320082176</v>
+        <v>46132.46653415509</v>
       </c>
       <c r="C157" s="9"/>
       <c r="D157" s="8">
-        <v>46196.91325182871</v>
+        <v>46196.746585162036</v>
       </c>
       <c r="E157" s="9" t="s">
         <v>174</v>
@@ -10922,11 +10922,11 @@
         <v>369</v>
       </c>
       <c r="B158" s="5">
-        <v>46132.63322097222</v>
+        <v>46132.46655430556</v>
       </c>
       <c r="C158" s="6"/>
       <c r="D158" s="5">
-        <v>46196.91325798611</v>
+        <v>46196.74659131945</v>
       </c>
       <c r="E158" s="6" t="s">
         <v>174</v>
@@ -10973,11 +10973,11 @@
         <v>370</v>
       </c>
       <c r="B159" s="8">
-        <v>46132.6332150463</v>
+        <v>46132.46654837963</v>
       </c>
       <c r="C159" s="9"/>
       <c r="D159" s="8">
-        <v>46196.91326434028</v>
+        <v>46196.74659767361</v>
       </c>
       <c r="E159" s="9" t="s">
         <v>174</v>
@@ -11024,11 +11024,11 @@
         <v>371</v>
       </c>
       <c r="B160" s="5">
-        <v>46132.63322802083</v>
+        <v>46132.466561354166</v>
       </c>
       <c r="C160" s="6"/>
       <c r="D160" s="5">
-        <v>46196.91327159722</v>
+        <v>46196.74660493055</v>
       </c>
       <c r="E160" s="6" t="s">
         <v>174</v>
@@ -11075,11 +11075,11 @@
         <v>372</v>
       </c>
       <c r="B161" s="8">
-        <v>46132.63323575231</v>
+        <v>46132.46656908565</v>
       </c>
       <c r="C161" s="9"/>
       <c r="D161" s="8">
-        <v>46196.913280625</v>
+        <v>46196.746613958334</v>
       </c>
       <c r="E161" s="9" t="s">
         <v>174</v>
@@ -11126,11 +11126,11 @@
         <v>373</v>
       </c>
       <c r="B162" s="5">
-        <v>46132.633244004624</v>
+        <v>46132.46657733797</v>
       </c>
       <c r="C162" s="6"/>
       <c r="D162" s="5">
-        <v>46196.91329380787</v>
+        <v>46196.746627141205</v>
       </c>
       <c r="E162" s="6" t="s">
         <v>174</v>
@@ -11177,11 +11177,11 @@
         <v>374</v>
       </c>
       <c r="B163" s="8">
-        <v>46132.58893171296</v>
+        <v>46132.4222650463</v>
       </c>
       <c r="C163" s="9"/>
       <c r="D163" s="8">
-        <v>46134.57915975695</v>
+        <v>46134.412493090276</v>
       </c>
       <c r="E163" s="9" t="s">
         <v>375</v>
@@ -11238,11 +11238,11 @@
         <v>376</v>
       </c>
       <c r="B164" s="5">
-        <v>46132.632804305555</v>
+        <v>46132.46613763889</v>
       </c>
       <c r="C164" s="6"/>
       <c r="D164" s="5">
-        <v>46196.91332662037</v>
+        <v>46196.7466599537</v>
       </c>
       <c r="E164" s="6" t="s">
         <v>174</v>
@@ -11289,11 +11289,11 @@
         <v>379</v>
       </c>
       <c r="B165" s="8">
-        <v>46132.632815624995</v>
+        <v>46132.46614895834</v>
       </c>
       <c r="C165" s="9"/>
       <c r="D165" s="8">
-        <v>46196.91333607639</v>
+        <v>46196.746669409724</v>
       </c>
       <c r="E165" s="9" t="s">
         <v>174</v>
@@ -11340,11 +11340,11 @@
         <v>380</v>
       </c>
       <c r="B166" s="5">
-        <v>46132.63282284723</v>
+        <v>46132.466156180555</v>
       </c>
       <c r="C166" s="6"/>
       <c r="D166" s="5">
-        <v>46196.913343078704</v>
+        <v>46196.74667641203</v>
       </c>
       <c r="E166" s="6" t="s">
         <v>174</v>
@@ -11391,11 +11391,11 @@
         <v>382</v>
       </c>
       <c r="B167" s="8">
-        <v>46132.63283236111</v>
+        <v>46132.466165694444</v>
       </c>
       <c r="C167" s="9"/>
       <c r="D167" s="8">
-        <v>46196.913348946764</v>
+        <v>46196.74668228009</v>
       </c>
       <c r="E167" s="9" t="s">
         <v>174</v>
@@ -11442,11 +11442,11 @@
         <v>383</v>
       </c>
       <c r="B168" s="5">
-        <v>46132.632837384255</v>
+        <v>46132.46617071759</v>
       </c>
       <c r="C168" s="6"/>
       <c r="D168" s="5">
-        <v>46196.9133558912</v>
+        <v>46196.746689224536</v>
       </c>
       <c r="E168" s="6" t="s">
         <v>174</v>
@@ -11493,11 +11493,11 @@
         <v>385</v>
       </c>
       <c r="B169" s="8">
-        <v>46132.63284362269</v>
+        <v>46132.46617695602</v>
       </c>
       <c r="C169" s="9"/>
       <c r="D169" s="8">
-        <v>46196.91336501157</v>
+        <v>46196.74669834491</v>
       </c>
       <c r="E169" s="9" t="s">
         <v>174</v>
@@ -11544,11 +11544,11 @@
         <v>386</v>
       </c>
       <c r="B170" s="5">
-        <v>46132.63284975695</v>
+        <v>46132.46618309028</v>
       </c>
       <c r="C170" s="6"/>
       <c r="D170" s="5">
-        <v>46196.91338157408</v>
+        <v>46196.74671490741</v>
       </c>
       <c r="E170" s="6" t="s">
         <v>174</v>
@@ -11595,11 +11595,11 @@
         <v>387</v>
       </c>
       <c r="B171" s="8">
-        <v>46132.63286226852</v>
+        <v>46132.46619560185</v>
       </c>
       <c r="C171" s="9"/>
       <c r="D171" s="8">
-        <v>46196.913389050926</v>
+        <v>46196.746722384254</v>
       </c>
       <c r="E171" s="9" t="s">
         <v>174</v>
@@ -11646,11 +11646,11 @@
         <v>388</v>
       </c>
       <c r="B172" s="5">
-        <v>46132.63285675926</v>
+        <v>46132.46619009259</v>
       </c>
       <c r="C172" s="6"/>
       <c r="D172" s="5">
-        <v>46196.91340076389</v>
+        <v>46196.74673409722</v>
       </c>
       <c r="E172" s="6" t="s">
         <v>174</v>
@@ -11697,11 +11697,11 @@
         <v>389</v>
       </c>
       <c r="B173" s="8">
-        <v>46132.63286828704</v>
+        <v>46132.466201620366</v>
       </c>
       <c r="C173" s="9"/>
       <c r="D173" s="8">
-        <v>46196.91340517361</v>
+        <v>46196.74673850695</v>
       </c>
       <c r="E173" s="9" t="s">
         <v>174</v>
@@ -11748,11 +11748,11 @@
         <v>390</v>
       </c>
       <c r="B174" s="5">
-        <v>46132.63287412037</v>
+        <v>46132.466207453705</v>
       </c>
       <c r="C174" s="6"/>
       <c r="D174" s="5">
-        <v>46196.91341680556</v>
+        <v>46196.74675013889</v>
       </c>
       <c r="E174" s="6" t="s">
         <v>174</v>
@@ -11799,11 +11799,11 @@
         <v>391</v>
       </c>
       <c r="B175" s="8">
-        <v>46132.63288133102</v>
+        <v>46132.46621466435</v>
       </c>
       <c r="C175" s="9"/>
       <c r="D175" s="8">
-        <v>46196.91342331019</v>
+        <v>46196.74675664352</v>
       </c>
       <c r="E175" s="9" t="s">
         <v>174</v>
@@ -11850,11 +11850,11 @@
         <v>392</v>
       </c>
       <c r="B176" s="5">
-        <v>46132.63288800926</v>
+        <v>46132.46622134259</v>
       </c>
       <c r="C176" s="6"/>
       <c r="D176" s="5">
-        <v>46196.913429849534</v>
+        <v>46196.74676318287</v>
       </c>
       <c r="E176" s="6" t="s">
         <v>174</v>
@@ -11901,11 +11901,11 @@
         <v>393</v>
       </c>
       <c r="B177" s="8">
-        <v>46132.63289421296</v>
+        <v>46132.4662275463</v>
       </c>
       <c r="C177" s="9"/>
       <c r="D177" s="8">
-        <v>46196.91343652778</v>
+        <v>46196.746769861114</v>
       </c>
       <c r="E177" s="9" t="s">
         <v>174</v>
@@ -11952,11 +11952,11 @@
         <v>394</v>
       </c>
       <c r="B178" s="5">
-        <v>46132.63290028935</v>
+        <v>46132.46623362269</v>
       </c>
       <c r="C178" s="6"/>
       <c r="D178" s="5">
-        <v>46196.91344907407</v>
+        <v>46196.74678240741</v>
       </c>
       <c r="E178" s="6" t="s">
         <v>174</v>
@@ -12003,11 +12003,11 @@
         <v>395</v>
       </c>
       <c r="B179" s="8">
-        <v>46132.632907719904</v>
+        <v>46132.46624105324</v>
       </c>
       <c r="C179" s="9"/>
       <c r="D179" s="8">
-        <v>46196.91346278935</v>
+        <v>46196.74679612269</v>
       </c>
       <c r="E179" s="9" t="s">
         <v>174</v>
@@ -12054,11 +12054,11 @@
         <v>396</v>
       </c>
       <c r="B180" s="5">
-        <v>46132.58895258102</v>
+        <v>46132.42228591435</v>
       </c>
       <c r="C180" s="6"/>
       <c r="D180" s="5">
-        <v>46134.579160567126</v>
+        <v>46134.41249390046</v>
       </c>
       <c r="E180" s="6" t="s">
         <v>397</v>
@@ -12115,11 +12115,11 @@
         <v>398</v>
       </c>
       <c r="B181" s="8">
-        <v>46132.63330006944</v>
+        <v>46132.46663340278</v>
       </c>
       <c r="C181" s="9"/>
       <c r="D181" s="8">
-        <v>46196.91349186342</v>
+        <v>46196.74682519676</v>
       </c>
       <c r="E181" s="9" t="s">
         <v>174</v>
@@ -12166,11 +12166,11 @@
         <v>401</v>
       </c>
       <c r="B182" s="5">
-        <v>46132.63330984954</v>
+        <v>46132.46664318287</v>
       </c>
       <c r="C182" s="6"/>
       <c r="D182" s="5">
-        <v>46196.913516817134</v>
+        <v>46196.74685015046</v>
       </c>
       <c r="E182" s="6" t="s">
         <v>174</v>
@@ -12217,11 +12217,11 @@
         <v>403</v>
       </c>
       <c r="B183" s="8">
-        <v>46132.633316377316</v>
+        <v>46132.46664971065</v>
       </c>
       <c r="C183" s="9"/>
       <c r="D183" s="8">
-        <v>46196.913533425926</v>
+        <v>46196.74686675926</v>
       </c>
       <c r="E183" s="9" t="s">
         <v>174</v>
@@ -12268,11 +12268,11 @@
         <v>405</v>
       </c>
       <c r="B184" s="5">
-        <v>46132.63332333333</v>
+        <v>46132.46665666667</v>
       </c>
       <c r="C184" s="6"/>
       <c r="D184" s="5">
-        <v>46196.91352673611</v>
+        <v>46196.74686006944</v>
       </c>
       <c r="E184" s="6" t="s">
         <v>174</v>
@@ -12319,11 +12319,11 @@
         <v>407</v>
       </c>
       <c r="B185" s="8">
-        <v>46132.63333568287</v>
+        <v>46132.466669016205</v>
       </c>
       <c r="C185" s="9"/>
       <c r="D185" s="8">
-        <v>46196.91354314815</v>
+        <v>46196.746876481484</v>
       </c>
       <c r="E185" s="9" t="s">
         <v>174</v>
@@ -12370,11 +12370,11 @@
         <v>409</v>
       </c>
       <c r="B186" s="5">
-        <v>46132.633329282406</v>
+        <v>46132.46666261574</v>
       </c>
       <c r="C186" s="6"/>
       <c r="D186" s="5">
-        <v>46196.913549942125</v>
+        <v>46196.74688327547</v>
       </c>
       <c r="E186" s="6" t="s">
         <v>174</v>
@@ -12421,11 +12421,11 @@
         <v>411</v>
       </c>
       <c r="B187" s="8">
-        <v>46132.63334925926</v>
+        <v>46132.466682592596</v>
       </c>
       <c r="C187" s="9"/>
       <c r="D187" s="8">
-        <v>46196.91355706019</v>
+        <v>46196.74689039352</v>
       </c>
       <c r="E187" s="9" t="s">
         <v>174</v>
@@ -12472,11 +12472,11 @@
         <v>413</v>
       </c>
       <c r="B188" s="5">
-        <v>46132.633353321755</v>
+        <v>46132.4666866551</v>
       </c>
       <c r="C188" s="6"/>
       <c r="D188" s="5">
-        <v>46196.91356591435</v>
+        <v>46196.746899247686</v>
       </c>
       <c r="E188" s="6" t="s">
         <v>174</v>
@@ -12523,11 +12523,11 @@
         <v>415</v>
       </c>
       <c r="B189" s="8">
-        <v>46132.63336115741</v>
+        <v>46132.46669449074</v>
       </c>
       <c r="C189" s="9"/>
       <c r="D189" s="8">
-        <v>46196.91357502315</v>
+        <v>46196.74690835648</v>
       </c>
       <c r="E189" s="9" t="s">
         <v>174</v>
@@ -12574,11 +12574,11 @@
         <v>417</v>
       </c>
       <c r="B190" s="5">
-        <v>46132.6333661574</v>
+        <v>46132.466699490746</v>
       </c>
       <c r="C190" s="6"/>
       <c r="D190" s="5">
-        <v>46196.91357896991</v>
+        <v>46196.74691230324</v>
       </c>
       <c r="E190" s="6" t="s">
         <v>174</v>
@@ -12625,11 +12625,11 @@
         <v>419</v>
       </c>
       <c r="B191" s="8">
-        <v>46132.633375046295</v>
+        <v>46132.46670837963</v>
       </c>
       <c r="C191" s="9"/>
       <c r="D191" s="8">
-        <v>46196.91359459491</v>
+        <v>46196.74692792824</v>
       </c>
       <c r="E191" s="9" t="s">
         <v>174</v>
@@ -12676,11 +12676,11 @@
         <v>421</v>
       </c>
       <c r="B192" s="5">
-        <v>46132.63337950232</v>
+        <v>46132.46671283565</v>
       </c>
       <c r="C192" s="6"/>
       <c r="D192" s="5">
-        <v>46196.913601423614</v>
+        <v>46196.74693475694</v>
       </c>
       <c r="E192" s="6" t="s">
         <v>174</v>
@@ -12727,11 +12727,11 @@
         <v>423</v>
       </c>
       <c r="B193" s="8">
-        <v>46132.63338666667</v>
+        <v>46132.46672</v>
       </c>
       <c r="C193" s="9"/>
       <c r="D193" s="8">
-        <v>46196.91361079861</v>
+        <v>46196.74694413194</v>
       </c>
       <c r="E193" s="9" t="s">
         <v>174</v>
@@ -12778,11 +12778,11 @@
         <v>425</v>
       </c>
       <c r="B194" s="5">
-        <v>46132.63339375</v>
+        <v>46132.46672708333</v>
       </c>
       <c r="C194" s="6"/>
       <c r="D194" s="5">
-        <v>46196.91361791667</v>
+        <v>46196.746951249996</v>
       </c>
       <c r="E194" s="6" t="s">
         <v>174</v>
@@ -12829,11 +12829,11 @@
         <v>427</v>
       </c>
       <c r="B195" s="8">
-        <v>46132.63339872685</v>
+        <v>46132.46673206019</v>
       </c>
       <c r="C195" s="9"/>
       <c r="D195" s="8">
-        <v>46196.91362990741</v>
+        <v>46196.746963240745</v>
       </c>
       <c r="E195" s="9" t="s">
         <v>174</v>
@@ -12880,11 +12880,11 @@
         <v>429</v>
       </c>
       <c r="B196" s="5">
-        <v>46132.633404085645</v>
+        <v>46132.46673741898</v>
       </c>
       <c r="C196" s="6"/>
       <c r="D196" s="5">
-        <v>46196.91364925926</v>
+        <v>46196.746982592595</v>
       </c>
       <c r="E196" s="6" t="s">
         <v>174</v>
@@ -12931,11 +12931,11 @@
         <v>431</v>
       </c>
       <c r="B197" s="8">
-        <v>46132.58900565973</v>
+        <v>46132.422338993056</v>
       </c>
       <c r="C197" s="9"/>
       <c r="D197" s="8">
-        <v>46134.579161331014</v>
+        <v>46134.41249466436</v>
       </c>
       <c r="E197" s="9" t="s">
         <v>432</v>
@@ -12992,11 +12992,11 @@
         <v>435</v>
       </c>
       <c r="B198" s="5">
-        <v>46132.6334534375</v>
+        <v>46132.466786770834</v>
       </c>
       <c r="C198" s="6"/>
       <c r="D198" s="5">
-        <v>46196.91368532408</v>
+        <v>46196.74701865741</v>
       </c>
       <c r="E198" s="6" t="s">
         <v>174</v>
@@ -13043,11 +13043,11 @@
         <v>437</v>
       </c>
       <c r="B199" s="8">
-        <v>46132.633462025464</v>
+        <v>46132.46679535879</v>
       </c>
       <c r="C199" s="9"/>
       <c r="D199" s="8">
-        <v>46196.91369168981</v>
+        <v>46196.74702502315</v>
       </c>
       <c r="E199" s="9" t="s">
         <v>174</v>
@@ -13094,11 +13094,11 @@
         <v>438</v>
       </c>
       <c r="B200" s="5">
-        <v>46132.633468622684</v>
+        <v>46132.46680195602</v>
       </c>
       <c r="C200" s="6"/>
       <c r="D200" s="5">
-        <v>46196.91369818287</v>
+        <v>46196.747031516206</v>
       </c>
       <c r="E200" s="6" t="s">
         <v>174</v>
@@ -13145,11 +13145,11 @@
         <v>439</v>
       </c>
       <c r="B201" s="8">
-        <v>46132.63347502315</v>
+        <v>46132.46680835648</v>
       </c>
       <c r="C201" s="9"/>
       <c r="D201" s="8">
-        <v>46196.91371429398</v>
+        <v>46196.747047627316</v>
       </c>
       <c r="E201" s="9" t="s">
         <v>174</v>
@@ -13196,11 +13196,11 @@
         <v>440</v>
       </c>
       <c r="B202" s="5">
-        <v>46132.63348070602</v>
+        <v>46132.46681403935</v>
       </c>
       <c r="C202" s="6"/>
       <c r="D202" s="5">
-        <v>46196.91372087963</v>
+        <v>46196.74705421296</v>
       </c>
       <c r="E202" s="6" t="s">
         <v>174</v>
@@ -13247,11 +13247,11 @@
         <v>441</v>
       </c>
       <c r="B203" s="8">
-        <v>46132.63348662037</v>
+        <v>46132.466819953705</v>
       </c>
       <c r="C203" s="9"/>
       <c r="D203" s="8">
-        <v>46196.91372986111</v>
+        <v>46196.747063194445</v>
       </c>
       <c r="E203" s="9" t="s">
         <v>174</v>
@@ -13298,11 +13298,11 @@
         <v>442</v>
       </c>
       <c r="B204" s="5">
-        <v>46132.63349295139</v>
+        <v>46132.466826284726</v>
       </c>
       <c r="C204" s="6"/>
       <c r="D204" s="5">
-        <v>46196.91373467592</v>
+        <v>46196.74706800926</v>
       </c>
       <c r="E204" s="6" t="s">
         <v>174</v>
@@ -13349,11 +13349,11 @@
         <v>444</v>
       </c>
       <c r="B205" s="8">
-        <v>46132.633500138894</v>
+        <v>46132.46683347222</v>
       </c>
       <c r="C205" s="9"/>
       <c r="D205" s="8">
-        <v>46196.91374106481</v>
+        <v>46196.74707439815</v>
       </c>
       <c r="E205" s="9" t="s">
         <v>174</v>
@@ -13400,11 +13400,11 @@
         <v>445</v>
       </c>
       <c r="B206" s="5">
-        <v>46132.633505983795</v>
+        <v>46132.46683931713</v>
       </c>
       <c r="C206" s="6"/>
       <c r="D206" s="5">
-        <v>46196.91374993055</v>
+        <v>46196.747083263894</v>
       </c>
       <c r="E206" s="6" t="s">
         <v>174</v>
@@ -13451,11 +13451,11 @@
         <v>446</v>
       </c>
       <c r="B207" s="8">
-        <v>46132.6335124537</v>
+        <v>46132.466845787036</v>
       </c>
       <c r="C207" s="9"/>
       <c r="D207" s="8">
-        <v>46196.91377486111</v>
+        <v>46196.747108194446</v>
       </c>
       <c r="E207" s="9" t="s">
         <v>174</v>
@@ -13502,11 +13502,11 @@
         <v>447</v>
       </c>
       <c r="B208" s="5">
-        <v>46132.63351974537</v>
+        <v>46132.4668530787</v>
       </c>
       <c r="C208" s="6"/>
       <c r="D208" s="5">
-        <v>46196.91379184028</v>
+        <v>46196.74712517361</v>
       </c>
       <c r="E208" s="6" t="s">
         <v>174</v>
@@ -13553,11 +13553,11 @@
         <v>448</v>
       </c>
       <c r="B209" s="8">
-        <v>46132.6335277662</v>
+        <v>46132.466861099536</v>
       </c>
       <c r="C209" s="9"/>
       <c r="D209" s="8">
-        <v>46196.913807916666</v>
+        <v>46196.74714125</v>
       </c>
       <c r="E209" s="9" t="s">
         <v>174</v>
@@ -13604,11 +13604,11 @@
         <v>449</v>
       </c>
       <c r="B210" s="5">
-        <v>46132.633534988425</v>
+        <v>46132.46686832176</v>
       </c>
       <c r="C210" s="6"/>
       <c r="D210" s="5">
-        <v>46196.91381409722</v>
+        <v>46196.74714743056</v>
       </c>
       <c r="E210" s="6" t="s">
         <v>174</v>
@@ -13655,11 +13655,11 @@
         <v>450</v>
       </c>
       <c r="B211" s="8">
-        <v>46132.63354082176</v>
+        <v>46132.46687415509</v>
       </c>
       <c r="C211" s="9"/>
       <c r="D211" s="8">
-        <v>46196.91383046296</v>
+        <v>46196.747163796295</v>
       </c>
       <c r="E211" s="9" t="s">
         <v>174</v>
@@ -13706,11 +13706,11 @@
         <v>451</v>
       </c>
       <c r="B212" s="5">
-        <v>46132.63354760417</v>
+        <v>46132.4668809375</v>
       </c>
       <c r="C212" s="6"/>
       <c r="D212" s="5">
-        <v>46196.913837025466</v>
+        <v>46196.747170358794</v>
       </c>
       <c r="E212" s="6" t="s">
         <v>452</v>
@@ -13757,11 +13757,11 @@
         <v>453</v>
       </c>
       <c r="B213" s="8">
-        <v>46133.58300138889</v>
+        <v>46133.41633472222</v>
       </c>
       <c r="C213" s="9"/>
       <c r="D213" s="8">
-        <v>46196.91385334491</v>
+        <v>46196.74718667824</v>
       </c>
       <c r="E213" s="9" t="s">
         <v>273</v>
@@ -13808,11 +13808,11 @@
         <v>454</v>
       </c>
       <c r="B214" s="5">
-        <v>46132.589012916666</v>
+        <v>46132.42234625</v>
       </c>
       <c r="C214" s="6"/>
       <c r="D214" s="5">
-        <v>46133.58769056713</v>
+        <v>46133.42102390046</v>
       </c>
       <c r="E214" s="6" t="s">
         <v>455</v>
@@ -13855,11 +13855,11 @@
         <v>457</v>
       </c>
       <c r="B215" s="8">
-        <v>46132.589016666665</v>
+        <v>46132.42235</v>
       </c>
       <c r="C215" s="9"/>
       <c r="D215" s="8">
-        <v>46133.58482033564</v>
+        <v>46133.41815366899</v>
       </c>
       <c r="E215" s="9" t="s">
         <v>458</v>
@@ -13916,11 +13916,11 @@
         <v>462</v>
       </c>
       <c r="B216" s="5">
-        <v>46132.63360670139</v>
+        <v>46132.46694003472</v>
       </c>
       <c r="C216" s="6"/>
       <c r="D216" s="5">
-        <v>46196.91388565973</v>
+        <v>46196.747218993056</v>
       </c>
       <c r="E216" s="6" t="s">
         <v>174</v>
@@ -13967,11 +13967,11 @@
         <v>463</v>
       </c>
       <c r="B217" s="8">
-        <v>46132.63361304398</v>
+        <v>46132.46694637732</v>
       </c>
       <c r="C217" s="9"/>
       <c r="D217" s="8">
-        <v>46196.91389173611</v>
+        <v>46196.74722506944</v>
       </c>
       <c r="E217" s="9" t="s">
         <v>174</v>
@@ -14018,11 +14018,11 @@
         <v>464</v>
       </c>
       <c r="B218" s="5">
-        <v>46132.63361974537</v>
+        <v>46132.46695307871</v>
       </c>
       <c r="C218" s="6"/>
       <c r="D218" s="5">
-        <v>46196.91390143518</v>
+        <v>46196.74723476852</v>
       </c>
       <c r="E218" s="6" t="s">
         <v>174</v>
@@ -14069,11 +14069,11 @@
         <v>465</v>
       </c>
       <c r="B219" s="8">
-        <v>46132.63363137731</v>
+        <v>46132.46696471065</v>
       </c>
       <c r="C219" s="9"/>
       <c r="D219" s="8">
-        <v>46196.913907152775</v>
+        <v>46196.74724048611</v>
       </c>
       <c r="E219" s="9" t="s">
         <v>174</v>
@@ -14120,11 +14120,11 @@
         <v>466</v>
       </c>
       <c r="B220" s="5">
-        <v>46132.63362555555</v>
+        <v>46132.466958888894</v>
       </c>
       <c r="C220" s="6"/>
       <c r="D220" s="5">
-        <v>46196.91391674768</v>
+        <v>46196.74725008102</v>
       </c>
       <c r="E220" s="6" t="s">
         <v>174</v>
@@ -14171,11 +14171,11 @@
         <v>467</v>
       </c>
       <c r="B221" s="8">
-        <v>46132.63363859954</v>
+        <v>46132.46697193287</v>
       </c>
       <c r="C221" s="9"/>
       <c r="D221" s="8">
-        <v>46196.913933171294</v>
+        <v>46196.74726650463</v>
       </c>
       <c r="E221" s="9" t="s">
         <v>174</v>
@@ -14222,11 +14222,11 @@
         <v>468</v>
       </c>
       <c r="B222" s="5">
-        <v>46132.63364667824</v>
+        <v>46132.46698001157</v>
       </c>
       <c r="C222" s="6"/>
       <c r="D222" s="5">
-        <v>46196.913939861115</v>
+        <v>46196.74727319444</v>
       </c>
       <c r="E222" s="6" t="s">
         <v>452</v>
@@ -14273,11 +14273,11 @@
         <v>469</v>
       </c>
       <c r="B223" s="8">
-        <v>46132.633653055556</v>
+        <v>46132.466986388885</v>
       </c>
       <c r="C223" s="9"/>
       <c r="D223" s="8">
-        <v>46196.91395613426</v>
+        <v>46196.74728946759</v>
       </c>
       <c r="E223" s="9" t="s">
         <v>174</v>
@@ -14324,11 +14324,11 @@
         <v>470</v>
       </c>
       <c r="B224" s="5">
-        <v>46132.63365921297</v>
+        <v>46132.466992546295</v>
       </c>
       <c r="C224" s="6"/>
       <c r="D224" s="5">
-        <v>46196.9139649537</v>
+        <v>46196.74729828704</v>
       </c>
       <c r="E224" s="6" t="s">
         <v>174</v>
@@ -14375,11 +14375,11 @@
         <v>471</v>
       </c>
       <c r="B225" s="8">
-        <v>46132.633665347224</v>
+        <v>46132.46699868055</v>
       </c>
       <c r="C225" s="9"/>
       <c r="D225" s="8">
-        <v>46196.91397201389</v>
+        <v>46196.74730534722</v>
       </c>
       <c r="E225" s="9" t="s">
         <v>174</v>
@@ -14426,11 +14426,11 @@
         <v>472</v>
       </c>
       <c r="B226" s="5">
-        <v>46132.63367407407</v>
+        <v>46132.46700740741</v>
       </c>
       <c r="C226" s="6"/>
       <c r="D226" s="5">
-        <v>46196.91398435185</v>
+        <v>46196.747317685185</v>
       </c>
       <c r="E226" s="6" t="s">
         <v>174</v>
@@ -14477,11 +14477,11 @@
         <v>473</v>
       </c>
       <c r="B227" s="8">
-        <v>46132.63368225694</v>
+        <v>46132.46701559028</v>
       </c>
       <c r="C227" s="9"/>
       <c r="D227" s="8">
-        <v>46196.91399296296</v>
+        <v>46196.747326296296</v>
       </c>
       <c r="E227" s="9" t="s">
         <v>174</v>
@@ -14528,11 +14528,11 @@
         <v>474</v>
       </c>
       <c r="B228" s="5">
-        <v>46132.63368885417</v>
+        <v>46132.4670221875</v>
       </c>
       <c r="C228" s="6"/>
       <c r="D228" s="5">
-        <v>46196.913999675926</v>
+        <v>46196.74733300926</v>
       </c>
       <c r="E228" s="6" t="s">
         <v>174</v>
@@ -14579,11 +14579,11 @@
         <v>475</v>
       </c>
       <c r="B229" s="8">
-        <v>46132.633694965276</v>
+        <v>46132.46702829861</v>
       </c>
       <c r="C229" s="9"/>
       <c r="D229" s="8">
-        <v>46196.914015358794</v>
+        <v>46196.74734869213</v>
       </c>
       <c r="E229" s="9" t="s">
         <v>174</v>
@@ -14630,11 +14630,11 @@
         <v>476</v>
       </c>
       <c r="B230" s="5">
-        <v>46132.63370111111</v>
+        <v>46132.467034444446</v>
       </c>
       <c r="C230" s="6"/>
       <c r="D230" s="5">
-        <v>46196.9140217824</v>
+        <v>46196.747355115745</v>
       </c>
       <c r="E230" s="6" t="s">
         <v>452</v>
@@ -14681,11 +14681,11 @@
         <v>477</v>
       </c>
       <c r="B231" s="8">
-        <v>46132.63378953704</v>
+        <v>46132.46712287037</v>
       </c>
       <c r="C231" s="9"/>
       <c r="D231" s="8">
-        <v>46196.91403721065</v>
+        <v>46196.74737054398</v>
       </c>
       <c r="E231" s="9" t="s">
         <v>174</v>
@@ -14732,11 +14732,11 @@
         <v>478</v>
       </c>
       <c r="B232" s="5">
-        <v>46132.589021736116</v>
+        <v>46132.422355069444</v>
       </c>
       <c r="C232" s="6"/>
       <c r="D232" s="5">
-        <v>46133.58651043981</v>
+        <v>46133.41984377315</v>
       </c>
       <c r="E232" s="6" t="s">
         <v>479</v>
@@ -14793,11 +14793,11 @@
         <v>481</v>
       </c>
       <c r="B233" s="8">
-        <v>46132.633861608796</v>
+        <v>46132.46719494213</v>
       </c>
       <c r="C233" s="9"/>
       <c r="D233" s="8">
-        <v>46196.91407126158</v>
+        <v>46196.747404594906</v>
       </c>
       <c r="E233" s="9" t="s">
         <v>174</v>
@@ -14844,11 +14844,11 @@
         <v>482</v>
       </c>
       <c r="B234" s="5">
-        <v>46132.633870011574</v>
+        <v>46132.4672033449</v>
       </c>
       <c r="C234" s="6"/>
       <c r="D234" s="5">
-        <v>46196.914077905094</v>
+        <v>46196.74741123842</v>
       </c>
       <c r="E234" s="6" t="s">
         <v>174</v>
@@ -14895,11 +14895,11 @@
         <v>483</v>
       </c>
       <c r="B235" s="8">
-        <v>46132.63387658565</v>
+        <v>46132.46720991898</v>
       </c>
       <c r="C235" s="9"/>
       <c r="D235" s="8">
-        <v>46196.914084212964</v>
+        <v>46196.7474175463</v>
       </c>
       <c r="E235" s="9" t="s">
         <v>174</v>
@@ -14946,11 +14946,11 @@
         <v>484</v>
       </c>
       <c r="B236" s="5">
-        <v>46132.63388259259</v>
+        <v>46132.46721592592</v>
       </c>
       <c r="C236" s="6"/>
       <c r="D236" s="5">
-        <v>46196.91409322916</v>
+        <v>46196.7474265625</v>
       </c>
       <c r="E236" s="6" t="s">
         <v>174</v>
@@ -14997,11 +14997,11 @@
         <v>485</v>
       </c>
       <c r="B237" s="8">
-        <v>46132.63388633102</v>
+        <v>46132.46721966435</v>
       </c>
       <c r="C237" s="9"/>
       <c r="D237" s="8">
-        <v>46196.914099340276</v>
+        <v>46196.74743267361</v>
       </c>
       <c r="E237" s="9" t="s">
         <v>174</v>
@@ -15048,11 +15048,11 @@
         <v>486</v>
       </c>
       <c r="B238" s="5">
-        <v>46132.63389106482</v>
+        <v>46132.46722439815</v>
       </c>
       <c r="C238" s="6"/>
       <c r="D238" s="5">
-        <v>46196.9141059838</v>
+        <v>46196.74743931713</v>
       </c>
       <c r="E238" s="6" t="s">
         <v>174</v>
@@ -15099,11 +15099,11 @@
         <v>487</v>
       </c>
       <c r="B239" s="8">
-        <v>46132.63389739583</v>
+        <v>46132.46723072916</v>
       </c>
       <c r="C239" s="9"/>
       <c r="D239" s="8">
-        <v>46196.91411261574</v>
+        <v>46196.74744594908</v>
       </c>
       <c r="E239" s="9" t="s">
         <v>174</v>
@@ -15150,11 +15150,11 @@
         <v>488</v>
       </c>
       <c r="B240" s="5">
-        <v>46132.63390288195</v>
+        <v>46132.46723621528</v>
       </c>
       <c r="C240" s="6"/>
       <c r="D240" s="5">
-        <v>46196.91411917824</v>
+        <v>46196.747452511576</v>
       </c>
       <c r="E240" s="6" t="s">
         <v>174</v>
@@ -15201,11 +15201,11 @@
         <v>489</v>
       </c>
       <c r="B241" s="8">
-        <v>46132.63390861111</v>
+        <v>46132.46724194444</v>
       </c>
       <c r="C241" s="9"/>
       <c r="D241" s="8">
-        <v>46196.91413769676</v>
+        <v>46196.74747103009</v>
       </c>
       <c r="E241" s="9" t="s">
         <v>174</v>
@@ -15252,11 +15252,11 @@
         <v>490</v>
       </c>
       <c r="B242" s="5">
-        <v>46132.63391276621</v>
+        <v>46132.467246099535</v>
       </c>
       <c r="C242" s="6"/>
       <c r="D242" s="5">
-        <v>46196.91415084491</v>
+        <v>46196.74748417824</v>
       </c>
       <c r="E242" s="6" t="s">
         <v>174</v>
@@ -15303,11 +15303,11 @@
         <v>491</v>
       </c>
       <c r="B243" s="8">
-        <v>46132.63391880787</v>
+        <v>46132.4672521412</v>
       </c>
       <c r="C243" s="9"/>
       <c r="D243" s="8">
-        <v>46196.914157175925</v>
+        <v>46196.74749050926</v>
       </c>
       <c r="E243" s="9" t="s">
         <v>174</v>
@@ -15354,11 +15354,11 @@
         <v>492</v>
       </c>
       <c r="B244" s="5">
-        <v>46132.63392302083</v>
+        <v>46132.46725635417</v>
       </c>
       <c r="C244" s="6"/>
       <c r="D244" s="5">
-        <v>46196.91416721065</v>
+        <v>46196.74750054398</v>
       </c>
       <c r="E244" s="6" t="s">
         <v>174</v>
@@ -15405,11 +15405,11 @@
         <v>493</v>
       </c>
       <c r="B245" s="8">
-        <v>46132.63393041666</v>
+        <v>46132.467263750004</v>
       </c>
       <c r="C245" s="9"/>
       <c r="D245" s="8">
-        <v>46196.91417351852</v>
+        <v>46196.747506851854</v>
       </c>
       <c r="E245" s="9" t="s">
         <v>174</v>
@@ -15456,11 +15456,11 @@
         <v>494</v>
       </c>
       <c r="B246" s="5">
-        <v>46132.63393689815</v>
+        <v>46132.467270231486</v>
       </c>
       <c r="C246" s="6"/>
       <c r="D246" s="5">
-        <v>46196.91418997685</v>
+        <v>46196.74752331019</v>
       </c>
       <c r="E246" s="6" t="s">
         <v>174</v>
@@ -15507,11 +15507,11 @@
         <v>495</v>
       </c>
       <c r="B247" s="8">
-        <v>46132.633943078705</v>
+        <v>46132.46727641203</v>
       </c>
       <c r="C247" s="9"/>
       <c r="D247" s="8">
-        <v>46196.91419930555</v>
+        <v>46196.74753263889</v>
       </c>
       <c r="E247" s="9" t="s">
         <v>452</v>
@@ -15558,11 +15558,11 @@
         <v>496</v>
       </c>
       <c r="B248" s="5">
-        <v>46132.633955578705</v>
+        <v>46132.46728891204</v>
       </c>
       <c r="C248" s="6"/>
       <c r="D248" s="5">
-        <v>46196.91421935185</v>
+        <v>46196.747552685185</v>
       </c>
       <c r="E248" s="6" t="s">
         <v>174</v>
@@ -15609,11 +15609,11 @@
         <v>497</v>
       </c>
       <c r="B249" s="8">
-        <v>46132.58902681713</v>
+        <v>46132.422360150464</v>
       </c>
       <c r="C249" s="9"/>
       <c r="D249" s="8">
-        <v>46133.58721105324</v>
+        <v>46133.42054438658</v>
       </c>
       <c r="E249" s="9" t="s">
         <v>498</v>
@@ -15672,11 +15672,11 @@
         <v>502</v>
       </c>
       <c r="B250" s="5">
-        <v>46132.634024432875</v>
+        <v>46132.4673577662</v>
       </c>
       <c r="C250" s="6"/>
       <c r="D250" s="5">
-        <v>46196.914276875</v>
+        <v>46196.74761020833</v>
       </c>
       <c r="E250" s="6" t="s">
         <v>174</v>
@@ -15723,11 +15723,11 @@
         <v>503</v>
       </c>
       <c r="B251" s="8">
-        <v>46132.634032685186</v>
+        <v>46132.46736601852</v>
       </c>
       <c r="C251" s="9"/>
       <c r="D251" s="8">
-        <v>46196.914286666666</v>
+        <v>46196.747619999995</v>
       </c>
       <c r="E251" s="9" t="s">
         <v>174</v>
@@ -15774,11 +15774,11 @@
         <v>504</v>
       </c>
       <c r="B252" s="5">
-        <v>46132.63404001157</v>
+        <v>46132.46737334491</v>
       </c>
       <c r="C252" s="6"/>
       <c r="D252" s="5">
-        <v>46196.91429060185</v>
+        <v>46196.74762393518</v>
       </c>
       <c r="E252" s="6" t="s">
         <v>174</v>
@@ -15825,11 +15825,11 @@
         <v>505</v>
       </c>
       <c r="B253" s="8">
-        <v>46132.63404659722</v>
+        <v>46132.46737993056</v>
       </c>
       <c r="C253" s="9"/>
       <c r="D253" s="8">
-        <v>46196.914299571756</v>
+        <v>46196.74763290509</v>
       </c>
       <c r="E253" s="9" t="s">
         <v>174</v>
@@ -15876,11 +15876,11 @@
         <v>506</v>
       </c>
       <c r="B254" s="5">
-        <v>46132.6340537037</v>
+        <v>46132.46738703703</v>
       </c>
       <c r="C254" s="6"/>
       <c r="D254" s="5">
-        <v>46196.91430931713</v>
+        <v>46196.74764265046</v>
       </c>
       <c r="E254" s="6" t="s">
         <v>174</v>
@@ -15927,11 +15927,11 @@
         <v>507</v>
       </c>
       <c r="B255" s="8">
-        <v>46132.63406115741</v>
+        <v>46132.46739449074</v>
       </c>
       <c r="C255" s="9"/>
       <c r="D255" s="8">
-        <v>46196.914319143514</v>
+        <v>46196.74765247686</v>
       </c>
       <c r="E255" s="9" t="s">
         <v>174</v>
@@ -15978,11 +15978,11 @@
         <v>508</v>
       </c>
       <c r="B256" s="5">
-        <v>46132.63406662037</v>
+        <v>46132.467399953704</v>
       </c>
       <c r="C256" s="6"/>
       <c r="D256" s="5">
-        <v>46196.91432607639</v>
+        <v>46196.747659409724</v>
       </c>
       <c r="E256" s="6" t="s">
         <v>174</v>
@@ -16029,11 +16029,11 @@
         <v>509</v>
       </c>
       <c r="B257" s="8">
-        <v>46132.634072395835</v>
+        <v>46132.46740572917</v>
       </c>
       <c r="C257" s="9"/>
       <c r="D257" s="8">
-        <v>46196.914335231486</v>
+        <v>46196.747668564814</v>
       </c>
       <c r="E257" s="9" t="s">
         <v>174</v>
@@ -16080,11 +16080,11 @@
         <v>510</v>
       </c>
       <c r="B258" s="5">
-        <v>46132.6340770949</v>
+        <v>46132.467410428246</v>
       </c>
       <c r="C258" s="6"/>
       <c r="D258" s="5">
-        <v>46196.914344687495</v>
+        <v>46196.74767802084</v>
       </c>
       <c r="E258" s="6" t="s">
         <v>174</v>
@@ -16131,11 +16131,11 @@
         <v>511</v>
       </c>
       <c r="B259" s="8">
-        <v>46132.634082777775</v>
+        <v>46132.46741611111</v>
       </c>
       <c r="C259" s="9"/>
       <c r="D259" s="8">
-        <v>46196.91435427083</v>
+        <v>46196.74768760416</v>
       </c>
       <c r="E259" s="9" t="s">
         <v>174</v>
@@ -16182,11 +16182,11 @@
         <v>512</v>
       </c>
       <c r="B260" s="5">
-        <v>46132.63408899306</v>
+        <v>46132.46742232639</v>
       </c>
       <c r="C260" s="6"/>
       <c r="D260" s="5">
-        <v>46196.91437050926</v>
+        <v>46196.74770384259</v>
       </c>
       <c r="E260" s="6" t="s">
         <v>174</v>
@@ -16233,11 +16233,11 @@
         <v>513</v>
       </c>
       <c r="B261" s="8">
-        <v>46132.63409545139</v>
+        <v>46132.46742878472</v>
       </c>
       <c r="C261" s="9"/>
       <c r="D261" s="8">
-        <v>46196.914380057875</v>
+        <v>46196.7477133912</v>
       </c>
       <c r="E261" s="9" t="s">
         <v>174</v>
@@ -16284,11 +16284,11 @@
         <v>514</v>
       </c>
       <c r="B262" s="5">
-        <v>46132.63410087963</v>
+        <v>46132.46743421296</v>
       </c>
       <c r="C262" s="6"/>
       <c r="D262" s="5">
-        <v>46196.914383738425</v>
+        <v>46196.74771707176</v>
       </c>
       <c r="E262" s="6" t="s">
         <v>174</v>
@@ -16335,11 +16335,11 @@
         <v>515</v>
       </c>
       <c r="B263" s="8">
-        <v>46132.63410688657</v>
+        <v>46132.46744021991</v>
       </c>
       <c r="C263" s="9"/>
       <c r="D263" s="8">
-        <v>46196.914396527776</v>
+        <v>46196.74772986111</v>
       </c>
       <c r="E263" s="9" t="s">
         <v>174</v>
@@ -16386,11 +16386,11 @@
         <v>516</v>
       </c>
       <c r="B264" s="5">
-        <v>46132.6341133449</v>
+        <v>46132.467446678245</v>
       </c>
       <c r="C264" s="6"/>
       <c r="D264" s="5">
-        <v>46196.914406261574</v>
+        <v>46196.74773959491</v>
       </c>
       <c r="E264" s="6" t="s">
         <v>174</v>
@@ -16437,11 +16437,11 @@
         <v>517</v>
       </c>
       <c r="B265" s="8">
-        <v>46132.63411966435</v>
+        <v>46132.467452997684</v>
       </c>
       <c r="C265" s="9"/>
       <c r="D265" s="8">
-        <v>46196.91441971065</v>
+        <v>46196.74775304398</v>
       </c>
       <c r="E265" s="9" t="s">
         <v>174</v>
@@ -16488,11 +16488,11 @@
         <v>518</v>
       </c>
       <c r="B266" s="5">
-        <v>46132.58903189815</v>
+        <v>46132.42236523148</v>
       </c>
       <c r="C266" s="6"/>
       <c r="D266" s="5">
-        <v>46133.65412578704</v>
+        <v>46133.48745912037</v>
       </c>
       <c r="E266" s="6" t="s">
         <v>519</v>
@@ -16549,11 +16549,11 @@
         <v>521</v>
       </c>
       <c r="B267" s="8">
-        <v>46132.63422869213</v>
+        <v>46132.467562025464</v>
       </c>
       <c r="C267" s="9"/>
       <c r="D267" s="8">
-        <v>46196.91446424769</v>
+        <v>46196.74779758102</v>
       </c>
       <c r="E267" s="9" t="s">
         <v>174</v>
@@ -16600,11 +16600,11 @@
         <v>523</v>
       </c>
       <c r="B268" s="5">
-        <v>46132.63423491898</v>
+        <v>46132.467568252316</v>
       </c>
       <c r="C268" s="6"/>
       <c r="D268" s="5">
-        <v>46196.91447116898</v>
+        <v>46196.747804502316</v>
       </c>
       <c r="E268" s="6" t="s">
         <v>174</v>
@@ -16651,11 +16651,11 @@
         <v>524</v>
       </c>
       <c r="B269" s="8">
-        <v>46132.634240960644</v>
+        <v>46132.46757429398</v>
       </c>
       <c r="C269" s="9"/>
       <c r="D269" s="8">
-        <v>46196.914480694446</v>
+        <v>46196.74781402778</v>
       </c>
       <c r="E269" s="9" t="s">
         <v>174</v>
@@ -16702,11 +16702,11 @@
         <v>525</v>
       </c>
       <c r="B270" s="5">
-        <v>46132.63424789352</v>
+        <v>46132.467581226854</v>
       </c>
       <c r="C270" s="6"/>
       <c r="D270" s="5">
-        <v>46196.91449018518</v>
+        <v>46196.74782351852</v>
       </c>
       <c r="E270" s="6" t="s">
         <v>174</v>
@@ -16753,11 +16753,11 @@
         <v>526</v>
       </c>
       <c r="B271" s="8">
-        <v>46132.634254386576</v>
+        <v>46132.467587719904</v>
       </c>
       <c r="C271" s="9"/>
       <c r="D271" s="8">
-        <v>46196.91449658565</v>
+        <v>46196.74782991898</v>
       </c>
       <c r="E271" s="9" t="s">
         <v>174</v>
@@ -16804,11 +16804,11 @@
         <v>527</v>
       </c>
       <c r="B272" s="5">
-        <v>46132.634260810184</v>
+        <v>46132.46759414352</v>
       </c>
       <c r="C272" s="6"/>
       <c r="D272" s="5">
-        <v>46196.914503645836</v>
+        <v>46196.747836979164</v>
       </c>
       <c r="E272" s="6" t="s">
         <v>174</v>
@@ -16855,11 +16855,11 @@
         <v>528</v>
       </c>
       <c r="B273" s="8">
-        <v>46132.634267256944</v>
+        <v>46132.46760059027</v>
       </c>
       <c r="C273" s="9"/>
       <c r="D273" s="8">
-        <v>46196.91450951389</v>
+        <v>46196.747842847224</v>
       </c>
       <c r="E273" s="9" t="s">
         <v>174</v>
@@ -16906,11 +16906,11 @@
         <v>529</v>
       </c>
       <c r="B274" s="5">
-        <v>46132.63427122685</v>
+        <v>46132.46760456018</v>
       </c>
       <c r="C274" s="6"/>
       <c r="D274" s="5">
-        <v>46196.91451931713</v>
+        <v>46196.747852650464</v>
       </c>
       <c r="E274" s="6" t="s">
         <v>174</v>
@@ -16957,11 +16957,11 @@
         <v>531</v>
       </c>
       <c r="B275" s="8">
-        <v>46132.634276365745</v>
+        <v>46132.46760969907</v>
       </c>
       <c r="C275" s="9"/>
       <c r="D275" s="8">
-        <v>46196.914524629625</v>
+        <v>46196.74785796297</v>
       </c>
       <c r="E275" s="9" t="s">
         <v>174</v>
@@ -17008,11 +17008,11 @@
         <v>532</v>
       </c>
       <c r="B276" s="5">
-        <v>46132.63428099537</v>
+        <v>46132.46761432871</v>
       </c>
       <c r="C276" s="6"/>
       <c r="D276" s="5">
-        <v>46196.91452907407</v>
+        <v>46196.74786240741</v>
       </c>
       <c r="E276" s="6" t="s">
         <v>174</v>
@@ -17059,11 +17059,11 @@
         <v>533</v>
       </c>
       <c r="B277" s="8">
-        <v>46132.63428524305</v>
+        <v>46132.46761857639</v>
       </c>
       <c r="C277" s="9"/>
       <c r="D277" s="8">
-        <v>46196.91453917824</v>
+        <v>46196.74787251157</v>
       </c>
       <c r="E277" s="9" t="s">
         <v>174</v>
@@ -17110,11 +17110,11 @@
         <v>534</v>
       </c>
       <c r="B278" s="5">
-        <v>46132.63429103009</v>
+        <v>46132.46762436343</v>
       </c>
       <c r="C278" s="6"/>
       <c r="D278" s="5">
-        <v>46196.91454204862</v>
+        <v>46196.747875381945</v>
       </c>
       <c r="E278" s="6" t="s">
         <v>174</v>
@@ -17161,11 +17161,11 @@
         <v>535</v>
       </c>
       <c r="B279" s="8">
-        <v>46132.63429523148</v>
+        <v>46132.46762856482</v>
       </c>
       <c r="C279" s="9"/>
       <c r="D279" s="8">
-        <v>46196.914551724534</v>
+        <v>46196.74788505787</v>
       </c>
       <c r="E279" s="9" t="s">
         <v>174</v>
@@ -17212,11 +17212,11 @@
         <v>536</v>
       </c>
       <c r="B280" s="5">
-        <v>46132.63430358796</v>
+        <v>46132.4676369213</v>
       </c>
       <c r="C280" s="6"/>
       <c r="D280" s="5">
-        <v>46196.91457195602</v>
+        <v>46196.74790528935</v>
       </c>
       <c r="E280" s="6" t="s">
         <v>174</v>
@@ -17263,11 +17263,11 @@
         <v>537</v>
       </c>
       <c r="B281" s="8">
-        <v>46132.63431148148</v>
+        <v>46132.46764481482</v>
       </c>
       <c r="C281" s="9"/>
       <c r="D281" s="8">
-        <v>46196.91458070602</v>
+        <v>46196.747914039355</v>
       </c>
       <c r="E281" s="9" t="s">
         <v>174</v>
@@ -17314,11 +17314,11 @@
         <v>538</v>
       </c>
       <c r="B282" s="5">
-        <v>46132.63437663195</v>
+        <v>46132.467709965276</v>
       </c>
       <c r="C282" s="6"/>
       <c r="D282" s="5">
-        <v>46196.91461018518</v>
+        <v>46196.74794351852</v>
       </c>
       <c r="E282" s="6" t="s">
         <v>174</v>
@@ -17365,11 +17365,11 @@
         <v>539</v>
       </c>
       <c r="B283" s="8">
-        <v>46132.589037604164</v>
+        <v>46132.4223709375</v>
       </c>
       <c r="C283" s="9"/>
       <c r="D283" s="8">
-        <v>46133.59235670139</v>
+        <v>46133.425690034725</v>
       </c>
       <c r="E283" s="9" t="s">
         <v>540</v>
@@ -17412,11 +17412,11 @@
         <v>541</v>
       </c>
       <c r="B284" s="5">
-        <v>46132.5890406713</v>
+        <v>46132.42237400463</v>
       </c>
       <c r="C284" s="6"/>
       <c r="D284" s="5">
-        <v>46134.57925581018</v>
+        <v>46134.41258914352</v>
       </c>
       <c r="E284" s="6" t="s">
         <v>542</v>
@@ -17475,11 +17475,11 @@
         <v>546</v>
       </c>
       <c r="B285" s="8">
-        <v>46132.58904559028</v>
+        <v>46132.42237892361</v>
       </c>
       <c r="C285" s="9"/>
       <c r="D285" s="8">
-        <v>46134.57925902778</v>
+        <v>46134.412592361114</v>
       </c>
       <c r="E285" s="9" t="s">
         <v>547</v>

--- a/data/50001541 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001541 - XEMORTIZ MINERA FRISCO.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3224" uniqueCount="547">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3224" uniqueCount="548">
   <si>
     <t>50001541 -  XEMORTIZ MINERA FRISCO</t>
   </si>
@@ -734,6 +734,9 @@
   </si>
   <si>
     <t xml:space="preserve">OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 </t>
+  </si>
+  <si>
+    <t>Media</t>
   </si>
   <si>
     <t>1214137717389464</t>
@@ -6294,7 +6297,7 @@
         <v>46196.69197697917</v>
       </c>
       <c r="D72" s="5">
-        <v>46196.692663379625</v>
+        <v>46199.17870534722</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>239</v>
@@ -6338,8 +6341,8 @@
       <c r="R72" s="5">
         <v>46184</v>
       </c>
-      <c r="S72" s="11" t="s">
-        <v>97</v>
+      <c r="S72" s="12" t="s">
+        <v>241</v>
       </c>
       <c r="T72" s="6">
         <v>1</v>
@@ -6350,7 +6353,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B73" s="8">
         <v>46132.631278472225</v>
@@ -6392,10 +6395,10 @@
         <v>239</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q73" s="9"/>
       <c r="R73" s="9"/>
@@ -6405,7 +6408,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B74" s="5">
         <v>46132.63129450232</v>
@@ -6447,10 +6450,10 @@
         <v>239</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6460,7 +6463,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B75" s="8">
         <v>46132.63130252315</v>
@@ -6502,10 +6505,10 @@
         <v>239</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q75" s="9"/>
       <c r="R75" s="9"/>
@@ -6515,7 +6518,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B76" s="5">
         <v>46132.63130869213</v>
@@ -6557,10 +6560,10 @@
         <v>239</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6570,7 +6573,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B77" s="8">
         <v>46132.631314467595</v>
@@ -6612,10 +6615,10 @@
         <v>239</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q77" s="9"/>
       <c r="R77" s="9"/>
@@ -6625,7 +6628,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B78" s="5">
         <v>46132.6313205787</v>
@@ -6667,10 +6670,10 @@
         <v>239</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6680,7 +6683,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B79" s="8">
         <v>46132.6313259375</v>
@@ -6722,10 +6725,10 @@
         <v>239</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q79" s="9"/>
       <c r="R79" s="9"/>
@@ -6735,7 +6738,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B80" s="5">
         <v>46132.63133041667</v>
@@ -6777,10 +6780,10 @@
         <v>239</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6790,7 +6793,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B81" s="8">
         <v>46132.63133645833</v>
@@ -6832,10 +6835,10 @@
         <v>239</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q81" s="9"/>
       <c r="R81" s="9"/>
@@ -6845,7 +6848,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B82" s="5">
         <v>46132.63134074074</v>
@@ -6887,10 +6890,10 @@
         <v>239</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6900,7 +6903,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B83" s="8">
         <v>46132.631346469905</v>
@@ -6942,10 +6945,10 @@
         <v>239</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q83" s="9"/>
       <c r="R83" s="9"/>
@@ -6955,7 +6958,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B84" s="5">
         <v>46132.631352083336</v>
@@ -6997,10 +7000,10 @@
         <v>239</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -7010,7 +7013,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B85" s="8">
         <v>46132.63135776621</v>
@@ -7052,10 +7055,10 @@
         <v>239</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q85" s="9"/>
       <c r="R85" s="9"/>
@@ -7065,7 +7068,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B86" s="5">
         <v>46132.63136296296</v>
@@ -7107,10 +7110,10 @@
         <v>239</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -7120,7 +7123,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B87" s="8">
         <v>46132.63136688658</v>
@@ -7162,10 +7165,10 @@
         <v>239</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P87" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q87" s="9"/>
       <c r="R87" s="9"/>
@@ -7175,7 +7178,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B88" s="5">
         <v>46132.63137239583</v>
@@ -7217,10 +7220,10 @@
         <v>239</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -7230,7 +7233,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B89" s="8">
         <v>46132.58889809028</v>
@@ -7240,7 +7243,7 @@
         <v>46196.91358532407</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
@@ -7270,7 +7273,7 @@
         <v>232</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="P89" s="9" t="s">
         <v>232</v>
@@ -7293,7 +7296,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B90" s="5">
         <v>46132.63147894676</v>
@@ -7305,7 +7308,7 @@
         <v>46196.913305381946</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -7332,13 +7335,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -7348,7 +7351,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B91" s="8">
         <v>46132.63149082176</v>
@@ -7360,7 +7363,7 @@
         <v>46196.9133102662</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
@@ -7387,13 +7390,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q91" s="9"/>
       <c r="R91" s="9"/>
@@ -7403,7 +7406,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B92" s="5">
         <v>46132.63149714121</v>
@@ -7415,7 +7418,7 @@
         <v>46196.91331809028</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -7442,13 +7445,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -7458,7 +7461,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B93" s="8">
         <v>46132.63150280093</v>
@@ -7470,7 +7473,7 @@
         <v>46196.91332601852</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
@@ -7497,13 +7500,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q93" s="9"/>
       <c r="R93" s="9"/>
@@ -7513,7 +7516,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B94" s="5">
         <v>46132.63150895834</v>
@@ -7525,7 +7528,7 @@
         <v>46196.91333064815</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -7552,13 +7555,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7568,7 +7571,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B95" s="8">
         <v>46132.63151432871</v>
@@ -7580,7 +7583,7 @@
         <v>46196.91333818287</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
@@ -7607,13 +7610,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q95" s="9"/>
       <c r="R95" s="9"/>
@@ -7623,7 +7626,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B96" s="5">
         <v>46132.631519525465</v>
@@ -7635,7 +7638,7 @@
         <v>46196.91334849537</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7662,13 +7665,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7678,7 +7681,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B97" s="8">
         <v>46132.631524247685</v>
@@ -7690,7 +7693,7 @@
         <v>46196.91335584491</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
@@ -7717,13 +7720,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q97" s="9"/>
       <c r="R97" s="9"/>
@@ -7733,7 +7736,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B98" s="5">
         <v>46132.63153150463</v>
@@ -7745,7 +7748,7 @@
         <v>46196.913360879626</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7772,13 +7775,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7788,7 +7791,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B99" s="8">
         <v>46132.631539270835</v>
@@ -7800,7 +7803,7 @@
         <v>46196.913369456015</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
@@ -7827,13 +7830,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P99" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q99" s="9"/>
       <c r="R99" s="9"/>
@@ -7843,7 +7846,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B100" s="5">
         <v>46132.63154616898</v>
@@ -7855,7 +7858,7 @@
         <v>46196.91338305555</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7882,13 +7885,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7898,7 +7901,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B101" s="8">
         <v>46132.63155506944</v>
@@ -7910,7 +7913,7 @@
         <v>46196.91339189815</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
@@ -7937,13 +7940,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P101" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q101" s="9"/>
       <c r="R101" s="9"/>
@@ -7953,7 +7956,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B102" s="5">
         <v>46132.63156422453</v>
@@ -7965,7 +7968,7 @@
         <v>46196.91339939815</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7992,13 +7995,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -8008,7 +8011,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B103" s="8">
         <v>46132.63157251157</v>
@@ -8018,7 +8021,7 @@
         <v>46196.912235208336</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>26</v>
@@ -8045,13 +8048,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P103" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q103" s="9"/>
       <c r="R103" s="9"/>
@@ -8061,7 +8064,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B104" s="5">
         <v>46132.631576643515</v>
@@ -8098,13 +8101,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -8114,7 +8117,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B105" s="8">
         <v>46132.6319078588</v>
@@ -8124,7 +8127,7 @@
         <v>46196.91227103009</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>26</v>
@@ -8151,13 +8154,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P105" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q105" s="9"/>
       <c r="R105" s="9"/>
@@ -8167,7 +8170,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B106" s="5">
         <v>46132.58890393519</v>
@@ -8179,7 +8182,7 @@
         <v>46198.65523800926</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>25</v>
@@ -8203,7 +8206,7 @@
         <v>26</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="P106" s="6" t="s">
         <v>26</v>
@@ -8220,7 +8223,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B107" s="8">
         <v>46132.58890717593</v>
@@ -8232,7 +8235,7 @@
         <v>46198.65511907407</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
@@ -8257,13 +8260,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="9" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="O107" s="9" t="s">
         <v>100</v>
       </c>
       <c r="P107" s="9" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q107" s="8">
         <v>46146</v>
@@ -8283,7 +8286,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B108" s="5">
         <v>46132.58891280093</v>
@@ -8295,7 +8298,7 @@
         <v>46163.18906322916</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -8320,13 +8323,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="O108" s="6" t="s">
         <v>109</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q108" s="5">
         <v>46162</v>
@@ -8346,7 +8349,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B109" s="8">
         <v>46132.588918090274</v>
@@ -8358,7 +8361,7 @@
         <v>46198.65526501158</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>26</v>
@@ -8383,13 +8386,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="9" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="O109" s="9" t="s">
         <v>119</v>
       </c>
       <c r="P109" s="9" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q109" s="8">
         <v>46176</v>
@@ -8409,7 +8412,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B110" s="5">
         <v>46132.58892311342</v>
@@ -8419,7 +8422,7 @@
         <v>46133.5836275926</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>25</v>
@@ -8443,7 +8446,7 @@
         <v>26</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>26</v>
@@ -8456,7 +8459,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B111" s="8">
         <v>46132.58892658565</v>
@@ -8466,7 +8469,7 @@
         <v>46134.57907140046</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
@@ -8493,13 +8496,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="9" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="P111" s="9" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q111" s="8">
         <v>46217</v>
@@ -8519,7 +8522,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B112" s="5">
         <v>46132.632033182876</v>
@@ -8556,13 +8559,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8572,7 +8575,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B113" s="8">
         <v>46132.6321053125</v>
@@ -8582,7 +8585,7 @@
         <v>46196.91331428241</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
@@ -8609,13 +8612,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P113" s="9" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q113" s="9"/>
       <c r="R113" s="9"/>
@@ -8625,7 +8628,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B114" s="5">
         <v>46132.63211394676</v>
@@ -8635,7 +8638,7 @@
         <v>46196.91332363426</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
@@ -8662,13 +8665,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -8678,7 +8681,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B115" s="8">
         <v>46132.6321221875</v>
@@ -8715,13 +8718,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O115" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P115" s="9" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q115" s="9"/>
       <c r="R115" s="9"/>
@@ -8731,7 +8734,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B116" s="5">
         <v>46132.63212829861</v>
@@ -8768,13 +8771,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8784,7 +8787,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B117" s="8">
         <v>46132.63213525463</v>
@@ -8821,13 +8824,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O117" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P117" s="9" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q117" s="9"/>
       <c r="R117" s="9"/>
@@ -8837,7 +8840,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B118" s="5">
         <v>46132.63214342593</v>
@@ -8847,7 +8850,7 @@
         <v>46196.913353067124</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -8874,13 +8877,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8890,7 +8893,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B119" s="8">
         <v>46132.63215114584</v>
@@ -8927,13 +8930,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O119" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P119" s="9" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q119" s="9"/>
       <c r="R119" s="9"/>
@@ -8943,7 +8946,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B120" s="5">
         <v>46132.63216016204</v>
@@ -8980,13 +8983,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8996,7 +8999,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B121" s="8">
         <v>46132.6321746412</v>
@@ -9006,7 +9009,7 @@
         <v>46196.913376006945</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>26</v>
@@ -9033,13 +9036,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O121" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P121" s="9" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q121" s="9"/>
       <c r="R121" s="9"/>
@@ -9049,7 +9052,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B122" s="5">
         <v>46132.63216719907</v>
@@ -9086,13 +9089,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -9102,7 +9105,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B123" s="8">
         <v>46132.63218074074</v>
@@ -9139,13 +9142,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O123" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P123" s="9" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q123" s="9"/>
       <c r="R123" s="9"/>
@@ -9155,7 +9158,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B124" s="5">
         <v>46132.632186863426</v>
@@ -9192,13 +9195,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -9208,7 +9211,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B125" s="8">
         <v>46132.63219409723</v>
@@ -9245,13 +9248,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O125" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P125" s="9" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q125" s="9"/>
       <c r="R125" s="9"/>
@@ -9261,7 +9264,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B126" s="5">
         <v>46132.63220086806</v>
@@ -9298,13 +9301,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O126" s="6" t="s">
         <v>173</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -9314,7 +9317,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B127" s="8">
         <v>46132.63220734954</v>
@@ -9351,13 +9354,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O127" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P127" s="9" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q127" s="9"/>
       <c r="R127" s="9"/>
@@ -9367,7 +9370,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B128" s="5">
         <v>46132.58893864583</v>
@@ -9377,7 +9380,7 @@
         <v>46134.57915813658</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
@@ -9402,13 +9405,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O128" s="6" t="s">
         <v>240</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q128" s="5">
         <v>46218</v>
@@ -9428,7 +9431,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B129" s="8">
         <v>46132.63296805556</v>
@@ -9463,13 +9466,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="9" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O129" s="9" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="P129" s="9" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q129" s="9"/>
       <c r="R129" s="9"/>
@@ -9479,7 +9482,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B130" s="5">
         <v>46132.63297954861</v>
@@ -9514,13 +9517,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -9530,7 +9533,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B131" s="8">
         <v>46132.63298759259</v>
@@ -9565,13 +9568,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="9" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O131" s="9" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="P131" s="9" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q131" s="9"/>
       <c r="R131" s="9"/>
@@ -9581,7 +9584,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B132" s="5">
         <v>46132.63299327546</v>
@@ -9616,13 +9619,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9632,7 +9635,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B133" s="8">
         <v>46132.63299994213</v>
@@ -9667,13 +9670,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="9" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O133" s="9" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="P133" s="9" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q133" s="9"/>
       <c r="R133" s="9"/>
@@ -9683,7 +9686,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B134" s="5">
         <v>46132.63300702546</v>
@@ -9718,13 +9721,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9734,7 +9737,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B135" s="8">
         <v>46132.633012708335</v>
@@ -9769,13 +9772,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="9" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O135" s="9" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="P135" s="9" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q135" s="9"/>
       <c r="R135" s="9"/>
@@ -9785,7 +9788,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B136" s="5">
         <v>46132.63302</v>
@@ -9820,13 +9823,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9836,7 +9839,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B137" s="8">
         <v>46132.63302648148</v>
@@ -9871,13 +9874,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="9" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O137" s="9" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="P137" s="9" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q137" s="9"/>
       <c r="R137" s="9"/>
@@ -9887,7 +9890,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B138" s="5">
         <v>46132.633032858794</v>
@@ -9922,13 +9925,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9938,7 +9941,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B139" s="8">
         <v>46132.633039409724</v>
@@ -9973,13 +9976,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="9" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O139" s="9" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="P139" s="9" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q139" s="9"/>
       <c r="R139" s="9"/>
@@ -9989,7 +9992,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B140" s="5">
         <v>46132.633045821756</v>
@@ -10024,13 +10027,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -10040,7 +10043,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B141" s="8">
         <v>46132.633060057866</v>
@@ -10075,13 +10078,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="9" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O141" s="9" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="P141" s="9" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q141" s="9"/>
       <c r="R141" s="9"/>
@@ -10091,7 +10094,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B142" s="5">
         <v>46132.633052986115</v>
@@ -10126,13 +10129,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -10142,7 +10145,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="7" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B143" s="8">
         <v>46132.63306579861</v>
@@ -10177,13 +10180,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="9" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O143" s="9" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="P143" s="9" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q143" s="9"/>
       <c r="R143" s="9"/>
@@ -10193,7 +10196,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B144" s="5">
         <v>46132.633072337965</v>
@@ -10228,13 +10231,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -10244,7 +10247,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B145" s="8">
         <v>46132.58894553241</v>
@@ -10254,7 +10257,7 @@
         <v>46134.579158981476</v>
       </c>
       <c r="E145" s="9" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>26</v>
@@ -10279,13 +10282,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="9" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O145" s="9" t="s">
         <v>240</v>
       </c>
       <c r="P145" s="9" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q145" s="8">
         <v>46219</v>
@@ -10305,7 +10308,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B146" s="5">
         <v>46132.633140289356</v>
@@ -10340,13 +10343,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q146" s="6"/>
       <c r="R146" s="6"/>
@@ -10356,7 +10359,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="7" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B147" s="8">
         <v>46132.63314908565</v>
@@ -10391,13 +10394,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="9" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O147" s="9" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="P147" s="9" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q147" s="9"/>
       <c r="R147" s="9"/>
@@ -10407,7 +10410,7 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B148" s="5">
         <v>46132.63315533564</v>
@@ -10442,13 +10445,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q148" s="6"/>
       <c r="R148" s="6"/>
@@ -10458,7 +10461,7 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="7" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B149" s="8">
         <v>46132.63316266204</v>
@@ -10493,13 +10496,13 @@
         <v>26</v>
       </c>
       <c r="N149" s="9" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O149" s="9" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="P149" s="9" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q149" s="9"/>
       <c r="R149" s="9"/>
@@ -10509,7 +10512,7 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B150" s="5">
         <v>46132.6331690625</v>
@@ -10544,13 +10547,13 @@
         <v>26</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="P150" s="6" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q150" s="6"/>
       <c r="R150" s="6"/>
@@ -10560,7 +10563,7 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="7" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B151" s="8">
         <v>46132.63317594907</v>
@@ -10595,13 +10598,13 @@
         <v>26</v>
       </c>
       <c r="N151" s="9" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O151" s="9" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="P151" s="9" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q151" s="9"/>
       <c r="R151" s="9"/>
@@ -10611,7 +10614,7 @@
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B152" s="5">
         <v>46132.633188506945</v>
@@ -10646,13 +10649,13 @@
         <v>26</v>
       </c>
       <c r="N152" s="6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O152" s="6" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="P152" s="6" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q152" s="6"/>
       <c r="R152" s="6"/>
@@ -10662,7 +10665,7 @@
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" s="7" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B153" s="8">
         <v>46132.63318159722</v>
@@ -10697,13 +10700,13 @@
         <v>26</v>
       </c>
       <c r="N153" s="9" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O153" s="9" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="P153" s="9" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q153" s="9"/>
       <c r="R153" s="9"/>
@@ -10713,7 +10716,7 @@
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B154" s="5">
         <v>46132.63319443287</v>
@@ -10748,13 +10751,13 @@
         <v>26</v>
       </c>
       <c r="N154" s="6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="P154" s="6" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q154" s="6"/>
       <c r="R154" s="6"/>
@@ -10764,7 +10767,7 @@
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155" s="7" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B155" s="8">
         <v>46132.63320815972</v>
@@ -10799,13 +10802,13 @@
         <v>26</v>
       </c>
       <c r="N155" s="9" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O155" s="9" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="P155" s="9" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q155" s="9"/>
       <c r="R155" s="9"/>
@@ -10815,7 +10818,7 @@
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B156" s="5">
         <v>46132.63320082176</v>
@@ -10850,13 +10853,13 @@
         <v>26</v>
       </c>
       <c r="N156" s="6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O156" s="6" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="P156" s="6" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q156" s="6"/>
       <c r="R156" s="6"/>
@@ -10866,7 +10869,7 @@
     </row>
     <row r="157" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A157" s="7" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B157" s="8">
         <v>46132.63322097222</v>
@@ -10901,13 +10904,13 @@
         <v>26</v>
       </c>
       <c r="N157" s="9" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O157" s="9" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="P157" s="9" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q157" s="9"/>
       <c r="R157" s="9"/>
@@ -10917,7 +10920,7 @@
     </row>
     <row r="158" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B158" s="5">
         <v>46132.6332150463</v>
@@ -10952,13 +10955,13 @@
         <v>26</v>
       </c>
       <c r="N158" s="6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O158" s="6" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="P158" s="6" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q158" s="6"/>
       <c r="R158" s="6"/>
@@ -10968,7 +10971,7 @@
     </row>
     <row r="159" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A159" s="7" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B159" s="8">
         <v>46132.63322802083</v>
@@ -11003,13 +11006,13 @@
         <v>26</v>
       </c>
       <c r="N159" s="9" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O159" s="9" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="P159" s="9" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q159" s="9"/>
       <c r="R159" s="9"/>
@@ -11019,7 +11022,7 @@
     </row>
     <row r="160" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B160" s="5">
         <v>46132.63323575231</v>
@@ -11054,13 +11057,13 @@
         <v>26</v>
       </c>
       <c r="N160" s="6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O160" s="6" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="P160" s="6" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q160" s="6"/>
       <c r="R160" s="6"/>
@@ -11070,7 +11073,7 @@
     </row>
     <row r="161" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A161" s="7" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B161" s="8">
         <v>46132.633244004624</v>
@@ -11105,13 +11108,13 @@
         <v>26</v>
       </c>
       <c r="N161" s="9" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O161" s="9" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="P161" s="9" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q161" s="9"/>
       <c r="R161" s="9"/>
@@ -11121,7 +11124,7 @@
     </row>
     <row r="162" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B162" s="5">
         <v>46132.58893171296</v>
@@ -11131,7 +11134,7 @@
         <v>46134.57915975695</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F162" s="6" t="s">
         <v>26</v>
@@ -11156,13 +11159,13 @@
         <v>26</v>
       </c>
       <c r="N162" s="6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O162" s="6" t="s">
         <v>240</v>
       </c>
       <c r="P162" s="6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q162" s="5">
         <v>46220</v>
@@ -11182,7 +11185,7 @@
     </row>
     <row r="163" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A163" s="7" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B163" s="8">
         <v>46132.632804305555</v>
@@ -11217,13 +11220,13 @@
         <v>26</v>
       </c>
       <c r="N163" s="9" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="O163" s="9" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="P163" s="9" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q163" s="9"/>
       <c r="R163" s="9"/>
@@ -11233,7 +11236,7 @@
     </row>
     <row r="164" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B164" s="5">
         <v>46132.632815624995</v>
@@ -11268,13 +11271,13 @@
         <v>26</v>
       </c>
       <c r="N164" s="6" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="O164" s="6" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="P164" s="6" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q164" s="6"/>
       <c r="R164" s="6"/>
@@ -11284,7 +11287,7 @@
     </row>
     <row r="165" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A165" s="7" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B165" s="8">
         <v>46132.63282284723</v>
@@ -11319,13 +11322,13 @@
         <v>26</v>
       </c>
       <c r="N165" s="9" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="O165" s="9" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="P165" s="9" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q165" s="9"/>
       <c r="R165" s="9"/>
@@ -11335,7 +11338,7 @@
     </row>
     <row r="166" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B166" s="5">
         <v>46132.63283236111</v>
@@ -11370,13 +11373,13 @@
         <v>26</v>
       </c>
       <c r="N166" s="6" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="O166" s="6" t="s">
         <v>173</v>
       </c>
       <c r="P166" s="6" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q166" s="6"/>
       <c r="R166" s="6"/>
@@ -11386,7 +11389,7 @@
     </row>
     <row r="167" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A167" s="7" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B167" s="8">
         <v>46132.632837384255</v>
@@ -11421,13 +11424,13 @@
         <v>26</v>
       </c>
       <c r="N167" s="9" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="O167" s="9" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="P167" s="9" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q167" s="9"/>
       <c r="R167" s="9"/>
@@ -11437,7 +11440,7 @@
     </row>
     <row r="168" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B168" s="5">
         <v>46132.63284362269</v>
@@ -11472,13 +11475,13 @@
         <v>26</v>
       </c>
       <c r="N168" s="6" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="O168" s="6" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="P168" s="6" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q168" s="6"/>
       <c r="R168" s="6"/>
@@ -11488,7 +11491,7 @@
     </row>
     <row r="169" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A169" s="7" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B169" s="8">
         <v>46132.63284975695</v>
@@ -11523,13 +11526,13 @@
         <v>26</v>
       </c>
       <c r="N169" s="9" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="O169" s="9" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="P169" s="9" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q169" s="9"/>
       <c r="R169" s="9"/>
@@ -11539,7 +11542,7 @@
     </row>
     <row r="170" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B170" s="5">
         <v>46132.63286226852</v>
@@ -11574,13 +11577,13 @@
         <v>26</v>
       </c>
       <c r="N170" s="6" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="O170" s="6" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="P170" s="6" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q170" s="6"/>
       <c r="R170" s="6"/>
@@ -11590,7 +11593,7 @@
     </row>
     <row r="171" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A171" s="7" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B171" s="8">
         <v>46132.63285675926</v>
@@ -11625,13 +11628,13 @@
         <v>26</v>
       </c>
       <c r="N171" s="9" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="O171" s="9" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="P171" s="9" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q171" s="9"/>
       <c r="R171" s="9"/>
@@ -11641,7 +11644,7 @@
     </row>
     <row r="172" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A172" s="4" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B172" s="5">
         <v>46132.63286828704</v>
@@ -11676,13 +11679,13 @@
         <v>26</v>
       </c>
       <c r="N172" s="6" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="O172" s="6" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="P172" s="6" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q172" s="6"/>
       <c r="R172" s="6"/>
@@ -11692,7 +11695,7 @@
     </row>
     <row r="173" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A173" s="7" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B173" s="8">
         <v>46132.63287412037</v>
@@ -11727,13 +11730,13 @@
         <v>26</v>
       </c>
       <c r="N173" s="9" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="O173" s="9" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="P173" s="9" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q173" s="9"/>
       <c r="R173" s="9"/>
@@ -11743,7 +11746,7 @@
     </row>
     <row r="174" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A174" s="4" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B174" s="5">
         <v>46132.63288133102</v>
@@ -11778,13 +11781,13 @@
         <v>26</v>
       </c>
       <c r="N174" s="6" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="O174" s="6" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="P174" s="6" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q174" s="6"/>
       <c r="R174" s="6"/>
@@ -11794,7 +11797,7 @@
     </row>
     <row r="175" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A175" s="7" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B175" s="8">
         <v>46132.63288800926</v>
@@ -11829,13 +11832,13 @@
         <v>26</v>
       </c>
       <c r="N175" s="9" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="O175" s="9" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="P175" s="9" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q175" s="9"/>
       <c r="R175" s="9"/>
@@ -11845,7 +11848,7 @@
     </row>
     <row r="176" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A176" s="4" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B176" s="5">
         <v>46132.63289421296</v>
@@ -11880,13 +11883,13 @@
         <v>26</v>
       </c>
       <c r="N176" s="6" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="O176" s="6" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="P176" s="6" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q176" s="6"/>
       <c r="R176" s="6"/>
@@ -11896,7 +11899,7 @@
     </row>
     <row r="177" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A177" s="7" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B177" s="8">
         <v>46132.63290028935</v>
@@ -11931,13 +11934,13 @@
         <v>26</v>
       </c>
       <c r="N177" s="9" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="O177" s="9" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="P177" s="9" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q177" s="9"/>
       <c r="R177" s="9"/>
@@ -11947,7 +11950,7 @@
     </row>
     <row r="178" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A178" s="4" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B178" s="5">
         <v>46132.632907719904</v>
@@ -11982,13 +11985,13 @@
         <v>26</v>
       </c>
       <c r="N178" s="6" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="O178" s="6" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="P178" s="6" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q178" s="6"/>
       <c r="R178" s="6"/>
@@ -11998,7 +12001,7 @@
     </row>
     <row r="179" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A179" s="7" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B179" s="8">
         <v>46132.58895258102</v>
@@ -12008,7 +12011,7 @@
         <v>46134.579160567126</v>
       </c>
       <c r="E179" s="9" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F179" s="9" t="s">
         <v>26</v>
@@ -12033,13 +12036,13 @@
         <v>26</v>
       </c>
       <c r="N179" s="9" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O179" s="9" t="s">
         <v>240</v>
       </c>
       <c r="P179" s="9" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q179" s="8">
         <v>46223</v>
@@ -12059,7 +12062,7 @@
     </row>
     <row r="180" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A180" s="4" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B180" s="5">
         <v>46132.63330006944</v>
@@ -12094,13 +12097,13 @@
         <v>26</v>
       </c>
       <c r="N180" s="6" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="O180" s="6" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="P180" s="6" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Q180" s="6"/>
       <c r="R180" s="6"/>
@@ -12110,7 +12113,7 @@
     </row>
     <row r="181" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A181" s="7" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B181" s="8">
         <v>46132.63330984954</v>
@@ -12145,13 +12148,13 @@
         <v>26</v>
       </c>
       <c r="N181" s="9" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="O181" s="9" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="P181" s="9" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="Q181" s="9"/>
       <c r="R181" s="9"/>
@@ -12161,7 +12164,7 @@
     </row>
     <row r="182" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A182" s="4" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B182" s="5">
         <v>46132.633316377316</v>
@@ -12196,13 +12199,13 @@
         <v>26</v>
       </c>
       <c r="N182" s="6" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="O182" s="6" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="P182" s="6" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Q182" s="6"/>
       <c r="R182" s="6"/>
@@ -12212,7 +12215,7 @@
     </row>
     <row r="183" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A183" s="7" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B183" s="8">
         <v>46132.63332333333</v>
@@ -12247,13 +12250,13 @@
         <v>26</v>
       </c>
       <c r="N183" s="9" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="O183" s="9" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="P183" s="9" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="Q183" s="9"/>
       <c r="R183" s="9"/>
@@ -12263,7 +12266,7 @@
     </row>
     <row r="184" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A184" s="4" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B184" s="5">
         <v>46132.63333568287</v>
@@ -12298,13 +12301,13 @@
         <v>26</v>
       </c>
       <c r="N184" s="6" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="O184" s="6" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="P184" s="6" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Q184" s="6"/>
       <c r="R184" s="6"/>
@@ -12314,7 +12317,7 @@
     </row>
     <row r="185" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A185" s="7" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B185" s="8">
         <v>46132.633329282406</v>
@@ -12349,13 +12352,13 @@
         <v>26</v>
       </c>
       <c r="N185" s="9" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="O185" s="9" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="P185" s="9" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="Q185" s="9"/>
       <c r="R185" s="9"/>
@@ -12365,7 +12368,7 @@
     </row>
     <row r="186" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A186" s="4" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B186" s="5">
         <v>46132.63334925926</v>
@@ -12400,13 +12403,13 @@
         <v>26</v>
       </c>
       <c r="N186" s="6" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="O186" s="6" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="P186" s="6" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Q186" s="6"/>
       <c r="R186" s="6"/>
@@ -12416,7 +12419,7 @@
     </row>
     <row r="187" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A187" s="7" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B187" s="8">
         <v>46132.633353321755</v>
@@ -12451,13 +12454,13 @@
         <v>26</v>
       </c>
       <c r="N187" s="9" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="O187" s="9" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="P187" s="9" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Q187" s="9"/>
       <c r="R187" s="9"/>
@@ -12467,7 +12470,7 @@
     </row>
     <row r="188" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A188" s="4" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B188" s="5">
         <v>46132.63336115741</v>
@@ -12502,13 +12505,13 @@
         <v>26</v>
       </c>
       <c r="N188" s="6" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="O188" s="6" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="P188" s="6" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="Q188" s="6"/>
       <c r="R188" s="6"/>
@@ -12518,7 +12521,7 @@
     </row>
     <row r="189" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A189" s="7" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B189" s="8">
         <v>46132.6333661574</v>
@@ -12553,13 +12556,13 @@
         <v>26</v>
       </c>
       <c r="N189" s="9" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="O189" s="9" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="P189" s="9" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Q189" s="9"/>
       <c r="R189" s="9"/>
@@ -12569,7 +12572,7 @@
     </row>
     <row r="190" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B190" s="5">
         <v>46132.633375046295</v>
@@ -12604,13 +12607,13 @@
         <v>26</v>
       </c>
       <c r="N190" s="6" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="O190" s="6" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="P190" s="6" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="Q190" s="6"/>
       <c r="R190" s="6"/>
@@ -12620,7 +12623,7 @@
     </row>
     <row r="191" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A191" s="7" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B191" s="8">
         <v>46132.63337950232</v>
@@ -12655,13 +12658,13 @@
         <v>26</v>
       </c>
       <c r="N191" s="9" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="O191" s="9" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="P191" s="9" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="Q191" s="9"/>
       <c r="R191" s="9"/>
@@ -12671,7 +12674,7 @@
     </row>
     <row r="192" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B192" s="5">
         <v>46132.63338666667</v>
@@ -12706,13 +12709,13 @@
         <v>26</v>
       </c>
       <c r="N192" s="6" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="O192" s="6" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="P192" s="6" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="Q192" s="6"/>
       <c r="R192" s="6"/>
@@ -12722,7 +12725,7 @@
     </row>
     <row r="193" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A193" s="7" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B193" s="8">
         <v>46132.63339375</v>
@@ -12757,13 +12760,13 @@
         <v>26</v>
       </c>
       <c r="N193" s="9" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="O193" s="9" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="P193" s="9" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="Q193" s="9"/>
       <c r="R193" s="9"/>
@@ -12773,7 +12776,7 @@
     </row>
     <row r="194" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B194" s="5">
         <v>46132.63339872685</v>
@@ -12808,13 +12811,13 @@
         <v>26</v>
       </c>
       <c r="N194" s="6" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="O194" s="6" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="P194" s="6" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="Q194" s="6"/>
       <c r="R194" s="6"/>
@@ -12824,7 +12827,7 @@
     </row>
     <row r="195" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A195" s="7" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B195" s="8">
         <v>46132.633404085645</v>
@@ -12859,13 +12862,13 @@
         <v>26</v>
       </c>
       <c r="N195" s="9" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="O195" s="9" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="P195" s="9" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="Q195" s="9"/>
       <c r="R195" s="9"/>
@@ -12875,7 +12878,7 @@
     </row>
     <row r="196" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B196" s="5">
         <v>46132.58900565973</v>
@@ -12885,7 +12888,7 @@
         <v>46134.579161331014</v>
       </c>
       <c r="E196" s="6" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F196" s="6" t="s">
         <v>26</v>
@@ -12910,13 +12913,13 @@
         <v>26</v>
       </c>
       <c r="N196" s="6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O196" s="6" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="P196" s="6" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="Q196" s="5">
         <v>46225</v>
@@ -12936,7 +12939,7 @@
     </row>
     <row r="197" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A197" s="7" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B197" s="8">
         <v>46132.6334534375</v>
@@ -12971,13 +12974,13 @@
         <v>26</v>
       </c>
       <c r="N197" s="9" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O197" s="9" t="s">
         <v>172</v>
       </c>
       <c r="P197" s="9" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="Q197" s="9"/>
       <c r="R197" s="9"/>
@@ -12987,7 +12990,7 @@
     </row>
     <row r="198" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A198" s="4" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B198" s="5">
         <v>46132.633462025464</v>
@@ -13022,13 +13025,13 @@
         <v>26</v>
       </c>
       <c r="N198" s="6" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O198" s="6" t="s">
         <v>176</v>
       </c>
       <c r="P198" s="6" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="Q198" s="6"/>
       <c r="R198" s="6"/>
@@ -13038,7 +13041,7 @@
     </row>
     <row r="199" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A199" s="7" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B199" s="8">
         <v>46132.633468622684</v>
@@ -13073,13 +13076,13 @@
         <v>26</v>
       </c>
       <c r="N199" s="9" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O199" s="9" t="s">
         <v>179</v>
       </c>
       <c r="P199" s="9" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="Q199" s="9"/>
       <c r="R199" s="9"/>
@@ -13089,7 +13092,7 @@
     </row>
     <row r="200" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A200" s="4" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B200" s="5">
         <v>46132.63347502315</v>
@@ -13124,13 +13127,13 @@
         <v>26</v>
       </c>
       <c r="N200" s="6" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O200" s="6" t="s">
         <v>181</v>
       </c>
       <c r="P200" s="6" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="Q200" s="6"/>
       <c r="R200" s="6"/>
@@ -13140,7 +13143,7 @@
     </row>
     <row r="201" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A201" s="7" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B201" s="8">
         <v>46132.63348070602</v>
@@ -13175,13 +13178,13 @@
         <v>26</v>
       </c>
       <c r="N201" s="9" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O201" s="9" t="s">
         <v>183</v>
       </c>
       <c r="P201" s="9" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="Q201" s="9"/>
       <c r="R201" s="9"/>
@@ -13191,7 +13194,7 @@
     </row>
     <row r="202" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A202" s="4" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B202" s="5">
         <v>46132.63348662037</v>
@@ -13226,13 +13229,13 @@
         <v>26</v>
       </c>
       <c r="N202" s="6" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O202" s="6" t="s">
         <v>185</v>
       </c>
       <c r="P202" s="6" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="Q202" s="6"/>
       <c r="R202" s="6"/>
@@ -13242,7 +13245,7 @@
     </row>
     <row r="203" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A203" s="7" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B203" s="8">
         <v>46132.63349295139</v>
@@ -13277,13 +13280,13 @@
         <v>26</v>
       </c>
       <c r="N203" s="9" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O203" s="9" t="s">
         <v>187</v>
       </c>
       <c r="P203" s="9" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="Q203" s="9"/>
       <c r="R203" s="9"/>
@@ -13293,7 +13296,7 @@
     </row>
     <row r="204" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A204" s="4" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B204" s="5">
         <v>46132.633500138894</v>
@@ -13328,13 +13331,13 @@
         <v>26</v>
       </c>
       <c r="N204" s="6" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O204" s="6" t="s">
         <v>190</v>
       </c>
       <c r="P204" s="6" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="Q204" s="6"/>
       <c r="R204" s="6"/>
@@ -13344,7 +13347,7 @@
     </row>
     <row r="205" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A205" s="7" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B205" s="8">
         <v>46132.633505983795</v>
@@ -13379,13 +13382,13 @@
         <v>26</v>
       </c>
       <c r="N205" s="9" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O205" s="9" t="s">
         <v>192</v>
       </c>
       <c r="P205" s="9" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="Q205" s="9"/>
       <c r="R205" s="9"/>
@@ -13395,7 +13398,7 @@
     </row>
     <row r="206" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A206" s="4" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B206" s="5">
         <v>46132.6335124537</v>
@@ -13430,13 +13433,13 @@
         <v>26</v>
       </c>
       <c r="N206" s="6" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O206" s="6" t="s">
         <v>194</v>
       </c>
       <c r="P206" s="6" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="Q206" s="6"/>
       <c r="R206" s="6"/>
@@ -13446,7 +13449,7 @@
     </row>
     <row r="207" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A207" s="7" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B207" s="8">
         <v>46132.63351974537</v>
@@ -13481,13 +13484,13 @@
         <v>26</v>
       </c>
       <c r="N207" s="9" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O207" s="9" t="s">
         <v>196</v>
       </c>
       <c r="P207" s="9" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="Q207" s="9"/>
       <c r="R207" s="9"/>
@@ -13497,7 +13500,7 @@
     </row>
     <row r="208" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A208" s="4" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B208" s="5">
         <v>46132.6335277662</v>
@@ -13532,13 +13535,13 @@
         <v>26</v>
       </c>
       <c r="N208" s="6" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O208" s="6" t="s">
         <v>198</v>
       </c>
       <c r="P208" s="6" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="Q208" s="6"/>
       <c r="R208" s="6"/>
@@ -13548,7 +13551,7 @@
     </row>
     <row r="209" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A209" s="7" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B209" s="8">
         <v>46132.633534988425</v>
@@ -13583,13 +13586,13 @@
         <v>26</v>
       </c>
       <c r="N209" s="9" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O209" s="9" t="s">
         <v>200</v>
       </c>
       <c r="P209" s="9" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="Q209" s="9"/>
       <c r="R209" s="9"/>
@@ -13599,7 +13602,7 @@
     </row>
     <row r="210" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A210" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B210" s="5">
         <v>46132.63354082176</v>
@@ -13634,13 +13637,13 @@
         <v>26</v>
       </c>
       <c r="N210" s="6" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O210" s="6" t="s">
         <v>202</v>
       </c>
       <c r="P210" s="6" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="Q210" s="6"/>
       <c r="R210" s="6"/>
@@ -13650,7 +13653,7 @@
     </row>
     <row r="211" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A211" s="7" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B211" s="8">
         <v>46132.63354760417</v>
@@ -13660,7 +13663,7 @@
         <v>46196.913837025466</v>
       </c>
       <c r="E211" s="9" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F211" s="9" t="s">
         <v>26</v>
@@ -13685,13 +13688,13 @@
         <v>26</v>
       </c>
       <c r="N211" s="9" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O211" s="9" t="s">
         <v>204</v>
       </c>
       <c r="P211" s="9" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="Q211" s="9"/>
       <c r="R211" s="9"/>
@@ -13701,7 +13704,7 @@
     </row>
     <row r="212" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A212" s="4" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B212" s="5">
         <v>46133.58300138889</v>
@@ -13711,7 +13714,7 @@
         <v>46196.91385334491</v>
       </c>
       <c r="E212" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F212" s="6" t="s">
         <v>26</v>
@@ -13736,13 +13739,13 @@
         <v>26</v>
       </c>
       <c r="N212" s="6" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O212" s="6" t="s">
         <v>207</v>
       </c>
       <c r="P212" s="6" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="Q212" s="6"/>
       <c r="R212" s="6"/>
@@ -13752,7 +13755,7 @@
     </row>
     <row r="213" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A213" s="7" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B213" s="8">
         <v>46132.589012916666</v>
@@ -13762,7 +13765,7 @@
         <v>46133.58769056713</v>
       </c>
       <c r="E213" s="9" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F213" s="9" t="s">
         <v>25</v>
@@ -13786,7 +13789,7 @@
         <v>26</v>
       </c>
       <c r="O213" s="9" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="P213" s="9" t="s">
         <v>26</v>
@@ -13799,7 +13802,7 @@
     </row>
     <row r="214" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A214" s="4" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B214" s="5">
         <v>46132.589016666665</v>
@@ -13809,16 +13812,16 @@
         <v>46133.58482033564</v>
       </c>
       <c r="E214" s="6" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="F214" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G214" s="6" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H214" s="6" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="I214" s="6"/>
       <c r="J214" s="5">
@@ -13834,13 +13837,13 @@
         <v>26</v>
       </c>
       <c r="N214" s="6" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="O214" s="6" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="P214" s="6" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="Q214" s="5">
         <v>46226</v>
@@ -13860,7 +13863,7 @@
     </row>
     <row r="215" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A215" s="7" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B215" s="8">
         <v>46132.63360670139</v>
@@ -13876,10 +13879,10 @@
         <v>26</v>
       </c>
       <c r="G215" s="9" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H215" s="9" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="I215" s="9"/>
       <c r="J215" s="8">
@@ -13895,7 +13898,7 @@
         <v>26</v>
       </c>
       <c r="N215" s="9" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O215" s="9" t="s">
         <v>173</v>
@@ -13911,7 +13914,7 @@
     </row>
     <row r="216" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A216" s="4" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B216" s="5">
         <v>46132.63361304398</v>
@@ -13927,10 +13930,10 @@
         <v>26</v>
       </c>
       <c r="G216" s="6" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H216" s="6" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="I216" s="6"/>
       <c r="J216" s="5">
@@ -13946,7 +13949,7 @@
         <v>26</v>
       </c>
       <c r="N216" s="6" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O216" s="6" t="s">
         <v>173</v>
@@ -13962,7 +13965,7 @@
     </row>
     <row r="217" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A217" s="7" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B217" s="8">
         <v>46132.63361974537</v>
@@ -13978,10 +13981,10 @@
         <v>26</v>
       </c>
       <c r="G217" s="9" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H217" s="9" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="I217" s="9"/>
       <c r="J217" s="8">
@@ -13997,7 +14000,7 @@
         <v>26</v>
       </c>
       <c r="N217" s="9" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O217" s="9" t="s">
         <v>173</v>
@@ -14013,7 +14016,7 @@
     </row>
     <row r="218" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A218" s="4" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B218" s="5">
         <v>46132.63363137731</v>
@@ -14029,10 +14032,10 @@
         <v>26</v>
       </c>
       <c r="G218" s="6" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H218" s="6" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="I218" s="6"/>
       <c r="J218" s="5">
@@ -14048,7 +14051,7 @@
         <v>26</v>
       </c>
       <c r="N218" s="6" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O218" s="6" t="s">
         <v>173</v>
@@ -14064,7 +14067,7 @@
     </row>
     <row r="219" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A219" s="7" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B219" s="8">
         <v>46132.63362555555</v>
@@ -14080,10 +14083,10 @@
         <v>26</v>
       </c>
       <c r="G219" s="9" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H219" s="9" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="I219" s="9"/>
       <c r="J219" s="8">
@@ -14099,7 +14102,7 @@
         <v>26</v>
       </c>
       <c r="N219" s="9" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O219" s="9" t="s">
         <v>173</v>
@@ -14115,7 +14118,7 @@
     </row>
     <row r="220" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A220" s="4" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B220" s="5">
         <v>46132.63363859954</v>
@@ -14131,10 +14134,10 @@
         <v>26</v>
       </c>
       <c r="G220" s="6" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H220" s="6" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="I220" s="6"/>
       <c r="J220" s="5">
@@ -14150,7 +14153,7 @@
         <v>26</v>
       </c>
       <c r="N220" s="6" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O220" s="6" t="s">
         <v>173</v>
@@ -14166,7 +14169,7 @@
     </row>
     <row r="221" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A221" s="7" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B221" s="8">
         <v>46132.63364667824</v>
@@ -14176,16 +14179,16 @@
         <v>46196.913939861115</v>
       </c>
       <c r="E221" s="9" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F221" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G221" s="9" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H221" s="9" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="I221" s="9"/>
       <c r="J221" s="8">
@@ -14201,7 +14204,7 @@
         <v>26</v>
       </c>
       <c r="N221" s="9" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O221" s="9" t="s">
         <v>173</v>
@@ -14217,7 +14220,7 @@
     </row>
     <row r="222" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A222" s="4" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B222" s="5">
         <v>46132.633653055556</v>
@@ -14233,10 +14236,10 @@
         <v>26</v>
       </c>
       <c r="G222" s="6" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H222" s="6" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="I222" s="6"/>
       <c r="J222" s="5">
@@ -14252,7 +14255,7 @@
         <v>26</v>
       </c>
       <c r="N222" s="6" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O222" s="6" t="s">
         <v>173</v>
@@ -14268,7 +14271,7 @@
     </row>
     <row r="223" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A223" s="7" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B223" s="8">
         <v>46132.63365921297</v>
@@ -14284,10 +14287,10 @@
         <v>26</v>
       </c>
       <c r="G223" s="9" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H223" s="9" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="I223" s="9"/>
       <c r="J223" s="8">
@@ -14303,7 +14306,7 @@
         <v>26</v>
       </c>
       <c r="N223" s="9" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O223" s="9" t="s">
         <v>173</v>
@@ -14319,7 +14322,7 @@
     </row>
     <row r="224" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A224" s="4" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B224" s="5">
         <v>46132.633665347224</v>
@@ -14335,10 +14338,10 @@
         <v>26</v>
       </c>
       <c r="G224" s="6" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H224" s="6" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="I224" s="6"/>
       <c r="J224" s="5">
@@ -14354,7 +14357,7 @@
         <v>26</v>
       </c>
       <c r="N224" s="6" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O224" s="6" t="s">
         <v>173</v>
@@ -14370,7 +14373,7 @@
     </row>
     <row r="225" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A225" s="7" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B225" s="8">
         <v>46132.63367407407</v>
@@ -14386,10 +14389,10 @@
         <v>26</v>
       </c>
       <c r="G225" s="9" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H225" s="9" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="I225" s="9"/>
       <c r="J225" s="8">
@@ -14405,7 +14408,7 @@
         <v>26</v>
       </c>
       <c r="N225" s="9" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O225" s="9" t="s">
         <v>173</v>
@@ -14421,7 +14424,7 @@
     </row>
     <row r="226" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A226" s="4" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B226" s="5">
         <v>46132.63368225694</v>
@@ -14437,10 +14440,10 @@
         <v>26</v>
       </c>
       <c r="G226" s="6" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H226" s="6" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="I226" s="6"/>
       <c r="J226" s="5">
@@ -14456,7 +14459,7 @@
         <v>26</v>
       </c>
       <c r="N226" s="6" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O226" s="6" t="s">
         <v>173</v>
@@ -14472,7 +14475,7 @@
     </row>
     <row r="227" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A227" s="7" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B227" s="8">
         <v>46132.63368885417</v>
@@ -14488,10 +14491,10 @@
         <v>26</v>
       </c>
       <c r="G227" s="9" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H227" s="9" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="I227" s="9"/>
       <c r="J227" s="8">
@@ -14507,7 +14510,7 @@
         <v>26</v>
       </c>
       <c r="N227" s="9" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O227" s="9" t="s">
         <v>173</v>
@@ -14523,7 +14526,7 @@
     </row>
     <row r="228" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A228" s="4" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B228" s="5">
         <v>46132.633694965276</v>
@@ -14539,10 +14542,10 @@
         <v>26</v>
       </c>
       <c r="G228" s="6" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H228" s="6" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="I228" s="6"/>
       <c r="J228" s="5">
@@ -14558,7 +14561,7 @@
         <v>26</v>
       </c>
       <c r="N228" s="6" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O228" s="6" t="s">
         <v>173</v>
@@ -14574,7 +14577,7 @@
     </row>
     <row r="229" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A229" s="7" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B229" s="8">
         <v>46132.63370111111</v>
@@ -14584,16 +14587,16 @@
         <v>46196.9140217824</v>
       </c>
       <c r="E229" s="9" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F229" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G229" s="9" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H229" s="9" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="I229" s="9"/>
       <c r="J229" s="8">
@@ -14609,13 +14612,13 @@
         <v>26</v>
       </c>
       <c r="N229" s="9" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O229" s="9" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="P229" s="9" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="Q229" s="9"/>
       <c r="R229" s="9"/>
@@ -14625,7 +14628,7 @@
     </row>
     <row r="230" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A230" s="4" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B230" s="5">
         <v>46132.63378953704</v>
@@ -14641,10 +14644,10 @@
         <v>26</v>
       </c>
       <c r="G230" s="6" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H230" s="6" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="I230" s="6"/>
       <c r="J230" s="5">
@@ -14660,10 +14663,10 @@
         <v>26</v>
       </c>
       <c r="N230" s="6" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O230" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P230" s="6" t="s">
         <v>173</v>
@@ -14676,7 +14679,7 @@
     </row>
     <row r="231" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A231" s="7" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B231" s="8">
         <v>46132.589021736116</v>
@@ -14686,7 +14689,7 @@
         <v>46133.58651043981</v>
       </c>
       <c r="E231" s="9" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F231" s="9" t="s">
         <v>26</v>
@@ -14711,13 +14714,13 @@
         <v>26</v>
       </c>
       <c r="N231" s="9" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="O231" s="9" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="P231" s="9" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="Q231" s="8">
         <v>46227</v>
@@ -14737,7 +14740,7 @@
     </row>
     <row r="232" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A232" s="4" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B232" s="5">
         <v>46132.633861608796</v>
@@ -14772,7 +14775,7 @@
         <v>26</v>
       </c>
       <c r="N232" s="6" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O232" s="6" t="s">
         <v>173</v>
@@ -14788,7 +14791,7 @@
     </row>
     <row r="233" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A233" s="7" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B233" s="8">
         <v>46132.633870011574</v>
@@ -14823,7 +14826,7 @@
         <v>26</v>
       </c>
       <c r="N233" s="9" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O233" s="9" t="s">
         <v>173</v>
@@ -14839,7 +14842,7 @@
     </row>
     <row r="234" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A234" s="4" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B234" s="5">
         <v>46132.63387658565</v>
@@ -14874,7 +14877,7 @@
         <v>26</v>
       </c>
       <c r="N234" s="6" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O234" s="6" t="s">
         <v>173</v>
@@ -14890,7 +14893,7 @@
     </row>
     <row r="235" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A235" s="7" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B235" s="8">
         <v>46132.63388259259</v>
@@ -14925,7 +14928,7 @@
         <v>26</v>
       </c>
       <c r="N235" s="9" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O235" s="9" t="s">
         <v>173</v>
@@ -14941,7 +14944,7 @@
     </row>
     <row r="236" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A236" s="4" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B236" s="5">
         <v>46132.63388633102</v>
@@ -14976,7 +14979,7 @@
         <v>26</v>
       </c>
       <c r="N236" s="6" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O236" s="6" t="s">
         <v>173</v>
@@ -14992,7 +14995,7 @@
     </row>
     <row r="237" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A237" s="7" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B237" s="8">
         <v>46132.63389106482</v>
@@ -15027,7 +15030,7 @@
         <v>26</v>
       </c>
       <c r="N237" s="9" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O237" s="9" t="s">
         <v>173</v>
@@ -15043,7 +15046,7 @@
     </row>
     <row r="238" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A238" s="4" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B238" s="5">
         <v>46132.63389739583</v>
@@ -15078,10 +15081,10 @@
         <v>26</v>
       </c>
       <c r="N238" s="6" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O238" s="6" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="P238" s="6" t="s">
         <v>173</v>
@@ -15094,7 +15097,7 @@
     </row>
     <row r="239" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A239" s="7" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B239" s="8">
         <v>46132.63390288195</v>
@@ -15129,7 +15132,7 @@
         <v>26</v>
       </c>
       <c r="N239" s="9" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O239" s="9" t="s">
         <v>173</v>
@@ -15145,7 +15148,7 @@
     </row>
     <row r="240" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A240" s="4" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B240" s="5">
         <v>46132.63390861111</v>
@@ -15180,7 +15183,7 @@
         <v>26</v>
       </c>
       <c r="N240" s="6" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O240" s="6" t="s">
         <v>173</v>
@@ -15196,7 +15199,7 @@
     </row>
     <row r="241" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A241" s="7" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B241" s="8">
         <v>46132.63391276621</v>
@@ -15231,7 +15234,7 @@
         <v>26</v>
       </c>
       <c r="N241" s="9" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O241" s="9" t="s">
         <v>173</v>
@@ -15247,7 +15250,7 @@
     </row>
     <row r="242" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A242" s="4" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B242" s="5">
         <v>46132.63391880787</v>
@@ -15282,7 +15285,7 @@
         <v>26</v>
       </c>
       <c r="N242" s="6" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O242" s="6" t="s">
         <v>173</v>
@@ -15298,7 +15301,7 @@
     </row>
     <row r="243" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A243" s="7" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B243" s="8">
         <v>46132.63392302083</v>
@@ -15333,7 +15336,7 @@
         <v>26</v>
       </c>
       <c r="N243" s="9" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O243" s="9" t="s">
         <v>173</v>
@@ -15349,7 +15352,7 @@
     </row>
     <row r="244" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A244" s="4" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B244" s="5">
         <v>46132.63393041666</v>
@@ -15384,7 +15387,7 @@
         <v>26</v>
       </c>
       <c r="N244" s="6" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O244" s="6" t="s">
         <v>173</v>
@@ -15400,7 +15403,7 @@
     </row>
     <row r="245" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A245" s="7" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B245" s="8">
         <v>46132.63393689815</v>
@@ -15435,7 +15438,7 @@
         <v>26</v>
       </c>
       <c r="N245" s="9" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O245" s="9" t="s">
         <v>173</v>
@@ -15451,7 +15454,7 @@
     </row>
     <row r="246" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A246" s="4" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B246" s="5">
         <v>46132.633943078705</v>
@@ -15461,7 +15464,7 @@
         <v>46196.91419930555</v>
       </c>
       <c r="E246" s="6" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F246" s="6" t="s">
         <v>26</v>
@@ -15486,10 +15489,10 @@
         <v>26</v>
       </c>
       <c r="N246" s="6" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O246" s="6" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="P246" s="6" t="s">
         <v>173</v>
@@ -15502,7 +15505,7 @@
     </row>
     <row r="247" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A247" s="7" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B247" s="8">
         <v>46132.633955578705</v>
@@ -15537,7 +15540,7 @@
         <v>26</v>
       </c>
       <c r="N247" s="9" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O247" s="9" t="s">
         <v>173</v>
@@ -15553,7 +15556,7 @@
     </row>
     <row r="248" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A248" s="4" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B248" s="5">
         <v>46132.58902681713</v>
@@ -15563,16 +15566,16 @@
         <v>46133.58721105324</v>
       </c>
       <c r="E248" s="6" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="F248" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G248" s="6" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H248" s="6" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I248" s="5">
         <v>46230</v>
@@ -15590,13 +15593,13 @@
         <v>26</v>
       </c>
       <c r="N248" s="6" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="O248" s="6" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="P248" s="6" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="Q248" s="5">
         <v>46230</v>
@@ -15616,7 +15619,7 @@
     </row>
     <row r="249" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A249" s="7" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B249" s="8">
         <v>46132.634024432875</v>
@@ -15632,10 +15635,10 @@
         <v>26</v>
       </c>
       <c r="G249" s="9" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H249" s="9" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I249" s="9"/>
       <c r="J249" s="8">
@@ -15651,7 +15654,7 @@
         <v>26</v>
       </c>
       <c r="N249" s="9" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="O249" s="9" t="s">
         <v>173</v>
@@ -15667,7 +15670,7 @@
     </row>
     <row r="250" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A250" s="4" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B250" s="5">
         <v>46132.634032685186</v>
@@ -15683,10 +15686,10 @@
         <v>26</v>
       </c>
       <c r="G250" s="6" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H250" s="6" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I250" s="6"/>
       <c r="J250" s="5">
@@ -15702,7 +15705,7 @@
         <v>26</v>
       </c>
       <c r="N250" s="6" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="O250" s="6" t="s">
         <v>173</v>
@@ -15718,7 +15721,7 @@
     </row>
     <row r="251" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A251" s="7" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B251" s="8">
         <v>46132.63404001157</v>
@@ -15734,10 +15737,10 @@
         <v>26</v>
       </c>
       <c r="G251" s="9" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H251" s="9" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I251" s="9"/>
       <c r="J251" s="8">
@@ -15753,7 +15756,7 @@
         <v>26</v>
       </c>
       <c r="N251" s="9" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="O251" s="9" t="s">
         <v>173</v>
@@ -15769,7 +15772,7 @@
     </row>
     <row r="252" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A252" s="4" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B252" s="5">
         <v>46132.63404659722</v>
@@ -15785,10 +15788,10 @@
         <v>26</v>
       </c>
       <c r="G252" s="6" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H252" s="6" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I252" s="6"/>
       <c r="J252" s="5">
@@ -15804,7 +15807,7 @@
         <v>26</v>
       </c>
       <c r="N252" s="6" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="O252" s="6" t="s">
         <v>173</v>
@@ -15820,7 +15823,7 @@
     </row>
     <row r="253" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A253" s="7" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B253" s="8">
         <v>46132.6340537037</v>
@@ -15836,10 +15839,10 @@
         <v>26</v>
       </c>
       <c r="G253" s="9" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H253" s="9" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I253" s="9"/>
       <c r="J253" s="8">
@@ -15855,7 +15858,7 @@
         <v>26</v>
       </c>
       <c r="N253" s="9" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="O253" s="9" t="s">
         <v>173</v>
@@ -15871,7 +15874,7 @@
     </row>
     <row r="254" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A254" s="4" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B254" s="5">
         <v>46132.63406115741</v>
@@ -15887,10 +15890,10 @@
         <v>26</v>
       </c>
       <c r="G254" s="6" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H254" s="6" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I254" s="6"/>
       <c r="J254" s="5">
@@ -15906,7 +15909,7 @@
         <v>26</v>
       </c>
       <c r="N254" s="6" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="O254" s="6" t="s">
         <v>173</v>
@@ -15922,7 +15925,7 @@
     </row>
     <row r="255" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A255" s="7" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B255" s="8">
         <v>46132.63406662037</v>
@@ -15938,10 +15941,10 @@
         <v>26</v>
       </c>
       <c r="G255" s="9" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H255" s="9" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I255" s="9"/>
       <c r="J255" s="8">
@@ -15957,7 +15960,7 @@
         <v>26</v>
       </c>
       <c r="N255" s="9" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="O255" s="9" t="s">
         <v>173</v>
@@ -15973,7 +15976,7 @@
     </row>
     <row r="256" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A256" s="4" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B256" s="5">
         <v>46132.634072395835</v>
@@ -15989,10 +15992,10 @@
         <v>26</v>
       </c>
       <c r="G256" s="6" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H256" s="6" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I256" s="6"/>
       <c r="J256" s="5">
@@ -16008,7 +16011,7 @@
         <v>26</v>
       </c>
       <c r="N256" s="6" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="O256" s="6" t="s">
         <v>173</v>
@@ -16024,7 +16027,7 @@
     </row>
     <row r="257" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A257" s="7" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B257" s="8">
         <v>46132.6340770949</v>
@@ -16040,10 +16043,10 @@
         <v>26</v>
       </c>
       <c r="G257" s="9" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H257" s="9" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I257" s="9"/>
       <c r="J257" s="8">
@@ -16059,7 +16062,7 @@
         <v>26</v>
       </c>
       <c r="N257" s="9" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="O257" s="9" t="s">
         <v>173</v>
@@ -16075,7 +16078,7 @@
     </row>
     <row r="258" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A258" s="4" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B258" s="5">
         <v>46132.634082777775</v>
@@ -16091,10 +16094,10 @@
         <v>26</v>
       </c>
       <c r="G258" s="6" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H258" s="6" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I258" s="6"/>
       <c r="J258" s="5">
@@ -16110,7 +16113,7 @@
         <v>26</v>
       </c>
       <c r="N258" s="6" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="O258" s="6" t="s">
         <v>173</v>
@@ -16126,7 +16129,7 @@
     </row>
     <row r="259" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A259" s="7" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B259" s="8">
         <v>46132.63408899306</v>
@@ -16142,10 +16145,10 @@
         <v>26</v>
       </c>
       <c r="G259" s="9" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H259" s="9" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I259" s="9"/>
       <c r="J259" s="8">
@@ -16161,7 +16164,7 @@
         <v>26</v>
       </c>
       <c r="N259" s="9" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="O259" s="9" t="s">
         <v>173</v>
@@ -16177,7 +16180,7 @@
     </row>
     <row r="260" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A260" s="4" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B260" s="5">
         <v>46132.63409545139</v>
@@ -16193,10 +16196,10 @@
         <v>26</v>
       </c>
       <c r="G260" s="6" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H260" s="6" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I260" s="6"/>
       <c r="J260" s="5">
@@ -16212,7 +16215,7 @@
         <v>26</v>
       </c>
       <c r="N260" s="6" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="O260" s="6" t="s">
         <v>173</v>
@@ -16228,7 +16231,7 @@
     </row>
     <row r="261" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A261" s="7" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B261" s="8">
         <v>46132.63410087963</v>
@@ -16244,10 +16247,10 @@
         <v>26</v>
       </c>
       <c r="G261" s="9" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H261" s="9" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I261" s="9"/>
       <c r="J261" s="8">
@@ -16263,7 +16266,7 @@
         <v>26</v>
       </c>
       <c r="N261" s="9" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="O261" s="9" t="s">
         <v>173</v>
@@ -16279,7 +16282,7 @@
     </row>
     <row r="262" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A262" s="4" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B262" s="5">
         <v>46132.63410688657</v>
@@ -16295,10 +16298,10 @@
         <v>26</v>
       </c>
       <c r="G262" s="6" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H262" s="6" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I262" s="6"/>
       <c r="J262" s="5">
@@ -16314,7 +16317,7 @@
         <v>26</v>
       </c>
       <c r="N262" s="6" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="O262" s="6" t="s">
         <v>173</v>
@@ -16330,7 +16333,7 @@
     </row>
     <row r="263" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A263" s="7" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B263" s="8">
         <v>46132.6341133449</v>
@@ -16346,10 +16349,10 @@
         <v>26</v>
       </c>
       <c r="G263" s="9" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H263" s="9" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I263" s="9"/>
       <c r="J263" s="8">
@@ -16365,10 +16368,10 @@
         <v>26</v>
       </c>
       <c r="N263" s="9" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="O263" s="9" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="P263" s="9" t="s">
         <v>173</v>
@@ -16381,7 +16384,7 @@
     </row>
     <row r="264" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A264" s="4" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B264" s="5">
         <v>46132.63411966435</v>
@@ -16397,10 +16400,10 @@
         <v>26</v>
       </c>
       <c r="G264" s="6" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H264" s="6" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I264" s="6"/>
       <c r="J264" s="5">
@@ -16416,7 +16419,7 @@
         <v>26</v>
       </c>
       <c r="N264" s="6" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="O264" s="6" t="s">
         <v>173</v>
@@ -16432,7 +16435,7 @@
     </row>
     <row r="265" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A265" s="7" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B265" s="8">
         <v>46132.58903189815</v>
@@ -16442,16 +16445,16 @@
         <v>46133.65412578704</v>
       </c>
       <c r="E265" s="9" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="F265" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G265" s="9" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H265" s="9" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I265" s="9"/>
       <c r="J265" s="8">
@@ -16467,13 +16470,13 @@
         <v>26</v>
       </c>
       <c r="N265" s="9" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="O265" s="9" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="P265" s="9" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="Q265" s="8">
         <v>46231</v>
@@ -16493,7 +16496,7 @@
     </row>
     <row r="266" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A266" s="4" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B266" s="5">
         <v>46132.63422869213</v>
@@ -16509,10 +16512,10 @@
         <v>26</v>
       </c>
       <c r="G266" s="6" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H266" s="6" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I266" s="6"/>
       <c r="J266" s="5">
@@ -16528,13 +16531,13 @@
         <v>26</v>
       </c>
       <c r="N266" s="6" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="O266" s="6" t="s">
         <v>173</v>
       </c>
       <c r="P266" s="6" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="Q266" s="6"/>
       <c r="R266" s="6"/>
@@ -16544,7 +16547,7 @@
     </row>
     <row r="267" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A267" s="7" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B267" s="8">
         <v>46132.63423491898</v>
@@ -16560,10 +16563,10 @@
         <v>26</v>
       </c>
       <c r="G267" s="9" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H267" s="9" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I267" s="9"/>
       <c r="J267" s="8">
@@ -16579,13 +16582,13 @@
         <v>26</v>
       </c>
       <c r="N267" s="9" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="O267" s="9" t="s">
         <v>173</v>
       </c>
       <c r="P267" s="9" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="Q267" s="9"/>
       <c r="R267" s="9"/>
@@ -16595,7 +16598,7 @@
     </row>
     <row r="268" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A268" s="4" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B268" s="5">
         <v>46132.634240960644</v>
@@ -16611,10 +16614,10 @@
         <v>26</v>
       </c>
       <c r="G268" s="6" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H268" s="6" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I268" s="6"/>
       <c r="J268" s="5">
@@ -16630,13 +16633,13 @@
         <v>26</v>
       </c>
       <c r="N268" s="6" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="O268" s="6" t="s">
         <v>173</v>
       </c>
       <c r="P268" s="6" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="Q268" s="6"/>
       <c r="R268" s="6"/>
@@ -16646,7 +16649,7 @@
     </row>
     <row r="269" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A269" s="7" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B269" s="8">
         <v>46132.63424789352</v>
@@ -16662,10 +16665,10 @@
         <v>26</v>
       </c>
       <c r="G269" s="9" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H269" s="9" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I269" s="9"/>
       <c r="J269" s="8">
@@ -16681,13 +16684,13 @@
         <v>26</v>
       </c>
       <c r="N269" s="9" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="O269" s="9" t="s">
         <v>173</v>
       </c>
       <c r="P269" s="9" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="Q269" s="9"/>
       <c r="R269" s="9"/>
@@ -16697,7 +16700,7 @@
     </row>
     <row r="270" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A270" s="4" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B270" s="5">
         <v>46132.634254386576</v>
@@ -16713,10 +16716,10 @@
         <v>26</v>
       </c>
       <c r="G270" s="6" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H270" s="6" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I270" s="6"/>
       <c r="J270" s="5">
@@ -16732,13 +16735,13 @@
         <v>26</v>
       </c>
       <c r="N270" s="6" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="O270" s="6" t="s">
         <v>173</v>
       </c>
       <c r="P270" s="6" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="Q270" s="6"/>
       <c r="R270" s="6"/>
@@ -16748,7 +16751,7 @@
     </row>
     <row r="271" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A271" s="7" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B271" s="8">
         <v>46132.634260810184</v>
@@ -16764,10 +16767,10 @@
         <v>26</v>
       </c>
       <c r="G271" s="9" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H271" s="9" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I271" s="9"/>
       <c r="J271" s="8">
@@ -16783,13 +16786,13 @@
         <v>26</v>
       </c>
       <c r="N271" s="9" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="O271" s="9" t="s">
         <v>173</v>
       </c>
       <c r="P271" s="9" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="Q271" s="9"/>
       <c r="R271" s="9"/>
@@ -16799,7 +16802,7 @@
     </row>
     <row r="272" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A272" s="4" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B272" s="5">
         <v>46132.634267256944</v>
@@ -16815,10 +16818,10 @@
         <v>26</v>
       </c>
       <c r="G272" s="6" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H272" s="6" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I272" s="6"/>
       <c r="J272" s="5">
@@ -16834,13 +16837,13 @@
         <v>26</v>
       </c>
       <c r="N272" s="6" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="O272" s="6" t="s">
         <v>173</v>
       </c>
       <c r="P272" s="6" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="Q272" s="6"/>
       <c r="R272" s="6"/>
@@ -16850,7 +16853,7 @@
     </row>
     <row r="273" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A273" s="7" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B273" s="8">
         <v>46132.63427122685</v>
@@ -16866,10 +16869,10 @@
         <v>26</v>
       </c>
       <c r="G273" s="9" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H273" s="9" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I273" s="9"/>
       <c r="J273" s="8">
@@ -16885,13 +16888,13 @@
         <v>26</v>
       </c>
       <c r="N273" s="9" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="O273" s="9" t="s">
         <v>173</v>
       </c>
       <c r="P273" s="9" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="Q273" s="9"/>
       <c r="R273" s="9"/>
@@ -16901,7 +16904,7 @@
     </row>
     <row r="274" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A274" s="4" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B274" s="5">
         <v>46132.634276365745</v>
@@ -16917,10 +16920,10 @@
         <v>26</v>
       </c>
       <c r="G274" s="6" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H274" s="6" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I274" s="6"/>
       <c r="J274" s="5">
@@ -16936,13 +16939,13 @@
         <v>26</v>
       </c>
       <c r="N274" s="6" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="O274" s="6" t="s">
         <v>173</v>
       </c>
       <c r="P274" s="6" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="Q274" s="6"/>
       <c r="R274" s="6"/>
@@ -16952,7 +16955,7 @@
     </row>
     <row r="275" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A275" s="7" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B275" s="8">
         <v>46132.63428099537</v>
@@ -16968,10 +16971,10 @@
         <v>26</v>
       </c>
       <c r="G275" s="9" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H275" s="9" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I275" s="9"/>
       <c r="J275" s="8">
@@ -16987,13 +16990,13 @@
         <v>26</v>
       </c>
       <c r="N275" s="9" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="O275" s="9" t="s">
         <v>173</v>
       </c>
       <c r="P275" s="9" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="Q275" s="9"/>
       <c r="R275" s="9"/>
@@ -17003,7 +17006,7 @@
     </row>
     <row r="276" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A276" s="4" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B276" s="5">
         <v>46132.63428524305</v>
@@ -17019,10 +17022,10 @@
         <v>26</v>
       </c>
       <c r="G276" s="6" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H276" s="6" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I276" s="6"/>
       <c r="J276" s="5">
@@ -17038,13 +17041,13 @@
         <v>26</v>
       </c>
       <c r="N276" s="6" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="O276" s="6" t="s">
         <v>173</v>
       </c>
       <c r="P276" s="6" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="Q276" s="6"/>
       <c r="R276" s="6"/>
@@ -17054,7 +17057,7 @@
     </row>
     <row r="277" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A277" s="7" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B277" s="8">
         <v>46132.63429103009</v>
@@ -17070,10 +17073,10 @@
         <v>26</v>
       </c>
       <c r="G277" s="9" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H277" s="9" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I277" s="9"/>
       <c r="J277" s="8">
@@ -17089,13 +17092,13 @@
         <v>26</v>
       </c>
       <c r="N277" s="9" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="O277" s="9" t="s">
         <v>173</v>
       </c>
       <c r="P277" s="9" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="Q277" s="9"/>
       <c r="R277" s="9"/>
@@ -17105,7 +17108,7 @@
     </row>
     <row r="278" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A278" s="4" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B278" s="5">
         <v>46132.63429523148</v>
@@ -17121,10 +17124,10 @@
         <v>26</v>
       </c>
       <c r="G278" s="6" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H278" s="6" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I278" s="6"/>
       <c r="J278" s="5">
@@ -17140,13 +17143,13 @@
         <v>26</v>
       </c>
       <c r="N278" s="6" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="O278" s="6" t="s">
         <v>173</v>
       </c>
       <c r="P278" s="6" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="Q278" s="6"/>
       <c r="R278" s="6"/>
@@ -17156,7 +17159,7 @@
     </row>
     <row r="279" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A279" s="7" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B279" s="8">
         <v>46132.63430358796</v>
@@ -17172,10 +17175,10 @@
         <v>26</v>
       </c>
       <c r="G279" s="9" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H279" s="9" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I279" s="9"/>
       <c r="J279" s="8">
@@ -17191,13 +17194,13 @@
         <v>26</v>
       </c>
       <c r="N279" s="9" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="O279" s="9" t="s">
         <v>173</v>
       </c>
       <c r="P279" s="9" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="Q279" s="9"/>
       <c r="R279" s="9"/>
@@ -17207,7 +17210,7 @@
     </row>
     <row r="280" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A280" s="4" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B280" s="5">
         <v>46132.63431148148</v>
@@ -17223,10 +17226,10 @@
         <v>26</v>
       </c>
       <c r="G280" s="6" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H280" s="6" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I280" s="6"/>
       <c r="J280" s="5">
@@ -17242,13 +17245,13 @@
         <v>26</v>
       </c>
       <c r="N280" s="6" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="O280" s="6" t="s">
         <v>173</v>
       </c>
       <c r="P280" s="6" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="Q280" s="6"/>
       <c r="R280" s="6"/>
@@ -17258,7 +17261,7 @@
     </row>
     <row r="281" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A281" s="7" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B281" s="8">
         <v>46132.63437663195</v>
@@ -17274,10 +17277,10 @@
         <v>26</v>
       </c>
       <c r="G281" s="9" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H281" s="9" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I281" s="9"/>
       <c r="J281" s="8">
@@ -17293,13 +17296,13 @@
         <v>26</v>
       </c>
       <c r="N281" s="9" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="O281" s="9" t="s">
         <v>173</v>
       </c>
       <c r="P281" s="9" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="Q281" s="9"/>
       <c r="R281" s="9"/>
@@ -17309,7 +17312,7 @@
     </row>
     <row r="282" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A282" s="4" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B282" s="5">
         <v>46132.589037604164</v>
@@ -17319,7 +17322,7 @@
         <v>46133.59235670139</v>
       </c>
       <c r="E282" s="6" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="F282" s="6" t="s">
         <v>25</v>
@@ -17343,7 +17346,7 @@
         <v>26</v>
       </c>
       <c r="O282" s="6" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="P282" s="6" t="s">
         <v>26</v>
@@ -17356,7 +17359,7 @@
     </row>
     <row r="283" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A283" s="7" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B283" s="8">
         <v>46132.5890406713</v>
@@ -17366,16 +17369,16 @@
         <v>46134.57925581018</v>
       </c>
       <c r="E283" s="9" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="F283" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G283" s="9" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H283" s="9" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="I283" s="8">
         <v>46232</v>
@@ -17393,13 +17396,13 @@
         <v>26</v>
       </c>
       <c r="N283" s="9" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="O283" s="9" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="P283" s="9" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="Q283" s="8">
         <v>46240</v>
@@ -17419,7 +17422,7 @@
     </row>
     <row r="284" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A284" s="4" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B284" s="5">
         <v>46132.58904559028</v>
@@ -17429,16 +17432,16 @@
         <v>46198.65442142361</v>
       </c>
       <c r="E284" s="6" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="F284" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G284" s="6" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H284" s="6" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="I284" s="5">
         <v>46232</v>
@@ -17456,13 +17459,13 @@
         <v>26</v>
       </c>
       <c r="N284" s="6" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="O284" s="6" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="P284" s="6" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="Q284" s="5">
         <v>46240</v>

--- a/data/50001541 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001541 - XEMORTIZ MINERA FRISCO.xlsx
@@ -7240,7 +7240,7 @@
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="8">
-        <v>46196.91358532407</v>
+        <v>46203.20341778935</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>270</v>
@@ -7284,8 +7284,8 @@
       <c r="R89" s="8">
         <v>46209</v>
       </c>
-      <c r="S89" s="11" t="s">
-        <v>97</v>
+      <c r="S89" s="12" t="s">
+        <v>241</v>
       </c>
       <c r="T89" s="9">
         <v>1</v>

--- a/data/50001541 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001541 - XEMORTIZ MINERA FRISCO.xlsx
@@ -2281,13 +2281,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46132.58858372685</v>
+        <v>46132.42191706019</v>
       </c>
       <c r="C4" s="5">
-        <v>46133.88825172454</v>
+        <v>46133.721585057865</v>
       </c>
       <c r="D4" s="5">
-        <v>46134.54185469907</v>
+        <v>46134.37518803241</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -2330,13 +2330,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46132.58866263889</v>
+        <v>46132.421995972225</v>
       </c>
       <c r="C5" s="8">
-        <v>46140.62775625</v>
+        <v>46140.46108958333</v>
       </c>
       <c r="D5" s="8">
-        <v>46140.627878831016</v>
+        <v>46140.46121216435</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -2395,13 +2395,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46132.58866574074</v>
+        <v>46132.421999074075</v>
       </c>
       <c r="C6" s="5">
-        <v>46133.89152399305</v>
+        <v>46133.72485732639</v>
       </c>
       <c r="D6" s="5">
-        <v>46133.891525370374</v>
+        <v>46133.7248587037</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -2460,13 +2460,13 @@
         <v>36</v>
       </c>
       <c r="B7" s="8">
-        <v>46132.58866841435</v>
+        <v>46132.422001747684</v>
       </c>
       <c r="C7" s="8">
-        <v>46133.89329033565</v>
+        <v>46133.72662366898</v>
       </c>
       <c r="D7" s="8">
-        <v>46133.893291562505</v>
+        <v>46133.72662489583</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>37</v>
@@ -2525,13 +2525,13 @@
         <v>38</v>
       </c>
       <c r="B8" s="5">
-        <v>46132.58867106482</v>
+        <v>46132.42200439815</v>
       </c>
       <c r="C8" s="5">
-        <v>46133.89329489583</v>
+        <v>46133.72662822917</v>
       </c>
       <c r="D8" s="5">
-        <v>46198.65442141204</v>
+        <v>46198.487754745365</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>39</v>
@@ -2590,13 +2590,13 @@
         <v>41</v>
       </c>
       <c r="B9" s="8">
-        <v>46132.58867449074</v>
+        <v>46132.422007824076</v>
       </c>
       <c r="C9" s="8">
-        <v>46133.89330225694</v>
+        <v>46133.72663559028</v>
       </c>
       <c r="D9" s="8">
-        <v>46133.89330362268</v>
+        <v>46133.726636956024</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>42</v>
@@ -2655,13 +2655,13 @@
         <v>43</v>
       </c>
       <c r="B10" s="5">
-        <v>46132.58858978009</v>
+        <v>46132.42192311343</v>
       </c>
       <c r="C10" s="5">
-        <v>46198.65467643518</v>
+        <v>46198.48800976852</v>
       </c>
       <c r="D10" s="5">
-        <v>46198.65469435185</v>
+        <v>46198.48802768518</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>44</v>
@@ -2708,13 +2708,13 @@
         <v>46</v>
       </c>
       <c r="B11" s="8">
-        <v>46132.58867828704</v>
+        <v>46132.422011620365</v>
       </c>
       <c r="C11" s="8">
-        <v>46183.87023324074</v>
+        <v>46183.70356657407</v>
       </c>
       <c r="D11" s="8">
-        <v>46183.87025299769</v>
+        <v>46183.703586331016</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>47</v>
@@ -2773,13 +2773,13 @@
         <v>49</v>
       </c>
       <c r="B12" s="5">
-        <v>46132.588683553244</v>
+        <v>46132.42201688657</v>
       </c>
       <c r="C12" s="5">
-        <v>46157.54164365741</v>
+        <v>46157.374976990744</v>
       </c>
       <c r="D12" s="5">
-        <v>46157.541660393515</v>
+        <v>46157.37499372685</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>50</v>
@@ -2838,13 +2838,13 @@
         <v>52</v>
       </c>
       <c r="B13" s="8">
-        <v>46132.588688738426</v>
+        <v>46132.422022071754</v>
       </c>
       <c r="C13" s="8">
-        <v>46175.72854943287</v>
+        <v>46175.561882766204</v>
       </c>
       <c r="D13" s="8">
-        <v>46175.72856798611</v>
+        <v>46175.561901319445</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>53</v>
@@ -2903,13 +2903,13 @@
         <v>55</v>
       </c>
       <c r="B14" s="5">
-        <v>46132.58859509259</v>
+        <v>46132.42192842593</v>
       </c>
       <c r="C14" s="5">
-        <v>46196.640665405095</v>
+        <v>46196.473998738424</v>
       </c>
       <c r="D14" s="5">
-        <v>46196.64067877315</v>
+        <v>46196.47401210648</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>56</v>
@@ -2956,13 +2956,13 @@
         <v>58</v>
       </c>
       <c r="B15" s="8">
-        <v>46132.58869895834</v>
+        <v>46132.422032291666</v>
       </c>
       <c r="C15" s="8">
-        <v>46157.54328243056</v>
+        <v>46157.37661576389</v>
       </c>
       <c r="D15" s="8">
-        <v>46157.54329741898</v>
+        <v>46157.37663075232</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>59</v>
@@ -3021,13 +3021,13 @@
         <v>61</v>
       </c>
       <c r="B16" s="5">
-        <v>46132.58870399305</v>
+        <v>46132.42203732639</v>
       </c>
       <c r="C16" s="5">
-        <v>46157.5417655787</v>
+        <v>46157.37509891204</v>
       </c>
       <c r="D16" s="5">
-        <v>46157.54178225694</v>
+        <v>46157.37511559028</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>62</v>
@@ -3086,13 +3086,13 @@
         <v>65</v>
       </c>
       <c r="B17" s="8">
-        <v>46132.588709097225</v>
+        <v>46132.42204243055</v>
       </c>
       <c r="C17" s="8">
-        <v>46183.8703028125</v>
+        <v>46183.70363614583</v>
       </c>
       <c r="D17" s="8">
-        <v>46183.87031994213</v>
+        <v>46183.703653275465</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>66</v>
@@ -3151,13 +3151,13 @@
         <v>68</v>
       </c>
       <c r="B18" s="5">
-        <v>46132.588713819445</v>
+        <v>46132.42204715278</v>
       </c>
       <c r="C18" s="5">
-        <v>46140.62659734953</v>
+        <v>46140.459930682875</v>
       </c>
       <c r="D18" s="5">
-        <v>46191.91766813658</v>
+        <v>46191.75100146991</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>69</v>
@@ -3216,13 +3216,13 @@
         <v>75</v>
       </c>
       <c r="B19" s="8">
-        <v>46132.62809104167</v>
+        <v>46132.461424375</v>
       </c>
       <c r="C19" s="8">
-        <v>46140.62653898148</v>
+        <v>46140.459872314816</v>
       </c>
       <c r="D19" s="8">
-        <v>46191.91766824074</v>
+        <v>46191.75100157407</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>76</v>
@@ -3281,13 +3281,13 @@
         <v>78</v>
       </c>
       <c r="B20" s="5">
-        <v>46132.62798736111</v>
+        <v>46132.46132069445</v>
       </c>
       <c r="C20" s="5">
-        <v>46196.64064614583</v>
+        <v>46196.47397947917</v>
       </c>
       <c r="D20" s="5">
-        <v>46196.6430977662</v>
+        <v>46196.47643109954</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>79</v>
@@ -3346,13 +3346,13 @@
         <v>81</v>
       </c>
       <c r="B21" s="8">
-        <v>46132.6280453125</v>
+        <v>46132.461378645836</v>
       </c>
       <c r="C21" s="8">
-        <v>46140.626452083336</v>
+        <v>46140.459785416664</v>
       </c>
       <c r="D21" s="8">
-        <v>46191.91766803241</v>
+        <v>46191.751001365745</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>82</v>
@@ -3411,11 +3411,11 @@
         <v>84</v>
       </c>
       <c r="B22" s="5">
-        <v>46132.588600312505</v>
+        <v>46132.42193364583</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46191.90919450231</v>
+        <v>46191.74252783565</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>85</v>
@@ -3460,13 +3460,13 @@
         <v>87</v>
       </c>
       <c r="B23" s="8">
-        <v>46132.588719548614</v>
+        <v>46132.42205288194</v>
       </c>
       <c r="C23" s="8">
-        <v>46157.543090798616</v>
+        <v>46157.376424131944</v>
       </c>
       <c r="D23" s="8">
-        <v>46157.54357984954</v>
+        <v>46157.376913182874</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>88</v>
@@ -3525,13 +3525,13 @@
         <v>92</v>
       </c>
       <c r="B24" s="5">
-        <v>46132.588724236106</v>
+        <v>46132.42205756945</v>
       </c>
       <c r="C24" s="5">
-        <v>46157.543350023145</v>
+        <v>46157.37668335648</v>
       </c>
       <c r="D24" s="5">
-        <v>46157.54335157407</v>
+        <v>46157.37668490741</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>93</v>
@@ -3586,13 +3586,13 @@
         <v>99</v>
       </c>
       <c r="B25" s="8">
-        <v>46132.58872892361</v>
+        <v>46132.42206225694</v>
       </c>
       <c r="C25" s="8">
-        <v>46157.54338710648</v>
+        <v>46157.37672043982</v>
       </c>
       <c r="D25" s="8">
-        <v>46157.543388425926</v>
+        <v>46157.376721759254</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>100</v>
@@ -3647,13 +3647,13 @@
         <v>102</v>
       </c>
       <c r="B26" s="5">
-        <v>46132.58873398148</v>
+        <v>46132.422067314816</v>
       </c>
       <c r="C26" s="5">
-        <v>46157.541870671295</v>
+        <v>46157.37520400463</v>
       </c>
       <c r="D26" s="5">
-        <v>46162.175749050926</v>
+        <v>46162.00908238426</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>103</v>
@@ -3712,13 +3712,13 @@
         <v>105</v>
       </c>
       <c r="B27" s="8">
-        <v>46132.58873894676</v>
+        <v>46132.4220722801</v>
       </c>
       <c r="C27" s="8">
-        <v>46157.54181472222</v>
+        <v>46157.37514805555</v>
       </c>
       <c r="D27" s="8">
-        <v>46157.541816655095</v>
+        <v>46157.375149988424</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>106</v>
@@ -3773,13 +3773,13 @@
         <v>108</v>
       </c>
       <c r="B28" s="5">
-        <v>46132.58874392361</v>
+        <v>46132.422077256946</v>
       </c>
       <c r="C28" s="5">
-        <v>46157.541855682866</v>
+        <v>46157.3751890162</v>
       </c>
       <c r="D28" s="5">
-        <v>46157.54185689815</v>
+        <v>46157.37519023148</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>109</v>
@@ -3834,13 +3834,13 @@
         <v>111</v>
       </c>
       <c r="B29" s="8">
-        <v>46132.58874878472</v>
+        <v>46132.42208211806</v>
       </c>
       <c r="C29" s="8">
-        <v>46191.90915011574</v>
+        <v>46191.742483449074</v>
       </c>
       <c r="D29" s="8">
-        <v>46191.90918642361</v>
+        <v>46191.74251975694</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>112</v>
@@ -3899,13 +3899,13 @@
         <v>114</v>
       </c>
       <c r="B30" s="5">
-        <v>46132.58875335648</v>
+        <v>46132.42208668981</v>
       </c>
       <c r="C30" s="5">
-        <v>46191.9085853125</v>
+        <v>46191.74191864583</v>
       </c>
       <c r="D30" s="5">
-        <v>46191.908590590276</v>
+        <v>46191.74192392361</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>115</v>
@@ -3960,13 +3960,13 @@
         <v>117</v>
       </c>
       <c r="B31" s="8">
-        <v>46132.58876267361</v>
+        <v>46132.42209600694</v>
       </c>
       <c r="C31" s="8">
-        <v>46191.909130879634</v>
+        <v>46191.74246421296</v>
       </c>
       <c r="D31" s="8">
-        <v>46191.90913269676</v>
+        <v>46191.74246603009</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>118</v>
@@ -4021,13 +4021,13 @@
         <v>121</v>
       </c>
       <c r="B32" s="5">
-        <v>46132.58875789352</v>
+        <v>46132.42209122685</v>
       </c>
       <c r="C32" s="5">
-        <v>46191.90908200231</v>
+        <v>46191.74241533565</v>
       </c>
       <c r="D32" s="5">
-        <v>46191.90908534722</v>
+        <v>46191.74241868056</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>119</v>
@@ -4082,13 +4082,13 @@
         <v>123</v>
       </c>
       <c r="B33" s="8">
-        <v>46132.588767037036</v>
+        <v>46132.42210037037</v>
       </c>
       <c r="C33" s="8">
-        <v>46140.62699269676</v>
+        <v>46140.460326030094</v>
       </c>
       <c r="D33" s="8">
-        <v>46178.16851243055</v>
+        <v>46178.00184576389</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>124</v>
@@ -4147,13 +4147,13 @@
         <v>128</v>
       </c>
       <c r="B34" s="5">
-        <v>46132.58877138889</v>
+        <v>46132.42210472222</v>
       </c>
       <c r="C34" s="5">
-        <v>46140.6269006713</v>
+        <v>46140.460234004626</v>
       </c>
       <c r="D34" s="5">
-        <v>46140.62690204861</v>
+        <v>46140.46023538194</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>129</v>
@@ -4208,13 +4208,13 @@
         <v>131</v>
       </c>
       <c r="B35" s="8">
-        <v>46132.58877590278</v>
+        <v>46132.42210923611</v>
       </c>
       <c r="C35" s="8">
-        <v>46140.62693832176</v>
+        <v>46140.460271655094</v>
       </c>
       <c r="D35" s="8">
-        <v>46140.62694037037</v>
+        <v>46140.460273703706</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>132</v>
@@ -4269,13 +4269,13 @@
         <v>134</v>
       </c>
       <c r="B36" s="5">
-        <v>46132.62683954861</v>
+        <v>46132.46017288194</v>
       </c>
       <c r="C36" s="5">
-        <v>46140.62696703704</v>
+        <v>46140.46030037037</v>
       </c>
       <c r="D36" s="5">
-        <v>46178.16851354166</v>
+        <v>46178.001846875</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>135</v>
@@ -4334,13 +4334,13 @@
         <v>137</v>
       </c>
       <c r="B37" s="8">
-        <v>46132.62712936343</v>
+        <v>46132.46046269676</v>
       </c>
       <c r="C37" s="8">
-        <v>46140.62678560185</v>
+        <v>46140.46011893518</v>
       </c>
       <c r="D37" s="8">
-        <v>46140.62678680556</v>
+        <v>46140.46012013889</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>77</v>
@@ -4389,13 +4389,13 @@
         <v>139</v>
       </c>
       <c r="B38" s="5">
-        <v>46132.62726841435</v>
+        <v>46132.46060174768</v>
       </c>
       <c r="C38" s="5">
-        <v>46140.62682609954</v>
+        <v>46140.46015943287</v>
       </c>
       <c r="D38" s="5">
-        <v>46140.62682733797</v>
+        <v>46140.4601606713</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>140</v>
@@ -4444,13 +4444,13 @@
         <v>142</v>
       </c>
       <c r="B39" s="8">
-        <v>46132.62697065972</v>
+        <v>46132.46030399305</v>
       </c>
       <c r="C39" s="8">
-        <v>46147.89775949074</v>
+        <v>46147.73109282408</v>
       </c>
       <c r="D39" s="8">
-        <v>46178.16851233796</v>
+        <v>46178.0018456713</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>143</v>
@@ -4509,13 +4509,13 @@
         <v>145</v>
       </c>
       <c r="B40" s="5">
-        <v>46132.62753372685</v>
+        <v>46132.46086706019</v>
       </c>
       <c r="C40" s="5">
-        <v>46140.6270855787</v>
+        <v>46140.46041891204</v>
       </c>
       <c r="D40" s="5">
-        <v>46140.62708736111</v>
+        <v>46140.46042069445</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>83</v>
@@ -4564,13 +4564,13 @@
         <v>147</v>
       </c>
       <c r="B41" s="8">
-        <v>46132.627615798614</v>
+        <v>46132.46094913194</v>
       </c>
       <c r="C41" s="8">
-        <v>46147.89774630787</v>
+        <v>46147.731079641206</v>
       </c>
       <c r="D41" s="8">
-        <v>46147.89774797454</v>
+        <v>46147.731081307866</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>148</v>
@@ -4619,11 +4619,11 @@
         <v>150</v>
       </c>
       <c r="B42" s="5">
-        <v>46132.58860650463</v>
+        <v>46132.421939837965</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46191.91760722222</v>
+        <v>46191.750940555554</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>151</v>
@@ -4666,13 +4666,13 @@
         <v>153</v>
       </c>
       <c r="B43" s="8">
-        <v>46132.58883957176</v>
+        <v>46132.42217290509</v>
       </c>
       <c r="C43" s="8">
-        <v>46175.72865314815</v>
+        <v>46175.56198648148</v>
       </c>
       <c r="D43" s="8">
-        <v>46197.71035199074</v>
+        <v>46197.543685324075</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>154</v>
@@ -4731,13 +4731,13 @@
         <v>158</v>
       </c>
       <c r="B44" s="5">
-        <v>46132.58884677083</v>
+        <v>46132.42218010417</v>
       </c>
       <c r="C44" s="5">
-        <v>46191.91739681713</v>
+        <v>46191.75073015047</v>
       </c>
       <c r="D44" s="5">
-        <v>46197.71038001157</v>
+        <v>46197.54371334491</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>159</v>
@@ -4796,13 +4796,13 @@
         <v>162</v>
       </c>
       <c r="B45" s="8">
-        <v>46132.5888534838</v>
+        <v>46132.42218681713</v>
       </c>
       <c r="C45" s="8">
-        <v>46191.917582326394</v>
+        <v>46191.75091565972</v>
       </c>
       <c r="D45" s="8">
-        <v>46191.91760793982</v>
+        <v>46191.750941273145</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>72</v>
@@ -4859,11 +4859,11 @@
         <v>166</v>
       </c>
       <c r="B46" s="5">
-        <v>46132.58886101852</v>
+        <v>46132.42219435185</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46134.580577280096</v>
+        <v>46134.413910613424</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>167</v>
@@ -4920,11 +4920,11 @@
         <v>171</v>
       </c>
       <c r="B47" s="8">
-        <v>46132.634550902774</v>
+        <v>46132.46788423611</v>
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="8">
-        <v>46196.91191069444</v>
+        <v>46196.74524402778</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>172</v>
@@ -4971,11 +4971,11 @@
         <v>175</v>
       </c>
       <c r="B48" s="5">
-        <v>46132.634558564816</v>
+        <v>46132.46789189815</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46196.91191847222</v>
+        <v>46196.74525180555</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>176</v>
@@ -5022,11 +5022,11 @@
         <v>178</v>
       </c>
       <c r="B49" s="8">
-        <v>46132.634567546294</v>
+        <v>46132.46790087963</v>
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="8">
-        <v>46196.911927002315</v>
+        <v>46196.74526033565</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>179</v>
@@ -5073,11 +5073,11 @@
         <v>180</v>
       </c>
       <c r="B50" s="5">
-        <v>46132.634571875</v>
+        <v>46132.46790520834</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46196.91193416667</v>
+        <v>46196.745267499995</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>181</v>
@@ -5124,11 +5124,11 @@
         <v>182</v>
       </c>
       <c r="B51" s="8">
-        <v>46132.6345777199</v>
+        <v>46132.467911053245</v>
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="8">
-        <v>46196.91194335648</v>
+        <v>46196.74527668981</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>183</v>
@@ -5175,11 +5175,11 @@
         <v>184</v>
       </c>
       <c r="B52" s="5">
-        <v>46132.634582071754</v>
+        <v>46132.4679154051</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46196.911952731476</v>
+        <v>46196.74528606482</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>185</v>
@@ -5226,11 +5226,11 @@
         <v>186</v>
       </c>
       <c r="B53" s="8">
-        <v>46132.63458603009</v>
+        <v>46132.46791936342</v>
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="8">
-        <v>46196.91195940972</v>
+        <v>46196.74529274306</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>187</v>
@@ -5277,11 +5277,11 @@
         <v>189</v>
       </c>
       <c r="B54" s="5">
-        <v>46132.63459168981</v>
+        <v>46132.46792502315</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46196.91196953703</v>
+        <v>46196.745302870375</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>190</v>
@@ -5328,11 +5328,11 @@
         <v>191</v>
       </c>
       <c r="B55" s="8">
-        <v>46132.634597094904</v>
+        <v>46132.46793042824</v>
       </c>
       <c r="C55" s="9"/>
       <c r="D55" s="8">
-        <v>46196.91198518519</v>
+        <v>46196.745318518515</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>192</v>
@@ -5379,11 +5379,11 @@
         <v>193</v>
       </c>
       <c r="B56" s="5">
-        <v>46132.6346025463</v>
+        <v>46132.46793587963</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46196.912005659724</v>
+        <v>46196.74533899306</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>194</v>
@@ -5430,11 +5430,11 @@
         <v>195</v>
       </c>
       <c r="B57" s="8">
-        <v>46132.634674050925</v>
+        <v>46132.46800738426</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46196.912017662034</v>
+        <v>46196.74535099537</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>196</v>
@@ -5481,11 +5481,11 @@
         <v>197</v>
       </c>
       <c r="B58" s="5">
-        <v>46132.63468899306</v>
+        <v>46132.468022326386</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46196.91202767361</v>
+        <v>46196.74536100695</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>198</v>
@@ -5532,11 +5532,11 @@
         <v>199</v>
       </c>
       <c r="B59" s="8">
-        <v>46132.63470766204</v>
+        <v>46132.46804099537</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46196.912036967595</v>
+        <v>46196.74537030092</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>200</v>
@@ -5583,11 +5583,11 @@
         <v>201</v>
       </c>
       <c r="B60" s="5">
-        <v>46132.634719884256</v>
+        <v>46132.46805321759</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46196.91204791667</v>
+        <v>46196.74538125</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>202</v>
@@ -5634,11 +5634,11 @@
         <v>203</v>
       </c>
       <c r="B61" s="8">
-        <v>46132.634727847224</v>
+        <v>46132.46806118055</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46196.9120665625</v>
+        <v>46196.74539989584</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>204</v>
@@ -5685,11 +5685,11 @@
         <v>206</v>
       </c>
       <c r="B62" s="5">
-        <v>46132.63460722222</v>
+        <v>46132.46794055555</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46196.91208912037</v>
+        <v>46196.74542245371</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>207</v>
@@ -5736,13 +5736,13 @@
         <v>209</v>
       </c>
       <c r="B63" s="8">
-        <v>46132.64721917824</v>
+        <v>46132.48055251157</v>
       </c>
       <c r="C63" s="8">
-        <v>46157.49397792824</v>
+        <v>46157.32731126157</v>
       </c>
       <c r="D63" s="8">
-        <v>46157.493989166665</v>
+        <v>46157.3273225</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>210</v>
@@ -5789,13 +5789,13 @@
         <v>212</v>
       </c>
       <c r="B64" s="5">
-        <v>46132.624842916666</v>
+        <v>46132.45817625</v>
       </c>
       <c r="C64" s="5">
-        <v>46157.493824652774</v>
+        <v>46157.32715798611</v>
       </c>
       <c r="D64" s="5">
-        <v>46182.18354462963</v>
+        <v>46182.01687796296</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>213</v>
@@ -5854,13 +5854,13 @@
         <v>215</v>
       </c>
       <c r="B65" s="8">
-        <v>46132.62490728009</v>
+        <v>46132.45824061343</v>
       </c>
       <c r="C65" s="8">
-        <v>46157.49385349537</v>
+        <v>46157.327186828705</v>
       </c>
       <c r="D65" s="8">
-        <v>46182.18354459491</v>
+        <v>46182.01687792824</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>216</v>
@@ -5919,13 +5919,13 @@
         <v>218</v>
       </c>
       <c r="B66" s="5">
-        <v>46132.62495362268</v>
+        <v>46132.45828695602</v>
       </c>
       <c r="C66" s="5">
-        <v>46157.49386780093</v>
+        <v>46157.32720113426</v>
       </c>
       <c r="D66" s="5">
-        <v>46182.183544768515</v>
+        <v>46182.01687810185</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>219</v>
@@ -5984,13 +5984,13 @@
         <v>221</v>
       </c>
       <c r="B67" s="8">
-        <v>46132.70742302084</v>
+        <v>46132.54075635417</v>
       </c>
       <c r="C67" s="8">
-        <v>46157.493948125004</v>
+        <v>46157.32728145833</v>
       </c>
       <c r="D67" s="8">
-        <v>46184.203094386576</v>
+        <v>46184.03642771991</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>222</v>
@@ -6049,13 +6049,13 @@
         <v>226</v>
       </c>
       <c r="B68" s="5">
-        <v>46132.70752974537</v>
+        <v>46132.5408630787</v>
       </c>
       <c r="C68" s="5">
-        <v>46157.49395293981</v>
+        <v>46157.32728627315</v>
       </c>
       <c r="D68" s="5">
-        <v>46184.20309802084</v>
+        <v>46184.036431354165</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>227</v>
@@ -6114,13 +6114,13 @@
         <v>229</v>
       </c>
       <c r="B69" s="8">
-        <v>46132.70760050926</v>
+        <v>46132.540933842596</v>
       </c>
       <c r="C69" s="8">
-        <v>46157.49396020833</v>
+        <v>46157.32729354167</v>
       </c>
       <c r="D69" s="8">
-        <v>46184.203094212964</v>
+        <v>46184.03642754629</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>230</v>
@@ -6179,11 +6179,11 @@
         <v>231</v>
       </c>
       <c r="B70" s="5">
-        <v>46132.58888190972</v>
+        <v>46132.42221524306</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46196.691984930556</v>
+        <v>46196.525318263884</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>232</v>
@@ -6226,13 +6226,13 @@
         <v>234</v>
       </c>
       <c r="B71" s="8">
-        <v>46132.588885185185</v>
+        <v>46132.42221851852</v>
       </c>
       <c r="C71" s="8">
-        <v>46196.68414012731</v>
+        <v>46196.51747346065</v>
       </c>
       <c r="D71" s="8">
-        <v>46196.68415487268</v>
+        <v>46196.517488206024</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>80</v>
@@ -6291,13 +6291,13 @@
         <v>238</v>
       </c>
       <c r="B72" s="5">
-        <v>46132.58889042824</v>
+        <v>46132.422223761576</v>
       </c>
       <c r="C72" s="5">
-        <v>46196.69197697917</v>
+        <v>46196.5253103125</v>
       </c>
       <c r="D72" s="5">
-        <v>46199.17870534722</v>
+        <v>46199.01203868055</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>239</v>
@@ -6356,13 +6356,13 @@
         <v>242</v>
       </c>
       <c r="B73" s="8">
-        <v>46132.631278472225</v>
+        <v>46132.46461180555</v>
       </c>
       <c r="C73" s="8">
-        <v>46196.69130792824</v>
+        <v>46196.524641261574</v>
       </c>
       <c r="D73" s="8">
-        <v>46196.69266049768</v>
+        <v>46196.52599383102</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>173</v>
@@ -6411,13 +6411,13 @@
         <v>245</v>
       </c>
       <c r="B74" s="5">
-        <v>46132.63129450232</v>
+        <v>46132.46462783565</v>
       </c>
       <c r="C74" s="5">
-        <v>46196.69160608796</v>
+        <v>46196.524939421295</v>
       </c>
       <c r="D74" s="5">
-        <v>46196.692844907404</v>
+        <v>46196.52617824074</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>173</v>
@@ -6466,13 +6466,13 @@
         <v>246</v>
       </c>
       <c r="B75" s="8">
-        <v>46132.63130252315</v>
+        <v>46132.46463585648</v>
       </c>
       <c r="C75" s="8">
-        <v>46196.69194896991</v>
+        <v>46196.52528230324</v>
       </c>
       <c r="D75" s="8">
-        <v>46196.69317986111</v>
+        <v>46196.52651319445</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>173</v>
@@ -6521,13 +6521,13 @@
         <v>249</v>
       </c>
       <c r="B76" s="5">
-        <v>46132.63130869213</v>
+        <v>46132.46464202546</v>
       </c>
       <c r="C76" s="5">
-        <v>46196.69194981482</v>
+        <v>46196.52528314815</v>
       </c>
       <c r="D76" s="5">
-        <v>46196.693142592594</v>
+        <v>46196.52647592593</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>173</v>
@@ -6576,13 +6576,13 @@
         <v>250</v>
       </c>
       <c r="B77" s="8">
-        <v>46132.631314467595</v>
+        <v>46132.46464780092</v>
       </c>
       <c r="C77" s="8">
-        <v>46196.691950416665</v>
+        <v>46196.52528375</v>
       </c>
       <c r="D77" s="8">
-        <v>46196.693131458334</v>
+        <v>46196.52646479166</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>173</v>
@@ -6631,13 +6631,13 @@
         <v>252</v>
       </c>
       <c r="B78" s="5">
-        <v>46132.6313205787</v>
+        <v>46132.46465391204</v>
       </c>
       <c r="C78" s="5">
-        <v>46196.69195099537</v>
+        <v>46196.5252843287</v>
       </c>
       <c r="D78" s="5">
-        <v>46196.693120717595</v>
+        <v>46196.52645405092</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>173</v>
@@ -6686,13 +6686,13 @@
         <v>254</v>
       </c>
       <c r="B79" s="8">
-        <v>46132.6313259375</v>
+        <v>46132.46465927083</v>
       </c>
       <c r="C79" s="8">
-        <v>46196.69195158565</v>
+        <v>46196.525284918986</v>
       </c>
       <c r="D79" s="8">
-        <v>46196.69310042824</v>
+        <v>46196.52643376157</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>173</v>
@@ -6741,13 +6741,13 @@
         <v>256</v>
       </c>
       <c r="B80" s="5">
-        <v>46132.63133041667</v>
+        <v>46132.46466375</v>
       </c>
       <c r="C80" s="5">
-        <v>46196.69195221065</v>
+        <v>46196.52528554398</v>
       </c>
       <c r="D80" s="5">
-        <v>46196.693085949075</v>
+        <v>46196.52641928241</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>173</v>
@@ -6796,13 +6796,13 @@
         <v>258</v>
       </c>
       <c r="B81" s="8">
-        <v>46132.63133645833</v>
+        <v>46132.46466979166</v>
       </c>
       <c r="C81" s="8">
-        <v>46196.69195284722</v>
+        <v>46196.52528618056</v>
       </c>
       <c r="D81" s="8">
-        <v>46196.69307368055</v>
+        <v>46196.52640701389</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>173</v>
@@ -6851,13 +6851,13 @@
         <v>259</v>
       </c>
       <c r="B82" s="5">
-        <v>46132.63134074074</v>
+        <v>46132.46467407407</v>
       </c>
       <c r="C82" s="5">
-        <v>46196.69174834491</v>
+        <v>46196.525081678235</v>
       </c>
       <c r="D82" s="5">
-        <v>46196.69306041667</v>
+        <v>46196.52639375</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>173</v>
@@ -6906,13 +6906,13 @@
         <v>261</v>
       </c>
       <c r="B83" s="8">
-        <v>46132.631346469905</v>
+        <v>46132.46467980324</v>
       </c>
       <c r="C83" s="8">
-        <v>46196.691953437505</v>
+        <v>46196.52528677083</v>
       </c>
       <c r="D83" s="8">
-        <v>46196.693049560185</v>
+        <v>46196.52638289351</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>173</v>
@@ -6961,13 +6961,13 @@
         <v>262</v>
       </c>
       <c r="B84" s="5">
-        <v>46132.631352083336</v>
+        <v>46132.464685416664</v>
       </c>
       <c r="C84" s="5">
-        <v>46196.69195403935</v>
+        <v>46196.525287372686</v>
       </c>
       <c r="D84" s="5">
-        <v>46196.6930421412</v>
+        <v>46196.52637547454</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>173</v>
@@ -7016,13 +7016,13 @@
         <v>263</v>
       </c>
       <c r="B85" s="8">
-        <v>46132.63135776621</v>
+        <v>46132.464691099536</v>
       </c>
       <c r="C85" s="8">
-        <v>46196.69195462963</v>
+        <v>46196.52528796296</v>
       </c>
       <c r="D85" s="8">
-        <v>46196.69303037037</v>
+        <v>46196.5263637037</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>173</v>
@@ -7071,13 +7071,13 @@
         <v>264</v>
       </c>
       <c r="B86" s="5">
-        <v>46132.63136296296</v>
+        <v>46132.4646962963</v>
       </c>
       <c r="C86" s="5">
-        <v>46196.6919552662</v>
+        <v>46196.525288599536</v>
       </c>
       <c r="D86" s="5">
-        <v>46196.69302122685</v>
+        <v>46196.526354560185</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>173</v>
@@ -7126,13 +7126,13 @@
         <v>266</v>
       </c>
       <c r="B87" s="8">
-        <v>46132.63136688658</v>
+        <v>46132.464700219905</v>
       </c>
       <c r="C87" s="8">
-        <v>46196.69195586805</v>
+        <v>46196.52528920139</v>
       </c>
       <c r="D87" s="8">
-        <v>46196.692995543985</v>
+        <v>46196.52632887731</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>173</v>
@@ -7181,13 +7181,13 @@
         <v>268</v>
       </c>
       <c r="B88" s="5">
-        <v>46132.63137239583</v>
+        <v>46132.464705729166</v>
       </c>
       <c r="C88" s="5">
-        <v>46196.69195645834</v>
+        <v>46196.525289791665</v>
       </c>
       <c r="D88" s="5">
-        <v>46196.69300998843</v>
+        <v>46196.52634332176</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>173</v>
@@ -7236,11 +7236,11 @@
         <v>269</v>
       </c>
       <c r="B89" s="8">
-        <v>46132.58889809028</v>
+        <v>46132.42223142361</v>
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="8">
-        <v>46203.20341778935</v>
+        <v>46203.03675112269</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>270</v>
@@ -7299,13 +7299,13 @@
         <v>272</v>
       </c>
       <c r="B90" s="5">
-        <v>46132.63147894676</v>
+        <v>46132.46481228009</v>
       </c>
       <c r="C90" s="5">
-        <v>46196.91330332176</v>
+        <v>46196.746636655094</v>
       </c>
       <c r="D90" s="5">
-        <v>46196.913305381946</v>
+        <v>46196.74663871528</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>273</v>
@@ -7354,13 +7354,13 @@
         <v>276</v>
       </c>
       <c r="B91" s="8">
-        <v>46132.63149082176</v>
+        <v>46132.46482415509</v>
       </c>
       <c r="C91" s="8">
-        <v>46196.91330880787</v>
+        <v>46196.7466421412</v>
       </c>
       <c r="D91" s="8">
-        <v>46196.9133102662</v>
+        <v>46196.74664359954</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>273</v>
@@ -7409,13 +7409,13 @@
         <v>278</v>
       </c>
       <c r="B92" s="5">
-        <v>46132.63149714121</v>
+        <v>46132.464830474535</v>
       </c>
       <c r="C92" s="5">
-        <v>46196.91331665509</v>
+        <v>46196.746649988425</v>
       </c>
       <c r="D92" s="5">
-        <v>46196.91331809028</v>
+        <v>46196.746651423615</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>273</v>
@@ -7464,13 +7464,13 @@
         <v>279</v>
       </c>
       <c r="B93" s="8">
-        <v>46132.63150280093</v>
+        <v>46132.464836134255</v>
       </c>
       <c r="C93" s="8">
-        <v>46196.9133241088</v>
+        <v>46196.74665744213</v>
       </c>
       <c r="D93" s="8">
-        <v>46196.91332601852</v>
+        <v>46196.74665935185</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>273</v>
@@ -7519,13 +7519,13 @@
         <v>280</v>
       </c>
       <c r="B94" s="5">
-        <v>46132.63150895834</v>
+        <v>46132.464842291665</v>
       </c>
       <c r="C94" s="5">
-        <v>46196.91332903935</v>
+        <v>46196.74666237269</v>
       </c>
       <c r="D94" s="5">
-        <v>46196.91333064815</v>
+        <v>46196.74666398148</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>273</v>
@@ -7574,13 +7574,13 @@
         <v>281</v>
       </c>
       <c r="B95" s="8">
-        <v>46132.63151432871</v>
+        <v>46132.464847662035</v>
       </c>
       <c r="C95" s="8">
-        <v>46196.91333642361</v>
+        <v>46196.74666975695</v>
       </c>
       <c r="D95" s="8">
-        <v>46196.91333818287</v>
+        <v>46196.7466715162</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>273</v>
@@ -7629,13 +7629,13 @@
         <v>282</v>
       </c>
       <c r="B96" s="5">
-        <v>46132.631519525465</v>
+        <v>46132.4648528588</v>
       </c>
       <c r="C96" s="5">
-        <v>46196.91334673611</v>
+        <v>46196.746680069446</v>
       </c>
       <c r="D96" s="5">
-        <v>46196.91334849537</v>
+        <v>46196.74668182871</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>273</v>
@@ -7684,13 +7684,13 @@
         <v>283</v>
       </c>
       <c r="B97" s="8">
-        <v>46132.631524247685</v>
+        <v>46132.46485758101</v>
       </c>
       <c r="C97" s="8">
-        <v>46196.913354247685</v>
+        <v>46196.74668758102</v>
       </c>
       <c r="D97" s="8">
-        <v>46196.91335584491</v>
+        <v>46196.74668917824</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>273</v>
@@ -7739,13 +7739,13 @@
         <v>284</v>
       </c>
       <c r="B98" s="5">
-        <v>46132.63153150463</v>
+        <v>46132.464864837966</v>
       </c>
       <c r="C98" s="5">
-        <v>46196.913358935184</v>
+        <v>46196.74669226852</v>
       </c>
       <c r="D98" s="5">
-        <v>46196.913360879626</v>
+        <v>46196.74669421296</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>273</v>
@@ -7794,13 +7794,13 @@
         <v>285</v>
       </c>
       <c r="B99" s="8">
-        <v>46132.631539270835</v>
+        <v>46132.46487260416</v>
       </c>
       <c r="C99" s="8">
-        <v>46196.91336784722</v>
+        <v>46196.74670118056</v>
       </c>
       <c r="D99" s="8">
-        <v>46196.913369456015</v>
+        <v>46196.74670278935</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>273</v>
@@ -7849,13 +7849,13 @@
         <v>286</v>
       </c>
       <c r="B100" s="5">
-        <v>46132.63154616898</v>
+        <v>46132.46487950231</v>
       </c>
       <c r="C100" s="5">
-        <v>46196.913381562495</v>
+        <v>46196.74671489584</v>
       </c>
       <c r="D100" s="5">
-        <v>46196.91338305555</v>
+        <v>46196.746716388894</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>273</v>
@@ -7904,13 +7904,13 @@
         <v>287</v>
       </c>
       <c r="B101" s="8">
-        <v>46132.63155506944</v>
+        <v>46132.46488840278</v>
       </c>
       <c r="C101" s="8">
-        <v>46196.913390381946</v>
+        <v>46196.746723715274</v>
       </c>
       <c r="D101" s="8">
-        <v>46196.91339189815</v>
+        <v>46196.74672523148</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>273</v>
@@ -7959,13 +7959,13 @@
         <v>288</v>
       </c>
       <c r="B102" s="5">
-        <v>46132.63156422453</v>
+        <v>46132.464897557875</v>
       </c>
       <c r="C102" s="5">
-        <v>46196.91339768519</v>
+        <v>46196.74673101852</v>
       </c>
       <c r="D102" s="5">
-        <v>46196.91339939815</v>
+        <v>46196.74673273148</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>273</v>
@@ -8014,11 +8014,11 @@
         <v>289</v>
       </c>
       <c r="B103" s="8">
-        <v>46132.63157251157</v>
+        <v>46132.46490584491</v>
       </c>
       <c r="C103" s="9"/>
       <c r="D103" s="8">
-        <v>46196.912235208336</v>
+        <v>46196.745568541664</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>273</v>
@@ -8067,11 +8067,11 @@
         <v>290</v>
       </c>
       <c r="B104" s="5">
-        <v>46132.631576643515</v>
+        <v>46132.46490997685</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46196.91224765046</v>
+        <v>46196.7455809838</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>173</v>
@@ -8120,11 +8120,11 @@
         <v>291</v>
       </c>
       <c r="B105" s="8">
-        <v>46132.6319078588</v>
+        <v>46132.46524119213</v>
       </c>
       <c r="C105" s="9"/>
       <c r="D105" s="8">
-        <v>46196.91227103009</v>
+        <v>46196.74560436343</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>273</v>
@@ -8173,13 +8173,13 @@
         <v>292</v>
       </c>
       <c r="B106" s="5">
-        <v>46132.58890393519</v>
+        <v>46132.42223726852</v>
       </c>
       <c r="C106" s="5">
-        <v>46198.65522429398</v>
+        <v>46198.488557627315</v>
       </c>
       <c r="D106" s="5">
-        <v>46198.65523800926</v>
+        <v>46198.48857134259</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>293</v>
@@ -8226,13 +8226,13 @@
         <v>295</v>
       </c>
       <c r="B107" s="8">
-        <v>46132.58890717593</v>
+        <v>46132.42224050926</v>
       </c>
       <c r="C107" s="8">
-        <v>46198.65510091435</v>
+        <v>46198.48843424769</v>
       </c>
       <c r="D107" s="8">
-        <v>46198.65511907407</v>
+        <v>46198.48845240741</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>296</v>
@@ -8289,13 +8289,13 @@
         <v>298</v>
       </c>
       <c r="B108" s="5">
-        <v>46132.58891280093</v>
+        <v>46132.42224613426</v>
       </c>
       <c r="C108" s="5">
-        <v>46157.542043761576</v>
+        <v>46157.37537709491</v>
       </c>
       <c r="D108" s="5">
-        <v>46163.18906322916</v>
+        <v>46163.022396562505</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>299</v>
@@ -8352,13 +8352,13 @@
         <v>300</v>
       </c>
       <c r="B109" s="8">
-        <v>46132.588918090274</v>
+        <v>46132.42225142361</v>
       </c>
       <c r="C109" s="8">
-        <v>46198.6552081713</v>
+        <v>46198.48854150463</v>
       </c>
       <c r="D109" s="8">
-        <v>46198.65526501158</v>
+        <v>46198.488598344906</v>
       </c>
       <c r="E109" s="9" t="s">
         <v>301</v>
@@ -8415,11 +8415,11 @@
         <v>303</v>
       </c>
       <c r="B110" s="5">
-        <v>46132.58892311342</v>
+        <v>46132.422256446764</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46133.5836275926</v>
+        <v>46205.3248571875</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>304</v>
@@ -8462,11 +8462,13 @@
         <v>306</v>
       </c>
       <c r="B111" s="8">
-        <v>46132.58892658565</v>
-      </c>
-      <c r="C111" s="9"/>
+        <v>46132.42225991898</v>
+      </c>
+      <c r="C111" s="8">
+        <v>46205.324844884264</v>
+      </c>
       <c r="D111" s="8">
-        <v>46134.57907140046</v>
+        <v>46205.32486144676</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>307</v>
@@ -8514,10 +8516,10 @@
         <v>97</v>
       </c>
       <c r="T111" s="9">
-        <v>0</v>
-      </c>
-      <c r="U111" s="10" t="s">
-        <v>98</v>
+        <v>1</v>
+      </c>
+      <c r="U111" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
@@ -8525,11 +8527,13 @@
         <v>309</v>
       </c>
       <c r="B112" s="5">
-        <v>46132.632033182876</v>
-      </c>
-      <c r="C112" s="6"/>
+        <v>46132.465366516204</v>
+      </c>
+      <c r="C112" s="5">
+        <v>46205.324200613424</v>
+      </c>
       <c r="D112" s="5">
-        <v>46196.913310648146</v>
+        <v>46205.32420275463</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>173</v>
@@ -8578,11 +8582,13 @@
         <v>311</v>
       </c>
       <c r="B113" s="8">
-        <v>46132.6321053125</v>
-      </c>
-      <c r="C113" s="9"/>
+        <v>46132.465438645835</v>
+      </c>
+      <c r="C113" s="8">
+        <v>46205.32423546296</v>
+      </c>
       <c r="D113" s="8">
-        <v>46196.91331428241</v>
+        <v>46205.324237256944</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>273</v>
@@ -8631,11 +8637,13 @@
         <v>312</v>
       </c>
       <c r="B114" s="5">
-        <v>46132.63211394676</v>
-      </c>
-      <c r="C114" s="6"/>
+        <v>46132.46544728009</v>
+      </c>
+      <c r="C114" s="5">
+        <v>46205.32425060185</v>
+      </c>
       <c r="D114" s="5">
-        <v>46196.91332363426</v>
+        <v>46205.32425197917</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>273</v>
@@ -8684,11 +8692,13 @@
         <v>314</v>
       </c>
       <c r="B115" s="8">
-        <v>46132.6321221875</v>
-      </c>
-      <c r="C115" s="9"/>
+        <v>46132.46545552083</v>
+      </c>
+      <c r="C115" s="8">
+        <v>46205.32426221065</v>
+      </c>
       <c r="D115" s="8">
-        <v>46196.913330208336</v>
+        <v>46205.32426384259</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>173</v>
@@ -8737,11 +8747,13 @@
         <v>315</v>
       </c>
       <c r="B116" s="5">
-        <v>46132.63212829861</v>
-      </c>
-      <c r="C116" s="6"/>
+        <v>46132.465461631946</v>
+      </c>
+      <c r="C116" s="5">
+        <v>46205.32427462963</v>
+      </c>
       <c r="D116" s="5">
-        <v>46196.91333635416</v>
+        <v>46205.32427606481</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>173</v>
@@ -8790,11 +8802,13 @@
         <v>316</v>
       </c>
       <c r="B117" s="8">
-        <v>46132.63213525463</v>
-      </c>
-      <c r="C117" s="9"/>
+        <v>46132.465468587965</v>
+      </c>
+      <c r="C117" s="8">
+        <v>46205.324280162036</v>
+      </c>
       <c r="D117" s="8">
-        <v>46196.91334300926</v>
+        <v>46205.324281747686</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>173</v>
@@ -8843,11 +8857,13 @@
         <v>318</v>
       </c>
       <c r="B118" s="5">
-        <v>46132.63214342593</v>
-      </c>
-      <c r="C118" s="6"/>
+        <v>46132.46547675926</v>
+      </c>
+      <c r="C118" s="5">
+        <v>46205.32428746528</v>
+      </c>
       <c r="D118" s="5">
-        <v>46196.913353067124</v>
+        <v>46205.32428944444</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>273</v>
@@ -8896,11 +8912,13 @@
         <v>319</v>
       </c>
       <c r="B119" s="8">
-        <v>46132.63215114584</v>
-      </c>
-      <c r="C119" s="9"/>
+        <v>46132.465484479166</v>
+      </c>
+      <c r="C119" s="8">
+        <v>46205.324294652775</v>
+      </c>
       <c r="D119" s="8">
-        <v>46196.91335983796</v>
+        <v>46205.32429625</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>173</v>
@@ -8949,11 +8967,13 @@
         <v>320</v>
       </c>
       <c r="B120" s="5">
-        <v>46132.63216016204</v>
-      </c>
-      <c r="C120" s="6"/>
+        <v>46132.46549349537</v>
+      </c>
+      <c r="C120" s="5">
+        <v>46205.32430099537</v>
+      </c>
       <c r="D120" s="5">
-        <v>46196.91336582176</v>
+        <v>46205.32430251157</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>173</v>
@@ -9002,11 +9022,13 @@
         <v>321</v>
       </c>
       <c r="B121" s="8">
-        <v>46132.6321746412</v>
-      </c>
-      <c r="C121" s="9"/>
+        <v>46132.465507974535</v>
+      </c>
+      <c r="C121" s="8">
+        <v>46205.324306759256</v>
+      </c>
       <c r="D121" s="8">
-        <v>46196.913376006945</v>
+        <v>46205.32430836806</v>
       </c>
       <c r="E121" s="9" t="s">
         <v>273</v>
@@ -9055,11 +9077,13 @@
         <v>322</v>
       </c>
       <c r="B122" s="5">
-        <v>46132.63216719907</v>
-      </c>
-      <c r="C122" s="6"/>
+        <v>46132.4655005324</v>
+      </c>
+      <c r="C122" s="5">
+        <v>46205.32432434028</v>
+      </c>
       <c r="D122" s="5">
-        <v>46196.91338866898</v>
+        <v>46205.32432596065</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>173</v>
@@ -9108,11 +9132,13 @@
         <v>323</v>
       </c>
       <c r="B123" s="8">
-        <v>46132.63218074074</v>
-      </c>
-      <c r="C123" s="9"/>
+        <v>46132.46551407407</v>
+      </c>
+      <c r="C123" s="8">
+        <v>46205.32433081018</v>
+      </c>
       <c r="D123" s="8">
-        <v>46196.913398680554</v>
+        <v>46205.32433265046</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>173</v>
@@ -9161,11 +9187,13 @@
         <v>324</v>
       </c>
       <c r="B124" s="5">
-        <v>46132.632186863426</v>
-      </c>
-      <c r="C124" s="6"/>
+        <v>46132.465520196754</v>
+      </c>
+      <c r="C124" s="5">
+        <v>46205.32433721065</v>
+      </c>
       <c r="D124" s="5">
-        <v>46196.91340450232</v>
+        <v>46205.32433876157</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>173</v>
@@ -9214,11 +9242,13 @@
         <v>325</v>
       </c>
       <c r="B125" s="8">
-        <v>46132.63219409723</v>
-      </c>
-      <c r="C125" s="9"/>
+        <v>46132.465527430555</v>
+      </c>
+      <c r="C125" s="8">
+        <v>46205.324675717595</v>
+      </c>
       <c r="D125" s="8">
-        <v>46196.91288795139</v>
+        <v>46205.32467703704</v>
       </c>
       <c r="E125" s="9" t="s">
         <v>173</v>
@@ -9267,11 +9297,13 @@
         <v>326</v>
       </c>
       <c r="B126" s="5">
-        <v>46132.63220086806</v>
-      </c>
-      <c r="C126" s="6"/>
+        <v>46132.46553420139</v>
+      </c>
+      <c r="C126" s="5">
+        <v>46205.324752650464</v>
+      </c>
       <c r="D126" s="5">
-        <v>46196.91289704861</v>
+        <v>46205.32475398148</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>173</v>
@@ -9320,11 +9352,13 @@
         <v>327</v>
       </c>
       <c r="B127" s="8">
-        <v>46132.63220734954</v>
-      </c>
-      <c r="C127" s="9"/>
+        <v>46132.46554068287</v>
+      </c>
+      <c r="C127" s="8">
+        <v>46205.324829641206</v>
+      </c>
       <c r="D127" s="8">
-        <v>46196.912913125</v>
+        <v>46205.324830972226</v>
       </c>
       <c r="E127" s="9" t="s">
         <v>173</v>
@@ -9373,11 +9407,11 @@
         <v>328</v>
       </c>
       <c r="B128" s="5">
-        <v>46132.58893864583</v>
+        <v>46132.422271979165</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46134.57915813658</v>
+        <v>46134.412491469906</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>329</v>
@@ -9434,11 +9468,11 @@
         <v>330</v>
       </c>
       <c r="B129" s="8">
-        <v>46132.63296805556</v>
+        <v>46132.46630138889</v>
       </c>
       <c r="C129" s="9"/>
       <c r="D129" s="8">
-        <v>46198.655107060185</v>
+        <v>46205.32420758102</v>
       </c>
       <c r="E129" s="9" t="s">
         <v>173</v>
@@ -9485,11 +9519,11 @@
         <v>333</v>
       </c>
       <c r="B130" s="5">
-        <v>46132.63297954861</v>
+        <v>46132.466312881945</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46198.655108321764</v>
+        <v>46205.32424365741</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>173</v>
@@ -9536,11 +9570,11 @@
         <v>335</v>
       </c>
       <c r="B131" s="8">
-        <v>46132.63298759259</v>
+        <v>46132.46632092593</v>
       </c>
       <c r="C131" s="9"/>
       <c r="D131" s="8">
-        <v>46198.655108946754</v>
+        <v>46205.324256817126</v>
       </c>
       <c r="E131" s="9" t="s">
         <v>173</v>
@@ -9587,11 +9621,11 @@
         <v>336</v>
       </c>
       <c r="B132" s="5">
-        <v>46132.63299327546</v>
+        <v>46132.466326608795</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46198.65510638889</v>
+        <v>46205.32427009259</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>173</v>
@@ -9638,11 +9672,11 @@
         <v>338</v>
       </c>
       <c r="B133" s="8">
-        <v>46132.63299994213</v>
+        <v>46132.466333275464</v>
       </c>
       <c r="C133" s="9"/>
       <c r="D133" s="8">
-        <v>46198.655107743056</v>
+        <v>46205.324280925925</v>
       </c>
       <c r="E133" s="9" t="s">
         <v>173</v>
@@ -9689,11 +9723,11 @@
         <v>339</v>
       </c>
       <c r="B134" s="5">
-        <v>46132.63300702546</v>
+        <v>46132.46634035879</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46198.655109513886</v>
+        <v>46205.32428731481</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>173</v>
@@ -9740,11 +9774,11 @@
         <v>341</v>
       </c>
       <c r="B135" s="8">
-        <v>46132.633012708335</v>
+        <v>46132.46634604166</v>
       </c>
       <c r="C135" s="9"/>
       <c r="D135" s="8">
-        <v>46198.65511009259</v>
+        <v>46205.32429421296</v>
       </c>
       <c r="E135" s="9" t="s">
         <v>173</v>
@@ -9791,11 +9825,11 @@
         <v>343</v>
       </c>
       <c r="B136" s="5">
-        <v>46132.63302</v>
+        <v>46132.46635333334</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46198.65511068287</v>
+        <v>46205.32430090278</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>173</v>
@@ -9842,11 +9876,11 @@
         <v>344</v>
       </c>
       <c r="B137" s="8">
-        <v>46132.63302648148</v>
+        <v>46132.46635981482</v>
       </c>
       <c r="C137" s="9"/>
       <c r="D137" s="8">
-        <v>46198.655115</v>
+        <v>46205.32430818287</v>
       </c>
       <c r="E137" s="9" t="s">
         <v>173</v>
@@ -9893,11 +9927,11 @@
         <v>345</v>
       </c>
       <c r="B138" s="5">
-        <v>46132.633032858794</v>
+        <v>46132.46636619213</v>
       </c>
       <c r="C138" s="6"/>
       <c r="D138" s="5">
-        <v>46198.65511443287</v>
+        <v>46205.324314259255</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>173</v>
@@ -9944,11 +9978,11 @@
         <v>347</v>
       </c>
       <c r="B139" s="8">
-        <v>46132.633039409724</v>
+        <v>46132.46637274306</v>
       </c>
       <c r="C139" s="9"/>
       <c r="D139" s="8">
-        <v>46198.65511385417</v>
+        <v>46205.32433091435</v>
       </c>
       <c r="E139" s="9" t="s">
         <v>173</v>
@@ -9995,11 +10029,11 @@
         <v>348</v>
       </c>
       <c r="B140" s="5">
-        <v>46132.633045821756</v>
+        <v>46132.46637915509</v>
       </c>
       <c r="C140" s="6"/>
       <c r="D140" s="5">
-        <v>46198.655113333334</v>
+        <v>46205.32433783565</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>173</v>
@@ -10046,11 +10080,11 @@
         <v>349</v>
       </c>
       <c r="B141" s="8">
-        <v>46132.633060057866</v>
+        <v>46132.46639339121</v>
       </c>
       <c r="C141" s="9"/>
       <c r="D141" s="8">
-        <v>46198.655112824075</v>
+        <v>46205.32434432871</v>
       </c>
       <c r="E141" s="9" t="s">
         <v>173</v>
@@ -10097,11 +10131,11 @@
         <v>350</v>
       </c>
       <c r="B142" s="5">
-        <v>46132.633052986115</v>
+        <v>46132.466386319444</v>
       </c>
       <c r="C142" s="6"/>
       <c r="D142" s="5">
-        <v>46198.65511228009</v>
+        <v>46205.32468230324</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>173</v>
@@ -10148,11 +10182,11 @@
         <v>351</v>
       </c>
       <c r="B143" s="8">
-        <v>46132.63306579861</v>
+        <v>46132.46639913194</v>
       </c>
       <c r="C143" s="9"/>
       <c r="D143" s="8">
-        <v>46198.65511175926</v>
+        <v>46205.324759571755</v>
       </c>
       <c r="E143" s="9" t="s">
         <v>173</v>
@@ -10199,11 +10233,11 @@
         <v>352</v>
       </c>
       <c r="B144" s="5">
-        <v>46132.633072337965</v>
+        <v>46132.46640567129</v>
       </c>
       <c r="C144" s="6"/>
       <c r="D144" s="5">
-        <v>46198.65511122685</v>
+        <v>46205.32483940972</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>173</v>
@@ -10250,11 +10284,11 @@
         <v>353</v>
       </c>
       <c r="B145" s="8">
-        <v>46132.58894553241</v>
+        <v>46132.42227886574</v>
       </c>
       <c r="C145" s="9"/>
       <c r="D145" s="8">
-        <v>46134.579158981476</v>
+        <v>46134.41249231482</v>
       </c>
       <c r="E145" s="9" t="s">
         <v>354</v>
@@ -10311,11 +10345,11 @@
         <v>355</v>
       </c>
       <c r="B146" s="5">
-        <v>46132.633140289356</v>
+        <v>46132.466473622684</v>
       </c>
       <c r="C146" s="6"/>
       <c r="D146" s="5">
-        <v>46196.91316769676</v>
+        <v>46205.32420971065</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>173</v>
@@ -10362,11 +10396,11 @@
         <v>358</v>
       </c>
       <c r="B147" s="8">
-        <v>46132.63314908565</v>
+        <v>46132.46648241898</v>
       </c>
       <c r="C147" s="9"/>
       <c r="D147" s="8">
-        <v>46196.913174201385</v>
+        <v>46205.32424541667</v>
       </c>
       <c r="E147" s="9" t="s">
         <v>173</v>
@@ -10413,11 +10447,11 @@
         <v>360</v>
       </c>
       <c r="B148" s="5">
-        <v>46132.63315533564</v>
+        <v>46132.466488668986</v>
       </c>
       <c r="C148" s="6"/>
       <c r="D148" s="5">
-        <v>46196.91318321759</v>
+        <v>46205.32425858796</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>173</v>
@@ -10464,11 +10498,11 @@
         <v>361</v>
       </c>
       <c r="B149" s="8">
-        <v>46132.63316266204</v>
+        <v>46132.466495995366</v>
       </c>
       <c r="C149" s="9"/>
       <c r="D149" s="8">
-        <v>46196.91318989583</v>
+        <v>46205.32427188657</v>
       </c>
       <c r="E149" s="9" t="s">
         <v>173</v>
@@ -10515,11 +10549,11 @@
         <v>362</v>
       </c>
       <c r="B150" s="5">
-        <v>46132.6331690625</v>
+        <v>46132.46650239584</v>
       </c>
       <c r="C150" s="6"/>
       <c r="D150" s="5">
-        <v>46196.913196319445</v>
+        <v>46205.32428262732</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>173</v>
@@ -10566,11 +10600,11 @@
         <v>363</v>
       </c>
       <c r="B151" s="8">
-        <v>46132.63317594907</v>
+        <v>46132.46650928241</v>
       </c>
       <c r="C151" s="9"/>
       <c r="D151" s="8">
-        <v>46196.913203275464</v>
+        <v>46205.32428863426</v>
       </c>
       <c r="E151" s="9" t="s">
         <v>173</v>
@@ -10617,11 +10651,11 @@
         <v>364</v>
       </c>
       <c r="B152" s="5">
-        <v>46132.633188506945</v>
+        <v>46132.46652184028</v>
       </c>
       <c r="C152" s="6"/>
       <c r="D152" s="5">
-        <v>46196.91320924769</v>
+        <v>46205.324295439816</v>
       </c>
       <c r="E152" s="6" t="s">
         <v>173</v>
@@ -10668,11 +10702,11 @@
         <v>365</v>
       </c>
       <c r="B153" s="8">
-        <v>46132.63318159722</v>
+        <v>46132.46651493055</v>
       </c>
       <c r="C153" s="9"/>
       <c r="D153" s="8">
-        <v>46196.9132163426</v>
+        <v>46205.32430184028</v>
       </c>
       <c r="E153" s="9" t="s">
         <v>173</v>
@@ -10719,11 +10753,11 @@
         <v>366</v>
       </c>
       <c r="B154" s="5">
-        <v>46132.63319443287</v>
+        <v>46132.4665277662</v>
       </c>
       <c r="C154" s="6"/>
       <c r="D154" s="5">
-        <v>46196.913238333334</v>
+        <v>46205.32430943287</v>
       </c>
       <c r="E154" s="6" t="s">
         <v>173</v>
@@ -10770,11 +10804,11 @@
         <v>367</v>
       </c>
       <c r="B155" s="8">
-        <v>46132.63320815972</v>
+        <v>46132.46654149306</v>
       </c>
       <c r="C155" s="9"/>
       <c r="D155" s="8">
-        <v>46196.91324483797</v>
+        <v>46205.324315578706</v>
       </c>
       <c r="E155" s="9" t="s">
         <v>173</v>
@@ -10821,11 +10855,11 @@
         <v>368</v>
       </c>
       <c r="B156" s="5">
-        <v>46132.63320082176</v>
+        <v>46132.46653415509</v>
       </c>
       <c r="C156" s="6"/>
       <c r="D156" s="5">
-        <v>46196.91325182871</v>
+        <v>46205.32433209491</v>
       </c>
       <c r="E156" s="6" t="s">
         <v>173</v>
@@ -10872,11 +10906,11 @@
         <v>369</v>
       </c>
       <c r="B157" s="8">
-        <v>46132.63322097222</v>
+        <v>46132.46655430556</v>
       </c>
       <c r="C157" s="9"/>
       <c r="D157" s="8">
-        <v>46196.91325798611</v>
+        <v>46205.32433899306</v>
       </c>
       <c r="E157" s="9" t="s">
         <v>173</v>
@@ -10923,11 +10957,11 @@
         <v>370</v>
       </c>
       <c r="B158" s="5">
-        <v>46132.6332150463</v>
+        <v>46132.46654837963</v>
       </c>
       <c r="C158" s="6"/>
       <c r="D158" s="5">
-        <v>46196.91326434028</v>
+        <v>46205.324345625</v>
       </c>
       <c r="E158" s="6" t="s">
         <v>173</v>
@@ -10974,11 +11008,11 @@
         <v>371</v>
       </c>
       <c r="B159" s="8">
-        <v>46132.63322802083</v>
+        <v>46132.466561354166</v>
       </c>
       <c r="C159" s="9"/>
       <c r="D159" s="8">
-        <v>46196.91327159722</v>
+        <v>46205.32468355324</v>
       </c>
       <c r="E159" s="9" t="s">
         <v>173</v>
@@ -11025,11 +11059,11 @@
         <v>372</v>
       </c>
       <c r="B160" s="5">
-        <v>46132.63323575231</v>
+        <v>46132.46656908565</v>
       </c>
       <c r="C160" s="6"/>
       <c r="D160" s="5">
-        <v>46196.913280625</v>
+        <v>46205.32476081018</v>
       </c>
       <c r="E160" s="6" t="s">
         <v>173</v>
@@ -11076,11 +11110,11 @@
         <v>373</v>
       </c>
       <c r="B161" s="8">
-        <v>46132.633244004624</v>
+        <v>46132.46657733797</v>
       </c>
       <c r="C161" s="9"/>
       <c r="D161" s="8">
-        <v>46196.91329380787</v>
+        <v>46205.32484065973</v>
       </c>
       <c r="E161" s="9" t="s">
         <v>173</v>
@@ -11127,11 +11161,11 @@
         <v>374</v>
       </c>
       <c r="B162" s="5">
-        <v>46132.58893171296</v>
+        <v>46132.4222650463</v>
       </c>
       <c r="C162" s="6"/>
       <c r="D162" s="5">
-        <v>46134.57915975695</v>
+        <v>46134.412493090276</v>
       </c>
       <c r="E162" s="6" t="s">
         <v>375</v>
@@ -11188,11 +11222,11 @@
         <v>376</v>
       </c>
       <c r="B163" s="8">
-        <v>46132.632804305555</v>
+        <v>46132.46613763889</v>
       </c>
       <c r="C163" s="9"/>
       <c r="D163" s="8">
-        <v>46198.655219224536</v>
+        <v>46198.48855255787</v>
       </c>
       <c r="E163" s="9" t="s">
         <v>173</v>
@@ -11239,11 +11273,11 @@
         <v>379</v>
       </c>
       <c r="B164" s="5">
-        <v>46132.632815624995</v>
+        <v>46132.46614895834</v>
       </c>
       <c r="C164" s="6"/>
       <c r="D164" s="5">
-        <v>46198.655218125</v>
+        <v>46198.48855145833</v>
       </c>
       <c r="E164" s="6" t="s">
         <v>173</v>
@@ -11290,11 +11324,11 @@
         <v>380</v>
       </c>
       <c r="B165" s="8">
-        <v>46132.63282284723</v>
+        <v>46132.466156180555</v>
       </c>
       <c r="C165" s="9"/>
       <c r="D165" s="8">
-        <v>46198.65521964121</v>
+        <v>46205.324262395836</v>
       </c>
       <c r="E165" s="9" t="s">
         <v>173</v>
@@ -11341,11 +11375,11 @@
         <v>382</v>
       </c>
       <c r="B166" s="5">
-        <v>46132.63283236111</v>
+        <v>46132.466165694444</v>
       </c>
       <c r="C166" s="6"/>
       <c r="D166" s="5">
-        <v>46196.913348946764</v>
+        <v>46205.32427363426</v>
       </c>
       <c r="E166" s="6" t="s">
         <v>173</v>
@@ -11392,11 +11426,11 @@
         <v>383</v>
       </c>
       <c r="B167" s="8">
-        <v>46132.632837384255</v>
+        <v>46132.46617071759</v>
       </c>
       <c r="C167" s="9"/>
       <c r="D167" s="8">
-        <v>46198.65522011574</v>
+        <v>46205.32428368056</v>
       </c>
       <c r="E167" s="9" t="s">
         <v>173</v>
@@ -11443,11 +11477,11 @@
         <v>385</v>
       </c>
       <c r="B168" s="5">
-        <v>46132.63284362269</v>
+        <v>46132.46617695602</v>
       </c>
       <c r="C168" s="6"/>
       <c r="D168" s="5">
-        <v>46198.65522056713</v>
+        <v>46205.324289780096</v>
       </c>
       <c r="E168" s="6" t="s">
         <v>173</v>
@@ -11494,11 +11528,11 @@
         <v>386</v>
       </c>
       <c r="B169" s="8">
-        <v>46132.63284975695</v>
+        <v>46132.46618309028</v>
       </c>
       <c r="C169" s="9"/>
       <c r="D169" s="8">
-        <v>46198.655220995366</v>
+        <v>46205.324296527775</v>
       </c>
       <c r="E169" s="9" t="s">
         <v>173</v>
@@ -11545,11 +11579,11 @@
         <v>387</v>
       </c>
       <c r="B170" s="5">
-        <v>46132.63286226852</v>
+        <v>46132.46619560185</v>
       </c>
       <c r="C170" s="6"/>
       <c r="D170" s="5">
-        <v>46198.65522143518</v>
+        <v>46205.32430266203</v>
       </c>
       <c r="E170" s="6" t="s">
         <v>173</v>
@@ -11596,11 +11630,11 @@
         <v>388</v>
       </c>
       <c r="B171" s="8">
-        <v>46132.63285675926</v>
+        <v>46132.46619009259</v>
       </c>
       <c r="C171" s="9"/>
       <c r="D171" s="8">
-        <v>46198.65522184028</v>
+        <v>46205.32431060185</v>
       </c>
       <c r="E171" s="9" t="s">
         <v>173</v>
@@ -11647,11 +11681,11 @@
         <v>389</v>
       </c>
       <c r="B172" s="5">
-        <v>46132.63286828704</v>
+        <v>46132.466201620366</v>
       </c>
       <c r="C172" s="6"/>
       <c r="D172" s="5">
-        <v>46198.655222430556</v>
+        <v>46205.32431672454</v>
       </c>
       <c r="E172" s="6" t="s">
         <v>173</v>
@@ -11698,11 +11732,11 @@
         <v>390</v>
       </c>
       <c r="B173" s="8">
-        <v>46132.63287412037</v>
+        <v>46132.466207453705</v>
       </c>
       <c r="C173" s="9"/>
       <c r="D173" s="8">
-        <v>46198.65522284722</v>
+        <v>46205.32433319444</v>
       </c>
       <c r="E173" s="9" t="s">
         <v>173</v>
@@ -11749,11 +11783,11 @@
         <v>391</v>
       </c>
       <c r="B174" s="5">
-        <v>46132.63288133102</v>
+        <v>46132.46621466435</v>
       </c>
       <c r="C174" s="6"/>
       <c r="D174" s="5">
-        <v>46198.65522325231</v>
+        <v>46205.32434010417</v>
       </c>
       <c r="E174" s="6" t="s">
         <v>173</v>
@@ -11800,11 +11834,11 @@
         <v>392</v>
       </c>
       <c r="B175" s="8">
-        <v>46132.63288800926</v>
+        <v>46132.46622134259</v>
       </c>
       <c r="C175" s="9"/>
       <c r="D175" s="8">
-        <v>46198.65522396991</v>
+        <v>46205.32434679398</v>
       </c>
       <c r="E175" s="9" t="s">
         <v>173</v>
@@ -11851,11 +11885,11 @@
         <v>393</v>
       </c>
       <c r="B176" s="5">
-        <v>46132.63289421296</v>
+        <v>46132.4662275463</v>
       </c>
       <c r="C176" s="6"/>
       <c r="D176" s="5">
-        <v>46198.65522444445</v>
+        <v>46205.3246845949</v>
       </c>
       <c r="E176" s="6" t="s">
         <v>173</v>
@@ -11902,11 +11936,11 @@
         <v>394</v>
       </c>
       <c r="B177" s="8">
-        <v>46132.63290028935</v>
+        <v>46132.46623362269</v>
       </c>
       <c r="C177" s="9"/>
       <c r="D177" s="8">
-        <v>46198.65522503472</v>
+        <v>46205.324761909724</v>
       </c>
       <c r="E177" s="9" t="s">
         <v>173</v>
@@ -11953,11 +11987,11 @@
         <v>395</v>
       </c>
       <c r="B178" s="5">
-        <v>46132.632907719904</v>
+        <v>46132.46624105324</v>
       </c>
       <c r="C178" s="6"/>
       <c r="D178" s="5">
-        <v>46198.65522554398</v>
+        <v>46205.324841747686</v>
       </c>
       <c r="E178" s="6" t="s">
         <v>173</v>
@@ -12004,11 +12038,11 @@
         <v>396</v>
       </c>
       <c r="B179" s="8">
-        <v>46132.58895258102</v>
+        <v>46132.42228591435</v>
       </c>
       <c r="C179" s="9"/>
       <c r="D179" s="8">
-        <v>46134.579160567126</v>
+        <v>46134.41249390046</v>
       </c>
       <c r="E179" s="9" t="s">
         <v>397</v>
@@ -12065,11 +12099,11 @@
         <v>398</v>
       </c>
       <c r="B180" s="5">
-        <v>46132.63330006944</v>
+        <v>46132.46663340278</v>
       </c>
       <c r="C180" s="6"/>
       <c r="D180" s="5">
-        <v>46196.91349186342</v>
+        <v>46196.74682519676</v>
       </c>
       <c r="E180" s="6" t="s">
         <v>173</v>
@@ -12116,11 +12150,11 @@
         <v>401</v>
       </c>
       <c r="B181" s="8">
-        <v>46132.63330984954</v>
+        <v>46132.46664318287</v>
       </c>
       <c r="C181" s="9"/>
       <c r="D181" s="8">
-        <v>46196.913516817134</v>
+        <v>46196.74685015046</v>
       </c>
       <c r="E181" s="9" t="s">
         <v>173</v>
@@ -12167,11 +12201,11 @@
         <v>403</v>
       </c>
       <c r="B182" s="5">
-        <v>46132.633316377316</v>
+        <v>46132.46664971065</v>
       </c>
       <c r="C182" s="6"/>
       <c r="D182" s="5">
-        <v>46196.913533425926</v>
+        <v>46196.74686675926</v>
       </c>
       <c r="E182" s="6" t="s">
         <v>173</v>
@@ -12218,11 +12252,11 @@
         <v>405</v>
       </c>
       <c r="B183" s="8">
-        <v>46132.63332333333</v>
+        <v>46132.46665666667</v>
       </c>
       <c r="C183" s="9"/>
       <c r="D183" s="8">
-        <v>46196.91352673611</v>
+        <v>46196.74686006944</v>
       </c>
       <c r="E183" s="9" t="s">
         <v>173</v>
@@ -12269,11 +12303,11 @@
         <v>407</v>
       </c>
       <c r="B184" s="5">
-        <v>46132.63333568287</v>
+        <v>46132.466669016205</v>
       </c>
       <c r="C184" s="6"/>
       <c r="D184" s="5">
-        <v>46196.91354314815</v>
+        <v>46196.746876481484</v>
       </c>
       <c r="E184" s="6" t="s">
         <v>173</v>
@@ -12320,11 +12354,11 @@
         <v>409</v>
       </c>
       <c r="B185" s="8">
-        <v>46132.633329282406</v>
+        <v>46132.46666261574</v>
       </c>
       <c r="C185" s="9"/>
       <c r="D185" s="8">
-        <v>46196.913549942125</v>
+        <v>46196.74688327547</v>
       </c>
       <c r="E185" s="9" t="s">
         <v>173</v>
@@ -12371,11 +12405,11 @@
         <v>411</v>
       </c>
       <c r="B186" s="5">
-        <v>46132.63334925926</v>
+        <v>46132.466682592596</v>
       </c>
       <c r="C186" s="6"/>
       <c r="D186" s="5">
-        <v>46196.91355706019</v>
+        <v>46196.74689039352</v>
       </c>
       <c r="E186" s="6" t="s">
         <v>173</v>
@@ -12422,11 +12456,11 @@
         <v>413</v>
       </c>
       <c r="B187" s="8">
-        <v>46132.633353321755</v>
+        <v>46132.4666866551</v>
       </c>
       <c r="C187" s="9"/>
       <c r="D187" s="8">
-        <v>46196.91356591435</v>
+        <v>46196.746899247686</v>
       </c>
       <c r="E187" s="9" t="s">
         <v>173</v>
@@ -12473,11 +12507,11 @@
         <v>415</v>
       </c>
       <c r="B188" s="5">
-        <v>46132.63336115741</v>
+        <v>46132.46669449074</v>
       </c>
       <c r="C188" s="6"/>
       <c r="D188" s="5">
-        <v>46196.91357502315</v>
+        <v>46196.74690835648</v>
       </c>
       <c r="E188" s="6" t="s">
         <v>173</v>
@@ -12524,11 +12558,11 @@
         <v>417</v>
       </c>
       <c r="B189" s="8">
-        <v>46132.6333661574</v>
+        <v>46132.466699490746</v>
       </c>
       <c r="C189" s="9"/>
       <c r="D189" s="8">
-        <v>46196.91357896991</v>
+        <v>46196.74691230324</v>
       </c>
       <c r="E189" s="9" t="s">
         <v>173</v>
@@ -12575,11 +12609,11 @@
         <v>419</v>
       </c>
       <c r="B190" s="5">
-        <v>46132.633375046295</v>
+        <v>46132.46670837963</v>
       </c>
       <c r="C190" s="6"/>
       <c r="D190" s="5">
-        <v>46196.91359459491</v>
+        <v>46196.74692792824</v>
       </c>
       <c r="E190" s="6" t="s">
         <v>173</v>
@@ -12626,11 +12660,11 @@
         <v>421</v>
       </c>
       <c r="B191" s="8">
-        <v>46132.63337950232</v>
+        <v>46132.46671283565</v>
       </c>
       <c r="C191" s="9"/>
       <c r="D191" s="8">
-        <v>46196.913601423614</v>
+        <v>46196.74693475694</v>
       </c>
       <c r="E191" s="9" t="s">
         <v>173</v>
@@ -12677,11 +12711,11 @@
         <v>423</v>
       </c>
       <c r="B192" s="5">
-        <v>46132.63338666667</v>
+        <v>46132.46672</v>
       </c>
       <c r="C192" s="6"/>
       <c r="D192" s="5">
-        <v>46196.91361079861</v>
+        <v>46196.74694413194</v>
       </c>
       <c r="E192" s="6" t="s">
         <v>173</v>
@@ -12728,11 +12762,11 @@
         <v>425</v>
       </c>
       <c r="B193" s="8">
-        <v>46132.63339375</v>
+        <v>46132.46672708333</v>
       </c>
       <c r="C193" s="9"/>
       <c r="D193" s="8">
-        <v>46196.91361791667</v>
+        <v>46196.746951249996</v>
       </c>
       <c r="E193" s="9" t="s">
         <v>173</v>
@@ -12779,11 +12813,11 @@
         <v>427</v>
       </c>
       <c r="B194" s="5">
-        <v>46132.63339872685</v>
+        <v>46132.46673206019</v>
       </c>
       <c r="C194" s="6"/>
       <c r="D194" s="5">
-        <v>46196.91362990741</v>
+        <v>46196.746963240745</v>
       </c>
       <c r="E194" s="6" t="s">
         <v>173</v>
@@ -12830,11 +12864,11 @@
         <v>429</v>
       </c>
       <c r="B195" s="8">
-        <v>46132.633404085645</v>
+        <v>46132.46673741898</v>
       </c>
       <c r="C195" s="9"/>
       <c r="D195" s="8">
-        <v>46196.91364925926</v>
+        <v>46196.746982592595</v>
       </c>
       <c r="E195" s="9" t="s">
         <v>173</v>
@@ -12881,11 +12915,11 @@
         <v>431</v>
       </c>
       <c r="B196" s="5">
-        <v>46132.58900565973</v>
+        <v>46132.422338993056</v>
       </c>
       <c r="C196" s="6"/>
       <c r="D196" s="5">
-        <v>46134.579161331014</v>
+        <v>46134.41249466436</v>
       </c>
       <c r="E196" s="6" t="s">
         <v>432</v>
@@ -12942,11 +12976,11 @@
         <v>435</v>
       </c>
       <c r="B197" s="8">
-        <v>46132.6334534375</v>
+        <v>46132.466786770834</v>
       </c>
       <c r="C197" s="9"/>
       <c r="D197" s="8">
-        <v>46196.91368532408</v>
+        <v>46196.74701865741</v>
       </c>
       <c r="E197" s="9" t="s">
         <v>173</v>
@@ -12993,11 +13027,11 @@
         <v>437</v>
       </c>
       <c r="B198" s="5">
-        <v>46132.633462025464</v>
+        <v>46132.46679535879</v>
       </c>
       <c r="C198" s="6"/>
       <c r="D198" s="5">
-        <v>46196.91369168981</v>
+        <v>46196.74702502315</v>
       </c>
       <c r="E198" s="6" t="s">
         <v>173</v>
@@ -13044,11 +13078,11 @@
         <v>438</v>
       </c>
       <c r="B199" s="8">
-        <v>46132.633468622684</v>
+        <v>46132.46680195602</v>
       </c>
       <c r="C199" s="9"/>
       <c r="D199" s="8">
-        <v>46196.91369818287</v>
+        <v>46196.747031516206</v>
       </c>
       <c r="E199" s="9" t="s">
         <v>173</v>
@@ -13095,11 +13129,11 @@
         <v>439</v>
       </c>
       <c r="B200" s="5">
-        <v>46132.63347502315</v>
+        <v>46132.46680835648</v>
       </c>
       <c r="C200" s="6"/>
       <c r="D200" s="5">
-        <v>46196.91371429398</v>
+        <v>46196.747047627316</v>
       </c>
       <c r="E200" s="6" t="s">
         <v>173</v>
@@ -13146,11 +13180,11 @@
         <v>440</v>
       </c>
       <c r="B201" s="8">
-        <v>46132.63348070602</v>
+        <v>46132.46681403935</v>
       </c>
       <c r="C201" s="9"/>
       <c r="D201" s="8">
-        <v>46196.91372087963</v>
+        <v>46196.74705421296</v>
       </c>
       <c r="E201" s="9" t="s">
         <v>173</v>
@@ -13197,11 +13231,11 @@
         <v>441</v>
       </c>
       <c r="B202" s="5">
-        <v>46132.63348662037</v>
+        <v>46132.466819953705</v>
       </c>
       <c r="C202" s="6"/>
       <c r="D202" s="5">
-        <v>46196.91372986111</v>
+        <v>46196.747063194445</v>
       </c>
       <c r="E202" s="6" t="s">
         <v>173</v>
@@ -13248,11 +13282,11 @@
         <v>442</v>
       </c>
       <c r="B203" s="8">
-        <v>46132.63349295139</v>
+        <v>46132.466826284726</v>
       </c>
       <c r="C203" s="9"/>
       <c r="D203" s="8">
-        <v>46196.91373467592</v>
+        <v>46196.74706800926</v>
       </c>
       <c r="E203" s="9" t="s">
         <v>173</v>
@@ -13299,11 +13333,11 @@
         <v>444</v>
       </c>
       <c r="B204" s="5">
-        <v>46132.633500138894</v>
+        <v>46132.46683347222</v>
       </c>
       <c r="C204" s="6"/>
       <c r="D204" s="5">
-        <v>46196.91374106481</v>
+        <v>46196.74707439815</v>
       </c>
       <c r="E204" s="6" t="s">
         <v>173</v>
@@ -13350,11 +13384,11 @@
         <v>445</v>
       </c>
       <c r="B205" s="8">
-        <v>46132.633505983795</v>
+        <v>46132.46683931713</v>
       </c>
       <c r="C205" s="9"/>
       <c r="D205" s="8">
-        <v>46196.91374993055</v>
+        <v>46196.747083263894</v>
       </c>
       <c r="E205" s="9" t="s">
         <v>173</v>
@@ -13401,11 +13435,11 @@
         <v>446</v>
       </c>
       <c r="B206" s="5">
-        <v>46132.6335124537</v>
+        <v>46132.466845787036</v>
       </c>
       <c r="C206" s="6"/>
       <c r="D206" s="5">
-        <v>46196.91377486111</v>
+        <v>46196.747108194446</v>
       </c>
       <c r="E206" s="6" t="s">
         <v>173</v>
@@ -13452,11 +13486,11 @@
         <v>447</v>
       </c>
       <c r="B207" s="8">
-        <v>46132.63351974537</v>
+        <v>46132.4668530787</v>
       </c>
       <c r="C207" s="9"/>
       <c r="D207" s="8">
-        <v>46196.91379184028</v>
+        <v>46196.74712517361</v>
       </c>
       <c r="E207" s="9" t="s">
         <v>173</v>
@@ -13503,11 +13537,11 @@
         <v>448</v>
       </c>
       <c r="B208" s="5">
-        <v>46132.6335277662</v>
+        <v>46132.466861099536</v>
       </c>
       <c r="C208" s="6"/>
       <c r="D208" s="5">
-        <v>46196.913807916666</v>
+        <v>46196.74714125</v>
       </c>
       <c r="E208" s="6" t="s">
         <v>173</v>
@@ -13554,11 +13588,11 @@
         <v>449</v>
       </c>
       <c r="B209" s="8">
-        <v>46132.633534988425</v>
+        <v>46132.46686832176</v>
       </c>
       <c r="C209" s="9"/>
       <c r="D209" s="8">
-        <v>46196.91381409722</v>
+        <v>46196.74714743056</v>
       </c>
       <c r="E209" s="9" t="s">
         <v>173</v>
@@ -13605,11 +13639,11 @@
         <v>450</v>
       </c>
       <c r="B210" s="5">
-        <v>46132.63354082176</v>
+        <v>46132.46687415509</v>
       </c>
       <c r="C210" s="6"/>
       <c r="D210" s="5">
-        <v>46196.91383046296</v>
+        <v>46196.747163796295</v>
       </c>
       <c r="E210" s="6" t="s">
         <v>173</v>
@@ -13656,11 +13690,11 @@
         <v>451</v>
       </c>
       <c r="B211" s="8">
-        <v>46132.63354760417</v>
+        <v>46132.4668809375</v>
       </c>
       <c r="C211" s="9"/>
       <c r="D211" s="8">
-        <v>46196.913837025466</v>
+        <v>46196.747170358794</v>
       </c>
       <c r="E211" s="9" t="s">
         <v>452</v>
@@ -13707,11 +13741,11 @@
         <v>453</v>
       </c>
       <c r="B212" s="5">
-        <v>46133.58300138889</v>
+        <v>46133.41633472222</v>
       </c>
       <c r="C212" s="6"/>
       <c r="D212" s="5">
-        <v>46196.91385334491</v>
+        <v>46196.74718667824</v>
       </c>
       <c r="E212" s="6" t="s">
         <v>273</v>
@@ -13758,11 +13792,11 @@
         <v>454</v>
       </c>
       <c r="B213" s="8">
-        <v>46132.589012916666</v>
+        <v>46132.42234625</v>
       </c>
       <c r="C213" s="9"/>
       <c r="D213" s="8">
-        <v>46133.58769056713</v>
+        <v>46133.42102390046</v>
       </c>
       <c r="E213" s="9" t="s">
         <v>455</v>
@@ -13805,11 +13839,11 @@
         <v>457</v>
       </c>
       <c r="B214" s="5">
-        <v>46132.589016666665</v>
+        <v>46132.42235</v>
       </c>
       <c r="C214" s="6"/>
       <c r="D214" s="5">
-        <v>46133.58482033564</v>
+        <v>46133.41815366899</v>
       </c>
       <c r="E214" s="6" t="s">
         <v>458</v>
@@ -13866,11 +13900,11 @@
         <v>462</v>
       </c>
       <c r="B215" s="8">
-        <v>46132.63360670139</v>
+        <v>46132.46694003472</v>
       </c>
       <c r="C215" s="9"/>
       <c r="D215" s="8">
-        <v>46196.91388565973</v>
+        <v>46196.747218993056</v>
       </c>
       <c r="E215" s="9" t="s">
         <v>173</v>
@@ -13917,11 +13951,11 @@
         <v>463</v>
       </c>
       <c r="B216" s="5">
-        <v>46132.63361304398</v>
+        <v>46132.46694637732</v>
       </c>
       <c r="C216" s="6"/>
       <c r="D216" s="5">
-        <v>46196.91389173611</v>
+        <v>46196.74722506944</v>
       </c>
       <c r="E216" s="6" t="s">
         <v>173</v>
@@ -13968,11 +14002,11 @@
         <v>464</v>
       </c>
       <c r="B217" s="8">
-        <v>46132.63361974537</v>
+        <v>46132.46695307871</v>
       </c>
       <c r="C217" s="9"/>
       <c r="D217" s="8">
-        <v>46196.91390143518</v>
+        <v>46196.74723476852</v>
       </c>
       <c r="E217" s="9" t="s">
         <v>173</v>
@@ -14019,11 +14053,11 @@
         <v>465</v>
       </c>
       <c r="B218" s="5">
-        <v>46132.63363137731</v>
+        <v>46132.46696471065</v>
       </c>
       <c r="C218" s="6"/>
       <c r="D218" s="5">
-        <v>46196.913907152775</v>
+        <v>46196.74724048611</v>
       </c>
       <c r="E218" s="6" t="s">
         <v>173</v>
@@ -14070,11 +14104,11 @@
         <v>466</v>
       </c>
       <c r="B219" s="8">
-        <v>46132.63362555555</v>
+        <v>46132.466958888894</v>
       </c>
       <c r="C219" s="9"/>
       <c r="D219" s="8">
-        <v>46196.91391674768</v>
+        <v>46196.74725008102</v>
       </c>
       <c r="E219" s="9" t="s">
         <v>173</v>
@@ -14121,11 +14155,11 @@
         <v>467</v>
       </c>
       <c r="B220" s="5">
-        <v>46132.63363859954</v>
+        <v>46132.46697193287</v>
       </c>
       <c r="C220" s="6"/>
       <c r="D220" s="5">
-        <v>46196.913933171294</v>
+        <v>46196.74726650463</v>
       </c>
       <c r="E220" s="6" t="s">
         <v>173</v>
@@ -14172,11 +14206,11 @@
         <v>468</v>
       </c>
       <c r="B221" s="8">
-        <v>46132.63364667824</v>
+        <v>46132.46698001157</v>
       </c>
       <c r="C221" s="9"/>
       <c r="D221" s="8">
-        <v>46196.913939861115</v>
+        <v>46196.74727319444</v>
       </c>
       <c r="E221" s="9" t="s">
         <v>452</v>
@@ -14223,11 +14257,11 @@
         <v>469</v>
       </c>
       <c r="B222" s="5">
-        <v>46132.633653055556</v>
+        <v>46132.466986388885</v>
       </c>
       <c r="C222" s="6"/>
       <c r="D222" s="5">
-        <v>46196.91395613426</v>
+        <v>46196.74728946759</v>
       </c>
       <c r="E222" s="6" t="s">
         <v>173</v>
@@ -14274,11 +14308,11 @@
         <v>470</v>
       </c>
       <c r="B223" s="8">
-        <v>46132.63365921297</v>
+        <v>46132.466992546295</v>
       </c>
       <c r="C223" s="9"/>
       <c r="D223" s="8">
-        <v>46196.9139649537</v>
+        <v>46196.74729828704</v>
       </c>
       <c r="E223" s="9" t="s">
         <v>173</v>
@@ -14325,11 +14359,11 @@
         <v>471</v>
       </c>
       <c r="B224" s="5">
-        <v>46132.633665347224</v>
+        <v>46132.46699868055</v>
       </c>
       <c r="C224" s="6"/>
       <c r="D224" s="5">
-        <v>46196.91397201389</v>
+        <v>46196.74730534722</v>
       </c>
       <c r="E224" s="6" t="s">
         <v>173</v>
@@ -14376,11 +14410,11 @@
         <v>472</v>
       </c>
       <c r="B225" s="8">
-        <v>46132.63367407407</v>
+        <v>46132.46700740741</v>
       </c>
       <c r="C225" s="9"/>
       <c r="D225" s="8">
-        <v>46196.91398435185</v>
+        <v>46196.747317685185</v>
       </c>
       <c r="E225" s="9" t="s">
         <v>173</v>
@@ -14427,11 +14461,11 @@
         <v>473</v>
       </c>
       <c r="B226" s="5">
-        <v>46132.63368225694</v>
+        <v>46132.46701559028</v>
       </c>
       <c r="C226" s="6"/>
       <c r="D226" s="5">
-        <v>46196.91399296296</v>
+        <v>46196.747326296296</v>
       </c>
       <c r="E226" s="6" t="s">
         <v>173</v>
@@ -14478,11 +14512,11 @@
         <v>474</v>
       </c>
       <c r="B227" s="8">
-        <v>46132.63368885417</v>
+        <v>46132.4670221875</v>
       </c>
       <c r="C227" s="9"/>
       <c r="D227" s="8">
-        <v>46196.913999675926</v>
+        <v>46196.74733300926</v>
       </c>
       <c r="E227" s="9" t="s">
         <v>173</v>
@@ -14529,11 +14563,11 @@
         <v>475</v>
       </c>
       <c r="B228" s="5">
-        <v>46132.633694965276</v>
+        <v>46132.46702829861</v>
       </c>
       <c r="C228" s="6"/>
       <c r="D228" s="5">
-        <v>46196.914015358794</v>
+        <v>46196.74734869213</v>
       </c>
       <c r="E228" s="6" t="s">
         <v>173</v>
@@ -14580,11 +14614,11 @@
         <v>476</v>
       </c>
       <c r="B229" s="8">
-        <v>46132.63370111111</v>
+        <v>46132.467034444446</v>
       </c>
       <c r="C229" s="9"/>
       <c r="D229" s="8">
-        <v>46196.9140217824</v>
+        <v>46196.747355115745</v>
       </c>
       <c r="E229" s="9" t="s">
         <v>452</v>
@@ -14631,11 +14665,11 @@
         <v>477</v>
       </c>
       <c r="B230" s="5">
-        <v>46132.63378953704</v>
+        <v>46132.46712287037</v>
       </c>
       <c r="C230" s="6"/>
       <c r="D230" s="5">
-        <v>46196.91403721065</v>
+        <v>46196.74737054398</v>
       </c>
       <c r="E230" s="6" t="s">
         <v>173</v>
@@ -14682,11 +14716,11 @@
         <v>478</v>
       </c>
       <c r="B231" s="8">
-        <v>46132.589021736116</v>
+        <v>46132.422355069444</v>
       </c>
       <c r="C231" s="9"/>
       <c r="D231" s="8">
-        <v>46133.58651043981</v>
+        <v>46133.41984377315</v>
       </c>
       <c r="E231" s="9" t="s">
         <v>479</v>
@@ -14743,11 +14777,11 @@
         <v>481</v>
       </c>
       <c r="B232" s="5">
-        <v>46132.633861608796</v>
+        <v>46132.46719494213</v>
       </c>
       <c r="C232" s="6"/>
       <c r="D232" s="5">
-        <v>46196.91407126158</v>
+        <v>46196.747404594906</v>
       </c>
       <c r="E232" s="6" t="s">
         <v>173</v>
@@ -14794,11 +14828,11 @@
         <v>482</v>
       </c>
       <c r="B233" s="8">
-        <v>46132.633870011574</v>
+        <v>46132.4672033449</v>
       </c>
       <c r="C233" s="9"/>
       <c r="D233" s="8">
-        <v>46196.914077905094</v>
+        <v>46196.74741123842</v>
       </c>
       <c r="E233" s="9" t="s">
         <v>173</v>
@@ -14845,11 +14879,11 @@
         <v>483</v>
       </c>
       <c r="B234" s="5">
-        <v>46132.63387658565</v>
+        <v>46132.46720991898</v>
       </c>
       <c r="C234" s="6"/>
       <c r="D234" s="5">
-        <v>46196.914084212964</v>
+        <v>46196.7474175463</v>
       </c>
       <c r="E234" s="6" t="s">
         <v>173</v>
@@ -14896,11 +14930,11 @@
         <v>484</v>
       </c>
       <c r="B235" s="8">
-        <v>46132.63388259259</v>
+        <v>46132.46721592592</v>
       </c>
       <c r="C235" s="9"/>
       <c r="D235" s="8">
-        <v>46196.91409322916</v>
+        <v>46196.7474265625</v>
       </c>
       <c r="E235" s="9" t="s">
         <v>173</v>
@@ -14947,11 +14981,11 @@
         <v>485</v>
       </c>
       <c r="B236" s="5">
-        <v>46132.63388633102</v>
+        <v>46132.46721966435</v>
       </c>
       <c r="C236" s="6"/>
       <c r="D236" s="5">
-        <v>46196.914099340276</v>
+        <v>46196.74743267361</v>
       </c>
       <c r="E236" s="6" t="s">
         <v>173</v>
@@ -14998,11 +15032,11 @@
         <v>486</v>
       </c>
       <c r="B237" s="8">
-        <v>46132.63389106482</v>
+        <v>46132.46722439815</v>
       </c>
       <c r="C237" s="9"/>
       <c r="D237" s="8">
-        <v>46196.9141059838</v>
+        <v>46196.74743931713</v>
       </c>
       <c r="E237" s="9" t="s">
         <v>173</v>
@@ -15049,11 +15083,11 @@
         <v>487</v>
       </c>
       <c r="B238" s="5">
-        <v>46132.63389739583</v>
+        <v>46132.46723072916</v>
       </c>
       <c r="C238" s="6"/>
       <c r="D238" s="5">
-        <v>46196.91411261574</v>
+        <v>46196.74744594908</v>
       </c>
       <c r="E238" s="6" t="s">
         <v>173</v>
@@ -15100,11 +15134,11 @@
         <v>488</v>
       </c>
       <c r="B239" s="8">
-        <v>46132.63390288195</v>
+        <v>46132.46723621528</v>
       </c>
       <c r="C239" s="9"/>
       <c r="D239" s="8">
-        <v>46196.91411917824</v>
+        <v>46196.747452511576</v>
       </c>
       <c r="E239" s="9" t="s">
         <v>173</v>
@@ -15151,11 +15185,11 @@
         <v>489</v>
       </c>
       <c r="B240" s="5">
-        <v>46132.63390861111</v>
+        <v>46132.46724194444</v>
       </c>
       <c r="C240" s="6"/>
       <c r="D240" s="5">
-        <v>46196.91413769676</v>
+        <v>46196.74747103009</v>
       </c>
       <c r="E240" s="6" t="s">
         <v>173</v>
@@ -15202,11 +15236,11 @@
         <v>490</v>
       </c>
       <c r="B241" s="8">
-        <v>46132.63391276621</v>
+        <v>46132.467246099535</v>
       </c>
       <c r="C241" s="9"/>
       <c r="D241" s="8">
-        <v>46196.91415084491</v>
+        <v>46196.74748417824</v>
       </c>
       <c r="E241" s="9" t="s">
         <v>173</v>
@@ -15253,11 +15287,11 @@
         <v>491</v>
       </c>
       <c r="B242" s="5">
-        <v>46132.63391880787</v>
+        <v>46132.4672521412</v>
       </c>
       <c r="C242" s="6"/>
       <c r="D242" s="5">
-        <v>46196.914157175925</v>
+        <v>46196.74749050926</v>
       </c>
       <c r="E242" s="6" t="s">
         <v>173</v>
@@ -15304,11 +15338,11 @@
         <v>492</v>
       </c>
       <c r="B243" s="8">
-        <v>46132.63392302083</v>
+        <v>46132.46725635417</v>
       </c>
       <c r="C243" s="9"/>
       <c r="D243" s="8">
-        <v>46196.91416721065</v>
+        <v>46196.74750054398</v>
       </c>
       <c r="E243" s="9" t="s">
         <v>173</v>
@@ -15355,11 +15389,11 @@
         <v>493</v>
       </c>
       <c r="B244" s="5">
-        <v>46132.63393041666</v>
+        <v>46132.467263750004</v>
       </c>
       <c r="C244" s="6"/>
       <c r="D244" s="5">
-        <v>46196.91417351852</v>
+        <v>46196.747506851854</v>
       </c>
       <c r="E244" s="6" t="s">
         <v>173</v>
@@ -15406,11 +15440,11 @@
         <v>494</v>
       </c>
       <c r="B245" s="8">
-        <v>46132.63393689815</v>
+        <v>46132.467270231486</v>
       </c>
       <c r="C245" s="9"/>
       <c r="D245" s="8">
-        <v>46196.91418997685</v>
+        <v>46196.74752331019</v>
       </c>
       <c r="E245" s="9" t="s">
         <v>173</v>
@@ -15457,11 +15491,11 @@
         <v>495</v>
       </c>
       <c r="B246" s="5">
-        <v>46132.633943078705</v>
+        <v>46132.46727641203</v>
       </c>
       <c r="C246" s="6"/>
       <c r="D246" s="5">
-        <v>46196.91419930555</v>
+        <v>46196.74753263889</v>
       </c>
       <c r="E246" s="6" t="s">
         <v>452</v>
@@ -15508,11 +15542,11 @@
         <v>496</v>
       </c>
       <c r="B247" s="8">
-        <v>46132.633955578705</v>
+        <v>46132.46728891204</v>
       </c>
       <c r="C247" s="9"/>
       <c r="D247" s="8">
-        <v>46196.91421935185</v>
+        <v>46196.747552685185</v>
       </c>
       <c r="E247" s="9" t="s">
         <v>173</v>
@@ -15559,11 +15593,11 @@
         <v>497</v>
       </c>
       <c r="B248" s="5">
-        <v>46132.58902681713</v>
+        <v>46132.422360150464</v>
       </c>
       <c r="C248" s="6"/>
       <c r="D248" s="5">
-        <v>46133.58721105324</v>
+        <v>46133.42054438658</v>
       </c>
       <c r="E248" s="6" t="s">
         <v>498</v>
@@ -15622,11 +15656,11 @@
         <v>502</v>
       </c>
       <c r="B249" s="8">
-        <v>46132.634024432875</v>
+        <v>46132.4673577662</v>
       </c>
       <c r="C249" s="9"/>
       <c r="D249" s="8">
-        <v>46196.914276875</v>
+        <v>46196.74761020833</v>
       </c>
       <c r="E249" s="9" t="s">
         <v>173</v>
@@ -15673,11 +15707,11 @@
         <v>503</v>
       </c>
       <c r="B250" s="5">
-        <v>46132.634032685186</v>
+        <v>46132.46736601852</v>
       </c>
       <c r="C250" s="6"/>
       <c r="D250" s="5">
-        <v>46196.914286666666</v>
+        <v>46196.747619999995</v>
       </c>
       <c r="E250" s="6" t="s">
         <v>173</v>
@@ -15724,11 +15758,11 @@
         <v>504</v>
       </c>
       <c r="B251" s="8">
-        <v>46132.63404001157</v>
+        <v>46132.46737334491</v>
       </c>
       <c r="C251" s="9"/>
       <c r="D251" s="8">
-        <v>46196.91429060185</v>
+        <v>46196.74762393518</v>
       </c>
       <c r="E251" s="9" t="s">
         <v>173</v>
@@ -15775,11 +15809,11 @@
         <v>505</v>
       </c>
       <c r="B252" s="5">
-        <v>46132.63404659722</v>
+        <v>46132.46737993056</v>
       </c>
       <c r="C252" s="6"/>
       <c r="D252" s="5">
-        <v>46196.914299571756</v>
+        <v>46196.74763290509</v>
       </c>
       <c r="E252" s="6" t="s">
         <v>173</v>
@@ -15826,11 +15860,11 @@
         <v>506</v>
       </c>
       <c r="B253" s="8">
-        <v>46132.6340537037</v>
+        <v>46132.46738703703</v>
       </c>
       <c r="C253" s="9"/>
       <c r="D253" s="8">
-        <v>46196.91430931713</v>
+        <v>46196.74764265046</v>
       </c>
       <c r="E253" s="9" t="s">
         <v>173</v>
@@ -15877,11 +15911,11 @@
         <v>507</v>
       </c>
       <c r="B254" s="5">
-        <v>46132.63406115741</v>
+        <v>46132.46739449074</v>
       </c>
       <c r="C254" s="6"/>
       <c r="D254" s="5">
-        <v>46196.914319143514</v>
+        <v>46196.74765247686</v>
       </c>
       <c r="E254" s="6" t="s">
         <v>173</v>
@@ -15928,11 +15962,11 @@
         <v>508</v>
       </c>
       <c r="B255" s="8">
-        <v>46132.63406662037</v>
+        <v>46132.467399953704</v>
       </c>
       <c r="C255" s="9"/>
       <c r="D255" s="8">
-        <v>46196.91432607639</v>
+        <v>46196.747659409724</v>
       </c>
       <c r="E255" s="9" t="s">
         <v>173</v>
@@ -15979,11 +16013,11 @@
         <v>509</v>
       </c>
       <c r="B256" s="5">
-        <v>46132.634072395835</v>
+        <v>46132.46740572917</v>
       </c>
       <c r="C256" s="6"/>
       <c r="D256" s="5">
-        <v>46196.914335231486</v>
+        <v>46196.747668564814</v>
       </c>
       <c r="E256" s="6" t="s">
         <v>173</v>
@@ -16030,11 +16064,11 @@
         <v>510</v>
       </c>
       <c r="B257" s="8">
-        <v>46132.6340770949</v>
+        <v>46132.467410428246</v>
       </c>
       <c r="C257" s="9"/>
       <c r="D257" s="8">
-        <v>46196.914344687495</v>
+        <v>46196.74767802084</v>
       </c>
       <c r="E257" s="9" t="s">
         <v>173</v>
@@ -16081,11 +16115,11 @@
         <v>511</v>
       </c>
       <c r="B258" s="5">
-        <v>46132.634082777775</v>
+        <v>46132.46741611111</v>
       </c>
       <c r="C258" s="6"/>
       <c r="D258" s="5">
-        <v>46196.91435427083</v>
+        <v>46196.74768760416</v>
       </c>
       <c r="E258" s="6" t="s">
         <v>173</v>
@@ -16132,11 +16166,11 @@
         <v>512</v>
       </c>
       <c r="B259" s="8">
-        <v>46132.63408899306</v>
+        <v>46132.46742232639</v>
       </c>
       <c r="C259" s="9"/>
       <c r="D259" s="8">
-        <v>46196.91437050926</v>
+        <v>46196.74770384259</v>
       </c>
       <c r="E259" s="9" t="s">
         <v>173</v>
@@ -16183,11 +16217,11 @@
         <v>513</v>
       </c>
       <c r="B260" s="5">
-        <v>46132.63409545139</v>
+        <v>46132.46742878472</v>
       </c>
       <c r="C260" s="6"/>
       <c r="D260" s="5">
-        <v>46196.914380057875</v>
+        <v>46196.7477133912</v>
       </c>
       <c r="E260" s="6" t="s">
         <v>173</v>
@@ -16234,11 +16268,11 @@
         <v>514</v>
       </c>
       <c r="B261" s="8">
-        <v>46132.63410087963</v>
+        <v>46132.46743421296</v>
       </c>
       <c r="C261" s="9"/>
       <c r="D261" s="8">
-        <v>46196.914383738425</v>
+        <v>46196.74771707176</v>
       </c>
       <c r="E261" s="9" t="s">
         <v>173</v>
@@ -16285,11 +16319,11 @@
         <v>515</v>
       </c>
       <c r="B262" s="5">
-        <v>46132.63410688657</v>
+        <v>46132.46744021991</v>
       </c>
       <c r="C262" s="6"/>
       <c r="D262" s="5">
-        <v>46196.914396527776</v>
+        <v>46196.74772986111</v>
       </c>
       <c r="E262" s="6" t="s">
         <v>173</v>
@@ -16336,11 +16370,11 @@
         <v>516</v>
       </c>
       <c r="B263" s="8">
-        <v>46132.6341133449</v>
+        <v>46132.467446678245</v>
       </c>
       <c r="C263" s="9"/>
       <c r="D263" s="8">
-        <v>46196.914406261574</v>
+        <v>46196.74773959491</v>
       </c>
       <c r="E263" s="9" t="s">
         <v>173</v>
@@ -16387,11 +16421,11 @@
         <v>517</v>
       </c>
       <c r="B264" s="5">
-        <v>46132.63411966435</v>
+        <v>46132.467452997684</v>
       </c>
       <c r="C264" s="6"/>
       <c r="D264" s="5">
-        <v>46196.91441971065</v>
+        <v>46196.74775304398</v>
       </c>
       <c r="E264" s="6" t="s">
         <v>173</v>
@@ -16438,11 +16472,11 @@
         <v>518</v>
       </c>
       <c r="B265" s="8">
-        <v>46132.58903189815</v>
+        <v>46132.42236523148</v>
       </c>
       <c r="C265" s="9"/>
       <c r="D265" s="8">
-        <v>46133.65412578704</v>
+        <v>46133.48745912037</v>
       </c>
       <c r="E265" s="9" t="s">
         <v>519</v>
@@ -16499,11 +16533,11 @@
         <v>521</v>
       </c>
       <c r="B266" s="5">
-        <v>46132.63422869213</v>
+        <v>46132.467562025464</v>
       </c>
       <c r="C266" s="6"/>
       <c r="D266" s="5">
-        <v>46196.91446424769</v>
+        <v>46196.74779758102</v>
       </c>
       <c r="E266" s="6" t="s">
         <v>173</v>
@@ -16550,11 +16584,11 @@
         <v>523</v>
       </c>
       <c r="B267" s="8">
-        <v>46132.63423491898</v>
+        <v>46132.467568252316</v>
       </c>
       <c r="C267" s="9"/>
       <c r="D267" s="8">
-        <v>46196.91447116898</v>
+        <v>46196.747804502316</v>
       </c>
       <c r="E267" s="9" t="s">
         <v>173</v>
@@ -16601,11 +16635,11 @@
         <v>524</v>
       </c>
       <c r="B268" s="5">
-        <v>46132.634240960644</v>
+        <v>46132.46757429398</v>
       </c>
       <c r="C268" s="6"/>
       <c r="D268" s="5">
-        <v>46196.914480694446</v>
+        <v>46196.74781402778</v>
       </c>
       <c r="E268" s="6" t="s">
         <v>173</v>
@@ -16652,11 +16686,11 @@
         <v>525</v>
       </c>
       <c r="B269" s="8">
-        <v>46132.63424789352</v>
+        <v>46132.467581226854</v>
       </c>
       <c r="C269" s="9"/>
       <c r="D269" s="8">
-        <v>46196.91449018518</v>
+        <v>46196.74782351852</v>
       </c>
       <c r="E269" s="9" t="s">
         <v>173</v>
@@ -16703,11 +16737,11 @@
         <v>526</v>
       </c>
       <c r="B270" s="5">
-        <v>46132.634254386576</v>
+        <v>46132.467587719904</v>
       </c>
       <c r="C270" s="6"/>
       <c r="D270" s="5">
-        <v>46196.91449658565</v>
+        <v>46196.74782991898</v>
       </c>
       <c r="E270" s="6" t="s">
         <v>173</v>
@@ -16754,11 +16788,11 @@
         <v>527</v>
       </c>
       <c r="B271" s="8">
-        <v>46132.634260810184</v>
+        <v>46132.46759414352</v>
       </c>
       <c r="C271" s="9"/>
       <c r="D271" s="8">
-        <v>46196.914503645836</v>
+        <v>46196.747836979164</v>
       </c>
       <c r="E271" s="9" t="s">
         <v>173</v>
@@ -16805,11 +16839,11 @@
         <v>528</v>
       </c>
       <c r="B272" s="5">
-        <v>46132.634267256944</v>
+        <v>46132.46760059027</v>
       </c>
       <c r="C272" s="6"/>
       <c r="D272" s="5">
-        <v>46196.91450951389</v>
+        <v>46196.747842847224</v>
       </c>
       <c r="E272" s="6" t="s">
         <v>173</v>
@@ -16856,11 +16890,11 @@
         <v>529</v>
       </c>
       <c r="B273" s="8">
-        <v>46132.63427122685</v>
+        <v>46132.46760456018</v>
       </c>
       <c r="C273" s="9"/>
       <c r="D273" s="8">
-        <v>46196.91451931713</v>
+        <v>46196.747852650464</v>
       </c>
       <c r="E273" s="9" t="s">
         <v>173</v>
@@ -16907,11 +16941,11 @@
         <v>531</v>
       </c>
       <c r="B274" s="5">
-        <v>46132.634276365745</v>
+        <v>46132.46760969907</v>
       </c>
       <c r="C274" s="6"/>
       <c r="D274" s="5">
-        <v>46196.914524629625</v>
+        <v>46196.74785796297</v>
       </c>
       <c r="E274" s="6" t="s">
         <v>173</v>
@@ -16958,11 +16992,11 @@
         <v>532</v>
       </c>
       <c r="B275" s="8">
-        <v>46132.63428099537</v>
+        <v>46132.46761432871</v>
       </c>
       <c r="C275" s="9"/>
       <c r="D275" s="8">
-        <v>46196.91452907407</v>
+        <v>46196.74786240741</v>
       </c>
       <c r="E275" s="9" t="s">
         <v>173</v>
@@ -17009,11 +17043,11 @@
         <v>533</v>
       </c>
       <c r="B276" s="5">
-        <v>46132.63428524305</v>
+        <v>46132.46761857639</v>
       </c>
       <c r="C276" s="6"/>
       <c r="D276" s="5">
-        <v>46196.91453917824</v>
+        <v>46196.74787251157</v>
       </c>
       <c r="E276" s="6" t="s">
         <v>173</v>
@@ -17060,11 +17094,11 @@
         <v>534</v>
       </c>
       <c r="B277" s="8">
-        <v>46132.63429103009</v>
+        <v>46132.46762436343</v>
       </c>
       <c r="C277" s="9"/>
       <c r="D277" s="8">
-        <v>46196.91454204862</v>
+        <v>46196.747875381945</v>
       </c>
       <c r="E277" s="9" t="s">
         <v>173</v>
@@ -17111,11 +17145,11 @@
         <v>535</v>
       </c>
       <c r="B278" s="5">
-        <v>46132.63429523148</v>
+        <v>46132.46762856482</v>
       </c>
       <c r="C278" s="6"/>
       <c r="D278" s="5">
-        <v>46196.914551724534</v>
+        <v>46196.74788505787</v>
       </c>
       <c r="E278" s="6" t="s">
         <v>173</v>
@@ -17162,11 +17196,11 @@
         <v>536</v>
       </c>
       <c r="B279" s="8">
-        <v>46132.63430358796</v>
+        <v>46132.4676369213</v>
       </c>
       <c r="C279" s="9"/>
       <c r="D279" s="8">
-        <v>46196.91457195602</v>
+        <v>46196.74790528935</v>
       </c>
       <c r="E279" s="9" t="s">
         <v>173</v>
@@ -17213,11 +17247,11 @@
         <v>537</v>
       </c>
       <c r="B280" s="5">
-        <v>46132.63431148148</v>
+        <v>46132.46764481482</v>
       </c>
       <c r="C280" s="6"/>
       <c r="D280" s="5">
-        <v>46196.91458070602</v>
+        <v>46196.747914039355</v>
       </c>
       <c r="E280" s="6" t="s">
         <v>173</v>
@@ -17264,11 +17298,11 @@
         <v>538</v>
       </c>
       <c r="B281" s="8">
-        <v>46132.63437663195</v>
+        <v>46132.467709965276</v>
       </c>
       <c r="C281" s="9"/>
       <c r="D281" s="8">
-        <v>46196.91461018518</v>
+        <v>46196.74794351852</v>
       </c>
       <c r="E281" s="9" t="s">
         <v>173</v>
@@ -17315,11 +17349,11 @@
         <v>539</v>
       </c>
       <c r="B282" s="5">
-        <v>46132.589037604164</v>
+        <v>46132.4223709375</v>
       </c>
       <c r="C282" s="6"/>
       <c r="D282" s="5">
-        <v>46133.59235670139</v>
+        <v>46133.425690034725</v>
       </c>
       <c r="E282" s="6" t="s">
         <v>540</v>
@@ -17362,11 +17396,11 @@
         <v>541</v>
       </c>
       <c r="B283" s="8">
-        <v>46132.5890406713</v>
+        <v>46132.42237400463</v>
       </c>
       <c r="C283" s="9"/>
       <c r="D283" s="8">
-        <v>46134.57925581018</v>
+        <v>46134.41258914352</v>
       </c>
       <c r="E283" s="9" t="s">
         <v>542</v>
@@ -17425,11 +17459,11 @@
         <v>546</v>
       </c>
       <c r="B284" s="5">
-        <v>46132.58904559028</v>
+        <v>46132.42237892361</v>
       </c>
       <c r="C284" s="6"/>
       <c r="D284" s="5">
-        <v>46198.65442142361</v>
+        <v>46198.48775475695</v>
       </c>
       <c r="E284" s="6" t="s">
         <v>547</v>

--- a/data/50001541 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001541 - XEMORTIZ MINERA FRISCO.xlsx
@@ -736,97 +736,97 @@
     <t xml:space="preserve">OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 </t>
   </si>
   <si>
+    <t>1214137717389464</t>
+  </si>
+  <si>
+    <t>Generación OC Fabricación externa ,Control de calidad Mecanizado,Control de calidad corte Laser,Control de calidad Corte plasma ,Check Planos</t>
+  </si>
+  <si>
+    <t>OT 4307 ZVN 1-9-86/2,Armado</t>
+  </si>
+  <si>
+    <t>1214137717389465</t>
+  </si>
+  <si>
+    <t>1214137717389466</t>
+  </si>
+  <si>
+    <t>Generación OC Fabricación externa ,Control de calidad corte Laser,Control de calidad Corte plasma ,Control de calidad Mecanizado,Check Planos</t>
+  </si>
+  <si>
+    <t>Armado,OT 4307 ZVN 1-9-86/2</t>
+  </si>
+  <si>
+    <t>1214137717389467</t>
+  </si>
+  <si>
+    <t>1214137717389468</t>
+  </si>
+  <si>
+    <t>Generación OC Fabricación externa ,Control de calidad corte Laser,Control de calidad Mecanizado,Check Planos</t>
+  </si>
+  <si>
+    <t>1214137717389469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Mecanizado,Generación OC Fabricación externa ,Check Planos,Control de calidad corte Laser,Control de calidad Corte plasma </t>
+  </si>
+  <si>
+    <t>1214137717389470</t>
+  </si>
+  <si>
+    <t>Control de calidad corte Laser,Control de calidad Corte plasma ,Control de calidad Mecanizado,Generación OC Fabricación externa ,Check Planos</t>
+  </si>
+  <si>
+    <t>1214137717389471</t>
+  </si>
+  <si>
+    <t>Control de calidad Corte plasma ,Generación OC Fabricación externa ,Check Planos,Control de calidad corte Laser</t>
+  </si>
+  <si>
+    <t>1214137717389472</t>
+  </si>
+  <si>
+    <t>1214137717389473</t>
+  </si>
+  <si>
+    <t>Control de calidad corte Laser,Control de calidad Corte plasma ,Generación OC Fabricación externa ,Check Planos</t>
+  </si>
+  <si>
+    <t>1214137717389474</t>
+  </si>
+  <si>
+    <t>1214137717389475</t>
+  </si>
+  <si>
+    <t>1214137717389476</t>
+  </si>
+  <si>
+    <t>1214137717389477</t>
+  </si>
+  <si>
+    <t>Control de calidad corte Laser,Control de calidad Mecanizado,Generación OC Fabricación externa ,Check Planos</t>
+  </si>
+  <si>
+    <t>1214137717389478</t>
+  </si>
+  <si>
+    <t>OT 4307 ZVN 1-9-86/2 ,Armado</t>
+  </si>
+  <si>
+    <t>1214137717389479</t>
+  </si>
+  <si>
+    <t>1214138711519194</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1214137717389464</t>
-  </si>
-  <si>
-    <t>Generación OC Fabricación externa ,Control de calidad Mecanizado,Control de calidad corte Laser,Control de calidad Corte plasma ,Check Planos</t>
-  </si>
-  <si>
-    <t>OT 4307 ZVN 1-9-86/2,Armado</t>
-  </si>
-  <si>
-    <t>1214137717389465</t>
-  </si>
-  <si>
-    <t>1214137717389466</t>
-  </si>
-  <si>
-    <t>Generación OC Fabricación externa ,Control de calidad corte Laser,Control de calidad Corte plasma ,Control de calidad Mecanizado,Check Planos</t>
-  </si>
-  <si>
-    <t>Armado,OT 4307 ZVN 1-9-86/2</t>
-  </si>
-  <si>
-    <t>1214137717389467</t>
-  </si>
-  <si>
-    <t>1214137717389468</t>
-  </si>
-  <si>
-    <t>Generación OC Fabricación externa ,Control de calidad corte Laser,Control de calidad Mecanizado,Check Planos</t>
-  </si>
-  <si>
-    <t>1214137717389469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Mecanizado,Generación OC Fabricación externa ,Check Planos,Control de calidad corte Laser,Control de calidad Corte plasma </t>
-  </si>
-  <si>
-    <t>1214137717389470</t>
-  </si>
-  <si>
-    <t>Control de calidad corte Laser,Control de calidad Corte plasma ,Control de calidad Mecanizado,Generación OC Fabricación externa ,Check Planos</t>
-  </si>
-  <si>
-    <t>1214137717389471</t>
-  </si>
-  <si>
-    <t>Control de calidad Corte plasma ,Generación OC Fabricación externa ,Check Planos,Control de calidad corte Laser</t>
-  </si>
-  <si>
-    <t>1214137717389472</t>
-  </si>
-  <si>
-    <t>1214137717389473</t>
-  </si>
-  <si>
-    <t>Control de calidad corte Laser,Control de calidad Corte plasma ,Generación OC Fabricación externa ,Check Planos</t>
-  </si>
-  <si>
-    <t>1214137717389474</t>
-  </si>
-  <si>
-    <t>1214137717389475</t>
-  </si>
-  <si>
-    <t>1214137717389476</t>
-  </si>
-  <si>
-    <t>1214137717389477</t>
-  </si>
-  <si>
-    <t>Control de calidad corte Laser,Control de calidad Mecanizado,Generación OC Fabricación externa ,Check Planos</t>
-  </si>
-  <si>
-    <t>1214137717389478</t>
-  </si>
-  <si>
-    <t>OT 4307 ZVN 1-9-86/2 ,Armado</t>
-  </si>
-  <si>
-    <t>1214137717389479</t>
-  </si>
-  <si>
-    <t>1214138711519194</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2</t>
   </si>
   <si>
     <t>1214137717389481</t>
@@ -6297,7 +6297,7 @@
         <v>46196.69197697917</v>
       </c>
       <c r="D72" s="5">
-        <v>46199.17870534722</v>
+        <v>46207.18038831018</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>239</v>
@@ -6341,8 +6341,8 @@
       <c r="R72" s="5">
         <v>46184</v>
       </c>
-      <c r="S72" s="12" t="s">
-        <v>241</v>
+      <c r="S72" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T72" s="6">
         <v>1</v>
@@ -6353,7 +6353,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B73" s="8">
         <v>46132.631278472225</v>
@@ -6395,10 +6395,10 @@
         <v>239</v>
       </c>
       <c r="O73" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="P73" s="9" t="s">
         <v>243</v>
-      </c>
-      <c r="P73" s="9" t="s">
-        <v>244</v>
       </c>
       <c r="Q73" s="9"/>
       <c r="R73" s="9"/>
@@ -6408,7 +6408,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B74" s="5">
         <v>46132.63129450232</v>
@@ -6450,10 +6450,10 @@
         <v>239</v>
       </c>
       <c r="O74" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="P74" s="6" t="s">
         <v>243</v>
-      </c>
-      <c r="P74" s="6" t="s">
-        <v>244</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6463,7 +6463,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B75" s="8">
         <v>46132.63130252315</v>
@@ -6505,10 +6505,10 @@
         <v>239</v>
       </c>
       <c r="O75" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="P75" s="9" t="s">
         <v>247</v>
-      </c>
-      <c r="P75" s="9" t="s">
-        <v>248</v>
       </c>
       <c r="Q75" s="9"/>
       <c r="R75" s="9"/>
@@ -6518,7 +6518,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B76" s="5">
         <v>46132.63130869213</v>
@@ -6560,10 +6560,10 @@
         <v>239</v>
       </c>
       <c r="O76" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="P76" s="6" t="s">
         <v>243</v>
-      </c>
-      <c r="P76" s="6" t="s">
-        <v>244</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6573,7 +6573,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B77" s="8">
         <v>46132.631314467595</v>
@@ -6615,10 +6615,10 @@
         <v>239</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Q77" s="9"/>
       <c r="R77" s="9"/>
@@ -6628,7 +6628,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B78" s="5">
         <v>46132.6313205787</v>
@@ -6670,10 +6670,10 @@
         <v>239</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6683,7 +6683,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B79" s="8">
         <v>46132.6313259375</v>
@@ -6725,10 +6725,10 @@
         <v>239</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Q79" s="9"/>
       <c r="R79" s="9"/>
@@ -6738,7 +6738,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B80" s="5">
         <v>46132.63133041667</v>
@@ -6780,10 +6780,10 @@
         <v>239</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6793,7 +6793,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B81" s="8">
         <v>46132.63133645833</v>
@@ -6835,10 +6835,10 @@
         <v>239</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Q81" s="9"/>
       <c r="R81" s="9"/>
@@ -6848,7 +6848,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B82" s="5">
         <v>46132.63134074074</v>
@@ -6890,10 +6890,10 @@
         <v>239</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6903,7 +6903,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B83" s="8">
         <v>46132.631346469905</v>
@@ -6945,10 +6945,10 @@
         <v>239</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Q83" s="9"/>
       <c r="R83" s="9"/>
@@ -6958,7 +6958,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B84" s="5">
         <v>46132.631352083336</v>
@@ -7000,10 +7000,10 @@
         <v>239</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -7013,7 +7013,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B85" s="8">
         <v>46132.63135776621</v>
@@ -7055,10 +7055,10 @@
         <v>239</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Q85" s="9"/>
       <c r="R85" s="9"/>
@@ -7068,7 +7068,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B86" s="5">
         <v>46132.63136296296</v>
@@ -7110,10 +7110,10 @@
         <v>239</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -7123,7 +7123,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B87" s="8">
         <v>46132.63136688658</v>
@@ -7165,10 +7165,10 @@
         <v>239</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="P87" s="9" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="Q87" s="9"/>
       <c r="R87" s="9"/>
@@ -7178,7 +7178,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B88" s="5">
         <v>46132.63137239583</v>
@@ -7220,10 +7220,10 @@
         <v>239</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -7233,7 +7233,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B89" s="8">
         <v>46132.58889809028</v>
@@ -7243,7 +7243,7 @@
         <v>46203.20341778935</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
@@ -7273,7 +7273,7 @@
         <v>232</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="P89" s="9" t="s">
         <v>232</v>
@@ -7285,7 +7285,7 @@
         <v>46209</v>
       </c>
       <c r="S89" s="12" t="s">
-        <v>241</v>
+        <v>271</v>
       </c>
       <c r="T89" s="9">
         <v>1</v>
@@ -7335,7 +7335,7 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="O90" s="6" t="s">
         <v>274</v>
@@ -7390,7 +7390,7 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="O91" s="9" t="s">
         <v>274</v>
@@ -7445,7 +7445,7 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="O92" s="6" t="s">
         <v>274</v>
@@ -7500,7 +7500,7 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="O93" s="9" t="s">
         <v>274</v>
@@ -7555,7 +7555,7 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="O94" s="6" t="s">
         <v>274</v>
@@ -7610,7 +7610,7 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="O95" s="9" t="s">
         <v>274</v>
@@ -7665,7 +7665,7 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="O96" s="6" t="s">
         <v>274</v>
@@ -7720,7 +7720,7 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="O97" s="9" t="s">
         <v>274</v>
@@ -7775,7 +7775,7 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="O98" s="6" t="s">
         <v>274</v>
@@ -7830,7 +7830,7 @@
         <v>26</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="O99" s="9" t="s">
         <v>274</v>
@@ -7885,7 +7885,7 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="O100" s="6" t="s">
         <v>274</v>
@@ -7940,7 +7940,7 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="O101" s="9" t="s">
         <v>274</v>
@@ -7995,7 +7995,7 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="O102" s="6" t="s">
         <v>274</v>
@@ -8048,7 +8048,7 @@
         <v>26</v>
       </c>
       <c r="N103" s="9" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="O103" s="9" t="s">
         <v>274</v>
@@ -8101,7 +8101,7 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="O104" s="6" t="s">
         <v>274</v>
@@ -8154,7 +8154,7 @@
         <v>26</v>
       </c>
       <c r="N105" s="9" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="O105" s="9" t="s">
         <v>274</v>

--- a/data/50001541 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001541 - XEMORTIZ MINERA FRISCO.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3224" uniqueCount="548">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3225" uniqueCount="548">
   <si>
     <t>50001541 -  XEMORTIZ MINERA FRISCO</t>
   </si>
@@ -6181,9 +6181,11 @@
       <c r="B70" s="5">
         <v>46132.58888190972</v>
       </c>
-      <c r="C70" s="6"/>
+      <c r="C70" s="5">
+        <v>46209.63277412037</v>
+      </c>
       <c r="D70" s="5">
-        <v>46196.691984930556</v>
+        <v>46209.6327872338</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>232</v>
@@ -6218,8 +6220,12 @@
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
       <c r="S70" s="6"/>
-      <c r="T70" s="6"/>
-      <c r="U70" s="6"/>
+      <c r="T70" s="6">
+        <v>1</v>
+      </c>
+      <c r="U70" s="11" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
@@ -7238,9 +7244,11 @@
       <c r="B89" s="8">
         <v>46132.58889809028</v>
       </c>
-      <c r="C89" s="9"/>
+      <c r="C89" s="8">
+        <v>46209.6327590162</v>
+      </c>
       <c r="D89" s="8">
-        <v>46203.20341778935</v>
+        <v>46209.63276071759</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>269</v>
@@ -7290,8 +7298,8 @@
       <c r="T89" s="9">
         <v>1</v>
       </c>
-      <c r="U89" s="10" t="s">
-        <v>98</v>
+      <c r="U89" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
@@ -8016,9 +8024,11 @@
       <c r="B103" s="8">
         <v>46132.63157251157</v>
       </c>
-      <c r="C103" s="9"/>
+      <c r="C103" s="8">
+        <v>46209.63248238426</v>
+      </c>
       <c r="D103" s="8">
-        <v>46196.912235208336</v>
+        <v>46209.63248512732</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>273</v>
@@ -8069,9 +8079,11 @@
       <c r="B104" s="5">
         <v>46132.631576643515</v>
       </c>
-      <c r="C104" s="6"/>
+      <c r="C104" s="5">
+        <v>46209.63248900463</v>
+      </c>
       <c r="D104" s="5">
-        <v>46196.91224765046</v>
+        <v>46209.63249092593</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>173</v>
@@ -8122,9 +8134,11 @@
       <c r="B105" s="8">
         <v>46132.6319078588</v>
       </c>
-      <c r="C105" s="9"/>
+      <c r="C105" s="8">
+        <v>46209.63249508102</v>
+      </c>
       <c r="D105" s="8">
-        <v>46196.91227103009</v>
+        <v>46209.63249679398</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>273</v>
@@ -9248,7 +9262,7 @@
         <v>46205.49134238426</v>
       </c>
       <c r="D125" s="8">
-        <v>46205.4913437037</v>
+        <v>46209.63248880787</v>
       </c>
       <c r="E125" s="9" t="s">
         <v>173</v>
@@ -9303,7 +9317,7 @@
         <v>46205.49141931713</v>
       </c>
       <c r="D126" s="5">
-        <v>46205.49142064815</v>
+        <v>46209.63249525463</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>173</v>
@@ -9358,7 +9372,7 @@
         <v>46205.49149630787</v>
       </c>
       <c r="D127" s="8">
-        <v>46205.49149763889</v>
+        <v>46209.632502152774</v>
       </c>
       <c r="E127" s="9" t="s">
         <v>173</v>

--- a/data/50001541 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001541 - XEMORTIZ MINERA FRISCO.xlsx
@@ -8482,7 +8482,7 @@
         <v>46205.49151155092</v>
       </c>
       <c r="D111" s="8">
-        <v>46205.49152811343</v>
+        <v>46210.19028358796</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>307</v>
@@ -8526,8 +8526,8 @@
       <c r="R111" s="8">
         <v>46211</v>
       </c>
-      <c r="S111" s="11" t="s">
-        <v>97</v>
+      <c r="S111" s="12" t="s">
+        <v>271</v>
       </c>
       <c r="T111" s="9">
         <v>1</v>

--- a/data/50001541 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001541 - XEMORTIZ MINERA FRISCO.xlsx
@@ -826,118 +826,118 @@
     <t>OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2</t>
   </si>
   <si>
+    <t>1214137717389481</t>
+  </si>
+  <si>
+    <t>OT 4307 ZVN 1-9-86/2</t>
+  </si>
+  <si>
+    <t>OT 4307 ZVN 1-9-86/2 ,Check Planos</t>
+  </si>
+  <si>
+    <t>OT 4307 ZVN 1-9-86/2 ,Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>1214137717389482</t>
+  </si>
+  <si>
+    <t>OT 4307 ZVN 1-9-86/2,Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>1214137717389483</t>
+  </si>
+  <si>
+    <t>1214137717389484</t>
+  </si>
+  <si>
+    <t>1214137717389485</t>
+  </si>
+  <si>
+    <t>1214137717389486</t>
+  </si>
+  <si>
+    <t>1214137717389487</t>
+  </si>
+  <si>
+    <t>1214137717389488</t>
+  </si>
+  <si>
+    <t>1214137717389489</t>
+  </si>
+  <si>
+    <t>1214137717389490</t>
+  </si>
+  <si>
+    <t>1214137717389491</t>
+  </si>
+  <si>
+    <t>1214137717389492</t>
+  </si>
+  <si>
+    <t>1214137717389493</t>
+  </si>
+  <si>
+    <t>1214137717389494</t>
+  </si>
+  <si>
+    <t>1214137717389495</t>
+  </si>
+  <si>
+    <t>1214137717389497</t>
+  </si>
+  <si>
+    <t>1214138720971081</t>
+  </si>
+  <si>
+    <t>Bodega:</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete,Recepcion motor,Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>1214138844805204</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodega:,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 </t>
+  </si>
+  <si>
+    <t>1214138844805224</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete</t>
+  </si>
+  <si>
+    <t>1214138720975469</t>
+  </si>
+  <si>
+    <t>Recepcion motor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodega:,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 </t>
+  </si>
+  <si>
+    <t>1214138720975489</t>
+  </si>
+  <si>
+    <t>Montaje:</t>
+  </si>
+  <si>
+    <t>Revestimiento,Montaje motor,Montaje Rodete,RE-PINTADO,Montaje Alabe,Pruebas FAT</t>
+  </si>
+  <si>
+    <t>1214138644320327</t>
+  </si>
+  <si>
+    <t>Revestimiento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 </t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1214137717389481</t>
-  </si>
-  <si>
-    <t>OT 4307 ZVN 1-9-86/2</t>
-  </si>
-  <si>
-    <t>OT 4307 ZVN 1-9-86/2 ,Check Planos</t>
-  </si>
-  <si>
-    <t>OT 4307 ZVN 1-9-86/2 ,Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>1214137717389482</t>
-  </si>
-  <si>
-    <t>OT 4307 ZVN 1-9-86/2,Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>1214137717389483</t>
-  </si>
-  <si>
-    <t>1214137717389484</t>
-  </si>
-  <si>
-    <t>1214137717389485</t>
-  </si>
-  <si>
-    <t>1214137717389486</t>
-  </si>
-  <si>
-    <t>1214137717389487</t>
-  </si>
-  <si>
-    <t>1214137717389488</t>
-  </si>
-  <si>
-    <t>1214137717389489</t>
-  </si>
-  <si>
-    <t>1214137717389490</t>
-  </si>
-  <si>
-    <t>1214137717389491</t>
-  </si>
-  <si>
-    <t>1214137717389492</t>
-  </si>
-  <si>
-    <t>1214137717389493</t>
-  </si>
-  <si>
-    <t>1214137717389494</t>
-  </si>
-  <si>
-    <t>1214137717389495</t>
-  </si>
-  <si>
-    <t>1214137717389497</t>
-  </si>
-  <si>
-    <t>1214138720971081</t>
-  </si>
-  <si>
-    <t>Bodega:</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete,Recepcion motor,Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>1214138844805204</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodega:,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 </t>
-  </si>
-  <si>
-    <t>1214138844805224</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete</t>
-  </si>
-  <si>
-    <t>1214138720975469</t>
-  </si>
-  <si>
-    <t>Recepcion motor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodega:,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 </t>
-  </si>
-  <si>
-    <t>1214138720975489</t>
-  </si>
-  <si>
-    <t>Montaje:</t>
-  </si>
-  <si>
-    <t>Revestimiento,Montaje motor,Montaje Rodete,RE-PINTADO,Montaje Alabe,Pruebas FAT</t>
-  </si>
-  <si>
-    <t>1214138644320327</t>
-  </si>
-  <si>
-    <t>Revestimiento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 </t>
   </si>
   <si>
     <t>1214137717389498</t>
@@ -7248,7 +7248,7 @@
         <v>46209.6327590162</v>
       </c>
       <c r="D89" s="8">
-        <v>46209.63276071759</v>
+        <v>46211.16681866898</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>269</v>
@@ -7292,8 +7292,8 @@
       <c r="R89" s="8">
         <v>46209</v>
       </c>
-      <c r="S89" s="12" t="s">
-        <v>271</v>
+      <c r="S89" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T89" s="9">
         <v>1</v>
@@ -7304,7 +7304,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B90" s="5">
         <v>46132.63147894676</v>
@@ -7316,7 +7316,7 @@
         <v>46196.913305381946</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -7346,10 +7346,10 @@
         <v>269</v>
       </c>
       <c r="O90" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="P90" s="6" t="s">
         <v>274</v>
-      </c>
-      <c r="P90" s="6" t="s">
-        <v>275</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -7359,7 +7359,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B91" s="8">
         <v>46132.63149082176</v>
@@ -7371,7 +7371,7 @@
         <v>46196.9133102662</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
@@ -7401,10 +7401,10 @@
         <v>269</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Q91" s="9"/>
       <c r="R91" s="9"/>
@@ -7414,7 +7414,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B92" s="5">
         <v>46132.63149714121</v>
@@ -7426,7 +7426,7 @@
         <v>46196.91331809028</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -7456,10 +7456,10 @@
         <v>269</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -7469,7 +7469,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B93" s="8">
         <v>46132.63150280093</v>
@@ -7481,7 +7481,7 @@
         <v>46196.91332601852</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
@@ -7511,10 +7511,10 @@
         <v>269</v>
       </c>
       <c r="O93" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="P93" s="9" t="s">
         <v>274</v>
-      </c>
-      <c r="P93" s="9" t="s">
-        <v>275</v>
       </c>
       <c r="Q93" s="9"/>
       <c r="R93" s="9"/>
@@ -7524,7 +7524,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B94" s="5">
         <v>46132.63150895834</v>
@@ -7536,7 +7536,7 @@
         <v>46196.91333064815</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -7566,10 +7566,10 @@
         <v>269</v>
       </c>
       <c r="O94" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="P94" s="6" t="s">
         <v>274</v>
-      </c>
-      <c r="P94" s="6" t="s">
-        <v>275</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7579,7 +7579,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B95" s="8">
         <v>46132.63151432871</v>
@@ -7591,7 +7591,7 @@
         <v>46196.91333818287</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
@@ -7621,10 +7621,10 @@
         <v>269</v>
       </c>
       <c r="O95" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="P95" s="9" t="s">
         <v>274</v>
-      </c>
-      <c r="P95" s="9" t="s">
-        <v>275</v>
       </c>
       <c r="Q95" s="9"/>
       <c r="R95" s="9"/>
@@ -7634,7 +7634,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B96" s="5">
         <v>46132.631519525465</v>
@@ -7646,7 +7646,7 @@
         <v>46196.91334849537</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7676,10 +7676,10 @@
         <v>269</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7689,7 +7689,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B97" s="8">
         <v>46132.631524247685</v>
@@ -7701,7 +7701,7 @@
         <v>46196.91335584491</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
@@ -7731,10 +7731,10 @@
         <v>269</v>
       </c>
       <c r="O97" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="P97" s="9" t="s">
         <v>274</v>
-      </c>
-      <c r="P97" s="9" t="s">
-        <v>275</v>
       </c>
       <c r="Q97" s="9"/>
       <c r="R97" s="9"/>
@@ -7744,7 +7744,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B98" s="5">
         <v>46132.63153150463</v>
@@ -7756,7 +7756,7 @@
         <v>46196.913360879626</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7786,10 +7786,10 @@
         <v>269</v>
       </c>
       <c r="O98" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="P98" s="6" t="s">
         <v>274</v>
-      </c>
-      <c r="P98" s="6" t="s">
-        <v>275</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7799,7 +7799,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B99" s="8">
         <v>46132.631539270835</v>
@@ -7811,7 +7811,7 @@
         <v>46196.913369456015</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
@@ -7841,10 +7841,10 @@
         <v>269</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="P99" s="9" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Q99" s="9"/>
       <c r="R99" s="9"/>
@@ -7854,7 +7854,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B100" s="5">
         <v>46132.63154616898</v>
@@ -7866,7 +7866,7 @@
         <v>46196.91338305555</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7896,10 +7896,10 @@
         <v>269</v>
       </c>
       <c r="O100" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="P100" s="6" t="s">
         <v>274</v>
-      </c>
-      <c r="P100" s="6" t="s">
-        <v>275</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7909,7 +7909,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B101" s="8">
         <v>46132.63155506944</v>
@@ -7921,7 +7921,7 @@
         <v>46196.91339189815</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
@@ -7951,10 +7951,10 @@
         <v>269</v>
       </c>
       <c r="O101" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="P101" s="9" t="s">
         <v>274</v>
-      </c>
-      <c r="P101" s="9" t="s">
-        <v>275</v>
       </c>
       <c r="Q101" s="9"/>
       <c r="R101" s="9"/>
@@ -7964,7 +7964,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B102" s="5">
         <v>46132.63156422453</v>
@@ -7976,7 +7976,7 @@
         <v>46196.91339939815</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -8006,10 +8006,10 @@
         <v>269</v>
       </c>
       <c r="O102" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="P102" s="6" t="s">
         <v>274</v>
-      </c>
-      <c r="P102" s="6" t="s">
-        <v>275</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -8019,7 +8019,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B103" s="8">
         <v>46132.63157251157</v>
@@ -8031,7 +8031,7 @@
         <v>46209.63248512732</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>26</v>
@@ -8061,10 +8061,10 @@
         <v>269</v>
       </c>
       <c r="O103" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="P103" s="9" t="s">
         <v>274</v>
-      </c>
-      <c r="P103" s="9" t="s">
-        <v>275</v>
       </c>
       <c r="Q103" s="9"/>
       <c r="R103" s="9"/>
@@ -8074,7 +8074,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B104" s="5">
         <v>46132.631576643515</v>
@@ -8116,10 +8116,10 @@
         <v>269</v>
       </c>
       <c r="O104" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="P104" s="6" t="s">
         <v>274</v>
-      </c>
-      <c r="P104" s="6" t="s">
-        <v>275</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -8129,7 +8129,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B105" s="8">
         <v>46132.6319078588</v>
@@ -8141,7 +8141,7 @@
         <v>46209.63249679398</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>26</v>
@@ -8171,10 +8171,10 @@
         <v>269</v>
       </c>
       <c r="O105" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="P105" s="9" t="s">
         <v>274</v>
-      </c>
-      <c r="P105" s="9" t="s">
-        <v>275</v>
       </c>
       <c r="Q105" s="9"/>
       <c r="R105" s="9"/>
@@ -8184,7 +8184,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B106" s="5">
         <v>46132.58890393519</v>
@@ -8196,7 +8196,7 @@
         <v>46198.65523800926</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>25</v>
@@ -8220,7 +8220,7 @@
         <v>26</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="P106" s="6" t="s">
         <v>26</v>
@@ -8237,7 +8237,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B107" s="8">
         <v>46132.58890717593</v>
@@ -8249,7 +8249,7 @@
         <v>46198.65511907407</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
@@ -8274,13 +8274,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="9" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="O107" s="9" t="s">
         <v>100</v>
       </c>
       <c r="P107" s="9" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="Q107" s="8">
         <v>46146</v>
@@ -8300,7 +8300,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B108" s="5">
         <v>46132.58891280093</v>
@@ -8312,7 +8312,7 @@
         <v>46163.18906322916</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -8337,13 +8337,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="O108" s="6" t="s">
         <v>109</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="Q108" s="5">
         <v>46162</v>
@@ -8363,7 +8363,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B109" s="8">
         <v>46132.588918090274</v>
@@ -8375,7 +8375,7 @@
         <v>46198.65526501158</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>26</v>
@@ -8400,13 +8400,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="9" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="O109" s="9" t="s">
         <v>119</v>
       </c>
       <c r="P109" s="9" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="Q109" s="8">
         <v>46176</v>
@@ -8426,7 +8426,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B110" s="5">
         <v>46132.58892311342</v>
@@ -8436,7 +8436,7 @@
         <v>46205.491523854165</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>25</v>
@@ -8460,7 +8460,7 @@
         <v>26</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>26</v>
@@ -8473,7 +8473,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B111" s="8">
         <v>46132.58892658565</v>
@@ -8485,7 +8485,7 @@
         <v>46210.19028358796</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
@@ -8512,13 +8512,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="9" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P111" s="9" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="Q111" s="8">
         <v>46217</v>
@@ -8527,7 +8527,7 @@
         <v>46211</v>
       </c>
       <c r="S111" s="12" t="s">
-        <v>271</v>
+        <v>308</v>
       </c>
       <c r="T111" s="9">
         <v>1</v>
@@ -8577,10 +8577,10 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P112" s="6" t="s">
         <v>310</v>
@@ -8605,7 +8605,7 @@
         <v>46205.49090392361</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
@@ -8632,10 +8632,10 @@
         <v>26</v>
       </c>
       <c r="N113" s="9" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P113" s="9" t="s">
         <v>310</v>
@@ -8660,7 +8660,7 @@
         <v>46205.49091864583</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
@@ -8687,10 +8687,10 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P114" s="6" t="s">
         <v>313</v>
@@ -8742,10 +8742,10 @@
         <v>26</v>
       </c>
       <c r="N115" s="9" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="O115" s="9" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P115" s="9" t="s">
         <v>313</v>
@@ -8797,10 +8797,10 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P116" s="6" t="s">
         <v>313</v>
@@ -8852,10 +8852,10 @@
         <v>26</v>
       </c>
       <c r="N117" s="9" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="O117" s="9" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P117" s="9" t="s">
         <v>317</v>
@@ -8880,7 +8880,7 @@
         <v>46205.49095611111</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -8907,10 +8907,10 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P118" s="6" t="s">
         <v>317</v>
@@ -8962,10 +8962,10 @@
         <v>26</v>
       </c>
       <c r="N119" s="9" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="O119" s="9" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P119" s="9" t="s">
         <v>317</v>
@@ -9017,10 +9017,10 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P120" s="6" t="s">
         <v>317</v>
@@ -9045,7 +9045,7 @@
         <v>46205.49097503472</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>26</v>
@@ -9072,10 +9072,10 @@
         <v>26</v>
       </c>
       <c r="N121" s="9" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="O121" s="9" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P121" s="9" t="s">
         <v>317</v>
@@ -9127,10 +9127,10 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P122" s="6" t="s">
         <v>317</v>
@@ -9182,10 +9182,10 @@
         <v>26</v>
       </c>
       <c r="N123" s="9" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="O123" s="9" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P123" s="9" t="s">
         <v>317</v>
@@ -9237,10 +9237,10 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P124" s="6" t="s">
         <v>317</v>
@@ -9292,10 +9292,10 @@
         <v>26</v>
       </c>
       <c r="N125" s="9" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="O125" s="9" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P125" s="9" t="s">
         <v>317</v>
@@ -9347,7 +9347,7 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="O126" s="6" t="s">
         <v>173</v>
@@ -9402,10 +9402,10 @@
         <v>26</v>
       </c>
       <c r="N127" s="9" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="O127" s="9" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P127" s="9" t="s">
         <v>317</v>
@@ -9425,7 +9425,7 @@
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46134.57915813658</v>
+        <v>46211.180433483794</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>329</v>
@@ -9453,13 +9453,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="O128" s="6" t="s">
         <v>240</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="Q128" s="5">
         <v>46218</v>
@@ -9467,8 +9467,8 @@
       <c r="R128" s="5">
         <v>46218</v>
       </c>
-      <c r="S128" s="11" t="s">
-        <v>97</v>
+      <c r="S128" s="12" t="s">
+        <v>308</v>
       </c>
       <c r="T128" s="6">
         <v>0</v>
@@ -10330,13 +10330,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="9" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="O145" s="9" t="s">
         <v>240</v>
       </c>
       <c r="P145" s="9" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="Q145" s="8">
         <v>46219</v>
@@ -11207,13 +11207,13 @@
         <v>26</v>
       </c>
       <c r="N162" s="6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="O162" s="6" t="s">
         <v>240</v>
       </c>
       <c r="P162" s="6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="Q162" s="5">
         <v>46220</v>
@@ -12084,13 +12084,13 @@
         <v>26</v>
       </c>
       <c r="N179" s="9" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="O179" s="9" t="s">
         <v>240</v>
       </c>
       <c r="P179" s="9" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="Q179" s="8">
         <v>46223</v>
@@ -12961,7 +12961,7 @@
         <v>26</v>
       </c>
       <c r="N196" s="6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="O196" s="6" t="s">
         <v>433</v>
@@ -13762,7 +13762,7 @@
         <v>46196.91385334491</v>
       </c>
       <c r="E212" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F212" s="6" t="s">
         <v>26</v>
@@ -14714,7 +14714,7 @@
         <v>458</v>
       </c>
       <c r="O230" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P230" s="6" t="s">
         <v>173</v>

--- a/data/50001541 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001541 - XEMORTIZ MINERA FRISCO.xlsx
@@ -10302,7 +10302,7 @@
       </c>
       <c r="C145" s="9"/>
       <c r="D145" s="8">
-        <v>46134.579158981476</v>
+        <v>46212.19057934028</v>
       </c>
       <c r="E145" s="9" t="s">
         <v>354</v>
@@ -10344,8 +10344,8 @@
       <c r="R145" s="8">
         <v>46219</v>
       </c>
-      <c r="S145" s="11" t="s">
-        <v>97</v>
+      <c r="S145" s="12" t="s">
+        <v>308</v>
       </c>
       <c r="T145" s="9">
         <v>0</v>

--- a/data/50001541 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001541 - XEMORTIZ MINERA FRISCO.xlsx
@@ -544,7 +544,7 @@
     <t xml:space="preserve">OT2 4307 ZVN 1-9-86/2 </t>
   </si>
   <si>
-    <t>OT 4307 ZVN 1-9-86/2 ,Check pruebas FAT,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales</t>
+    <t>OT 4307 ZVN 1-9-86/2 ,Check pruebas FAT,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,OT 4347 Preparación Materiales</t>
   </si>
   <si>
     <t>1214137717389662</t>

--- a/data/50001541 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001541 - XEMORTIZ MINERA FRISCO.xlsx
@@ -9425,7 +9425,7 @@
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46211.180433483794</v>
+        <v>46213.546479745375</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>329</v>
@@ -9484,9 +9484,11 @@
       <c r="B129" s="8">
         <v>46132.63296805556</v>
       </c>
-      <c r="C129" s="9"/>
+      <c r="C129" s="8">
+        <v>46213.54645357639</v>
+      </c>
       <c r="D129" s="8">
-        <v>46205.490874247684</v>
+        <v>46213.546456041666</v>
       </c>
       <c r="E129" s="9" t="s">
         <v>173</v>
@@ -9535,9 +9537,11 @@
       <c r="B130" s="5">
         <v>46132.63297954861</v>
       </c>
-      <c r="C130" s="6"/>
+      <c r="C130" s="5">
+        <v>46213.54645896991</v>
+      </c>
       <c r="D130" s="5">
-        <v>46205.49091032408</v>
+        <v>46213.54646055556</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>173</v>
@@ -9586,9 +9590,11 @@
       <c r="B131" s="8">
         <v>46132.63298759259</v>
       </c>
-      <c r="C131" s="9"/>
+      <c r="C131" s="8">
+        <v>46213.54646347222</v>
+      </c>
       <c r="D131" s="8">
-        <v>46205.4909234838</v>
+        <v>46213.54646633102</v>
       </c>
       <c r="E131" s="9" t="s">
         <v>173</v>
@@ -9637,9 +9643,11 @@
       <c r="B132" s="5">
         <v>46132.63299327546</v>
       </c>
-      <c r="C132" s="6"/>
+      <c r="C132" s="5">
+        <v>46213.54646974537</v>
+      </c>
       <c r="D132" s="5">
-        <v>46205.49093675926</v>
+        <v>46213.546471423615</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>173</v>
@@ -9688,9 +9696,11 @@
       <c r="B133" s="8">
         <v>46132.63299994213</v>
       </c>
-      <c r="C133" s="9"/>
+      <c r="C133" s="8">
+        <v>46213.54647332176</v>
+      </c>
       <c r="D133" s="8">
-        <v>46205.490947592596</v>
+        <v>46213.5464743287</v>
       </c>
       <c r="E133" s="9" t="s">
         <v>173</v>
@@ -10302,7 +10312,7 @@
       </c>
       <c r="C145" s="9"/>
       <c r="D145" s="8">
-        <v>46212.19057934028</v>
+        <v>46213.546549328705</v>
       </c>
       <c r="E145" s="9" t="s">
         <v>354</v>
@@ -10361,9 +10371,11 @@
       <c r="B146" s="5">
         <v>46132.633140289356</v>
       </c>
-      <c r="C146" s="6"/>
+      <c r="C146" s="5">
+        <v>46213.5465221875</v>
+      </c>
       <c r="D146" s="5">
-        <v>46205.49087637731</v>
+        <v>46213.54652379629</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>173</v>
@@ -10412,9 +10424,11 @@
       <c r="B147" s="8">
         <v>46132.63314908565</v>
       </c>
-      <c r="C147" s="9"/>
+      <c r="C147" s="8">
+        <v>46213.54652690972</v>
+      </c>
       <c r="D147" s="8">
-        <v>46205.49091208333</v>
+        <v>46213.54652849537</v>
       </c>
       <c r="E147" s="9" t="s">
         <v>173</v>
@@ -10463,9 +10477,11 @@
       <c r="B148" s="5">
         <v>46132.63315533564</v>
       </c>
-      <c r="C148" s="6"/>
+      <c r="C148" s="5">
+        <v>46213.546531307875</v>
+      </c>
       <c r="D148" s="5">
-        <v>46205.490925254635</v>
+        <v>46213.54653331019</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>173</v>
@@ -10514,9 +10530,11 @@
       <c r="B149" s="8">
         <v>46132.63316266204</v>
       </c>
-      <c r="C149" s="9"/>
+      <c r="C149" s="8">
+        <v>46213.546540208336</v>
+      </c>
       <c r="D149" s="8">
-        <v>46205.49093855324</v>
+        <v>46213.546542372686</v>
       </c>
       <c r="E149" s="9" t="s">
         <v>173</v>
@@ -10565,9 +10583,11 @@
       <c r="B150" s="5">
         <v>46132.6331690625</v>
       </c>
-      <c r="C150" s="6"/>
+      <c r="C150" s="5">
+        <v>46213.546544259254</v>
+      </c>
       <c r="D150" s="5">
-        <v>46205.49094929398</v>
+        <v>46213.54654524305</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>173</v>
@@ -11179,7 +11199,7 @@
       </c>
       <c r="C162" s="6"/>
       <c r="D162" s="5">
-        <v>46134.57915975695</v>
+        <v>46213.54667520833</v>
       </c>
       <c r="E162" s="6" t="s">
         <v>375</v>
@@ -11221,8 +11241,8 @@
       <c r="R162" s="5">
         <v>46220</v>
       </c>
-      <c r="S162" s="11" t="s">
-        <v>97</v>
+      <c r="S162" s="12" t="s">
+        <v>308</v>
       </c>
       <c r="T162" s="6">
         <v>0</v>
@@ -11238,9 +11258,11 @@
       <c r="B163" s="8">
         <v>46132.632804305555</v>
       </c>
-      <c r="C163" s="9"/>
+      <c r="C163" s="8">
+        <v>46213.54663619213</v>
+      </c>
       <c r="D163" s="8">
-        <v>46198.655219224536</v>
+        <v>46213.54663787037</v>
       </c>
       <c r="E163" s="9" t="s">
         <v>173</v>
@@ -11289,9 +11311,11 @@
       <c r="B164" s="5">
         <v>46132.632815624995</v>
       </c>
-      <c r="C164" s="6"/>
+      <c r="C164" s="5">
+        <v>46213.54664094908</v>
+      </c>
       <c r="D164" s="5">
-        <v>46198.655218125</v>
+        <v>46213.54664256945</v>
       </c>
       <c r="E164" s="6" t="s">
         <v>173</v>
@@ -11340,9 +11364,11 @@
       <c r="B165" s="8">
         <v>46132.63282284723</v>
       </c>
-      <c r="C165" s="9"/>
+      <c r="C165" s="8">
+        <v>46213.5466527199</v>
+      </c>
       <c r="D165" s="8">
-        <v>46205.4909290625</v>
+        <v>46213.5466544213</v>
       </c>
       <c r="E165" s="9" t="s">
         <v>173</v>
@@ -11391,9 +11417,11 @@
       <c r="B166" s="5">
         <v>46132.63283236111</v>
       </c>
-      <c r="C166" s="6"/>
+      <c r="C166" s="5">
+        <v>46213.546661134256</v>
+      </c>
       <c r="D166" s="5">
-        <v>46205.49094030092</v>
+        <v>46213.546663217596</v>
       </c>
       <c r="E166" s="6" t="s">
         <v>173</v>
@@ -11442,9 +11470,11 @@
       <c r="B167" s="8">
         <v>46132.632837384255</v>
       </c>
-      <c r="C167" s="9"/>
+      <c r="C167" s="8">
+        <v>46213.54666658565</v>
+      </c>
       <c r="D167" s="8">
-        <v>46205.49095034722</v>
+        <v>46213.54666836806</v>
       </c>
       <c r="E167" s="9" t="s">
         <v>173</v>
@@ -12117,7 +12147,7 @@
       </c>
       <c r="C180" s="6"/>
       <c r="D180" s="5">
-        <v>46196.91349186342</v>
+        <v>46213.54664231482</v>
       </c>
       <c r="E180" s="6" t="s">
         <v>173</v>
@@ -12168,7 +12198,7 @@
       </c>
       <c r="C181" s="9"/>
       <c r="D181" s="8">
-        <v>46196.913516817134</v>
+        <v>46213.546648055555</v>
       </c>
       <c r="E181" s="9" t="s">
         <v>173</v>
@@ -12219,7 +12249,7 @@
       </c>
       <c r="C182" s="6"/>
       <c r="D182" s="5">
-        <v>46196.913533425926</v>
+        <v>46213.54665771991</v>
       </c>
       <c r="E182" s="6" t="s">
         <v>173</v>
@@ -12270,7 +12300,7 @@
       </c>
       <c r="C183" s="9"/>
       <c r="D183" s="8">
-        <v>46196.91352673611</v>
+        <v>46213.54666795139</v>
       </c>
       <c r="E183" s="9" t="s">
         <v>173</v>
@@ -12321,7 +12351,7 @@
       </c>
       <c r="C184" s="6"/>
       <c r="D184" s="5">
-        <v>46196.91354314815</v>
+        <v>46213.54667460648</v>
       </c>
       <c r="E184" s="6" t="s">
         <v>173</v>

--- a/data/50001541 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001541 - XEMORTIZ MINERA FRISCO.xlsx
@@ -8482,7 +8482,7 @@
         <v>46205.49151155092</v>
       </c>
       <c r="D111" s="8">
-        <v>46210.19028358796</v>
+        <v>46218.17036590278</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>307</v>
@@ -8526,8 +8526,8 @@
       <c r="R111" s="8">
         <v>46211</v>
       </c>
-      <c r="S111" s="12" t="s">
-        <v>171</v>
+      <c r="S111" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T111" s="9">
         <v>1</v>
@@ -9425,7 +9425,7 @@
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46213.546479745375</v>
+        <v>46218.16820684027</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>329</v>
@@ -9751,7 +9751,7 @@
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46205.49095398148</v>
+        <v>46218.16818836806</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>174</v>
@@ -9802,7 +9802,7 @@
       </c>
       <c r="C135" s="9"/>
       <c r="D135" s="8">
-        <v>46205.49096087963</v>
+        <v>46218.16818998843</v>
       </c>
       <c r="E135" s="9" t="s">
         <v>174</v>
@@ -9853,7 +9853,7 @@
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46205.49096756944</v>
+        <v>46218.16819125</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>174</v>
@@ -9904,7 +9904,7 @@
       </c>
       <c r="C137" s="9"/>
       <c r="D137" s="8">
-        <v>46205.49097484954</v>
+        <v>46218.16819265047</v>
       </c>
       <c r="E137" s="9" t="s">
         <v>174</v>
@@ -9955,7 +9955,7 @@
       </c>
       <c r="C138" s="6"/>
       <c r="D138" s="5">
-        <v>46205.490980925926</v>
+        <v>46218.16819402778</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>174</v>
@@ -10006,7 +10006,7 @@
       </c>
       <c r="C139" s="9"/>
       <c r="D139" s="8">
-        <v>46205.490997581015</v>
+        <v>46218.16819523148</v>
       </c>
       <c r="E139" s="9" t="s">
         <v>174</v>
@@ -10057,7 +10057,7 @@
       </c>
       <c r="C140" s="6"/>
       <c r="D140" s="5">
-        <v>46205.49100450231</v>
+        <v>46218.16819655093</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>174</v>
@@ -10108,7 +10108,7 @@
       </c>
       <c r="C141" s="9"/>
       <c r="D141" s="8">
-        <v>46205.49101099537</v>
+        <v>46218.168198935186</v>
       </c>
       <c r="E141" s="9" t="s">
         <v>174</v>
@@ -10159,7 +10159,7 @@
       </c>
       <c r="C142" s="6"/>
       <c r="D142" s="5">
-        <v>46205.49134896991</v>
+        <v>46218.168197754625</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>174</v>
@@ -10210,7 +10210,7 @@
       </c>
       <c r="C143" s="9"/>
       <c r="D143" s="8">
-        <v>46205.491426238426</v>
+        <v>46218.16820015047</v>
       </c>
       <c r="E143" s="9" t="s">
         <v>174</v>
@@ -10261,7 +10261,7 @@
       </c>
       <c r="C144" s="6"/>
       <c r="D144" s="5">
-        <v>46205.49150607639</v>
+        <v>46218.16820136574</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>174</v>
@@ -12963,7 +12963,7 @@
       </c>
       <c r="C196" s="6"/>
       <c r="D196" s="5">
-        <v>46134.579161331014</v>
+        <v>46218.167600706016</v>
       </c>
       <c r="E196" s="6" t="s">
         <v>432</v>
@@ -13005,8 +13005,8 @@
       <c r="R196" s="5">
         <v>46225</v>
       </c>
-      <c r="S196" s="11" t="s">
-        <v>97</v>
+      <c r="S196" s="12" t="s">
+        <v>171</v>
       </c>
       <c r="T196" s="6">
         <v>0</v>

--- a/data/50001541 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001541 - XEMORTIZ MINERA FRISCO.xlsx
@@ -9372,7 +9372,7 @@
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46218.16820684027</v>
+        <v>46219.17992138889</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>326</v>
@@ -9412,8 +9412,8 @@
       <c r="R128" s="5">
         <v>46218</v>
       </c>
-      <c r="S128" s="12" t="s">
-        <v>168</v>
+      <c r="S128" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T128" s="6">
         <v>0</v>
@@ -13664,7 +13664,7 @@
       </c>
       <c r="C214" s="6"/>
       <c r="D214" s="5">
-        <v>46133.58482033564</v>
+        <v>46219.16942784722</v>
       </c>
       <c r="E214" s="6" t="s">
         <v>455</v>
@@ -13706,8 +13706,8 @@
       <c r="R214" s="5">
         <v>46226</v>
       </c>
-      <c r="S214" s="11" t="s">
-        <v>94</v>
+      <c r="S214" s="12" t="s">
+        <v>168</v>
       </c>
       <c r="T214" s="6">
         <v>0</v>

--- a/data/50001541 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001541 - XEMORTIZ MINERA FRISCO.xlsx
@@ -10225,7 +10225,7 @@
       </c>
       <c r="C145" s="9"/>
       <c r="D145" s="8">
-        <v>46213.546549328705</v>
+        <v>46220.17490450232</v>
       </c>
       <c r="E145" s="9" t="s">
         <v>351</v>
@@ -10265,8 +10265,8 @@
       <c r="R145" s="8">
         <v>46219</v>
       </c>
-      <c r="S145" s="12" t="s">
-        <v>168</v>
+      <c r="S145" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T145" s="9">
         <v>0</v>
@@ -14541,7 +14541,7 @@
       </c>
       <c r="C231" s="9"/>
       <c r="D231" s="8">
-        <v>46133.58651043981</v>
+        <v>46220.16981112269</v>
       </c>
       <c r="E231" s="9" t="s">
         <v>476</v>
@@ -14581,8 +14581,8 @@
       <c r="R231" s="8">
         <v>46227</v>
       </c>
-      <c r="S231" s="11" t="s">
-        <v>94</v>
+      <c r="S231" s="12" t="s">
+        <v>168</v>
       </c>
       <c r="T231" s="9">
         <v>0</v>

--- a/data/50001541 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001541 - XEMORTIZ MINERA FRISCO.xlsx
@@ -11078,7 +11078,7 @@
       </c>
       <c r="C162" s="6"/>
       <c r="D162" s="5">
-        <v>46213.54667520833</v>
+        <v>46221.20680732639</v>
       </c>
       <c r="E162" s="6" t="s">
         <v>372</v>
@@ -11118,8 +11118,8 @@
       <c r="R162" s="5">
         <v>46220</v>
       </c>
-      <c r="S162" s="12" t="s">
-        <v>168</v>
+      <c r="S162" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T162" s="6">
         <v>0</v>

--- a/data/50001541 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001541 - XEMORTIZ MINERA FRISCO.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3224" uniqueCount="546">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3225" uniqueCount="546">
   <si>
     <t>50001541 -  XEMORTIZ MINERA FRISCO</t>
   </si>
@@ -3281,7 +3281,7 @@
         <v>46196.64064614583</v>
       </c>
       <c r="D20" s="5">
-        <v>46196.6430977662</v>
+        <v>46223.835789375</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>77</v>
@@ -3290,9 +3290,11 @@
         <v>26</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H20" s="6"/>
+        <v>63</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>63</v>
+      </c>
       <c r="I20" s="5">
         <v>46167</v>
       </c>

--- a/data/50001541 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001541 - XEMORTIZ MINERA FRISCO.xlsx
@@ -4857,7 +4857,7 @@
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46217.17228673611</v>
+        <v>46224.167821111114</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>165</v>
@@ -4918,7 +4918,7 @@
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="8">
-        <v>46196.91191069444</v>
+        <v>46224.1677925463</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>171</v>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46196.91191847222</v>
+        <v>46224.16779487269</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>175</v>
@@ -5020,7 +5020,7 @@
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="8">
-        <v>46196.911927002315</v>
+        <v>46224.167796215275</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>178</v>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46196.91193416667</v>
+        <v>46224.1677978125</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>180</v>
@@ -5122,7 +5122,7 @@
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="8">
-        <v>46196.91194335648</v>
+        <v>46224.16779921296</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>182</v>
@@ -5173,7 +5173,7 @@
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46196.911952731476</v>
+        <v>46224.167800717594</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>184</v>
@@ -5224,7 +5224,7 @@
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="8">
-        <v>46196.91195940972</v>
+        <v>46224.16780229167</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>186</v>
@@ -5275,7 +5275,7 @@
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46196.91196953703</v>
+        <v>46224.167803668985</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>189</v>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="C55" s="9"/>
       <c r="D55" s="8">
-        <v>46196.91198518519</v>
+        <v>46224.16780512732</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>191</v>
@@ -5377,7 +5377,7 @@
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46196.912005659724</v>
+        <v>46224.16780649306</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>193</v>
@@ -5428,7 +5428,7 @@
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46196.912017662034</v>
+        <v>46224.167809293984</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>195</v>
@@ -5479,7 +5479,7 @@
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46196.91202767361</v>
+        <v>46224.167810625004</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>197</v>
@@ -5530,7 +5530,7 @@
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46196.912036967595</v>
+        <v>46224.16781208334</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>199</v>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46196.91204791667</v>
+        <v>46224.16781392361</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>201</v>
@@ -5632,7 +5632,7 @@
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46196.9120665625</v>
+        <v>46224.16781546296</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>203</v>
@@ -5683,7 +5683,7 @@
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46196.91208912037</v>
+        <v>46224.16780783565</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>206</v>
@@ -12080,7 +12080,7 @@
       </c>
       <c r="C179" s="9"/>
       <c r="D179" s="8">
-        <v>46223.604696423616</v>
+        <v>46224.19308488426</v>
       </c>
       <c r="E179" s="9" t="s">
         <v>395</v>
@@ -12122,8 +12122,8 @@
       <c r="R179" s="8">
         <v>46223</v>
       </c>
-      <c r="S179" s="12" t="s">
-        <v>169</v>
+      <c r="S179" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T179" s="9">
         <v>0</v>
@@ -16514,7 +16514,7 @@
       </c>
       <c r="C265" s="9"/>
       <c r="D265" s="8">
-        <v>46133.65412578704</v>
+        <v>46224.169102106476</v>
       </c>
       <c r="E265" s="9" t="s">
         <v>517</v>
@@ -16556,8 +16556,8 @@
       <c r="R265" s="8">
         <v>46231</v>
       </c>
-      <c r="S265" s="11" t="s">
-        <v>95</v>
+      <c r="S265" s="12" t="s">
+        <v>169</v>
       </c>
       <c r="T265" s="9">
         <v>0</v>

--- a/data/50001541 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001541 - XEMORTIZ MINERA FRISCO.xlsx
@@ -520,796 +520,796 @@
     <t xml:space="preserve">OT1 4307 ZVN 1-9-86/2 ,OT2 4307 ZVN 1-9-86/2 ,OT3 4307 ZVN 1-9-86/2 ,OT4 4307 ZVN 1-9-86/2 ,OT5 4307 ZVN 1-9-86/2 ,OT6 4307 ZVN 1-9-86/2 ,OT7 4307 ZVN 1-9-86/2 ,OT8 4307  ZVN 1-9-86/2 ,OT9 4307 ZVN 1-9-86/2 ,OT10 4307 ZVN 1-9-86/2  ,OT11 4307 ZVN 1-9-86/2 ,OT12 4307 ZVN 1-9-86/2 ,OT13 4307 ZVN 1-9-86/2 ,OT14 4307 ZVN 1-9-86/2 ,OT15 4307 ZVN 1-9-86/2 ,OT16 4307 ZVN 1-9-86/2 </t>
   </si>
   <si>
+    <t>1214137717389660</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT1 4307 ZVN 1-9-86/2 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4307 ZVN 1-9-86/2 </t>
+  </si>
+  <si>
+    <t>OT 4307 ZVN 1-9-86/2 ,Check pruebas FAT</t>
+  </si>
+  <si>
+    <t>1214137717389661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT2 4307 ZVN 1-9-86/2 </t>
+  </si>
+  <si>
+    <t>OT 4307 ZVN 1-9-86/2 ,Check pruebas FAT,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,OT 4347 Preparación Materiales</t>
+  </si>
+  <si>
+    <t>1214137717389662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT3 4307 ZVN 1-9-86/2 </t>
+  </si>
+  <si>
+    <t>1214137717389663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT4 4307 ZVN 1-9-86/2 </t>
+  </si>
+  <si>
+    <t>1214137717389664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT5 4307 ZVN 1-9-86/2 </t>
+  </si>
+  <si>
+    <t>1214137717389665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT6 4307 ZVN 1-9-86/2 </t>
+  </si>
+  <si>
+    <t>1214137717389666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT7 4307 ZVN 1-9-86/2 </t>
+  </si>
+  <si>
+    <t>OT 4307 ZVN 1-9-86/2 ,Check pruebas FAT,OT 4325- ZVN 1-7-63/2,OT 4327- ZVN 2-9-103/2</t>
+  </si>
+  <si>
+    <t>1214137717389667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT8 4307  ZVN 1-9-86/2 </t>
+  </si>
+  <si>
+    <t>1214137717389668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT9 4307 ZVN 1-9-86/2 </t>
+  </si>
+  <si>
+    <t>1214137717389669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT10 4307 ZVN 1-9-86/2  </t>
+  </si>
+  <si>
+    <t>1214137717389671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT11 4307 ZVN 1-9-86/2 </t>
+  </si>
+  <si>
+    <t>1214137717389672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT12 4307 ZVN 1-9-86/2 </t>
+  </si>
+  <si>
+    <t>1214137717389673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT13 4307 ZVN 1-9-86/2 </t>
+  </si>
+  <si>
+    <t>1214137717389674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT14 4307 ZVN 1-9-86/2 </t>
+  </si>
+  <si>
+    <t>1214137717389675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT15 4307 ZVN 1-9-86/2 </t>
+  </si>
+  <si>
+    <t>OT 4307  ZVN 1-9-86/2 ,Check pruebas FAT</t>
+  </si>
+  <si>
+    <t>1214137717389670</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT16 4307 ZVN 1-9-86/2 </t>
+  </si>
+  <si>
+    <t>OT 4307 ZVN 1-9-86/2,Check pruebas FAT</t>
+  </si>
+  <si>
+    <t>1214137717389712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodega </t>
+  </si>
+  <si>
+    <t>Recepcion corte laser ,Recepcion corte plasma ,Recepcion mecanizado,Control de calidad corte Laser,Control de calidad Corte plasma ,Control de calidad Mecanizado</t>
+  </si>
+  <si>
+    <t>1214137717389442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion corte laser </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad corte Laser,Bodega </t>
+  </si>
+  <si>
+    <t>1214137717389443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion corte plasma </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Corte plasma ,Bodega </t>
+  </si>
+  <si>
+    <t>1214137717389444</t>
+  </si>
+  <si>
+    <t>Recepcion mecanizado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Mecanizado,Bodega </t>
+  </si>
+  <si>
+    <t>1214137717389804</t>
+  </si>
+  <si>
+    <t>Control de calidad corte Laser</t>
+  </si>
+  <si>
+    <t>Nicolás López</t>
+  </si>
+  <si>
+    <t>nicolas.lopez@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodega ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 </t>
+  </si>
+  <si>
+    <t>1214137717389805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Corte plasma </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodega ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 </t>
+  </si>
+  <si>
+    <t>1214137717389806</t>
+  </si>
+  <si>
+    <t>Control de calidad Mecanizado</t>
+  </si>
+  <si>
+    <t>1214138801637009</t>
+  </si>
+  <si>
+    <t>Fabricación externa:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armado,Control de calidad Armado,Generación OC Fabricación externa </t>
+  </si>
+  <si>
+    <t>1214138801637019</t>
+  </si>
+  <si>
+    <t>Rosemary Singh</t>
+  </si>
+  <si>
+    <t>rosemary.singh@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación externa:,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 </t>
+  </si>
+  <si>
+    <t>1214138711519166</t>
+  </si>
+  <si>
+    <t>Armado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 </t>
+  </si>
+  <si>
+    <t>1214137717389464</t>
+  </si>
+  <si>
+    <t>Generación OC Fabricación externa ,Control de calidad Mecanizado,Control de calidad corte Laser,Control de calidad Corte plasma ,Check Planos</t>
+  </si>
+  <si>
+    <t>OT 4307 ZVN 1-9-86/2,Armado</t>
+  </si>
+  <si>
+    <t>1214137717389465</t>
+  </si>
+  <si>
+    <t>1214137717389466</t>
+  </si>
+  <si>
+    <t>Generación OC Fabricación externa ,Control de calidad corte Laser,Control de calidad Corte plasma ,Control de calidad Mecanizado,Check Planos</t>
+  </si>
+  <si>
+    <t>Armado,OT 4307 ZVN 1-9-86/2</t>
+  </si>
+  <si>
+    <t>1214137717389467</t>
+  </si>
+  <si>
+    <t>1214137717389468</t>
+  </si>
+  <si>
+    <t>Generación OC Fabricación externa ,Control de calidad corte Laser,Control de calidad Mecanizado,Check Planos</t>
+  </si>
+  <si>
+    <t>1214137717389469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Mecanizado,Generación OC Fabricación externa ,Check Planos,Control de calidad corte Laser,Control de calidad Corte plasma </t>
+  </si>
+  <si>
+    <t>1214137717389470</t>
+  </si>
+  <si>
+    <t>Control de calidad corte Laser,Control de calidad Corte plasma ,Control de calidad Mecanizado,Generación OC Fabricación externa ,Check Planos</t>
+  </si>
+  <si>
+    <t>1214137717389471</t>
+  </si>
+  <si>
+    <t>Control de calidad Corte plasma ,Generación OC Fabricación externa ,Check Planos,Control de calidad corte Laser</t>
+  </si>
+  <si>
+    <t>1214137717389472</t>
+  </si>
+  <si>
+    <t>1214137717389473</t>
+  </si>
+  <si>
+    <t>Control de calidad corte Laser,Control de calidad Corte plasma ,Generación OC Fabricación externa ,Check Planos</t>
+  </si>
+  <si>
+    <t>1214137717389474</t>
+  </si>
+  <si>
+    <t>1214137717389475</t>
+  </si>
+  <si>
+    <t>1214137717389476</t>
+  </si>
+  <si>
+    <t>1214137717389477</t>
+  </si>
+  <si>
+    <t>Control de calidad corte Laser,Control de calidad Mecanizado,Generación OC Fabricación externa ,Check Planos</t>
+  </si>
+  <si>
+    <t>1214137717389478</t>
+  </si>
+  <si>
+    <t>OT 4307 ZVN 1-9-86/2 ,Armado</t>
+  </si>
+  <si>
+    <t>1214137717389479</t>
+  </si>
+  <si>
+    <t>1214138711519194</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2</t>
+  </si>
+  <si>
+    <t>1214137717389481</t>
+  </si>
+  <si>
+    <t>OT 4307 ZVN 1-9-86/2</t>
+  </si>
+  <si>
+    <t>OT 4307 ZVN 1-9-86/2 ,Check Planos</t>
+  </si>
+  <si>
+    <t>OT 4307 ZVN 1-9-86/2 ,Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>1214137717389482</t>
+  </si>
+  <si>
+    <t>OT 4307 ZVN 1-9-86/2,Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>1214137717389483</t>
+  </si>
+  <si>
+    <t>1214137717389484</t>
+  </si>
+  <si>
+    <t>1214137717389485</t>
+  </si>
+  <si>
+    <t>1214137717389486</t>
+  </si>
+  <si>
+    <t>1214137717389487</t>
+  </si>
+  <si>
+    <t>1214137717389488</t>
+  </si>
+  <si>
+    <t>1214137717389489</t>
+  </si>
+  <si>
+    <t>1214137717389490</t>
+  </si>
+  <si>
+    <t>1214137717389491</t>
+  </si>
+  <si>
+    <t>1214137717389492</t>
+  </si>
+  <si>
+    <t>1214137717389493</t>
+  </si>
+  <si>
+    <t>1214137717389494</t>
+  </si>
+  <si>
+    <t>1214137717389495</t>
+  </si>
+  <si>
+    <t>1214137717389497</t>
+  </si>
+  <si>
+    <t>1214138720971081</t>
+  </si>
+  <si>
+    <t>Bodega:</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete,Recepcion motor,Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>1214138844805204</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodega:,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 </t>
+  </si>
+  <si>
+    <t>1214138844805224</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete</t>
+  </si>
+  <si>
+    <t>1214138720975469</t>
+  </si>
+  <si>
+    <t>Recepcion motor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodega:,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 </t>
+  </si>
+  <si>
+    <t>1214138720975489</t>
+  </si>
+  <si>
+    <t>Montaje:</t>
+  </si>
+  <si>
+    <t>Revestimiento,Montaje motor,Montaje Rodete,RE-PINTADO,Montaje Alabe,Pruebas FAT</t>
+  </si>
+  <si>
+    <t>1214138644320327</t>
+  </si>
+  <si>
+    <t>Revestimiento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 </t>
+  </si>
+  <si>
+    <t>1214137717389498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4307 ZVN 1-9-86/2 ,Revestimiento,OT 4307 ZVN 1-9-86/2 </t>
+  </si>
+  <si>
+    <t>1214137717389499</t>
+  </si>
+  <si>
+    <t>1214137717389500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4307 ZVN 1-9-86/2 ,Revestimiento,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 </t>
+  </si>
+  <si>
+    <t>1214137717389501</t>
+  </si>
+  <si>
+    <t>1214137717389502</t>
+  </si>
+  <si>
+    <t>1214137717389503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revestimiento,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 </t>
+  </si>
+  <si>
+    <t>1214137717389504</t>
+  </si>
+  <si>
+    <t>1214137717389505</t>
+  </si>
+  <si>
+    <t>1214137717389506</t>
+  </si>
+  <si>
+    <t>1214137717389508</t>
+  </si>
+  <si>
+    <t>1214137717389507</t>
+  </si>
+  <si>
+    <t>1214137717389509</t>
+  </si>
+  <si>
+    <t>1214137717389510</t>
+  </si>
+  <si>
+    <t>1214137717389511</t>
+  </si>
+  <si>
+    <t>1214137717389512</t>
+  </si>
+  <si>
+    <t>1214137717389513</t>
+  </si>
+  <si>
+    <t>1214138711530631</t>
+  </si>
+  <si>
+    <t>Montaje Alabe</t>
+  </si>
+  <si>
+    <t>1214137717389530</t>
+  </si>
+  <si>
+    <t>OT 4307 ZVN 1-9-86/2 ,Recepcion Alabe,Check Planos</t>
+  </si>
+  <si>
+    <t>OT 4307 ZVN 1-9-86/2 ,Montaje Alabe</t>
+  </si>
+  <si>
+    <t>1214137717389531</t>
+  </si>
+  <si>
+    <t>OT 4307 ZVN 1-9-86/2,Recepcion Alabe,Check Planos</t>
+  </si>
+  <si>
+    <t>1214137717389532</t>
+  </si>
+  <si>
+    <t>1214137717389533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion Alabe,Check Planos,OT 4307 ZVN 1-9-86/2 </t>
+  </si>
+  <si>
+    <t>1214137717389534</t>
+  </si>
+  <si>
+    <t>1214137717389535</t>
+  </si>
+  <si>
+    <t>OT 4307 ZVN 1-9-86/2 ,Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>1214137717389536</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe,OT 4307 ZVN 1-9-86/2</t>
+  </si>
+  <si>
+    <t>1214137717389537</t>
+  </si>
+  <si>
+    <t>1214137717389538</t>
+  </si>
+  <si>
+    <t>1214137717389539</t>
+  </si>
+  <si>
+    <t>OT 4307 ZVN 1-9-86/2,Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>1214137717389540</t>
+  </si>
+  <si>
+    <t>1214137717389541</t>
+  </si>
+  <si>
+    <t>1214137717389543</t>
+  </si>
+  <si>
+    <t>1214137717389542</t>
+  </si>
+  <si>
+    <t>1214137717389544</t>
+  </si>
+  <si>
+    <t>1214137717389545</t>
+  </si>
+  <si>
+    <t>1214138844821480</t>
+  </si>
+  <si>
+    <t>Montaje Rodete</t>
+  </si>
+  <si>
+    <t>1214137717389546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion Rodete,OT 4307 ZVN 1-9-86/2 </t>
+  </si>
+  <si>
+    <t>OT 4307 ZVN 1-9-86/2 ,Montaje Rodete</t>
+  </si>
+  <si>
+    <t>1214137717389547</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete,OT 4307 ZVN 1-9-86/2</t>
+  </si>
+  <si>
+    <t>1214137717389548</t>
+  </si>
+  <si>
+    <t>1214137717389549</t>
+  </si>
+  <si>
+    <t>1214137717389550</t>
+  </si>
+  <si>
+    <t>1214137717389551</t>
+  </si>
+  <si>
+    <t>1214137717389553</t>
+  </si>
+  <si>
+    <t>1214137717389552</t>
+  </si>
+  <si>
+    <t>1214137717389554</t>
+  </si>
+  <si>
+    <t>1214137717389556</t>
+  </si>
+  <si>
+    <t>1214137717389555</t>
+  </si>
+  <si>
+    <t>1214137717389558</t>
+  </si>
+  <si>
+    <t>1214137717389557</t>
+  </si>
+  <si>
+    <t>1214137717389559</t>
+  </si>
+  <si>
+    <t>1214137717389560</t>
+  </si>
+  <si>
+    <t>1214137717389561</t>
+  </si>
+  <si>
+    <t>1214138644320347</t>
+  </si>
+  <si>
+    <t>Montaje motor</t>
+  </si>
+  <si>
+    <t>1214137717389514</t>
+  </si>
+  <si>
+    <t>Recepcion motor,Check Planos</t>
+  </si>
+  <si>
+    <t>OT 4307 ZVN 1-9-86/2 ,Montaje motor</t>
+  </si>
+  <si>
+    <t>1214137717389515</t>
+  </si>
+  <si>
+    <t>1214137717389516</t>
+  </si>
+  <si>
+    <t>OT 4307 ZVN 1-9-86/2,Recepcion motor</t>
+  </si>
+  <si>
+    <t>1214137717389517</t>
+  </si>
+  <si>
+    <t>1214137717389518</t>
+  </si>
+  <si>
+    <t>OT 4307 ZVN 1-9-86/2 ,Recepcion motor</t>
+  </si>
+  <si>
+    <t>1214137717389519</t>
+  </si>
+  <si>
+    <t>1214137717389520</t>
+  </si>
+  <si>
+    <t>1214137717389522</t>
+  </si>
+  <si>
+    <t>1214137717389521</t>
+  </si>
+  <si>
+    <t>1214137717389523</t>
+  </si>
+  <si>
+    <t>1214137717389524</t>
+  </si>
+  <si>
+    <t>1214137717389525</t>
+  </si>
+  <si>
+    <t>1214137717389526</t>
+  </si>
+  <si>
+    <t>1214137717389527</t>
+  </si>
+  <si>
+    <t>1214137717389528</t>
+  </si>
+  <si>
+    <t>1214137717389529</t>
+  </si>
+  <si>
+    <t>1214138711537176</t>
+  </si>
+  <si>
+    <t>Pruebas FAT</t>
+  </si>
+  <si>
+    <t>1214137717389562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 </t>
+  </si>
+  <si>
+    <t>OT1 4307 ZVN 1-9-86/2 ,Pruebas FAT</t>
+  </si>
+  <si>
+    <t>1214137717389563</t>
+  </si>
+  <si>
+    <t>OT2 4307 ZVN 1-9-86/2 ,Pruebas FAT</t>
+  </si>
+  <si>
+    <t>1214137717389564</t>
+  </si>
+  <si>
+    <t>OT3 4307 ZVN 1-9-86/2 ,Pruebas FAT</t>
+  </si>
+  <si>
+    <t>1214137717389565</t>
+  </si>
+  <si>
+    <t>OT4 4307 ZVN 1-9-86/2 ,Pruebas FAT</t>
+  </si>
+  <si>
+    <t>1214137717389567</t>
+  </si>
+  <si>
+    <t>OT5 4307 ZVN 1-9-86/2 ,Pruebas FAT</t>
+  </si>
+  <si>
+    <t>1214137717389566</t>
+  </si>
+  <si>
+    <t>OT6 4307 ZVN 1-9-86/2 ,Pruebas FAT</t>
+  </si>
+  <si>
+    <t>1214137717389568</t>
+  </si>
+  <si>
+    <t>OT7 4307 ZVN 1-9-86/2 ,Pruebas FAT</t>
+  </si>
+  <si>
+    <t>1214137717389569</t>
+  </si>
+  <si>
+    <t>OT8 4307  ZVN 1-9-86/2 ,Pruebas FAT</t>
+  </si>
+  <si>
+    <t>1214137717389570</t>
+  </si>
+  <si>
+    <t>OT9 4307 ZVN 1-9-86/2 ,Pruebas FAT</t>
+  </si>
+  <si>
+    <t>1214137717389571</t>
+  </si>
+  <si>
+    <t>OT10 4307 ZVN 1-9-86/2  ,Pruebas FAT</t>
+  </si>
+  <si>
+    <t>1214137717389572</t>
+  </si>
+  <si>
+    <t>OT11 4307 ZVN 1-9-86/2 ,Pruebas FAT</t>
+  </si>
+  <si>
+    <t>1214137717389573</t>
+  </si>
+  <si>
+    <t>OT12 4307 ZVN 1-9-86/2 ,Pruebas FAT</t>
+  </si>
+  <si>
+    <t>1214137717389574</t>
+  </si>
+  <si>
+    <t>OT13 4307 ZVN 1-9-86/2 ,Pruebas FAT</t>
+  </si>
+  <si>
+    <t>1214137717389575</t>
+  </si>
+  <si>
+    <t>OT14 4307 ZVN 1-9-86/2 ,Pruebas FAT</t>
+  </si>
+  <si>
+    <t>1214137717389576</t>
+  </si>
+  <si>
+    <t>OT15 4307 ZVN 1-9-86/2 ,Pruebas FAT</t>
+  </si>
+  <si>
+    <t>1214137717389577</t>
+  </si>
+  <si>
+    <t>OT16 4307 ZVN 1-9-86/2 ,Pruebas FAT</t>
+  </si>
+  <si>
+    <t>1214138801633922</t>
+  </si>
+  <si>
+    <t>RE-PINTADO</t>
+  </si>
+  <si>
+    <t>OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307  ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2</t>
+  </si>
+  <si>
+    <t>Coordinacion Entrega con Cliente,Montaje:</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1214137717389660</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT1 4307 ZVN 1-9-86/2 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4307 ZVN 1-9-86/2 </t>
-  </si>
-  <si>
-    <t>OT 4307 ZVN 1-9-86/2 ,Check pruebas FAT</t>
-  </si>
-  <si>
-    <t>1214137717389661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT2 4307 ZVN 1-9-86/2 </t>
-  </si>
-  <si>
-    <t>OT 4307 ZVN 1-9-86/2 ,Check pruebas FAT,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,OT 4347 Preparación Materiales</t>
-  </si>
-  <si>
-    <t>1214137717389662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT3 4307 ZVN 1-9-86/2 </t>
-  </si>
-  <si>
-    <t>1214137717389663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT4 4307 ZVN 1-9-86/2 </t>
-  </si>
-  <si>
-    <t>1214137717389664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT5 4307 ZVN 1-9-86/2 </t>
-  </si>
-  <si>
-    <t>1214137717389665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT6 4307 ZVN 1-9-86/2 </t>
-  </si>
-  <si>
-    <t>1214137717389666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT7 4307 ZVN 1-9-86/2 </t>
-  </si>
-  <si>
-    <t>OT 4307 ZVN 1-9-86/2 ,Check pruebas FAT,OT 4325- ZVN 1-7-63/2,OT 4327- ZVN 2-9-103/2</t>
-  </si>
-  <si>
-    <t>1214137717389667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT8 4307  ZVN 1-9-86/2 </t>
-  </si>
-  <si>
-    <t>1214137717389668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT9 4307 ZVN 1-9-86/2 </t>
-  </si>
-  <si>
-    <t>1214137717389669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT10 4307 ZVN 1-9-86/2  </t>
-  </si>
-  <si>
-    <t>1214137717389671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT11 4307 ZVN 1-9-86/2 </t>
-  </si>
-  <si>
-    <t>1214137717389672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT12 4307 ZVN 1-9-86/2 </t>
-  </si>
-  <si>
-    <t>1214137717389673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT13 4307 ZVN 1-9-86/2 </t>
-  </si>
-  <si>
-    <t>1214137717389674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT14 4307 ZVN 1-9-86/2 </t>
-  </si>
-  <si>
-    <t>1214137717389675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT15 4307 ZVN 1-9-86/2 </t>
-  </si>
-  <si>
-    <t>OT 4307  ZVN 1-9-86/2 ,Check pruebas FAT</t>
-  </si>
-  <si>
-    <t>1214137717389670</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT16 4307 ZVN 1-9-86/2 </t>
-  </si>
-  <si>
-    <t>OT 4307 ZVN 1-9-86/2,Check pruebas FAT</t>
-  </si>
-  <si>
-    <t>1214137717389712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodega </t>
-  </si>
-  <si>
-    <t>Recepcion corte laser ,Recepcion corte plasma ,Recepcion mecanizado,Control de calidad corte Laser,Control de calidad Corte plasma ,Control de calidad Mecanizado</t>
-  </si>
-  <si>
-    <t>1214137717389442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion corte laser </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad corte Laser,Bodega </t>
-  </si>
-  <si>
-    <t>1214137717389443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion corte plasma </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Corte plasma ,Bodega </t>
-  </si>
-  <si>
-    <t>1214137717389444</t>
-  </si>
-  <si>
-    <t>Recepcion mecanizado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Mecanizado,Bodega </t>
-  </si>
-  <si>
-    <t>1214137717389804</t>
-  </si>
-  <si>
-    <t>Control de calidad corte Laser</t>
-  </si>
-  <si>
-    <t>Nicolás López</t>
-  </si>
-  <si>
-    <t>nicolas.lopez@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodega ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 </t>
-  </si>
-  <si>
-    <t>1214137717389805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Corte plasma </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodega ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 </t>
-  </si>
-  <si>
-    <t>1214137717389806</t>
-  </si>
-  <si>
-    <t>Control de calidad Mecanizado</t>
-  </si>
-  <si>
-    <t>1214138801637009</t>
-  </si>
-  <si>
-    <t>Fabricación externa:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Armado,Control de calidad Armado,Generación OC Fabricación externa </t>
-  </si>
-  <si>
-    <t>1214138801637019</t>
-  </si>
-  <si>
-    <t>Rosemary Singh</t>
-  </si>
-  <si>
-    <t>rosemary.singh@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación externa:,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 </t>
-  </si>
-  <si>
-    <t>1214138711519166</t>
-  </si>
-  <si>
-    <t>Armado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 </t>
-  </si>
-  <si>
-    <t>1214137717389464</t>
-  </si>
-  <si>
-    <t>Generación OC Fabricación externa ,Control de calidad Mecanizado,Control de calidad corte Laser,Control de calidad Corte plasma ,Check Planos</t>
-  </si>
-  <si>
-    <t>OT 4307 ZVN 1-9-86/2,Armado</t>
-  </si>
-  <si>
-    <t>1214137717389465</t>
-  </si>
-  <si>
-    <t>1214137717389466</t>
-  </si>
-  <si>
-    <t>Generación OC Fabricación externa ,Control de calidad corte Laser,Control de calidad Corte plasma ,Control de calidad Mecanizado,Check Planos</t>
-  </si>
-  <si>
-    <t>Armado,OT 4307 ZVN 1-9-86/2</t>
-  </si>
-  <si>
-    <t>1214137717389467</t>
-  </si>
-  <si>
-    <t>1214137717389468</t>
-  </si>
-  <si>
-    <t>Generación OC Fabricación externa ,Control de calidad corte Laser,Control de calidad Mecanizado,Check Planos</t>
-  </si>
-  <si>
-    <t>1214137717389469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Mecanizado,Generación OC Fabricación externa ,Check Planos,Control de calidad corte Laser,Control de calidad Corte plasma </t>
-  </si>
-  <si>
-    <t>1214137717389470</t>
-  </si>
-  <si>
-    <t>Control de calidad corte Laser,Control de calidad Corte plasma ,Control de calidad Mecanizado,Generación OC Fabricación externa ,Check Planos</t>
-  </si>
-  <si>
-    <t>1214137717389471</t>
-  </si>
-  <si>
-    <t>Control de calidad Corte plasma ,Generación OC Fabricación externa ,Check Planos,Control de calidad corte Laser</t>
-  </si>
-  <si>
-    <t>1214137717389472</t>
-  </si>
-  <si>
-    <t>1214137717389473</t>
-  </si>
-  <si>
-    <t>Control de calidad corte Laser,Control de calidad Corte plasma ,Generación OC Fabricación externa ,Check Planos</t>
-  </si>
-  <si>
-    <t>1214137717389474</t>
-  </si>
-  <si>
-    <t>1214137717389475</t>
-  </si>
-  <si>
-    <t>1214137717389476</t>
-  </si>
-  <si>
-    <t>1214137717389477</t>
-  </si>
-  <si>
-    <t>Control de calidad corte Laser,Control de calidad Mecanizado,Generación OC Fabricación externa ,Check Planos</t>
-  </si>
-  <si>
-    <t>1214137717389478</t>
-  </si>
-  <si>
-    <t>OT 4307 ZVN 1-9-86/2 ,Armado</t>
-  </si>
-  <si>
-    <t>1214137717389479</t>
-  </si>
-  <si>
-    <t>1214138711519194</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2</t>
-  </si>
-  <si>
-    <t>1214137717389481</t>
-  </si>
-  <si>
-    <t>OT 4307 ZVN 1-9-86/2</t>
-  </si>
-  <si>
-    <t>OT 4307 ZVN 1-9-86/2 ,Check Planos</t>
-  </si>
-  <si>
-    <t>OT 4307 ZVN 1-9-86/2 ,Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>1214137717389482</t>
-  </si>
-  <si>
-    <t>OT 4307 ZVN 1-9-86/2,Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>1214137717389483</t>
-  </si>
-  <si>
-    <t>1214137717389484</t>
-  </si>
-  <si>
-    <t>1214137717389485</t>
-  </si>
-  <si>
-    <t>1214137717389486</t>
-  </si>
-  <si>
-    <t>1214137717389487</t>
-  </si>
-  <si>
-    <t>1214137717389488</t>
-  </si>
-  <si>
-    <t>1214137717389489</t>
-  </si>
-  <si>
-    <t>1214137717389490</t>
-  </si>
-  <si>
-    <t>1214137717389491</t>
-  </si>
-  <si>
-    <t>1214137717389492</t>
-  </si>
-  <si>
-    <t>1214137717389493</t>
-  </si>
-  <si>
-    <t>1214137717389494</t>
-  </si>
-  <si>
-    <t>1214137717389495</t>
-  </si>
-  <si>
-    <t>1214137717389497</t>
-  </si>
-  <si>
-    <t>1214138720971081</t>
-  </si>
-  <si>
-    <t>Bodega:</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete,Recepcion motor,Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>1214138844805204</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodega:,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 </t>
-  </si>
-  <si>
-    <t>1214138844805224</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete</t>
-  </si>
-  <si>
-    <t>1214138720975469</t>
-  </si>
-  <si>
-    <t>Recepcion motor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodega:,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 </t>
-  </si>
-  <si>
-    <t>1214138720975489</t>
-  </si>
-  <si>
-    <t>Montaje:</t>
-  </si>
-  <si>
-    <t>Revestimiento,Montaje motor,Montaje Rodete,RE-PINTADO,Montaje Alabe,Pruebas FAT</t>
-  </si>
-  <si>
-    <t>1214138644320327</t>
-  </si>
-  <si>
-    <t>Revestimiento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 </t>
-  </si>
-  <si>
-    <t>1214137717389498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4307 ZVN 1-9-86/2 ,Revestimiento,OT 4307 ZVN 1-9-86/2 </t>
-  </si>
-  <si>
-    <t>1214137717389499</t>
-  </si>
-  <si>
-    <t>1214137717389500</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4307 ZVN 1-9-86/2 ,Revestimiento,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 </t>
-  </si>
-  <si>
-    <t>1214137717389501</t>
-  </si>
-  <si>
-    <t>1214137717389502</t>
-  </si>
-  <si>
-    <t>1214137717389503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revestimiento,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 </t>
-  </si>
-  <si>
-    <t>1214137717389504</t>
-  </si>
-  <si>
-    <t>1214137717389505</t>
-  </si>
-  <si>
-    <t>1214137717389506</t>
-  </si>
-  <si>
-    <t>1214137717389508</t>
-  </si>
-  <si>
-    <t>1214137717389507</t>
-  </si>
-  <si>
-    <t>1214137717389509</t>
-  </si>
-  <si>
-    <t>1214137717389510</t>
-  </si>
-  <si>
-    <t>1214137717389511</t>
-  </si>
-  <si>
-    <t>1214137717389512</t>
-  </si>
-  <si>
-    <t>1214137717389513</t>
-  </si>
-  <si>
-    <t>1214138711530631</t>
-  </si>
-  <si>
-    <t>Montaje Alabe</t>
-  </si>
-  <si>
-    <t>1214137717389530</t>
-  </si>
-  <si>
-    <t>OT 4307 ZVN 1-9-86/2 ,Recepcion Alabe,Check Planos</t>
-  </si>
-  <si>
-    <t>OT 4307 ZVN 1-9-86/2 ,Montaje Alabe</t>
-  </si>
-  <si>
-    <t>1214137717389531</t>
-  </si>
-  <si>
-    <t>OT 4307 ZVN 1-9-86/2,Recepcion Alabe,Check Planos</t>
-  </si>
-  <si>
-    <t>1214137717389532</t>
-  </si>
-  <si>
-    <t>1214137717389533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion Alabe,Check Planos,OT 4307 ZVN 1-9-86/2 </t>
-  </si>
-  <si>
-    <t>1214137717389534</t>
-  </si>
-  <si>
-    <t>1214137717389535</t>
-  </si>
-  <si>
-    <t>OT 4307 ZVN 1-9-86/2 ,Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>1214137717389536</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe,OT 4307 ZVN 1-9-86/2</t>
-  </si>
-  <si>
-    <t>1214137717389537</t>
-  </si>
-  <si>
-    <t>1214137717389538</t>
-  </si>
-  <si>
-    <t>1214137717389539</t>
-  </si>
-  <si>
-    <t>OT 4307 ZVN 1-9-86/2,Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>1214137717389540</t>
-  </si>
-  <si>
-    <t>1214137717389541</t>
-  </si>
-  <si>
-    <t>1214137717389543</t>
-  </si>
-  <si>
-    <t>1214137717389542</t>
-  </si>
-  <si>
-    <t>1214137717389544</t>
-  </si>
-  <si>
-    <t>1214137717389545</t>
-  </si>
-  <si>
-    <t>1214138844821480</t>
-  </si>
-  <si>
-    <t>Montaje Rodete</t>
-  </si>
-  <si>
-    <t>1214137717389546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion Rodete,OT 4307 ZVN 1-9-86/2 </t>
-  </si>
-  <si>
-    <t>OT 4307 ZVN 1-9-86/2 ,Montaje Rodete</t>
-  </si>
-  <si>
-    <t>1214137717389547</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete,OT 4307 ZVN 1-9-86/2</t>
-  </si>
-  <si>
-    <t>1214137717389548</t>
-  </si>
-  <si>
-    <t>1214137717389549</t>
-  </si>
-  <si>
-    <t>1214137717389550</t>
-  </si>
-  <si>
-    <t>1214137717389551</t>
-  </si>
-  <si>
-    <t>1214137717389553</t>
-  </si>
-  <si>
-    <t>1214137717389552</t>
-  </si>
-  <si>
-    <t>1214137717389554</t>
-  </si>
-  <si>
-    <t>1214137717389556</t>
-  </si>
-  <si>
-    <t>1214137717389555</t>
-  </si>
-  <si>
-    <t>1214137717389558</t>
-  </si>
-  <si>
-    <t>1214137717389557</t>
-  </si>
-  <si>
-    <t>1214137717389559</t>
-  </si>
-  <si>
-    <t>1214137717389560</t>
-  </si>
-  <si>
-    <t>1214137717389561</t>
-  </si>
-  <si>
-    <t>1214138644320347</t>
-  </si>
-  <si>
-    <t>Montaje motor</t>
-  </si>
-  <si>
-    <t>1214137717389514</t>
-  </si>
-  <si>
-    <t>Recepcion motor,Check Planos</t>
-  </si>
-  <si>
-    <t>OT 4307 ZVN 1-9-86/2 ,Montaje motor</t>
-  </si>
-  <si>
-    <t>1214137717389515</t>
-  </si>
-  <si>
-    <t>1214137717389516</t>
-  </si>
-  <si>
-    <t>OT 4307 ZVN 1-9-86/2,Recepcion motor</t>
-  </si>
-  <si>
-    <t>1214137717389517</t>
-  </si>
-  <si>
-    <t>1214137717389518</t>
-  </si>
-  <si>
-    <t>OT 4307 ZVN 1-9-86/2 ,Recepcion motor</t>
-  </si>
-  <si>
-    <t>1214137717389519</t>
-  </si>
-  <si>
-    <t>1214137717389520</t>
-  </si>
-  <si>
-    <t>1214137717389522</t>
-  </si>
-  <si>
-    <t>1214137717389521</t>
-  </si>
-  <si>
-    <t>1214137717389523</t>
-  </si>
-  <si>
-    <t>1214137717389524</t>
-  </si>
-  <si>
-    <t>1214137717389525</t>
-  </si>
-  <si>
-    <t>1214137717389526</t>
-  </si>
-  <si>
-    <t>1214137717389527</t>
-  </si>
-  <si>
-    <t>1214137717389528</t>
-  </si>
-  <si>
-    <t>1214137717389529</t>
-  </si>
-  <si>
-    <t>1214138711537176</t>
-  </si>
-  <si>
-    <t>Pruebas FAT</t>
-  </si>
-  <si>
-    <t>1214137717389562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 </t>
-  </si>
-  <si>
-    <t>OT1 4307 ZVN 1-9-86/2 ,Pruebas FAT</t>
-  </si>
-  <si>
-    <t>1214137717389563</t>
-  </si>
-  <si>
-    <t>OT2 4307 ZVN 1-9-86/2 ,Pruebas FAT</t>
-  </si>
-  <si>
-    <t>1214137717389564</t>
-  </si>
-  <si>
-    <t>OT3 4307 ZVN 1-9-86/2 ,Pruebas FAT</t>
-  </si>
-  <si>
-    <t>1214137717389565</t>
-  </si>
-  <si>
-    <t>OT4 4307 ZVN 1-9-86/2 ,Pruebas FAT</t>
-  </si>
-  <si>
-    <t>1214137717389567</t>
-  </si>
-  <si>
-    <t>OT5 4307 ZVN 1-9-86/2 ,Pruebas FAT</t>
-  </si>
-  <si>
-    <t>1214137717389566</t>
-  </si>
-  <si>
-    <t>OT6 4307 ZVN 1-9-86/2 ,Pruebas FAT</t>
-  </si>
-  <si>
-    <t>1214137717389568</t>
-  </si>
-  <si>
-    <t>OT7 4307 ZVN 1-9-86/2 ,Pruebas FAT</t>
-  </si>
-  <si>
-    <t>1214137717389569</t>
-  </si>
-  <si>
-    <t>OT8 4307  ZVN 1-9-86/2 ,Pruebas FAT</t>
-  </si>
-  <si>
-    <t>1214137717389570</t>
-  </si>
-  <si>
-    <t>OT9 4307 ZVN 1-9-86/2 ,Pruebas FAT</t>
-  </si>
-  <si>
-    <t>1214137717389571</t>
-  </si>
-  <si>
-    <t>OT10 4307 ZVN 1-9-86/2  ,Pruebas FAT</t>
-  </si>
-  <si>
-    <t>1214137717389572</t>
-  </si>
-  <si>
-    <t>OT11 4307 ZVN 1-9-86/2 ,Pruebas FAT</t>
-  </si>
-  <si>
-    <t>1214137717389573</t>
-  </si>
-  <si>
-    <t>OT12 4307 ZVN 1-9-86/2 ,Pruebas FAT</t>
-  </si>
-  <si>
-    <t>1214137717389574</t>
-  </si>
-  <si>
-    <t>OT13 4307 ZVN 1-9-86/2 ,Pruebas FAT</t>
-  </si>
-  <si>
-    <t>1214137717389575</t>
-  </si>
-  <si>
-    <t>OT14 4307 ZVN 1-9-86/2 ,Pruebas FAT</t>
-  </si>
-  <si>
-    <t>1214137717389576</t>
-  </si>
-  <si>
-    <t>OT15 4307 ZVN 1-9-86/2 ,Pruebas FAT</t>
-  </si>
-  <si>
-    <t>1214137717389577</t>
-  </si>
-  <si>
-    <t>OT16 4307 ZVN 1-9-86/2 ,Pruebas FAT</t>
-  </si>
-  <si>
-    <t>1214138801633922</t>
-  </si>
-  <si>
-    <t>RE-PINTADO</t>
-  </si>
-  <si>
-    <t>OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307  ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2</t>
-  </si>
-  <si>
-    <t>Coordinacion Entrega con Cliente,Montaje:</t>
   </si>
   <si>
     <t>1214137717389578</t>
@@ -4857,7 +4857,7 @@
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46224.167821111114</v>
+        <v>46225.18671469907</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>165</v>
@@ -4899,8 +4899,8 @@
       <c r="R46" s="5">
         <v>46224</v>
       </c>
-      <c r="S46" s="12" t="s">
-        <v>169</v>
+      <c r="S46" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T46" s="6">
         <v>0</v>
@@ -4911,7 +4911,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B47" s="8">
         <v>46132.634550902774</v>
@@ -4921,7 +4921,7 @@
         <v>46224.1677925463</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
@@ -4949,10 +4949,10 @@
         <v>165</v>
       </c>
       <c r="O47" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="P47" s="9" t="s">
         <v>172</v>
-      </c>
-      <c r="P47" s="9" t="s">
-        <v>173</v>
       </c>
       <c r="Q47" s="9"/>
       <c r="R47" s="9"/>
@@ -4962,7 +4962,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B48" s="5">
         <v>46132.634558564816</v>
@@ -4972,7 +4972,7 @@
         <v>46224.16779487269</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
@@ -5000,10 +5000,10 @@
         <v>165</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -5013,7 +5013,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B49" s="8">
         <v>46132.634567546294</v>
@@ -5023,7 +5023,7 @@
         <v>46224.167796215275</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
@@ -5051,10 +5051,10 @@
         <v>165</v>
       </c>
       <c r="O49" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="P49" s="9" t="s">
         <v>172</v>
-      </c>
-      <c r="P49" s="9" t="s">
-        <v>173</v>
       </c>
       <c r="Q49" s="9"/>
       <c r="R49" s="9"/>
@@ -5064,7 +5064,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B50" s="5">
         <v>46132.634571875</v>
@@ -5074,7 +5074,7 @@
         <v>46224.1677978125</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
@@ -5102,10 +5102,10 @@
         <v>165</v>
       </c>
       <c r="O50" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="P50" s="6" t="s">
         <v>172</v>
-      </c>
-      <c r="P50" s="6" t="s">
-        <v>173</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -5115,7 +5115,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B51" s="8">
         <v>46132.6345777199</v>
@@ -5125,7 +5125,7 @@
         <v>46224.16779921296</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
@@ -5153,10 +5153,10 @@
         <v>165</v>
       </c>
       <c r="O51" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="P51" s="9" t="s">
         <v>172</v>
-      </c>
-      <c r="P51" s="9" t="s">
-        <v>173</v>
       </c>
       <c r="Q51" s="9"/>
       <c r="R51" s="9"/>
@@ -5166,7 +5166,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B52" s="5">
         <v>46132.634582071754</v>
@@ -5176,7 +5176,7 @@
         <v>46224.167800717594</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
@@ -5204,10 +5204,10 @@
         <v>165</v>
       </c>
       <c r="O52" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="P52" s="6" t="s">
         <v>172</v>
-      </c>
-      <c r="P52" s="6" t="s">
-        <v>173</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -5217,7 +5217,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B53" s="8">
         <v>46132.63458603009</v>
@@ -5227,7 +5227,7 @@
         <v>46224.16780229167</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
@@ -5255,10 +5255,10 @@
         <v>165</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
@@ -5268,7 +5268,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B54" s="5">
         <v>46132.63459168981</v>
@@ -5278,7 +5278,7 @@
         <v>46224.167803668985</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
@@ -5306,10 +5306,10 @@
         <v>165</v>
       </c>
       <c r="O54" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="P54" s="6" t="s">
         <v>172</v>
-      </c>
-      <c r="P54" s="6" t="s">
-        <v>173</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -5319,7 +5319,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B55" s="8">
         <v>46132.634597094904</v>
@@ -5329,7 +5329,7 @@
         <v>46224.16780512732</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
@@ -5357,10 +5357,10 @@
         <v>165</v>
       </c>
       <c r="O55" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="P55" s="9" t="s">
         <v>172</v>
-      </c>
-      <c r="P55" s="9" t="s">
-        <v>173</v>
       </c>
       <c r="Q55" s="9"/>
       <c r="R55" s="9"/>
@@ -5370,7 +5370,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B56" s="5">
         <v>46132.6346025463</v>
@@ -5380,7 +5380,7 @@
         <v>46224.16780649306</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
@@ -5408,10 +5408,10 @@
         <v>165</v>
       </c>
       <c r="O56" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="P56" s="6" t="s">
         <v>172</v>
-      </c>
-      <c r="P56" s="6" t="s">
-        <v>173</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -5421,7 +5421,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B57" s="8">
         <v>46132.634674050925</v>
@@ -5431,7 +5431,7 @@
         <v>46224.167809293984</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
@@ -5459,10 +5459,10 @@
         <v>165</v>
       </c>
       <c r="O57" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="P57" s="9" t="s">
         <v>172</v>
-      </c>
-      <c r="P57" s="9" t="s">
-        <v>173</v>
       </c>
       <c r="Q57" s="9"/>
       <c r="R57" s="9"/>
@@ -5472,7 +5472,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B58" s="5">
         <v>46132.63468899306</v>
@@ -5482,7 +5482,7 @@
         <v>46224.167810625004</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
@@ -5510,10 +5510,10 @@
         <v>165</v>
       </c>
       <c r="O58" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="P58" s="6" t="s">
         <v>172</v>
-      </c>
-      <c r="P58" s="6" t="s">
-        <v>173</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -5523,7 +5523,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B59" s="8">
         <v>46132.63470766204</v>
@@ -5533,7 +5533,7 @@
         <v>46224.16781208334</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
@@ -5561,10 +5561,10 @@
         <v>165</v>
       </c>
       <c r="O59" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="P59" s="9" t="s">
         <v>172</v>
-      </c>
-      <c r="P59" s="9" t="s">
-        <v>173</v>
       </c>
       <c r="Q59" s="9"/>
       <c r="R59" s="9"/>
@@ -5574,7 +5574,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B60" s="5">
         <v>46132.634719884256</v>
@@ -5584,7 +5584,7 @@
         <v>46224.16781392361</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
@@ -5612,10 +5612,10 @@
         <v>165</v>
       </c>
       <c r="O60" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="P60" s="6" t="s">
         <v>172</v>
-      </c>
-      <c r="P60" s="6" t="s">
-        <v>173</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5625,7 +5625,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B61" s="8">
         <v>46132.634727847224</v>
@@ -5635,7 +5635,7 @@
         <v>46224.16781546296</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
@@ -5663,10 +5663,10 @@
         <v>165</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Q61" s="9"/>
       <c r="R61" s="9"/>
@@ -5676,7 +5676,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B62" s="5">
         <v>46132.63460722222</v>
@@ -5686,7 +5686,7 @@
         <v>46224.16780783565</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
@@ -5714,10 +5714,10 @@
         <v>165</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5727,7 +5727,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B63" s="8">
         <v>46132.64721917824</v>
@@ -5739,7 +5739,7 @@
         <v>46157.493989166665</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>25</v>
@@ -5763,7 +5763,7 @@
         <v>26</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="P63" s="9" t="s">
         <v>26</v>
@@ -5780,7 +5780,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B64" s="5">
         <v>46132.624842916666</v>
@@ -5792,7 +5792,7 @@
         <v>46182.18354462963</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
@@ -5819,13 +5819,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="O64" s="6" t="s">
         <v>130</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q64" s="5">
         <v>46181</v>
@@ -5845,7 +5845,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B65" s="8">
         <v>46132.62490728009</v>
@@ -5857,7 +5857,7 @@
         <v>46182.18354459491</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
@@ -5884,13 +5884,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="O65" s="9" t="s">
         <v>138</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="Q65" s="8">
         <v>46181</v>
@@ -5910,7 +5910,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B66" s="5">
         <v>46132.62495362268</v>
@@ -5922,7 +5922,7 @@
         <v>46182.183544768515</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
@@ -5949,13 +5949,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="O66" s="6" t="s">
         <v>146</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Q66" s="5">
         <v>46181</v>
@@ -5975,7 +5975,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B67" s="8">
         <v>46132.70742302084</v>
@@ -5987,16 +5987,16 @@
         <v>46184.203094386576</v>
       </c>
       <c r="E67" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="F67" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G67" s="9" t="s">
         <v>221</v>
       </c>
-      <c r="F67" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G67" s="9" t="s">
+      <c r="H67" s="9" t="s">
         <v>222</v>
-      </c>
-      <c r="H67" s="9" t="s">
-        <v>223</v>
       </c>
       <c r="I67" s="8">
         <v>46182</v>
@@ -6014,13 +6014,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="Q67" s="8">
         <v>46183</v>
@@ -6040,7 +6040,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B68" s="5">
         <v>46132.70752974537</v>
@@ -6052,16 +6052,16 @@
         <v>46184.20309802084</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="H68" s="6" t="s">
         <v>222</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>223</v>
       </c>
       <c r="I68" s="5">
         <v>46182</v>
@@ -6079,13 +6079,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Q68" s="5">
         <v>46183</v>
@@ -6105,7 +6105,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B69" s="8">
         <v>46132.70760050926</v>
@@ -6117,16 +6117,16 @@
         <v>46184.203094212964</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="H69" s="9" t="s">
         <v>222</v>
-      </c>
-      <c r="H69" s="9" t="s">
-        <v>223</v>
       </c>
       <c r="I69" s="8">
         <v>46182</v>
@@ -6144,13 +6144,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Q69" s="8">
         <v>46183</v>
@@ -6170,7 +6170,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B70" s="5">
         <v>46132.58888190972</v>
@@ -6182,7 +6182,7 @@
         <v>46209.6327872338</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>25</v>
@@ -6206,7 +6206,7 @@
         <v>26</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>26</v>
@@ -6223,7 +6223,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B71" s="8">
         <v>46132.588885185185</v>
@@ -6241,10 +6241,10 @@
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="H71" s="9" t="s">
         <v>234</v>
-      </c>
-      <c r="H71" s="9" t="s">
-        <v>235</v>
       </c>
       <c r="I71" s="8">
         <v>46169</v>
@@ -6262,13 +6262,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="O71" s="9" t="s">
         <v>77</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="Q71" s="8">
         <v>46147</v>
@@ -6288,7 +6288,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B72" s="5">
         <v>46132.58889042824</v>
@@ -6300,16 +6300,16 @@
         <v>46207.18038831018</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="H72" s="6" t="s">
         <v>234</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>235</v>
       </c>
       <c r="I72" s="5">
         <v>46184</v>
@@ -6327,13 +6327,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="Q72" s="5">
         <v>46206</v>
@@ -6353,7 +6353,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B73" s="8">
         <v>46132.631278472225</v>
@@ -6365,16 +6365,16 @@
         <v>46196.69266049768</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="H73" s="9" t="s">
         <v>234</v>
-      </c>
-      <c r="H73" s="9" t="s">
-        <v>235</v>
       </c>
       <c r="I73" s="8">
         <v>46184</v>
@@ -6392,13 +6392,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="O73" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="P73" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="P73" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="Q73" s="9"/>
       <c r="R73" s="9"/>
@@ -6408,7 +6408,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B74" s="5">
         <v>46132.63129450232</v>
@@ -6420,16 +6420,16 @@
         <v>46196.692844907404</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="H74" s="6" t="s">
         <v>234</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>235</v>
       </c>
       <c r="I74" s="5">
         <v>46184</v>
@@ -6447,13 +6447,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="O74" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="P74" s="6" t="s">
         <v>241</v>
-      </c>
-      <c r="P74" s="6" t="s">
-        <v>242</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6463,7 +6463,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B75" s="8">
         <v>46132.63130252315</v>
@@ -6475,16 +6475,16 @@
         <v>46196.69317986111</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="H75" s="9" t="s">
         <v>234</v>
-      </c>
-      <c r="H75" s="9" t="s">
-        <v>235</v>
       </c>
       <c r="I75" s="8">
         <v>46184</v>
@@ -6502,13 +6502,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="O75" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="P75" s="9" t="s">
         <v>245</v>
-      </c>
-      <c r="P75" s="9" t="s">
-        <v>246</v>
       </c>
       <c r="Q75" s="9"/>
       <c r="R75" s="9"/>
@@ -6518,7 +6518,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B76" s="5">
         <v>46132.63130869213</v>
@@ -6530,16 +6530,16 @@
         <v>46196.693142592594</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="H76" s="6" t="s">
         <v>234</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>235</v>
       </c>
       <c r="I76" s="5">
         <v>46184</v>
@@ -6557,13 +6557,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="O76" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="P76" s="6" t="s">
         <v>241</v>
-      </c>
-      <c r="P76" s="6" t="s">
-        <v>242</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6573,7 +6573,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B77" s="8">
         <v>46132.631314467595</v>
@@ -6585,16 +6585,16 @@
         <v>46196.693131458334</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="H77" s="9" t="s">
         <v>234</v>
-      </c>
-      <c r="H77" s="9" t="s">
-        <v>235</v>
       </c>
       <c r="I77" s="8">
         <v>46184</v>
@@ -6612,13 +6612,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q77" s="9"/>
       <c r="R77" s="9"/>
@@ -6628,7 +6628,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B78" s="5">
         <v>46132.6313205787</v>
@@ -6640,16 +6640,16 @@
         <v>46196.693120717595</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="H78" s="6" t="s">
         <v>234</v>
-      </c>
-      <c r="H78" s="6" t="s">
-        <v>235</v>
       </c>
       <c r="I78" s="5">
         <v>46184</v>
@@ -6667,13 +6667,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6683,7 +6683,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B79" s="8">
         <v>46132.6313259375</v>
@@ -6695,16 +6695,16 @@
         <v>46196.69310042824</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="H79" s="9" t="s">
         <v>234</v>
-      </c>
-      <c r="H79" s="9" t="s">
-        <v>235</v>
       </c>
       <c r="I79" s="8">
         <v>46184</v>
@@ -6722,13 +6722,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q79" s="9"/>
       <c r="R79" s="9"/>
@@ -6738,7 +6738,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B80" s="5">
         <v>46132.63133041667</v>
@@ -6750,16 +6750,16 @@
         <v>46196.693085949075</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="H80" s="6" t="s">
         <v>234</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>235</v>
       </c>
       <c r="I80" s="5">
         <v>46184</v>
@@ -6777,13 +6777,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6793,7 +6793,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B81" s="8">
         <v>46132.63133645833</v>
@@ -6805,16 +6805,16 @@
         <v>46196.69307368055</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="H81" s="9" t="s">
         <v>234</v>
-      </c>
-      <c r="H81" s="9" t="s">
-        <v>235</v>
       </c>
       <c r="I81" s="8">
         <v>46184</v>
@@ -6832,13 +6832,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q81" s="9"/>
       <c r="R81" s="9"/>
@@ -6848,7 +6848,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B82" s="5">
         <v>46132.63134074074</v>
@@ -6860,16 +6860,16 @@
         <v>46196.69306041667</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="H82" s="6" t="s">
         <v>234</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>235</v>
       </c>
       <c r="I82" s="5">
         <v>46184</v>
@@ -6887,13 +6887,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6903,7 +6903,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B83" s="8">
         <v>46132.631346469905</v>
@@ -6915,16 +6915,16 @@
         <v>46196.693049560185</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="H83" s="9" t="s">
         <v>234</v>
-      </c>
-      <c r="H83" s="9" t="s">
-        <v>235</v>
       </c>
       <c r="I83" s="8">
         <v>46184</v>
@@ -6942,13 +6942,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q83" s="9"/>
       <c r="R83" s="9"/>
@@ -6958,7 +6958,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B84" s="5">
         <v>46132.631352083336</v>
@@ -6970,16 +6970,16 @@
         <v>46196.6930421412</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="H84" s="6" t="s">
         <v>234</v>
-      </c>
-      <c r="H84" s="6" t="s">
-        <v>235</v>
       </c>
       <c r="I84" s="5">
         <v>46184</v>
@@ -6997,13 +6997,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -7013,7 +7013,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B85" s="8">
         <v>46132.63135776621</v>
@@ -7025,16 +7025,16 @@
         <v>46196.69303037037</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="H85" s="9" t="s">
         <v>234</v>
-      </c>
-      <c r="H85" s="9" t="s">
-        <v>235</v>
       </c>
       <c r="I85" s="8">
         <v>46184</v>
@@ -7052,13 +7052,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q85" s="9"/>
       <c r="R85" s="9"/>
@@ -7068,7 +7068,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B86" s="5">
         <v>46132.63136296296</v>
@@ -7080,16 +7080,16 @@
         <v>46196.69302122685</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="H86" s="6" t="s">
         <v>234</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>235</v>
       </c>
       <c r="I86" s="5">
         <v>46184</v>
@@ -7107,13 +7107,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -7123,7 +7123,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B87" s="8">
         <v>46132.63136688658</v>
@@ -7135,16 +7135,16 @@
         <v>46196.692995543985</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="H87" s="9" t="s">
         <v>234</v>
-      </c>
-      <c r="H87" s="9" t="s">
-        <v>235</v>
       </c>
       <c r="I87" s="8">
         <v>46184</v>
@@ -7162,13 +7162,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="P87" s="9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q87" s="9"/>
       <c r="R87" s="9"/>
@@ -7178,7 +7178,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B88" s="5">
         <v>46132.63137239583</v>
@@ -7190,16 +7190,16 @@
         <v>46196.69300998843</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="H88" s="6" t="s">
         <v>234</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>235</v>
       </c>
       <c r="I88" s="5">
         <v>46184</v>
@@ -7217,13 +7217,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -7233,7 +7233,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B89" s="8">
         <v>46132.58889809028</v>
@@ -7245,16 +7245,16 @@
         <v>46211.16681866898</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="H89" s="9" t="s">
         <v>222</v>
-      </c>
-      <c r="H89" s="9" t="s">
-        <v>223</v>
       </c>
       <c r="I89" s="8">
         <v>46209</v>
@@ -7272,13 +7272,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="Q89" s="8">
         <v>46210</v>
@@ -7298,7 +7298,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B90" s="5">
         <v>46132.63147894676</v>
@@ -7310,16 +7310,16 @@
         <v>46196.913305381946</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="H90" s="6" t="s">
         <v>222</v>
-      </c>
-      <c r="H90" s="6" t="s">
-        <v>223</v>
       </c>
       <c r="I90" s="5">
         <v>46209</v>
@@ -7337,13 +7337,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="O90" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="P90" s="6" t="s">
         <v>272</v>
-      </c>
-      <c r="P90" s="6" t="s">
-        <v>273</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -7353,7 +7353,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B91" s="8">
         <v>46132.63149082176</v>
@@ -7365,16 +7365,16 @@
         <v>46196.9133102662</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="H91" s="9" t="s">
         <v>222</v>
-      </c>
-      <c r="H91" s="9" t="s">
-        <v>223</v>
       </c>
       <c r="I91" s="8">
         <v>46209</v>
@@ -7392,13 +7392,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="Q91" s="9"/>
       <c r="R91" s="9"/>
@@ -7408,7 +7408,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B92" s="5">
         <v>46132.63149714121</v>
@@ -7420,16 +7420,16 @@
         <v>46196.91331809028</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="H92" s="6" t="s">
         <v>222</v>
-      </c>
-      <c r="H92" s="6" t="s">
-        <v>223</v>
       </c>
       <c r="I92" s="5">
         <v>46209</v>
@@ -7447,13 +7447,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -7463,7 +7463,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B93" s="8">
         <v>46132.63150280093</v>
@@ -7475,16 +7475,16 @@
         <v>46196.91332601852</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="H93" s="9" t="s">
         <v>222</v>
-      </c>
-      <c r="H93" s="9" t="s">
-        <v>223</v>
       </c>
       <c r="I93" s="8">
         <v>46209</v>
@@ -7502,13 +7502,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="O93" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="P93" s="9" t="s">
         <v>272</v>
-      </c>
-      <c r="P93" s="9" t="s">
-        <v>273</v>
       </c>
       <c r="Q93" s="9"/>
       <c r="R93" s="9"/>
@@ -7518,7 +7518,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B94" s="5">
         <v>46132.63150895834</v>
@@ -7530,16 +7530,16 @@
         <v>46196.91333064815</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="H94" s="6" t="s">
         <v>222</v>
-      </c>
-      <c r="H94" s="6" t="s">
-        <v>223</v>
       </c>
       <c r="I94" s="5">
         <v>46209</v>
@@ -7557,13 +7557,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="O94" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="P94" s="6" t="s">
         <v>272</v>
-      </c>
-      <c r="P94" s="6" t="s">
-        <v>273</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7573,7 +7573,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B95" s="8">
         <v>46132.63151432871</v>
@@ -7585,16 +7585,16 @@
         <v>46196.91333818287</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="H95" s="9" t="s">
         <v>222</v>
-      </c>
-      <c r="H95" s="9" t="s">
-        <v>223</v>
       </c>
       <c r="I95" s="8">
         <v>46209</v>
@@ -7612,13 +7612,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="O95" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="P95" s="9" t="s">
         <v>272</v>
-      </c>
-      <c r="P95" s="9" t="s">
-        <v>273</v>
       </c>
       <c r="Q95" s="9"/>
       <c r="R95" s="9"/>
@@ -7628,7 +7628,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B96" s="5">
         <v>46132.631519525465</v>
@@ -7640,16 +7640,16 @@
         <v>46196.91334849537</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="H96" s="6" t="s">
         <v>222</v>
-      </c>
-      <c r="H96" s="6" t="s">
-        <v>223</v>
       </c>
       <c r="I96" s="5">
         <v>46209</v>
@@ -7667,13 +7667,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7683,7 +7683,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B97" s="8">
         <v>46132.631524247685</v>
@@ -7695,16 +7695,16 @@
         <v>46196.91335584491</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="H97" s="9" t="s">
         <v>222</v>
-      </c>
-      <c r="H97" s="9" t="s">
-        <v>223</v>
       </c>
       <c r="I97" s="8">
         <v>46209</v>
@@ -7722,13 +7722,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="O97" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="P97" s="9" t="s">
         <v>272</v>
-      </c>
-      <c r="P97" s="9" t="s">
-        <v>273</v>
       </c>
       <c r="Q97" s="9"/>
       <c r="R97" s="9"/>
@@ -7738,7 +7738,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B98" s="5">
         <v>46132.63153150463</v>
@@ -7750,16 +7750,16 @@
         <v>46196.913360879626</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="H98" s="6" t="s">
         <v>222</v>
-      </c>
-      <c r="H98" s="6" t="s">
-        <v>223</v>
       </c>
       <c r="I98" s="5">
         <v>46209</v>
@@ -7777,13 +7777,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="O98" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="P98" s="6" t="s">
         <v>272</v>
-      </c>
-      <c r="P98" s="6" t="s">
-        <v>273</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7793,7 +7793,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B99" s="8">
         <v>46132.631539270835</v>
@@ -7805,16 +7805,16 @@
         <v>46196.913369456015</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="H99" s="9" t="s">
         <v>222</v>
-      </c>
-      <c r="H99" s="9" t="s">
-        <v>223</v>
       </c>
       <c r="I99" s="8">
         <v>46209</v>
@@ -7832,13 +7832,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="P99" s="9" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="Q99" s="9"/>
       <c r="R99" s="9"/>
@@ -7848,7 +7848,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B100" s="5">
         <v>46132.63154616898</v>
@@ -7860,16 +7860,16 @@
         <v>46196.91338305555</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="H100" s="6" t="s">
         <v>222</v>
-      </c>
-      <c r="H100" s="6" t="s">
-        <v>223</v>
       </c>
       <c r="I100" s="5">
         <v>46209</v>
@@ -7887,13 +7887,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="O100" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="P100" s="6" t="s">
         <v>272</v>
-      </c>
-      <c r="P100" s="6" t="s">
-        <v>273</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7903,7 +7903,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B101" s="8">
         <v>46132.63155506944</v>
@@ -7915,16 +7915,16 @@
         <v>46196.91339189815</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="H101" s="9" t="s">
         <v>222</v>
-      </c>
-      <c r="H101" s="9" t="s">
-        <v>223</v>
       </c>
       <c r="I101" s="8">
         <v>46209</v>
@@ -7942,13 +7942,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="O101" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="P101" s="9" t="s">
         <v>272</v>
-      </c>
-      <c r="P101" s="9" t="s">
-        <v>273</v>
       </c>
       <c r="Q101" s="9"/>
       <c r="R101" s="9"/>
@@ -7958,7 +7958,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B102" s="5">
         <v>46132.63156422453</v>
@@ -7970,16 +7970,16 @@
         <v>46196.91339939815</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="H102" s="6" t="s">
         <v>222</v>
-      </c>
-      <c r="H102" s="6" t="s">
-        <v>223</v>
       </c>
       <c r="I102" s="5">
         <v>46209</v>
@@ -7997,13 +7997,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="O102" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="P102" s="6" t="s">
         <v>272</v>
-      </c>
-      <c r="P102" s="6" t="s">
-        <v>273</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -8013,7 +8013,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B103" s="8">
         <v>46132.63157251157</v>
@@ -8025,16 +8025,16 @@
         <v>46209.63248512732</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="H103" s="9" t="s">
         <v>222</v>
-      </c>
-      <c r="H103" s="9" t="s">
-        <v>223</v>
       </c>
       <c r="I103" s="8">
         <v>46209</v>
@@ -8052,13 +8052,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="9" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="O103" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="P103" s="9" t="s">
         <v>272</v>
-      </c>
-      <c r="P103" s="9" t="s">
-        <v>273</v>
       </c>
       <c r="Q103" s="9"/>
       <c r="R103" s="9"/>
@@ -8068,7 +8068,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B104" s="5">
         <v>46132.631576643515</v>
@@ -8080,16 +8080,16 @@
         <v>46209.63249092593</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="H104" s="6" t="s">
         <v>222</v>
-      </c>
-      <c r="H104" s="6" t="s">
-        <v>223</v>
       </c>
       <c r="I104" s="5">
         <v>46209</v>
@@ -8107,13 +8107,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="O104" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="P104" s="6" t="s">
         <v>272</v>
-      </c>
-      <c r="P104" s="6" t="s">
-        <v>273</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -8123,7 +8123,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B105" s="8">
         <v>46132.6319078588</v>
@@ -8135,16 +8135,16 @@
         <v>46209.63249679398</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="H105" s="9" t="s">
         <v>222</v>
-      </c>
-      <c r="H105" s="9" t="s">
-        <v>223</v>
       </c>
       <c r="I105" s="8">
         <v>46209</v>
@@ -8162,13 +8162,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="9" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="O105" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="P105" s="9" t="s">
         <v>272</v>
-      </c>
-      <c r="P105" s="9" t="s">
-        <v>273</v>
       </c>
       <c r="Q105" s="9"/>
       <c r="R105" s="9"/>
@@ -8178,7 +8178,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B106" s="5">
         <v>46132.58890393519</v>
@@ -8190,7 +8190,7 @@
         <v>46198.65523800926</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>25</v>
@@ -8214,7 +8214,7 @@
         <v>26</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="P106" s="6" t="s">
         <v>26</v>
@@ -8231,7 +8231,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B107" s="8">
         <v>46132.58890717593</v>
@@ -8243,7 +8243,7 @@
         <v>46198.65511907407</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
@@ -8268,13 +8268,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="9" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="O107" s="9" t="s">
         <v>98</v>
       </c>
       <c r="P107" s="9" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="Q107" s="8">
         <v>46146</v>
@@ -8294,7 +8294,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B108" s="5">
         <v>46132.58891280093</v>
@@ -8306,7 +8306,7 @@
         <v>46163.18906322916</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -8331,13 +8331,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="O108" s="6" t="s">
         <v>107</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="Q108" s="5">
         <v>46162</v>
@@ -8357,7 +8357,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B109" s="8">
         <v>46132.588918090274</v>
@@ -8369,7 +8369,7 @@
         <v>46198.65526501158</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>26</v>
@@ -8394,13 +8394,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="9" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="O109" s="9" t="s">
         <v>117</v>
       </c>
       <c r="P109" s="9" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="Q109" s="8">
         <v>46176</v>
@@ -8420,7 +8420,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B110" s="5">
         <v>46132.58892311342</v>
@@ -8430,7 +8430,7 @@
         <v>46205.491523854165</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>25</v>
@@ -8454,7 +8454,7 @@
         <v>26</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>26</v>
@@ -8467,7 +8467,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B111" s="8">
         <v>46132.58892658565</v>
@@ -8479,7 +8479,7 @@
         <v>46223.603908819445</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
@@ -8506,13 +8506,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="9" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P111" s="9" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="Q111" s="8">
         <v>46217</v>
@@ -8532,7 +8532,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B112" s="5">
         <v>46132.632033182876</v>
@@ -8544,7 +8544,7 @@
         <v>46223.603719872684</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8571,13 +8571,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8587,7 +8587,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B113" s="8">
         <v>46132.6321053125</v>
@@ -8599,7 +8599,7 @@
         <v>46223.60371622685</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
@@ -8626,13 +8626,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="9" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="P113" s="9" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="Q113" s="9"/>
       <c r="R113" s="9"/>
@@ -8642,7 +8642,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B114" s="5">
         <v>46132.63211394676</v>
@@ -8654,7 +8654,7 @@
         <v>46223.60371229167</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
@@ -8681,13 +8681,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -8697,7 +8697,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B115" s="8">
         <v>46132.6321221875</v>
@@ -8709,7 +8709,7 @@
         <v>46223.60370868056</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>26</v>
@@ -8736,13 +8736,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="9" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="O115" s="9" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="P115" s="9" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="Q115" s="9"/>
       <c r="R115" s="9"/>
@@ -8752,7 +8752,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B116" s="5">
         <v>46132.63212829861</v>
@@ -8764,7 +8764,7 @@
         <v>46223.60370479166</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8791,13 +8791,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8807,7 +8807,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B117" s="8">
         <v>46132.63213525463</v>
@@ -8819,7 +8819,7 @@
         <v>46223.60370101852</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
@@ -8846,13 +8846,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="9" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="O117" s="9" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="P117" s="9" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="Q117" s="9"/>
       <c r="R117" s="9"/>
@@ -8862,7 +8862,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B118" s="5">
         <v>46132.63214342593</v>
@@ -8874,7 +8874,7 @@
         <v>46223.603697303246</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -8901,13 +8901,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8917,7 +8917,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B119" s="8">
         <v>46132.63215114584</v>
@@ -8929,7 +8929,7 @@
         <v>46223.603693564815</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>26</v>
@@ -8956,13 +8956,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="9" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="O119" s="9" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="P119" s="9" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="Q119" s="9"/>
       <c r="R119" s="9"/>
@@ -8972,7 +8972,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B120" s="5">
         <v>46132.63216016204</v>
@@ -8984,7 +8984,7 @@
         <v>46223.603689456024</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -9011,13 +9011,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -9027,7 +9027,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B121" s="8">
         <v>46132.6321746412</v>
@@ -9039,7 +9039,7 @@
         <v>46223.603685821756</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>26</v>
@@ -9066,13 +9066,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="9" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="O121" s="9" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="P121" s="9" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="Q121" s="9"/>
       <c r="R121" s="9"/>
@@ -9082,7 +9082,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B122" s="5">
         <v>46132.63216719907</v>
@@ -9094,7 +9094,7 @@
         <v>46223.60368157407</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -9121,13 +9121,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -9137,7 +9137,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B123" s="8">
         <v>46132.63218074074</v>
@@ -9149,7 +9149,7 @@
         <v>46223.60367759259</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>26</v>
@@ -9176,13 +9176,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="9" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="O123" s="9" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="P123" s="9" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="Q123" s="9"/>
       <c r="R123" s="9"/>
@@ -9192,7 +9192,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B124" s="5">
         <v>46132.632186863426</v>
@@ -9204,7 +9204,7 @@
         <v>46223.60367399306</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -9231,13 +9231,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -9247,7 +9247,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B125" s="8">
         <v>46132.63219409723</v>
@@ -9259,7 +9259,7 @@
         <v>46223.60366275463</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>26</v>
@@ -9286,13 +9286,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="9" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="O125" s="9" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="P125" s="9" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="Q125" s="9"/>
       <c r="R125" s="9"/>
@@ -9302,7 +9302,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B126" s="5">
         <v>46132.63220086806</v>
@@ -9314,7 +9314,7 @@
         <v>46223.603662141206</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
@@ -9341,13 +9341,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -9357,7 +9357,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B127" s="8">
         <v>46132.63220734954</v>
@@ -9369,7 +9369,7 @@
         <v>46223.60366150463</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>26</v>
@@ -9396,13 +9396,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="9" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="O127" s="9" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="P127" s="9" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="Q127" s="9"/>
       <c r="R127" s="9"/>
@@ -9412,7 +9412,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B128" s="5">
         <v>46132.58893864583</v>
@@ -9422,7 +9422,7 @@
         <v>46223.60390307871</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
@@ -9447,13 +9447,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="Q128" s="5">
         <v>46218</v>
@@ -9473,7 +9473,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B129" s="8">
         <v>46132.63296805556</v>
@@ -9485,7 +9485,7 @@
         <v>46223.55793672454</v>
       </c>
       <c r="E129" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>26</v>
@@ -9510,13 +9510,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="9" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="O129" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="P129" s="9" t="s">
         <v>329</v>
-      </c>
-      <c r="P129" s="9" t="s">
-        <v>330</v>
       </c>
       <c r="Q129" s="9"/>
       <c r="R129" s="9"/>
@@ -9526,7 +9526,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B130" s="5">
         <v>46132.63297954861</v>
@@ -9538,7 +9538,7 @@
         <v>46223.557933055556</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
@@ -9563,13 +9563,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -9579,7 +9579,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B131" s="8">
         <v>46132.63298759259</v>
@@ -9591,7 +9591,7 @@
         <v>46223.5579291551</v>
       </c>
       <c r="E131" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F131" s="9" t="s">
         <v>26</v>
@@ -9616,13 +9616,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="9" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="O131" s="9" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="P131" s="9" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="Q131" s="9"/>
       <c r="R131" s="9"/>
@@ -9632,7 +9632,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B132" s="5">
         <v>46132.63299327546</v>
@@ -9644,7 +9644,7 @@
         <v>46223.55792547454</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
@@ -9669,13 +9669,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9685,7 +9685,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B133" s="8">
         <v>46132.63299994213</v>
@@ -9697,7 +9697,7 @@
         <v>46223.557921562504</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>26</v>
@@ -9722,13 +9722,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="9" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="O133" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="P133" s="9" t="s">
         <v>329</v>
-      </c>
-      <c r="P133" s="9" t="s">
-        <v>330</v>
       </c>
       <c r="Q133" s="9"/>
       <c r="R133" s="9"/>
@@ -9738,7 +9738,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B134" s="5">
         <v>46132.63300702546</v>
@@ -9748,7 +9748,7 @@
         <v>46223.55789310185</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
@@ -9773,13 +9773,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9789,7 +9789,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B135" s="8">
         <v>46132.633012708335</v>
@@ -9799,7 +9799,7 @@
         <v>46223.55789246528</v>
       </c>
       <c r="E135" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F135" s="9" t="s">
         <v>26</v>
@@ -9824,13 +9824,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="9" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="O135" s="9" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="P135" s="9" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="Q135" s="9"/>
       <c r="R135" s="9"/>
@@ -9840,7 +9840,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B136" s="5">
         <v>46132.63302</v>
@@ -9850,7 +9850,7 @@
         <v>46223.557891874996</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
@@ -9875,13 +9875,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9891,7 +9891,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B137" s="8">
         <v>46132.63302648148</v>
@@ -9901,7 +9901,7 @@
         <v>46223.557891296296</v>
       </c>
       <c r="E137" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F137" s="9" t="s">
         <v>26</v>
@@ -9926,13 +9926,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="9" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="O137" s="9" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="P137" s="9" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="Q137" s="9"/>
       <c r="R137" s="9"/>
@@ -9942,7 +9942,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B138" s="5">
         <v>46132.633032858794</v>
@@ -9952,7 +9952,7 @@
         <v>46223.55789070602</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
@@ -9977,13 +9977,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9993,7 +9993,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B139" s="8">
         <v>46132.633039409724</v>
@@ -10003,7 +10003,7 @@
         <v>46223.55789011574</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>26</v>
@@ -10028,13 +10028,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="9" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="O139" s="9" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="P139" s="9" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="Q139" s="9"/>
       <c r="R139" s="9"/>
@@ -10044,7 +10044,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B140" s="5">
         <v>46132.633045821756</v>
@@ -10054,7 +10054,7 @@
         <v>46223.55788950231</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
@@ -10079,13 +10079,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -10095,7 +10095,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B141" s="8">
         <v>46132.633060057866</v>
@@ -10105,7 +10105,7 @@
         <v>46223.557888923606</v>
       </c>
       <c r="E141" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F141" s="9" t="s">
         <v>26</v>
@@ -10130,13 +10130,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="9" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="O141" s="9" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="P141" s="9" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="Q141" s="9"/>
       <c r="R141" s="9"/>
@@ -10146,7 +10146,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B142" s="5">
         <v>46132.633052986115</v>
@@ -10156,7 +10156,7 @@
         <v>46223.55788832176</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
@@ -10181,13 +10181,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -10197,7 +10197,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="7" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B143" s="8">
         <v>46132.63306579861</v>
@@ -10207,7 +10207,7 @@
         <v>46223.60357828704</v>
       </c>
       <c r="E143" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F143" s="9" t="s">
         <v>26</v>
@@ -10232,13 +10232,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="9" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="O143" s="9" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="P143" s="9" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="Q143" s="9"/>
       <c r="R143" s="9"/>
@@ -10248,7 +10248,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B144" s="5">
         <v>46132.633072337965</v>
@@ -10258,7 +10258,7 @@
         <v>46223.55788715278</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
@@ -10283,13 +10283,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -10299,7 +10299,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B145" s="8">
         <v>46132.58894553241</v>
@@ -10309,7 +10309,7 @@
         <v>46223.60418087963</v>
       </c>
       <c r="E145" s="9" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>26</v>
@@ -10334,13 +10334,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="9" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="O145" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="P145" s="9" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="Q145" s="8">
         <v>46219</v>
@@ -10360,7 +10360,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B146" s="5">
         <v>46132.633140289356</v>
@@ -10372,7 +10372,7 @@
         <v>46223.604202187504</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
@@ -10397,13 +10397,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="O146" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="P146" s="6" t="s">
         <v>354</v>
-      </c>
-      <c r="P146" s="6" t="s">
-        <v>355</v>
       </c>
       <c r="Q146" s="6"/>
       <c r="R146" s="6"/>
@@ -10413,7 +10413,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="7" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B147" s="8">
         <v>46132.63314908565</v>
@@ -10425,7 +10425,7 @@
         <v>46223.604198078705</v>
       </c>
       <c r="E147" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>26</v>
@@ -10450,13 +10450,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="9" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="O147" s="9" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="P147" s="9" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="Q147" s="9"/>
       <c r="R147" s="9"/>
@@ -10466,7 +10466,7 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B148" s="5">
         <v>46132.63315533564</v>
@@ -10478,7 +10478,7 @@
         <v>46223.60419431713</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
@@ -10503,13 +10503,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="Q148" s="6"/>
       <c r="R148" s="6"/>
@@ -10519,7 +10519,7 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="7" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B149" s="8">
         <v>46132.63316266204</v>
@@ -10531,7 +10531,7 @@
         <v>46223.60419068287</v>
       </c>
       <c r="E149" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F149" s="9" t="s">
         <v>26</v>
@@ -10556,13 +10556,13 @@
         <v>26</v>
       </c>
       <c r="N149" s="9" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="O149" s="9" t="s">
+        <v>353</v>
+      </c>
+      <c r="P149" s="9" t="s">
         <v>354</v>
-      </c>
-      <c r="P149" s="9" t="s">
-        <v>355</v>
       </c>
       <c r="Q149" s="9"/>
       <c r="R149" s="9"/>
@@ -10572,7 +10572,7 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B150" s="5">
         <v>46132.6331690625</v>
@@ -10584,7 +10584,7 @@
         <v>46223.60418627315</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>26</v>
@@ -10609,13 +10609,13 @@
         <v>26</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="O150" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="P150" s="6" t="s">
         <v>354</v>
-      </c>
-      <c r="P150" s="6" t="s">
-        <v>355</v>
       </c>
       <c r="Q150" s="6"/>
       <c r="R150" s="6"/>
@@ -10625,7 +10625,7 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="7" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B151" s="8">
         <v>46132.63317594907</v>
@@ -10635,7 +10635,7 @@
         <v>46223.604156747686</v>
       </c>
       <c r="E151" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F151" s="9" t="s">
         <v>26</v>
@@ -10660,13 +10660,13 @@
         <v>26</v>
       </c>
       <c r="N151" s="9" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="O151" s="9" t="s">
+        <v>353</v>
+      </c>
+      <c r="P151" s="9" t="s">
         <v>354</v>
-      </c>
-      <c r="P151" s="9" t="s">
-        <v>355</v>
       </c>
       <c r="Q151" s="9"/>
       <c r="R151" s="9"/>
@@ -10676,7 +10676,7 @@
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B152" s="5">
         <v>46132.633188506945</v>
@@ -10686,7 +10686,7 @@
         <v>46223.60415612269</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F152" s="6" t="s">
         <v>26</v>
@@ -10711,13 +10711,13 @@
         <v>26</v>
       </c>
       <c r="N152" s="6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="O152" s="6" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="P152" s="6" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="Q152" s="6"/>
       <c r="R152" s="6"/>
@@ -10727,7 +10727,7 @@
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" s="7" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B153" s="8">
         <v>46132.63318159722</v>
@@ -10737,7 +10737,7 @@
         <v>46223.604155520836</v>
       </c>
       <c r="E153" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F153" s="9" t="s">
         <v>26</v>
@@ -10762,13 +10762,13 @@
         <v>26</v>
       </c>
       <c r="N153" s="9" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="O153" s="9" t="s">
+        <v>353</v>
+      </c>
+      <c r="P153" s="9" t="s">
         <v>354</v>
-      </c>
-      <c r="P153" s="9" t="s">
-        <v>355</v>
       </c>
       <c r="Q153" s="9"/>
       <c r="R153" s="9"/>
@@ -10778,7 +10778,7 @@
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B154" s="5">
         <v>46132.63319443287</v>
@@ -10788,7 +10788,7 @@
         <v>46223.60415488426</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F154" s="6" t="s">
         <v>26</v>
@@ -10813,13 +10813,13 @@
         <v>26</v>
       </c>
       <c r="N154" s="6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="O154" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="P154" s="6" t="s">
         <v>354</v>
-      </c>
-      <c r="P154" s="6" t="s">
-        <v>355</v>
       </c>
       <c r="Q154" s="6"/>
       <c r="R154" s="6"/>
@@ -10829,7 +10829,7 @@
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155" s="7" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B155" s="8">
         <v>46132.63320815972</v>
@@ -10839,7 +10839,7 @@
         <v>46223.60415423611</v>
       </c>
       <c r="E155" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F155" s="9" t="s">
         <v>26</v>
@@ -10864,13 +10864,13 @@
         <v>26</v>
       </c>
       <c r="N155" s="9" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="O155" s="9" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="P155" s="9" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="Q155" s="9"/>
       <c r="R155" s="9"/>
@@ -10880,7 +10880,7 @@
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B156" s="5">
         <v>46132.63320082176</v>
@@ -10890,7 +10890,7 @@
         <v>46223.60415359953</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>26</v>
@@ -10915,13 +10915,13 @@
         <v>26</v>
       </c>
       <c r="N156" s="6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="O156" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="P156" s="6" t="s">
         <v>354</v>
-      </c>
-      <c r="P156" s="6" t="s">
-        <v>355</v>
       </c>
       <c r="Q156" s="6"/>
       <c r="R156" s="6"/>
@@ -10931,7 +10931,7 @@
     </row>
     <row r="157" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A157" s="7" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B157" s="8">
         <v>46132.63322097222</v>
@@ -10941,7 +10941,7 @@
         <v>46223.60415291667</v>
       </c>
       <c r="E157" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F157" s="9" t="s">
         <v>26</v>
@@ -10966,13 +10966,13 @@
         <v>26</v>
       </c>
       <c r="N157" s="9" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="O157" s="9" t="s">
+        <v>353</v>
+      </c>
+      <c r="P157" s="9" t="s">
         <v>354</v>
-      </c>
-      <c r="P157" s="9" t="s">
-        <v>355</v>
       </c>
       <c r="Q157" s="9"/>
       <c r="R157" s="9"/>
@@ -10982,7 +10982,7 @@
     </row>
     <row r="158" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B158" s="5">
         <v>46132.6332150463</v>
@@ -10992,7 +10992,7 @@
         <v>46223.604152280095</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F158" s="6" t="s">
         <v>26</v>
@@ -11017,13 +11017,13 @@
         <v>26</v>
       </c>
       <c r="N158" s="6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="O158" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="P158" s="6" t="s">
         <v>354</v>
-      </c>
-      <c r="P158" s="6" t="s">
-        <v>355</v>
       </c>
       <c r="Q158" s="6"/>
       <c r="R158" s="6"/>
@@ -11033,7 +11033,7 @@
     </row>
     <row r="159" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A159" s="7" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B159" s="8">
         <v>46132.63322802083</v>
@@ -11043,7 +11043,7 @@
         <v>46223.60415166667</v>
       </c>
       <c r="E159" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F159" s="9" t="s">
         <v>26</v>
@@ -11068,13 +11068,13 @@
         <v>26</v>
       </c>
       <c r="N159" s="9" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="O159" s="9" t="s">
+        <v>353</v>
+      </c>
+      <c r="P159" s="9" t="s">
         <v>354</v>
-      </c>
-      <c r="P159" s="9" t="s">
-        <v>355</v>
       </c>
       <c r="Q159" s="9"/>
       <c r="R159" s="9"/>
@@ -11084,7 +11084,7 @@
     </row>
     <row r="160" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B160" s="5">
         <v>46132.63323575231</v>
@@ -11094,7 +11094,7 @@
         <v>46223.60415104167</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F160" s="6" t="s">
         <v>26</v>
@@ -11119,13 +11119,13 @@
         <v>26</v>
       </c>
       <c r="N160" s="6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="O160" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="P160" s="6" t="s">
         <v>354</v>
-      </c>
-      <c r="P160" s="6" t="s">
-        <v>355</v>
       </c>
       <c r="Q160" s="6"/>
       <c r="R160" s="6"/>
@@ -11135,7 +11135,7 @@
     </row>
     <row r="161" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A161" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B161" s="8">
         <v>46132.633244004624</v>
@@ -11145,7 +11145,7 @@
         <v>46223.604150416664</v>
       </c>
       <c r="E161" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F161" s="9" t="s">
         <v>26</v>
@@ -11170,13 +11170,13 @@
         <v>26</v>
       </c>
       <c r="N161" s="9" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="O161" s="9" t="s">
+        <v>353</v>
+      </c>
+      <c r="P161" s="9" t="s">
         <v>354</v>
-      </c>
-      <c r="P161" s="9" t="s">
-        <v>355</v>
       </c>
       <c r="Q161" s="9"/>
       <c r="R161" s="9"/>
@@ -11186,7 +11186,7 @@
     </row>
     <row r="162" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B162" s="5">
         <v>46132.58893171296</v>
@@ -11196,7 +11196,7 @@
         <v>46223.60436486111</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="F162" s="6" t="s">
         <v>26</v>
@@ -11221,13 +11221,13 @@
         <v>26</v>
       </c>
       <c r="N162" s="6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="O162" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="P162" s="6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="Q162" s="5">
         <v>46220</v>
@@ -11247,7 +11247,7 @@
     </row>
     <row r="163" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A163" s="7" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B163" s="8">
         <v>46132.632804305555</v>
@@ -11259,7 +11259,7 @@
         <v>46223.55831635417</v>
       </c>
       <c r="E163" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F163" s="9" t="s">
         <v>26</v>
@@ -11284,13 +11284,13 @@
         <v>26</v>
       </c>
       <c r="N163" s="9" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="O163" s="9" t="s">
+        <v>374</v>
+      </c>
+      <c r="P163" s="9" t="s">
         <v>375</v>
-      </c>
-      <c r="P163" s="9" t="s">
-        <v>376</v>
       </c>
       <c r="Q163" s="9"/>
       <c r="R163" s="9"/>
@@ -11300,7 +11300,7 @@
     </row>
     <row r="164" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B164" s="5">
         <v>46132.632815624995</v>
@@ -11312,7 +11312,7 @@
         <v>46223.558312650464</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F164" s="6" t="s">
         <v>26</v>
@@ -11337,13 +11337,13 @@
         <v>26</v>
       </c>
       <c r="N164" s="6" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="O164" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="P164" s="6" t="s">
         <v>375</v>
-      </c>
-      <c r="P164" s="6" t="s">
-        <v>376</v>
       </c>
       <c r="Q164" s="6"/>
       <c r="R164" s="6"/>
@@ -11353,7 +11353,7 @@
     </row>
     <row r="165" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A165" s="7" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B165" s="8">
         <v>46132.63282284723</v>
@@ -11365,7 +11365,7 @@
         <v>46223.55830900463</v>
       </c>
       <c r="E165" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F165" s="9" t="s">
         <v>26</v>
@@ -11390,13 +11390,13 @@
         <v>26</v>
       </c>
       <c r="N165" s="9" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="O165" s="9" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="P165" s="9" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="Q165" s="9"/>
       <c r="R165" s="9"/>
@@ -11406,7 +11406,7 @@
     </row>
     <row r="166" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B166" s="5">
         <v>46132.63283236111</v>
@@ -11418,7 +11418,7 @@
         <v>46223.55830547454</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F166" s="6" t="s">
         <v>26</v>
@@ -11443,13 +11443,13 @@
         <v>26</v>
       </c>
       <c r="N166" s="6" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="O166" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P166" s="6" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="Q166" s="6"/>
       <c r="R166" s="6"/>
@@ -11459,7 +11459,7 @@
     </row>
     <row r="167" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A167" s="7" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B167" s="8">
         <v>46132.632837384255</v>
@@ -11471,7 +11471,7 @@
         <v>46223.55830142361</v>
       </c>
       <c r="E167" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F167" s="9" t="s">
         <v>26</v>
@@ -11496,13 +11496,13 @@
         <v>26</v>
       </c>
       <c r="N167" s="9" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="O167" s="9" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="P167" s="9" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="Q167" s="9"/>
       <c r="R167" s="9"/>
@@ -11512,7 +11512,7 @@
     </row>
     <row r="168" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B168" s="5">
         <v>46132.63284362269</v>
@@ -11522,7 +11522,7 @@
         <v>46223.55725636574</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F168" s="6" t="s">
         <v>26</v>
@@ -11547,13 +11547,13 @@
         <v>26</v>
       </c>
       <c r="N168" s="6" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="O168" s="6" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="P168" s="6" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="Q168" s="6"/>
       <c r="R168" s="6"/>
@@ -11563,7 +11563,7 @@
     </row>
     <row r="169" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A169" s="7" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B169" s="8">
         <v>46132.63284975695</v>
@@ -11573,7 +11573,7 @@
         <v>46223.55827238426</v>
       </c>
       <c r="E169" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F169" s="9" t="s">
         <v>26</v>
@@ -11598,13 +11598,13 @@
         <v>26</v>
       </c>
       <c r="N169" s="9" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="O169" s="9" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="P169" s="9" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="Q169" s="9"/>
       <c r="R169" s="9"/>
@@ -11614,7 +11614,7 @@
     </row>
     <row r="170" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B170" s="5">
         <v>46132.63286226852</v>
@@ -11624,7 +11624,7 @@
         <v>46223.55827179398</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F170" s="6" t="s">
         <v>26</v>
@@ -11649,13 +11649,13 @@
         <v>26</v>
       </c>
       <c r="N170" s="6" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="O170" s="6" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="P170" s="6" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="Q170" s="6"/>
       <c r="R170" s="6"/>
@@ -11665,7 +11665,7 @@
     </row>
     <row r="171" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A171" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B171" s="8">
         <v>46132.63285675926</v>
@@ -11675,7 +11675,7 @@
         <v>46223.55827119213</v>
       </c>
       <c r="E171" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F171" s="9" t="s">
         <v>26</v>
@@ -11700,13 +11700,13 @@
         <v>26</v>
       </c>
       <c r="N171" s="9" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="O171" s="9" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="P171" s="9" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="Q171" s="9"/>
       <c r="R171" s="9"/>
@@ -11716,7 +11716,7 @@
     </row>
     <row r="172" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A172" s="4" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B172" s="5">
         <v>46132.63286828704</v>
@@ -11726,7 +11726,7 @@
         <v>46223.558270567126</v>
       </c>
       <c r="E172" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F172" s="6" t="s">
         <v>26</v>
@@ -11751,13 +11751,13 @@
         <v>26</v>
       </c>
       <c r="N172" s="6" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="O172" s="6" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="P172" s="6" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="Q172" s="6"/>
       <c r="R172" s="6"/>
@@ -11767,7 +11767,7 @@
     </row>
     <row r="173" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A173" s="7" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B173" s="8">
         <v>46132.63287412037</v>
@@ -11777,7 +11777,7 @@
         <v>46223.55826994213</v>
       </c>
       <c r="E173" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F173" s="9" t="s">
         <v>26</v>
@@ -11802,13 +11802,13 @@
         <v>26</v>
       </c>
       <c r="N173" s="9" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="O173" s="9" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="P173" s="9" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="Q173" s="9"/>
       <c r="R173" s="9"/>
@@ -11818,7 +11818,7 @@
     </row>
     <row r="174" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A174" s="4" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B174" s="5">
         <v>46132.63288133102</v>
@@ -11828,7 +11828,7 @@
         <v>46223.55826935185</v>
       </c>
       <c r="E174" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F174" s="6" t="s">
         <v>26</v>
@@ -11853,13 +11853,13 @@
         <v>26</v>
       </c>
       <c r="N174" s="6" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="O174" s="6" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="P174" s="6" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="Q174" s="6"/>
       <c r="R174" s="6"/>
@@ -11869,7 +11869,7 @@
     </row>
     <row r="175" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A175" s="7" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B175" s="8">
         <v>46132.63288800926</v>
@@ -11879,7 +11879,7 @@
         <v>46223.558268761575</v>
       </c>
       <c r="E175" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F175" s="9" t="s">
         <v>26</v>
@@ -11904,13 +11904,13 @@
         <v>26</v>
       </c>
       <c r="N175" s="9" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="O175" s="9" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="P175" s="9" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="Q175" s="9"/>
       <c r="R175" s="9"/>
@@ -11920,7 +11920,7 @@
     </row>
     <row r="176" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A176" s="4" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B176" s="5">
         <v>46132.63289421296</v>
@@ -11930,7 +11930,7 @@
         <v>46223.55826814815</v>
       </c>
       <c r="E176" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F176" s="6" t="s">
         <v>26</v>
@@ -11955,13 +11955,13 @@
         <v>26</v>
       </c>
       <c r="N176" s="6" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="O176" s="6" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="P176" s="6" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="Q176" s="6"/>
       <c r="R176" s="6"/>
@@ -11971,7 +11971,7 @@
     </row>
     <row r="177" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A177" s="7" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B177" s="8">
         <v>46132.63290028935</v>
@@ -11981,7 +11981,7 @@
         <v>46223.60358047453</v>
       </c>
       <c r="E177" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F177" s="9" t="s">
         <v>26</v>
@@ -12006,13 +12006,13 @@
         <v>26</v>
       </c>
       <c r="N177" s="9" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="O177" s="9" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="P177" s="9" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="Q177" s="9"/>
       <c r="R177" s="9"/>
@@ -12022,7 +12022,7 @@
     </row>
     <row r="178" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A178" s="4" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B178" s="5">
         <v>46132.632907719904</v>
@@ -12032,7 +12032,7 @@
         <v>46223.55826689815</v>
       </c>
       <c r="E178" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F178" s="6" t="s">
         <v>26</v>
@@ -12057,13 +12057,13 @@
         <v>26</v>
       </c>
       <c r="N178" s="6" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="O178" s="6" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="P178" s="6" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="Q178" s="6"/>
       <c r="R178" s="6"/>
@@ -12073,7 +12073,7 @@
     </row>
     <row r="179" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A179" s="7" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B179" s="8">
         <v>46132.58895258102</v>
@@ -12083,7 +12083,7 @@
         <v>46224.19308488426</v>
       </c>
       <c r="E179" s="9" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="F179" s="9" t="s">
         <v>26</v>
@@ -12108,13 +12108,13 @@
         <v>26</v>
       </c>
       <c r="N179" s="9" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="O179" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="P179" s="9" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="Q179" s="8">
         <v>46223</v>
@@ -12134,7 +12134,7 @@
     </row>
     <row r="180" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A180" s="4" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B180" s="5">
         <v>46132.63330006944</v>
@@ -12144,7 +12144,7 @@
         <v>46223.60457672454</v>
       </c>
       <c r="E180" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F180" s="6" t="s">
         <v>26</v>
@@ -12169,13 +12169,13 @@
         <v>26</v>
       </c>
       <c r="N180" s="6" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="O180" s="6" t="s">
+        <v>396</v>
+      </c>
+      <c r="P180" s="6" t="s">
         <v>397</v>
-      </c>
-      <c r="P180" s="6" t="s">
-        <v>398</v>
       </c>
       <c r="Q180" s="6"/>
       <c r="R180" s="6"/>
@@ -12185,7 +12185,7 @@
     </row>
     <row r="181" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A181" s="7" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B181" s="8">
         <v>46132.63330984954</v>
@@ -12195,7 +12195,7 @@
         <v>46223.60457603009</v>
       </c>
       <c r="E181" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F181" s="9" t="s">
         <v>26</v>
@@ -12220,13 +12220,13 @@
         <v>26</v>
       </c>
       <c r="N181" s="9" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="O181" s="9" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P181" s="9" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="Q181" s="9"/>
       <c r="R181" s="9"/>
@@ -12236,7 +12236,7 @@
     </row>
     <row r="182" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A182" s="4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B182" s="5">
         <v>46132.633316377316</v>
@@ -12246,7 +12246,7 @@
         <v>46223.60457538195</v>
       </c>
       <c r="E182" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F182" s="6" t="s">
         <v>26</v>
@@ -12271,13 +12271,13 @@
         <v>26</v>
       </c>
       <c r="N182" s="6" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="O182" s="6" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P182" s="6" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="Q182" s="6"/>
       <c r="R182" s="6"/>
@@ -12287,7 +12287,7 @@
     </row>
     <row r="183" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A183" s="7" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B183" s="8">
         <v>46132.63332333333</v>
@@ -12297,7 +12297,7 @@
         <v>46223.60457480324</v>
       </c>
       <c r="E183" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F183" s="9" t="s">
         <v>26</v>
@@ -12322,13 +12322,13 @@
         <v>26</v>
       </c>
       <c r="N183" s="9" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="O183" s="9" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P183" s="9" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="Q183" s="9"/>
       <c r="R183" s="9"/>
@@ -12338,7 +12338,7 @@
     </row>
     <row r="184" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A184" s="4" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B184" s="5">
         <v>46132.63333568287</v>
@@ -12348,7 +12348,7 @@
         <v>46223.604574178244</v>
       </c>
       <c r="E184" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F184" s="6" t="s">
         <v>26</v>
@@ -12373,13 +12373,13 @@
         <v>26</v>
       </c>
       <c r="N184" s="6" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="O184" s="6" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P184" s="6" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="Q184" s="6"/>
       <c r="R184" s="6"/>
@@ -12389,7 +12389,7 @@
     </row>
     <row r="185" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A185" s="7" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B185" s="8">
         <v>46132.633329282406</v>
@@ -12399,7 +12399,7 @@
         <v>46223.60457357639</v>
       </c>
       <c r="E185" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F185" s="9" t="s">
         <v>26</v>
@@ -12424,13 +12424,13 @@
         <v>26</v>
       </c>
       <c r="N185" s="9" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="O185" s="9" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P185" s="9" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="Q185" s="9"/>
       <c r="R185" s="9"/>
@@ -12440,7 +12440,7 @@
     </row>
     <row r="186" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A186" s="4" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B186" s="5">
         <v>46132.63334925926</v>
@@ -12450,7 +12450,7 @@
         <v>46223.60457297454</v>
       </c>
       <c r="E186" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F186" s="6" t="s">
         <v>26</v>
@@ -12475,13 +12475,13 @@
         <v>26</v>
       </c>
       <c r="N186" s="6" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="O186" s="6" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P186" s="6" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="Q186" s="6"/>
       <c r="R186" s="6"/>
@@ -12491,7 +12491,7 @@
     </row>
     <row r="187" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A187" s="7" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B187" s="8">
         <v>46132.633353321755</v>
@@ -12501,7 +12501,7 @@
         <v>46223.604572372686</v>
       </c>
       <c r="E187" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F187" s="9" t="s">
         <v>26</v>
@@ -12526,13 +12526,13 @@
         <v>26</v>
       </c>
       <c r="N187" s="9" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="O187" s="9" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P187" s="9" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="Q187" s="9"/>
       <c r="R187" s="9"/>
@@ -12542,7 +12542,7 @@
     </row>
     <row r="188" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A188" s="4" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B188" s="5">
         <v>46132.63336115741</v>
@@ -12552,7 +12552,7 @@
         <v>46223.60457173611</v>
       </c>
       <c r="E188" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F188" s="6" t="s">
         <v>26</v>
@@ -12577,13 +12577,13 @@
         <v>26</v>
       </c>
       <c r="N188" s="6" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="O188" s="6" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P188" s="6" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="Q188" s="6"/>
       <c r="R188" s="6"/>
@@ -12593,7 +12593,7 @@
     </row>
     <row r="189" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A189" s="7" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B189" s="8">
         <v>46132.6333661574</v>
@@ -12603,7 +12603,7 @@
         <v>46223.60457111111</v>
       </c>
       <c r="E189" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F189" s="9" t="s">
         <v>26</v>
@@ -12628,13 +12628,13 @@
         <v>26</v>
       </c>
       <c r="N189" s="9" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="O189" s="9" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P189" s="9" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="Q189" s="9"/>
       <c r="R189" s="9"/>
@@ -12644,7 +12644,7 @@
     </row>
     <row r="190" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B190" s="5">
         <v>46132.633375046295</v>
@@ -12654,7 +12654,7 @@
         <v>46223.60457043981</v>
       </c>
       <c r="E190" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F190" s="6" t="s">
         <v>26</v>
@@ -12679,13 +12679,13 @@
         <v>26</v>
       </c>
       <c r="N190" s="6" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="O190" s="6" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P190" s="6" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="Q190" s="6"/>
       <c r="R190" s="6"/>
@@ -12695,7 +12695,7 @@
     </row>
     <row r="191" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A191" s="7" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B191" s="8">
         <v>46132.63337950232</v>
@@ -12705,7 +12705,7 @@
         <v>46223.60456982639</v>
       </c>
       <c r="E191" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F191" s="9" t="s">
         <v>26</v>
@@ -12730,13 +12730,13 @@
         <v>26</v>
       </c>
       <c r="N191" s="9" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="O191" s="9" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P191" s="9" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="Q191" s="9"/>
       <c r="R191" s="9"/>
@@ -12746,7 +12746,7 @@
     </row>
     <row r="192" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B192" s="5">
         <v>46132.63338666667</v>
@@ -12756,7 +12756,7 @@
         <v>46223.60456921296</v>
       </c>
       <c r="E192" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F192" s="6" t="s">
         <v>26</v>
@@ -12781,13 +12781,13 @@
         <v>26</v>
       </c>
       <c r="N192" s="6" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="O192" s="6" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P192" s="6" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="Q192" s="6"/>
       <c r="R192" s="6"/>
@@ -12797,7 +12797,7 @@
     </row>
     <row r="193" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A193" s="7" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B193" s="8">
         <v>46132.63339375</v>
@@ -12807,7 +12807,7 @@
         <v>46223.604568634255</v>
       </c>
       <c r="E193" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F193" s="9" t="s">
         <v>26</v>
@@ -12832,13 +12832,13 @@
         <v>26</v>
       </c>
       <c r="N193" s="9" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="O193" s="9" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P193" s="9" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="Q193" s="9"/>
       <c r="R193" s="9"/>
@@ -12848,7 +12848,7 @@
     </row>
     <row r="194" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B194" s="5">
         <v>46132.63339872685</v>
@@ -12858,7 +12858,7 @@
         <v>46223.6045680324</v>
       </c>
       <c r="E194" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F194" s="6" t="s">
         <v>26</v>
@@ -12883,13 +12883,13 @@
         <v>26</v>
       </c>
       <c r="N194" s="6" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="O194" s="6" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P194" s="6" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="Q194" s="6"/>
       <c r="R194" s="6"/>
@@ -12899,7 +12899,7 @@
     </row>
     <row r="195" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A195" s="7" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B195" s="8">
         <v>46132.633404085645</v>
@@ -12909,7 +12909,7 @@
         <v>46223.60456738426</v>
       </c>
       <c r="E195" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F195" s="9" t="s">
         <v>26</v>
@@ -12934,13 +12934,13 @@
         <v>26</v>
       </c>
       <c r="N195" s="9" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="O195" s="9" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P195" s="9" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="Q195" s="9"/>
       <c r="R195" s="9"/>
@@ -12950,17 +12950,17 @@
     </row>
     <row r="196" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B196" s="5">
         <v>46132.58900565973</v>
       </c>
       <c r="C196" s="6"/>
       <c r="D196" s="5">
-        <v>46223.605003495366</v>
+        <v>46225.25027892361</v>
       </c>
       <c r="E196" s="6" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="F196" s="6" t="s">
         <v>26</v>
@@ -12985,13 +12985,13 @@
         <v>26</v>
       </c>
       <c r="N196" s="6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="O196" s="6" t="s">
+        <v>430</v>
+      </c>
+      <c r="P196" s="6" t="s">
         <v>431</v>
-      </c>
-      <c r="P196" s="6" t="s">
-        <v>432</v>
       </c>
       <c r="Q196" s="5">
         <v>46225</v>
@@ -13000,7 +13000,7 @@
         <v>46225</v>
       </c>
       <c r="S196" s="12" t="s">
-        <v>169</v>
+        <v>432</v>
       </c>
       <c r="T196" s="6">
         <v>0</v>
@@ -13018,10 +13018,10 @@
       </c>
       <c r="C197" s="9"/>
       <c r="D197" s="8">
-        <v>46223.56000864583</v>
+        <v>46225.25025936343</v>
       </c>
       <c r="E197" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F197" s="9" t="s">
         <v>26</v>
@@ -13046,10 +13046,10 @@
         <v>26</v>
       </c>
       <c r="N197" s="9" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="O197" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P197" s="9" t="s">
         <v>434</v>
@@ -13069,10 +13069,10 @@
       </c>
       <c r="C198" s="6"/>
       <c r="D198" s="5">
-        <v>46223.56000805556</v>
+        <v>46225.250260960645</v>
       </c>
       <c r="E198" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F198" s="6" t="s">
         <v>26</v>
@@ -13097,10 +13097,10 @@
         <v>26</v>
       </c>
       <c r="N198" s="6" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="O198" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P198" s="6" t="s">
         <v>434</v>
@@ -13120,10 +13120,10 @@
       </c>
       <c r="C199" s="9"/>
       <c r="D199" s="8">
-        <v>46223.56000744213</v>
+        <v>46225.2502621875</v>
       </c>
       <c r="E199" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F199" s="9" t="s">
         <v>26</v>
@@ -13148,10 +13148,10 @@
         <v>26</v>
       </c>
       <c r="N199" s="9" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="O199" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P199" s="9" t="s">
         <v>434</v>
@@ -13171,10 +13171,10 @@
       </c>
       <c r="C200" s="6"/>
       <c r="D200" s="5">
-        <v>46223.56000681713</v>
+        <v>46225.2502634375</v>
       </c>
       <c r="E200" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F200" s="6" t="s">
         <v>26</v>
@@ -13199,10 +13199,10 @@
         <v>26</v>
       </c>
       <c r="N200" s="6" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="O200" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="P200" s="6" t="s">
         <v>434</v>
@@ -13222,10 +13222,10 @@
       </c>
       <c r="C201" s="9"/>
       <c r="D201" s="8">
-        <v>46223.560006203705</v>
+        <v>46225.25026458333</v>
       </c>
       <c r="E201" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F201" s="9" t="s">
         <v>26</v>
@@ -13250,10 +13250,10 @@
         <v>26</v>
       </c>
       <c r="N201" s="9" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="O201" s="9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="P201" s="9" t="s">
         <v>434</v>
@@ -13273,10 +13273,10 @@
       </c>
       <c r="C202" s="6"/>
       <c r="D202" s="5">
-        <v>46223.56000560185</v>
+        <v>46225.25026579861</v>
       </c>
       <c r="E202" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F202" s="6" t="s">
         <v>26</v>
@@ -13301,10 +13301,10 @@
         <v>26</v>
       </c>
       <c r="N202" s="6" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="O202" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="P202" s="6" t="s">
         <v>434</v>
@@ -13324,10 +13324,10 @@
       </c>
       <c r="C203" s="9"/>
       <c r="D203" s="8">
-        <v>46223.560005</v>
+        <v>46225.250267083335</v>
       </c>
       <c r="E203" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F203" s="9" t="s">
         <v>26</v>
@@ -13352,10 +13352,10 @@
         <v>26</v>
       </c>
       <c r="N203" s="9" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="O203" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="P203" s="9" t="s">
         <v>441</v>
@@ -13375,10 +13375,10 @@
       </c>
       <c r="C204" s="6"/>
       <c r="D204" s="5">
-        <v>46223.56000439815</v>
+        <v>46225.25026822917</v>
       </c>
       <c r="E204" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F204" s="6" t="s">
         <v>26</v>
@@ -13403,10 +13403,10 @@
         <v>26</v>
       </c>
       <c r="N204" s="6" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="O204" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P204" s="6" t="s">
         <v>434</v>
@@ -13426,10 +13426,10 @@
       </c>
       <c r="C205" s="9"/>
       <c r="D205" s="8">
-        <v>46223.56000377315</v>
+        <v>46225.25026947916</v>
       </c>
       <c r="E205" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F205" s="9" t="s">
         <v>26</v>
@@ -13454,10 +13454,10 @@
         <v>26</v>
       </c>
       <c r="N205" s="9" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="O205" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P205" s="9" t="s">
         <v>434</v>
@@ -13477,10 +13477,10 @@
       </c>
       <c r="C206" s="6"/>
       <c r="D206" s="5">
-        <v>46223.56000319445</v>
+        <v>46225.25027071759</v>
       </c>
       <c r="E206" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F206" s="6" t="s">
         <v>26</v>
@@ -13505,10 +13505,10 @@
         <v>26</v>
       </c>
       <c r="N206" s="6" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="O206" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="P206" s="6" t="s">
         <v>434</v>
@@ -13528,10 +13528,10 @@
       </c>
       <c r="C207" s="9"/>
       <c r="D207" s="8">
-        <v>46223.560002604165</v>
+        <v>46225.25027203704</v>
       </c>
       <c r="E207" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F207" s="9" t="s">
         <v>26</v>
@@ -13556,10 +13556,10 @@
         <v>26</v>
       </c>
       <c r="N207" s="9" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="O207" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="P207" s="9" t="s">
         <v>434</v>
@@ -13579,10 +13579,10 @@
       </c>
       <c r="C208" s="6"/>
       <c r="D208" s="5">
-        <v>46223.56000199074</v>
+        <v>46225.2502734375</v>
       </c>
       <c r="E208" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F208" s="6" t="s">
         <v>26</v>
@@ -13607,10 +13607,10 @@
         <v>26</v>
       </c>
       <c r="N208" s="6" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="O208" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P208" s="6" t="s">
         <v>434</v>
@@ -13630,10 +13630,10 @@
       </c>
       <c r="C209" s="9"/>
       <c r="D209" s="8">
-        <v>46223.560001412035</v>
+        <v>46225.250274606486</v>
       </c>
       <c r="E209" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F209" s="9" t="s">
         <v>26</v>
@@ -13658,10 +13658,10 @@
         <v>26</v>
       </c>
       <c r="N209" s="9" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="O209" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P209" s="9" t="s">
         <v>434</v>
@@ -13681,10 +13681,10 @@
       </c>
       <c r="C210" s="6"/>
       <c r="D210" s="5">
-        <v>46223.56000084491</v>
+        <v>46225.25027587963</v>
       </c>
       <c r="E210" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F210" s="6" t="s">
         <v>26</v>
@@ -13709,10 +13709,10 @@
         <v>26</v>
       </c>
       <c r="N210" s="6" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="O210" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="P210" s="6" t="s">
         <v>434</v>
@@ -13732,7 +13732,7 @@
       </c>
       <c r="C211" s="9"/>
       <c r="D211" s="8">
-        <v>46223.56000027778</v>
+        <v>46225.2502774537</v>
       </c>
       <c r="E211" s="9" t="s">
         <v>450</v>
@@ -13760,10 +13760,10 @@
         <v>26</v>
       </c>
       <c r="N211" s="9" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="O211" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="P211" s="9" t="s">
         <v>441</v>
@@ -13783,10 +13783,10 @@
       </c>
       <c r="C212" s="6"/>
       <c r="D212" s="5">
-        <v>46223.55999969908</v>
+        <v>46225.25028299769</v>
       </c>
       <c r="E212" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F212" s="6" t="s">
         <v>26</v>
@@ -13811,10 +13811,10 @@
         <v>26</v>
       </c>
       <c r="N212" s="6" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="O212" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="P212" s="6" t="s">
         <v>434</v>
@@ -13912,7 +13912,7 @@
         <v>453</v>
       </c>
       <c r="O214" s="6" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="P214" s="6" t="s">
         <v>459</v>
@@ -13924,7 +13924,7 @@
         <v>46226</v>
       </c>
       <c r="S214" s="12" t="s">
-        <v>169</v>
+        <v>432</v>
       </c>
       <c r="T214" s="6">
         <v>0</v>
@@ -13945,7 +13945,7 @@
         <v>46196.91388565973</v>
       </c>
       <c r="E215" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F215" s="9" t="s">
         <v>26</v>
@@ -13973,10 +13973,10 @@
         <v>456</v>
       </c>
       <c r="O215" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P215" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q215" s="9"/>
       <c r="R215" s="9"/>
@@ -13996,7 +13996,7 @@
         <v>46196.91389173611</v>
       </c>
       <c r="E216" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F216" s="6" t="s">
         <v>26</v>
@@ -14024,10 +14024,10 @@
         <v>456</v>
       </c>
       <c r="O216" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P216" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q216" s="6"/>
       <c r="R216" s="6"/>
@@ -14047,7 +14047,7 @@
         <v>46196.91390143518</v>
       </c>
       <c r="E217" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F217" s="9" t="s">
         <v>26</v>
@@ -14075,10 +14075,10 @@
         <v>456</v>
       </c>
       <c r="O217" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P217" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q217" s="9"/>
       <c r="R217" s="9"/>
@@ -14098,7 +14098,7 @@
         <v>46196.913907152775</v>
       </c>
       <c r="E218" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F218" s="6" t="s">
         <v>26</v>
@@ -14126,10 +14126,10 @@
         <v>456</v>
       </c>
       <c r="O218" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P218" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q218" s="6"/>
       <c r="R218" s="6"/>
@@ -14149,7 +14149,7 @@
         <v>46196.91391674768</v>
       </c>
       <c r="E219" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F219" s="9" t="s">
         <v>26</v>
@@ -14177,10 +14177,10 @@
         <v>456</v>
       </c>
       <c r="O219" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P219" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q219" s="9"/>
       <c r="R219" s="9"/>
@@ -14200,7 +14200,7 @@
         <v>46196.913933171294</v>
       </c>
       <c r="E220" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F220" s="6" t="s">
         <v>26</v>
@@ -14228,10 +14228,10 @@
         <v>456</v>
       </c>
       <c r="O220" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P220" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q220" s="6"/>
       <c r="R220" s="6"/>
@@ -14279,10 +14279,10 @@
         <v>456</v>
       </c>
       <c r="O221" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P221" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q221" s="9"/>
       <c r="R221" s="9"/>
@@ -14302,7 +14302,7 @@
         <v>46196.91395613426</v>
       </c>
       <c r="E222" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F222" s="6" t="s">
         <v>26</v>
@@ -14330,10 +14330,10 @@
         <v>456</v>
       </c>
       <c r="O222" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P222" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q222" s="6"/>
       <c r="R222" s="6"/>
@@ -14353,7 +14353,7 @@
         <v>46196.9139649537</v>
       </c>
       <c r="E223" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F223" s="9" t="s">
         <v>26</v>
@@ -14381,10 +14381,10 @@
         <v>456</v>
       </c>
       <c r="O223" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P223" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q223" s="9"/>
       <c r="R223" s="9"/>
@@ -14404,7 +14404,7 @@
         <v>46196.91397201389</v>
       </c>
       <c r="E224" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F224" s="6" t="s">
         <v>26</v>
@@ -14432,10 +14432,10 @@
         <v>456</v>
       </c>
       <c r="O224" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P224" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q224" s="6"/>
       <c r="R224" s="6"/>
@@ -14455,7 +14455,7 @@
         <v>46196.91398435185</v>
       </c>
       <c r="E225" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F225" s="9" t="s">
         <v>26</v>
@@ -14483,10 +14483,10 @@
         <v>456</v>
       </c>
       <c r="O225" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P225" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q225" s="9"/>
       <c r="R225" s="9"/>
@@ -14506,7 +14506,7 @@
         <v>46196.91399296296</v>
       </c>
       <c r="E226" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F226" s="6" t="s">
         <v>26</v>
@@ -14534,10 +14534,10 @@
         <v>456</v>
       </c>
       <c r="O226" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P226" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q226" s="6"/>
       <c r="R226" s="6"/>
@@ -14557,7 +14557,7 @@
         <v>46196.913999675926</v>
       </c>
       <c r="E227" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F227" s="9" t="s">
         <v>26</v>
@@ -14585,10 +14585,10 @@
         <v>456</v>
       </c>
       <c r="O227" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P227" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q227" s="9"/>
       <c r="R227" s="9"/>
@@ -14608,7 +14608,7 @@
         <v>46196.914015358794</v>
       </c>
       <c r="E228" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F228" s="6" t="s">
         <v>26</v>
@@ -14636,10 +14636,10 @@
         <v>456</v>
       </c>
       <c r="O228" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P228" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q228" s="6"/>
       <c r="R228" s="6"/>
@@ -14710,7 +14710,7 @@
         <v>46196.91403721065</v>
       </c>
       <c r="E230" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F230" s="6" t="s">
         <v>26</v>
@@ -14738,10 +14738,10 @@
         <v>456</v>
       </c>
       <c r="O230" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="P230" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q230" s="6"/>
       <c r="R230" s="6"/>
@@ -14801,7 +14801,7 @@
         <v>46227</v>
       </c>
       <c r="S231" s="12" t="s">
-        <v>169</v>
+        <v>432</v>
       </c>
       <c r="T231" s="9">
         <v>0</v>
@@ -14822,7 +14822,7 @@
         <v>46223.557647037036</v>
       </c>
       <c r="E232" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F232" s="6" t="s">
         <v>26</v>
@@ -14850,10 +14850,10 @@
         <v>477</v>
       </c>
       <c r="O232" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P232" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q232" s="6"/>
       <c r="R232" s="6"/>
@@ -14873,7 +14873,7 @@
         <v>46223.55764646991</v>
       </c>
       <c r="E233" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F233" s="9" t="s">
         <v>26</v>
@@ -14901,10 +14901,10 @@
         <v>477</v>
       </c>
       <c r="O233" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P233" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q233" s="9"/>
       <c r="R233" s="9"/>
@@ -14924,7 +14924,7 @@
         <v>46223.55764586806</v>
       </c>
       <c r="E234" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F234" s="6" t="s">
         <v>26</v>
@@ -14952,10 +14952,10 @@
         <v>477</v>
       </c>
       <c r="O234" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P234" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q234" s="6"/>
       <c r="R234" s="6"/>
@@ -14975,7 +14975,7 @@
         <v>46223.55764528935</v>
       </c>
       <c r="E235" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F235" s="9" t="s">
         <v>26</v>
@@ -15003,10 +15003,10 @@
         <v>477</v>
       </c>
       <c r="O235" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P235" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q235" s="9"/>
       <c r="R235" s="9"/>
@@ -15026,7 +15026,7 @@
         <v>46223.55764474537</v>
       </c>
       <c r="E236" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F236" s="6" t="s">
         <v>26</v>
@@ -15054,10 +15054,10 @@
         <v>477</v>
       </c>
       <c r="O236" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P236" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q236" s="6"/>
       <c r="R236" s="6"/>
@@ -15077,7 +15077,7 @@
         <v>46223.557644201384</v>
       </c>
       <c r="E237" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F237" s="9" t="s">
         <v>26</v>
@@ -15105,10 +15105,10 @@
         <v>477</v>
       </c>
       <c r="O237" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P237" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q237" s="9"/>
       <c r="R237" s="9"/>
@@ -15128,7 +15128,7 @@
         <v>46223.557643657405</v>
       </c>
       <c r="E238" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F238" s="6" t="s">
         <v>26</v>
@@ -15159,7 +15159,7 @@
         <v>450</v>
       </c>
       <c r="P238" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q238" s="6"/>
       <c r="R238" s="6"/>
@@ -15179,7 +15179,7 @@
         <v>46223.557643078704</v>
       </c>
       <c r="E239" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F239" s="9" t="s">
         <v>26</v>
@@ -15207,10 +15207,10 @@
         <v>477</v>
       </c>
       <c r="O239" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P239" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q239" s="9"/>
       <c r="R239" s="9"/>
@@ -15230,7 +15230,7 @@
         <v>46223.5576425</v>
       </c>
       <c r="E240" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F240" s="6" t="s">
         <v>26</v>
@@ -15258,10 +15258,10 @@
         <v>477</v>
       </c>
       <c r="O240" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P240" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q240" s="6"/>
       <c r="R240" s="6"/>
@@ -15281,7 +15281,7 @@
         <v>46223.557641921296</v>
       </c>
       <c r="E241" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F241" s="9" t="s">
         <v>26</v>
@@ -15309,10 +15309,10 @@
         <v>477</v>
       </c>
       <c r="O241" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P241" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q241" s="9"/>
       <c r="R241" s="9"/>
@@ -15332,7 +15332,7 @@
         <v>46223.55764133102</v>
       </c>
       <c r="E242" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F242" s="6" t="s">
         <v>26</v>
@@ -15360,10 +15360,10 @@
         <v>477</v>
       </c>
       <c r="O242" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P242" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q242" s="6"/>
       <c r="R242" s="6"/>
@@ -15383,7 +15383,7 @@
         <v>46223.55764076389</v>
       </c>
       <c r="E243" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F243" s="9" t="s">
         <v>26</v>
@@ -15411,10 +15411,10 @@
         <v>477</v>
       </c>
       <c r="O243" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P243" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q243" s="9"/>
       <c r="R243" s="9"/>
@@ -15434,7 +15434,7 @@
         <v>46223.557640150466</v>
       </c>
       <c r="E244" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F244" s="6" t="s">
         <v>26</v>
@@ -15462,10 +15462,10 @@
         <v>477</v>
       </c>
       <c r="O244" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P244" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q244" s="6"/>
       <c r="R244" s="6"/>
@@ -15485,7 +15485,7 @@
         <v>46223.557639583334</v>
       </c>
       <c r="E245" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F245" s="9" t="s">
         <v>26</v>
@@ -15513,10 +15513,10 @@
         <v>477</v>
       </c>
       <c r="O245" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P245" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q245" s="9"/>
       <c r="R245" s="9"/>
@@ -15567,7 +15567,7 @@
         <v>450</v>
       </c>
       <c r="P246" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q246" s="6"/>
       <c r="R246" s="6"/>
@@ -15587,7 +15587,7 @@
         <v>46223.55763841435</v>
       </c>
       <c r="E247" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F247" s="9" t="s">
         <v>26</v>
@@ -15615,10 +15615,10 @@
         <v>477</v>
       </c>
       <c r="O247" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P247" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q247" s="9"/>
       <c r="R247" s="9"/>
@@ -15680,7 +15680,7 @@
         <v>46230</v>
       </c>
       <c r="S248" s="12" t="s">
-        <v>169</v>
+        <v>432</v>
       </c>
       <c r="T248" s="6">
         <v>0</v>
@@ -15701,7 +15701,7 @@
         <v>46196.914276875</v>
       </c>
       <c r="E249" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F249" s="9" t="s">
         <v>26</v>
@@ -15729,10 +15729,10 @@
         <v>496</v>
       </c>
       <c r="O249" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P249" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q249" s="9"/>
       <c r="R249" s="9"/>
@@ -15752,7 +15752,7 @@
         <v>46196.914286666666</v>
       </c>
       <c r="E250" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F250" s="6" t="s">
         <v>26</v>
@@ -15780,10 +15780,10 @@
         <v>496</v>
       </c>
       <c r="O250" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P250" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q250" s="6"/>
       <c r="R250" s="6"/>
@@ -15803,7 +15803,7 @@
         <v>46196.91429060185</v>
       </c>
       <c r="E251" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F251" s="9" t="s">
         <v>26</v>
@@ -15831,10 +15831,10 @@
         <v>496</v>
       </c>
       <c r="O251" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P251" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q251" s="9"/>
       <c r="R251" s="9"/>
@@ -15854,7 +15854,7 @@
         <v>46196.914299571756</v>
       </c>
       <c r="E252" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F252" s="6" t="s">
         <v>26</v>
@@ -15882,10 +15882,10 @@
         <v>496</v>
       </c>
       <c r="O252" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P252" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q252" s="6"/>
       <c r="R252" s="6"/>
@@ -15905,7 +15905,7 @@
         <v>46196.91430931713</v>
       </c>
       <c r="E253" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F253" s="9" t="s">
         <v>26</v>
@@ -15933,10 +15933,10 @@
         <v>496</v>
       </c>
       <c r="O253" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P253" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q253" s="9"/>
       <c r="R253" s="9"/>
@@ -15956,7 +15956,7 @@
         <v>46196.914319143514</v>
       </c>
       <c r="E254" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F254" s="6" t="s">
         <v>26</v>
@@ -15984,10 +15984,10 @@
         <v>496</v>
       </c>
       <c r="O254" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P254" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q254" s="6"/>
       <c r="R254" s="6"/>
@@ -16007,7 +16007,7 @@
         <v>46196.91432607639</v>
       </c>
       <c r="E255" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F255" s="9" t="s">
         <v>26</v>
@@ -16035,10 +16035,10 @@
         <v>496</v>
       </c>
       <c r="O255" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P255" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q255" s="9"/>
       <c r="R255" s="9"/>
@@ -16058,7 +16058,7 @@
         <v>46196.914335231486</v>
       </c>
       <c r="E256" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F256" s="6" t="s">
         <v>26</v>
@@ -16086,10 +16086,10 @@
         <v>496</v>
       </c>
       <c r="O256" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P256" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q256" s="6"/>
       <c r="R256" s="6"/>
@@ -16109,7 +16109,7 @@
         <v>46196.914344687495</v>
       </c>
       <c r="E257" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F257" s="9" t="s">
         <v>26</v>
@@ -16137,10 +16137,10 @@
         <v>496</v>
       </c>
       <c r="O257" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P257" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q257" s="9"/>
       <c r="R257" s="9"/>
@@ -16160,7 +16160,7 @@
         <v>46196.91435427083</v>
       </c>
       <c r="E258" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F258" s="6" t="s">
         <v>26</v>
@@ -16188,10 +16188,10 @@
         <v>496</v>
       </c>
       <c r="O258" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P258" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q258" s="6"/>
       <c r="R258" s="6"/>
@@ -16211,7 +16211,7 @@
         <v>46196.91437050926</v>
       </c>
       <c r="E259" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F259" s="9" t="s">
         <v>26</v>
@@ -16239,10 +16239,10 @@
         <v>496</v>
       </c>
       <c r="O259" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P259" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q259" s="9"/>
       <c r="R259" s="9"/>
@@ -16262,7 +16262,7 @@
         <v>46196.914380057875</v>
       </c>
       <c r="E260" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F260" s="6" t="s">
         <v>26</v>
@@ -16290,10 +16290,10 @@
         <v>496</v>
       </c>
       <c r="O260" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P260" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q260" s="6"/>
       <c r="R260" s="6"/>
@@ -16313,7 +16313,7 @@
         <v>46196.914383738425</v>
       </c>
       <c r="E261" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F261" s="9" t="s">
         <v>26</v>
@@ -16341,10 +16341,10 @@
         <v>496</v>
       </c>
       <c r="O261" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P261" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q261" s="9"/>
       <c r="R261" s="9"/>
@@ -16364,7 +16364,7 @@
         <v>46196.914396527776</v>
       </c>
       <c r="E262" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F262" s="6" t="s">
         <v>26</v>
@@ -16392,10 +16392,10 @@
         <v>496</v>
       </c>
       <c r="O262" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P262" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q262" s="6"/>
       <c r="R262" s="6"/>
@@ -16415,7 +16415,7 @@
         <v>46196.914406261574</v>
       </c>
       <c r="E263" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F263" s="9" t="s">
         <v>26</v>
@@ -16446,7 +16446,7 @@
         <v>450</v>
       </c>
       <c r="P263" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q263" s="9"/>
       <c r="R263" s="9"/>
@@ -16466,7 +16466,7 @@
         <v>46196.91441971065</v>
       </c>
       <c r="E264" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F264" s="6" t="s">
         <v>26</v>
@@ -16494,10 +16494,10 @@
         <v>496</v>
       </c>
       <c r="O264" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P264" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q264" s="6"/>
       <c r="R264" s="6"/>
@@ -16557,7 +16557,7 @@
         <v>46231</v>
       </c>
       <c r="S265" s="12" t="s">
-        <v>169</v>
+        <v>432</v>
       </c>
       <c r="T265" s="9">
         <v>0</v>
@@ -16578,7 +16578,7 @@
         <v>46196.91446424769</v>
       </c>
       <c r="E266" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F266" s="6" t="s">
         <v>26</v>
@@ -16606,7 +16606,7 @@
         <v>517</v>
       </c>
       <c r="O266" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P266" s="6" t="s">
         <v>520</v>
@@ -16629,7 +16629,7 @@
         <v>46196.91447116898</v>
       </c>
       <c r="E267" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F267" s="9" t="s">
         <v>26</v>
@@ -16657,7 +16657,7 @@
         <v>517</v>
       </c>
       <c r="O267" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P267" s="9" t="s">
         <v>520</v>
@@ -16680,7 +16680,7 @@
         <v>46196.914480694446</v>
       </c>
       <c r="E268" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F268" s="6" t="s">
         <v>26</v>
@@ -16708,7 +16708,7 @@
         <v>517</v>
       </c>
       <c r="O268" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P268" s="6" t="s">
         <v>520</v>
@@ -16731,7 +16731,7 @@
         <v>46196.91449018518</v>
       </c>
       <c r="E269" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F269" s="9" t="s">
         <v>26</v>
@@ -16759,7 +16759,7 @@
         <v>517</v>
       </c>
       <c r="O269" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P269" s="9" t="s">
         <v>520</v>
@@ -16782,7 +16782,7 @@
         <v>46196.91449658565</v>
       </c>
       <c r="E270" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F270" s="6" t="s">
         <v>26</v>
@@ -16810,7 +16810,7 @@
         <v>517</v>
       </c>
       <c r="O270" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P270" s="6" t="s">
         <v>520</v>
@@ -16833,7 +16833,7 @@
         <v>46196.914503645836</v>
       </c>
       <c r="E271" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F271" s="9" t="s">
         <v>26</v>
@@ -16861,7 +16861,7 @@
         <v>517</v>
       </c>
       <c r="O271" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P271" s="9" t="s">
         <v>520</v>
@@ -16884,7 +16884,7 @@
         <v>46196.91450951389</v>
       </c>
       <c r="E272" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F272" s="6" t="s">
         <v>26</v>
@@ -16912,7 +16912,7 @@
         <v>517</v>
       </c>
       <c r="O272" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P272" s="6" t="s">
         <v>520</v>
@@ -16935,7 +16935,7 @@
         <v>46196.91451931713</v>
       </c>
       <c r="E273" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F273" s="9" t="s">
         <v>26</v>
@@ -16963,7 +16963,7 @@
         <v>517</v>
       </c>
       <c r="O273" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P273" s="9" t="s">
         <v>528</v>
@@ -16986,7 +16986,7 @@
         <v>46196.914524629625</v>
       </c>
       <c r="E274" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F274" s="6" t="s">
         <v>26</v>
@@ -17014,7 +17014,7 @@
         <v>517</v>
       </c>
       <c r="O274" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P274" s="6" t="s">
         <v>528</v>
@@ -17037,7 +17037,7 @@
         <v>46196.91452907407</v>
       </c>
       <c r="E275" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F275" s="9" t="s">
         <v>26</v>
@@ -17065,7 +17065,7 @@
         <v>517</v>
       </c>
       <c r="O275" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P275" s="9" t="s">
         <v>528</v>
@@ -17088,7 +17088,7 @@
         <v>46196.91453917824</v>
       </c>
       <c r="E276" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F276" s="6" t="s">
         <v>26</v>
@@ -17116,7 +17116,7 @@
         <v>517</v>
       </c>
       <c r="O276" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P276" s="6" t="s">
         <v>528</v>
@@ -17139,7 +17139,7 @@
         <v>46196.91454204862</v>
       </c>
       <c r="E277" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F277" s="9" t="s">
         <v>26</v>
@@ -17167,7 +17167,7 @@
         <v>517</v>
       </c>
       <c r="O277" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P277" s="9" t="s">
         <v>528</v>
@@ -17190,7 +17190,7 @@
         <v>46196.914551724534</v>
       </c>
       <c r="E278" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F278" s="6" t="s">
         <v>26</v>
@@ -17218,7 +17218,7 @@
         <v>517</v>
       </c>
       <c r="O278" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P278" s="6" t="s">
         <v>528</v>
@@ -17241,7 +17241,7 @@
         <v>46196.91457195602</v>
       </c>
       <c r="E279" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F279" s="9" t="s">
         <v>26</v>
@@ -17269,7 +17269,7 @@
         <v>517</v>
       </c>
       <c r="O279" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P279" s="9" t="s">
         <v>528</v>
@@ -17292,7 +17292,7 @@
         <v>46196.91458070602</v>
       </c>
       <c r="E280" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F280" s="6" t="s">
         <v>26</v>
@@ -17320,7 +17320,7 @@
         <v>517</v>
       </c>
       <c r="O280" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P280" s="6" t="s">
         <v>528</v>
@@ -17343,7 +17343,7 @@
         <v>46196.91461018518</v>
       </c>
       <c r="E281" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F281" s="9" t="s">
         <v>26</v>
@@ -17371,7 +17371,7 @@
         <v>517</v>
       </c>
       <c r="O281" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P281" s="9" t="s">
         <v>528</v>

--- a/data/50001541 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001541 - XEMORTIZ MINERA FRISCO.xlsx
@@ -1312,88 +1312,88 @@
     <t>Coordinacion Entrega con Cliente,Montaje:</t>
   </si>
   <si>
+    <t>1214137717389578</t>
+  </si>
+  <si>
+    <t>OT 4307 ZVN 1-9-86/2 ,RE-PINTADO</t>
+  </si>
+  <si>
+    <t>1214137717389579</t>
+  </si>
+  <si>
+    <t>1214137717389580</t>
+  </si>
+  <si>
+    <t>1214137717389581</t>
+  </si>
+  <si>
+    <t>1214137717389582</t>
+  </si>
+  <si>
+    <t>1214137717389583</t>
+  </si>
+  <si>
+    <t>1214137717389584</t>
+  </si>
+  <si>
+    <t>OT 4307  ZVN 1-9-86/2 ,RE-PINTADO</t>
+  </si>
+  <si>
+    <t>1214137717389585</t>
+  </si>
+  <si>
+    <t>1214137717389586</t>
+  </si>
+  <si>
+    <t>1214137717389587</t>
+  </si>
+  <si>
+    <t>1214137717389588</t>
+  </si>
+  <si>
+    <t>1214137717389589</t>
+  </si>
+  <si>
+    <t>1214137717389590</t>
+  </si>
+  <si>
+    <t>1214137717389591</t>
+  </si>
+  <si>
+    <t>1214137717389592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4307  ZVN 1-9-86/2 </t>
+  </si>
+  <si>
+    <t>1214150417415297</t>
+  </si>
+  <si>
+    <t>1214138644347586</t>
+  </si>
+  <si>
+    <t>Logistica:</t>
+  </si>
+  <si>
+    <t>Coordinacion Entrega con Cliente,Embalaje,PACKING LIST,Despacho</t>
+  </si>
+  <si>
+    <t>1214138644347596</t>
+  </si>
+  <si>
+    <t>Coordinacion Entrega con Cliente</t>
+  </si>
+  <si>
+    <t>Karin Pinto</t>
+  </si>
+  <si>
+    <t>kpinto@zitron.com</t>
+  </si>
+  <si>
+    <t>Logistica:,Embalaje</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1214137717389578</t>
-  </si>
-  <si>
-    <t>OT 4307 ZVN 1-9-86/2 ,RE-PINTADO</t>
-  </si>
-  <si>
-    <t>1214137717389579</t>
-  </si>
-  <si>
-    <t>1214137717389580</t>
-  </si>
-  <si>
-    <t>1214137717389581</t>
-  </si>
-  <si>
-    <t>1214137717389582</t>
-  </si>
-  <si>
-    <t>1214137717389583</t>
-  </si>
-  <si>
-    <t>1214137717389584</t>
-  </si>
-  <si>
-    <t>OT 4307  ZVN 1-9-86/2 ,RE-PINTADO</t>
-  </si>
-  <si>
-    <t>1214137717389585</t>
-  </si>
-  <si>
-    <t>1214137717389586</t>
-  </si>
-  <si>
-    <t>1214137717389587</t>
-  </si>
-  <si>
-    <t>1214137717389588</t>
-  </si>
-  <si>
-    <t>1214137717389589</t>
-  </si>
-  <si>
-    <t>1214137717389590</t>
-  </si>
-  <si>
-    <t>1214137717389591</t>
-  </si>
-  <si>
-    <t>1214137717389592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4307  ZVN 1-9-86/2 </t>
-  </si>
-  <si>
-    <t>1214150417415297</t>
-  </si>
-  <si>
-    <t>1214138644347586</t>
-  </si>
-  <si>
-    <t>Logistica:</t>
-  </si>
-  <si>
-    <t>Coordinacion Entrega con Cliente,Embalaje,PACKING LIST,Despacho</t>
-  </si>
-  <si>
-    <t>1214138644347596</t>
-  </si>
-  <si>
-    <t>Coordinacion Entrega con Cliente</t>
-  </si>
-  <si>
-    <t>Karin Pinto</t>
-  </si>
-  <si>
-    <t>kpinto@zitron.com</t>
-  </si>
-  <si>
-    <t>Logistica:,Embalaje</t>
   </si>
   <si>
     <t>1214137717389594</t>
@@ -12960,7 +12960,7 @@
       </c>
       <c r="C196" s="6"/>
       <c r="D196" s="5">
-        <v>46225.25027892361</v>
+        <v>46226.18398983796</v>
       </c>
       <c r="E196" s="6" t="s">
         <v>430</v>
@@ -13002,8 +13002,8 @@
       <c r="R196" s="5">
         <v>46225</v>
       </c>
-      <c r="S196" s="12" t="s">
-        <v>433</v>
+      <c r="S196" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T196" s="6">
         <v>0</v>
@@ -13014,7 +13014,7 @@
     </row>
     <row r="197" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A197" s="7" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B197" s="8">
         <v>46132.6334534375</v>
@@ -13055,7 +13055,7 @@
         <v>171</v>
       </c>
       <c r="P197" s="9" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="Q197" s="9"/>
       <c r="R197" s="9"/>
@@ -13065,7 +13065,7 @@
     </row>
     <row r="198" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A198" s="4" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B198" s="5">
         <v>46132.633462025464</v>
@@ -13106,7 +13106,7 @@
         <v>175</v>
       </c>
       <c r="P198" s="6" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="Q198" s="6"/>
       <c r="R198" s="6"/>
@@ -13116,7 +13116,7 @@
     </row>
     <row r="199" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A199" s="7" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B199" s="8">
         <v>46132.633468622684</v>
@@ -13157,7 +13157,7 @@
         <v>178</v>
       </c>
       <c r="P199" s="9" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="Q199" s="9"/>
       <c r="R199" s="9"/>
@@ -13167,7 +13167,7 @@
     </row>
     <row r="200" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A200" s="4" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B200" s="5">
         <v>46132.63347502315</v>
@@ -13208,7 +13208,7 @@
         <v>180</v>
       </c>
       <c r="P200" s="6" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="Q200" s="6"/>
       <c r="R200" s="6"/>
@@ -13218,7 +13218,7 @@
     </row>
     <row r="201" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A201" s="7" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B201" s="8">
         <v>46132.63348070602</v>
@@ -13259,7 +13259,7 @@
         <v>182</v>
       </c>
       <c r="P201" s="9" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="Q201" s="9"/>
       <c r="R201" s="9"/>
@@ -13269,7 +13269,7 @@
     </row>
     <row r="202" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A202" s="4" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B202" s="5">
         <v>46132.63348662037</v>
@@ -13310,7 +13310,7 @@
         <v>184</v>
       </c>
       <c r="P202" s="6" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="Q202" s="6"/>
       <c r="R202" s="6"/>
@@ -13320,7 +13320,7 @@
     </row>
     <row r="203" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A203" s="7" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B203" s="8">
         <v>46132.63349295139</v>
@@ -13361,7 +13361,7 @@
         <v>186</v>
       </c>
       <c r="P203" s="9" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q203" s="9"/>
       <c r="R203" s="9"/>
@@ -13371,7 +13371,7 @@
     </row>
     <row r="204" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A204" s="4" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B204" s="5">
         <v>46132.633500138894</v>
@@ -13412,7 +13412,7 @@
         <v>189</v>
       </c>
       <c r="P204" s="6" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="Q204" s="6"/>
       <c r="R204" s="6"/>
@@ -13422,7 +13422,7 @@
     </row>
     <row r="205" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A205" s="7" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B205" s="8">
         <v>46132.633505983795</v>
@@ -13463,7 +13463,7 @@
         <v>191</v>
       </c>
       <c r="P205" s="9" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="Q205" s="9"/>
       <c r="R205" s="9"/>
@@ -13473,7 +13473,7 @@
     </row>
     <row r="206" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A206" s="4" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B206" s="5">
         <v>46132.6335124537</v>
@@ -13514,7 +13514,7 @@
         <v>193</v>
       </c>
       <c r="P206" s="6" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="Q206" s="6"/>
       <c r="R206" s="6"/>
@@ -13524,7 +13524,7 @@
     </row>
     <row r="207" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A207" s="7" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B207" s="8">
         <v>46132.63351974537</v>
@@ -13565,7 +13565,7 @@
         <v>195</v>
       </c>
       <c r="P207" s="9" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="Q207" s="9"/>
       <c r="R207" s="9"/>
@@ -13575,7 +13575,7 @@
     </row>
     <row r="208" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A208" s="4" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B208" s="5">
         <v>46132.6335277662</v>
@@ -13616,7 +13616,7 @@
         <v>197</v>
       </c>
       <c r="P208" s="6" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="Q208" s="6"/>
       <c r="R208" s="6"/>
@@ -13626,7 +13626,7 @@
     </row>
     <row r="209" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A209" s="7" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B209" s="8">
         <v>46132.633534988425</v>
@@ -13667,7 +13667,7 @@
         <v>199</v>
       </c>
       <c r="P209" s="9" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="Q209" s="9"/>
       <c r="R209" s="9"/>
@@ -13677,7 +13677,7 @@
     </row>
     <row r="210" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A210" s="4" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B210" s="5">
         <v>46132.63354082176</v>
@@ -13718,7 +13718,7 @@
         <v>201</v>
       </c>
       <c r="P210" s="6" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="Q210" s="6"/>
       <c r="R210" s="6"/>
@@ -13728,7 +13728,7 @@
     </row>
     <row r="211" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A211" s="7" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B211" s="8">
         <v>46132.63354760417</v>
@@ -13738,7 +13738,7 @@
         <v>46225.2502774537</v>
       </c>
       <c r="E211" s="9" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="F211" s="9" t="s">
         <v>26</v>
@@ -13769,7 +13769,7 @@
         <v>203</v>
       </c>
       <c r="P211" s="9" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q211" s="9"/>
       <c r="R211" s="9"/>
@@ -13779,7 +13779,7 @@
     </row>
     <row r="212" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A212" s="4" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B212" s="5">
         <v>46133.58300138889</v>
@@ -13820,7 +13820,7 @@
         <v>206</v>
       </c>
       <c r="P212" s="6" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="Q212" s="6"/>
       <c r="R212" s="6"/>
@@ -13830,7 +13830,7 @@
     </row>
     <row r="213" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A213" s="7" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B213" s="8">
         <v>46132.589012916666</v>
@@ -13840,7 +13840,7 @@
         <v>46133.58769056713</v>
       </c>
       <c r="E213" s="9" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="F213" s="9" t="s">
         <v>25</v>
@@ -13864,7 +13864,7 @@
         <v>26</v>
       </c>
       <c r="O213" s="9" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="P213" s="9" t="s">
         <v>26</v>
@@ -13877,26 +13877,26 @@
     </row>
     <row r="214" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A214" s="4" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B214" s="5">
         <v>46132.589016666665</v>
       </c>
       <c r="C214" s="6"/>
       <c r="D214" s="5">
-        <v>46219.16942784722</v>
+        <v>46226.16770928241</v>
       </c>
       <c r="E214" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="F214" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G214" s="6" t="s">
         <v>457</v>
       </c>
-      <c r="F214" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G214" s="6" t="s">
+      <c r="H214" s="6" t="s">
         <v>458</v>
-      </c>
-      <c r="H214" s="6" t="s">
-        <v>459</v>
       </c>
       <c r="I214" s="6"/>
       <c r="J214" s="5">
@@ -13912,13 +13912,13 @@
         <v>26</v>
       </c>
       <c r="N214" s="6" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="O214" s="6" t="s">
         <v>430</v>
       </c>
       <c r="P214" s="6" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="Q214" s="5">
         <v>46226</v>
@@ -13927,7 +13927,7 @@
         <v>46226</v>
       </c>
       <c r="S214" s="12" t="s">
-        <v>433</v>
+        <v>460</v>
       </c>
       <c r="T214" s="6">
         <v>0</v>
@@ -13945,7 +13945,7 @@
       </c>
       <c r="C215" s="9"/>
       <c r="D215" s="8">
-        <v>46196.91388565973</v>
+        <v>46226.167681631945</v>
       </c>
       <c r="E215" s="9" t="s">
         <v>172</v>
@@ -13954,10 +13954,10 @@
         <v>26</v>
       </c>
       <c r="G215" s="9" t="s">
+        <v>457</v>
+      </c>
+      <c r="H215" s="9" t="s">
         <v>458</v>
-      </c>
-      <c r="H215" s="9" t="s">
-        <v>459</v>
       </c>
       <c r="I215" s="9"/>
       <c r="J215" s="8">
@@ -13973,7 +13973,7 @@
         <v>26</v>
       </c>
       <c r="N215" s="9" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="O215" s="9" t="s">
         <v>172</v>
@@ -13996,7 +13996,7 @@
       </c>
       <c r="C216" s="6"/>
       <c r="D216" s="5">
-        <v>46196.91389173611</v>
+        <v>46226.167683541666</v>
       </c>
       <c r="E216" s="6" t="s">
         <v>172</v>
@@ -14005,10 +14005,10 @@
         <v>26</v>
       </c>
       <c r="G216" s="6" t="s">
+        <v>457</v>
+      </c>
+      <c r="H216" s="6" t="s">
         <v>458</v>
-      </c>
-      <c r="H216" s="6" t="s">
-        <v>459</v>
       </c>
       <c r="I216" s="6"/>
       <c r="J216" s="5">
@@ -14024,7 +14024,7 @@
         <v>26</v>
       </c>
       <c r="N216" s="6" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="O216" s="6" t="s">
         <v>172</v>
@@ -14047,7 +14047,7 @@
       </c>
       <c r="C217" s="9"/>
       <c r="D217" s="8">
-        <v>46196.91390143518</v>
+        <v>46226.16768490741</v>
       </c>
       <c r="E217" s="9" t="s">
         <v>172</v>
@@ -14056,10 +14056,10 @@
         <v>26</v>
       </c>
       <c r="G217" s="9" t="s">
+        <v>457</v>
+      </c>
+      <c r="H217" s="9" t="s">
         <v>458</v>
-      </c>
-      <c r="H217" s="9" t="s">
-        <v>459</v>
       </c>
       <c r="I217" s="9"/>
       <c r="J217" s="8">
@@ -14075,7 +14075,7 @@
         <v>26</v>
       </c>
       <c r="N217" s="9" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="O217" s="9" t="s">
         <v>172</v>
@@ -14098,7 +14098,7 @@
       </c>
       <c r="C218" s="6"/>
       <c r="D218" s="5">
-        <v>46196.913907152775</v>
+        <v>46226.16768748843</v>
       </c>
       <c r="E218" s="6" t="s">
         <v>172</v>
@@ -14107,10 +14107,10 @@
         <v>26</v>
       </c>
       <c r="G218" s="6" t="s">
+        <v>457</v>
+      </c>
+      <c r="H218" s="6" t="s">
         <v>458</v>
-      </c>
-      <c r="H218" s="6" t="s">
-        <v>459</v>
       </c>
       <c r="I218" s="6"/>
       <c r="J218" s="5">
@@ -14126,7 +14126,7 @@
         <v>26</v>
       </c>
       <c r="N218" s="6" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="O218" s="6" t="s">
         <v>172</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C219" s="9"/>
       <c r="D219" s="8">
-        <v>46196.91391674768</v>
+        <v>46226.16768627315</v>
       </c>
       <c r="E219" s="9" t="s">
         <v>172</v>
@@ -14158,10 +14158,10 @@
         <v>26</v>
       </c>
       <c r="G219" s="9" t="s">
+        <v>457</v>
+      </c>
+      <c r="H219" s="9" t="s">
         <v>458</v>
-      </c>
-      <c r="H219" s="9" t="s">
-        <v>459</v>
       </c>
       <c r="I219" s="9"/>
       <c r="J219" s="8">
@@ -14177,7 +14177,7 @@
         <v>26</v>
       </c>
       <c r="N219" s="9" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="O219" s="9" t="s">
         <v>172</v>
@@ -14200,7 +14200,7 @@
       </c>
       <c r="C220" s="6"/>
       <c r="D220" s="5">
-        <v>46196.913933171294</v>
+        <v>46226.16768871528</v>
       </c>
       <c r="E220" s="6" t="s">
         <v>172</v>
@@ -14209,10 +14209,10 @@
         <v>26</v>
       </c>
       <c r="G220" s="6" t="s">
+        <v>457</v>
+      </c>
+      <c r="H220" s="6" t="s">
         <v>458</v>
-      </c>
-      <c r="H220" s="6" t="s">
-        <v>459</v>
       </c>
       <c r="I220" s="6"/>
       <c r="J220" s="5">
@@ -14228,7 +14228,7 @@
         <v>26</v>
       </c>
       <c r="N220" s="6" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="O220" s="6" t="s">
         <v>172</v>
@@ -14251,19 +14251,19 @@
       </c>
       <c r="C221" s="9"/>
       <c r="D221" s="8">
-        <v>46196.913939861115</v>
+        <v>46226.167689988426</v>
       </c>
       <c r="E221" s="9" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="F221" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G221" s="9" t="s">
+        <v>457</v>
+      </c>
+      <c r="H221" s="9" t="s">
         <v>458</v>
-      </c>
-      <c r="H221" s="9" t="s">
-        <v>459</v>
       </c>
       <c r="I221" s="9"/>
       <c r="J221" s="8">
@@ -14279,7 +14279,7 @@
         <v>26</v>
       </c>
       <c r="N221" s="9" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="O221" s="9" t="s">
         <v>172</v>
@@ -14302,7 +14302,7 @@
       </c>
       <c r="C222" s="6"/>
       <c r="D222" s="5">
-        <v>46196.91395613426</v>
+        <v>46226.167691435185</v>
       </c>
       <c r="E222" s="6" t="s">
         <v>172</v>
@@ -14311,10 +14311,10 @@
         <v>26</v>
       </c>
       <c r="G222" s="6" t="s">
+        <v>457</v>
+      </c>
+      <c r="H222" s="6" t="s">
         <v>458</v>
-      </c>
-      <c r="H222" s="6" t="s">
-        <v>459</v>
       </c>
       <c r="I222" s="6"/>
       <c r="J222" s="5">
@@ -14330,7 +14330,7 @@
         <v>26</v>
       </c>
       <c r="N222" s="6" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="O222" s="6" t="s">
         <v>172</v>
@@ -14353,7 +14353,7 @@
       </c>
       <c r="C223" s="9"/>
       <c r="D223" s="8">
-        <v>46196.9139649537</v>
+        <v>46226.167693020834</v>
       </c>
       <c r="E223" s="9" t="s">
         <v>172</v>
@@ -14362,10 +14362,10 @@
         <v>26</v>
       </c>
       <c r="G223" s="9" t="s">
+        <v>457</v>
+      </c>
+      <c r="H223" s="9" t="s">
         <v>458</v>
-      </c>
-      <c r="H223" s="9" t="s">
-        <v>459</v>
       </c>
       <c r="I223" s="9"/>
       <c r="J223" s="8">
@@ -14381,7 +14381,7 @@
         <v>26</v>
       </c>
       <c r="N223" s="9" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="O223" s="9" t="s">
         <v>172</v>
@@ -14404,7 +14404,7 @@
       </c>
       <c r="C224" s="6"/>
       <c r="D224" s="5">
-        <v>46196.91397201389</v>
+        <v>46226.16769430556</v>
       </c>
       <c r="E224" s="6" t="s">
         <v>172</v>
@@ -14413,10 +14413,10 @@
         <v>26</v>
       </c>
       <c r="G224" s="6" t="s">
+        <v>457</v>
+      </c>
+      <c r="H224" s="6" t="s">
         <v>458</v>
-      </c>
-      <c r="H224" s="6" t="s">
-        <v>459</v>
       </c>
       <c r="I224" s="6"/>
       <c r="J224" s="5">
@@ -14432,7 +14432,7 @@
         <v>26</v>
       </c>
       <c r="N224" s="6" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="O224" s="6" t="s">
         <v>172</v>
@@ -14455,7 +14455,7 @@
       </c>
       <c r="C225" s="9"/>
       <c r="D225" s="8">
-        <v>46196.91398435185</v>
+        <v>46226.16769577547</v>
       </c>
       <c r="E225" s="9" t="s">
         <v>172</v>
@@ -14464,10 +14464,10 @@
         <v>26</v>
       </c>
       <c r="G225" s="9" t="s">
+        <v>457</v>
+      </c>
+      <c r="H225" s="9" t="s">
         <v>458</v>
-      </c>
-      <c r="H225" s="9" t="s">
-        <v>459</v>
       </c>
       <c r="I225" s="9"/>
       <c r="J225" s="8">
@@ -14483,7 +14483,7 @@
         <v>26</v>
       </c>
       <c r="N225" s="9" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="O225" s="9" t="s">
         <v>172</v>
@@ -14506,7 +14506,7 @@
       </c>
       <c r="C226" s="6"/>
       <c r="D226" s="5">
-        <v>46196.91399296296</v>
+        <v>46226.16769702546</v>
       </c>
       <c r="E226" s="6" t="s">
         <v>172</v>
@@ -14515,10 +14515,10 @@
         <v>26</v>
       </c>
       <c r="G226" s="6" t="s">
+        <v>457</v>
+      </c>
+      <c r="H226" s="6" t="s">
         <v>458</v>
-      </c>
-      <c r="H226" s="6" t="s">
-        <v>459</v>
       </c>
       <c r="I226" s="6"/>
       <c r="J226" s="5">
@@ -14534,7 +14534,7 @@
         <v>26</v>
       </c>
       <c r="N226" s="6" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="O226" s="6" t="s">
         <v>172</v>
@@ -14557,7 +14557,7 @@
       </c>
       <c r="C227" s="9"/>
       <c r="D227" s="8">
-        <v>46196.913999675926</v>
+        <v>46226.16769825231</v>
       </c>
       <c r="E227" s="9" t="s">
         <v>172</v>
@@ -14566,10 +14566,10 @@
         <v>26</v>
       </c>
       <c r="G227" s="9" t="s">
+        <v>457</v>
+      </c>
+      <c r="H227" s="9" t="s">
         <v>458</v>
-      </c>
-      <c r="H227" s="9" t="s">
-        <v>459</v>
       </c>
       <c r="I227" s="9"/>
       <c r="J227" s="8">
@@ -14585,7 +14585,7 @@
         <v>26</v>
       </c>
       <c r="N227" s="9" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="O227" s="9" t="s">
         <v>172</v>
@@ -14608,7 +14608,7 @@
       </c>
       <c r="C228" s="6"/>
       <c r="D228" s="5">
-        <v>46196.914015358794</v>
+        <v>46226.16769980324</v>
       </c>
       <c r="E228" s="6" t="s">
         <v>172</v>
@@ -14617,10 +14617,10 @@
         <v>26</v>
       </c>
       <c r="G228" s="6" t="s">
+        <v>457</v>
+      </c>
+      <c r="H228" s="6" t="s">
         <v>458</v>
-      </c>
-      <c r="H228" s="6" t="s">
-        <v>459</v>
       </c>
       <c r="I228" s="6"/>
       <c r="J228" s="5">
@@ -14636,7 +14636,7 @@
         <v>26</v>
       </c>
       <c r="N228" s="6" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="O228" s="6" t="s">
         <v>172</v>
@@ -14659,19 +14659,19 @@
       </c>
       <c r="C229" s="9"/>
       <c r="D229" s="8">
-        <v>46196.9140217824</v>
+        <v>46226.16770127315</v>
       </c>
       <c r="E229" s="9" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="F229" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G229" s="9" t="s">
+        <v>457</v>
+      </c>
+      <c r="H229" s="9" t="s">
         <v>458</v>
-      </c>
-      <c r="H229" s="9" t="s">
-        <v>459</v>
       </c>
       <c r="I229" s="9"/>
       <c r="J229" s="8">
@@ -14687,13 +14687,13 @@
         <v>26</v>
       </c>
       <c r="N229" s="9" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="O229" s="9" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="P229" s="9" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="Q229" s="9"/>
       <c r="R229" s="9"/>
@@ -14710,7 +14710,7 @@
       </c>
       <c r="C230" s="6"/>
       <c r="D230" s="5">
-        <v>46196.91403721065</v>
+        <v>46226.16770262731</v>
       </c>
       <c r="E230" s="6" t="s">
         <v>172</v>
@@ -14719,10 +14719,10 @@
         <v>26</v>
       </c>
       <c r="G230" s="6" t="s">
+        <v>457</v>
+      </c>
+      <c r="H230" s="6" t="s">
         <v>458</v>
-      </c>
-      <c r="H230" s="6" t="s">
-        <v>459</v>
       </c>
       <c r="I230" s="6"/>
       <c r="J230" s="5">
@@ -14738,7 +14738,7 @@
         <v>26</v>
       </c>
       <c r="N230" s="6" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="O230" s="6" t="s">
         <v>271</v>
@@ -14789,10 +14789,10 @@
         <v>26</v>
       </c>
       <c r="N231" s="9" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="O231" s="9" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="P231" s="9" t="s">
         <v>479</v>
@@ -14804,7 +14804,7 @@
         <v>46227</v>
       </c>
       <c r="S231" s="12" t="s">
-        <v>433</v>
+        <v>460</v>
       </c>
       <c r="T231" s="9">
         <v>0</v>
@@ -15159,7 +15159,7 @@
         <v>478</v>
       </c>
       <c r="O238" s="6" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="P238" s="6" t="s">
         <v>172</v>
@@ -15539,7 +15539,7 @@
         <v>46223.55763899305</v>
       </c>
       <c r="E246" s="6" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="F246" s="6" t="s">
         <v>26</v>
@@ -15567,7 +15567,7 @@
         <v>478</v>
       </c>
       <c r="O246" s="6" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="P246" s="6" t="s">
         <v>172</v>
@@ -15668,7 +15668,7 @@
         <v>26</v>
       </c>
       <c r="N248" s="6" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="O248" s="6" t="s">
         <v>478</v>
@@ -15683,7 +15683,7 @@
         <v>46230</v>
       </c>
       <c r="S248" s="12" t="s">
-        <v>433</v>
+        <v>460</v>
       </c>
       <c r="T248" s="6">
         <v>0</v>
@@ -16446,7 +16446,7 @@
         <v>497</v>
       </c>
       <c r="O263" s="9" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="P263" s="9" t="s">
         <v>172</v>
@@ -16545,7 +16545,7 @@
         <v>26</v>
       </c>
       <c r="N265" s="9" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="O265" s="9" t="s">
         <v>497</v>
@@ -16560,7 +16560,7 @@
         <v>46231</v>
       </c>
       <c r="S265" s="12" t="s">
-        <v>433</v>
+        <v>460</v>
       </c>
       <c r="T265" s="9">
         <v>0</v>

--- a/data/50001541 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001541 - XEMORTIZ MINERA FRISCO.xlsx
@@ -1513,64 +1513,64 @@
     <t>Logistica:,Despacho</t>
   </si>
   <si>
+    <t>1214137717389627</t>
+  </si>
+  <si>
+    <t>1214137717389628</t>
+  </si>
+  <si>
+    <t>1214137717389629</t>
+  </si>
+  <si>
+    <t>1214137717389630</t>
+  </si>
+  <si>
+    <t>1214137717389631</t>
+  </si>
+  <si>
+    <t>1214137717389632</t>
+  </si>
+  <si>
+    <t>1214137717389633</t>
+  </si>
+  <si>
+    <t>1214137717389634</t>
+  </si>
+  <si>
+    <t>1214137717389635</t>
+  </si>
+  <si>
+    <t>1214137717389636</t>
+  </si>
+  <si>
+    <t>1214137717389637</t>
+  </si>
+  <si>
+    <t>1214137717389638</t>
+  </si>
+  <si>
+    <t>1214137717389639</t>
+  </si>
+  <si>
+    <t>1214137717389640</t>
+  </si>
+  <si>
+    <t>1214137717389641</t>
+  </si>
+  <si>
+    <t>1214137717389642</t>
+  </si>
+  <si>
+    <t>1214138721009959</t>
+  </si>
+  <si>
+    <t>Despacho</t>
+  </si>
+  <si>
+    <t>Logistica:,Gestion,Costos</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1214137717389627</t>
-  </si>
-  <si>
-    <t>1214137717389628</t>
-  </si>
-  <si>
-    <t>1214137717389629</t>
-  </si>
-  <si>
-    <t>1214137717389630</t>
-  </si>
-  <si>
-    <t>1214137717389631</t>
-  </si>
-  <si>
-    <t>1214137717389632</t>
-  </si>
-  <si>
-    <t>1214137717389633</t>
-  </si>
-  <si>
-    <t>1214137717389634</t>
-  </si>
-  <si>
-    <t>1214137717389635</t>
-  </si>
-  <si>
-    <t>1214137717389636</t>
-  </si>
-  <si>
-    <t>1214137717389637</t>
-  </si>
-  <si>
-    <t>1214137717389638</t>
-  </si>
-  <si>
-    <t>1214137717389639</t>
-  </si>
-  <si>
-    <t>1214137717389640</t>
-  </si>
-  <si>
-    <t>1214137717389641</t>
-  </si>
-  <si>
-    <t>1214137717389642</t>
-  </si>
-  <si>
-    <t>1214138721009959</t>
-  </si>
-  <si>
-    <t>Despacho</t>
-  </si>
-  <si>
-    <t>Logistica:,Gestion,Costos</t>
   </si>
   <si>
     <t>1214137717389643</t>
@@ -15638,7 +15638,7 @@
       </c>
       <c r="C248" s="6"/>
       <c r="D248" s="5">
-        <v>46230.16810980324</v>
+        <v>46231.18365072917</v>
       </c>
       <c r="E248" s="6" t="s">
         <v>496</v>
@@ -15682,8 +15682,8 @@
       <c r="R248" s="5">
         <v>46230</v>
       </c>
-      <c r="S248" s="12" t="s">
-        <v>500</v>
+      <c r="S248" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T248" s="6">
         <v>0</v>
@@ -15694,7 +15694,7 @@
     </row>
     <row r="249" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A249" s="7" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B249" s="8">
         <v>46132.634024432875</v>
@@ -15745,7 +15745,7 @@
     </row>
     <row r="250" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A250" s="4" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B250" s="5">
         <v>46132.634032685186</v>
@@ -15796,7 +15796,7 @@
     </row>
     <row r="251" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A251" s="7" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B251" s="8">
         <v>46132.63404001157</v>
@@ -15847,7 +15847,7 @@
     </row>
     <row r="252" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A252" s="4" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B252" s="5">
         <v>46132.63404659722</v>
@@ -15898,7 +15898,7 @@
     </row>
     <row r="253" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A253" s="7" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B253" s="8">
         <v>46132.6340537037</v>
@@ -15949,7 +15949,7 @@
     </row>
     <row r="254" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A254" s="4" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B254" s="5">
         <v>46132.63406115741</v>
@@ -16000,7 +16000,7 @@
     </row>
     <row r="255" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A255" s="7" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B255" s="8">
         <v>46132.63406662037</v>
@@ -16051,7 +16051,7 @@
     </row>
     <row r="256" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A256" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B256" s="5">
         <v>46132.634072395835</v>
@@ -16102,7 +16102,7 @@
     </row>
     <row r="257" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A257" s="7" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B257" s="8">
         <v>46132.6340770949</v>
@@ -16153,7 +16153,7 @@
     </row>
     <row r="258" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A258" s="4" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B258" s="5">
         <v>46132.634082777775</v>
@@ -16204,7 +16204,7 @@
     </row>
     <row r="259" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A259" s="7" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B259" s="8">
         <v>46132.63408899306</v>
@@ -16255,7 +16255,7 @@
     </row>
     <row r="260" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A260" s="4" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B260" s="5">
         <v>46132.63409545139</v>
@@ -16306,7 +16306,7 @@
     </row>
     <row r="261" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A261" s="7" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B261" s="8">
         <v>46132.63410087963</v>
@@ -16357,7 +16357,7 @@
     </row>
     <row r="262" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A262" s="4" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B262" s="5">
         <v>46132.63410688657</v>
@@ -16408,7 +16408,7 @@
     </row>
     <row r="263" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A263" s="7" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B263" s="8">
         <v>46132.6341133449</v>
@@ -16459,7 +16459,7 @@
     </row>
     <row r="264" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A264" s="4" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B264" s="5">
         <v>46132.63411966435</v>
@@ -16510,17 +16510,17 @@
     </row>
     <row r="265" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A265" s="7" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B265" s="8">
         <v>46132.58903189815</v>
       </c>
       <c r="C265" s="9"/>
       <c r="D265" s="8">
-        <v>46229.54992409723</v>
+        <v>46231.16782274305</v>
       </c>
       <c r="E265" s="9" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F265" s="9" t="s">
         <v>26</v>
@@ -16551,7 +16551,7 @@
         <v>496</v>
       </c>
       <c r="P265" s="9" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="Q265" s="8">
         <v>46231</v>
@@ -16560,7 +16560,7 @@
         <v>46231</v>
       </c>
       <c r="S265" s="12" t="s">
-        <v>500</v>
+        <v>519</v>
       </c>
       <c r="T265" s="9">
         <v>0</v>
@@ -16578,7 +16578,7 @@
       </c>
       <c r="C266" s="6"/>
       <c r="D266" s="5">
-        <v>46196.91446424769</v>
+        <v>46231.16777215278</v>
       </c>
       <c r="E266" s="6" t="s">
         <v>172</v>
@@ -16606,7 +16606,7 @@
         <v>26</v>
       </c>
       <c r="N266" s="6" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="O266" s="6" t="s">
         <v>172</v>
@@ -16629,7 +16629,7 @@
       </c>
       <c r="C267" s="9"/>
       <c r="D267" s="8">
-        <v>46196.91447116898</v>
+        <v>46231.16777465278</v>
       </c>
       <c r="E267" s="9" t="s">
         <v>172</v>
@@ -16657,7 +16657,7 @@
         <v>26</v>
       </c>
       <c r="N267" s="9" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="O267" s="9" t="s">
         <v>172</v>
@@ -16680,7 +16680,7 @@
       </c>
       <c r="C268" s="6"/>
       <c r="D268" s="5">
-        <v>46196.914480694446</v>
+        <v>46231.16777594907</v>
       </c>
       <c r="E268" s="6" t="s">
         <v>172</v>
@@ -16708,7 +16708,7 @@
         <v>26</v>
       </c>
       <c r="N268" s="6" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="O268" s="6" t="s">
         <v>172</v>
@@ -16731,7 +16731,7 @@
       </c>
       <c r="C269" s="9"/>
       <c r="D269" s="8">
-        <v>46196.91449018518</v>
+        <v>46231.16777724537</v>
       </c>
       <c r="E269" s="9" t="s">
         <v>172</v>
@@ -16759,7 +16759,7 @@
         <v>26</v>
       </c>
       <c r="N269" s="9" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="O269" s="9" t="s">
         <v>172</v>
@@ -16782,7 +16782,7 @@
       </c>
       <c r="C270" s="6"/>
       <c r="D270" s="5">
-        <v>46196.91449658565</v>
+        <v>46231.16777849537</v>
       </c>
       <c r="E270" s="6" t="s">
         <v>172</v>
@@ -16810,7 +16810,7 @@
         <v>26</v>
       </c>
       <c r="N270" s="6" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="O270" s="6" t="s">
         <v>172</v>
@@ -16833,7 +16833,7 @@
       </c>
       <c r="C271" s="9"/>
       <c r="D271" s="8">
-        <v>46196.914503645836</v>
+        <v>46231.167779745374</v>
       </c>
       <c r="E271" s="9" t="s">
         <v>172</v>
@@ -16861,7 +16861,7 @@
         <v>26</v>
       </c>
       <c r="N271" s="9" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="O271" s="9" t="s">
         <v>172</v>
@@ -16884,7 +16884,7 @@
       </c>
       <c r="C272" s="6"/>
       <c r="D272" s="5">
-        <v>46196.91450951389</v>
+        <v>46231.16778097222</v>
       </c>
       <c r="E272" s="6" t="s">
         <v>172</v>
@@ -16912,7 +16912,7 @@
         <v>26</v>
       </c>
       <c r="N272" s="6" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="O272" s="6" t="s">
         <v>172</v>
@@ -16935,7 +16935,7 @@
       </c>
       <c r="C273" s="9"/>
       <c r="D273" s="8">
-        <v>46196.91451931713</v>
+        <v>46231.16778246527</v>
       </c>
       <c r="E273" s="9" t="s">
         <v>172</v>
@@ -16963,7 +16963,7 @@
         <v>26</v>
       </c>
       <c r="N273" s="9" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="O273" s="9" t="s">
         <v>172</v>
@@ -16986,7 +16986,7 @@
       </c>
       <c r="C274" s="6"/>
       <c r="D274" s="5">
-        <v>46196.914524629625</v>
+        <v>46231.16780969907</v>
       </c>
       <c r="E274" s="6" t="s">
         <v>172</v>
@@ -17014,7 +17014,7 @@
         <v>26</v>
       </c>
       <c r="N274" s="6" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="O274" s="6" t="s">
         <v>172</v>
@@ -17037,7 +17037,7 @@
       </c>
       <c r="C275" s="9"/>
       <c r="D275" s="8">
-        <v>46196.91452907407</v>
+        <v>46231.16781326389</v>
       </c>
       <c r="E275" s="9" t="s">
         <v>172</v>
@@ -17065,7 +17065,7 @@
         <v>26</v>
       </c>
       <c r="N275" s="9" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="O275" s="9" t="s">
         <v>172</v>
@@ -17088,7 +17088,7 @@
       </c>
       <c r="C276" s="6"/>
       <c r="D276" s="5">
-        <v>46196.91453917824</v>
+        <v>46231.16781449074</v>
       </c>
       <c r="E276" s="6" t="s">
         <v>172</v>
@@ -17116,7 +17116,7 @@
         <v>26</v>
       </c>
       <c r="N276" s="6" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="O276" s="6" t="s">
         <v>172</v>
@@ -17139,7 +17139,7 @@
       </c>
       <c r="C277" s="9"/>
       <c r="D277" s="8">
-        <v>46196.91454204862</v>
+        <v>46231.16781590278</v>
       </c>
       <c r="E277" s="9" t="s">
         <v>172</v>
@@ -17167,7 +17167,7 @@
         <v>26</v>
       </c>
       <c r="N277" s="9" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="O277" s="9" t="s">
         <v>172</v>
@@ -17190,7 +17190,7 @@
       </c>
       <c r="C278" s="6"/>
       <c r="D278" s="5">
-        <v>46196.914551724534</v>
+        <v>46231.16781758102</v>
       </c>
       <c r="E278" s="6" t="s">
         <v>172</v>
@@ -17218,7 +17218,7 @@
         <v>26</v>
       </c>
       <c r="N278" s="6" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="O278" s="6" t="s">
         <v>172</v>
@@ -17241,7 +17241,7 @@
       </c>
       <c r="C279" s="9"/>
       <c r="D279" s="8">
-        <v>46196.91457195602</v>
+        <v>46231.167818877315</v>
       </c>
       <c r="E279" s="9" t="s">
         <v>172</v>
@@ -17269,7 +17269,7 @@
         <v>26</v>
       </c>
       <c r="N279" s="9" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="O279" s="9" t="s">
         <v>172</v>
@@ -17292,7 +17292,7 @@
       </c>
       <c r="C280" s="6"/>
       <c r="D280" s="5">
-        <v>46196.91458070602</v>
+        <v>46231.16782008102</v>
       </c>
       <c r="E280" s="6" t="s">
         <v>172</v>
@@ -17320,7 +17320,7 @@
         <v>26</v>
       </c>
       <c r="N280" s="6" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="O280" s="6" t="s">
         <v>172</v>
@@ -17343,7 +17343,7 @@
       </c>
       <c r="C281" s="9"/>
       <c r="D281" s="8">
-        <v>46196.91461018518</v>
+        <v>46231.16782137731</v>
       </c>
       <c r="E281" s="9" t="s">
         <v>172</v>
@@ -17371,7 +17371,7 @@
         <v>26</v>
       </c>
       <c r="N281" s="9" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="O281" s="9" t="s">
         <v>172</v>

--- a/data/50001541 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001541 - XEMORTIZ MINERA FRISCO.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3225" uniqueCount="547">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3225" uniqueCount="546">
   <si>
     <t>50001541 -  XEMORTIZ MINERA FRISCO</t>
   </si>
@@ -1568,9 +1568,6 @@
   </si>
   <si>
     <t>Logistica:,Gestion,Costos</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1214137717389643</t>
@@ -16517,7 +16514,7 @@
       </c>
       <c r="C265" s="9"/>
       <c r="D265" s="8">
-        <v>46231.16782274305</v>
+        <v>46232.197325057874</v>
       </c>
       <c r="E265" s="9" t="s">
         <v>517</v>
@@ -16559,8 +16556,8 @@
       <c r="R265" s="8">
         <v>46231</v>
       </c>
-      <c r="S265" s="12" t="s">
-        <v>519</v>
+      <c r="S265" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T265" s="9">
         <v>0</v>
@@ -16571,7 +16568,7 @@
     </row>
     <row r="266" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A266" s="4" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B266" s="5">
         <v>46132.63422869213</v>
@@ -16612,7 +16609,7 @@
         <v>172</v>
       </c>
       <c r="P266" s="6" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="Q266" s="6"/>
       <c r="R266" s="6"/>
@@ -16622,7 +16619,7 @@
     </row>
     <row r="267" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A267" s="7" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B267" s="8">
         <v>46132.63423491898</v>
@@ -16663,7 +16660,7 @@
         <v>172</v>
       </c>
       <c r="P267" s="9" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="Q267" s="9"/>
       <c r="R267" s="9"/>
@@ -16673,7 +16670,7 @@
     </row>
     <row r="268" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A268" s="4" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B268" s="5">
         <v>46132.634240960644</v>
@@ -16714,7 +16711,7 @@
         <v>172</v>
       </c>
       <c r="P268" s="6" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="Q268" s="6"/>
       <c r="R268" s="6"/>
@@ -16724,7 +16721,7 @@
     </row>
     <row r="269" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A269" s="7" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B269" s="8">
         <v>46132.63424789352</v>
@@ -16765,7 +16762,7 @@
         <v>172</v>
       </c>
       <c r="P269" s="9" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="Q269" s="9"/>
       <c r="R269" s="9"/>
@@ -16775,7 +16772,7 @@
     </row>
     <row r="270" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A270" s="4" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B270" s="5">
         <v>46132.634254386576</v>
@@ -16816,7 +16813,7 @@
         <v>172</v>
       </c>
       <c r="P270" s="6" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="Q270" s="6"/>
       <c r="R270" s="6"/>
@@ -16826,7 +16823,7 @@
     </row>
     <row r="271" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A271" s="7" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B271" s="8">
         <v>46132.634260810184</v>
@@ -16867,7 +16864,7 @@
         <v>172</v>
       </c>
       <c r="P271" s="9" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="Q271" s="9"/>
       <c r="R271" s="9"/>
@@ -16877,7 +16874,7 @@
     </row>
     <row r="272" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A272" s="4" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B272" s="5">
         <v>46132.634267256944</v>
@@ -16918,7 +16915,7 @@
         <v>172</v>
       </c>
       <c r="P272" s="6" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="Q272" s="6"/>
       <c r="R272" s="6"/>
@@ -16928,7 +16925,7 @@
     </row>
     <row r="273" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A273" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B273" s="8">
         <v>46132.63427122685</v>
@@ -16969,7 +16966,7 @@
         <v>172</v>
       </c>
       <c r="P273" s="9" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="Q273" s="9"/>
       <c r="R273" s="9"/>
@@ -16979,7 +16976,7 @@
     </row>
     <row r="274" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A274" s="4" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B274" s="5">
         <v>46132.634276365745</v>
@@ -17020,7 +17017,7 @@
         <v>172</v>
       </c>
       <c r="P274" s="6" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="Q274" s="6"/>
       <c r="R274" s="6"/>
@@ -17030,7 +17027,7 @@
     </row>
     <row r="275" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A275" s="7" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B275" s="8">
         <v>46132.63428099537</v>
@@ -17071,7 +17068,7 @@
         <v>172</v>
       </c>
       <c r="P275" s="9" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="Q275" s="9"/>
       <c r="R275" s="9"/>
@@ -17081,7 +17078,7 @@
     </row>
     <row r="276" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A276" s="4" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B276" s="5">
         <v>46132.63428524305</v>
@@ -17122,7 +17119,7 @@
         <v>172</v>
       </c>
       <c r="P276" s="6" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="Q276" s="6"/>
       <c r="R276" s="6"/>
@@ -17132,7 +17129,7 @@
     </row>
     <row r="277" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A277" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B277" s="8">
         <v>46132.63429103009</v>
@@ -17173,7 +17170,7 @@
         <v>172</v>
       </c>
       <c r="P277" s="9" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="Q277" s="9"/>
       <c r="R277" s="9"/>
@@ -17183,7 +17180,7 @@
     </row>
     <row r="278" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A278" s="4" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B278" s="5">
         <v>46132.63429523148</v>
@@ -17224,7 +17221,7 @@
         <v>172</v>
       </c>
       <c r="P278" s="6" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="Q278" s="6"/>
       <c r="R278" s="6"/>
@@ -17234,7 +17231,7 @@
     </row>
     <row r="279" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A279" s="7" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B279" s="8">
         <v>46132.63430358796</v>
@@ -17275,7 +17272,7 @@
         <v>172</v>
       </c>
       <c r="P279" s="9" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="Q279" s="9"/>
       <c r="R279" s="9"/>
@@ -17285,7 +17282,7 @@
     </row>
     <row r="280" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A280" s="4" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B280" s="5">
         <v>46132.63431148148</v>
@@ -17326,7 +17323,7 @@
         <v>172</v>
       </c>
       <c r="P280" s="6" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="Q280" s="6"/>
       <c r="R280" s="6"/>
@@ -17336,7 +17333,7 @@
     </row>
     <row r="281" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A281" s="7" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B281" s="8">
         <v>46132.63437663195</v>
@@ -17377,7 +17374,7 @@
         <v>172</v>
       </c>
       <c r="P281" s="9" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="Q281" s="9"/>
       <c r="R281" s="9"/>
@@ -17387,7 +17384,7 @@
     </row>
     <row r="282" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A282" s="4" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B282" s="5">
         <v>46132.589037604164</v>
@@ -17397,7 +17394,7 @@
         <v>46133.59235670139</v>
       </c>
       <c r="E282" s="6" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="F282" s="6" t="s">
         <v>25</v>
@@ -17421,7 +17418,7 @@
         <v>26</v>
       </c>
       <c r="O282" s="6" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="P282" s="6" t="s">
         <v>26</v>
@@ -17434,7 +17431,7 @@
     </row>
     <row r="283" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A283" s="7" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B283" s="8">
         <v>46132.5890406713</v>
@@ -17444,16 +17441,16 @@
         <v>46134.57925581018</v>
       </c>
       <c r="E283" s="9" t="s">
+        <v>540</v>
+      </c>
+      <c r="F283" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G283" s="9" t="s">
         <v>541</v>
       </c>
-      <c r="F283" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G283" s="9" t="s">
+      <c r="H283" s="9" t="s">
         <v>542</v>
-      </c>
-      <c r="H283" s="9" t="s">
-        <v>543</v>
       </c>
       <c r="I283" s="8">
         <v>46232</v>
@@ -17471,13 +17468,13 @@
         <v>26</v>
       </c>
       <c r="N283" s="9" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="O283" s="9" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="P283" s="9" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="Q283" s="8">
         <v>46240</v>
@@ -17497,7 +17494,7 @@
     </row>
     <row r="284" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A284" s="4" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B284" s="5">
         <v>46132.58904559028</v>
@@ -17507,16 +17504,16 @@
         <v>46198.65442142361</v>
       </c>
       <c r="E284" s="6" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="F284" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G284" s="6" t="s">
+        <v>541</v>
+      </c>
+      <c r="H284" s="6" t="s">
         <v>542</v>
-      </c>
-      <c r="H284" s="6" t="s">
-        <v>543</v>
       </c>
       <c r="I284" s="5">
         <v>46232</v>
@@ -17534,13 +17531,13 @@
         <v>26</v>
       </c>
       <c r="N284" s="6" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="O284" s="6" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="P284" s="6" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="Q284" s="5">
         <v>46240</v>

--- a/data/50001541 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001541 - XEMORTIZ MINERA FRISCO.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3225" uniqueCount="546">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3225" uniqueCount="547">
   <si>
     <t>50001541 -  XEMORTIZ MINERA FRISCO</t>
   </si>
@@ -1643,6 +1643,9 @@
   </si>
   <si>
     <t xml:space="preserve">Despacho,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 ,OT 4307 ZVN 1-9-86/2 </t>
+  </si>
+  <si>
+    <t>Media</t>
   </si>
   <si>
     <t>1214138801687063</t>
@@ -17438,7 +17441,7 @@
       </c>
       <c r="C283" s="9"/>
       <c r="D283" s="8">
-        <v>46134.57925581018</v>
+        <v>46233.1676958912</v>
       </c>
       <c r="E283" s="9" t="s">
         <v>540</v>
@@ -17482,8 +17485,8 @@
       <c r="R283" s="8">
         <v>46232</v>
       </c>
-      <c r="S283" s="11" t="s">
-        <v>96</v>
+      <c r="S283" s="12" t="s">
+        <v>544</v>
       </c>
       <c r="T283" s="9">
         <v>0</v>
@@ -17494,17 +17497,17 @@
     </row>
     <row r="284" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A284" s="4" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B284" s="5">
         <v>46132.58904559028</v>
       </c>
       <c r="C284" s="6"/>
       <c r="D284" s="5">
-        <v>46198.65442142361</v>
+        <v>46233.1676958912</v>
       </c>
       <c r="E284" s="6" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="F284" s="6" t="s">
         <v>26</v>
@@ -17545,8 +17548,8 @@
       <c r="R284" s="5">
         <v>46232</v>
       </c>
-      <c r="S284" s="11" t="s">
-        <v>96</v>
+      <c r="S284" s="12" t="s">
+        <v>544</v>
       </c>
       <c r="T284" s="6">
         <v>0</v>

--- a/data/50001541 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001541 - XEMORTIZ MINERA FRISCO.xlsx
@@ -17441,7 +17441,7 @@
       </c>
       <c r="C283" s="9"/>
       <c r="D283" s="8">
-        <v>46233.1676958912</v>
+        <v>46240.1676943287</v>
       </c>
       <c r="E283" s="9" t="s">
         <v>540</v>
@@ -17504,7 +17504,7 @@
       </c>
       <c r="C284" s="6"/>
       <c r="D284" s="5">
-        <v>46233.1676958912</v>
+        <v>46240.16769664352</v>
       </c>
       <c r="E284" s="6" t="s">
         <v>546</v>

--- a/data/50001541 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001541 - XEMORTIZ MINERA FRISCO.xlsx
@@ -2275,13 +2275,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46132.58858372685</v>
+        <v>46132.42191706019</v>
       </c>
       <c r="C4" s="5">
-        <v>46133.88825172454</v>
+        <v>46133.721585057865</v>
       </c>
       <c r="D4" s="5">
-        <v>46134.54185469907</v>
+        <v>46134.37518803241</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -2324,13 +2324,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46132.58866263889</v>
+        <v>46132.421995972225</v>
       </c>
       <c r="C5" s="8">
-        <v>46140.62775625</v>
+        <v>46140.46108958333</v>
       </c>
       <c r="D5" s="8">
-        <v>46140.627878831016</v>
+        <v>46140.46121216435</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -2389,13 +2389,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46132.58866574074</v>
+        <v>46132.421999074075</v>
       </c>
       <c r="C6" s="5">
-        <v>46133.89152399305</v>
+        <v>46133.72485732639</v>
       </c>
       <c r="D6" s="5">
-        <v>46133.891525370374</v>
+        <v>46133.7248587037</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -2454,13 +2454,13 @@
         <v>36</v>
       </c>
       <c r="B7" s="8">
-        <v>46132.58866841435</v>
+        <v>46132.422001747684</v>
       </c>
       <c r="C7" s="8">
-        <v>46133.89329033565</v>
+        <v>46133.72662366898</v>
       </c>
       <c r="D7" s="8">
-        <v>46133.893291562505</v>
+        <v>46133.72662489583</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>37</v>
@@ -2519,13 +2519,13 @@
         <v>38</v>
       </c>
       <c r="B8" s="5">
-        <v>46132.58867106482</v>
+        <v>46132.42200439815</v>
       </c>
       <c r="C8" s="5">
-        <v>46133.89329489583</v>
+        <v>46133.72662822917</v>
       </c>
       <c r="D8" s="5">
-        <v>46198.65442141204</v>
+        <v>46198.487754745365</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>39</v>
@@ -2584,13 +2584,13 @@
         <v>41</v>
       </c>
       <c r="B9" s="8">
-        <v>46132.58867449074</v>
+        <v>46132.422007824076</v>
       </c>
       <c r="C9" s="8">
-        <v>46133.89330225694</v>
+        <v>46133.72663559028</v>
       </c>
       <c r="D9" s="8">
-        <v>46133.89330362268</v>
+        <v>46133.726636956024</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>42</v>
@@ -2649,13 +2649,13 @@
         <v>43</v>
       </c>
       <c r="B10" s="5">
-        <v>46132.58858978009</v>
+        <v>46132.42192311343</v>
       </c>
       <c r="C10" s="5">
-        <v>46198.65467643518</v>
+        <v>46198.48800976852</v>
       </c>
       <c r="D10" s="5">
-        <v>46198.65469435185</v>
+        <v>46198.48802768518</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>44</v>
@@ -2702,13 +2702,13 @@
         <v>46</v>
       </c>
       <c r="B11" s="8">
-        <v>46132.58867828704</v>
+        <v>46132.422011620365</v>
       </c>
       <c r="C11" s="8">
-        <v>46183.87023324074</v>
+        <v>46183.70356657407</v>
       </c>
       <c r="D11" s="8">
-        <v>46183.87025299769</v>
+        <v>46183.703586331016</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>47</v>
@@ -2767,13 +2767,13 @@
         <v>49</v>
       </c>
       <c r="B12" s="5">
-        <v>46132.588683553244</v>
+        <v>46132.42201688657</v>
       </c>
       <c r="C12" s="5">
-        <v>46157.54164365741</v>
+        <v>46157.374976990744</v>
       </c>
       <c r="D12" s="5">
-        <v>46157.541660393515</v>
+        <v>46157.37499372685</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>50</v>
@@ -2832,13 +2832,13 @@
         <v>52</v>
       </c>
       <c r="B13" s="8">
-        <v>46132.588688738426</v>
+        <v>46132.422022071754</v>
       </c>
       <c r="C13" s="8">
-        <v>46175.72854943287</v>
+        <v>46175.561882766204</v>
       </c>
       <c r="D13" s="8">
-        <v>46175.72856798611</v>
+        <v>46175.561901319445</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>53</v>
@@ -2897,13 +2897,13 @@
         <v>55</v>
       </c>
       <c r="B14" s="5">
-        <v>46132.58859509259</v>
+        <v>46132.42192842593</v>
       </c>
       <c r="C14" s="5">
-        <v>46196.640665405095</v>
+        <v>46196.473998738424</v>
       </c>
       <c r="D14" s="5">
-        <v>46196.64067877315</v>
+        <v>46196.47401210648</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>56</v>
@@ -2950,13 +2950,13 @@
         <v>58</v>
       </c>
       <c r="B15" s="8">
-        <v>46132.58869895834</v>
+        <v>46132.422032291666</v>
       </c>
       <c r="C15" s="8">
-        <v>46157.54328243056</v>
+        <v>46157.37661576389</v>
       </c>
       <c r="D15" s="8">
-        <v>46157.54329741898</v>
+        <v>46157.37663075232</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>59</v>
@@ -3015,13 +3015,13 @@
         <v>61</v>
       </c>
       <c r="B16" s="5">
-        <v>46132.58870399305</v>
+        <v>46132.42203732639</v>
       </c>
       <c r="C16" s="5">
-        <v>46157.5417655787</v>
+        <v>46157.37509891204</v>
       </c>
       <c r="D16" s="5">
-        <v>46223.602773969906</v>
+        <v>46223.43610730324</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>62</v>
@@ -3080,13 +3080,13 @@
         <v>66</v>
       </c>
       <c r="B17" s="8">
-        <v>46132.588709097225</v>
+        <v>46132.42204243055</v>
       </c>
       <c r="C17" s="8">
-        <v>46183.8703028125</v>
+        <v>46183.70363614583</v>
       </c>
       <c r="D17" s="8">
-        <v>46183.87031994213</v>
+        <v>46183.703653275465</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>67</v>
@@ -3145,13 +3145,13 @@
         <v>69</v>
       </c>
       <c r="B18" s="5">
-        <v>46132.588713819445</v>
+        <v>46132.42204715278</v>
       </c>
       <c r="C18" s="5">
-        <v>46140.62659734953</v>
+        <v>46140.459930682875</v>
       </c>
       <c r="D18" s="5">
-        <v>46237.535513043986</v>
+        <v>46237.368846377314</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>70</v>
@@ -3210,13 +3210,13 @@
         <v>73</v>
       </c>
       <c r="B19" s="8">
-        <v>46132.62809104167</v>
+        <v>46132.461424375</v>
       </c>
       <c r="C19" s="8">
-        <v>46140.62653898148</v>
+        <v>46140.459872314816</v>
       </c>
       <c r="D19" s="8">
-        <v>46237.53553451389</v>
+        <v>46237.368867847224</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>74</v>
@@ -3275,13 +3275,13 @@
         <v>76</v>
       </c>
       <c r="B20" s="5">
-        <v>46132.62798736111</v>
+        <v>46132.46132069445</v>
       </c>
       <c r="C20" s="5">
-        <v>46196.64064614583</v>
+        <v>46196.47397947917</v>
       </c>
       <c r="D20" s="5">
-        <v>46223.835789375</v>
+        <v>46223.669122708336</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>77</v>
@@ -3340,13 +3340,13 @@
         <v>79</v>
       </c>
       <c r="B21" s="8">
-        <v>46132.6280453125</v>
+        <v>46132.461378645836</v>
       </c>
       <c r="C21" s="8">
-        <v>46140.626452083336</v>
+        <v>46140.459785416664</v>
       </c>
       <c r="D21" s="8">
-        <v>46237.535560648146</v>
+        <v>46237.36889398148</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>80</v>
@@ -3405,11 +3405,11 @@
         <v>82</v>
       </c>
       <c r="B22" s="5">
-        <v>46132.588600312505</v>
+        <v>46132.42193364583</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46229.567146817135</v>
+        <v>46229.40048015046</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>83</v>
@@ -3454,13 +3454,13 @@
         <v>86</v>
       </c>
       <c r="B23" s="8">
-        <v>46132.588719548614</v>
+        <v>46132.42205288194</v>
       </c>
       <c r="C23" s="8">
-        <v>46157.543090798616</v>
+        <v>46157.376424131944</v>
       </c>
       <c r="D23" s="8">
-        <v>46157.54357984954</v>
+        <v>46157.376913182874</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>87</v>
@@ -3519,13 +3519,13 @@
         <v>91</v>
       </c>
       <c r="B24" s="5">
-        <v>46132.588724236106</v>
+        <v>46132.42205756945</v>
       </c>
       <c r="C24" s="5">
-        <v>46157.543350023145</v>
+        <v>46157.37668335648</v>
       </c>
       <c r="D24" s="5">
-        <v>46157.54335157407</v>
+        <v>46157.37668490741</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>92</v>
@@ -3580,13 +3580,13 @@
         <v>98</v>
       </c>
       <c r="B25" s="8">
-        <v>46132.58872892361</v>
+        <v>46132.42206225694</v>
       </c>
       <c r="C25" s="8">
-        <v>46157.54338710648</v>
+        <v>46157.37672043982</v>
       </c>
       <c r="D25" s="8">
-        <v>46157.543388425926</v>
+        <v>46157.376721759254</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>99</v>
@@ -3641,13 +3641,13 @@
         <v>101</v>
       </c>
       <c r="B26" s="5">
-        <v>46132.58873398148</v>
+        <v>46132.422067314816</v>
       </c>
       <c r="C26" s="5">
-        <v>46157.541870671295</v>
+        <v>46157.37520400463</v>
       </c>
       <c r="D26" s="5">
-        <v>46162.175749050926</v>
+        <v>46162.00908238426</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>102</v>
@@ -3706,13 +3706,13 @@
         <v>104</v>
       </c>
       <c r="B27" s="8">
-        <v>46132.58873894676</v>
+        <v>46132.4220722801</v>
       </c>
       <c r="C27" s="8">
-        <v>46157.54181472222</v>
+        <v>46157.37514805555</v>
       </c>
       <c r="D27" s="8">
-        <v>46157.541816655095</v>
+        <v>46157.375149988424</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>105</v>
@@ -3767,13 +3767,13 @@
         <v>107</v>
       </c>
       <c r="B28" s="5">
-        <v>46132.58874392361</v>
+        <v>46132.422077256946</v>
       </c>
       <c r="C28" s="5">
-        <v>46157.541855682866</v>
+        <v>46157.3751890162</v>
       </c>
       <c r="D28" s="5">
-        <v>46157.54185689815</v>
+        <v>46157.37519023148</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>108</v>
@@ -3828,13 +3828,13 @@
         <v>110</v>
       </c>
       <c r="B29" s="8">
-        <v>46132.58874878472</v>
+        <v>46132.42208211806</v>
       </c>
       <c r="C29" s="8">
-        <v>46191.90915011574</v>
+        <v>46191.742483449074</v>
       </c>
       <c r="D29" s="8">
-        <v>46191.90918642361</v>
+        <v>46191.74251975694</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>111</v>
@@ -3893,13 +3893,13 @@
         <v>113</v>
       </c>
       <c r="B30" s="5">
-        <v>46132.58875335648</v>
+        <v>46132.42208668981</v>
       </c>
       <c r="C30" s="5">
-        <v>46191.9085853125</v>
+        <v>46191.74191864583</v>
       </c>
       <c r="D30" s="5">
-        <v>46191.908590590276</v>
+        <v>46191.74192392361</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>114</v>
@@ -3954,13 +3954,13 @@
         <v>116</v>
       </c>
       <c r="B31" s="8">
-        <v>46132.58876267361</v>
+        <v>46132.42209600694</v>
       </c>
       <c r="C31" s="8">
-        <v>46191.909130879634</v>
+        <v>46191.74246421296</v>
       </c>
       <c r="D31" s="8">
-        <v>46191.90913269676</v>
+        <v>46191.74246603009</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>117</v>
@@ -4015,13 +4015,13 @@
         <v>120</v>
       </c>
       <c r="B32" s="5">
-        <v>46132.58875789352</v>
+        <v>46132.42209122685</v>
       </c>
       <c r="C32" s="5">
-        <v>46191.90908200231</v>
+        <v>46191.74241533565</v>
       </c>
       <c r="D32" s="5">
-        <v>46191.90908534722</v>
+        <v>46191.74241868056</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>118</v>
@@ -4076,13 +4076,13 @@
         <v>122</v>
       </c>
       <c r="B33" s="8">
-        <v>46132.588767037036</v>
+        <v>46132.42210037037</v>
       </c>
       <c r="C33" s="8">
-        <v>46140.62699269676</v>
+        <v>46140.460326030094</v>
       </c>
       <c r="D33" s="8">
-        <v>46178.16851243055</v>
+        <v>46178.00184576389</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>123</v>
@@ -4141,13 +4141,13 @@
         <v>127</v>
       </c>
       <c r="B34" s="5">
-        <v>46132.58877138889</v>
+        <v>46132.42210472222</v>
       </c>
       <c r="C34" s="5">
-        <v>46140.6269006713</v>
+        <v>46140.460234004626</v>
       </c>
       <c r="D34" s="5">
-        <v>46140.62690204861</v>
+        <v>46140.46023538194</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>128</v>
@@ -4202,13 +4202,13 @@
         <v>130</v>
       </c>
       <c r="B35" s="8">
-        <v>46132.58877590278</v>
+        <v>46132.42210923611</v>
       </c>
       <c r="C35" s="8">
-        <v>46140.62693832176</v>
+        <v>46140.460271655094</v>
       </c>
       <c r="D35" s="8">
-        <v>46140.62694037037</v>
+        <v>46140.460273703706</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>131</v>
@@ -4263,13 +4263,13 @@
         <v>133</v>
       </c>
       <c r="B36" s="5">
-        <v>46132.62683954861</v>
+        <v>46132.46017288194</v>
       </c>
       <c r="C36" s="5">
-        <v>46140.62696703704</v>
+        <v>46140.46030037037</v>
       </c>
       <c r="D36" s="5">
-        <v>46178.16851354166</v>
+        <v>46178.001846875</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>134</v>
@@ -4328,13 +4328,13 @@
         <v>136</v>
       </c>
       <c r="B37" s="8">
-        <v>46132.62712936343</v>
+        <v>46132.46046269676</v>
       </c>
       <c r="C37" s="8">
-        <v>46140.62678560185</v>
+        <v>46140.46011893518</v>
       </c>
       <c r="D37" s="8">
-        <v>46140.62678680556</v>
+        <v>46140.46012013889</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>75</v>
@@ -4383,13 +4383,13 @@
         <v>138</v>
       </c>
       <c r="B38" s="5">
-        <v>46132.62726841435</v>
+        <v>46132.46060174768</v>
       </c>
       <c r="C38" s="5">
-        <v>46140.62682609954</v>
+        <v>46140.46015943287</v>
       </c>
       <c r="D38" s="5">
-        <v>46140.62682733797</v>
+        <v>46140.4601606713</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>139</v>
@@ -4438,13 +4438,13 @@
         <v>141</v>
       </c>
       <c r="B39" s="8">
-        <v>46132.62697065972</v>
+        <v>46132.46030399305</v>
       </c>
       <c r="C39" s="8">
-        <v>46147.89775949074</v>
+        <v>46147.73109282408</v>
       </c>
       <c r="D39" s="8">
-        <v>46178.16851233796</v>
+        <v>46178.0018456713</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>142</v>
@@ -4503,13 +4503,13 @@
         <v>144</v>
       </c>
       <c r="B40" s="5">
-        <v>46132.62753372685</v>
+        <v>46132.46086706019</v>
       </c>
       <c r="C40" s="5">
-        <v>46140.6270855787</v>
+        <v>46140.46041891204</v>
       </c>
       <c r="D40" s="5">
-        <v>46140.62708736111</v>
+        <v>46140.46042069445</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>81</v>
@@ -4558,13 +4558,13 @@
         <v>146</v>
       </c>
       <c r="B41" s="8">
-        <v>46132.627615798614</v>
+        <v>46132.46094913194</v>
       </c>
       <c r="C41" s="8">
-        <v>46147.89774630787</v>
+        <v>46147.731079641206</v>
       </c>
       <c r="D41" s="8">
-        <v>46147.89774797454</v>
+        <v>46147.731081307866</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>147</v>
@@ -4613,11 +4613,11 @@
         <v>149</v>
       </c>
       <c r="B42" s="5">
-        <v>46132.58860650463</v>
+        <v>46132.421939837965</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46191.91760722222</v>
+        <v>46191.750940555554</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>150</v>
@@ -4660,13 +4660,13 @@
         <v>152</v>
       </c>
       <c r="B43" s="8">
-        <v>46132.58883957176</v>
+        <v>46132.42217290509</v>
       </c>
       <c r="C43" s="8">
-        <v>46175.72865314815</v>
+        <v>46175.56198648148</v>
       </c>
       <c r="D43" s="8">
-        <v>46197.71035199074</v>
+        <v>46197.543685324075</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>153</v>
@@ -4725,13 +4725,13 @@
         <v>157</v>
       </c>
       <c r="B44" s="5">
-        <v>46132.58884677083</v>
+        <v>46132.42218010417</v>
       </c>
       <c r="C44" s="5">
-        <v>46191.91739681713</v>
+        <v>46191.75073015047</v>
       </c>
       <c r="D44" s="5">
-        <v>46197.71038001157</v>
+        <v>46197.54371334491</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>158</v>
@@ -4790,13 +4790,13 @@
         <v>161</v>
       </c>
       <c r="B45" s="8">
-        <v>46132.5888534838</v>
+        <v>46132.42218681713</v>
       </c>
       <c r="C45" s="8">
-        <v>46191.917582326394</v>
+        <v>46191.75091565972</v>
       </c>
       <c r="D45" s="8">
-        <v>46191.91760793982</v>
+        <v>46191.750941273145</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>71</v>
@@ -4853,11 +4853,11 @@
         <v>165</v>
       </c>
       <c r="B46" s="5">
-        <v>46132.58886101852</v>
+        <v>46132.42219435185</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46225.18671469907</v>
+        <v>46225.020048032406</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>166</v>
@@ -4914,11 +4914,11 @@
         <v>170</v>
       </c>
       <c r="B47" s="8">
-        <v>46132.634550902774</v>
+        <v>46132.46788423611</v>
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="8">
-        <v>46224.1677925463</v>
+        <v>46224.00112587963</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>171</v>
@@ -4965,11 +4965,11 @@
         <v>174</v>
       </c>
       <c r="B48" s="5">
-        <v>46132.634558564816</v>
+        <v>46132.46789189815</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46224.16779487269</v>
+        <v>46224.001128206015</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>175</v>
@@ -5016,11 +5016,11 @@
         <v>177</v>
       </c>
       <c r="B49" s="8">
-        <v>46132.634567546294</v>
+        <v>46132.46790087963</v>
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="8">
-        <v>46224.167796215275</v>
+        <v>46224.00112954861</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>178</v>
@@ -5067,11 +5067,11 @@
         <v>179</v>
       </c>
       <c r="B50" s="5">
-        <v>46132.634571875</v>
+        <v>46132.46790520834</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46224.1677978125</v>
+        <v>46224.00113114584</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>180</v>
@@ -5118,11 +5118,11 @@
         <v>181</v>
       </c>
       <c r="B51" s="8">
-        <v>46132.6345777199</v>
+        <v>46132.467911053245</v>
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="8">
-        <v>46224.16779921296</v>
+        <v>46224.0011325463</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>182</v>
@@ -5169,11 +5169,11 @@
         <v>183</v>
       </c>
       <c r="B52" s="5">
-        <v>46132.634582071754</v>
+        <v>46132.4679154051</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46224.167800717594</v>
+        <v>46224.00113405092</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>184</v>
@@ -5220,11 +5220,11 @@
         <v>185</v>
       </c>
       <c r="B53" s="8">
-        <v>46132.63458603009</v>
+        <v>46132.46791936342</v>
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="8">
-        <v>46224.16780229167</v>
+        <v>46224.001135625</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>186</v>
@@ -5271,11 +5271,11 @@
         <v>188</v>
       </c>
       <c r="B54" s="5">
-        <v>46132.63459168981</v>
+        <v>46132.46792502315</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46224.167803668985</v>
+        <v>46224.00113700231</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>189</v>
@@ -5322,11 +5322,11 @@
         <v>190</v>
       </c>
       <c r="B55" s="8">
-        <v>46132.634597094904</v>
+        <v>46132.46793042824</v>
       </c>
       <c r="C55" s="9"/>
       <c r="D55" s="8">
-        <v>46224.16780512732</v>
+        <v>46224.00113846065</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>191</v>
@@ -5373,11 +5373,11 @@
         <v>192</v>
       </c>
       <c r="B56" s="5">
-        <v>46132.6346025463</v>
+        <v>46132.46793587963</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46224.16780649306</v>
+        <v>46224.00113982639</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>193</v>
@@ -5424,11 +5424,11 @@
         <v>194</v>
       </c>
       <c r="B57" s="8">
-        <v>46132.634674050925</v>
+        <v>46132.46800738426</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46224.167809293984</v>
+        <v>46224.00114262731</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>195</v>
@@ -5475,11 +5475,11 @@
         <v>196</v>
       </c>
       <c r="B58" s="5">
-        <v>46132.63468899306</v>
+        <v>46132.468022326386</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46224.167810625004</v>
+        <v>46224.00114395833</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>197</v>
@@ -5526,11 +5526,11 @@
         <v>198</v>
       </c>
       <c r="B59" s="8">
-        <v>46132.63470766204</v>
+        <v>46132.46804099537</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46224.16781208334</v>
+        <v>46224.00114541667</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>199</v>
@@ -5577,11 +5577,11 @@
         <v>200</v>
       </c>
       <c r="B60" s="5">
-        <v>46132.634719884256</v>
+        <v>46132.46805321759</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46224.16781392361</v>
+        <v>46224.001147256946</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>201</v>
@@ -5628,11 +5628,11 @@
         <v>202</v>
       </c>
       <c r="B61" s="8">
-        <v>46132.634727847224</v>
+        <v>46132.46806118055</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46224.16781546296</v>
+        <v>46224.00114879629</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>203</v>
@@ -5679,11 +5679,11 @@
         <v>205</v>
       </c>
       <c r="B62" s="5">
-        <v>46132.63460722222</v>
+        <v>46132.46794055555</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46224.16780783565</v>
+        <v>46224.00114116898</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>206</v>
@@ -5730,13 +5730,13 @@
         <v>208</v>
       </c>
       <c r="B63" s="8">
-        <v>46132.64721917824</v>
+        <v>46132.48055251157</v>
       </c>
       <c r="C63" s="8">
-        <v>46157.49397792824</v>
+        <v>46157.32731126157</v>
       </c>
       <c r="D63" s="8">
-        <v>46229.5764716088</v>
+        <v>46229.40980494213</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>209</v>
@@ -5783,13 +5783,13 @@
         <v>211</v>
       </c>
       <c r="B64" s="5">
-        <v>46132.624842916666</v>
+        <v>46132.45817625</v>
       </c>
       <c r="C64" s="5">
-        <v>46157.493824652774</v>
+        <v>46157.32715798611</v>
       </c>
       <c r="D64" s="5">
-        <v>46182.18354462963</v>
+        <v>46182.01687796296</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>212</v>
@@ -5848,13 +5848,13 @@
         <v>214</v>
       </c>
       <c r="B65" s="8">
-        <v>46132.62490728009</v>
+        <v>46132.45824061343</v>
       </c>
       <c r="C65" s="8">
-        <v>46157.49385349537</v>
+        <v>46157.327186828705</v>
       </c>
       <c r="D65" s="8">
-        <v>46182.18354459491</v>
+        <v>46182.01687792824</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>215</v>
@@ -5913,13 +5913,13 @@
         <v>217</v>
       </c>
       <c r="B66" s="5">
-        <v>46132.62495362268</v>
+        <v>46132.45828695602</v>
       </c>
       <c r="C66" s="5">
-        <v>46157.49386780093</v>
+        <v>46157.32720113426</v>
       </c>
       <c r="D66" s="5">
-        <v>46182.183544768515</v>
+        <v>46182.01687810185</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>218</v>
@@ -5978,13 +5978,13 @@
         <v>220</v>
       </c>
       <c r="B67" s="8">
-        <v>46132.70742302084</v>
+        <v>46132.54075635417</v>
       </c>
       <c r="C67" s="8">
-        <v>46157.493948125004</v>
+        <v>46157.32728145833</v>
       </c>
       <c r="D67" s="8">
-        <v>46184.203094386576</v>
+        <v>46184.03642771991</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>221</v>
@@ -6043,13 +6043,13 @@
         <v>225</v>
       </c>
       <c r="B68" s="5">
-        <v>46132.70752974537</v>
+        <v>46132.5408630787</v>
       </c>
       <c r="C68" s="5">
-        <v>46157.49395293981</v>
+        <v>46157.32728627315</v>
       </c>
       <c r="D68" s="5">
-        <v>46184.20309802084</v>
+        <v>46184.036431354165</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>226</v>
@@ -6108,13 +6108,13 @@
         <v>228</v>
       </c>
       <c r="B69" s="8">
-        <v>46132.70760050926</v>
+        <v>46132.540933842596</v>
       </c>
       <c r="C69" s="8">
-        <v>46157.49396020833</v>
+        <v>46157.32729354167</v>
       </c>
       <c r="D69" s="8">
-        <v>46184.203094212964</v>
+        <v>46184.03642754629</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>229</v>
@@ -6173,13 +6173,13 @@
         <v>230</v>
       </c>
       <c r="B70" s="5">
-        <v>46132.58888190972</v>
+        <v>46132.42221524306</v>
       </c>
       <c r="C70" s="5">
-        <v>46209.63277412037</v>
+        <v>46209.4661074537</v>
       </c>
       <c r="D70" s="5">
-        <v>46209.6327872338</v>
+        <v>46209.46612056713</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>231</v>
@@ -6226,13 +6226,13 @@
         <v>233</v>
       </c>
       <c r="B71" s="8">
-        <v>46132.588885185185</v>
+        <v>46132.42221851852</v>
       </c>
       <c r="C71" s="8">
-        <v>46196.68414012731</v>
+        <v>46196.51747346065</v>
       </c>
       <c r="D71" s="8">
-        <v>46196.68415487268</v>
+        <v>46196.517488206024</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>78</v>
@@ -6291,13 +6291,13 @@
         <v>237</v>
       </c>
       <c r="B72" s="5">
-        <v>46132.58889042824</v>
+        <v>46132.422223761576</v>
       </c>
       <c r="C72" s="5">
-        <v>46196.69197697917</v>
+        <v>46196.5253103125</v>
       </c>
       <c r="D72" s="5">
-        <v>46229.54909206019</v>
+        <v>46229.382425393516</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>238</v>
@@ -6356,13 +6356,13 @@
         <v>240</v>
       </c>
       <c r="B73" s="8">
-        <v>46132.631278472225</v>
+        <v>46132.46461180555</v>
       </c>
       <c r="C73" s="8">
-        <v>46196.69130792824</v>
+        <v>46196.524641261574</v>
       </c>
       <c r="D73" s="8">
-        <v>46196.69266049768</v>
+        <v>46196.52599383102</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>172</v>
@@ -6411,13 +6411,13 @@
         <v>243</v>
       </c>
       <c r="B74" s="5">
-        <v>46132.63129450232</v>
+        <v>46132.46462783565</v>
       </c>
       <c r="C74" s="5">
-        <v>46196.69160608796</v>
+        <v>46196.524939421295</v>
       </c>
       <c r="D74" s="5">
-        <v>46196.692844907404</v>
+        <v>46196.52617824074</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>172</v>
@@ -6466,13 +6466,13 @@
         <v>244</v>
       </c>
       <c r="B75" s="8">
-        <v>46132.63130252315</v>
+        <v>46132.46463585648</v>
       </c>
       <c r="C75" s="8">
-        <v>46196.69194896991</v>
+        <v>46196.52528230324</v>
       </c>
       <c r="D75" s="8">
-        <v>46196.69317986111</v>
+        <v>46196.52651319445</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>172</v>
@@ -6521,13 +6521,13 @@
         <v>247</v>
       </c>
       <c r="B76" s="5">
-        <v>46132.63130869213</v>
+        <v>46132.46464202546</v>
       </c>
       <c r="C76" s="5">
-        <v>46196.69194981482</v>
+        <v>46196.52528314815</v>
       </c>
       <c r="D76" s="5">
-        <v>46196.693142592594</v>
+        <v>46196.52647592593</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>172</v>
@@ -6576,13 +6576,13 @@
         <v>248</v>
       </c>
       <c r="B77" s="8">
-        <v>46132.631314467595</v>
+        <v>46132.46464780092</v>
       </c>
       <c r="C77" s="8">
-        <v>46196.691950416665</v>
+        <v>46196.52528375</v>
       </c>
       <c r="D77" s="8">
-        <v>46196.693131458334</v>
+        <v>46196.52646479166</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>172</v>
@@ -6631,13 +6631,13 @@
         <v>250</v>
       </c>
       <c r="B78" s="5">
-        <v>46132.6313205787</v>
+        <v>46132.46465391204</v>
       </c>
       <c r="C78" s="5">
-        <v>46196.69195099537</v>
+        <v>46196.5252843287</v>
       </c>
       <c r="D78" s="5">
-        <v>46196.693120717595</v>
+        <v>46196.52645405092</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>172</v>
@@ -6686,13 +6686,13 @@
         <v>252</v>
       </c>
       <c r="B79" s="8">
-        <v>46132.6313259375</v>
+        <v>46132.46465927083</v>
       </c>
       <c r="C79" s="8">
-        <v>46196.69195158565</v>
+        <v>46196.525284918986</v>
       </c>
       <c r="D79" s="8">
-        <v>46196.69310042824</v>
+        <v>46196.52643376157</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>172</v>
@@ -6741,13 +6741,13 @@
         <v>254</v>
       </c>
       <c r="B80" s="5">
-        <v>46132.63133041667</v>
+        <v>46132.46466375</v>
       </c>
       <c r="C80" s="5">
-        <v>46196.69195221065</v>
+        <v>46196.52528554398</v>
       </c>
       <c r="D80" s="5">
-        <v>46196.693085949075</v>
+        <v>46196.52641928241</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>172</v>
@@ -6796,13 +6796,13 @@
         <v>256</v>
       </c>
       <c r="B81" s="8">
-        <v>46132.63133645833</v>
+        <v>46132.46466979166</v>
       </c>
       <c r="C81" s="8">
-        <v>46196.69195284722</v>
+        <v>46196.52528618056</v>
       </c>
       <c r="D81" s="8">
-        <v>46196.69307368055</v>
+        <v>46196.52640701389</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>172</v>
@@ -6851,13 +6851,13 @@
         <v>257</v>
       </c>
       <c r="B82" s="5">
-        <v>46132.63134074074</v>
+        <v>46132.46467407407</v>
       </c>
       <c r="C82" s="5">
-        <v>46196.69174834491</v>
+        <v>46196.525081678235</v>
       </c>
       <c r="D82" s="5">
-        <v>46196.69306041667</v>
+        <v>46196.52639375</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>172</v>
@@ -6906,13 +6906,13 @@
         <v>259</v>
       </c>
       <c r="B83" s="8">
-        <v>46132.631346469905</v>
+        <v>46132.46467980324</v>
       </c>
       <c r="C83" s="8">
-        <v>46196.691953437505</v>
+        <v>46196.52528677083</v>
       </c>
       <c r="D83" s="8">
-        <v>46196.693049560185</v>
+        <v>46196.52638289351</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>172</v>
@@ -6961,13 +6961,13 @@
         <v>260</v>
       </c>
       <c r="B84" s="5">
-        <v>46132.631352083336</v>
+        <v>46132.464685416664</v>
       </c>
       <c r="C84" s="5">
-        <v>46196.69195403935</v>
+        <v>46196.525287372686</v>
       </c>
       <c r="D84" s="5">
-        <v>46196.6930421412</v>
+        <v>46196.52637547454</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>172</v>
@@ -7016,13 +7016,13 @@
         <v>261</v>
       </c>
       <c r="B85" s="8">
-        <v>46132.63135776621</v>
+        <v>46132.464691099536</v>
       </c>
       <c r="C85" s="8">
-        <v>46196.69195462963</v>
+        <v>46196.52528796296</v>
       </c>
       <c r="D85" s="8">
-        <v>46196.69303037037</v>
+        <v>46196.5263637037</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>172</v>
@@ -7071,13 +7071,13 @@
         <v>262</v>
       </c>
       <c r="B86" s="5">
-        <v>46132.63136296296</v>
+        <v>46132.4646962963</v>
       </c>
       <c r="C86" s="5">
-        <v>46196.6919552662</v>
+        <v>46196.525288599536</v>
       </c>
       <c r="D86" s="5">
-        <v>46196.69302122685</v>
+        <v>46196.526354560185</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>172</v>
@@ -7126,13 +7126,13 @@
         <v>264</v>
       </c>
       <c r="B87" s="8">
-        <v>46132.63136688658</v>
+        <v>46132.464700219905</v>
       </c>
       <c r="C87" s="8">
-        <v>46196.69195586805</v>
+        <v>46196.52528920139</v>
       </c>
       <c r="D87" s="8">
-        <v>46196.692995543985</v>
+        <v>46196.52632887731</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>172</v>
@@ -7181,13 +7181,13 @@
         <v>266</v>
       </c>
       <c r="B88" s="5">
-        <v>46132.63137239583</v>
+        <v>46132.464705729166</v>
       </c>
       <c r="C88" s="5">
-        <v>46196.69195645834</v>
+        <v>46196.525289791665</v>
       </c>
       <c r="D88" s="5">
-        <v>46196.69300998843</v>
+        <v>46196.52634332176</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>172</v>
@@ -7236,13 +7236,13 @@
         <v>267</v>
       </c>
       <c r="B89" s="8">
-        <v>46132.58889809028</v>
+        <v>46132.42223142361</v>
       </c>
       <c r="C89" s="8">
-        <v>46209.6327590162</v>
+        <v>46209.46609234954</v>
       </c>
       <c r="D89" s="8">
-        <v>46229.54911224537</v>
+        <v>46229.3824455787</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>268</v>
@@ -7301,13 +7301,13 @@
         <v>270</v>
       </c>
       <c r="B90" s="5">
-        <v>46132.63147894676</v>
+        <v>46132.46481228009</v>
       </c>
       <c r="C90" s="5">
-        <v>46196.91330332176</v>
+        <v>46196.746636655094</v>
       </c>
       <c r="D90" s="5">
-        <v>46196.913305381946</v>
+        <v>46196.74663871528</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>271</v>
@@ -7356,13 +7356,13 @@
         <v>274</v>
       </c>
       <c r="B91" s="8">
-        <v>46132.63149082176</v>
+        <v>46132.46482415509</v>
       </c>
       <c r="C91" s="8">
-        <v>46196.91330880787</v>
+        <v>46196.7466421412</v>
       </c>
       <c r="D91" s="8">
-        <v>46196.9133102662</v>
+        <v>46196.74664359954</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>271</v>
@@ -7411,13 +7411,13 @@
         <v>276</v>
       </c>
       <c r="B92" s="5">
-        <v>46132.63149714121</v>
+        <v>46132.464830474535</v>
       </c>
       <c r="C92" s="5">
-        <v>46196.91331665509</v>
+        <v>46196.746649988425</v>
       </c>
       <c r="D92" s="5">
-        <v>46196.91331809028</v>
+        <v>46196.746651423615</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>271</v>
@@ -7466,13 +7466,13 @@
         <v>277</v>
       </c>
       <c r="B93" s="8">
-        <v>46132.63150280093</v>
+        <v>46132.464836134255</v>
       </c>
       <c r="C93" s="8">
-        <v>46196.9133241088</v>
+        <v>46196.74665744213</v>
       </c>
       <c r="D93" s="8">
-        <v>46196.91332601852</v>
+        <v>46196.74665935185</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>271</v>
@@ -7521,13 +7521,13 @@
         <v>278</v>
       </c>
       <c r="B94" s="5">
-        <v>46132.63150895834</v>
+        <v>46132.464842291665</v>
       </c>
       <c r="C94" s="5">
-        <v>46196.91332903935</v>
+        <v>46196.74666237269</v>
       </c>
       <c r="D94" s="5">
-        <v>46196.91333064815</v>
+        <v>46196.74666398148</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>271</v>
@@ -7576,13 +7576,13 @@
         <v>279</v>
       </c>
       <c r="B95" s="8">
-        <v>46132.63151432871</v>
+        <v>46132.464847662035</v>
       </c>
       <c r="C95" s="8">
-        <v>46196.91333642361</v>
+        <v>46196.74666975695</v>
       </c>
       <c r="D95" s="8">
-        <v>46196.91333818287</v>
+        <v>46196.7466715162</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>271</v>
@@ -7631,13 +7631,13 @@
         <v>280</v>
       </c>
       <c r="B96" s="5">
-        <v>46132.631519525465</v>
+        <v>46132.4648528588</v>
       </c>
       <c r="C96" s="5">
-        <v>46196.91334673611</v>
+        <v>46196.746680069446</v>
       </c>
       <c r="D96" s="5">
-        <v>46196.91334849537</v>
+        <v>46196.74668182871</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>271</v>
@@ -7686,13 +7686,13 @@
         <v>281</v>
       </c>
       <c r="B97" s="8">
-        <v>46132.631524247685</v>
+        <v>46132.46485758101</v>
       </c>
       <c r="C97" s="8">
-        <v>46196.913354247685</v>
+        <v>46196.74668758102</v>
       </c>
       <c r="D97" s="8">
-        <v>46196.91335584491</v>
+        <v>46196.74668917824</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>271</v>
@@ -7741,13 +7741,13 @@
         <v>282</v>
       </c>
       <c r="B98" s="5">
-        <v>46132.63153150463</v>
+        <v>46132.464864837966</v>
       </c>
       <c r="C98" s="5">
-        <v>46196.913358935184</v>
+        <v>46196.74669226852</v>
       </c>
       <c r="D98" s="5">
-        <v>46196.913360879626</v>
+        <v>46196.74669421296</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>271</v>
@@ -7796,13 +7796,13 @@
         <v>283</v>
       </c>
       <c r="B99" s="8">
-        <v>46132.631539270835</v>
+        <v>46132.46487260416</v>
       </c>
       <c r="C99" s="8">
-        <v>46196.91336784722</v>
+        <v>46196.74670118056</v>
       </c>
       <c r="D99" s="8">
-        <v>46196.913369456015</v>
+        <v>46196.74670278935</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>271</v>
@@ -7851,13 +7851,13 @@
         <v>284</v>
       </c>
       <c r="B100" s="5">
-        <v>46132.63154616898</v>
+        <v>46132.46487950231</v>
       </c>
       <c r="C100" s="5">
-        <v>46196.913381562495</v>
+        <v>46196.74671489584</v>
       </c>
       <c r="D100" s="5">
-        <v>46196.91338305555</v>
+        <v>46196.746716388894</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>271</v>
@@ -7906,13 +7906,13 @@
         <v>285</v>
       </c>
       <c r="B101" s="8">
-        <v>46132.63155506944</v>
+        <v>46132.46488840278</v>
       </c>
       <c r="C101" s="8">
-        <v>46196.913390381946</v>
+        <v>46196.746723715274</v>
       </c>
       <c r="D101" s="8">
-        <v>46196.91339189815</v>
+        <v>46196.74672523148</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>271</v>
@@ -7961,13 +7961,13 @@
         <v>286</v>
       </c>
       <c r="B102" s="5">
-        <v>46132.63156422453</v>
+        <v>46132.464897557875</v>
       </c>
       <c r="C102" s="5">
-        <v>46196.91339768519</v>
+        <v>46196.74673101852</v>
       </c>
       <c r="D102" s="5">
-        <v>46196.91339939815</v>
+        <v>46196.74673273148</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>271</v>
@@ -8016,13 +8016,13 @@
         <v>287</v>
       </c>
       <c r="B103" s="8">
-        <v>46132.63157251157</v>
+        <v>46132.46490584491</v>
       </c>
       <c r="C103" s="8">
-        <v>46209.63248238426</v>
+        <v>46209.46581571759</v>
       </c>
       <c r="D103" s="8">
-        <v>46209.63248512732</v>
+        <v>46209.46581846065</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>271</v>
@@ -8071,13 +8071,13 @@
         <v>288</v>
       </c>
       <c r="B104" s="5">
-        <v>46132.631576643515</v>
+        <v>46132.46490997685</v>
       </c>
       <c r="C104" s="5">
-        <v>46209.63248900463</v>
+        <v>46209.46582233797</v>
       </c>
       <c r="D104" s="5">
-        <v>46209.63249092593</v>
+        <v>46209.465824259256</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>172</v>
@@ -8126,13 +8126,13 @@
         <v>289</v>
       </c>
       <c r="B105" s="8">
-        <v>46132.6319078588</v>
+        <v>46132.46524119213</v>
       </c>
       <c r="C105" s="8">
-        <v>46209.63249508102</v>
+        <v>46209.46582841435</v>
       </c>
       <c r="D105" s="8">
-        <v>46209.63249679398</v>
+        <v>46209.465830127316</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>271</v>
@@ -8181,13 +8181,13 @@
         <v>290</v>
       </c>
       <c r="B106" s="5">
-        <v>46132.58890393519</v>
+        <v>46132.42223726852</v>
       </c>
       <c r="C106" s="5">
-        <v>46198.65522429398</v>
+        <v>46198.488557627315</v>
       </c>
       <c r="D106" s="5">
-        <v>46198.65523800926</v>
+        <v>46198.48857134259</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>291</v>
@@ -8234,13 +8234,13 @@
         <v>293</v>
       </c>
       <c r="B107" s="8">
-        <v>46132.58890717593</v>
+        <v>46132.42224050926</v>
       </c>
       <c r="C107" s="8">
-        <v>46198.65510091435</v>
+        <v>46198.48843424769</v>
       </c>
       <c r="D107" s="8">
-        <v>46198.65511907407</v>
+        <v>46198.48845240741</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>294</v>
@@ -8297,13 +8297,13 @@
         <v>296</v>
       </c>
       <c r="B108" s="5">
-        <v>46132.58891280093</v>
+        <v>46132.42224613426</v>
       </c>
       <c r="C108" s="5">
-        <v>46157.542043761576</v>
+        <v>46157.37537709491</v>
       </c>
       <c r="D108" s="5">
-        <v>46163.18906322916</v>
+        <v>46163.022396562505</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>297</v>
@@ -8360,13 +8360,13 @@
         <v>298</v>
       </c>
       <c r="B109" s="8">
-        <v>46132.588918090274</v>
+        <v>46132.42225142361</v>
       </c>
       <c r="C109" s="8">
-        <v>46198.6552081713</v>
+        <v>46198.48854150463</v>
       </c>
       <c r="D109" s="8">
-        <v>46198.65526501158</v>
+        <v>46198.488598344906</v>
       </c>
       <c r="E109" s="9" t="s">
         <v>299</v>
@@ -8423,11 +8423,11 @@
         <v>301</v>
       </c>
       <c r="B110" s="5">
-        <v>46132.58892311342</v>
+        <v>46132.422256446764</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46205.491523854165</v>
+        <v>46205.3248571875</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>302</v>
@@ -8470,13 +8470,13 @@
         <v>304</v>
       </c>
       <c r="B111" s="8">
-        <v>46132.58892658565</v>
+        <v>46132.42225991898</v>
       </c>
       <c r="C111" s="8">
-        <v>46205.49151155092</v>
+        <v>46205.324844884264</v>
       </c>
       <c r="D111" s="8">
-        <v>46229.98726652778</v>
+        <v>46229.82059986111</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>305</v>
@@ -8535,13 +8535,13 @@
         <v>307</v>
       </c>
       <c r="B112" s="5">
-        <v>46132.632033182876</v>
+        <v>46132.465366516204</v>
       </c>
       <c r="C112" s="5">
-        <v>46205.490867280096</v>
+        <v>46205.324200613424</v>
       </c>
       <c r="D112" s="5">
-        <v>46223.603719872684</v>
+        <v>46223.43705320602</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>172</v>
@@ -8590,13 +8590,13 @@
         <v>309</v>
       </c>
       <c r="B113" s="8">
-        <v>46132.6321053125</v>
+        <v>46132.465438645835</v>
       </c>
       <c r="C113" s="8">
-        <v>46205.49090212963</v>
+        <v>46205.32423546296</v>
       </c>
       <c r="D113" s="8">
-        <v>46223.60371622685</v>
+        <v>46223.43704956018</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>271</v>
@@ -8645,13 +8645,13 @@
         <v>310</v>
       </c>
       <c r="B114" s="5">
-        <v>46132.63211394676</v>
+        <v>46132.46544728009</v>
       </c>
       <c r="C114" s="5">
-        <v>46205.490917268515</v>
+        <v>46205.32425060185</v>
       </c>
       <c r="D114" s="5">
-        <v>46223.60371229167</v>
+        <v>46223.437045625</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>271</v>
@@ -8700,13 +8700,13 @@
         <v>312</v>
       </c>
       <c r="B115" s="8">
-        <v>46132.6321221875</v>
+        <v>46132.46545552083</v>
       </c>
       <c r="C115" s="8">
-        <v>46205.49092887732</v>
+        <v>46205.32426221065</v>
       </c>
       <c r="D115" s="8">
-        <v>46223.60370868056</v>
+        <v>46223.43704201389</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>172</v>
@@ -8755,13 +8755,13 @@
         <v>313</v>
       </c>
       <c r="B116" s="5">
-        <v>46132.63212829861</v>
+        <v>46132.465461631946</v>
       </c>
       <c r="C116" s="5">
-        <v>46205.490941296295</v>
+        <v>46205.32427462963</v>
       </c>
       <c r="D116" s="5">
-        <v>46223.60370479166</v>
+        <v>46223.437038125005</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>172</v>
@@ -8810,13 +8810,13 @@
         <v>314</v>
       </c>
       <c r="B117" s="8">
-        <v>46132.63213525463</v>
+        <v>46132.465468587965</v>
       </c>
       <c r="C117" s="8">
-        <v>46205.49094682871</v>
+        <v>46205.324280162036</v>
       </c>
       <c r="D117" s="8">
-        <v>46223.60370101852</v>
+        <v>46223.43703435185</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>172</v>
@@ -8865,13 +8865,13 @@
         <v>316</v>
       </c>
       <c r="B118" s="5">
-        <v>46132.63214342593</v>
+        <v>46132.46547675926</v>
       </c>
       <c r="C118" s="5">
-        <v>46205.49095413194</v>
+        <v>46205.32428746528</v>
       </c>
       <c r="D118" s="5">
-        <v>46223.603697303246</v>
+        <v>46223.437030636574</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>271</v>
@@ -8920,13 +8920,13 @@
         <v>317</v>
       </c>
       <c r="B119" s="8">
-        <v>46132.63215114584</v>
+        <v>46132.465484479166</v>
       </c>
       <c r="C119" s="8">
-        <v>46205.49096131945</v>
+        <v>46205.324294652775</v>
       </c>
       <c r="D119" s="8">
-        <v>46223.603693564815</v>
+        <v>46223.437026898144</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>172</v>
@@ -8975,13 +8975,13 @@
         <v>318</v>
       </c>
       <c r="B120" s="5">
-        <v>46132.63216016204</v>
+        <v>46132.46549349537</v>
       </c>
       <c r="C120" s="5">
-        <v>46205.49096766204</v>
+        <v>46205.32430099537</v>
       </c>
       <c r="D120" s="5">
-        <v>46223.603689456024</v>
+        <v>46223.43702278935</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>172</v>
@@ -9030,13 +9030,13 @@
         <v>319</v>
       </c>
       <c r="B121" s="8">
-        <v>46132.6321746412</v>
+        <v>46132.465507974535</v>
       </c>
       <c r="C121" s="8">
-        <v>46205.49097342593</v>
+        <v>46205.324306759256</v>
       </c>
       <c r="D121" s="8">
-        <v>46223.603685821756</v>
+        <v>46223.43701915509</v>
       </c>
       <c r="E121" s="9" t="s">
         <v>271</v>
@@ -9085,13 +9085,13 @@
         <v>320</v>
       </c>
       <c r="B122" s="5">
-        <v>46132.63216719907</v>
+        <v>46132.4655005324</v>
       </c>
       <c r="C122" s="5">
-        <v>46205.49099100694</v>
+        <v>46205.32432434028</v>
       </c>
       <c r="D122" s="5">
-        <v>46223.60368157407</v>
+        <v>46223.43701490741</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>172</v>
@@ -9140,13 +9140,13 @@
         <v>321</v>
       </c>
       <c r="B123" s="8">
-        <v>46132.63218074074</v>
+        <v>46132.46551407407</v>
       </c>
       <c r="C123" s="8">
-        <v>46205.49099747685</v>
+        <v>46205.32433081018</v>
       </c>
       <c r="D123" s="8">
-        <v>46223.60367759259</v>
+        <v>46223.437010925925</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>172</v>
@@ -9195,13 +9195,13 @@
         <v>322</v>
       </c>
       <c r="B124" s="5">
-        <v>46132.632186863426</v>
+        <v>46132.465520196754</v>
       </c>
       <c r="C124" s="5">
-        <v>46205.491003877316</v>
+        <v>46205.32433721065</v>
       </c>
       <c r="D124" s="5">
-        <v>46223.60367399306</v>
+        <v>46223.437007326385</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>172</v>
@@ -9250,13 +9250,13 @@
         <v>323</v>
       </c>
       <c r="B125" s="8">
-        <v>46132.63219409723</v>
+        <v>46132.465527430555</v>
       </c>
       <c r="C125" s="8">
-        <v>46205.49134238426</v>
+        <v>46205.324675717595</v>
       </c>
       <c r="D125" s="8">
-        <v>46223.60366275463</v>
+        <v>46223.43699608796</v>
       </c>
       <c r="E125" s="9" t="s">
         <v>172</v>
@@ -9305,13 +9305,13 @@
         <v>324</v>
       </c>
       <c r="B126" s="5">
-        <v>46132.63220086806</v>
+        <v>46132.46553420139</v>
       </c>
       <c r="C126" s="5">
-        <v>46223.603567060185</v>
+        <v>46223.43690039351</v>
       </c>
       <c r="D126" s="5">
-        <v>46223.603662141206</v>
+        <v>46223.436995474534</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>172</v>
@@ -9360,13 +9360,13 @@
         <v>325</v>
       </c>
       <c r="B127" s="8">
-        <v>46132.63220734954</v>
+        <v>46132.46554068287</v>
       </c>
       <c r="C127" s="8">
-        <v>46205.49149630787</v>
+        <v>46205.324829641206</v>
       </c>
       <c r="D127" s="8">
-        <v>46223.60366150463</v>
+        <v>46223.43699483796</v>
       </c>
       <c r="E127" s="9" t="s">
         <v>172</v>
@@ -9415,11 +9415,11 @@
         <v>326</v>
       </c>
       <c r="B128" s="5">
-        <v>46132.58893864583</v>
+        <v>46132.422271979165</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46237.53575319445</v>
+        <v>46237.369086527775</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>327</v>
@@ -9476,13 +9476,13 @@
         <v>328</v>
       </c>
       <c r="B129" s="8">
-        <v>46132.63296805556</v>
+        <v>46132.46630138889</v>
       </c>
       <c r="C129" s="8">
-        <v>46213.54645357639</v>
+        <v>46213.37978690972</v>
       </c>
       <c r="D129" s="8">
-        <v>46223.55793672454</v>
+        <v>46223.391270057866</v>
       </c>
       <c r="E129" s="9" t="s">
         <v>172</v>
@@ -9529,13 +9529,13 @@
         <v>331</v>
       </c>
       <c r="B130" s="5">
-        <v>46132.63297954861</v>
+        <v>46132.466312881945</v>
       </c>
       <c r="C130" s="5">
-        <v>46213.54645896991</v>
+        <v>46213.37979230324</v>
       </c>
       <c r="D130" s="5">
-        <v>46223.557933055556</v>
+        <v>46223.39126638889</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>172</v>
@@ -9582,13 +9582,13 @@
         <v>333</v>
       </c>
       <c r="B131" s="8">
-        <v>46132.63298759259</v>
+        <v>46132.46632092593</v>
       </c>
       <c r="C131" s="8">
-        <v>46213.54646347222</v>
+        <v>46213.37979680556</v>
       </c>
       <c r="D131" s="8">
-        <v>46223.5579291551</v>
+        <v>46223.391262488425</v>
       </c>
       <c r="E131" s="9" t="s">
         <v>172</v>
@@ -9635,13 +9635,13 @@
         <v>334</v>
       </c>
       <c r="B132" s="5">
-        <v>46132.63299327546</v>
+        <v>46132.466326608795</v>
       </c>
       <c r="C132" s="5">
-        <v>46213.54646974537</v>
+        <v>46213.3798030787</v>
       </c>
       <c r="D132" s="5">
-        <v>46223.55792547454</v>
+        <v>46223.39125880787</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>172</v>
@@ -9688,13 +9688,13 @@
         <v>336</v>
       </c>
       <c r="B133" s="8">
-        <v>46132.63299994213</v>
+        <v>46132.466333275464</v>
       </c>
       <c r="C133" s="8">
-        <v>46213.54647332176</v>
+        <v>46213.379806655095</v>
       </c>
       <c r="D133" s="8">
-        <v>46223.557921562504</v>
+        <v>46223.39125489583</v>
       </c>
       <c r="E133" s="9" t="s">
         <v>172</v>
@@ -9741,11 +9741,11 @@
         <v>337</v>
       </c>
       <c r="B134" s="5">
-        <v>46132.63300702546</v>
+        <v>46132.46634035879</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46223.55789310185</v>
+        <v>46223.39122643518</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>172</v>
@@ -9792,11 +9792,11 @@
         <v>339</v>
       </c>
       <c r="B135" s="8">
-        <v>46132.633012708335</v>
+        <v>46132.46634604166</v>
       </c>
       <c r="C135" s="9"/>
       <c r="D135" s="8">
-        <v>46223.55789246528</v>
+        <v>46223.39122579861</v>
       </c>
       <c r="E135" s="9" t="s">
         <v>172</v>
@@ -9843,11 +9843,11 @@
         <v>341</v>
       </c>
       <c r="B136" s="5">
-        <v>46132.63302</v>
+        <v>46132.46635333334</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46223.557891874996</v>
+        <v>46223.39122520833</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>172</v>
@@ -9894,11 +9894,11 @@
         <v>342</v>
       </c>
       <c r="B137" s="8">
-        <v>46132.63302648148</v>
+        <v>46132.46635981482</v>
       </c>
       <c r="C137" s="9"/>
       <c r="D137" s="8">
-        <v>46223.557891296296</v>
+        <v>46223.39122462963</v>
       </c>
       <c r="E137" s="9" t="s">
         <v>172</v>
@@ -9945,11 +9945,11 @@
         <v>343</v>
       </c>
       <c r="B138" s="5">
-        <v>46132.633032858794</v>
+        <v>46132.46636619213</v>
       </c>
       <c r="C138" s="6"/>
       <c r="D138" s="5">
-        <v>46223.55789070602</v>
+        <v>46223.391224039355</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>172</v>
@@ -9996,11 +9996,11 @@
         <v>345</v>
       </c>
       <c r="B139" s="8">
-        <v>46132.633039409724</v>
+        <v>46132.46637274306</v>
       </c>
       <c r="C139" s="9"/>
       <c r="D139" s="8">
-        <v>46223.55789011574</v>
+        <v>46223.39122344907</v>
       </c>
       <c r="E139" s="9" t="s">
         <v>172</v>
@@ -10047,11 +10047,11 @@
         <v>346</v>
       </c>
       <c r="B140" s="5">
-        <v>46132.633045821756</v>
+        <v>46132.46637915509</v>
       </c>
       <c r="C140" s="6"/>
       <c r="D140" s="5">
-        <v>46223.55788950231</v>
+        <v>46223.39122283565</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>172</v>
@@ -10098,11 +10098,11 @@
         <v>347</v>
       </c>
       <c r="B141" s="8">
-        <v>46132.633060057866</v>
+        <v>46132.46639339121</v>
       </c>
       <c r="C141" s="9"/>
       <c r="D141" s="8">
-        <v>46223.557888923606</v>
+        <v>46223.39122225695</v>
       </c>
       <c r="E141" s="9" t="s">
         <v>172</v>
@@ -10149,11 +10149,11 @@
         <v>348</v>
       </c>
       <c r="B142" s="5">
-        <v>46132.633052986115</v>
+        <v>46132.466386319444</v>
       </c>
       <c r="C142" s="6"/>
       <c r="D142" s="5">
-        <v>46223.55788832176</v>
+        <v>46223.391221655096</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>172</v>
@@ -10200,11 +10200,11 @@
         <v>349</v>
       </c>
       <c r="B143" s="8">
-        <v>46132.63306579861</v>
+        <v>46132.46639913194</v>
       </c>
       <c r="C143" s="9"/>
       <c r="D143" s="8">
-        <v>46223.60357828704</v>
+        <v>46223.436911620374</v>
       </c>
       <c r="E143" s="9" t="s">
         <v>172</v>
@@ -10251,11 +10251,11 @@
         <v>350</v>
       </c>
       <c r="B144" s="5">
-        <v>46132.633072337965</v>
+        <v>46132.46640567129</v>
       </c>
       <c r="C144" s="6"/>
       <c r="D144" s="5">
-        <v>46223.55788715278</v>
+        <v>46223.39122048611</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>172</v>
@@ -10302,11 +10302,11 @@
         <v>351</v>
       </c>
       <c r="B145" s="8">
-        <v>46132.58894553241</v>
+        <v>46132.42227886574</v>
       </c>
       <c r="C145" s="9"/>
       <c r="D145" s="8">
-        <v>46237.535776296296</v>
+        <v>46237.369109629624</v>
       </c>
       <c r="E145" s="9" t="s">
         <v>352</v>
@@ -10363,13 +10363,13 @@
         <v>353</v>
       </c>
       <c r="B146" s="5">
-        <v>46132.633140289356</v>
+        <v>46132.466473622684</v>
       </c>
       <c r="C146" s="5">
-        <v>46213.5465221875</v>
+        <v>46213.379855520834</v>
       </c>
       <c r="D146" s="5">
-        <v>46223.604202187504</v>
+        <v>46223.43753552083</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>172</v>
@@ -10416,13 +10416,13 @@
         <v>356</v>
       </c>
       <c r="B147" s="8">
-        <v>46132.63314908565</v>
+        <v>46132.46648241898</v>
       </c>
       <c r="C147" s="8">
-        <v>46213.54652690972</v>
+        <v>46213.379860243054</v>
       </c>
       <c r="D147" s="8">
-        <v>46223.604198078705</v>
+        <v>46223.43753141204</v>
       </c>
       <c r="E147" s="9" t="s">
         <v>172</v>
@@ -10469,13 +10469,13 @@
         <v>358</v>
       </c>
       <c r="B148" s="5">
-        <v>46132.63315533564</v>
+        <v>46132.466488668986</v>
       </c>
       <c r="C148" s="5">
-        <v>46213.546531307875</v>
+        <v>46213.3798646412</v>
       </c>
       <c r="D148" s="5">
-        <v>46223.60419431713</v>
+        <v>46223.43752765046</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>172</v>
@@ -10522,13 +10522,13 @@
         <v>359</v>
       </c>
       <c r="B149" s="8">
-        <v>46132.63316266204</v>
+        <v>46132.466495995366</v>
       </c>
       <c r="C149" s="8">
-        <v>46213.546540208336</v>
+        <v>46213.379873541664</v>
       </c>
       <c r="D149" s="8">
-        <v>46223.60419068287</v>
+        <v>46223.437524016204</v>
       </c>
       <c r="E149" s="9" t="s">
         <v>172</v>
@@ -10575,13 +10575,13 @@
         <v>360</v>
       </c>
       <c r="B150" s="5">
-        <v>46132.6331690625</v>
+        <v>46132.46650239584</v>
       </c>
       <c r="C150" s="5">
-        <v>46213.546544259254</v>
+        <v>46213.3798775926</v>
       </c>
       <c r="D150" s="5">
-        <v>46223.60418627315</v>
+        <v>46223.43751960648</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>172</v>
@@ -10628,11 +10628,11 @@
         <v>361</v>
       </c>
       <c r="B151" s="8">
-        <v>46132.63317594907</v>
+        <v>46132.46650928241</v>
       </c>
       <c r="C151" s="9"/>
       <c r="D151" s="8">
-        <v>46223.604156747686</v>
+        <v>46223.43749008102</v>
       </c>
       <c r="E151" s="9" t="s">
         <v>172</v>
@@ -10679,11 +10679,11 @@
         <v>362</v>
       </c>
       <c r="B152" s="5">
-        <v>46132.633188506945</v>
+        <v>46132.46652184028</v>
       </c>
       <c r="C152" s="6"/>
       <c r="D152" s="5">
-        <v>46223.60415612269</v>
+        <v>46223.43748945602</v>
       </c>
       <c r="E152" s="6" t="s">
         <v>172</v>
@@ -10730,11 +10730,11 @@
         <v>363</v>
       </c>
       <c r="B153" s="8">
-        <v>46132.63318159722</v>
+        <v>46132.46651493055</v>
       </c>
       <c r="C153" s="9"/>
       <c r="D153" s="8">
-        <v>46223.604155520836</v>
+        <v>46223.437488854164</v>
       </c>
       <c r="E153" s="9" t="s">
         <v>172</v>
@@ -10781,11 +10781,11 @@
         <v>364</v>
       </c>
       <c r="B154" s="5">
-        <v>46132.63319443287</v>
+        <v>46132.4665277662</v>
       </c>
       <c r="C154" s="6"/>
       <c r="D154" s="5">
-        <v>46223.60415488426</v>
+        <v>46223.43748821759</v>
       </c>
       <c r="E154" s="6" t="s">
         <v>172</v>
@@ -10832,11 +10832,11 @@
         <v>365</v>
       </c>
       <c r="B155" s="8">
-        <v>46132.63320815972</v>
+        <v>46132.46654149306</v>
       </c>
       <c r="C155" s="9"/>
       <c r="D155" s="8">
-        <v>46223.60415423611</v>
+        <v>46223.43748756945</v>
       </c>
       <c r="E155" s="9" t="s">
         <v>172</v>
@@ -10883,11 +10883,11 @@
         <v>366</v>
       </c>
       <c r="B156" s="5">
-        <v>46132.63320082176</v>
+        <v>46132.46653415509</v>
       </c>
       <c r="C156" s="6"/>
       <c r="D156" s="5">
-        <v>46223.60415359953</v>
+        <v>46223.437486932875</v>
       </c>
       <c r="E156" s="6" t="s">
         <v>172</v>
@@ -10934,11 +10934,11 @@
         <v>367</v>
       </c>
       <c r="B157" s="8">
-        <v>46132.63322097222</v>
+        <v>46132.46655430556</v>
       </c>
       <c r="C157" s="9"/>
       <c r="D157" s="8">
-        <v>46223.60415291667</v>
+        <v>46223.43748625</v>
       </c>
       <c r="E157" s="9" t="s">
         <v>172</v>
@@ -10985,11 +10985,11 @@
         <v>368</v>
       </c>
       <c r="B158" s="5">
-        <v>46132.6332150463</v>
+        <v>46132.46654837963</v>
       </c>
       <c r="C158" s="6"/>
       <c r="D158" s="5">
-        <v>46223.604152280095</v>
+        <v>46223.43748561342</v>
       </c>
       <c r="E158" s="6" t="s">
         <v>172</v>
@@ -11036,11 +11036,11 @@
         <v>369</v>
       </c>
       <c r="B159" s="8">
-        <v>46132.63322802083</v>
+        <v>46132.466561354166</v>
       </c>
       <c r="C159" s="9"/>
       <c r="D159" s="8">
-        <v>46223.60415166667</v>
+        <v>46223.437485</v>
       </c>
       <c r="E159" s="9" t="s">
         <v>172</v>
@@ -11087,11 +11087,11 @@
         <v>370</v>
       </c>
       <c r="B160" s="5">
-        <v>46132.63323575231</v>
+        <v>46132.46656908565</v>
       </c>
       <c r="C160" s="6"/>
       <c r="D160" s="5">
-        <v>46223.60415104167</v>
+        <v>46223.437484375</v>
       </c>
       <c r="E160" s="6" t="s">
         <v>172</v>
@@ -11138,11 +11138,11 @@
         <v>371</v>
       </c>
       <c r="B161" s="8">
-        <v>46132.633244004624</v>
+        <v>46132.46657733797</v>
       </c>
       <c r="C161" s="9"/>
       <c r="D161" s="8">
-        <v>46223.604150416664</v>
+        <v>46223.43748375</v>
       </c>
       <c r="E161" s="9" t="s">
         <v>172</v>
@@ -11189,11 +11189,11 @@
         <v>372</v>
       </c>
       <c r="B162" s="5">
-        <v>46132.58893171296</v>
+        <v>46132.4222650463</v>
       </c>
       <c r="C162" s="6"/>
       <c r="D162" s="5">
-        <v>46237.53579454861</v>
+        <v>46237.369127881946</v>
       </c>
       <c r="E162" s="6" t="s">
         <v>373</v>
@@ -11250,13 +11250,13 @@
         <v>374</v>
       </c>
       <c r="B163" s="8">
-        <v>46132.632804305555</v>
+        <v>46132.46613763889</v>
       </c>
       <c r="C163" s="8">
-        <v>46213.54663619213</v>
+        <v>46213.379969525464</v>
       </c>
       <c r="D163" s="8">
-        <v>46223.55831635417</v>
+        <v>46223.3916496875</v>
       </c>
       <c r="E163" s="9" t="s">
         <v>172</v>
@@ -11303,13 +11303,13 @@
         <v>377</v>
       </c>
       <c r="B164" s="5">
-        <v>46132.632815624995</v>
+        <v>46132.46614895834</v>
       </c>
       <c r="C164" s="5">
-        <v>46213.54664094908</v>
+        <v>46213.379974282405</v>
       </c>
       <c r="D164" s="5">
-        <v>46223.558312650464</v>
+        <v>46223.39164598379</v>
       </c>
       <c r="E164" s="6" t="s">
         <v>172</v>
@@ -11356,13 +11356,13 @@
         <v>378</v>
       </c>
       <c r="B165" s="8">
-        <v>46132.63282284723</v>
+        <v>46132.466156180555</v>
       </c>
       <c r="C165" s="8">
-        <v>46213.5466527199</v>
+        <v>46213.379986053245</v>
       </c>
       <c r="D165" s="8">
-        <v>46223.55830900463</v>
+        <v>46223.39164233796</v>
       </c>
       <c r="E165" s="9" t="s">
         <v>172</v>
@@ -11409,13 +11409,13 @@
         <v>380</v>
       </c>
       <c r="B166" s="5">
-        <v>46132.63283236111</v>
+        <v>46132.466165694444</v>
       </c>
       <c r="C166" s="5">
-        <v>46213.546661134256</v>
+        <v>46213.37999446759</v>
       </c>
       <c r="D166" s="5">
-        <v>46223.55830547454</v>
+        <v>46223.391638807865</v>
       </c>
       <c r="E166" s="6" t="s">
         <v>172</v>
@@ -11462,13 +11462,13 @@
         <v>381</v>
       </c>
       <c r="B167" s="8">
-        <v>46132.632837384255</v>
+        <v>46132.46617071759</v>
       </c>
       <c r="C167" s="8">
-        <v>46213.54666658565</v>
+        <v>46213.37999991898</v>
       </c>
       <c r="D167" s="8">
-        <v>46223.55830142361</v>
+        <v>46223.39163475695</v>
       </c>
       <c r="E167" s="9" t="s">
         <v>172</v>
@@ -11515,11 +11515,11 @@
         <v>383</v>
       </c>
       <c r="B168" s="5">
-        <v>46132.63284362269</v>
+        <v>46132.46617695602</v>
       </c>
       <c r="C168" s="6"/>
       <c r="D168" s="5">
-        <v>46223.55725636574</v>
+        <v>46223.39058969908</v>
       </c>
       <c r="E168" s="6" t="s">
         <v>172</v>
@@ -11566,11 +11566,11 @@
         <v>384</v>
       </c>
       <c r="B169" s="8">
-        <v>46132.63284975695</v>
+        <v>46132.46618309028</v>
       </c>
       <c r="C169" s="9"/>
       <c r="D169" s="8">
-        <v>46223.55827238426</v>
+        <v>46223.391605717596</v>
       </c>
       <c r="E169" s="9" t="s">
         <v>172</v>
@@ -11617,11 +11617,11 @@
         <v>385</v>
       </c>
       <c r="B170" s="5">
-        <v>46132.63286226852</v>
+        <v>46132.46619560185</v>
       </c>
       <c r="C170" s="6"/>
       <c r="D170" s="5">
-        <v>46223.55827179398</v>
+        <v>46223.39160512731</v>
       </c>
       <c r="E170" s="6" t="s">
         <v>172</v>
@@ -11668,11 +11668,11 @@
         <v>386</v>
       </c>
       <c r="B171" s="8">
-        <v>46132.63285675926</v>
+        <v>46132.46619009259</v>
       </c>
       <c r="C171" s="9"/>
       <c r="D171" s="8">
-        <v>46223.55827119213</v>
+        <v>46223.39160452546</v>
       </c>
       <c r="E171" s="9" t="s">
         <v>172</v>
@@ -11719,11 +11719,11 @@
         <v>387</v>
       </c>
       <c r="B172" s="5">
-        <v>46132.63286828704</v>
+        <v>46132.466201620366</v>
       </c>
       <c r="C172" s="6"/>
       <c r="D172" s="5">
-        <v>46223.558270567126</v>
+        <v>46223.39160390046</v>
       </c>
       <c r="E172" s="6" t="s">
         <v>172</v>
@@ -11770,11 +11770,11 @@
         <v>388</v>
       </c>
       <c r="B173" s="8">
-        <v>46132.63287412037</v>
+        <v>46132.466207453705</v>
       </c>
       <c r="C173" s="9"/>
       <c r="D173" s="8">
-        <v>46223.55826994213</v>
+        <v>46223.391603275464</v>
       </c>
       <c r="E173" s="9" t="s">
         <v>172</v>
@@ -11821,11 +11821,11 @@
         <v>389</v>
       </c>
       <c r="B174" s="5">
-        <v>46132.63288133102</v>
+        <v>46132.46621466435</v>
       </c>
       <c r="C174" s="6"/>
       <c r="D174" s="5">
-        <v>46223.55826935185</v>
+        <v>46223.39160268518</v>
       </c>
       <c r="E174" s="6" t="s">
         <v>172</v>
@@ -11872,11 +11872,11 @@
         <v>390</v>
       </c>
       <c r="B175" s="8">
-        <v>46132.63288800926</v>
+        <v>46132.46622134259</v>
       </c>
       <c r="C175" s="9"/>
       <c r="D175" s="8">
-        <v>46223.558268761575</v>
+        <v>46223.39160209491</v>
       </c>
       <c r="E175" s="9" t="s">
         <v>172</v>
@@ -11923,11 +11923,11 @@
         <v>391</v>
       </c>
       <c r="B176" s="5">
-        <v>46132.63289421296</v>
+        <v>46132.4662275463</v>
       </c>
       <c r="C176" s="6"/>
       <c r="D176" s="5">
-        <v>46223.55826814815</v>
+        <v>46223.39160148148</v>
       </c>
       <c r="E176" s="6" t="s">
         <v>172</v>
@@ -11974,11 +11974,11 @@
         <v>392</v>
       </c>
       <c r="B177" s="8">
-        <v>46132.63290028935</v>
+        <v>46132.46623362269</v>
       </c>
       <c r="C177" s="9"/>
       <c r="D177" s="8">
-        <v>46223.60358047453</v>
+        <v>46223.43691380787</v>
       </c>
       <c r="E177" s="9" t="s">
         <v>172</v>
@@ -12025,11 +12025,11 @@
         <v>393</v>
       </c>
       <c r="B178" s="5">
-        <v>46132.632907719904</v>
+        <v>46132.46624105324</v>
       </c>
       <c r="C178" s="6"/>
       <c r="D178" s="5">
-        <v>46223.55826689815</v>
+        <v>46223.39160023148</v>
       </c>
       <c r="E178" s="6" t="s">
         <v>172</v>
@@ -12076,11 +12076,11 @@
         <v>394</v>
       </c>
       <c r="B179" s="8">
-        <v>46132.58895258102</v>
+        <v>46132.42228591435</v>
       </c>
       <c r="C179" s="9"/>
       <c r="D179" s="8">
-        <v>46237.53581487268</v>
+        <v>46237.369148206024</v>
       </c>
       <c r="E179" s="9" t="s">
         <v>395</v>
@@ -12137,11 +12137,11 @@
         <v>396</v>
       </c>
       <c r="B180" s="5">
-        <v>46132.63330006944</v>
+        <v>46132.46663340278</v>
       </c>
       <c r="C180" s="6"/>
       <c r="D180" s="5">
-        <v>46223.60457672454</v>
+        <v>46223.437910057866</v>
       </c>
       <c r="E180" s="6" t="s">
         <v>172</v>
@@ -12188,11 +12188,11 @@
         <v>399</v>
       </c>
       <c r="B181" s="8">
-        <v>46132.63330984954</v>
+        <v>46132.46664318287</v>
       </c>
       <c r="C181" s="9"/>
       <c r="D181" s="8">
-        <v>46223.60457603009</v>
+        <v>46223.43790936343</v>
       </c>
       <c r="E181" s="9" t="s">
         <v>172</v>
@@ -12239,11 +12239,11 @@
         <v>401</v>
       </c>
       <c r="B182" s="5">
-        <v>46132.633316377316</v>
+        <v>46132.46664971065</v>
       </c>
       <c r="C182" s="6"/>
       <c r="D182" s="5">
-        <v>46223.60457538195</v>
+        <v>46223.43790871528</v>
       </c>
       <c r="E182" s="6" t="s">
         <v>172</v>
@@ -12290,11 +12290,11 @@
         <v>403</v>
       </c>
       <c r="B183" s="8">
-        <v>46132.63332333333</v>
+        <v>46132.46665666667</v>
       </c>
       <c r="C183" s="9"/>
       <c r="D183" s="8">
-        <v>46223.60457480324</v>
+        <v>46223.43790813658</v>
       </c>
       <c r="E183" s="9" t="s">
         <v>172</v>
@@ -12341,11 +12341,11 @@
         <v>405</v>
       </c>
       <c r="B184" s="5">
-        <v>46132.63333568287</v>
+        <v>46132.466669016205</v>
       </c>
       <c r="C184" s="6"/>
       <c r="D184" s="5">
-        <v>46223.604574178244</v>
+        <v>46223.43790751157</v>
       </c>
       <c r="E184" s="6" t="s">
         <v>172</v>
@@ -12392,11 +12392,11 @@
         <v>407</v>
       </c>
       <c r="B185" s="8">
-        <v>46132.633329282406</v>
+        <v>46132.46666261574</v>
       </c>
       <c r="C185" s="9"/>
       <c r="D185" s="8">
-        <v>46223.60457357639</v>
+        <v>46223.43790690972</v>
       </c>
       <c r="E185" s="9" t="s">
         <v>172</v>
@@ -12443,11 +12443,11 @@
         <v>409</v>
       </c>
       <c r="B186" s="5">
-        <v>46132.63334925926</v>
+        <v>46132.466682592596</v>
       </c>
       <c r="C186" s="6"/>
       <c r="D186" s="5">
-        <v>46223.60457297454</v>
+        <v>46223.43790630787</v>
       </c>
       <c r="E186" s="6" t="s">
         <v>172</v>
@@ -12494,11 +12494,11 @@
         <v>411</v>
       </c>
       <c r="B187" s="8">
-        <v>46132.633353321755</v>
+        <v>46132.4666866551</v>
       </c>
       <c r="C187" s="9"/>
       <c r="D187" s="8">
-        <v>46223.604572372686</v>
+        <v>46223.437905706014</v>
       </c>
       <c r="E187" s="9" t="s">
         <v>172</v>
@@ -12545,11 +12545,11 @@
         <v>413</v>
       </c>
       <c r="B188" s="5">
-        <v>46132.63336115741</v>
+        <v>46132.46669449074</v>
       </c>
       <c r="C188" s="6"/>
       <c r="D188" s="5">
-        <v>46223.60457173611</v>
+        <v>46223.43790506944</v>
       </c>
       <c r="E188" s="6" t="s">
         <v>172</v>
@@ -12596,11 +12596,11 @@
         <v>415</v>
       </c>
       <c r="B189" s="8">
-        <v>46132.6333661574</v>
+        <v>46132.466699490746</v>
       </c>
       <c r="C189" s="9"/>
       <c r="D189" s="8">
-        <v>46223.60457111111</v>
+        <v>46223.43790444444</v>
       </c>
       <c r="E189" s="9" t="s">
         <v>172</v>
@@ -12647,11 +12647,11 @@
         <v>417</v>
       </c>
       <c r="B190" s="5">
-        <v>46132.633375046295</v>
+        <v>46132.46670837963</v>
       </c>
       <c r="C190" s="6"/>
       <c r="D190" s="5">
-        <v>46223.60457043981</v>
+        <v>46223.43790377315</v>
       </c>
       <c r="E190" s="6" t="s">
         <v>172</v>
@@ -12698,11 +12698,11 @@
         <v>419</v>
       </c>
       <c r="B191" s="8">
-        <v>46132.63337950232</v>
+        <v>46132.46671283565</v>
       </c>
       <c r="C191" s="9"/>
       <c r="D191" s="8">
-        <v>46223.60456982639</v>
+        <v>46223.43790315972</v>
       </c>
       <c r="E191" s="9" t="s">
         <v>172</v>
@@ -12749,11 +12749,11 @@
         <v>421</v>
       </c>
       <c r="B192" s="5">
-        <v>46132.63338666667</v>
+        <v>46132.46672</v>
       </c>
       <c r="C192" s="6"/>
       <c r="D192" s="5">
-        <v>46223.60456921296</v>
+        <v>46223.4379025463</v>
       </c>
       <c r="E192" s="6" t="s">
         <v>172</v>
@@ -12800,11 +12800,11 @@
         <v>423</v>
       </c>
       <c r="B193" s="8">
-        <v>46132.63339375</v>
+        <v>46132.46672708333</v>
       </c>
       <c r="C193" s="9"/>
       <c r="D193" s="8">
-        <v>46223.604568634255</v>
+        <v>46223.4379019676</v>
       </c>
       <c r="E193" s="9" t="s">
         <v>172</v>
@@ -12851,11 +12851,11 @@
         <v>425</v>
       </c>
       <c r="B194" s="5">
-        <v>46132.63339872685</v>
+        <v>46132.46673206019</v>
       </c>
       <c r="C194" s="6"/>
       <c r="D194" s="5">
-        <v>46223.6045680324</v>
+        <v>46223.437901365745</v>
       </c>
       <c r="E194" s="6" t="s">
         <v>172</v>
@@ -12902,11 +12902,11 @@
         <v>427</v>
       </c>
       <c r="B195" s="8">
-        <v>46132.633404085645</v>
+        <v>46132.46673741898</v>
       </c>
       <c r="C195" s="9"/>
       <c r="D195" s="8">
-        <v>46223.60456738426</v>
+        <v>46223.43790071759</v>
       </c>
       <c r="E195" s="9" t="s">
         <v>172</v>
@@ -12953,11 +12953,11 @@
         <v>429</v>
       </c>
       <c r="B196" s="5">
-        <v>46132.58900565973</v>
+        <v>46132.422338993056</v>
       </c>
       <c r="C196" s="6"/>
       <c r="D196" s="5">
-        <v>46229.86452372685</v>
+        <v>46229.697857060186</v>
       </c>
       <c r="E196" s="6" t="s">
         <v>430</v>
@@ -13014,11 +13014,11 @@
         <v>433</v>
       </c>
       <c r="B197" s="8">
-        <v>46132.6334534375</v>
+        <v>46132.466786770834</v>
       </c>
       <c r="C197" s="9"/>
       <c r="D197" s="8">
-        <v>46225.25025936343</v>
+        <v>46225.083592696756</v>
       </c>
       <c r="E197" s="9" t="s">
         <v>172</v>
@@ -13065,11 +13065,11 @@
         <v>435</v>
       </c>
       <c r="B198" s="5">
-        <v>46132.633462025464</v>
+        <v>46132.46679535879</v>
       </c>
       <c r="C198" s="6"/>
       <c r="D198" s="5">
-        <v>46225.250260960645</v>
+        <v>46225.08359429398</v>
       </c>
       <c r="E198" s="6" t="s">
         <v>172</v>
@@ -13116,11 +13116,11 @@
         <v>436</v>
       </c>
       <c r="B199" s="8">
-        <v>46132.633468622684</v>
+        <v>46132.46680195602</v>
       </c>
       <c r="C199" s="9"/>
       <c r="D199" s="8">
-        <v>46225.2502621875</v>
+        <v>46225.08359552083</v>
       </c>
       <c r="E199" s="9" t="s">
         <v>172</v>
@@ -13167,11 +13167,11 @@
         <v>437</v>
       </c>
       <c r="B200" s="5">
-        <v>46132.63347502315</v>
+        <v>46132.46680835648</v>
       </c>
       <c r="C200" s="6"/>
       <c r="D200" s="5">
-        <v>46225.2502634375</v>
+        <v>46225.08359677083</v>
       </c>
       <c r="E200" s="6" t="s">
         <v>172</v>
@@ -13218,11 +13218,11 @@
         <v>438</v>
       </c>
       <c r="B201" s="8">
-        <v>46132.63348070602</v>
+        <v>46132.46681403935</v>
       </c>
       <c r="C201" s="9"/>
       <c r="D201" s="8">
-        <v>46225.25026458333</v>
+        <v>46225.083597916666</v>
       </c>
       <c r="E201" s="9" t="s">
         <v>172</v>
@@ -13269,11 +13269,11 @@
         <v>439</v>
       </c>
       <c r="B202" s="5">
-        <v>46132.63348662037</v>
+        <v>46132.466819953705</v>
       </c>
       <c r="C202" s="6"/>
       <c r="D202" s="5">
-        <v>46225.25026579861</v>
+        <v>46225.08359913195</v>
       </c>
       <c r="E202" s="6" t="s">
         <v>172</v>
@@ -13320,11 +13320,11 @@
         <v>440</v>
       </c>
       <c r="B203" s="8">
-        <v>46132.63349295139</v>
+        <v>46132.466826284726</v>
       </c>
       <c r="C203" s="9"/>
       <c r="D203" s="8">
-        <v>46225.250267083335</v>
+        <v>46225.08360041666</v>
       </c>
       <c r="E203" s="9" t="s">
         <v>172</v>
@@ -13371,11 +13371,11 @@
         <v>442</v>
       </c>
       <c r="B204" s="5">
-        <v>46132.633500138894</v>
+        <v>46132.46683347222</v>
       </c>
       <c r="C204" s="6"/>
       <c r="D204" s="5">
-        <v>46225.25026822917</v>
+        <v>46225.083601562495</v>
       </c>
       <c r="E204" s="6" t="s">
         <v>172</v>
@@ -13422,11 +13422,11 @@
         <v>443</v>
       </c>
       <c r="B205" s="8">
-        <v>46132.633505983795</v>
+        <v>46132.46683931713</v>
       </c>
       <c r="C205" s="9"/>
       <c r="D205" s="8">
-        <v>46225.25026947916</v>
+        <v>46225.083602812505</v>
       </c>
       <c r="E205" s="9" t="s">
         <v>172</v>
@@ -13473,11 +13473,11 @@
         <v>444</v>
       </c>
       <c r="B206" s="5">
-        <v>46132.6335124537</v>
+        <v>46132.466845787036</v>
       </c>
       <c r="C206" s="6"/>
       <c r="D206" s="5">
-        <v>46225.25027071759</v>
+        <v>46225.08360405093</v>
       </c>
       <c r="E206" s="6" t="s">
         <v>172</v>
@@ -13524,11 +13524,11 @@
         <v>445</v>
       </c>
       <c r="B207" s="8">
-        <v>46132.63351974537</v>
+        <v>46132.4668530787</v>
       </c>
       <c r="C207" s="9"/>
       <c r="D207" s="8">
-        <v>46225.25027203704</v>
+        <v>46225.08360537037</v>
       </c>
       <c r="E207" s="9" t="s">
         <v>172</v>
@@ -13575,11 +13575,11 @@
         <v>446</v>
       </c>
       <c r="B208" s="5">
-        <v>46132.6335277662</v>
+        <v>46132.466861099536</v>
       </c>
       <c r="C208" s="6"/>
       <c r="D208" s="5">
-        <v>46225.2502734375</v>
+        <v>46225.08360677083</v>
       </c>
       <c r="E208" s="6" t="s">
         <v>172</v>
@@ -13626,11 +13626,11 @@
         <v>447</v>
       </c>
       <c r="B209" s="8">
-        <v>46132.633534988425</v>
+        <v>46132.46686832176</v>
       </c>
       <c r="C209" s="9"/>
       <c r="D209" s="8">
-        <v>46225.250274606486</v>
+        <v>46225.083607939814</v>
       </c>
       <c r="E209" s="9" t="s">
         <v>172</v>
@@ -13677,11 +13677,11 @@
         <v>448</v>
       </c>
       <c r="B210" s="5">
-        <v>46132.63354082176</v>
+        <v>46132.46687415509</v>
       </c>
       <c r="C210" s="6"/>
       <c r="D210" s="5">
-        <v>46225.25027587963</v>
+        <v>46225.08360921296</v>
       </c>
       <c r="E210" s="6" t="s">
         <v>172</v>
@@ -13728,11 +13728,11 @@
         <v>449</v>
       </c>
       <c r="B211" s="8">
-        <v>46132.63354760417</v>
+        <v>46132.4668809375</v>
       </c>
       <c r="C211" s="9"/>
       <c r="D211" s="8">
-        <v>46225.2502774537</v>
+        <v>46225.08361078704</v>
       </c>
       <c r="E211" s="9" t="s">
         <v>450</v>
@@ -13779,11 +13779,11 @@
         <v>451</v>
       </c>
       <c r="B212" s="5">
-        <v>46133.58300138889</v>
+        <v>46133.41633472222</v>
       </c>
       <c r="C212" s="6"/>
       <c r="D212" s="5">
-        <v>46225.25028299769</v>
+        <v>46225.083616331016</v>
       </c>
       <c r="E212" s="6" t="s">
         <v>271</v>
@@ -13830,11 +13830,11 @@
         <v>452</v>
       </c>
       <c r="B213" s="8">
-        <v>46132.589012916666</v>
+        <v>46132.42234625</v>
       </c>
       <c r="C213" s="9"/>
       <c r="D213" s="8">
-        <v>46133.58769056713</v>
+        <v>46133.42102390046</v>
       </c>
       <c r="E213" s="9" t="s">
         <v>453</v>
@@ -13877,11 +13877,11 @@
         <v>455</v>
       </c>
       <c r="B214" s="5">
-        <v>46132.589016666665</v>
+        <v>46132.42235</v>
       </c>
       <c r="C214" s="6"/>
       <c r="D214" s="5">
-        <v>46229.5497865625</v>
+        <v>46229.383119895836</v>
       </c>
       <c r="E214" s="6" t="s">
         <v>456</v>
@@ -13938,11 +13938,11 @@
         <v>460</v>
       </c>
       <c r="B215" s="8">
-        <v>46132.63360670139</v>
+        <v>46132.46694003472</v>
       </c>
       <c r="C215" s="9"/>
       <c r="D215" s="8">
-        <v>46226.167681631945</v>
+        <v>46226.00101496528</v>
       </c>
       <c r="E215" s="9" t="s">
         <v>172</v>
@@ -13989,11 +13989,11 @@
         <v>461</v>
       </c>
       <c r="B216" s="5">
-        <v>46132.63361304398</v>
+        <v>46132.46694637732</v>
       </c>
       <c r="C216" s="6"/>
       <c r="D216" s="5">
-        <v>46226.167683541666</v>
+        <v>46226.001016875</v>
       </c>
       <c r="E216" s="6" t="s">
         <v>172</v>
@@ -14040,11 +14040,11 @@
         <v>462</v>
       </c>
       <c r="B217" s="8">
-        <v>46132.63361974537</v>
+        <v>46132.46695307871</v>
       </c>
       <c r="C217" s="9"/>
       <c r="D217" s="8">
-        <v>46226.16768490741</v>
+        <v>46226.00101824074</v>
       </c>
       <c r="E217" s="9" t="s">
         <v>172</v>
@@ -14091,11 +14091,11 @@
         <v>463</v>
       </c>
       <c r="B218" s="5">
-        <v>46132.63363137731</v>
+        <v>46132.46696471065</v>
       </c>
       <c r="C218" s="6"/>
       <c r="D218" s="5">
-        <v>46226.16768748843</v>
+        <v>46226.00102082176</v>
       </c>
       <c r="E218" s="6" t="s">
         <v>172</v>
@@ -14142,11 +14142,11 @@
         <v>464</v>
       </c>
       <c r="B219" s="8">
-        <v>46132.63362555555</v>
+        <v>46132.466958888894</v>
       </c>
       <c r="C219" s="9"/>
       <c r="D219" s="8">
-        <v>46226.16768627315</v>
+        <v>46226.00101960648</v>
       </c>
       <c r="E219" s="9" t="s">
         <v>172</v>
@@ -14193,11 +14193,11 @@
         <v>465</v>
       </c>
       <c r="B220" s="5">
-        <v>46132.63363859954</v>
+        <v>46132.46697193287</v>
       </c>
       <c r="C220" s="6"/>
       <c r="D220" s="5">
-        <v>46226.16768871528</v>
+        <v>46226.001022048615</v>
       </c>
       <c r="E220" s="6" t="s">
         <v>172</v>
@@ -14244,11 +14244,11 @@
         <v>466</v>
       </c>
       <c r="B221" s="8">
-        <v>46132.63364667824</v>
+        <v>46132.46698001157</v>
       </c>
       <c r="C221" s="9"/>
       <c r="D221" s="8">
-        <v>46226.167689988426</v>
+        <v>46226.00102332176</v>
       </c>
       <c r="E221" s="9" t="s">
         <v>450</v>
@@ -14295,11 +14295,11 @@
         <v>467</v>
       </c>
       <c r="B222" s="5">
-        <v>46132.633653055556</v>
+        <v>46132.466986388885</v>
       </c>
       <c r="C222" s="6"/>
       <c r="D222" s="5">
-        <v>46226.167691435185</v>
+        <v>46226.00102476851</v>
       </c>
       <c r="E222" s="6" t="s">
         <v>172</v>
@@ -14346,11 +14346,11 @@
         <v>468</v>
       </c>
       <c r="B223" s="8">
-        <v>46132.63365921297</v>
+        <v>46132.466992546295</v>
       </c>
       <c r="C223" s="9"/>
       <c r="D223" s="8">
-        <v>46226.167693020834</v>
+        <v>46226.00102635416</v>
       </c>
       <c r="E223" s="9" t="s">
         <v>172</v>
@@ -14397,11 +14397,11 @@
         <v>469</v>
       </c>
       <c r="B224" s="5">
-        <v>46132.633665347224</v>
+        <v>46132.46699868055</v>
       </c>
       <c r="C224" s="6"/>
       <c r="D224" s="5">
-        <v>46226.16769430556</v>
+        <v>46226.00102763889</v>
       </c>
       <c r="E224" s="6" t="s">
         <v>172</v>
@@ -14448,11 +14448,11 @@
         <v>470</v>
       </c>
       <c r="B225" s="8">
-        <v>46132.63367407407</v>
+        <v>46132.46700740741</v>
       </c>
       <c r="C225" s="9"/>
       <c r="D225" s="8">
-        <v>46226.16769577547</v>
+        <v>46226.0010291088</v>
       </c>
       <c r="E225" s="9" t="s">
         <v>172</v>
@@ -14499,11 +14499,11 @@
         <v>471</v>
       </c>
       <c r="B226" s="5">
-        <v>46132.63368225694</v>
+        <v>46132.46701559028</v>
       </c>
       <c r="C226" s="6"/>
       <c r="D226" s="5">
-        <v>46226.16769702546</v>
+        <v>46226.00103035879</v>
       </c>
       <c r="E226" s="6" t="s">
         <v>172</v>
@@ -14550,11 +14550,11 @@
         <v>472</v>
       </c>
       <c r="B227" s="8">
-        <v>46132.63368885417</v>
+        <v>46132.4670221875</v>
       </c>
       <c r="C227" s="9"/>
       <c r="D227" s="8">
-        <v>46226.16769825231</v>
+        <v>46226.00103158565</v>
       </c>
       <c r="E227" s="9" t="s">
         <v>172</v>
@@ -14601,11 +14601,11 @@
         <v>473</v>
       </c>
       <c r="B228" s="5">
-        <v>46132.633694965276</v>
+        <v>46132.46702829861</v>
       </c>
       <c r="C228" s="6"/>
       <c r="D228" s="5">
-        <v>46226.16769980324</v>
+        <v>46226.00103313658</v>
       </c>
       <c r="E228" s="6" t="s">
         <v>172</v>
@@ -14652,11 +14652,11 @@
         <v>474</v>
       </c>
       <c r="B229" s="8">
-        <v>46132.63370111111</v>
+        <v>46132.467034444446</v>
       </c>
       <c r="C229" s="9"/>
       <c r="D229" s="8">
-        <v>46226.16770127315</v>
+        <v>46226.00103460648</v>
       </c>
       <c r="E229" s="9" t="s">
         <v>450</v>
@@ -14703,11 +14703,11 @@
         <v>475</v>
       </c>
       <c r="B230" s="5">
-        <v>46132.63378953704</v>
+        <v>46132.46712287037</v>
       </c>
       <c r="C230" s="6"/>
       <c r="D230" s="5">
-        <v>46226.16770262731</v>
+        <v>46226.00103596065</v>
       </c>
       <c r="E230" s="6" t="s">
         <v>172</v>
@@ -14754,11 +14754,11 @@
         <v>476</v>
       </c>
       <c r="B231" s="8">
-        <v>46132.589021736116</v>
+        <v>46132.422355069444</v>
       </c>
       <c r="C231" s="9"/>
       <c r="D231" s="8">
-        <v>46237.53586916666</v>
+        <v>46237.3692025</v>
       </c>
       <c r="E231" s="9" t="s">
         <v>477</v>
@@ -14815,11 +14815,11 @@
         <v>479</v>
       </c>
       <c r="B232" s="5">
-        <v>46132.633861608796</v>
+        <v>46132.46719494213</v>
       </c>
       <c r="C232" s="6"/>
       <c r="D232" s="5">
-        <v>46227.16814662037</v>
+        <v>46227.0014799537</v>
       </c>
       <c r="E232" s="6" t="s">
         <v>172</v>
@@ -14866,11 +14866,11 @@
         <v>480</v>
       </c>
       <c r="B233" s="8">
-        <v>46132.633870011574</v>
+        <v>46132.4672033449</v>
       </c>
       <c r="C233" s="9"/>
       <c r="D233" s="8">
-        <v>46227.16814866898</v>
+        <v>46227.00148200231</v>
       </c>
       <c r="E233" s="9" t="s">
         <v>172</v>
@@ -14917,11 +14917,11 @@
         <v>481</v>
       </c>
       <c r="B234" s="5">
-        <v>46132.63387658565</v>
+        <v>46132.46720991898</v>
       </c>
       <c r="C234" s="6"/>
       <c r="D234" s="5">
-        <v>46227.16815003472</v>
+        <v>46227.001483368054</v>
       </c>
       <c r="E234" s="6" t="s">
         <v>172</v>
@@ -14968,11 +14968,11 @@
         <v>482</v>
       </c>
       <c r="B235" s="8">
-        <v>46132.63388259259</v>
+        <v>46132.46721592592</v>
       </c>
       <c r="C235" s="9"/>
       <c r="D235" s="8">
-        <v>46227.168151273145</v>
+        <v>46227.00148460648</v>
       </c>
       <c r="E235" s="9" t="s">
         <v>172</v>
@@ -15019,11 +15019,11 @@
         <v>483</v>
       </c>
       <c r="B236" s="5">
-        <v>46132.63388633102</v>
+        <v>46132.46721966435</v>
       </c>
       <c r="C236" s="6"/>
       <c r="D236" s="5">
-        <v>46227.168152557875</v>
+        <v>46227.0014858912</v>
       </c>
       <c r="E236" s="6" t="s">
         <v>172</v>
@@ -15070,11 +15070,11 @@
         <v>484</v>
       </c>
       <c r="B237" s="8">
-        <v>46132.63389106482</v>
+        <v>46132.46722439815</v>
       </c>
       <c r="C237" s="9"/>
       <c r="D237" s="8">
-        <v>46227.168153935185</v>
+        <v>46227.00148726851</v>
       </c>
       <c r="E237" s="9" t="s">
         <v>172</v>
@@ -15121,11 +15121,11 @@
         <v>485</v>
       </c>
       <c r="B238" s="5">
-        <v>46132.63389739583</v>
+        <v>46132.46723072916</v>
       </c>
       <c r="C238" s="6"/>
       <c r="D238" s="5">
-        <v>46227.16815527777</v>
+        <v>46227.00148861111</v>
       </c>
       <c r="E238" s="6" t="s">
         <v>172</v>
@@ -15172,11 +15172,11 @@
         <v>486</v>
       </c>
       <c r="B239" s="8">
-        <v>46132.63390288195</v>
+        <v>46132.46723621528</v>
       </c>
       <c r="C239" s="9"/>
       <c r="D239" s="8">
-        <v>46227.168156643515</v>
+        <v>46227.00148997685</v>
       </c>
       <c r="E239" s="9" t="s">
         <v>172</v>
@@ -15223,11 +15223,11 @@
         <v>487</v>
       </c>
       <c r="B240" s="5">
-        <v>46132.63390861111</v>
+        <v>46132.46724194444</v>
       </c>
       <c r="C240" s="6"/>
       <c r="D240" s="5">
-        <v>46227.16815799769</v>
+        <v>46227.001491331015</v>
       </c>
       <c r="E240" s="6" t="s">
         <v>172</v>
@@ -15274,11 +15274,11 @@
         <v>488</v>
       </c>
       <c r="B241" s="8">
-        <v>46132.63391276621</v>
+        <v>46132.467246099535</v>
       </c>
       <c r="C241" s="9"/>
       <c r="D241" s="8">
-        <v>46227.16815940972</v>
+        <v>46227.00149274306</v>
       </c>
       <c r="E241" s="9" t="s">
         <v>172</v>
@@ -15325,11 +15325,11 @@
         <v>489</v>
       </c>
       <c r="B242" s="5">
-        <v>46132.63391880787</v>
+        <v>46132.4672521412</v>
       </c>
       <c r="C242" s="6"/>
       <c r="D242" s="5">
-        <v>46227.16816072917</v>
+        <v>46227.0014940625</v>
       </c>
       <c r="E242" s="6" t="s">
         <v>172</v>
@@ -15376,11 +15376,11 @@
         <v>490</v>
       </c>
       <c r="B243" s="8">
-        <v>46132.63392302083</v>
+        <v>46132.46725635417</v>
       </c>
       <c r="C243" s="9"/>
       <c r="D243" s="8">
-        <v>46227.16816206019</v>
+        <v>46227.00149539352</v>
       </c>
       <c r="E243" s="9" t="s">
         <v>172</v>
@@ -15427,11 +15427,11 @@
         <v>491</v>
       </c>
       <c r="B244" s="5">
-        <v>46132.63393041666</v>
+        <v>46132.467263750004</v>
       </c>
       <c r="C244" s="6"/>
       <c r="D244" s="5">
-        <v>46227.16816336806</v>
+        <v>46227.001496701385</v>
       </c>
       <c r="E244" s="6" t="s">
         <v>172</v>
@@ -15478,11 +15478,11 @@
         <v>492</v>
       </c>
       <c r="B245" s="8">
-        <v>46132.63393689815</v>
+        <v>46132.467270231486</v>
       </c>
       <c r="C245" s="9"/>
       <c r="D245" s="8">
-        <v>46227.16816472222</v>
+        <v>46227.00149805556</v>
       </c>
       <c r="E245" s="9" t="s">
         <v>172</v>
@@ -15529,11 +15529,11 @@
         <v>493</v>
       </c>
       <c r="B246" s="5">
-        <v>46132.633943078705</v>
+        <v>46132.46727641203</v>
       </c>
       <c r="C246" s="6"/>
       <c r="D246" s="5">
-        <v>46227.16816598379</v>
+        <v>46227.00149931713</v>
       </c>
       <c r="E246" s="6" t="s">
         <v>450</v>
@@ -15580,11 +15580,11 @@
         <v>494</v>
       </c>
       <c r="B247" s="8">
-        <v>46132.633955578705</v>
+        <v>46132.46728891204</v>
       </c>
       <c r="C247" s="9"/>
       <c r="D247" s="8">
-        <v>46227.16816758102</v>
+        <v>46227.00150091435</v>
       </c>
       <c r="E247" s="9" t="s">
         <v>172</v>
@@ -15631,11 +15631,11 @@
         <v>495</v>
       </c>
       <c r="B248" s="5">
-        <v>46132.58902681713</v>
+        <v>46132.422360150464</v>
       </c>
       <c r="C248" s="6"/>
       <c r="D248" s="5">
-        <v>46231.18365072917</v>
+        <v>46231.0169840625</v>
       </c>
       <c r="E248" s="6" t="s">
         <v>496</v>
@@ -15694,11 +15694,11 @@
         <v>500</v>
       </c>
       <c r="B249" s="8">
-        <v>46132.634024432875</v>
+        <v>46132.4673577662</v>
       </c>
       <c r="C249" s="9"/>
       <c r="D249" s="8">
-        <v>46230.16807828704</v>
+        <v>46230.00141162037</v>
       </c>
       <c r="E249" s="9" t="s">
         <v>172</v>
@@ -15745,11 +15745,11 @@
         <v>501</v>
       </c>
       <c r="B250" s="5">
-        <v>46132.634032685186</v>
+        <v>46132.46736601852</v>
       </c>
       <c r="C250" s="6"/>
       <c r="D250" s="5">
-        <v>46230.16808081018</v>
+        <v>46230.00141414352</v>
       </c>
       <c r="E250" s="6" t="s">
         <v>172</v>
@@ -15796,11 +15796,11 @@
         <v>502</v>
       </c>
       <c r="B251" s="8">
-        <v>46132.63404001157</v>
+        <v>46132.46737334491</v>
       </c>
       <c r="C251" s="9"/>
       <c r="D251" s="8">
-        <v>46230.16808221064</v>
+        <v>46230.001415543986</v>
       </c>
       <c r="E251" s="9" t="s">
         <v>172</v>
@@ -15847,11 +15847,11 @@
         <v>503</v>
       </c>
       <c r="B252" s="5">
-        <v>46132.63404659722</v>
+        <v>46132.46737993056</v>
       </c>
       <c r="C252" s="6"/>
       <c r="D252" s="5">
-        <v>46230.16808350694</v>
+        <v>46230.00141684028</v>
       </c>
       <c r="E252" s="6" t="s">
         <v>172</v>
@@ -15898,11 +15898,11 @@
         <v>504</v>
       </c>
       <c r="B253" s="8">
-        <v>46132.6340537037</v>
+        <v>46132.46738703703</v>
       </c>
       <c r="C253" s="9"/>
       <c r="D253" s="8">
-        <v>46230.16808476852</v>
+        <v>46230.00141810185</v>
       </c>
       <c r="E253" s="9" t="s">
         <v>172</v>
@@ -15949,11 +15949,11 @@
         <v>505</v>
       </c>
       <c r="B254" s="5">
-        <v>46132.63406115741</v>
+        <v>46132.46739449074</v>
       </c>
       <c r="C254" s="6"/>
       <c r="D254" s="5">
-        <v>46230.16808607639</v>
+        <v>46230.001419409724</v>
       </c>
       <c r="E254" s="6" t="s">
         <v>172</v>
@@ -16000,11 +16000,11 @@
         <v>506</v>
       </c>
       <c r="B255" s="8">
-        <v>46132.63406662037</v>
+        <v>46132.467399953704</v>
       </c>
       <c r="C255" s="9"/>
       <c r="D255" s="8">
-        <v>46230.16808741898</v>
+        <v>46230.00142075232</v>
       </c>
       <c r="E255" s="9" t="s">
         <v>172</v>
@@ -16051,11 +16051,11 @@
         <v>507</v>
       </c>
       <c r="B256" s="5">
-        <v>46132.634072395835</v>
+        <v>46132.46740572917</v>
       </c>
       <c r="C256" s="6"/>
       <c r="D256" s="5">
-        <v>46230.16808876157</v>
+        <v>46230.00142209491</v>
       </c>
       <c r="E256" s="6" t="s">
         <v>172</v>
@@ -16102,11 +16102,11 @@
         <v>508</v>
       </c>
       <c r="B257" s="8">
-        <v>46132.6340770949</v>
+        <v>46132.467410428246</v>
       </c>
       <c r="C257" s="9"/>
       <c r="D257" s="8">
-        <v>46230.16809005787</v>
+        <v>46230.00142339121</v>
       </c>
       <c r="E257" s="9" t="s">
         <v>172</v>
@@ -16153,11 +16153,11 @@
         <v>509</v>
       </c>
       <c r="B258" s="5">
-        <v>46132.634082777775</v>
+        <v>46132.46741611111</v>
       </c>
       <c r="C258" s="6"/>
       <c r="D258" s="5">
-        <v>46230.168091423606</v>
+        <v>46230.00142475695</v>
       </c>
       <c r="E258" s="6" t="s">
         <v>172</v>
@@ -16204,11 +16204,11 @@
         <v>510</v>
       </c>
       <c r="B259" s="8">
-        <v>46132.63408899306</v>
+        <v>46132.46742232639</v>
       </c>
       <c r="C259" s="9"/>
       <c r="D259" s="8">
-        <v>46230.16809290509</v>
+        <v>46230.00142623842</v>
       </c>
       <c r="E259" s="9" t="s">
         <v>172</v>
@@ -16255,11 +16255,11 @@
         <v>511</v>
       </c>
       <c r="B260" s="5">
-        <v>46132.63409545139</v>
+        <v>46132.46742878472</v>
       </c>
       <c r="C260" s="6"/>
       <c r="D260" s="5">
-        <v>46230.16809414352</v>
+        <v>46230.00142747685</v>
       </c>
       <c r="E260" s="6" t="s">
         <v>172</v>
@@ -16306,11 +16306,11 @@
         <v>512</v>
       </c>
       <c r="B261" s="8">
-        <v>46132.63410087963</v>
+        <v>46132.46743421296</v>
       </c>
       <c r="C261" s="9"/>
       <c r="D261" s="8">
-        <v>46230.16809559028</v>
+        <v>46230.00142892361</v>
       </c>
       <c r="E261" s="9" t="s">
         <v>172</v>
@@ -16357,11 +16357,11 @@
         <v>513</v>
       </c>
       <c r="B262" s="5">
-        <v>46132.63410688657</v>
+        <v>46132.46744021991</v>
       </c>
       <c r="C262" s="6"/>
       <c r="D262" s="5">
-        <v>46230.168096863425</v>
+        <v>46230.00143019676</v>
       </c>
       <c r="E262" s="6" t="s">
         <v>172</v>
@@ -16408,11 +16408,11 @@
         <v>514</v>
       </c>
       <c r="B263" s="8">
-        <v>46132.6341133449</v>
+        <v>46132.467446678245</v>
       </c>
       <c r="C263" s="9"/>
       <c r="D263" s="8">
-        <v>46230.168098124996</v>
+        <v>46230.00143145834</v>
       </c>
       <c r="E263" s="9" t="s">
         <v>172</v>
@@ -16459,11 +16459,11 @@
         <v>515</v>
       </c>
       <c r="B264" s="5">
-        <v>46132.63411966435</v>
+        <v>46132.467452997684</v>
       </c>
       <c r="C264" s="6"/>
       <c r="D264" s="5">
-        <v>46230.16809997685</v>
+        <v>46230.001433310186</v>
       </c>
       <c r="E264" s="6" t="s">
         <v>172</v>
@@ -16510,11 +16510,11 @@
         <v>516</v>
       </c>
       <c r="B265" s="8">
-        <v>46132.58903189815</v>
+        <v>46132.42236523148</v>
       </c>
       <c r="C265" s="9"/>
       <c r="D265" s="8">
-        <v>46232.197325057874</v>
+        <v>46232.0306583912</v>
       </c>
       <c r="E265" s="9" t="s">
         <v>517</v>
@@ -16571,11 +16571,11 @@
         <v>519</v>
       </c>
       <c r="B266" s="5">
-        <v>46132.63422869213</v>
+        <v>46132.467562025464</v>
       </c>
       <c r="C266" s="6"/>
       <c r="D266" s="5">
-        <v>46231.16777215278</v>
+        <v>46231.00110548611</v>
       </c>
       <c r="E266" s="6" t="s">
         <v>172</v>
@@ -16622,11 +16622,11 @@
         <v>521</v>
       </c>
       <c r="B267" s="8">
-        <v>46132.63423491898</v>
+        <v>46132.467568252316</v>
       </c>
       <c r="C267" s="9"/>
       <c r="D267" s="8">
-        <v>46231.16777465278</v>
+        <v>46231.001107986114</v>
       </c>
       <c r="E267" s="9" t="s">
         <v>172</v>
@@ -16673,11 +16673,11 @@
         <v>522</v>
       </c>
       <c r="B268" s="5">
-        <v>46132.634240960644</v>
+        <v>46132.46757429398</v>
       </c>
       <c r="C268" s="6"/>
       <c r="D268" s="5">
-        <v>46231.16777594907</v>
+        <v>46231.001109282406</v>
       </c>
       <c r="E268" s="6" t="s">
         <v>172</v>
@@ -16724,11 +16724,11 @@
         <v>523</v>
       </c>
       <c r="B269" s="8">
-        <v>46132.63424789352</v>
+        <v>46132.467581226854</v>
       </c>
       <c r="C269" s="9"/>
       <c r="D269" s="8">
-        <v>46231.16777724537</v>
+        <v>46231.001110578705</v>
       </c>
       <c r="E269" s="9" t="s">
         <v>172</v>
@@ -16775,11 +16775,11 @@
         <v>524</v>
       </c>
       <c r="B270" s="5">
-        <v>46132.634254386576</v>
+        <v>46132.467587719904</v>
       </c>
       <c r="C270" s="6"/>
       <c r="D270" s="5">
-        <v>46231.16777849537</v>
+        <v>46231.00111182871</v>
       </c>
       <c r="E270" s="6" t="s">
         <v>172</v>
@@ -16826,11 +16826,11 @@
         <v>525</v>
       </c>
       <c r="B271" s="8">
-        <v>46132.634260810184</v>
+        <v>46132.46759414352</v>
       </c>
       <c r="C271" s="9"/>
       <c r="D271" s="8">
-        <v>46231.167779745374</v>
+        <v>46231.0011130787</v>
       </c>
       <c r="E271" s="9" t="s">
         <v>172</v>
@@ -16877,11 +16877,11 @@
         <v>526</v>
       </c>
       <c r="B272" s="5">
-        <v>46132.634267256944</v>
+        <v>46132.46760059027</v>
       </c>
       <c r="C272" s="6"/>
       <c r="D272" s="5">
-        <v>46231.16778097222</v>
+        <v>46231.00111430556</v>
       </c>
       <c r="E272" s="6" t="s">
         <v>172</v>
@@ -16928,11 +16928,11 @@
         <v>527</v>
       </c>
       <c r="B273" s="8">
-        <v>46132.63427122685</v>
+        <v>46132.46760456018</v>
       </c>
       <c r="C273" s="9"/>
       <c r="D273" s="8">
-        <v>46231.16778246527</v>
+        <v>46231.001115798616</v>
       </c>
       <c r="E273" s="9" t="s">
         <v>172</v>
@@ -16979,11 +16979,11 @@
         <v>529</v>
       </c>
       <c r="B274" s="5">
-        <v>46132.634276365745</v>
+        <v>46132.46760969907</v>
       </c>
       <c r="C274" s="6"/>
       <c r="D274" s="5">
-        <v>46231.16780969907</v>
+        <v>46231.00114303241</v>
       </c>
       <c r="E274" s="6" t="s">
         <v>172</v>
@@ -17030,11 +17030,11 @@
         <v>530</v>
       </c>
       <c r="B275" s="8">
-        <v>46132.63428099537</v>
+        <v>46132.46761432871</v>
       </c>
       <c r="C275" s="9"/>
       <c r="D275" s="8">
-        <v>46231.16781326389</v>
+        <v>46231.00114659722</v>
       </c>
       <c r="E275" s="9" t="s">
         <v>172</v>
@@ -17081,11 +17081,11 @@
         <v>531</v>
       </c>
       <c r="B276" s="5">
-        <v>46132.63428524305</v>
+        <v>46132.46761857639</v>
       </c>
       <c r="C276" s="6"/>
       <c r="D276" s="5">
-        <v>46231.16781449074</v>
+        <v>46231.00114782408</v>
       </c>
       <c r="E276" s="6" t="s">
         <v>172</v>
@@ -17132,11 +17132,11 @@
         <v>532</v>
       </c>
       <c r="B277" s="8">
-        <v>46132.63429103009</v>
+        <v>46132.46762436343</v>
       </c>
       <c r="C277" s="9"/>
       <c r="D277" s="8">
-        <v>46231.16781590278</v>
+        <v>46231.00114923611</v>
       </c>
       <c r="E277" s="9" t="s">
         <v>172</v>
@@ -17183,11 +17183,11 @@
         <v>533</v>
       </c>
       <c r="B278" s="5">
-        <v>46132.63429523148</v>
+        <v>46132.46762856482</v>
       </c>
       <c r="C278" s="6"/>
       <c r="D278" s="5">
-        <v>46231.16781758102</v>
+        <v>46231.00115091435</v>
       </c>
       <c r="E278" s="6" t="s">
         <v>172</v>
@@ -17234,11 +17234,11 @@
         <v>534</v>
       </c>
       <c r="B279" s="8">
-        <v>46132.63430358796</v>
+        <v>46132.4676369213</v>
       </c>
       <c r="C279" s="9"/>
       <c r="D279" s="8">
-        <v>46231.167818877315</v>
+        <v>46231.00115221065</v>
       </c>
       <c r="E279" s="9" t="s">
         <v>172</v>
@@ -17285,11 +17285,11 @@
         <v>535</v>
       </c>
       <c r="B280" s="5">
-        <v>46132.63431148148</v>
+        <v>46132.46764481482</v>
       </c>
       <c r="C280" s="6"/>
       <c r="D280" s="5">
-        <v>46231.16782008102</v>
+        <v>46231.001153414356</v>
       </c>
       <c r="E280" s="6" t="s">
         <v>172</v>
@@ -17336,11 +17336,11 @@
         <v>536</v>
       </c>
       <c r="B281" s="8">
-        <v>46132.63437663195</v>
+        <v>46132.467709965276</v>
       </c>
       <c r="C281" s="9"/>
       <c r="D281" s="8">
-        <v>46231.16782137731</v>
+        <v>46231.00115471065</v>
       </c>
       <c r="E281" s="9" t="s">
         <v>172</v>
@@ -17387,11 +17387,11 @@
         <v>537</v>
       </c>
       <c r="B282" s="5">
-        <v>46132.589037604164</v>
+        <v>46132.4223709375</v>
       </c>
       <c r="C282" s="6"/>
       <c r="D282" s="5">
-        <v>46133.59235670139</v>
+        <v>46133.425690034725</v>
       </c>
       <c r="E282" s="6" t="s">
         <v>538</v>
@@ -17434,11 +17434,11 @@
         <v>539</v>
       </c>
       <c r="B283" s="8">
-        <v>46132.5890406713</v>
+        <v>46132.42237400463</v>
       </c>
       <c r="C283" s="9"/>
       <c r="D283" s="8">
-        <v>46241.17502087963</v>
+        <v>46241.00835421296</v>
       </c>
       <c r="E283" s="9" t="s">
         <v>540</v>
@@ -17497,11 +17497,11 @@
         <v>544</v>
       </c>
       <c r="B284" s="5">
-        <v>46132.58904559028</v>
+        <v>46132.42237892361</v>
       </c>
       <c r="C284" s="6"/>
       <c r="D284" s="5">
-        <v>46241.17502056713</v>
+        <v>46241.00835390046</v>
       </c>
       <c r="E284" s="6" t="s">
         <v>545</v>

--- a/data/50001541 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001541 - XEMORTIZ MINERA FRISCO.xlsx
@@ -2275,13 +2275,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46132.42191706019</v>
+        <v>46132.58858372685</v>
       </c>
       <c r="C4" s="5">
-        <v>46133.721585057865</v>
+        <v>46133.88825172454</v>
       </c>
       <c r="D4" s="5">
-        <v>46134.37518803241</v>
+        <v>46134.54185469907</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -2324,13 +2324,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46132.421995972225</v>
+        <v>46132.58866263889</v>
       </c>
       <c r="C5" s="8">
-        <v>46140.46108958333</v>
+        <v>46140.62775625</v>
       </c>
       <c r="D5" s="8">
-        <v>46140.46121216435</v>
+        <v>46140.627878831016</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -2389,13 +2389,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46132.421999074075</v>
+        <v>46132.58866574074</v>
       </c>
       <c r="C6" s="5">
-        <v>46133.72485732639</v>
+        <v>46133.89152399305</v>
       </c>
       <c r="D6" s="5">
-        <v>46133.7248587037</v>
+        <v>46133.891525370374</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -2454,13 +2454,13 @@
         <v>36</v>
       </c>
       <c r="B7" s="8">
-        <v>46132.422001747684</v>
+        <v>46132.58866841435</v>
       </c>
       <c r="C7" s="8">
-        <v>46133.72662366898</v>
+        <v>46133.89329033565</v>
       </c>
       <c r="D7" s="8">
-        <v>46133.72662489583</v>
+        <v>46133.893291562505</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>37</v>
@@ -2519,13 +2519,13 @@
         <v>38</v>
       </c>
       <c r="B8" s="5">
-        <v>46132.42200439815</v>
+        <v>46132.58867106482</v>
       </c>
       <c r="C8" s="5">
-        <v>46133.72662822917</v>
+        <v>46133.89329489583</v>
       </c>
       <c r="D8" s="5">
-        <v>46198.487754745365</v>
+        <v>46198.65442141204</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>39</v>
@@ -2584,13 +2584,13 @@
         <v>41</v>
       </c>
       <c r="B9" s="8">
-        <v>46132.422007824076</v>
+        <v>46132.58867449074</v>
       </c>
       <c r="C9" s="8">
-        <v>46133.72663559028</v>
+        <v>46133.89330225694</v>
       </c>
       <c r="D9" s="8">
-        <v>46133.726636956024</v>
+        <v>46133.89330362268</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>42</v>
@@ -2649,13 +2649,13 @@
         <v>43</v>
       </c>
       <c r="B10" s="5">
-        <v>46132.42192311343</v>
+        <v>46132.58858978009</v>
       </c>
       <c r="C10" s="5">
-        <v>46198.48800976852</v>
+        <v>46198.65467643518</v>
       </c>
       <c r="D10" s="5">
-        <v>46198.48802768518</v>
+        <v>46198.65469435185</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>44</v>
@@ -2702,13 +2702,13 @@
         <v>46</v>
       </c>
       <c r="B11" s="8">
-        <v>46132.422011620365</v>
+        <v>46132.58867828704</v>
       </c>
       <c r="C11" s="8">
-        <v>46183.70356657407</v>
+        <v>46183.87023324074</v>
       </c>
       <c r="D11" s="8">
-        <v>46183.703586331016</v>
+        <v>46183.87025299769</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>47</v>
@@ -2767,13 +2767,13 @@
         <v>49</v>
       </c>
       <c r="B12" s="5">
-        <v>46132.42201688657</v>
+        <v>46132.588683553244</v>
       </c>
       <c r="C12" s="5">
-        <v>46157.374976990744</v>
+        <v>46157.54164365741</v>
       </c>
       <c r="D12" s="5">
-        <v>46157.37499372685</v>
+        <v>46157.541660393515</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>50</v>
@@ -2832,13 +2832,13 @@
         <v>52</v>
       </c>
       <c r="B13" s="8">
-        <v>46132.422022071754</v>
+        <v>46132.588688738426</v>
       </c>
       <c r="C13" s="8">
-        <v>46175.561882766204</v>
+        <v>46175.72854943287</v>
       </c>
       <c r="D13" s="8">
-        <v>46175.561901319445</v>
+        <v>46175.72856798611</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>53</v>
@@ -2897,13 +2897,13 @@
         <v>55</v>
       </c>
       <c r="B14" s="5">
-        <v>46132.42192842593</v>
+        <v>46132.58859509259</v>
       </c>
       <c r="C14" s="5">
-        <v>46196.473998738424</v>
+        <v>46196.640665405095</v>
       </c>
       <c r="D14" s="5">
-        <v>46196.47401210648</v>
+        <v>46196.64067877315</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>56</v>
@@ -2950,13 +2950,13 @@
         <v>58</v>
       </c>
       <c r="B15" s="8">
-        <v>46132.422032291666</v>
+        <v>46132.58869895834</v>
       </c>
       <c r="C15" s="8">
-        <v>46157.37661576389</v>
+        <v>46157.54328243056</v>
       </c>
       <c r="D15" s="8">
-        <v>46157.37663075232</v>
+        <v>46157.54329741898</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>59</v>
@@ -3015,13 +3015,13 @@
         <v>61</v>
       </c>
       <c r="B16" s="5">
-        <v>46132.42203732639</v>
+        <v>46132.58870399305</v>
       </c>
       <c r="C16" s="5">
-        <v>46157.37509891204</v>
+        <v>46157.5417655787</v>
       </c>
       <c r="D16" s="5">
-        <v>46223.43610730324</v>
+        <v>46223.602773969906</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>62</v>
@@ -3080,13 +3080,13 @@
         <v>66</v>
       </c>
       <c r="B17" s="8">
-        <v>46132.42204243055</v>
+        <v>46132.588709097225</v>
       </c>
       <c r="C17" s="8">
-        <v>46183.70363614583</v>
+        <v>46183.8703028125</v>
       </c>
       <c r="D17" s="8">
-        <v>46183.703653275465</v>
+        <v>46183.87031994213</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>67</v>
@@ -3145,13 +3145,13 @@
         <v>69</v>
       </c>
       <c r="B18" s="5">
-        <v>46132.42204715278</v>
+        <v>46132.588713819445</v>
       </c>
       <c r="C18" s="5">
-        <v>46140.459930682875</v>
+        <v>46140.62659734953</v>
       </c>
       <c r="D18" s="5">
-        <v>46237.368846377314</v>
+        <v>46237.535513043986</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>70</v>
@@ -3210,13 +3210,13 @@
         <v>73</v>
       </c>
       <c r="B19" s="8">
-        <v>46132.461424375</v>
+        <v>46132.62809104167</v>
       </c>
       <c r="C19" s="8">
-        <v>46140.459872314816</v>
+        <v>46140.62653898148</v>
       </c>
       <c r="D19" s="8">
-        <v>46237.368867847224</v>
+        <v>46237.53553451389</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>74</v>
@@ -3275,13 +3275,13 @@
         <v>76</v>
       </c>
       <c r="B20" s="5">
-        <v>46132.46132069445</v>
+        <v>46132.62798736111</v>
       </c>
       <c r="C20" s="5">
-        <v>46196.47397947917</v>
+        <v>46196.64064614583</v>
       </c>
       <c r="D20" s="5">
-        <v>46223.669122708336</v>
+        <v>46223.835789375</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>77</v>
@@ -3340,13 +3340,13 @@
         <v>79</v>
       </c>
       <c r="B21" s="8">
-        <v>46132.461378645836</v>
+        <v>46132.6280453125</v>
       </c>
       <c r="C21" s="8">
-        <v>46140.459785416664</v>
+        <v>46140.626452083336</v>
       </c>
       <c r="D21" s="8">
-        <v>46237.36889398148</v>
+        <v>46237.535560648146</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>80</v>
@@ -3405,11 +3405,11 @@
         <v>82</v>
       </c>
       <c r="B22" s="5">
-        <v>46132.42193364583</v>
+        <v>46132.588600312505</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46229.40048015046</v>
+        <v>46229.567146817135</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>83</v>
@@ -3454,13 +3454,13 @@
         <v>86</v>
       </c>
       <c r="B23" s="8">
-        <v>46132.42205288194</v>
+        <v>46132.588719548614</v>
       </c>
       <c r="C23" s="8">
-        <v>46157.376424131944</v>
+        <v>46157.543090798616</v>
       </c>
       <c r="D23" s="8">
-        <v>46157.376913182874</v>
+        <v>46157.54357984954</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>87</v>
@@ -3519,13 +3519,13 @@
         <v>91</v>
       </c>
       <c r="B24" s="5">
-        <v>46132.42205756945</v>
+        <v>46132.588724236106</v>
       </c>
       <c r="C24" s="5">
-        <v>46157.37668335648</v>
+        <v>46157.543350023145</v>
       </c>
       <c r="D24" s="5">
-        <v>46157.37668490741</v>
+        <v>46157.54335157407</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>92</v>
@@ -3580,13 +3580,13 @@
         <v>98</v>
       </c>
       <c r="B25" s="8">
-        <v>46132.42206225694</v>
+        <v>46132.58872892361</v>
       </c>
       <c r="C25" s="8">
-        <v>46157.37672043982</v>
+        <v>46157.54338710648</v>
       </c>
       <c r="D25" s="8">
-        <v>46157.376721759254</v>
+        <v>46157.543388425926</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>99</v>
@@ -3641,13 +3641,13 @@
         <v>101</v>
       </c>
       <c r="B26" s="5">
-        <v>46132.422067314816</v>
+        <v>46132.58873398148</v>
       </c>
       <c r="C26" s="5">
-        <v>46157.37520400463</v>
+        <v>46157.541870671295</v>
       </c>
       <c r="D26" s="5">
-        <v>46162.00908238426</v>
+        <v>46162.175749050926</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>102</v>
@@ -3706,13 +3706,13 @@
         <v>104</v>
       </c>
       <c r="B27" s="8">
-        <v>46132.4220722801</v>
+        <v>46132.58873894676</v>
       </c>
       <c r="C27" s="8">
-        <v>46157.37514805555</v>
+        <v>46157.54181472222</v>
       </c>
       <c r="D27" s="8">
-        <v>46157.375149988424</v>
+        <v>46157.541816655095</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>105</v>
@@ -3767,13 +3767,13 @@
         <v>107</v>
       </c>
       <c r="B28" s="5">
-        <v>46132.422077256946</v>
+        <v>46132.58874392361</v>
       </c>
       <c r="C28" s="5">
-        <v>46157.3751890162</v>
+        <v>46157.541855682866</v>
       </c>
       <c r="D28" s="5">
-        <v>46157.37519023148</v>
+        <v>46157.54185689815</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>108</v>
@@ -3828,13 +3828,13 @@
         <v>110</v>
       </c>
       <c r="B29" s="8">
-        <v>46132.42208211806</v>
+        <v>46132.58874878472</v>
       </c>
       <c r="C29" s="8">
-        <v>46191.742483449074</v>
+        <v>46191.90915011574</v>
       </c>
       <c r="D29" s="8">
-        <v>46191.74251975694</v>
+        <v>46191.90918642361</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>111</v>
@@ -3893,13 +3893,13 @@
         <v>113</v>
       </c>
       <c r="B30" s="5">
-        <v>46132.42208668981</v>
+        <v>46132.58875335648</v>
       </c>
       <c r="C30" s="5">
-        <v>46191.74191864583</v>
+        <v>46191.9085853125</v>
       </c>
       <c r="D30" s="5">
-        <v>46191.74192392361</v>
+        <v>46191.908590590276</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>114</v>
@@ -3954,13 +3954,13 @@
         <v>116</v>
       </c>
       <c r="B31" s="8">
-        <v>46132.42209600694</v>
+        <v>46132.58876267361</v>
       </c>
       <c r="C31" s="8">
-        <v>46191.74246421296</v>
+        <v>46191.909130879634</v>
       </c>
       <c r="D31" s="8">
-        <v>46191.74246603009</v>
+        <v>46191.90913269676</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>117</v>
@@ -4015,13 +4015,13 @@
         <v>120</v>
       </c>
       <c r="B32" s="5">
-        <v>46132.42209122685</v>
+        <v>46132.58875789352</v>
       </c>
       <c r="C32" s="5">
-        <v>46191.74241533565</v>
+        <v>46191.90908200231</v>
       </c>
       <c r="D32" s="5">
-        <v>46191.74241868056</v>
+        <v>46191.90908534722</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>118</v>
@@ -4076,13 +4076,13 @@
         <v>122</v>
       </c>
       <c r="B33" s="8">
-        <v>46132.42210037037</v>
+        <v>46132.588767037036</v>
       </c>
       <c r="C33" s="8">
-        <v>46140.460326030094</v>
+        <v>46140.62699269676</v>
       </c>
       <c r="D33" s="8">
-        <v>46178.00184576389</v>
+        <v>46178.16851243055</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>123</v>
@@ -4141,13 +4141,13 @@
         <v>127</v>
       </c>
       <c r="B34" s="5">
-        <v>46132.42210472222</v>
+        <v>46132.58877138889</v>
       </c>
       <c r="C34" s="5">
-        <v>46140.460234004626</v>
+        <v>46140.6269006713</v>
       </c>
       <c r="D34" s="5">
-        <v>46140.46023538194</v>
+        <v>46140.62690204861</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>128</v>
@@ -4202,13 +4202,13 @@
         <v>130</v>
       </c>
       <c r="B35" s="8">
-        <v>46132.42210923611</v>
+        <v>46132.58877590278</v>
       </c>
       <c r="C35" s="8">
-        <v>46140.460271655094</v>
+        <v>46140.62693832176</v>
       </c>
       <c r="D35" s="8">
-        <v>46140.460273703706</v>
+        <v>46140.62694037037</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>131</v>
@@ -4263,13 +4263,13 @@
         <v>133</v>
       </c>
       <c r="B36" s="5">
-        <v>46132.46017288194</v>
+        <v>46132.62683954861</v>
       </c>
       <c r="C36" s="5">
-        <v>46140.46030037037</v>
+        <v>46140.62696703704</v>
       </c>
       <c r="D36" s="5">
-        <v>46178.001846875</v>
+        <v>46178.16851354166</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>134</v>
@@ -4328,13 +4328,13 @@
         <v>136</v>
       </c>
       <c r="B37" s="8">
-        <v>46132.46046269676</v>
+        <v>46132.62712936343</v>
       </c>
       <c r="C37" s="8">
-        <v>46140.46011893518</v>
+        <v>46140.62678560185</v>
       </c>
       <c r="D37" s="8">
-        <v>46140.46012013889</v>
+        <v>46140.62678680556</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>75</v>
@@ -4383,13 +4383,13 @@
         <v>138</v>
       </c>
       <c r="B38" s="5">
-        <v>46132.46060174768</v>
+        <v>46132.62726841435</v>
       </c>
       <c r="C38" s="5">
-        <v>46140.46015943287</v>
+        <v>46140.62682609954</v>
       </c>
       <c r="D38" s="5">
-        <v>46140.4601606713</v>
+        <v>46140.62682733797</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>139</v>
@@ -4438,13 +4438,13 @@
         <v>141</v>
       </c>
       <c r="B39" s="8">
-        <v>46132.46030399305</v>
+        <v>46132.62697065972</v>
       </c>
       <c r="C39" s="8">
-        <v>46147.73109282408</v>
+        <v>46147.89775949074</v>
       </c>
       <c r="D39" s="8">
-        <v>46178.0018456713</v>
+        <v>46178.16851233796</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>142</v>
@@ -4503,13 +4503,13 @@
         <v>144</v>
       </c>
       <c r="B40" s="5">
-        <v>46132.46086706019</v>
+        <v>46132.62753372685</v>
       </c>
       <c r="C40" s="5">
-        <v>46140.46041891204</v>
+        <v>46140.6270855787</v>
       </c>
       <c r="D40" s="5">
-        <v>46140.46042069445</v>
+        <v>46140.62708736111</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>81</v>
@@ -4558,13 +4558,13 @@
         <v>146</v>
       </c>
       <c r="B41" s="8">
-        <v>46132.46094913194</v>
+        <v>46132.627615798614</v>
       </c>
       <c r="C41" s="8">
-        <v>46147.731079641206</v>
+        <v>46147.89774630787</v>
       </c>
       <c r="D41" s="8">
-        <v>46147.731081307866</v>
+        <v>46147.89774797454</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>147</v>
@@ -4613,11 +4613,11 @@
         <v>149</v>
       </c>
       <c r="B42" s="5">
-        <v>46132.421939837965</v>
+        <v>46132.58860650463</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46191.750940555554</v>
+        <v>46191.91760722222</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>150</v>
@@ -4660,13 +4660,13 @@
         <v>152</v>
       </c>
       <c r="B43" s="8">
-        <v>46132.42217290509</v>
+        <v>46132.58883957176</v>
       </c>
       <c r="C43" s="8">
-        <v>46175.56198648148</v>
+        <v>46175.72865314815</v>
       </c>
       <c r="D43" s="8">
-        <v>46197.543685324075</v>
+        <v>46197.71035199074</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>153</v>
@@ -4725,13 +4725,13 @@
         <v>157</v>
       </c>
       <c r="B44" s="5">
-        <v>46132.42218010417</v>
+        <v>46132.58884677083</v>
       </c>
       <c r="C44" s="5">
-        <v>46191.75073015047</v>
+        <v>46191.91739681713</v>
       </c>
       <c r="D44" s="5">
-        <v>46197.54371334491</v>
+        <v>46197.71038001157</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>158</v>
@@ -4790,13 +4790,13 @@
         <v>161</v>
       </c>
       <c r="B45" s="8">
-        <v>46132.42218681713</v>
+        <v>46132.5888534838</v>
       </c>
       <c r="C45" s="8">
-        <v>46191.75091565972</v>
+        <v>46191.917582326394</v>
       </c>
       <c r="D45" s="8">
-        <v>46191.750941273145</v>
+        <v>46191.91760793982</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>71</v>
@@ -4853,11 +4853,11 @@
         <v>165</v>
       </c>
       <c r="B46" s="5">
-        <v>46132.42219435185</v>
+        <v>46132.58886101852</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46225.020048032406</v>
+        <v>46225.18671469907</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>166</v>
@@ -4914,11 +4914,11 @@
         <v>170</v>
       </c>
       <c r="B47" s="8">
-        <v>46132.46788423611</v>
+        <v>46132.634550902774</v>
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="8">
-        <v>46224.00112587963</v>
+        <v>46224.1677925463</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>171</v>
@@ -4965,11 +4965,11 @@
         <v>174</v>
       </c>
       <c r="B48" s="5">
-        <v>46132.46789189815</v>
+        <v>46132.634558564816</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46224.001128206015</v>
+        <v>46224.16779487269</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>175</v>
@@ -5016,11 +5016,11 @@
         <v>177</v>
       </c>
       <c r="B49" s="8">
-        <v>46132.46790087963</v>
+        <v>46132.634567546294</v>
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="8">
-        <v>46224.00112954861</v>
+        <v>46224.167796215275</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>178</v>
@@ -5067,11 +5067,11 @@
         <v>179</v>
       </c>
       <c r="B50" s="5">
-        <v>46132.46790520834</v>
+        <v>46132.634571875</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46224.00113114584</v>
+        <v>46224.1677978125</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>180</v>
@@ -5118,11 +5118,11 @@
         <v>181</v>
       </c>
       <c r="B51" s="8">
-        <v>46132.467911053245</v>
+        <v>46132.6345777199</v>
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="8">
-        <v>46224.0011325463</v>
+        <v>46224.16779921296</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>182</v>
@@ -5169,11 +5169,11 @@
         <v>183</v>
       </c>
       <c r="B52" s="5">
-        <v>46132.4679154051</v>
+        <v>46132.634582071754</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46224.00113405092</v>
+        <v>46224.167800717594</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>184</v>
@@ -5220,11 +5220,11 @@
         <v>185</v>
       </c>
       <c r="B53" s="8">
-        <v>46132.46791936342</v>
+        <v>46132.63458603009</v>
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="8">
-        <v>46224.001135625</v>
+        <v>46224.16780229167</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>186</v>
@@ -5271,11 +5271,11 @@
         <v>188</v>
       </c>
       <c r="B54" s="5">
-        <v>46132.46792502315</v>
+        <v>46132.63459168981</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46224.00113700231</v>
+        <v>46224.167803668985</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>189</v>
@@ -5322,11 +5322,11 @@
         <v>190</v>
       </c>
       <c r="B55" s="8">
-        <v>46132.46793042824</v>
+        <v>46132.634597094904</v>
       </c>
       <c r="C55" s="9"/>
       <c r="D55" s="8">
-        <v>46224.00113846065</v>
+        <v>46224.16780512732</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>191</v>
@@ -5373,11 +5373,11 @@
         <v>192</v>
       </c>
       <c r="B56" s="5">
-        <v>46132.46793587963</v>
+        <v>46132.6346025463</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46224.00113982639</v>
+        <v>46224.16780649306</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>193</v>
@@ -5424,11 +5424,11 @@
         <v>194</v>
       </c>
       <c r="B57" s="8">
-        <v>46132.46800738426</v>
+        <v>46132.634674050925</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46224.00114262731</v>
+        <v>46224.167809293984</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>195</v>
@@ -5475,11 +5475,11 @@
         <v>196</v>
       </c>
       <c r="B58" s="5">
-        <v>46132.468022326386</v>
+        <v>46132.63468899306</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46224.00114395833</v>
+        <v>46224.167810625004</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>197</v>
@@ -5526,11 +5526,11 @@
         <v>198</v>
       </c>
       <c r="B59" s="8">
-        <v>46132.46804099537</v>
+        <v>46132.63470766204</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46224.00114541667</v>
+        <v>46224.16781208334</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>199</v>
@@ -5577,11 +5577,11 @@
         <v>200</v>
       </c>
       <c r="B60" s="5">
-        <v>46132.46805321759</v>
+        <v>46132.634719884256</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46224.001147256946</v>
+        <v>46224.16781392361</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>201</v>
@@ -5628,11 +5628,11 @@
         <v>202</v>
       </c>
       <c r="B61" s="8">
-        <v>46132.46806118055</v>
+        <v>46132.634727847224</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46224.00114879629</v>
+        <v>46224.16781546296</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>203</v>
@@ -5679,11 +5679,11 @@
         <v>205</v>
       </c>
       <c r="B62" s="5">
-        <v>46132.46794055555</v>
+        <v>46132.63460722222</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46224.00114116898</v>
+        <v>46224.16780783565</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>206</v>
@@ -5730,13 +5730,13 @@
         <v>208</v>
       </c>
       <c r="B63" s="8">
-        <v>46132.48055251157</v>
+        <v>46132.64721917824</v>
       </c>
       <c r="C63" s="8">
-        <v>46157.32731126157</v>
+        <v>46157.49397792824</v>
       </c>
       <c r="D63" s="8">
-        <v>46229.40980494213</v>
+        <v>46229.5764716088</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>209</v>
@@ -5783,13 +5783,13 @@
         <v>211</v>
       </c>
       <c r="B64" s="5">
-        <v>46132.45817625</v>
+        <v>46132.624842916666</v>
       </c>
       <c r="C64" s="5">
-        <v>46157.32715798611</v>
+        <v>46157.493824652774</v>
       </c>
       <c r="D64" s="5">
-        <v>46182.01687796296</v>
+        <v>46182.18354462963</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>212</v>
@@ -5848,13 +5848,13 @@
         <v>214</v>
       </c>
       <c r="B65" s="8">
-        <v>46132.45824061343</v>
+        <v>46132.62490728009</v>
       </c>
       <c r="C65" s="8">
-        <v>46157.327186828705</v>
+        <v>46157.49385349537</v>
       </c>
       <c r="D65" s="8">
-        <v>46182.01687792824</v>
+        <v>46182.18354459491</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>215</v>
@@ -5913,13 +5913,13 @@
         <v>217</v>
       </c>
       <c r="B66" s="5">
-        <v>46132.45828695602</v>
+        <v>46132.62495362268</v>
       </c>
       <c r="C66" s="5">
-        <v>46157.32720113426</v>
+        <v>46157.49386780093</v>
       </c>
       <c r="D66" s="5">
-        <v>46182.01687810185</v>
+        <v>46182.183544768515</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>218</v>
@@ -5978,13 +5978,13 @@
         <v>220</v>
       </c>
       <c r="B67" s="8">
-        <v>46132.54075635417</v>
+        <v>46132.70742302084</v>
       </c>
       <c r="C67" s="8">
-        <v>46157.32728145833</v>
+        <v>46157.493948125004</v>
       </c>
       <c r="D67" s="8">
-        <v>46184.03642771991</v>
+        <v>46184.203094386576</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>221</v>
@@ -6043,13 +6043,13 @@
         <v>225</v>
       </c>
       <c r="B68" s="5">
-        <v>46132.5408630787</v>
+        <v>46132.70752974537</v>
       </c>
       <c r="C68" s="5">
-        <v>46157.32728627315</v>
+        <v>46157.49395293981</v>
       </c>
       <c r="D68" s="5">
-        <v>46184.036431354165</v>
+        <v>46184.20309802084</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>226</v>
@@ -6108,13 +6108,13 @@
         <v>228</v>
       </c>
       <c r="B69" s="8">
-        <v>46132.540933842596</v>
+        <v>46132.70760050926</v>
       </c>
       <c r="C69" s="8">
-        <v>46157.32729354167</v>
+        <v>46157.49396020833</v>
       </c>
       <c r="D69" s="8">
-        <v>46184.03642754629</v>
+        <v>46184.203094212964</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>229</v>
@@ -6173,13 +6173,13 @@
         <v>230</v>
       </c>
       <c r="B70" s="5">
-        <v>46132.42221524306</v>
+        <v>46132.58888190972</v>
       </c>
       <c r="C70" s="5">
-        <v>46209.4661074537</v>
+        <v>46209.63277412037</v>
       </c>
       <c r="D70" s="5">
-        <v>46209.46612056713</v>
+        <v>46209.6327872338</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>231</v>
@@ -6226,13 +6226,13 @@
         <v>233</v>
       </c>
       <c r="B71" s="8">
-        <v>46132.42221851852</v>
+        <v>46132.588885185185</v>
       </c>
       <c r="C71" s="8">
-        <v>46196.51747346065</v>
+        <v>46196.68414012731</v>
       </c>
       <c r="D71" s="8">
-        <v>46196.517488206024</v>
+        <v>46196.68415487268</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>78</v>
@@ -6291,13 +6291,13 @@
         <v>237</v>
       </c>
       <c r="B72" s="5">
-        <v>46132.422223761576</v>
+        <v>46132.58889042824</v>
       </c>
       <c r="C72" s="5">
-        <v>46196.5253103125</v>
+        <v>46196.69197697917</v>
       </c>
       <c r="D72" s="5">
-        <v>46229.382425393516</v>
+        <v>46229.54909206019</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>238</v>
@@ -6356,13 +6356,13 @@
         <v>240</v>
       </c>
       <c r="B73" s="8">
-        <v>46132.46461180555</v>
+        <v>46132.631278472225</v>
       </c>
       <c r="C73" s="8">
-        <v>46196.524641261574</v>
+        <v>46196.69130792824</v>
       </c>
       <c r="D73" s="8">
-        <v>46196.52599383102</v>
+        <v>46196.69266049768</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>172</v>
@@ -6411,13 +6411,13 @@
         <v>243</v>
       </c>
       <c r="B74" s="5">
-        <v>46132.46462783565</v>
+        <v>46132.63129450232</v>
       </c>
       <c r="C74" s="5">
-        <v>46196.524939421295</v>
+        <v>46196.69160608796</v>
       </c>
       <c r="D74" s="5">
-        <v>46196.52617824074</v>
+        <v>46196.692844907404</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>172</v>
@@ -6466,13 +6466,13 @@
         <v>244</v>
       </c>
       <c r="B75" s="8">
-        <v>46132.46463585648</v>
+        <v>46132.63130252315</v>
       </c>
       <c r="C75" s="8">
-        <v>46196.52528230324</v>
+        <v>46196.69194896991</v>
       </c>
       <c r="D75" s="8">
-        <v>46196.52651319445</v>
+        <v>46196.69317986111</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>172</v>
@@ -6521,13 +6521,13 @@
         <v>247</v>
       </c>
       <c r="B76" s="5">
-        <v>46132.46464202546</v>
+        <v>46132.63130869213</v>
       </c>
       <c r="C76" s="5">
-        <v>46196.52528314815</v>
+        <v>46196.69194981482</v>
       </c>
       <c r="D76" s="5">
-        <v>46196.52647592593</v>
+        <v>46196.693142592594</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>172</v>
@@ -6576,13 +6576,13 @@
         <v>248</v>
       </c>
       <c r="B77" s="8">
-        <v>46132.46464780092</v>
+        <v>46132.631314467595</v>
       </c>
       <c r="C77" s="8">
-        <v>46196.52528375</v>
+        <v>46196.691950416665</v>
       </c>
       <c r="D77" s="8">
-        <v>46196.52646479166</v>
+        <v>46196.693131458334</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>172</v>
@@ -6631,13 +6631,13 @@
         <v>250</v>
       </c>
       <c r="B78" s="5">
-        <v>46132.46465391204</v>
+        <v>46132.6313205787</v>
       </c>
       <c r="C78" s="5">
-        <v>46196.5252843287</v>
+        <v>46196.69195099537</v>
       </c>
       <c r="D78" s="5">
-        <v>46196.52645405092</v>
+        <v>46196.693120717595</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>172</v>
@@ -6686,13 +6686,13 @@
         <v>252</v>
       </c>
       <c r="B79" s="8">
-        <v>46132.46465927083</v>
+        <v>46132.6313259375</v>
       </c>
       <c r="C79" s="8">
-        <v>46196.525284918986</v>
+        <v>46196.69195158565</v>
       </c>
       <c r="D79" s="8">
-        <v>46196.52643376157</v>
+        <v>46196.69310042824</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>172</v>
@@ -6741,13 +6741,13 @@
         <v>254</v>
       </c>
       <c r="B80" s="5">
-        <v>46132.46466375</v>
+        <v>46132.63133041667</v>
       </c>
       <c r="C80" s="5">
-        <v>46196.52528554398</v>
+        <v>46196.69195221065</v>
       </c>
       <c r="D80" s="5">
-        <v>46196.52641928241</v>
+        <v>46196.693085949075</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>172</v>
@@ -6796,13 +6796,13 @@
         <v>256</v>
       </c>
       <c r="B81" s="8">
-        <v>46132.46466979166</v>
+        <v>46132.63133645833</v>
       </c>
       <c r="C81" s="8">
-        <v>46196.52528618056</v>
+        <v>46196.69195284722</v>
       </c>
       <c r="D81" s="8">
-        <v>46196.52640701389</v>
+        <v>46196.69307368055</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>172</v>
@@ -6851,13 +6851,13 @@
         <v>257</v>
       </c>
       <c r="B82" s="5">
-        <v>46132.46467407407</v>
+        <v>46132.63134074074</v>
       </c>
       <c r="C82" s="5">
-        <v>46196.525081678235</v>
+        <v>46196.69174834491</v>
       </c>
       <c r="D82" s="5">
-        <v>46196.52639375</v>
+        <v>46196.69306041667</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>172</v>
@@ -6906,13 +6906,13 @@
         <v>259</v>
       </c>
       <c r="B83" s="8">
-        <v>46132.46467980324</v>
+        <v>46132.631346469905</v>
       </c>
       <c r="C83" s="8">
-        <v>46196.52528677083</v>
+        <v>46196.691953437505</v>
       </c>
       <c r="D83" s="8">
-        <v>46196.52638289351</v>
+        <v>46196.693049560185</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>172</v>
@@ -6961,13 +6961,13 @@
         <v>260</v>
       </c>
       <c r="B84" s="5">
-        <v>46132.464685416664</v>
+        <v>46132.631352083336</v>
       </c>
       <c r="C84" s="5">
-        <v>46196.525287372686</v>
+        <v>46196.69195403935</v>
       </c>
       <c r="D84" s="5">
-        <v>46196.52637547454</v>
+        <v>46196.6930421412</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>172</v>
@@ -7016,13 +7016,13 @@
         <v>261</v>
       </c>
       <c r="B85" s="8">
-        <v>46132.464691099536</v>
+        <v>46132.63135776621</v>
       </c>
       <c r="C85" s="8">
-        <v>46196.52528796296</v>
+        <v>46196.69195462963</v>
       </c>
       <c r="D85" s="8">
-        <v>46196.5263637037</v>
+        <v>46196.69303037037</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>172</v>
@@ -7071,13 +7071,13 @@
         <v>262</v>
       </c>
       <c r="B86" s="5">
-        <v>46132.4646962963</v>
+        <v>46132.63136296296</v>
       </c>
       <c r="C86" s="5">
-        <v>46196.525288599536</v>
+        <v>46196.6919552662</v>
       </c>
       <c r="D86" s="5">
-        <v>46196.526354560185</v>
+        <v>46196.69302122685</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>172</v>
@@ -7126,13 +7126,13 @@
         <v>264</v>
       </c>
       <c r="B87" s="8">
-        <v>46132.464700219905</v>
+        <v>46132.63136688658</v>
       </c>
       <c r="C87" s="8">
-        <v>46196.52528920139</v>
+        <v>46196.69195586805</v>
       </c>
       <c r="D87" s="8">
-        <v>46196.52632887731</v>
+        <v>46196.692995543985</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>172</v>
@@ -7181,13 +7181,13 @@
         <v>266</v>
       </c>
       <c r="B88" s="5">
-        <v>46132.464705729166</v>
+        <v>46132.63137239583</v>
       </c>
       <c r="C88" s="5">
-        <v>46196.525289791665</v>
+        <v>46196.69195645834</v>
       </c>
       <c r="D88" s="5">
-        <v>46196.52634332176</v>
+        <v>46196.69300998843</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>172</v>
@@ -7236,13 +7236,13 @@
         <v>267</v>
       </c>
       <c r="B89" s="8">
-        <v>46132.42223142361</v>
+        <v>46132.58889809028</v>
       </c>
       <c r="C89" s="8">
-        <v>46209.46609234954</v>
+        <v>46209.6327590162</v>
       </c>
       <c r="D89" s="8">
-        <v>46229.3824455787</v>
+        <v>46229.54911224537</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>268</v>
@@ -7301,13 +7301,13 @@
         <v>270</v>
       </c>
       <c r="B90" s="5">
-        <v>46132.46481228009</v>
+        <v>46132.63147894676</v>
       </c>
       <c r="C90" s="5">
-        <v>46196.746636655094</v>
+        <v>46196.91330332176</v>
       </c>
       <c r="D90" s="5">
-        <v>46196.74663871528</v>
+        <v>46196.913305381946</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>271</v>
@@ -7356,13 +7356,13 @@
         <v>274</v>
       </c>
       <c r="B91" s="8">
-        <v>46132.46482415509</v>
+        <v>46132.63149082176</v>
       </c>
       <c r="C91" s="8">
-        <v>46196.7466421412</v>
+        <v>46196.91330880787</v>
       </c>
       <c r="D91" s="8">
-        <v>46196.74664359954</v>
+        <v>46196.9133102662</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>271</v>
@@ -7411,13 +7411,13 @@
         <v>276</v>
       </c>
       <c r="B92" s="5">
-        <v>46132.464830474535</v>
+        <v>46132.63149714121</v>
       </c>
       <c r="C92" s="5">
-        <v>46196.746649988425</v>
+        <v>46196.91331665509</v>
       </c>
       <c r="D92" s="5">
-        <v>46196.746651423615</v>
+        <v>46196.91331809028</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>271</v>
@@ -7466,13 +7466,13 @@
         <v>277</v>
       </c>
       <c r="B93" s="8">
-        <v>46132.464836134255</v>
+        <v>46132.63150280093</v>
       </c>
       <c r="C93" s="8">
-        <v>46196.74665744213</v>
+        <v>46196.9133241088</v>
       </c>
       <c r="D93" s="8">
-        <v>46196.74665935185</v>
+        <v>46196.91332601852</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>271</v>
@@ -7521,13 +7521,13 @@
         <v>278</v>
       </c>
       <c r="B94" s="5">
-        <v>46132.464842291665</v>
+        <v>46132.63150895834</v>
       </c>
       <c r="C94" s="5">
-        <v>46196.74666237269</v>
+        <v>46196.91332903935</v>
       </c>
       <c r="D94" s="5">
-        <v>46196.74666398148</v>
+        <v>46196.91333064815</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>271</v>
@@ -7576,13 +7576,13 @@
         <v>279</v>
       </c>
       <c r="B95" s="8">
-        <v>46132.464847662035</v>
+        <v>46132.63151432871</v>
       </c>
       <c r="C95" s="8">
-        <v>46196.74666975695</v>
+        <v>46196.91333642361</v>
       </c>
       <c r="D95" s="8">
-        <v>46196.7466715162</v>
+        <v>46196.91333818287</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>271</v>
@@ -7631,13 +7631,13 @@
         <v>280</v>
       </c>
       <c r="B96" s="5">
-        <v>46132.4648528588</v>
+        <v>46132.631519525465</v>
       </c>
       <c r="C96" s="5">
-        <v>46196.746680069446</v>
+        <v>46196.91334673611</v>
       </c>
       <c r="D96" s="5">
-        <v>46196.74668182871</v>
+        <v>46196.91334849537</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>271</v>
@@ -7686,13 +7686,13 @@
         <v>281</v>
       </c>
       <c r="B97" s="8">
-        <v>46132.46485758101</v>
+        <v>46132.631524247685</v>
       </c>
       <c r="C97" s="8">
-        <v>46196.74668758102</v>
+        <v>46196.913354247685</v>
       </c>
       <c r="D97" s="8">
-        <v>46196.74668917824</v>
+        <v>46196.91335584491</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>271</v>
@@ -7741,13 +7741,13 @@
         <v>282</v>
       </c>
       <c r="B98" s="5">
-        <v>46132.464864837966</v>
+        <v>46132.63153150463</v>
       </c>
       <c r="C98" s="5">
-        <v>46196.74669226852</v>
+        <v>46196.913358935184</v>
       </c>
       <c r="D98" s="5">
-        <v>46196.74669421296</v>
+        <v>46196.913360879626</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>271</v>
@@ -7796,13 +7796,13 @@
         <v>283</v>
       </c>
       <c r="B99" s="8">
-        <v>46132.46487260416</v>
+        <v>46132.631539270835</v>
       </c>
       <c r="C99" s="8">
-        <v>46196.74670118056</v>
+        <v>46196.91336784722</v>
       </c>
       <c r="D99" s="8">
-        <v>46196.74670278935</v>
+        <v>46196.913369456015</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>271</v>
@@ -7851,13 +7851,13 @@
         <v>284</v>
       </c>
       <c r="B100" s="5">
-        <v>46132.46487950231</v>
+        <v>46132.63154616898</v>
       </c>
       <c r="C100" s="5">
-        <v>46196.74671489584</v>
+        <v>46196.913381562495</v>
       </c>
       <c r="D100" s="5">
-        <v>46196.746716388894</v>
+        <v>46196.91338305555</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>271</v>
@@ -7906,13 +7906,13 @@
         <v>285</v>
       </c>
       <c r="B101" s="8">
-        <v>46132.46488840278</v>
+        <v>46132.63155506944</v>
       </c>
       <c r="C101" s="8">
-        <v>46196.746723715274</v>
+        <v>46196.913390381946</v>
       </c>
       <c r="D101" s="8">
-        <v>46196.74672523148</v>
+        <v>46196.91339189815</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>271</v>
@@ -7961,13 +7961,13 @@
         <v>286</v>
       </c>
       <c r="B102" s="5">
-        <v>46132.464897557875</v>
+        <v>46132.63156422453</v>
       </c>
       <c r="C102" s="5">
-        <v>46196.74673101852</v>
+        <v>46196.91339768519</v>
       </c>
       <c r="D102" s="5">
-        <v>46196.74673273148</v>
+        <v>46196.91339939815</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>271</v>
@@ -8016,13 +8016,13 @@
         <v>287</v>
       </c>
       <c r="B103" s="8">
-        <v>46132.46490584491</v>
+        <v>46132.63157251157</v>
       </c>
       <c r="C103" s="8">
-        <v>46209.46581571759</v>
+        <v>46209.63248238426</v>
       </c>
       <c r="D103" s="8">
-        <v>46209.46581846065</v>
+        <v>46209.63248512732</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>271</v>
@@ -8071,13 +8071,13 @@
         <v>288</v>
       </c>
       <c r="B104" s="5">
-        <v>46132.46490997685</v>
+        <v>46132.631576643515</v>
       </c>
       <c r="C104" s="5">
-        <v>46209.46582233797</v>
+        <v>46209.63248900463</v>
       </c>
       <c r="D104" s="5">
-        <v>46209.465824259256</v>
+        <v>46209.63249092593</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>172</v>
@@ -8126,13 +8126,13 @@
         <v>289</v>
       </c>
       <c r="B105" s="8">
-        <v>46132.46524119213</v>
+        <v>46132.6319078588</v>
       </c>
       <c r="C105" s="8">
-        <v>46209.46582841435</v>
+        <v>46209.63249508102</v>
       </c>
       <c r="D105" s="8">
-        <v>46209.465830127316</v>
+        <v>46209.63249679398</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>271</v>
@@ -8181,13 +8181,13 @@
         <v>290</v>
       </c>
       <c r="B106" s="5">
-        <v>46132.42223726852</v>
+        <v>46132.58890393519</v>
       </c>
       <c r="C106" s="5">
-        <v>46198.488557627315</v>
+        <v>46198.65522429398</v>
       </c>
       <c r="D106" s="5">
-        <v>46198.48857134259</v>
+        <v>46198.65523800926</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>291</v>
@@ -8234,13 +8234,13 @@
         <v>293</v>
       </c>
       <c r="B107" s="8">
-        <v>46132.42224050926</v>
+        <v>46132.58890717593</v>
       </c>
       <c r="C107" s="8">
-        <v>46198.48843424769</v>
+        <v>46198.65510091435</v>
       </c>
       <c r="D107" s="8">
-        <v>46198.48845240741</v>
+        <v>46198.65511907407</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>294</v>
@@ -8297,13 +8297,13 @@
         <v>296</v>
       </c>
       <c r="B108" s="5">
-        <v>46132.42224613426</v>
+        <v>46132.58891280093</v>
       </c>
       <c r="C108" s="5">
-        <v>46157.37537709491</v>
+        <v>46157.542043761576</v>
       </c>
       <c r="D108" s="5">
-        <v>46163.022396562505</v>
+        <v>46163.18906322916</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>297</v>
@@ -8360,13 +8360,13 @@
         <v>298</v>
       </c>
       <c r="B109" s="8">
-        <v>46132.42225142361</v>
+        <v>46132.588918090274</v>
       </c>
       <c r="C109" s="8">
-        <v>46198.48854150463</v>
+        <v>46198.6552081713</v>
       </c>
       <c r="D109" s="8">
-        <v>46198.488598344906</v>
+        <v>46198.65526501158</v>
       </c>
       <c r="E109" s="9" t="s">
         <v>299</v>
@@ -8423,11 +8423,11 @@
         <v>301</v>
       </c>
       <c r="B110" s="5">
-        <v>46132.422256446764</v>
+        <v>46132.58892311342</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46205.3248571875</v>
+        <v>46205.491523854165</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>302</v>
@@ -8470,13 +8470,13 @@
         <v>304</v>
       </c>
       <c r="B111" s="8">
-        <v>46132.42225991898</v>
+        <v>46132.58892658565</v>
       </c>
       <c r="C111" s="8">
-        <v>46205.324844884264</v>
+        <v>46205.49151155092</v>
       </c>
       <c r="D111" s="8">
-        <v>46229.82059986111</v>
+        <v>46229.98726652778</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>305</v>
@@ -8535,13 +8535,13 @@
         <v>307</v>
       </c>
       <c r="B112" s="5">
-        <v>46132.465366516204</v>
+        <v>46132.632033182876</v>
       </c>
       <c r="C112" s="5">
-        <v>46205.324200613424</v>
+        <v>46205.490867280096</v>
       </c>
       <c r="D112" s="5">
-        <v>46223.43705320602</v>
+        <v>46223.603719872684</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>172</v>
@@ -8590,13 +8590,13 @@
         <v>309</v>
       </c>
       <c r="B113" s="8">
-        <v>46132.465438645835</v>
+        <v>46132.6321053125</v>
       </c>
       <c r="C113" s="8">
-        <v>46205.32423546296</v>
+        <v>46205.49090212963</v>
       </c>
       <c r="D113" s="8">
-        <v>46223.43704956018</v>
+        <v>46223.60371622685</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>271</v>
@@ -8645,13 +8645,13 @@
         <v>310</v>
       </c>
       <c r="B114" s="5">
-        <v>46132.46544728009</v>
+        <v>46132.63211394676</v>
       </c>
       <c r="C114" s="5">
-        <v>46205.32425060185</v>
+        <v>46205.490917268515</v>
       </c>
       <c r="D114" s="5">
-        <v>46223.437045625</v>
+        <v>46223.60371229167</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>271</v>
@@ -8700,13 +8700,13 @@
         <v>312</v>
       </c>
       <c r="B115" s="8">
-        <v>46132.46545552083</v>
+        <v>46132.6321221875</v>
       </c>
       <c r="C115" s="8">
-        <v>46205.32426221065</v>
+        <v>46205.49092887732</v>
       </c>
       <c r="D115" s="8">
-        <v>46223.43704201389</v>
+        <v>46223.60370868056</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>172</v>
@@ -8755,13 +8755,13 @@
         <v>313</v>
       </c>
       <c r="B116" s="5">
-        <v>46132.465461631946</v>
+        <v>46132.63212829861</v>
       </c>
       <c r="C116" s="5">
-        <v>46205.32427462963</v>
+        <v>46205.490941296295</v>
       </c>
       <c r="D116" s="5">
-        <v>46223.437038125005</v>
+        <v>46223.60370479166</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>172</v>
@@ -8810,13 +8810,13 @@
         <v>314</v>
       </c>
       <c r="B117" s="8">
-        <v>46132.465468587965</v>
+        <v>46132.63213525463</v>
       </c>
       <c r="C117" s="8">
-        <v>46205.324280162036</v>
+        <v>46205.49094682871</v>
       </c>
       <c r="D117" s="8">
-        <v>46223.43703435185</v>
+        <v>46223.60370101852</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>172</v>
@@ -8865,13 +8865,13 @@
         <v>316</v>
       </c>
       <c r="B118" s="5">
-        <v>46132.46547675926</v>
+        <v>46132.63214342593</v>
       </c>
       <c r="C118" s="5">
-        <v>46205.32428746528</v>
+        <v>46205.49095413194</v>
       </c>
       <c r="D118" s="5">
-        <v>46223.437030636574</v>
+        <v>46223.603697303246</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>271</v>
@@ -8920,13 +8920,13 @@
         <v>317</v>
       </c>
       <c r="B119" s="8">
-        <v>46132.465484479166</v>
+        <v>46132.63215114584</v>
       </c>
       <c r="C119" s="8">
-        <v>46205.324294652775</v>
+        <v>46205.49096131945</v>
       </c>
       <c r="D119" s="8">
-        <v>46223.437026898144</v>
+        <v>46223.603693564815</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>172</v>
@@ -8975,13 +8975,13 @@
         <v>318</v>
       </c>
       <c r="B120" s="5">
-        <v>46132.46549349537</v>
+        <v>46132.63216016204</v>
       </c>
       <c r="C120" s="5">
-        <v>46205.32430099537</v>
+        <v>46205.49096766204</v>
       </c>
       <c r="D120" s="5">
-        <v>46223.43702278935</v>
+        <v>46223.603689456024</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>172</v>
@@ -9030,13 +9030,13 @@
         <v>319</v>
       </c>
       <c r="B121" s="8">
-        <v>46132.465507974535</v>
+        <v>46132.6321746412</v>
       </c>
       <c r="C121" s="8">
-        <v>46205.324306759256</v>
+        <v>46205.49097342593</v>
       </c>
       <c r="D121" s="8">
-        <v>46223.43701915509</v>
+        <v>46223.603685821756</v>
       </c>
       <c r="E121" s="9" t="s">
         <v>271</v>
@@ -9085,13 +9085,13 @@
         <v>320</v>
       </c>
       <c r="B122" s="5">
-        <v>46132.4655005324</v>
+        <v>46132.63216719907</v>
       </c>
       <c r="C122" s="5">
-        <v>46205.32432434028</v>
+        <v>46205.49099100694</v>
       </c>
       <c r="D122" s="5">
-        <v>46223.43701490741</v>
+        <v>46223.60368157407</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>172</v>
@@ -9140,13 +9140,13 @@
         <v>321</v>
       </c>
       <c r="B123" s="8">
-        <v>46132.46551407407</v>
+        <v>46132.63218074074</v>
       </c>
       <c r="C123" s="8">
-        <v>46205.32433081018</v>
+        <v>46205.49099747685</v>
       </c>
       <c r="D123" s="8">
-        <v>46223.437010925925</v>
+        <v>46223.60367759259</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>172</v>
@@ -9195,13 +9195,13 @@
         <v>322</v>
       </c>
       <c r="B124" s="5">
-        <v>46132.465520196754</v>
+        <v>46132.632186863426</v>
       </c>
       <c r="C124" s="5">
-        <v>46205.32433721065</v>
+        <v>46205.491003877316</v>
       </c>
       <c r="D124" s="5">
-        <v>46223.437007326385</v>
+        <v>46223.60367399306</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>172</v>
@@ -9250,13 +9250,13 @@
         <v>323</v>
       </c>
       <c r="B125" s="8">
-        <v>46132.465527430555</v>
+        <v>46132.63219409723</v>
       </c>
       <c r="C125" s="8">
-        <v>46205.324675717595</v>
+        <v>46205.49134238426</v>
       </c>
       <c r="D125" s="8">
-        <v>46223.43699608796</v>
+        <v>46223.60366275463</v>
       </c>
       <c r="E125" s="9" t="s">
         <v>172</v>
@@ -9305,13 +9305,13 @@
         <v>324</v>
       </c>
       <c r="B126" s="5">
-        <v>46132.46553420139</v>
+        <v>46132.63220086806</v>
       </c>
       <c r="C126" s="5">
-        <v>46223.43690039351</v>
+        <v>46223.603567060185</v>
       </c>
       <c r="D126" s="5">
-        <v>46223.436995474534</v>
+        <v>46223.603662141206</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>172</v>
@@ -9360,13 +9360,13 @@
         <v>325</v>
       </c>
       <c r="B127" s="8">
-        <v>46132.46554068287</v>
+        <v>46132.63220734954</v>
       </c>
       <c r="C127" s="8">
-        <v>46205.324829641206</v>
+        <v>46205.49149630787</v>
       </c>
       <c r="D127" s="8">
-        <v>46223.43699483796</v>
+        <v>46223.60366150463</v>
       </c>
       <c r="E127" s="9" t="s">
         <v>172</v>
@@ -9415,11 +9415,11 @@
         <v>326</v>
       </c>
       <c r="B128" s="5">
-        <v>46132.422271979165</v>
+        <v>46132.58893864583</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46237.369086527775</v>
+        <v>46237.53575319445</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>327</v>
@@ -9476,13 +9476,13 @@
         <v>328</v>
       </c>
       <c r="B129" s="8">
-        <v>46132.46630138889</v>
+        <v>46132.63296805556</v>
       </c>
       <c r="C129" s="8">
-        <v>46213.37978690972</v>
+        <v>46213.54645357639</v>
       </c>
       <c r="D129" s="8">
-        <v>46223.391270057866</v>
+        <v>46223.55793672454</v>
       </c>
       <c r="E129" s="9" t="s">
         <v>172</v>
@@ -9529,13 +9529,13 @@
         <v>331</v>
       </c>
       <c r="B130" s="5">
-        <v>46132.466312881945</v>
+        <v>46132.63297954861</v>
       </c>
       <c r="C130" s="5">
-        <v>46213.37979230324</v>
+        <v>46213.54645896991</v>
       </c>
       <c r="D130" s="5">
-        <v>46223.39126638889</v>
+        <v>46223.557933055556</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>172</v>
@@ -9582,13 +9582,13 @@
         <v>333</v>
       </c>
       <c r="B131" s="8">
-        <v>46132.46632092593</v>
+        <v>46132.63298759259</v>
       </c>
       <c r="C131" s="8">
-        <v>46213.37979680556</v>
+        <v>46213.54646347222</v>
       </c>
       <c r="D131" s="8">
-        <v>46223.391262488425</v>
+        <v>46223.5579291551</v>
       </c>
       <c r="E131" s="9" t="s">
         <v>172</v>
@@ -9635,13 +9635,13 @@
         <v>334</v>
       </c>
       <c r="B132" s="5">
-        <v>46132.466326608795</v>
+        <v>46132.63299327546</v>
       </c>
       <c r="C132" s="5">
-        <v>46213.3798030787</v>
+        <v>46213.54646974537</v>
       </c>
       <c r="D132" s="5">
-        <v>46223.39125880787</v>
+        <v>46223.55792547454</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>172</v>
@@ -9688,13 +9688,13 @@
         <v>336</v>
       </c>
       <c r="B133" s="8">
-        <v>46132.466333275464</v>
+        <v>46132.63299994213</v>
       </c>
       <c r="C133" s="8">
-        <v>46213.379806655095</v>
+        <v>46213.54647332176</v>
       </c>
       <c r="D133" s="8">
-        <v>46223.39125489583</v>
+        <v>46223.557921562504</v>
       </c>
       <c r="E133" s="9" t="s">
         <v>172</v>
@@ -9741,11 +9741,11 @@
         <v>337</v>
       </c>
       <c r="B134" s="5">
-        <v>46132.46634035879</v>
+        <v>46132.63300702546</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46223.39122643518</v>
+        <v>46223.55789310185</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>172</v>
@@ -9792,11 +9792,11 @@
         <v>339</v>
       </c>
       <c r="B135" s="8">
-        <v>46132.46634604166</v>
+        <v>46132.633012708335</v>
       </c>
       <c r="C135" s="9"/>
       <c r="D135" s="8">
-        <v>46223.39122579861</v>
+        <v>46223.55789246528</v>
       </c>
       <c r="E135" s="9" t="s">
         <v>172</v>
@@ -9843,11 +9843,11 @@
         <v>341</v>
       </c>
       <c r="B136" s="5">
-        <v>46132.46635333334</v>
+        <v>46132.63302</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46223.39122520833</v>
+        <v>46223.557891874996</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>172</v>
@@ -9894,11 +9894,11 @@
         <v>342</v>
       </c>
       <c r="B137" s="8">
-        <v>46132.46635981482</v>
+        <v>46132.63302648148</v>
       </c>
       <c r="C137" s="9"/>
       <c r="D137" s="8">
-        <v>46223.39122462963</v>
+        <v>46223.557891296296</v>
       </c>
       <c r="E137" s="9" t="s">
         <v>172</v>
@@ -9945,11 +9945,11 @@
         <v>343</v>
       </c>
       <c r="B138" s="5">
-        <v>46132.46636619213</v>
+        <v>46132.633032858794</v>
       </c>
       <c r="C138" s="6"/>
       <c r="D138" s="5">
-        <v>46223.391224039355</v>
+        <v>46223.55789070602</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>172</v>
@@ -9996,11 +9996,11 @@
         <v>345</v>
       </c>
       <c r="B139" s="8">
-        <v>46132.46637274306</v>
+        <v>46132.633039409724</v>
       </c>
       <c r="C139" s="9"/>
       <c r="D139" s="8">
-        <v>46223.39122344907</v>
+        <v>46223.55789011574</v>
       </c>
       <c r="E139" s="9" t="s">
         <v>172</v>
@@ -10047,11 +10047,11 @@
         <v>346</v>
       </c>
       <c r="B140" s="5">
-        <v>46132.46637915509</v>
+        <v>46132.633045821756</v>
       </c>
       <c r="C140" s="6"/>
       <c r="D140" s="5">
-        <v>46223.39122283565</v>
+        <v>46223.55788950231</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>172</v>
@@ -10098,11 +10098,11 @@
         <v>347</v>
       </c>
       <c r="B141" s="8">
-        <v>46132.46639339121</v>
+        <v>46132.633060057866</v>
       </c>
       <c r="C141" s="9"/>
       <c r="D141" s="8">
-        <v>46223.39122225695</v>
+        <v>46223.557888923606</v>
       </c>
       <c r="E141" s="9" t="s">
         <v>172</v>
@@ -10149,11 +10149,11 @@
         <v>348</v>
       </c>
       <c r="B142" s="5">
-        <v>46132.466386319444</v>
+        <v>46132.633052986115</v>
       </c>
       <c r="C142" s="6"/>
       <c r="D142" s="5">
-        <v>46223.391221655096</v>
+        <v>46223.55788832176</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>172</v>
@@ -10200,11 +10200,11 @@
         <v>349</v>
       </c>
       <c r="B143" s="8">
-        <v>46132.46639913194</v>
+        <v>46132.63306579861</v>
       </c>
       <c r="C143" s="9"/>
       <c r="D143" s="8">
-        <v>46223.436911620374</v>
+        <v>46223.60357828704</v>
       </c>
       <c r="E143" s="9" t="s">
         <v>172</v>
@@ -10251,11 +10251,11 @@
         <v>350</v>
       </c>
       <c r="B144" s="5">
-        <v>46132.46640567129</v>
+        <v>46132.633072337965</v>
       </c>
       <c r="C144" s="6"/>
       <c r="D144" s="5">
-        <v>46223.39122048611</v>
+        <v>46223.55788715278</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>172</v>
@@ -10302,11 +10302,11 @@
         <v>351</v>
       </c>
       <c r="B145" s="8">
-        <v>46132.42227886574</v>
+        <v>46132.58894553241</v>
       </c>
       <c r="C145" s="9"/>
       <c r="D145" s="8">
-        <v>46237.369109629624</v>
+        <v>46237.535776296296</v>
       </c>
       <c r="E145" s="9" t="s">
         <v>352</v>
@@ -10363,13 +10363,13 @@
         <v>353</v>
       </c>
       <c r="B146" s="5">
-        <v>46132.466473622684</v>
+        <v>46132.633140289356</v>
       </c>
       <c r="C146" s="5">
-        <v>46213.379855520834</v>
+        <v>46213.5465221875</v>
       </c>
       <c r="D146" s="5">
-        <v>46223.43753552083</v>
+        <v>46223.604202187504</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>172</v>
@@ -10416,13 +10416,13 @@
         <v>356</v>
       </c>
       <c r="B147" s="8">
-        <v>46132.46648241898</v>
+        <v>46132.63314908565</v>
       </c>
       <c r="C147" s="8">
-        <v>46213.379860243054</v>
+        <v>46213.54652690972</v>
       </c>
       <c r="D147" s="8">
-        <v>46223.43753141204</v>
+        <v>46223.604198078705</v>
       </c>
       <c r="E147" s="9" t="s">
         <v>172</v>
@@ -10469,13 +10469,13 @@
         <v>358</v>
       </c>
       <c r="B148" s="5">
-        <v>46132.466488668986</v>
+        <v>46132.63315533564</v>
       </c>
       <c r="C148" s="5">
-        <v>46213.3798646412</v>
+        <v>46213.546531307875</v>
       </c>
       <c r="D148" s="5">
-        <v>46223.43752765046</v>
+        <v>46223.60419431713</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>172</v>
@@ -10522,13 +10522,13 @@
         <v>359</v>
       </c>
       <c r="B149" s="8">
-        <v>46132.466495995366</v>
+        <v>46132.63316266204</v>
       </c>
       <c r="C149" s="8">
-        <v>46213.379873541664</v>
+        <v>46213.546540208336</v>
       </c>
       <c r="D149" s="8">
-        <v>46223.437524016204</v>
+        <v>46223.60419068287</v>
       </c>
       <c r="E149" s="9" t="s">
         <v>172</v>
@@ -10575,13 +10575,13 @@
         <v>360</v>
       </c>
       <c r="B150" s="5">
-        <v>46132.46650239584</v>
+        <v>46132.6331690625</v>
       </c>
       <c r="C150" s="5">
-        <v>46213.3798775926</v>
+        <v>46213.546544259254</v>
       </c>
       <c r="D150" s="5">
-        <v>46223.43751960648</v>
+        <v>46223.60418627315</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>172</v>
@@ -10628,11 +10628,11 @@
         <v>361</v>
       </c>
       <c r="B151" s="8">
-        <v>46132.46650928241</v>
+        <v>46132.63317594907</v>
       </c>
       <c r="C151" s="9"/>
       <c r="D151" s="8">
-        <v>46223.43749008102</v>
+        <v>46223.604156747686</v>
       </c>
       <c r="E151" s="9" t="s">
         <v>172</v>
@@ -10679,11 +10679,11 @@
         <v>362</v>
       </c>
       <c r="B152" s="5">
-        <v>46132.46652184028</v>
+        <v>46132.633188506945</v>
       </c>
       <c r="C152" s="6"/>
       <c r="D152" s="5">
-        <v>46223.43748945602</v>
+        <v>46223.60415612269</v>
       </c>
       <c r="E152" s="6" t="s">
         <v>172</v>
@@ -10730,11 +10730,11 @@
         <v>363</v>
       </c>
       <c r="B153" s="8">
-        <v>46132.46651493055</v>
+        <v>46132.63318159722</v>
       </c>
       <c r="C153" s="9"/>
       <c r="D153" s="8">
-        <v>46223.437488854164</v>
+        <v>46223.604155520836</v>
       </c>
       <c r="E153" s="9" t="s">
         <v>172</v>
@@ -10781,11 +10781,11 @@
         <v>364</v>
       </c>
       <c r="B154" s="5">
-        <v>46132.4665277662</v>
+        <v>46132.63319443287</v>
       </c>
       <c r="C154" s="6"/>
       <c r="D154" s="5">
-        <v>46223.43748821759</v>
+        <v>46223.60415488426</v>
       </c>
       <c r="E154" s="6" t="s">
         <v>172</v>
@@ -10832,11 +10832,11 @@
         <v>365</v>
       </c>
       <c r="B155" s="8">
-        <v>46132.46654149306</v>
+        <v>46132.63320815972</v>
       </c>
       <c r="C155" s="9"/>
       <c r="D155" s="8">
-        <v>46223.43748756945</v>
+        <v>46223.60415423611</v>
       </c>
       <c r="E155" s="9" t="s">
         <v>172</v>
@@ -10883,11 +10883,11 @@
         <v>366</v>
       </c>
       <c r="B156" s="5">
-        <v>46132.46653415509</v>
+        <v>46132.63320082176</v>
       </c>
       <c r="C156" s="6"/>
       <c r="D156" s="5">
-        <v>46223.437486932875</v>
+        <v>46223.60415359953</v>
       </c>
       <c r="E156" s="6" t="s">
         <v>172</v>
@@ -10934,11 +10934,11 @@
         <v>367</v>
       </c>
       <c r="B157" s="8">
-        <v>46132.46655430556</v>
+        <v>46132.63322097222</v>
       </c>
       <c r="C157" s="9"/>
       <c r="D157" s="8">
-        <v>46223.43748625</v>
+        <v>46223.60415291667</v>
       </c>
       <c r="E157" s="9" t="s">
         <v>172</v>
@@ -10985,11 +10985,11 @@
         <v>368</v>
       </c>
       <c r="B158" s="5">
-        <v>46132.46654837963</v>
+        <v>46132.6332150463</v>
       </c>
       <c r="C158" s="6"/>
       <c r="D158" s="5">
-        <v>46223.43748561342</v>
+        <v>46223.604152280095</v>
       </c>
       <c r="E158" s="6" t="s">
         <v>172</v>
@@ -11036,11 +11036,11 @@
         <v>369</v>
       </c>
       <c r="B159" s="8">
-        <v>46132.466561354166</v>
+        <v>46132.63322802083</v>
       </c>
       <c r="C159" s="9"/>
       <c r="D159" s="8">
-        <v>46223.437485</v>
+        <v>46223.60415166667</v>
       </c>
       <c r="E159" s="9" t="s">
         <v>172</v>
@@ -11087,11 +11087,11 @@
         <v>370</v>
       </c>
       <c r="B160" s="5">
-        <v>46132.46656908565</v>
+        <v>46132.63323575231</v>
       </c>
       <c r="C160" s="6"/>
       <c r="D160" s="5">
-        <v>46223.437484375</v>
+        <v>46223.60415104167</v>
       </c>
       <c r="E160" s="6" t="s">
         <v>172</v>
@@ -11138,11 +11138,11 @@
         <v>371</v>
       </c>
       <c r="B161" s="8">
-        <v>46132.46657733797</v>
+        <v>46132.633244004624</v>
       </c>
       <c r="C161" s="9"/>
       <c r="D161" s="8">
-        <v>46223.43748375</v>
+        <v>46223.604150416664</v>
       </c>
       <c r="E161" s="9" t="s">
         <v>172</v>
@@ -11189,11 +11189,11 @@
         <v>372</v>
       </c>
       <c r="B162" s="5">
-        <v>46132.4222650463</v>
+        <v>46132.58893171296</v>
       </c>
       <c r="C162" s="6"/>
       <c r="D162" s="5">
-        <v>46237.369127881946</v>
+        <v>46237.53579454861</v>
       </c>
       <c r="E162" s="6" t="s">
         <v>373</v>
@@ -11250,13 +11250,13 @@
         <v>374</v>
       </c>
       <c r="B163" s="8">
-        <v>46132.46613763889</v>
+        <v>46132.632804305555</v>
       </c>
       <c r="C163" s="8">
-        <v>46213.379969525464</v>
+        <v>46213.54663619213</v>
       </c>
       <c r="D163" s="8">
-        <v>46223.3916496875</v>
+        <v>46223.55831635417</v>
       </c>
       <c r="E163" s="9" t="s">
         <v>172</v>
@@ -11303,13 +11303,13 @@
         <v>377</v>
       </c>
       <c r="B164" s="5">
-        <v>46132.46614895834</v>
+        <v>46132.632815624995</v>
       </c>
       <c r="C164" s="5">
-        <v>46213.379974282405</v>
+        <v>46213.54664094908</v>
       </c>
       <c r="D164" s="5">
-        <v>46223.39164598379</v>
+        <v>46223.558312650464</v>
       </c>
       <c r="E164" s="6" t="s">
         <v>172</v>
@@ -11356,13 +11356,13 @@
         <v>378</v>
       </c>
       <c r="B165" s="8">
-        <v>46132.466156180555</v>
+        <v>46132.63282284723</v>
       </c>
       <c r="C165" s="8">
-        <v>46213.379986053245</v>
+        <v>46213.5466527199</v>
       </c>
       <c r="D165" s="8">
-        <v>46223.39164233796</v>
+        <v>46223.55830900463</v>
       </c>
       <c r="E165" s="9" t="s">
         <v>172</v>
@@ -11409,13 +11409,13 @@
         <v>380</v>
       </c>
       <c r="B166" s="5">
-        <v>46132.466165694444</v>
+        <v>46132.63283236111</v>
       </c>
       <c r="C166" s="5">
-        <v>46213.37999446759</v>
+        <v>46213.546661134256</v>
       </c>
       <c r="D166" s="5">
-        <v>46223.391638807865</v>
+        <v>46223.55830547454</v>
       </c>
       <c r="E166" s="6" t="s">
         <v>172</v>
@@ -11462,13 +11462,13 @@
         <v>381</v>
       </c>
       <c r="B167" s="8">
-        <v>46132.46617071759</v>
+        <v>46132.632837384255</v>
       </c>
       <c r="C167" s="8">
-        <v>46213.37999991898</v>
+        <v>46213.54666658565</v>
       </c>
       <c r="D167" s="8">
-        <v>46223.39163475695</v>
+        <v>46223.55830142361</v>
       </c>
       <c r="E167" s="9" t="s">
         <v>172</v>
@@ -11515,11 +11515,11 @@
         <v>383</v>
       </c>
       <c r="B168" s="5">
-        <v>46132.46617695602</v>
+        <v>46132.63284362269</v>
       </c>
       <c r="C168" s="6"/>
       <c r="D168" s="5">
-        <v>46223.39058969908</v>
+        <v>46223.55725636574</v>
       </c>
       <c r="E168" s="6" t="s">
         <v>172</v>
@@ -11566,11 +11566,11 @@
         <v>384</v>
       </c>
       <c r="B169" s="8">
-        <v>46132.46618309028</v>
+        <v>46132.63284975695</v>
       </c>
       <c r="C169" s="9"/>
       <c r="D169" s="8">
-        <v>46223.391605717596</v>
+        <v>46223.55827238426</v>
       </c>
       <c r="E169" s="9" t="s">
         <v>172</v>
@@ -11617,11 +11617,11 @@
         <v>385</v>
       </c>
       <c r="B170" s="5">
-        <v>46132.46619560185</v>
+        <v>46132.63286226852</v>
       </c>
       <c r="C170" s="6"/>
       <c r="D170" s="5">
-        <v>46223.39160512731</v>
+        <v>46223.55827179398</v>
       </c>
       <c r="E170" s="6" t="s">
         <v>172</v>
@@ -11668,11 +11668,11 @@
         <v>386</v>
       </c>
       <c r="B171" s="8">
-        <v>46132.46619009259</v>
+        <v>46132.63285675926</v>
       </c>
       <c r="C171" s="9"/>
       <c r="D171" s="8">
-        <v>46223.39160452546</v>
+        <v>46223.55827119213</v>
       </c>
       <c r="E171" s="9" t="s">
         <v>172</v>
@@ -11719,11 +11719,11 @@
         <v>387</v>
       </c>
       <c r="B172" s="5">
-        <v>46132.466201620366</v>
+        <v>46132.63286828704</v>
       </c>
       <c r="C172" s="6"/>
       <c r="D172" s="5">
-        <v>46223.39160390046</v>
+        <v>46223.558270567126</v>
       </c>
       <c r="E172" s="6" t="s">
         <v>172</v>
@@ -11770,11 +11770,11 @@
         <v>388</v>
       </c>
       <c r="B173" s="8">
-        <v>46132.466207453705</v>
+        <v>46132.63287412037</v>
       </c>
       <c r="C173" s="9"/>
       <c r="D173" s="8">
-        <v>46223.391603275464</v>
+        <v>46223.55826994213</v>
       </c>
       <c r="E173" s="9" t="s">
         <v>172</v>
@@ -11821,11 +11821,11 @@
         <v>389</v>
       </c>
       <c r="B174" s="5">
-        <v>46132.46621466435</v>
+        <v>46132.63288133102</v>
       </c>
       <c r="C174" s="6"/>
       <c r="D174" s="5">
-        <v>46223.39160268518</v>
+        <v>46223.55826935185</v>
       </c>
       <c r="E174" s="6" t="s">
         <v>172</v>
@@ -11872,11 +11872,11 @@
         <v>390</v>
       </c>
       <c r="B175" s="8">
-        <v>46132.46622134259</v>
+        <v>46132.63288800926</v>
       </c>
       <c r="C175" s="9"/>
       <c r="D175" s="8">
-        <v>46223.39160209491</v>
+        <v>46223.558268761575</v>
       </c>
       <c r="E175" s="9" t="s">
         <v>172</v>
@@ -11923,11 +11923,11 @@
         <v>391</v>
       </c>
       <c r="B176" s="5">
-        <v>46132.4662275463</v>
+        <v>46132.63289421296</v>
       </c>
       <c r="C176" s="6"/>
       <c r="D176" s="5">
-        <v>46223.39160148148</v>
+        <v>46223.55826814815</v>
       </c>
       <c r="E176" s="6" t="s">
         <v>172</v>
@@ -11974,11 +11974,11 @@
         <v>392</v>
       </c>
       <c r="B177" s="8">
-        <v>46132.46623362269</v>
+        <v>46132.63290028935</v>
       </c>
       <c r="C177" s="9"/>
       <c r="D177" s="8">
-        <v>46223.43691380787</v>
+        <v>46223.60358047453</v>
       </c>
       <c r="E177" s="9" t="s">
         <v>172</v>
@@ -12025,11 +12025,11 @@
         <v>393</v>
       </c>
       <c r="B178" s="5">
-        <v>46132.46624105324</v>
+        <v>46132.632907719904</v>
       </c>
       <c r="C178" s="6"/>
       <c r="D178" s="5">
-        <v>46223.39160023148</v>
+        <v>46223.55826689815</v>
       </c>
       <c r="E178" s="6" t="s">
         <v>172</v>
@@ -12076,11 +12076,11 @@
         <v>394</v>
       </c>
       <c r="B179" s="8">
-        <v>46132.42228591435</v>
+        <v>46132.58895258102</v>
       </c>
       <c r="C179" s="9"/>
       <c r="D179" s="8">
-        <v>46237.369148206024</v>
+        <v>46237.53581487268</v>
       </c>
       <c r="E179" s="9" t="s">
         <v>395</v>
@@ -12137,11 +12137,11 @@
         <v>396</v>
       </c>
       <c r="B180" s="5">
-        <v>46132.46663340278</v>
+        <v>46132.63330006944</v>
       </c>
       <c r="C180" s="6"/>
       <c r="D180" s="5">
-        <v>46223.437910057866</v>
+        <v>46223.60457672454</v>
       </c>
       <c r="E180" s="6" t="s">
         <v>172</v>
@@ -12188,11 +12188,11 @@
         <v>399</v>
       </c>
       <c r="B181" s="8">
-        <v>46132.46664318287</v>
+        <v>46132.63330984954</v>
       </c>
       <c r="C181" s="9"/>
       <c r="D181" s="8">
-        <v>46223.43790936343</v>
+        <v>46223.60457603009</v>
       </c>
       <c r="E181" s="9" t="s">
         <v>172</v>
@@ -12239,11 +12239,11 @@
         <v>401</v>
       </c>
       <c r="B182" s="5">
-        <v>46132.46664971065</v>
+        <v>46132.633316377316</v>
       </c>
       <c r="C182" s="6"/>
       <c r="D182" s="5">
-        <v>46223.43790871528</v>
+        <v>46223.60457538195</v>
       </c>
       <c r="E182" s="6" t="s">
         <v>172</v>
@@ -12290,11 +12290,11 @@
         <v>403</v>
       </c>
       <c r="B183" s="8">
-        <v>46132.46665666667</v>
+        <v>46132.63332333333</v>
       </c>
       <c r="C183" s="9"/>
       <c r="D183" s="8">
-        <v>46223.43790813658</v>
+        <v>46223.60457480324</v>
       </c>
       <c r="E183" s="9" t="s">
         <v>172</v>
@@ -12341,11 +12341,11 @@
         <v>405</v>
       </c>
       <c r="B184" s="5">
-        <v>46132.466669016205</v>
+        <v>46132.63333568287</v>
       </c>
       <c r="C184" s="6"/>
       <c r="D184" s="5">
-        <v>46223.43790751157</v>
+        <v>46223.604574178244</v>
       </c>
       <c r="E184" s="6" t="s">
         <v>172</v>
@@ -12392,11 +12392,11 @@
         <v>407</v>
       </c>
       <c r="B185" s="8">
-        <v>46132.46666261574</v>
+        <v>46132.633329282406</v>
       </c>
       <c r="C185" s="9"/>
       <c r="D185" s="8">
-        <v>46223.43790690972</v>
+        <v>46223.60457357639</v>
       </c>
       <c r="E185" s="9" t="s">
         <v>172</v>
@@ -12443,11 +12443,11 @@
         <v>409</v>
       </c>
       <c r="B186" s="5">
-        <v>46132.466682592596</v>
+        <v>46132.63334925926</v>
       </c>
       <c r="C186" s="6"/>
       <c r="D186" s="5">
-        <v>46223.43790630787</v>
+        <v>46223.60457297454</v>
       </c>
       <c r="E186" s="6" t="s">
         <v>172</v>
@@ -12494,11 +12494,11 @@
         <v>411</v>
       </c>
       <c r="B187" s="8">
-        <v>46132.4666866551</v>
+        <v>46132.633353321755</v>
       </c>
       <c r="C187" s="9"/>
       <c r="D187" s="8">
-        <v>46223.437905706014</v>
+        <v>46223.604572372686</v>
       </c>
       <c r="E187" s="9" t="s">
         <v>172</v>
@@ -12545,11 +12545,11 @@
         <v>413</v>
       </c>
       <c r="B188" s="5">
-        <v>46132.46669449074</v>
+        <v>46132.63336115741</v>
       </c>
       <c r="C188" s="6"/>
       <c r="D188" s="5">
-        <v>46223.43790506944</v>
+        <v>46223.60457173611</v>
       </c>
       <c r="E188" s="6" t="s">
         <v>172</v>
@@ -12596,11 +12596,11 @@
         <v>415</v>
       </c>
       <c r="B189" s="8">
-        <v>46132.466699490746</v>
+        <v>46132.6333661574</v>
       </c>
       <c r="C189" s="9"/>
       <c r="D189" s="8">
-        <v>46223.43790444444</v>
+        <v>46223.60457111111</v>
       </c>
       <c r="E189" s="9" t="s">
         <v>172</v>
@@ -12647,11 +12647,11 @@
         <v>417</v>
       </c>
       <c r="B190" s="5">
-        <v>46132.46670837963</v>
+        <v>46132.633375046295</v>
       </c>
       <c r="C190" s="6"/>
       <c r="D190" s="5">
-        <v>46223.43790377315</v>
+        <v>46223.60457043981</v>
       </c>
       <c r="E190" s="6" t="s">
         <v>172</v>
@@ -12698,11 +12698,11 @@
         <v>419</v>
       </c>
       <c r="B191" s="8">
-        <v>46132.46671283565</v>
+        <v>46132.63337950232</v>
       </c>
       <c r="C191" s="9"/>
       <c r="D191" s="8">
-        <v>46223.43790315972</v>
+        <v>46223.60456982639</v>
       </c>
       <c r="E191" s="9" t="s">
         <v>172</v>
@@ -12749,11 +12749,11 @@
         <v>421</v>
       </c>
       <c r="B192" s="5">
-        <v>46132.46672</v>
+        <v>46132.63338666667</v>
       </c>
       <c r="C192" s="6"/>
       <c r="D192" s="5">
-        <v>46223.4379025463</v>
+        <v>46223.60456921296</v>
       </c>
       <c r="E192" s="6" t="s">
         <v>172</v>
@@ -12800,11 +12800,11 @@
         <v>423</v>
       </c>
       <c r="B193" s="8">
-        <v>46132.46672708333</v>
+        <v>46132.63339375</v>
       </c>
       <c r="C193" s="9"/>
       <c r="D193" s="8">
-        <v>46223.4379019676</v>
+        <v>46223.604568634255</v>
       </c>
       <c r="E193" s="9" t="s">
         <v>172</v>
@@ -12851,11 +12851,11 @@
         <v>425</v>
       </c>
       <c r="B194" s="5">
-        <v>46132.46673206019</v>
+        <v>46132.63339872685</v>
       </c>
       <c r="C194" s="6"/>
       <c r="D194" s="5">
-        <v>46223.437901365745</v>
+        <v>46223.6045680324</v>
       </c>
       <c r="E194" s="6" t="s">
         <v>172</v>
@@ -12902,11 +12902,11 @@
         <v>427</v>
       </c>
       <c r="B195" s="8">
-        <v>46132.46673741898</v>
+        <v>46132.633404085645</v>
       </c>
       <c r="C195" s="9"/>
       <c r="D195" s="8">
-        <v>46223.43790071759</v>
+        <v>46223.60456738426</v>
       </c>
       <c r="E195" s="9" t="s">
         <v>172</v>
@@ -12953,11 +12953,11 @@
         <v>429</v>
       </c>
       <c r="B196" s="5">
-        <v>46132.422338993056</v>
+        <v>46132.58900565973</v>
       </c>
       <c r="C196" s="6"/>
       <c r="D196" s="5">
-        <v>46229.697857060186</v>
+        <v>46229.86452372685</v>
       </c>
       <c r="E196" s="6" t="s">
         <v>430</v>
@@ -13014,11 +13014,11 @@
         <v>433</v>
       </c>
       <c r="B197" s="8">
-        <v>46132.466786770834</v>
+        <v>46132.6334534375</v>
       </c>
       <c r="C197" s="9"/>
       <c r="D197" s="8">
-        <v>46225.083592696756</v>
+        <v>46225.25025936343</v>
       </c>
       <c r="E197" s="9" t="s">
         <v>172</v>
@@ -13065,11 +13065,11 @@
         <v>435</v>
       </c>
       <c r="B198" s="5">
-        <v>46132.46679535879</v>
+        <v>46132.633462025464</v>
       </c>
       <c r="C198" s="6"/>
       <c r="D198" s="5">
-        <v>46225.08359429398</v>
+        <v>46225.250260960645</v>
       </c>
       <c r="E198" s="6" t="s">
         <v>172</v>
@@ -13116,11 +13116,11 @@
         <v>436</v>
       </c>
       <c r="B199" s="8">
-        <v>46132.46680195602</v>
+        <v>46132.633468622684</v>
       </c>
       <c r="C199" s="9"/>
       <c r="D199" s="8">
-        <v>46225.08359552083</v>
+        <v>46225.2502621875</v>
       </c>
       <c r="E199" s="9" t="s">
         <v>172</v>
@@ -13167,11 +13167,11 @@
         <v>437</v>
       </c>
       <c r="B200" s="5">
-        <v>46132.46680835648</v>
+        <v>46132.63347502315</v>
       </c>
       <c r="C200" s="6"/>
       <c r="D200" s="5">
-        <v>46225.08359677083</v>
+        <v>46225.2502634375</v>
       </c>
       <c r="E200" s="6" t="s">
         <v>172</v>
@@ -13218,11 +13218,11 @@
         <v>438</v>
       </c>
       <c r="B201" s="8">
-        <v>46132.46681403935</v>
+        <v>46132.63348070602</v>
       </c>
       <c r="C201" s="9"/>
       <c r="D201" s="8">
-        <v>46225.083597916666</v>
+        <v>46225.25026458333</v>
       </c>
       <c r="E201" s="9" t="s">
         <v>172</v>
@@ -13269,11 +13269,11 @@
         <v>439</v>
       </c>
       <c r="B202" s="5">
-        <v>46132.466819953705</v>
+        <v>46132.63348662037</v>
       </c>
       <c r="C202" s="6"/>
       <c r="D202" s="5">
-        <v>46225.08359913195</v>
+        <v>46225.25026579861</v>
       </c>
       <c r="E202" s="6" t="s">
         <v>172</v>
@@ -13320,11 +13320,11 @@
         <v>440</v>
       </c>
       <c r="B203" s="8">
-        <v>46132.466826284726</v>
+        <v>46132.63349295139</v>
       </c>
       <c r="C203" s="9"/>
       <c r="D203" s="8">
-        <v>46225.08360041666</v>
+        <v>46225.250267083335</v>
       </c>
       <c r="E203" s="9" t="s">
         <v>172</v>
@@ -13371,11 +13371,11 @@
         <v>442</v>
       </c>
       <c r="B204" s="5">
-        <v>46132.46683347222</v>
+        <v>46132.633500138894</v>
       </c>
       <c r="C204" s="6"/>
       <c r="D204" s="5">
-        <v>46225.083601562495</v>
+        <v>46225.25026822917</v>
       </c>
       <c r="E204" s="6" t="s">
         <v>172</v>
@@ -13422,11 +13422,11 @@
         <v>443</v>
       </c>
       <c r="B205" s="8">
-        <v>46132.46683931713</v>
+        <v>46132.633505983795</v>
       </c>
       <c r="C205" s="9"/>
       <c r="D205" s="8">
-        <v>46225.083602812505</v>
+        <v>46225.25026947916</v>
       </c>
       <c r="E205" s="9" t="s">
         <v>172</v>
@@ -13473,11 +13473,11 @@
         <v>444</v>
       </c>
       <c r="B206" s="5">
-        <v>46132.466845787036</v>
+        <v>46132.6335124537</v>
       </c>
       <c r="C206" s="6"/>
       <c r="D206" s="5">
-        <v>46225.08360405093</v>
+        <v>46225.25027071759</v>
       </c>
       <c r="E206" s="6" t="s">
         <v>172</v>
@@ -13524,11 +13524,11 @@
         <v>445</v>
       </c>
       <c r="B207" s="8">
-        <v>46132.4668530787</v>
+        <v>46132.63351974537</v>
       </c>
       <c r="C207" s="9"/>
       <c r="D207" s="8">
-        <v>46225.08360537037</v>
+        <v>46225.25027203704</v>
       </c>
       <c r="E207" s="9" t="s">
         <v>172</v>
@@ -13575,11 +13575,11 @@
         <v>446</v>
       </c>
       <c r="B208" s="5">
-        <v>46132.466861099536</v>
+        <v>46132.6335277662</v>
       </c>
       <c r="C208" s="6"/>
       <c r="D208" s="5">
-        <v>46225.08360677083</v>
+        <v>46225.2502734375</v>
       </c>
       <c r="E208" s="6" t="s">
         <v>172</v>
@@ -13626,11 +13626,11 @@
         <v>447</v>
       </c>
       <c r="B209" s="8">
-        <v>46132.46686832176</v>
+        <v>46132.633534988425</v>
       </c>
       <c r="C209" s="9"/>
       <c r="D209" s="8">
-        <v>46225.083607939814</v>
+        <v>46225.250274606486</v>
       </c>
       <c r="E209" s="9" t="s">
         <v>172</v>
@@ -13677,11 +13677,11 @@
         <v>448</v>
       </c>
       <c r="B210" s="5">
-        <v>46132.46687415509</v>
+        <v>46132.63354082176</v>
       </c>
       <c r="C210" s="6"/>
       <c r="D210" s="5">
-        <v>46225.08360921296</v>
+        <v>46225.25027587963</v>
       </c>
       <c r="E210" s="6" t="s">
         <v>172</v>
@@ -13728,11 +13728,11 @@
         <v>449</v>
       </c>
       <c r="B211" s="8">
-        <v>46132.4668809375</v>
+        <v>46132.63354760417</v>
       </c>
       <c r="C211" s="9"/>
       <c r="D211" s="8">
-        <v>46225.08361078704</v>
+        <v>46225.2502774537</v>
       </c>
       <c r="E211" s="9" t="s">
         <v>450</v>
@@ -13779,11 +13779,11 @@
         <v>451</v>
       </c>
       <c r="B212" s="5">
-        <v>46133.41633472222</v>
+        <v>46133.58300138889</v>
       </c>
       <c r="C212" s="6"/>
       <c r="D212" s="5">
-        <v>46225.083616331016</v>
+        <v>46225.25028299769</v>
       </c>
       <c r="E212" s="6" t="s">
         <v>271</v>
@@ -13830,11 +13830,11 @@
         <v>452</v>
       </c>
       <c r="B213" s="8">
-        <v>46132.42234625</v>
+        <v>46132.589012916666</v>
       </c>
       <c r="C213" s="9"/>
       <c r="D213" s="8">
-        <v>46133.42102390046</v>
+        <v>46133.58769056713</v>
       </c>
       <c r="E213" s="9" t="s">
         <v>453</v>
@@ -13877,11 +13877,11 @@
         <v>455</v>
       </c>
       <c r="B214" s="5">
-        <v>46132.42235</v>
+        <v>46132.589016666665</v>
       </c>
       <c r="C214" s="6"/>
       <c r="D214" s="5">
-        <v>46229.383119895836</v>
+        <v>46229.5497865625</v>
       </c>
       <c r="E214" s="6" t="s">
         <v>456</v>
@@ -13938,11 +13938,11 @@
         <v>460</v>
       </c>
       <c r="B215" s="8">
-        <v>46132.46694003472</v>
+        <v>46132.63360670139</v>
       </c>
       <c r="C215" s="9"/>
       <c r="D215" s="8">
-        <v>46226.00101496528</v>
+        <v>46226.167681631945</v>
       </c>
       <c r="E215" s="9" t="s">
         <v>172</v>
@@ -13989,11 +13989,11 @@
         <v>461</v>
       </c>
       <c r="B216" s="5">
-        <v>46132.46694637732</v>
+        <v>46132.63361304398</v>
       </c>
       <c r="C216" s="6"/>
       <c r="D216" s="5">
-        <v>46226.001016875</v>
+        <v>46226.167683541666</v>
       </c>
       <c r="E216" s="6" t="s">
         <v>172</v>
@@ -14040,11 +14040,11 @@
         <v>462</v>
       </c>
       <c r="B217" s="8">
-        <v>46132.46695307871</v>
+        <v>46132.63361974537</v>
       </c>
       <c r="C217" s="9"/>
       <c r="D217" s="8">
-        <v>46226.00101824074</v>
+        <v>46226.16768490741</v>
       </c>
       <c r="E217" s="9" t="s">
         <v>172</v>
@@ -14091,11 +14091,11 @@
         <v>463</v>
       </c>
       <c r="B218" s="5">
-        <v>46132.46696471065</v>
+        <v>46132.63363137731</v>
       </c>
       <c r="C218" s="6"/>
       <c r="D218" s="5">
-        <v>46226.00102082176</v>
+        <v>46226.16768748843</v>
       </c>
       <c r="E218" s="6" t="s">
         <v>172</v>
@@ -14142,11 +14142,11 @@
         <v>464</v>
       </c>
       <c r="B219" s="8">
-        <v>46132.466958888894</v>
+        <v>46132.63362555555</v>
       </c>
       <c r="C219" s="9"/>
       <c r="D219" s="8">
-        <v>46226.00101960648</v>
+        <v>46226.16768627315</v>
       </c>
       <c r="E219" s="9" t="s">
         <v>172</v>
@@ -14193,11 +14193,11 @@
         <v>465</v>
       </c>
       <c r="B220" s="5">
-        <v>46132.46697193287</v>
+        <v>46132.63363859954</v>
       </c>
       <c r="C220" s="6"/>
       <c r="D220" s="5">
-        <v>46226.001022048615</v>
+        <v>46226.16768871528</v>
       </c>
       <c r="E220" s="6" t="s">
         <v>172</v>
@@ -14244,11 +14244,11 @@
         <v>466</v>
       </c>
       <c r="B221" s="8">
-        <v>46132.46698001157</v>
+        <v>46132.63364667824</v>
       </c>
       <c r="C221" s="9"/>
       <c r="D221" s="8">
-        <v>46226.00102332176</v>
+        <v>46226.167689988426</v>
       </c>
       <c r="E221" s="9" t="s">
         <v>450</v>
@@ -14295,11 +14295,11 @@
         <v>467</v>
       </c>
       <c r="B222" s="5">
-        <v>46132.466986388885</v>
+        <v>46132.633653055556</v>
       </c>
       <c r="C222" s="6"/>
       <c r="D222" s="5">
-        <v>46226.00102476851</v>
+        <v>46226.167691435185</v>
       </c>
       <c r="E222" s="6" t="s">
         <v>172</v>
@@ -14346,11 +14346,11 @@
         <v>468</v>
       </c>
       <c r="B223" s="8">
-        <v>46132.466992546295</v>
+        <v>46132.63365921297</v>
       </c>
       <c r="C223" s="9"/>
       <c r="D223" s="8">
-        <v>46226.00102635416</v>
+        <v>46226.167693020834</v>
       </c>
       <c r="E223" s="9" t="s">
         <v>172</v>
@@ -14397,11 +14397,11 @@
         <v>469</v>
       </c>
       <c r="B224" s="5">
-        <v>46132.46699868055</v>
+        <v>46132.633665347224</v>
       </c>
       <c r="C224" s="6"/>
       <c r="D224" s="5">
-        <v>46226.00102763889</v>
+        <v>46226.16769430556</v>
       </c>
       <c r="E224" s="6" t="s">
         <v>172</v>
@@ -14448,11 +14448,11 @@
         <v>470</v>
       </c>
       <c r="B225" s="8">
-        <v>46132.46700740741</v>
+        <v>46132.63367407407</v>
       </c>
       <c r="C225" s="9"/>
       <c r="D225" s="8">
-        <v>46226.0010291088</v>
+        <v>46226.16769577547</v>
       </c>
       <c r="E225" s="9" t="s">
         <v>172</v>
@@ -14499,11 +14499,11 @@
         <v>471</v>
       </c>
       <c r="B226" s="5">
-        <v>46132.46701559028</v>
+        <v>46132.63368225694</v>
       </c>
       <c r="C226" s="6"/>
       <c r="D226" s="5">
-        <v>46226.00103035879</v>
+        <v>46226.16769702546</v>
       </c>
       <c r="E226" s="6" t="s">
         <v>172</v>
@@ -14550,11 +14550,11 @@
         <v>472</v>
       </c>
       <c r="B227" s="8">
-        <v>46132.4670221875</v>
+        <v>46132.63368885417</v>
       </c>
       <c r="C227" s="9"/>
       <c r="D227" s="8">
-        <v>46226.00103158565</v>
+        <v>46226.16769825231</v>
       </c>
       <c r="E227" s="9" t="s">
         <v>172</v>
@@ -14601,11 +14601,11 @@
         <v>473</v>
       </c>
       <c r="B228" s="5">
-        <v>46132.46702829861</v>
+        <v>46132.633694965276</v>
       </c>
       <c r="C228" s="6"/>
       <c r="D228" s="5">
-        <v>46226.00103313658</v>
+        <v>46226.16769980324</v>
       </c>
       <c r="E228" s="6" t="s">
         <v>172</v>
@@ -14652,11 +14652,11 @@
         <v>474</v>
       </c>
       <c r="B229" s="8">
-        <v>46132.467034444446</v>
+        <v>46132.63370111111</v>
       </c>
       <c r="C229" s="9"/>
       <c r="D229" s="8">
-        <v>46226.00103460648</v>
+        <v>46226.16770127315</v>
       </c>
       <c r="E229" s="9" t="s">
         <v>450</v>
@@ -14703,11 +14703,11 @@
         <v>475</v>
       </c>
       <c r="B230" s="5">
-        <v>46132.46712287037</v>
+        <v>46132.63378953704</v>
       </c>
       <c r="C230" s="6"/>
       <c r="D230" s="5">
-        <v>46226.00103596065</v>
+        <v>46226.16770262731</v>
       </c>
       <c r="E230" s="6" t="s">
         <v>172</v>
@@ -14754,11 +14754,11 @@
         <v>476</v>
       </c>
       <c r="B231" s="8">
-        <v>46132.422355069444</v>
+        <v>46132.589021736116</v>
       </c>
       <c r="C231" s="9"/>
       <c r="D231" s="8">
-        <v>46237.3692025</v>
+        <v>46237.53586916666</v>
       </c>
       <c r="E231" s="9" t="s">
         <v>477</v>
@@ -14815,11 +14815,11 @@
         <v>479</v>
       </c>
       <c r="B232" s="5">
-        <v>46132.46719494213</v>
+        <v>46132.633861608796</v>
       </c>
       <c r="C232" s="6"/>
       <c r="D232" s="5">
-        <v>46227.0014799537</v>
+        <v>46227.16814662037</v>
       </c>
       <c r="E232" s="6" t="s">
         <v>172</v>
@@ -14866,11 +14866,11 @@
         <v>480</v>
       </c>
       <c r="B233" s="8">
-        <v>46132.4672033449</v>
+        <v>46132.633870011574</v>
       </c>
       <c r="C233" s="9"/>
       <c r="D233" s="8">
-        <v>46227.00148200231</v>
+        <v>46227.16814866898</v>
       </c>
       <c r="E233" s="9" t="s">
         <v>172</v>
@@ -14917,11 +14917,11 @@
         <v>481</v>
       </c>
       <c r="B234" s="5">
-        <v>46132.46720991898</v>
+        <v>46132.63387658565</v>
       </c>
       <c r="C234" s="6"/>
       <c r="D234" s="5">
-        <v>46227.001483368054</v>
+        <v>46227.16815003472</v>
       </c>
       <c r="E234" s="6" t="s">
         <v>172</v>
@@ -14968,11 +14968,11 @@
         <v>482</v>
       </c>
       <c r="B235" s="8">
-        <v>46132.46721592592</v>
+        <v>46132.63388259259</v>
       </c>
       <c r="C235" s="9"/>
       <c r="D235" s="8">
-        <v>46227.00148460648</v>
+        <v>46227.168151273145</v>
       </c>
       <c r="E235" s="9" t="s">
         <v>172</v>
@@ -15019,11 +15019,11 @@
         <v>483</v>
       </c>
       <c r="B236" s="5">
-        <v>46132.46721966435</v>
+        <v>46132.63388633102</v>
       </c>
       <c r="C236" s="6"/>
       <c r="D236" s="5">
-        <v>46227.0014858912</v>
+        <v>46227.168152557875</v>
       </c>
       <c r="E236" s="6" t="s">
         <v>172</v>
@@ -15070,11 +15070,11 @@
         <v>484</v>
       </c>
       <c r="B237" s="8">
-        <v>46132.46722439815</v>
+        <v>46132.63389106482</v>
       </c>
       <c r="C237" s="9"/>
       <c r="D237" s="8">
-        <v>46227.00148726851</v>
+        <v>46227.168153935185</v>
       </c>
       <c r="E237" s="9" t="s">
         <v>172</v>
@@ -15121,11 +15121,11 @@
         <v>485</v>
       </c>
       <c r="B238" s="5">
-        <v>46132.46723072916</v>
+        <v>46132.63389739583</v>
       </c>
       <c r="C238" s="6"/>
       <c r="D238" s="5">
-        <v>46227.00148861111</v>
+        <v>46227.16815527777</v>
       </c>
       <c r="E238" s="6" t="s">
         <v>172</v>
@@ -15172,11 +15172,11 @@
         <v>486</v>
       </c>
       <c r="B239" s="8">
-        <v>46132.46723621528</v>
+        <v>46132.63390288195</v>
       </c>
       <c r="C239" s="9"/>
       <c r="D239" s="8">
-        <v>46227.00148997685</v>
+        <v>46227.168156643515</v>
       </c>
       <c r="E239" s="9" t="s">
         <v>172</v>
@@ -15223,11 +15223,11 @@
         <v>487</v>
       </c>
       <c r="B240" s="5">
-        <v>46132.46724194444</v>
+        <v>46132.63390861111</v>
       </c>
       <c r="C240" s="6"/>
       <c r="D240" s="5">
-        <v>46227.001491331015</v>
+        <v>46227.16815799769</v>
       </c>
       <c r="E240" s="6" t="s">
         <v>172</v>
@@ -15274,11 +15274,11 @@
         <v>488</v>
       </c>
       <c r="B241" s="8">
-        <v>46132.467246099535</v>
+        <v>46132.63391276621</v>
       </c>
       <c r="C241" s="9"/>
       <c r="D241" s="8">
-        <v>46227.00149274306</v>
+        <v>46227.16815940972</v>
       </c>
       <c r="E241" s="9" t="s">
         <v>172</v>
@@ -15325,11 +15325,11 @@
         <v>489</v>
       </c>
       <c r="B242" s="5">
-        <v>46132.4672521412</v>
+        <v>46132.63391880787</v>
       </c>
       <c r="C242" s="6"/>
       <c r="D242" s="5">
-        <v>46227.0014940625</v>
+        <v>46227.16816072917</v>
       </c>
       <c r="E242" s="6" t="s">
         <v>172</v>
@@ -15376,11 +15376,11 @@
         <v>490</v>
       </c>
       <c r="B243" s="8">
-        <v>46132.46725635417</v>
+        <v>46132.63392302083</v>
       </c>
       <c r="C243" s="9"/>
       <c r="D243" s="8">
-        <v>46227.00149539352</v>
+        <v>46227.16816206019</v>
       </c>
       <c r="E243" s="9" t="s">
         <v>172</v>
@@ -15427,11 +15427,11 @@
         <v>491</v>
       </c>
       <c r="B244" s="5">
-        <v>46132.467263750004</v>
+        <v>46132.63393041666</v>
       </c>
       <c r="C244" s="6"/>
       <c r="D244" s="5">
-        <v>46227.001496701385</v>
+        <v>46227.16816336806</v>
       </c>
       <c r="E244" s="6" t="s">
         <v>172</v>
@@ -15478,11 +15478,11 @@
         <v>492</v>
       </c>
       <c r="B245" s="8">
-        <v>46132.467270231486</v>
+        <v>46132.63393689815</v>
       </c>
       <c r="C245" s="9"/>
       <c r="D245" s="8">
-        <v>46227.00149805556</v>
+        <v>46227.16816472222</v>
       </c>
       <c r="E245" s="9" t="s">
         <v>172</v>
@@ -15529,11 +15529,11 @@
         <v>493</v>
       </c>
       <c r="B246" s="5">
-        <v>46132.46727641203</v>
+        <v>46132.633943078705</v>
       </c>
       <c r="C246" s="6"/>
       <c r="D246" s="5">
-        <v>46227.00149931713</v>
+        <v>46227.16816598379</v>
       </c>
       <c r="E246" s="6" t="s">
         <v>450</v>
@@ -15580,11 +15580,11 @@
         <v>494</v>
       </c>
       <c r="B247" s="8">
-        <v>46132.46728891204</v>
+        <v>46132.633955578705</v>
       </c>
       <c r="C247" s="9"/>
       <c r="D247" s="8">
-        <v>46227.00150091435</v>
+        <v>46227.16816758102</v>
       </c>
       <c r="E247" s="9" t="s">
         <v>172</v>
@@ -15631,11 +15631,11 @@
         <v>495</v>
       </c>
       <c r="B248" s="5">
-        <v>46132.422360150464</v>
+        <v>46132.58902681713</v>
       </c>
       <c r="C248" s="6"/>
       <c r="D248" s="5">
-        <v>46231.0169840625</v>
+        <v>46231.18365072917</v>
       </c>
       <c r="E248" s="6" t="s">
         <v>496</v>
@@ -15694,11 +15694,11 @@
         <v>500</v>
       </c>
       <c r="B249" s="8">
-        <v>46132.4673577662</v>
+        <v>46132.634024432875</v>
       </c>
       <c r="C249" s="9"/>
       <c r="D249" s="8">
-        <v>46230.00141162037</v>
+        <v>46230.16807828704</v>
       </c>
       <c r="E249" s="9" t="s">
         <v>172</v>
@@ -15745,11 +15745,11 @@
         <v>501</v>
       </c>
       <c r="B250" s="5">
-        <v>46132.46736601852</v>
+        <v>46132.634032685186</v>
       </c>
       <c r="C250" s="6"/>
       <c r="D250" s="5">
-        <v>46230.00141414352</v>
+        <v>46230.16808081018</v>
       </c>
       <c r="E250" s="6" t="s">
         <v>172</v>
@@ -15796,11 +15796,11 @@
         <v>502</v>
       </c>
       <c r="B251" s="8">
-        <v>46132.46737334491</v>
+        <v>46132.63404001157</v>
       </c>
       <c r="C251" s="9"/>
       <c r="D251" s="8">
-        <v>46230.001415543986</v>
+        <v>46230.16808221064</v>
       </c>
       <c r="E251" s="9" t="s">
         <v>172</v>
@@ -15847,11 +15847,11 @@
         <v>503</v>
       </c>
       <c r="B252" s="5">
-        <v>46132.46737993056</v>
+        <v>46132.63404659722</v>
       </c>
       <c r="C252" s="6"/>
       <c r="D252" s="5">
-        <v>46230.00141684028</v>
+        <v>46230.16808350694</v>
       </c>
       <c r="E252" s="6" t="s">
         <v>172</v>
@@ -15898,11 +15898,11 @@
         <v>504</v>
       </c>
       <c r="B253" s="8">
-        <v>46132.46738703703</v>
+        <v>46132.6340537037</v>
       </c>
       <c r="C253" s="9"/>
       <c r="D253" s="8">
-        <v>46230.00141810185</v>
+        <v>46230.16808476852</v>
       </c>
       <c r="E253" s="9" t="s">
         <v>172</v>
@@ -15949,11 +15949,11 @@
         <v>505</v>
       </c>
       <c r="B254" s="5">
-        <v>46132.46739449074</v>
+        <v>46132.63406115741</v>
       </c>
       <c r="C254" s="6"/>
       <c r="D254" s="5">
-        <v>46230.001419409724</v>
+        <v>46230.16808607639</v>
       </c>
       <c r="E254" s="6" t="s">
         <v>172</v>
@@ -16000,11 +16000,11 @@
         <v>506</v>
       </c>
       <c r="B255" s="8">
-        <v>46132.467399953704</v>
+        <v>46132.63406662037</v>
       </c>
       <c r="C255" s="9"/>
       <c r="D255" s="8">
-        <v>46230.00142075232</v>
+        <v>46230.16808741898</v>
       </c>
       <c r="E255" s="9" t="s">
         <v>172</v>
@@ -16051,11 +16051,11 @@
         <v>507</v>
       </c>
       <c r="B256" s="5">
-        <v>46132.46740572917</v>
+        <v>46132.634072395835</v>
       </c>
       <c r="C256" s="6"/>
       <c r="D256" s="5">
-        <v>46230.00142209491</v>
+        <v>46230.16808876157</v>
       </c>
       <c r="E256" s="6" t="s">
         <v>172</v>
@@ -16102,11 +16102,11 @@
         <v>508</v>
       </c>
       <c r="B257" s="8">
-        <v>46132.467410428246</v>
+        <v>46132.6340770949</v>
       </c>
       <c r="C257" s="9"/>
       <c r="D257" s="8">
-        <v>46230.00142339121</v>
+        <v>46230.16809005787</v>
       </c>
       <c r="E257" s="9" t="s">
         <v>172</v>
@@ -16153,11 +16153,11 @@
         <v>509</v>
       </c>
       <c r="B258" s="5">
-        <v>46132.46741611111</v>
+        <v>46132.634082777775</v>
       </c>
       <c r="C258" s="6"/>
       <c r="D258" s="5">
-        <v>46230.00142475695</v>
+        <v>46230.168091423606</v>
       </c>
       <c r="E258" s="6" t="s">
         <v>172</v>
@@ -16204,11 +16204,11 @@
         <v>510</v>
       </c>
       <c r="B259" s="8">
-        <v>46132.46742232639</v>
+        <v>46132.63408899306</v>
       </c>
       <c r="C259" s="9"/>
       <c r="D259" s="8">
-        <v>46230.00142623842</v>
+        <v>46230.16809290509</v>
       </c>
       <c r="E259" s="9" t="s">
         <v>172</v>
@@ -16255,11 +16255,11 @@
         <v>511</v>
       </c>
       <c r="B260" s="5">
-        <v>46132.46742878472</v>
+        <v>46132.63409545139</v>
       </c>
       <c r="C260" s="6"/>
       <c r="D260" s="5">
-        <v>46230.00142747685</v>
+        <v>46230.16809414352</v>
       </c>
       <c r="E260" s="6" t="s">
         <v>172</v>
@@ -16306,11 +16306,11 @@
         <v>512</v>
       </c>
       <c r="B261" s="8">
-        <v>46132.46743421296</v>
+        <v>46132.63410087963</v>
       </c>
       <c r="C261" s="9"/>
       <c r="D261" s="8">
-        <v>46230.00142892361</v>
+        <v>46230.16809559028</v>
       </c>
       <c r="E261" s="9" t="s">
         <v>172</v>
@@ -16357,11 +16357,11 @@
         <v>513</v>
       </c>
       <c r="B262" s="5">
-        <v>46132.46744021991</v>
+        <v>46132.63410688657</v>
       </c>
       <c r="C262" s="6"/>
       <c r="D262" s="5">
-        <v>46230.00143019676</v>
+        <v>46230.168096863425</v>
       </c>
       <c r="E262" s="6" t="s">
         <v>172</v>
@@ -16408,11 +16408,11 @@
         <v>514</v>
       </c>
       <c r="B263" s="8">
-        <v>46132.467446678245</v>
+        <v>46132.6341133449</v>
       </c>
       <c r="C263" s="9"/>
       <c r="D263" s="8">
-        <v>46230.00143145834</v>
+        <v>46230.168098124996</v>
       </c>
       <c r="E263" s="9" t="s">
         <v>172</v>
@@ -16459,11 +16459,11 @@
         <v>515</v>
       </c>
       <c r="B264" s="5">
-        <v>46132.467452997684</v>
+        <v>46132.63411966435</v>
       </c>
       <c r="C264" s="6"/>
       <c r="D264" s="5">
-        <v>46230.001433310186</v>
+        <v>46230.16809997685</v>
       </c>
       <c r="E264" s="6" t="s">
         <v>172</v>
@@ -16510,11 +16510,11 @@
         <v>516</v>
       </c>
       <c r="B265" s="8">
-        <v>46132.42236523148</v>
+        <v>46132.58903189815</v>
       </c>
       <c r="C265" s="9"/>
       <c r="D265" s="8">
-        <v>46232.0306583912</v>
+        <v>46232.197325057874</v>
       </c>
       <c r="E265" s="9" t="s">
         <v>517</v>
@@ -16571,11 +16571,11 @@
         <v>519</v>
       </c>
       <c r="B266" s="5">
-        <v>46132.467562025464</v>
+        <v>46132.63422869213</v>
       </c>
       <c r="C266" s="6"/>
       <c r="D266" s="5">
-        <v>46231.00110548611</v>
+        <v>46231.16777215278</v>
       </c>
       <c r="E266" s="6" t="s">
         <v>172</v>
@@ -16622,11 +16622,11 @@
         <v>521</v>
       </c>
       <c r="B267" s="8">
-        <v>46132.467568252316</v>
+        <v>46132.63423491898</v>
       </c>
       <c r="C267" s="9"/>
       <c r="D267" s="8">
-        <v>46231.001107986114</v>
+        <v>46231.16777465278</v>
       </c>
       <c r="E267" s="9" t="s">
         <v>172</v>
@@ -16673,11 +16673,11 @@
         <v>522</v>
       </c>
       <c r="B268" s="5">
-        <v>46132.46757429398</v>
+        <v>46132.634240960644</v>
       </c>
       <c r="C268" s="6"/>
       <c r="D268" s="5">
-        <v>46231.001109282406</v>
+        <v>46231.16777594907</v>
       </c>
       <c r="E268" s="6" t="s">
         <v>172</v>
@@ -16724,11 +16724,11 @@
         <v>523</v>
       </c>
       <c r="B269" s="8">
-        <v>46132.467581226854</v>
+        <v>46132.63424789352</v>
       </c>
       <c r="C269" s="9"/>
       <c r="D269" s="8">
-        <v>46231.001110578705</v>
+        <v>46231.16777724537</v>
       </c>
       <c r="E269" s="9" t="s">
         <v>172</v>
@@ -16775,11 +16775,11 @@
         <v>524</v>
       </c>
       <c r="B270" s="5">
-        <v>46132.467587719904</v>
+        <v>46132.634254386576</v>
       </c>
       <c r="C270" s="6"/>
       <c r="D270" s="5">
-        <v>46231.00111182871</v>
+        <v>46231.16777849537</v>
       </c>
       <c r="E270" s="6" t="s">
         <v>172</v>
@@ -16826,11 +16826,11 @@
         <v>525</v>
       </c>
       <c r="B271" s="8">
-        <v>46132.46759414352</v>
+        <v>46132.634260810184</v>
       </c>
       <c r="C271" s="9"/>
       <c r="D271" s="8">
-        <v>46231.0011130787</v>
+        <v>46231.167779745374</v>
       </c>
       <c r="E271" s="9" t="s">
         <v>172</v>
@@ -16877,11 +16877,11 @@
         <v>526</v>
       </c>
       <c r="B272" s="5">
-        <v>46132.46760059027</v>
+        <v>46132.634267256944</v>
       </c>
       <c r="C272" s="6"/>
       <c r="D272" s="5">
-        <v>46231.00111430556</v>
+        <v>46231.16778097222</v>
       </c>
       <c r="E272" s="6" t="s">
         <v>172</v>
@@ -16928,11 +16928,11 @@
         <v>527</v>
       </c>
       <c r="B273" s="8">
-        <v>46132.46760456018</v>
+        <v>46132.63427122685</v>
       </c>
       <c r="C273" s="9"/>
       <c r="D273" s="8">
-        <v>46231.001115798616</v>
+        <v>46231.16778246527</v>
       </c>
       <c r="E273" s="9" t="s">
         <v>172</v>
@@ -16979,11 +16979,11 @@
         <v>529</v>
       </c>
       <c r="B274" s="5">
-        <v>46132.46760969907</v>
+        <v>46132.634276365745</v>
       </c>
       <c r="C274" s="6"/>
       <c r="D274" s="5">
-        <v>46231.00114303241</v>
+        <v>46231.16780969907</v>
       </c>
       <c r="E274" s="6" t="s">
         <v>172</v>
@@ -17030,11 +17030,11 @@
         <v>530</v>
       </c>
       <c r="B275" s="8">
-        <v>46132.46761432871</v>
+        <v>46132.63428099537</v>
       </c>
       <c r="C275" s="9"/>
       <c r="D275" s="8">
-        <v>46231.00114659722</v>
+        <v>46231.16781326389</v>
       </c>
       <c r="E275" s="9" t="s">
         <v>172</v>
@@ -17081,11 +17081,11 @@
         <v>531</v>
       </c>
       <c r="B276" s="5">
-        <v>46132.46761857639</v>
+        <v>46132.63428524305</v>
       </c>
       <c r="C276" s="6"/>
       <c r="D276" s="5">
-        <v>46231.00114782408</v>
+        <v>46231.16781449074</v>
       </c>
       <c r="E276" s="6" t="s">
         <v>172</v>
@@ -17132,11 +17132,11 @@
         <v>532</v>
       </c>
       <c r="B277" s="8">
-        <v>46132.46762436343</v>
+        <v>46132.63429103009</v>
       </c>
       <c r="C277" s="9"/>
       <c r="D277" s="8">
-        <v>46231.00114923611</v>
+        <v>46231.16781590278</v>
       </c>
       <c r="E277" s="9" t="s">
         <v>172</v>
@@ -17183,11 +17183,11 @@
         <v>533</v>
       </c>
       <c r="B278" s="5">
-        <v>46132.46762856482</v>
+        <v>46132.63429523148</v>
       </c>
       <c r="C278" s="6"/>
       <c r="D278" s="5">
-        <v>46231.00115091435</v>
+        <v>46231.16781758102</v>
       </c>
       <c r="E278" s="6" t="s">
         <v>172</v>
@@ -17234,11 +17234,11 @@
         <v>534</v>
       </c>
       <c r="B279" s="8">
-        <v>46132.4676369213</v>
+        <v>46132.63430358796</v>
       </c>
       <c r="C279" s="9"/>
       <c r="D279" s="8">
-        <v>46231.00115221065</v>
+        <v>46231.167818877315</v>
       </c>
       <c r="E279" s="9" t="s">
         <v>172</v>
@@ -17285,11 +17285,11 @@
         <v>535</v>
       </c>
       <c r="B280" s="5">
-        <v>46132.46764481482</v>
+        <v>46132.63431148148</v>
       </c>
       <c r="C280" s="6"/>
       <c r="D280" s="5">
-        <v>46231.001153414356</v>
+        <v>46231.16782008102</v>
       </c>
       <c r="E280" s="6" t="s">
         <v>172</v>
@@ -17336,11 +17336,11 @@
         <v>536</v>
       </c>
       <c r="B281" s="8">
-        <v>46132.467709965276</v>
+        <v>46132.63437663195</v>
       </c>
       <c r="C281" s="9"/>
       <c r="D281" s="8">
-        <v>46231.00115471065</v>
+        <v>46231.16782137731</v>
       </c>
       <c r="E281" s="9" t="s">
         <v>172</v>
@@ -17387,11 +17387,11 @@
         <v>537</v>
       </c>
       <c r="B282" s="5">
-        <v>46132.4223709375</v>
+        <v>46132.589037604164</v>
       </c>
       <c r="C282" s="6"/>
       <c r="D282" s="5">
-        <v>46133.425690034725</v>
+        <v>46133.59235670139</v>
       </c>
       <c r="E282" s="6" t="s">
         <v>538</v>
@@ -17434,11 +17434,11 @@
         <v>539</v>
       </c>
       <c r="B283" s="8">
-        <v>46132.42237400463</v>
+        <v>46132.5890406713</v>
       </c>
       <c r="C283" s="9"/>
       <c r="D283" s="8">
-        <v>46241.00835421296</v>
+        <v>46241.17502087963</v>
       </c>
       <c r="E283" s="9" t="s">
         <v>540</v>
@@ -17497,11 +17497,11 @@
         <v>544</v>
       </c>
       <c r="B284" s="5">
-        <v>46132.42237892361</v>
+        <v>46132.58904559028</v>
       </c>
       <c r="C284" s="6"/>
       <c r="D284" s="5">
-        <v>46241.00835390046</v>
+        <v>46241.17502056713</v>
       </c>
       <c r="E284" s="6" t="s">
         <v>545</v>

--- a/data/50001541 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001541 - XEMORTIZ MINERA FRISCO.xlsx
@@ -6297,7 +6297,7 @@
         <v>46196.69197697917</v>
       </c>
       <c r="D72" s="5">
-        <v>46229.54909206019</v>
+        <v>46260.58108960648</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>238</v>
@@ -8476,7 +8476,7 @@
         <v>46205.49151155092</v>
       </c>
       <c r="D111" s="8">
-        <v>46229.98726652778</v>
+        <v>46260.58113824074</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>305</v>
@@ -8526,8 +8526,8 @@
       <c r="T111" s="9">
         <v>1</v>
       </c>
-      <c r="U111" s="12" t="s">
-        <v>85</v>
+      <c r="U111" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
@@ -9419,7 +9419,7 @@
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46237.53575319445</v>
+        <v>46260.58116327546</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>327</v>
@@ -9467,8 +9467,8 @@
       <c r="T128" s="6">
         <v>0</v>
       </c>
-      <c r="U128" s="12" t="s">
-        <v>85</v>
+      <c r="U128" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
@@ -10306,7 +10306,7 @@
       </c>
       <c r="C145" s="9"/>
       <c r="D145" s="8">
-        <v>46237.535776296296</v>
+        <v>46260.5811917824</v>
       </c>
       <c r="E145" s="9" t="s">
         <v>352</v>
@@ -10354,8 +10354,8 @@
       <c r="T145" s="9">
         <v>0</v>
       </c>
-      <c r="U145" s="12" t="s">
-        <v>85</v>
+      <c r="U145" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
@@ -11193,7 +11193,7 @@
       </c>
       <c r="C162" s="6"/>
       <c r="D162" s="5">
-        <v>46237.53579454861</v>
+        <v>46260.58121265046</v>
       </c>
       <c r="E162" s="6" t="s">
         <v>373</v>
@@ -11241,8 +11241,8 @@
       <c r="T162" s="6">
         <v>0</v>
       </c>
-      <c r="U162" s="12" t="s">
-        <v>85</v>
+      <c r="U162" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="163" spans="1:21" x14ac:dyDescent="0.25">
@@ -12080,7 +12080,7 @@
       </c>
       <c r="C179" s="9"/>
       <c r="D179" s="8">
-        <v>46237.53581487268</v>
+        <v>46260.58130074074</v>
       </c>
       <c r="E179" s="9" t="s">
         <v>395</v>
@@ -12957,7 +12957,7 @@
       </c>
       <c r="C196" s="6"/>
       <c r="D196" s="5">
-        <v>46229.86452372685</v>
+        <v>46260.581324178245</v>
       </c>
       <c r="E196" s="6" t="s">
         <v>430</v>
@@ -13005,8 +13005,8 @@
       <c r="T196" s="6">
         <v>0</v>
       </c>
-      <c r="U196" s="10" t="s">
-        <v>97</v>
+      <c r="U196" s="12" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="197" spans="1:21" x14ac:dyDescent="0.25">
@@ -15635,7 +15635,7 @@
       </c>
       <c r="C248" s="6"/>
       <c r="D248" s="5">
-        <v>46231.18365072917</v>
+        <v>46260.58139493056</v>
       </c>
       <c r="E248" s="6" t="s">
         <v>496</v>
@@ -15685,8 +15685,8 @@
       <c r="T248" s="6">
         <v>0</v>
       </c>
-      <c r="U248" s="10" t="s">
-        <v>97</v>
+      <c r="U248" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="249" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001541 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001541 - XEMORTIZ MINERA FRISCO.xlsx
@@ -2655,7 +2655,7 @@
         <v>46198.65467643518</v>
       </c>
       <c r="D10" s="5">
-        <v>46198.65469435185</v>
+        <v>46264.463179178245</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>44</v>
@@ -6297,7 +6297,7 @@
         <v>46196.69197697917</v>
       </c>
       <c r="D72" s="5">
-        <v>46260.58108960648</v>
+        <v>46264.05806130787</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>238</v>
